--- a/04-Bieu-Mau/04-FRM-400/FRM-411_Outsourced_Process_Incoming_Verification.xlsx
+++ b/04-Bieu-Mau/04-FRM-400/FRM-411_Outsourced_Process_Incoming_Verification.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="79">
+  <fonts count="81">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -468,6 +468,16 @@
       <color rgb="00334155"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color theme="1"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="47">
     <fill>
@@ -702,7 +712,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="271">
+  <borders count="293">
     <border>
       <left/>
       <right/>
@@ -3621,11 +3631,227 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="337">
+  <cellXfs count="414">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -4361,6 +4587,189 @@
     <xf numFmtId="0" fontId="53" fillId="3" borderId="130" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="272" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="273" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="275" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="276" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="276" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="277" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="278" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="279" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="277" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="275" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="276" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="276" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="276" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="273" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="281" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="276" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="282" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="281" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="281" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="281" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="281" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="275" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="276" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="280" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="277" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="283" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="7" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="3" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="284" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="287" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="286" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="291" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="292" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="289" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="287" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="284" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="285" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="289" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="290" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="285" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="288" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="284" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="287" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="286" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="291" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="292" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="289" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -4434,41 +4843,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>161925</colOff>
-      <row>0</row>
-      <rowOff>314325</rowOff>
-    </from>
-    <ext cx="1123950" cy="323850"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="/xl/media/image1.png"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4729,1734 +5103,2027 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="329">
-      <c r="A1" s="267" t="n"/>
-      <c r="B1" s="320" t="n"/>
-      <c r="C1" s="320" t="n"/>
-      <c r="D1" s="320" t="n"/>
-      <c r="E1" s="320" t="n"/>
-      <c r="F1" s="320" t="n"/>
-      <c r="G1" s="320" t="n"/>
-      <c r="H1" s="320" t="n"/>
-      <c r="I1" s="269" t="inlineStr">
+      <c r="A1" s="337" t="n"/>
+      <c r="B1" s="408" t="n"/>
+      <c r="C1" s="408" t="n"/>
+      <c r="D1" s="408" t="n"/>
+      <c r="E1" s="408" t="n"/>
+      <c r="F1" s="408" t="n"/>
+      <c r="G1" s="408" t="n"/>
+      <c r="H1" s="408" t="n"/>
+      <c r="I1" s="339" t="inlineStr">
         <is>
           <t>Outsourced Process Incoming Verification</t>
         </is>
       </c>
-      <c r="J1" s="320" t="n"/>
-      <c r="K1" s="320" t="n"/>
-      <c r="L1" s="320" t="n"/>
-      <c r="M1" s="320" t="n"/>
-      <c r="N1" s="320" t="n"/>
-      <c r="O1" s="320" t="n"/>
-      <c r="P1" s="320" t="n"/>
-      <c r="Q1" s="320" t="n"/>
-      <c r="R1" s="320" t="n"/>
-      <c r="S1" s="320" t="n"/>
-      <c r="T1" s="320" t="n"/>
-      <c r="U1" s="320" t="n"/>
-      <c r="V1" s="320" t="n"/>
-      <c r="W1" s="320" t="n"/>
-      <c r="X1" s="320" t="n"/>
-      <c r="Y1" s="320" t="n"/>
-      <c r="Z1" s="320" t="n"/>
-      <c r="AA1" s="320" t="n"/>
-      <c r="AB1" s="320" t="n"/>
-      <c r="AC1" s="320" t="n"/>
-      <c r="AD1" s="320" t="n"/>
-      <c r="AE1" s="270" t="n"/>
-      <c r="AF1" s="317" t="n"/>
-      <c r="AG1" s="317" t="n"/>
-      <c r="AH1" s="318" t="n"/>
-      <c r="AI1" s="273" t="inlineStr">
+      <c r="J1" s="408" t="n"/>
+      <c r="K1" s="408" t="n"/>
+      <c r="L1" s="408" t="n"/>
+      <c r="M1" s="408" t="n"/>
+      <c r="N1" s="408" t="n"/>
+      <c r="O1" s="408" t="n"/>
+      <c r="P1" s="408" t="n"/>
+      <c r="Q1" s="408" t="n"/>
+      <c r="R1" s="408" t="n"/>
+      <c r="S1" s="408" t="n"/>
+      <c r="T1" s="408" t="n"/>
+      <c r="U1" s="408" t="n"/>
+      <c r="V1" s="408" t="n"/>
+      <c r="W1" s="408" t="n"/>
+      <c r="X1" s="408" t="n"/>
+      <c r="Y1" s="408" t="n"/>
+      <c r="Z1" s="408" t="n"/>
+      <c r="AA1" s="408" t="n"/>
+      <c r="AB1" s="408" t="n"/>
+      <c r="AC1" s="408" t="n"/>
+      <c r="AD1" s="408" t="n"/>
+      <c r="AE1" s="340" t="n"/>
+      <c r="AF1" s="409" t="n"/>
+      <c r="AG1" s="409" t="n"/>
+      <c r="AH1" s="410" t="n"/>
+      <c r="AI1" s="343" t="inlineStr">
         <is>
           <t>FRM-411</t>
         </is>
       </c>
-      <c r="AJ1" s="317" t="n"/>
-      <c r="AK1" s="317" t="n"/>
-      <c r="AL1" s="317" t="n"/>
-      <c r="AM1" s="317" t="n"/>
-      <c r="AN1" s="319" t="n"/>
+      <c r="AJ1" s="409" t="n"/>
+      <c r="AK1" s="409" t="n"/>
+      <c r="AL1" s="409" t="n"/>
+      <c r="AM1" s="409" t="n"/>
+      <c r="AN1" s="410" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1" s="329">
-      <c r="A2" s="328" t="n"/>
-      <c r="I2" s="328" t="n"/>
-      <c r="AE2" s="270" t="n"/>
-      <c r="AF2" s="317" t="n"/>
-      <c r="AG2" s="317" t="n"/>
-      <c r="AH2" s="318" t="n"/>
-      <c r="AI2" s="273" t="inlineStr">
+      <c r="A2" s="411" t="n"/>
+      <c r="I2" s="411" t="n"/>
+      <c r="AE2" s="340" t="n"/>
+      <c r="AF2" s="409" t="n"/>
+      <c r="AG2" s="409" t="n"/>
+      <c r="AH2" s="410" t="n"/>
+      <c r="AI2" s="343" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AJ2" s="317" t="n"/>
-      <c r="AK2" s="317" t="n"/>
-      <c r="AL2" s="317" t="n"/>
-      <c r="AM2" s="317" t="n"/>
-      <c r="AN2" s="319" t="n"/>
+      <c r="AJ2" s="409" t="n"/>
+      <c r="AK2" s="409" t="n"/>
+      <c r="AL2" s="409" t="n"/>
+      <c r="AM2" s="409" t="n"/>
+      <c r="AN2" s="410" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1" s="329">
-      <c r="A3" s="328" t="n"/>
-      <c r="I3" s="279" t="n"/>
-      <c r="J3" s="322" t="n"/>
-      <c r="K3" s="322" t="n"/>
-      <c r="L3" s="322" t="n"/>
-      <c r="M3" s="322" t="n"/>
-      <c r="N3" s="322" t="n"/>
-      <c r="O3" s="322" t="n"/>
-      <c r="P3" s="322" t="n"/>
-      <c r="Q3" s="322" t="n"/>
-      <c r="R3" s="322" t="n"/>
-      <c r="S3" s="322" t="n"/>
-      <c r="T3" s="322" t="n"/>
-      <c r="U3" s="322" t="n"/>
-      <c r="V3" s="322" t="n"/>
-      <c r="W3" s="322" t="n"/>
-      <c r="X3" s="322" t="n"/>
-      <c r="Y3" s="322" t="n"/>
-      <c r="Z3" s="322" t="n"/>
-      <c r="AA3" s="322" t="n"/>
-      <c r="AB3" s="322" t="n"/>
-      <c r="AC3" s="322" t="n"/>
-      <c r="AD3" s="322" t="n"/>
-      <c r="AE3" s="270" t="n"/>
-      <c r="AF3" s="317" t="n"/>
-      <c r="AG3" s="317" t="n"/>
-      <c r="AH3" s="318" t="n"/>
-      <c r="AI3" s="273" t="inlineStr">
+      <c r="A3" s="411" t="n"/>
+      <c r="I3" s="412" t="n"/>
+      <c r="J3" s="413" t="n"/>
+      <c r="K3" s="413" t="n"/>
+      <c r="L3" s="413" t="n"/>
+      <c r="M3" s="413" t="n"/>
+      <c r="N3" s="413" t="n"/>
+      <c r="O3" s="413" t="n"/>
+      <c r="P3" s="413" t="n"/>
+      <c r="Q3" s="413" t="n"/>
+      <c r="R3" s="413" t="n"/>
+      <c r="S3" s="413" t="n"/>
+      <c r="T3" s="413" t="n"/>
+      <c r="U3" s="413" t="n"/>
+      <c r="V3" s="413" t="n"/>
+      <c r="W3" s="413" t="n"/>
+      <c r="X3" s="413" t="n"/>
+      <c r="Y3" s="413" t="n"/>
+      <c r="Z3" s="413" t="n"/>
+      <c r="AA3" s="413" t="n"/>
+      <c r="AB3" s="413" t="n"/>
+      <c r="AC3" s="413" t="n"/>
+      <c r="AD3" s="413" t="n"/>
+      <c r="AE3" s="340" t="n"/>
+      <c r="AF3" s="409" t="n"/>
+      <c r="AG3" s="409" t="n"/>
+      <c r="AH3" s="410" t="n"/>
+      <c r="AI3" s="343" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AJ3" s="317" t="n"/>
-      <c r="AK3" s="317" t="n"/>
-      <c r="AL3" s="317" t="n"/>
-      <c r="AM3" s="317" t="n"/>
-      <c r="AN3" s="319" t="n"/>
+      <c r="AJ3" s="409" t="n"/>
+      <c r="AK3" s="409" t="n"/>
+      <c r="AL3" s="409" t="n"/>
+      <c r="AM3" s="409" t="n"/>
+      <c r="AN3" s="410" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1" s="329">
-      <c r="A4" s="328" t="n"/>
-      <c r="I4" s="17" t="inlineStr">
+      <c r="A4" s="411" t="n"/>
+      <c r="I4" s="348" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AE4" s="270" t="n"/>
-      <c r="AF4" s="317" t="n"/>
-      <c r="AG4" s="317" t="n"/>
-      <c r="AH4" s="318" t="n"/>
-      <c r="AI4" s="273" t="inlineStr">
+      <c r="AE4" s="340" t="n"/>
+      <c r="AF4" s="409" t="n"/>
+      <c r="AG4" s="409" t="n"/>
+      <c r="AH4" s="410" t="n"/>
+      <c r="AI4" s="343" t="inlineStr">
         <is>
           <t>Purchasing + QA</t>
         </is>
       </c>
-      <c r="AJ4" s="317" t="n"/>
-      <c r="AK4" s="317" t="n"/>
-      <c r="AL4" s="317" t="n"/>
-      <c r="AM4" s="317" t="n"/>
-      <c r="AN4" s="319" t="n"/>
+      <c r="AJ4" s="409" t="n"/>
+      <c r="AK4" s="409" t="n"/>
+      <c r="AL4" s="409" t="n"/>
+      <c r="AM4" s="409" t="n"/>
+      <c r="AN4" s="410" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1" s="329">
-      <c r="A5" s="331" t="n"/>
-      <c r="B5" s="332" t="n"/>
-      <c r="C5" s="332" t="n"/>
-      <c r="D5" s="332" t="n"/>
-      <c r="E5" s="332" t="n"/>
-      <c r="F5" s="332" t="n"/>
-      <c r="G5" s="332" t="n"/>
-      <c r="H5" s="332" t="n"/>
-      <c r="I5" s="20" t="inlineStr">
+      <c r="A5" s="412" t="n"/>
+      <c r="B5" s="413" t="n"/>
+      <c r="C5" s="413" t="n"/>
+      <c r="D5" s="413" t="n"/>
+      <c r="E5" s="413" t="n"/>
+      <c r="F5" s="413" t="n"/>
+      <c r="G5" s="413" t="n"/>
+      <c r="H5" s="413" t="n"/>
+      <c r="I5" s="349" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="J5" s="332" t="n"/>
-      <c r="K5" s="332" t="n"/>
-      <c r="L5" s="332" t="n"/>
-      <c r="M5" s="332" t="n"/>
-      <c r="N5" s="332" t="n"/>
-      <c r="O5" s="332" t="n"/>
-      <c r="P5" s="332" t="n"/>
-      <c r="Q5" s="332" t="n"/>
-      <c r="R5" s="332" t="n"/>
-      <c r="S5" s="332" t="n"/>
-      <c r="T5" s="332" t="n"/>
-      <c r="U5" s="332" t="n"/>
-      <c r="V5" s="332" t="n"/>
-      <c r="W5" s="332" t="n"/>
-      <c r="X5" s="332" t="n"/>
-      <c r="Y5" s="332" t="n"/>
-      <c r="Z5" s="332" t="n"/>
-      <c r="AA5" s="332" t="n"/>
-      <c r="AB5" s="332" t="n"/>
-      <c r="AC5" s="332" t="n"/>
-      <c r="AD5" s="332" t="n"/>
-      <c r="AE5" s="270" t="n"/>
-      <c r="AF5" s="317" t="n"/>
-      <c r="AG5" s="317" t="n"/>
-      <c r="AH5" s="318" t="n"/>
-      <c r="AI5" s="273" t="inlineStr">
+      <c r="J5" s="413" t="n"/>
+      <c r="K5" s="413" t="n"/>
+      <c r="L5" s="413" t="n"/>
+      <c r="M5" s="413" t="n"/>
+      <c r="N5" s="413" t="n"/>
+      <c r="O5" s="413" t="n"/>
+      <c r="P5" s="413" t="n"/>
+      <c r="Q5" s="413" t="n"/>
+      <c r="R5" s="413" t="n"/>
+      <c r="S5" s="413" t="n"/>
+      <c r="T5" s="413" t="n"/>
+      <c r="U5" s="413" t="n"/>
+      <c r="V5" s="413" t="n"/>
+      <c r="W5" s="413" t="n"/>
+      <c r="X5" s="413" t="n"/>
+      <c r="Y5" s="413" t="n"/>
+      <c r="Z5" s="413" t="n"/>
+      <c r="AA5" s="413" t="n"/>
+      <c r="AB5" s="413" t="n"/>
+      <c r="AC5" s="413" t="n"/>
+      <c r="AD5" s="413" t="n"/>
+      <c r="AE5" s="340" t="n"/>
+      <c r="AF5" s="409" t="n"/>
+      <c r="AG5" s="409" t="n"/>
+      <c r="AH5" s="410" t="n"/>
+      <c r="AI5" s="343" t="inlineStr">
         <is>
           <t>General Manager</t>
         </is>
       </c>
-      <c r="AJ5" s="317" t="n"/>
-      <c r="AK5" s="317" t="n"/>
-      <c r="AL5" s="317" t="n"/>
-      <c r="AM5" s="317" t="n"/>
-      <c r="AN5" s="319" t="n"/>
+      <c r="AJ5" s="409" t="n"/>
+      <c r="AK5" s="409" t="n"/>
+      <c r="AL5" s="409" t="n"/>
+      <c r="AM5" s="409" t="n"/>
+      <c r="AN5" s="410" t="n"/>
     </row>
     <row r="6" ht="4" customHeight="1" s="329">
-      <c r="A6" s="25" t="n"/>
+      <c r="A6" s="350" t="n"/>
+      <c r="B6" s="407" t="n"/>
+      <c r="C6" s="407" t="n"/>
+      <c r="D6" s="407" t="n"/>
+      <c r="E6" s="407" t="n"/>
+      <c r="F6" s="407" t="n"/>
+      <c r="G6" s="407" t="n"/>
+      <c r="H6" s="407" t="n"/>
+      <c r="I6" s="407" t="n"/>
+      <c r="J6" s="407" t="n"/>
+      <c r="K6" s="407" t="n"/>
+      <c r="L6" s="407" t="n"/>
+      <c r="M6" s="407" t="n"/>
+      <c r="N6" s="407" t="n"/>
+      <c r="O6" s="407" t="n"/>
+      <c r="P6" s="407" t="n"/>
+      <c r="Q6" s="407" t="n"/>
+      <c r="R6" s="407" t="n"/>
+      <c r="S6" s="407" t="n"/>
+      <c r="T6" s="407" t="n"/>
+      <c r="U6" s="407" t="n"/>
+      <c r="V6" s="407" t="n"/>
+      <c r="W6" s="407" t="n"/>
+      <c r="X6" s="407" t="n"/>
+      <c r="Y6" s="407" t="n"/>
+      <c r="Z6" s="407" t="n"/>
+      <c r="AA6" s="407" t="n"/>
+      <c r="AB6" s="407" t="n"/>
+      <c r="AC6" s="407" t="n"/>
+      <c r="AD6" s="407" t="n"/>
+      <c r="AE6" s="407" t="n"/>
+      <c r="AF6" s="407" t="n"/>
+      <c r="AG6" s="407" t="n"/>
+      <c r="AH6" s="407" t="n"/>
+      <c r="AI6" s="407" t="n"/>
+      <c r="AJ6" s="407" t="n"/>
+      <c r="AK6" s="407" t="n"/>
+      <c r="AL6" s="407" t="n"/>
+      <c r="AM6" s="407" t="n"/>
+      <c r="AN6" s="407" t="n"/>
     </row>
     <row r="7" ht="17" customHeight="1" s="329">
-      <c r="A7" s="284" t="inlineStr">
+      <c r="A7" s="351" t="inlineStr">
         <is>
           <t xml:space="preserve">  1. REFERENCE INFORMATION</t>
         </is>
       </c>
-      <c r="B7" s="285" t="n"/>
-      <c r="C7" s="285" t="n"/>
-      <c r="D7" s="285" t="n"/>
-      <c r="E7" s="285" t="n"/>
-      <c r="F7" s="285" t="n"/>
-      <c r="G7" s="285" t="n"/>
-      <c r="H7" s="285" t="n"/>
-      <c r="I7" s="285" t="n"/>
-      <c r="J7" s="285" t="n"/>
-      <c r="K7" s="285" t="n"/>
-      <c r="L7" s="285" t="n"/>
-      <c r="M7" s="285" t="n"/>
-      <c r="N7" s="285" t="n"/>
-      <c r="O7" s="285" t="n"/>
-      <c r="P7" s="285" t="n"/>
-      <c r="Q7" s="285" t="n"/>
-      <c r="R7" s="285" t="n"/>
-      <c r="S7" s="285" t="n"/>
-      <c r="T7" s="285" t="n"/>
-      <c r="U7" s="285" t="n"/>
-      <c r="V7" s="285" t="n"/>
-      <c r="W7" s="285" t="n"/>
-      <c r="X7" s="285" t="n"/>
-      <c r="Y7" s="285" t="n"/>
-      <c r="Z7" s="285" t="n"/>
-      <c r="AA7" s="285" t="n"/>
-      <c r="AB7" s="285" t="n"/>
-      <c r="AC7" s="285" t="n"/>
-      <c r="AD7" s="285" t="n"/>
-      <c r="AE7" s="285" t="n"/>
-      <c r="AF7" s="285" t="n"/>
-      <c r="AG7" s="285" t="n"/>
-      <c r="AH7" s="285" t="n"/>
-      <c r="AI7" s="285" t="n"/>
-      <c r="AJ7" s="285" t="n"/>
-      <c r="AK7" s="285" t="n"/>
-      <c r="AL7" s="285" t="n"/>
-      <c r="AM7" s="285" t="n"/>
-      <c r="AN7" s="286" t="n"/>
+      <c r="B7" s="409" t="n"/>
+      <c r="C7" s="409" t="n"/>
+      <c r="D7" s="409" t="n"/>
+      <c r="E7" s="409" t="n"/>
+      <c r="F7" s="409" t="n"/>
+      <c r="G7" s="409" t="n"/>
+      <c r="H7" s="409" t="n"/>
+      <c r="I7" s="409" t="n"/>
+      <c r="J7" s="409" t="n"/>
+      <c r="K7" s="409" t="n"/>
+      <c r="L7" s="409" t="n"/>
+      <c r="M7" s="409" t="n"/>
+      <c r="N7" s="409" t="n"/>
+      <c r="O7" s="409" t="n"/>
+      <c r="P7" s="409" t="n"/>
+      <c r="Q7" s="409" t="n"/>
+      <c r="R7" s="409" t="n"/>
+      <c r="S7" s="409" t="n"/>
+      <c r="T7" s="409" t="n"/>
+      <c r="U7" s="409" t="n"/>
+      <c r="V7" s="409" t="n"/>
+      <c r="W7" s="409" t="n"/>
+      <c r="X7" s="409" t="n"/>
+      <c r="Y7" s="409" t="n"/>
+      <c r="Z7" s="409" t="n"/>
+      <c r="AA7" s="409" t="n"/>
+      <c r="AB7" s="409" t="n"/>
+      <c r="AC7" s="409" t="n"/>
+      <c r="AD7" s="409" t="n"/>
+      <c r="AE7" s="409" t="n"/>
+      <c r="AF7" s="409" t="n"/>
+      <c r="AG7" s="409" t="n"/>
+      <c r="AH7" s="409" t="n"/>
+      <c r="AI7" s="409" t="n"/>
+      <c r="AJ7" s="409" t="n"/>
+      <c r="AK7" s="409" t="n"/>
+      <c r="AL7" s="409" t="n"/>
+      <c r="AM7" s="409" t="n"/>
+      <c r="AN7" s="410" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1" s="329">
-      <c r="A8" s="287" t="inlineStr">
+      <c r="A8" s="352" t="inlineStr">
         <is>
           <t>Incoming Verification ID</t>
         </is>
       </c>
-      <c r="B8" s="317" t="n"/>
-      <c r="C8" s="317" t="n"/>
-      <c r="D8" s="317" t="n"/>
-      <c r="E8" s="317" t="n"/>
-      <c r="F8" s="317" t="n"/>
-      <c r="G8" s="318" t="n"/>
-      <c r="H8" s="288" t="n"/>
-      <c r="I8" s="317" t="n"/>
-      <c r="J8" s="317" t="n"/>
-      <c r="K8" s="317" t="n"/>
-      <c r="L8" s="317" t="n"/>
-      <c r="M8" s="317" t="n"/>
-      <c r="N8" s="317" t="n"/>
-      <c r="O8" s="317" t="n"/>
-      <c r="P8" s="317" t="n"/>
-      <c r="Q8" s="317" t="n"/>
-      <c r="R8" s="317" t="n"/>
-      <c r="S8" s="317" t="n"/>
-      <c r="T8" s="318" t="n"/>
-      <c r="U8" s="289" t="inlineStr">
+      <c r="B8" s="397" t="n"/>
+      <c r="C8" s="397" t="n"/>
+      <c r="D8" s="397" t="n"/>
+      <c r="E8" s="397" t="n"/>
+      <c r="F8" s="397" t="n"/>
+      <c r="G8" s="398" t="n"/>
+      <c r="H8" s="355" t="n"/>
+      <c r="I8" s="397" t="n"/>
+      <c r="J8" s="397" t="n"/>
+      <c r="K8" s="397" t="n"/>
+      <c r="L8" s="397" t="n"/>
+      <c r="M8" s="397" t="n"/>
+      <c r="N8" s="397" t="n"/>
+      <c r="O8" s="397" t="n"/>
+      <c r="P8" s="397" t="n"/>
+      <c r="Q8" s="397" t="n"/>
+      <c r="R8" s="397" t="n"/>
+      <c r="S8" s="397" t="n"/>
+      <c r="T8" s="398" t="n"/>
+      <c r="U8" s="356" t="inlineStr">
         <is>
           <t>Disposition Status</t>
         </is>
       </c>
-      <c r="V8" s="317" t="n"/>
-      <c r="W8" s="317" t="n"/>
-      <c r="X8" s="317" t="n"/>
-      <c r="Y8" s="317" t="n"/>
-      <c r="Z8" s="317" t="n"/>
-      <c r="AA8" s="318" t="n"/>
-      <c r="AB8" s="290" t="n"/>
-      <c r="AC8" s="317" t="n"/>
-      <c r="AD8" s="317" t="n"/>
-      <c r="AE8" s="317" t="n"/>
-      <c r="AF8" s="317" t="n"/>
-      <c r="AG8" s="317" t="n"/>
-      <c r="AH8" s="317" t="n"/>
-      <c r="AI8" s="317" t="n"/>
-      <c r="AJ8" s="317" t="n"/>
-      <c r="AK8" s="317" t="n"/>
-      <c r="AL8" s="317" t="n"/>
-      <c r="AM8" s="317" t="n"/>
-      <c r="AN8" s="319" t="n"/>
+      <c r="V8" s="397" t="n"/>
+      <c r="W8" s="397" t="n"/>
+      <c r="X8" s="397" t="n"/>
+      <c r="Y8" s="397" t="n"/>
+      <c r="Z8" s="397" t="n"/>
+      <c r="AA8" s="398" t="n"/>
+      <c r="AB8" s="355" t="n"/>
+      <c r="AC8" s="397" t="n"/>
+      <c r="AD8" s="397" t="n"/>
+      <c r="AE8" s="397" t="n"/>
+      <c r="AF8" s="397" t="n"/>
+      <c r="AG8" s="397" t="n"/>
+      <c r="AH8" s="397" t="n"/>
+      <c r="AI8" s="397" t="n"/>
+      <c r="AJ8" s="397" t="n"/>
+      <c r="AK8" s="397" t="n"/>
+      <c r="AL8" s="397" t="n"/>
+      <c r="AM8" s="397" t="n"/>
+      <c r="AN8" s="398" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1" s="329">
-      <c r="A9" s="287" t="inlineStr">
+      <c r="A9" s="352" t="inlineStr">
         <is>
           <t>Supplier / Processor / Cert</t>
         </is>
       </c>
-      <c r="B9" s="317" t="n"/>
-      <c r="C9" s="317" t="n"/>
-      <c r="D9" s="317" t="n"/>
-      <c r="E9" s="317" t="n"/>
-      <c r="F9" s="317" t="n"/>
-      <c r="G9" s="318" t="n"/>
-      <c r="H9" s="288" t="n"/>
-      <c r="I9" s="317" t="n"/>
-      <c r="J9" s="317" t="n"/>
-      <c r="K9" s="317" t="n"/>
-      <c r="L9" s="317" t="n"/>
-      <c r="M9" s="317" t="n"/>
-      <c r="N9" s="317" t="n"/>
-      <c r="O9" s="317" t="n"/>
-      <c r="P9" s="317" t="n"/>
-      <c r="Q9" s="317" t="n"/>
-      <c r="R9" s="317" t="n"/>
-      <c r="S9" s="317" t="n"/>
-      <c r="T9" s="318" t="n"/>
-      <c r="U9" s="289" t="inlineStr">
+      <c r="B9" s="397" t="n"/>
+      <c r="C9" s="397" t="n"/>
+      <c r="D9" s="397" t="n"/>
+      <c r="E9" s="397" t="n"/>
+      <c r="F9" s="397" t="n"/>
+      <c r="G9" s="398" t="n"/>
+      <c r="H9" s="355" t="n"/>
+      <c r="I9" s="397" t="n"/>
+      <c r="J9" s="397" t="n"/>
+      <c r="K9" s="397" t="n"/>
+      <c r="L9" s="397" t="n"/>
+      <c r="M9" s="397" t="n"/>
+      <c r="N9" s="397" t="n"/>
+      <c r="O9" s="397" t="n"/>
+      <c r="P9" s="397" t="n"/>
+      <c r="Q9" s="397" t="n"/>
+      <c r="R9" s="397" t="n"/>
+      <c r="S9" s="397" t="n"/>
+      <c r="T9" s="398" t="n"/>
+      <c r="U9" s="356" t="inlineStr">
         <is>
           <t>PO / Cert / Lot Ref</t>
         </is>
       </c>
-      <c r="V9" s="317" t="n"/>
-      <c r="W9" s="317" t="n"/>
-      <c r="X9" s="317" t="n"/>
-      <c r="Y9" s="317" t="n"/>
-      <c r="Z9" s="317" t="n"/>
-      <c r="AA9" s="318" t="n"/>
-      <c r="AB9" s="290" t="n"/>
-      <c r="AC9" s="317" t="n"/>
-      <c r="AD9" s="317" t="n"/>
-      <c r="AE9" s="317" t="n"/>
-      <c r="AF9" s="317" t="n"/>
-      <c r="AG9" s="317" t="n"/>
-      <c r="AH9" s="317" t="n"/>
-      <c r="AI9" s="317" t="n"/>
-      <c r="AJ9" s="317" t="n"/>
-      <c r="AK9" s="317" t="n"/>
-      <c r="AL9" s="317" t="n"/>
-      <c r="AM9" s="317" t="n"/>
-      <c r="AN9" s="319" t="n"/>
+      <c r="V9" s="397" t="n"/>
+      <c r="W9" s="397" t="n"/>
+      <c r="X9" s="397" t="n"/>
+      <c r="Y9" s="397" t="n"/>
+      <c r="Z9" s="397" t="n"/>
+      <c r="AA9" s="398" t="n"/>
+      <c r="AB9" s="355" t="n"/>
+      <c r="AC9" s="397" t="n"/>
+      <c r="AD9" s="397" t="n"/>
+      <c r="AE9" s="397" t="n"/>
+      <c r="AF9" s="397" t="n"/>
+      <c r="AG9" s="397" t="n"/>
+      <c r="AH9" s="397" t="n"/>
+      <c r="AI9" s="397" t="n"/>
+      <c r="AJ9" s="397" t="n"/>
+      <c r="AK9" s="397" t="n"/>
+      <c r="AL9" s="397" t="n"/>
+      <c r="AM9" s="397" t="n"/>
+      <c r="AN9" s="398" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1" s="329">
-      <c r="A10" s="287" t="inlineStr">
+      <c r="A10" s="352" t="inlineStr">
         <is>
           <t>Part / Lot / Qty</t>
         </is>
       </c>
-      <c r="B10" s="317" t="n"/>
-      <c r="C10" s="317" t="n"/>
-      <c r="D10" s="317" t="n"/>
-      <c r="E10" s="317" t="n"/>
-      <c r="F10" s="317" t="n"/>
-      <c r="G10" s="318" t="n"/>
-      <c r="H10" s="288" t="n"/>
-      <c r="I10" s="317" t="n"/>
-      <c r="J10" s="317" t="n"/>
-      <c r="K10" s="317" t="n"/>
-      <c r="L10" s="317" t="n"/>
-      <c r="M10" s="317" t="n"/>
-      <c r="N10" s="317" t="n"/>
-      <c r="O10" s="317" t="n"/>
-      <c r="P10" s="317" t="n"/>
-      <c r="Q10" s="317" t="n"/>
-      <c r="R10" s="317" t="n"/>
-      <c r="S10" s="317" t="n"/>
-      <c r="T10" s="318" t="n"/>
-      <c r="U10" s="289" t="inlineStr">
+      <c r="B10" s="397" t="n"/>
+      <c r="C10" s="397" t="n"/>
+      <c r="D10" s="397" t="n"/>
+      <c r="E10" s="397" t="n"/>
+      <c r="F10" s="397" t="n"/>
+      <c r="G10" s="398" t="n"/>
+      <c r="H10" s="355" t="n"/>
+      <c r="I10" s="397" t="n"/>
+      <c r="J10" s="397" t="n"/>
+      <c r="K10" s="397" t="n"/>
+      <c r="L10" s="397" t="n"/>
+      <c r="M10" s="397" t="n"/>
+      <c r="N10" s="397" t="n"/>
+      <c r="O10" s="397" t="n"/>
+      <c r="P10" s="397" t="n"/>
+      <c r="Q10" s="397" t="n"/>
+      <c r="R10" s="397" t="n"/>
+      <c r="S10" s="397" t="n"/>
+      <c r="T10" s="398" t="n"/>
+      <c r="U10" s="356" t="inlineStr">
         <is>
           <t>Supplier-Quality Owner</t>
         </is>
       </c>
-      <c r="V10" s="317" t="n"/>
-      <c r="W10" s="317" t="n"/>
-      <c r="X10" s="317" t="n"/>
-      <c r="Y10" s="317" t="n"/>
-      <c r="Z10" s="317" t="n"/>
-      <c r="AA10" s="318" t="n"/>
-      <c r="AB10" s="290" t="n"/>
-      <c r="AC10" s="317" t="n"/>
-      <c r="AD10" s="317" t="n"/>
-      <c r="AE10" s="317" t="n"/>
-      <c r="AF10" s="317" t="n"/>
-      <c r="AG10" s="317" t="n"/>
-      <c r="AH10" s="317" t="n"/>
-      <c r="AI10" s="317" t="n"/>
-      <c r="AJ10" s="317" t="n"/>
-      <c r="AK10" s="317" t="n"/>
-      <c r="AL10" s="317" t="n"/>
-      <c r="AM10" s="317" t="n"/>
-      <c r="AN10" s="319" t="n"/>
+      <c r="V10" s="397" t="n"/>
+      <c r="W10" s="397" t="n"/>
+      <c r="X10" s="397" t="n"/>
+      <c r="Y10" s="397" t="n"/>
+      <c r="Z10" s="397" t="n"/>
+      <c r="AA10" s="398" t="n"/>
+      <c r="AB10" s="355" t="n"/>
+      <c r="AC10" s="397" t="n"/>
+      <c r="AD10" s="397" t="n"/>
+      <c r="AE10" s="397" t="n"/>
+      <c r="AF10" s="397" t="n"/>
+      <c r="AG10" s="397" t="n"/>
+      <c r="AH10" s="397" t="n"/>
+      <c r="AI10" s="397" t="n"/>
+      <c r="AJ10" s="397" t="n"/>
+      <c r="AK10" s="397" t="n"/>
+      <c r="AL10" s="397" t="n"/>
+      <c r="AM10" s="397" t="n"/>
+      <c r="AN10" s="398" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1" s="329">
-      <c r="A11" s="287" t="inlineStr">
+      <c r="A11" s="352" t="inlineStr">
         <is>
           <t>Prepared by / Date-Time</t>
         </is>
       </c>
-      <c r="B11" s="317" t="n"/>
-      <c r="C11" s="317" t="n"/>
-      <c r="D11" s="317" t="n"/>
-      <c r="E11" s="317" t="n"/>
-      <c r="F11" s="317" t="n"/>
-      <c r="G11" s="318" t="n"/>
-      <c r="H11" s="288" t="n"/>
-      <c r="I11" s="317" t="n"/>
-      <c r="J11" s="317" t="n"/>
-      <c r="K11" s="317" t="n"/>
-      <c r="L11" s="317" t="n"/>
-      <c r="M11" s="317" t="n"/>
-      <c r="N11" s="317" t="n"/>
-      <c r="O11" s="317" t="n"/>
-      <c r="P11" s="317" t="n"/>
-      <c r="Q11" s="317" t="n"/>
-      <c r="R11" s="317" t="n"/>
-      <c r="S11" s="317" t="n"/>
-      <c r="T11" s="318" t="n"/>
-      <c r="U11" s="289" t="inlineStr">
+      <c r="B11" s="392" t="n"/>
+      <c r="C11" s="392" t="n"/>
+      <c r="D11" s="392" t="n"/>
+      <c r="E11" s="392" t="n"/>
+      <c r="F11" s="392" t="n"/>
+      <c r="G11" s="393" t="n"/>
+      <c r="H11" s="355" t="n"/>
+      <c r="I11" s="392" t="n"/>
+      <c r="J11" s="392" t="n"/>
+      <c r="K11" s="392" t="n"/>
+      <c r="L11" s="392" t="n"/>
+      <c r="M11" s="392" t="n"/>
+      <c r="N11" s="392" t="n"/>
+      <c r="O11" s="392" t="n"/>
+      <c r="P11" s="392" t="n"/>
+      <c r="Q11" s="392" t="n"/>
+      <c r="R11" s="392" t="n"/>
+      <c r="S11" s="392" t="n"/>
+      <c r="T11" s="393" t="n"/>
+      <c r="U11" s="356" t="inlineStr">
         <is>
           <t>Record Status</t>
         </is>
       </c>
-      <c r="V11" s="317" t="n"/>
-      <c r="W11" s="317" t="n"/>
-      <c r="X11" s="317" t="n"/>
-      <c r="Y11" s="317" t="n"/>
-      <c r="Z11" s="317" t="n"/>
-      <c r="AA11" s="318" t="n"/>
-      <c r="AB11" s="290" t="n"/>
-      <c r="AC11" s="317" t="n"/>
-      <c r="AD11" s="317" t="n"/>
-      <c r="AE11" s="317" t="n"/>
-      <c r="AF11" s="317" t="n"/>
-      <c r="AG11" s="317" t="n"/>
-      <c r="AH11" s="317" t="n"/>
-      <c r="AI11" s="317" t="n"/>
-      <c r="AJ11" s="317" t="n"/>
-      <c r="AK11" s="317" t="n"/>
-      <c r="AL11" s="317" t="n"/>
-      <c r="AM11" s="317" t="n"/>
-      <c r="AN11" s="319" t="n"/>
+      <c r="V11" s="392" t="n"/>
+      <c r="W11" s="392" t="n"/>
+      <c r="X11" s="392" t="n"/>
+      <c r="Y11" s="392" t="n"/>
+      <c r="Z11" s="392" t="n"/>
+      <c r="AA11" s="393" t="n"/>
+      <c r="AB11" s="355" t="n"/>
+      <c r="AC11" s="392" t="n"/>
+      <c r="AD11" s="392" t="n"/>
+      <c r="AE11" s="392" t="n"/>
+      <c r="AF11" s="392" t="n"/>
+      <c r="AG11" s="392" t="n"/>
+      <c r="AH11" s="392" t="n"/>
+      <c r="AI11" s="392" t="n"/>
+      <c r="AJ11" s="392" t="n"/>
+      <c r="AK11" s="392" t="n"/>
+      <c r="AL11" s="392" t="n"/>
+      <c r="AM11" s="392" t="n"/>
+      <c r="AN11" s="393" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1" s="329">
-      <c r="A12" s="287" t="inlineStr">
+      <c r="A12" s="352" t="inlineStr">
         <is>
           <t>Evidence Package Ref</t>
         </is>
       </c>
-      <c r="B12" s="317" t="n"/>
-      <c r="C12" s="317" t="n"/>
-      <c r="D12" s="317" t="n"/>
-      <c r="E12" s="317" t="n"/>
-      <c r="F12" s="317" t="n"/>
-      <c r="G12" s="318" t="n"/>
-      <c r="H12" s="288" t="n"/>
-      <c r="I12" s="317" t="n"/>
-      <c r="J12" s="317" t="n"/>
-      <c r="K12" s="317" t="n"/>
-      <c r="L12" s="317" t="n"/>
-      <c r="M12" s="317" t="n"/>
-      <c r="N12" s="317" t="n"/>
-      <c r="O12" s="317" t="n"/>
-      <c r="P12" s="317" t="n"/>
-      <c r="Q12" s="317" t="n"/>
-      <c r="R12" s="317" t="n"/>
-      <c r="S12" s="317" t="n"/>
-      <c r="T12" s="318" t="n"/>
-      <c r="U12" s="289" t="inlineStr">
+      <c r="B12" s="397" t="n"/>
+      <c r="C12" s="397" t="n"/>
+      <c r="D12" s="397" t="n"/>
+      <c r="E12" s="397" t="n"/>
+      <c r="F12" s="397" t="n"/>
+      <c r="G12" s="398" t="n"/>
+      <c r="H12" s="355" t="n"/>
+      <c r="I12" s="397" t="n"/>
+      <c r="J12" s="397" t="n"/>
+      <c r="K12" s="397" t="n"/>
+      <c r="L12" s="397" t="n"/>
+      <c r="M12" s="397" t="n"/>
+      <c r="N12" s="397" t="n"/>
+      <c r="O12" s="397" t="n"/>
+      <c r="P12" s="397" t="n"/>
+      <c r="Q12" s="397" t="n"/>
+      <c r="R12" s="397" t="n"/>
+      <c r="S12" s="397" t="n"/>
+      <c r="T12" s="398" t="n"/>
+      <c r="U12" s="356" t="inlineStr">
         <is>
           <t>Risk Level</t>
         </is>
       </c>
-      <c r="V12" s="317" t="n"/>
-      <c r="W12" s="317" t="n"/>
-      <c r="X12" s="317" t="n"/>
-      <c r="Y12" s="317" t="n"/>
-      <c r="Z12" s="317" t="n"/>
-      <c r="AA12" s="318" t="n"/>
-      <c r="AB12" s="290" t="n"/>
-      <c r="AC12" s="317" t="n"/>
-      <c r="AD12" s="317" t="n"/>
-      <c r="AE12" s="317" t="n"/>
-      <c r="AF12" s="317" t="n"/>
-      <c r="AG12" s="317" t="n"/>
-      <c r="AH12" s="317" t="n"/>
-      <c r="AI12" s="317" t="n"/>
-      <c r="AJ12" s="317" t="n"/>
-      <c r="AK12" s="317" t="n"/>
-      <c r="AL12" s="317" t="n"/>
-      <c r="AM12" s="317" t="n"/>
-      <c r="AN12" s="319" t="n"/>
+      <c r="V12" s="397" t="n"/>
+      <c r="W12" s="397" t="n"/>
+      <c r="X12" s="397" t="n"/>
+      <c r="Y12" s="397" t="n"/>
+      <c r="Z12" s="397" t="n"/>
+      <c r="AA12" s="398" t="n"/>
+      <c r="AB12" s="355" t="n"/>
+      <c r="AC12" s="397" t="n"/>
+      <c r="AD12" s="397" t="n"/>
+      <c r="AE12" s="397" t="n"/>
+      <c r="AF12" s="397" t="n"/>
+      <c r="AG12" s="397" t="n"/>
+      <c r="AH12" s="397" t="n"/>
+      <c r="AI12" s="397" t="n"/>
+      <c r="AJ12" s="397" t="n"/>
+      <c r="AK12" s="397" t="n"/>
+      <c r="AL12" s="397" t="n"/>
+      <c r="AM12" s="397" t="n"/>
+      <c r="AN12" s="398" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1" s="329">
-      <c r="A13" s="287" t="inlineStr">
+      <c r="A13" s="352" t="inlineStr">
         <is>
           <t>Method / Acceptance Ref</t>
         </is>
       </c>
-      <c r="B13" s="317" t="n"/>
-      <c r="C13" s="317" t="n"/>
-      <c r="D13" s="317" t="n"/>
-      <c r="E13" s="317" t="n"/>
-      <c r="F13" s="317" t="n"/>
-      <c r="G13" s="318" t="n"/>
-      <c r="H13" s="288" t="n"/>
-      <c r="I13" s="317" t="n"/>
-      <c r="J13" s="317" t="n"/>
-      <c r="K13" s="317" t="n"/>
-      <c r="L13" s="317" t="n"/>
-      <c r="M13" s="317" t="n"/>
-      <c r="N13" s="317" t="n"/>
-      <c r="O13" s="317" t="n"/>
-      <c r="P13" s="317" t="n"/>
-      <c r="Q13" s="317" t="n"/>
-      <c r="R13" s="317" t="n"/>
-      <c r="S13" s="317" t="n"/>
-      <c r="T13" s="318" t="n"/>
-      <c r="U13" s="289" t="inlineStr">
+      <c r="B13" s="397" t="n"/>
+      <c r="C13" s="397" t="n"/>
+      <c r="D13" s="397" t="n"/>
+      <c r="E13" s="397" t="n"/>
+      <c r="F13" s="397" t="n"/>
+      <c r="G13" s="398" t="n"/>
+      <c r="H13" s="355" t="n"/>
+      <c r="I13" s="397" t="n"/>
+      <c r="J13" s="397" t="n"/>
+      <c r="K13" s="397" t="n"/>
+      <c r="L13" s="397" t="n"/>
+      <c r="M13" s="397" t="n"/>
+      <c r="N13" s="397" t="n"/>
+      <c r="O13" s="397" t="n"/>
+      <c r="P13" s="397" t="n"/>
+      <c r="Q13" s="397" t="n"/>
+      <c r="R13" s="397" t="n"/>
+      <c r="S13" s="397" t="n"/>
+      <c r="T13" s="398" t="n"/>
+      <c r="U13" s="356" t="inlineStr">
         <is>
           <t>Affected Job Ref</t>
         </is>
       </c>
-      <c r="V13" s="317" t="n"/>
-      <c r="W13" s="317" t="n"/>
-      <c r="X13" s="317" t="n"/>
-      <c r="Y13" s="317" t="n"/>
-      <c r="Z13" s="317" t="n"/>
-      <c r="AA13" s="318" t="n"/>
-      <c r="AB13" s="290" t="n"/>
-      <c r="AC13" s="317" t="n"/>
-      <c r="AD13" s="317" t="n"/>
-      <c r="AE13" s="317" t="n"/>
-      <c r="AF13" s="317" t="n"/>
-      <c r="AG13" s="317" t="n"/>
-      <c r="AH13" s="317" t="n"/>
-      <c r="AI13" s="317" t="n"/>
-      <c r="AJ13" s="317" t="n"/>
-      <c r="AK13" s="317" t="n"/>
-      <c r="AL13" s="317" t="n"/>
-      <c r="AM13" s="317" t="n"/>
-      <c r="AN13" s="319" t="n"/>
+      <c r="V13" s="397" t="n"/>
+      <c r="W13" s="397" t="n"/>
+      <c r="X13" s="397" t="n"/>
+      <c r="Y13" s="397" t="n"/>
+      <c r="Z13" s="397" t="n"/>
+      <c r="AA13" s="398" t="n"/>
+      <c r="AB13" s="355" t="n"/>
+      <c r="AC13" s="397" t="n"/>
+      <c r="AD13" s="397" t="n"/>
+      <c r="AE13" s="397" t="n"/>
+      <c r="AF13" s="397" t="n"/>
+      <c r="AG13" s="397" t="n"/>
+      <c r="AH13" s="397" t="n"/>
+      <c r="AI13" s="397" t="n"/>
+      <c r="AJ13" s="397" t="n"/>
+      <c r="AK13" s="397" t="n"/>
+      <c r="AL13" s="397" t="n"/>
+      <c r="AM13" s="397" t="n"/>
+      <c r="AN13" s="398" t="n"/>
     </row>
     <row r="14" ht="4" customHeight="1" s="329">
-      <c r="A14" s="284" t="n"/>
+      <c r="A14" s="357" t="n"/>
+      <c r="B14" s="350" t="n"/>
+      <c r="C14" s="350" t="n"/>
+      <c r="D14" s="350" t="n"/>
+      <c r="E14" s="350" t="n"/>
+      <c r="F14" s="350" t="n"/>
+      <c r="G14" s="350" t="n"/>
+      <c r="H14" s="350" t="n"/>
+      <c r="I14" s="350" t="n"/>
+      <c r="J14" s="350" t="n"/>
+      <c r="K14" s="350" t="n"/>
+      <c r="L14" s="350" t="n"/>
+      <c r="M14" s="350" t="n"/>
+      <c r="N14" s="350" t="n"/>
+      <c r="O14" s="350" t="n"/>
+      <c r="P14" s="350" t="n"/>
+      <c r="Q14" s="350" t="n"/>
+      <c r="R14" s="350" t="n"/>
+      <c r="S14" s="350" t="n"/>
+      <c r="T14" s="350" t="n"/>
+      <c r="U14" s="350" t="n"/>
+      <c r="V14" s="350" t="n"/>
+      <c r="W14" s="350" t="n"/>
+      <c r="X14" s="350" t="n"/>
+      <c r="Y14" s="350" t="n"/>
+      <c r="Z14" s="350" t="n"/>
+      <c r="AA14" s="350" t="n"/>
+      <c r="AB14" s="350" t="n"/>
+      <c r="AC14" s="350" t="n"/>
+      <c r="AD14" s="350" t="n"/>
+      <c r="AE14" s="350" t="n"/>
+      <c r="AF14" s="350" t="n"/>
+      <c r="AG14" s="350" t="n"/>
+      <c r="AH14" s="350" t="n"/>
+      <c r="AI14" s="350" t="n"/>
+      <c r="AJ14" s="350" t="n"/>
+      <c r="AK14" s="350" t="n"/>
+      <c r="AL14" s="350" t="n"/>
+      <c r="AM14" s="350" t="n"/>
+      <c r="AN14" s="350" t="n"/>
     </row>
-    <row r="15" ht="17" customHeight="1" s="329">
-      <c r="A15" s="284" t="inlineStr">
+    <row r="15" ht="20" customHeight="1" s="329">
+      <c r="A15" s="351" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. INCOMING VERIFICATION / FINDING DETAIL</t>
         </is>
       </c>
-      <c r="B15" s="285" t="n"/>
-      <c r="C15" s="285" t="n"/>
-      <c r="D15" s="285" t="n"/>
-      <c r="E15" s="285" t="n"/>
-      <c r="F15" s="285" t="n"/>
-      <c r="G15" s="285" t="n"/>
-      <c r="H15" s="285" t="n"/>
-      <c r="I15" s="285" t="n"/>
-      <c r="J15" s="285" t="n"/>
-      <c r="K15" s="285" t="n"/>
-      <c r="L15" s="285" t="n"/>
-      <c r="M15" s="285" t="n"/>
-      <c r="N15" s="285" t="n"/>
-      <c r="O15" s="285" t="n"/>
-      <c r="P15" s="285" t="n"/>
-      <c r="Q15" s="285" t="n"/>
-      <c r="R15" s="285" t="n"/>
-      <c r="S15" s="285" t="n"/>
-      <c r="T15" s="285" t="n"/>
-      <c r="U15" s="285" t="n"/>
-      <c r="V15" s="285" t="n"/>
-      <c r="W15" s="285" t="n"/>
-      <c r="X15" s="285" t="n"/>
-      <c r="Y15" s="285" t="n"/>
-      <c r="Z15" s="285" t="n"/>
-      <c r="AA15" s="285" t="n"/>
-      <c r="AB15" s="285" t="n"/>
-      <c r="AC15" s="285" t="n"/>
-      <c r="AD15" s="285" t="n"/>
-      <c r="AE15" s="285" t="n"/>
-      <c r="AF15" s="285" t="n"/>
-      <c r="AG15" s="285" t="n"/>
-      <c r="AH15" s="285" t="n"/>
-      <c r="AI15" s="285" t="n"/>
-      <c r="AJ15" s="285" t="n"/>
-      <c r="AK15" s="285" t="n"/>
-      <c r="AL15" s="285" t="n"/>
-      <c r="AM15" s="285" t="n"/>
-      <c r="AN15" s="286" t="n"/>
+      <c r="B15" s="397" t="n"/>
+      <c r="C15" s="397" t="n"/>
+      <c r="D15" s="397" t="n"/>
+      <c r="E15" s="397" t="n"/>
+      <c r="F15" s="397" t="n"/>
+      <c r="G15" s="397" t="n"/>
+      <c r="H15" s="397" t="n"/>
+      <c r="I15" s="397" t="n"/>
+      <c r="J15" s="397" t="n"/>
+      <c r="K15" s="397" t="n"/>
+      <c r="L15" s="397" t="n"/>
+      <c r="M15" s="397" t="n"/>
+      <c r="N15" s="397" t="n"/>
+      <c r="O15" s="397" t="n"/>
+      <c r="P15" s="397" t="n"/>
+      <c r="Q15" s="397" t="n"/>
+      <c r="R15" s="397" t="n"/>
+      <c r="S15" s="397" t="n"/>
+      <c r="T15" s="397" t="n"/>
+      <c r="U15" s="397" t="n"/>
+      <c r="V15" s="397" t="n"/>
+      <c r="W15" s="397" t="n"/>
+      <c r="X15" s="397" t="n"/>
+      <c r="Y15" s="397" t="n"/>
+      <c r="Z15" s="397" t="n"/>
+      <c r="AA15" s="397" t="n"/>
+      <c r="AB15" s="397" t="n"/>
+      <c r="AC15" s="397" t="n"/>
+      <c r="AD15" s="397" t="n"/>
+      <c r="AE15" s="397" t="n"/>
+      <c r="AF15" s="397" t="n"/>
+      <c r="AG15" s="397" t="n"/>
+      <c r="AH15" s="397" t="n"/>
+      <c r="AI15" s="397" t="n"/>
+      <c r="AJ15" s="397" t="n"/>
+      <c r="AK15" s="397" t="n"/>
+      <c r="AL15" s="397" t="n"/>
+      <c r="AM15" s="397" t="n"/>
+      <c r="AN15" s="398" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1" s="329">
-      <c r="A16" s="287" t="inlineStr">
+      <c r="A16" s="352" t="inlineStr">
         <is>
           <t>Risk Level</t>
         </is>
       </c>
-      <c r="B16" s="317" t="n"/>
-      <c r="C16" s="317" t="n"/>
-      <c r="D16" s="317" t="n"/>
-      <c r="E16" s="317" t="n"/>
-      <c r="F16" s="317" t="n"/>
-      <c r="G16" s="318" t="n"/>
-      <c r="H16" s="288" t="n"/>
-      <c r="I16" s="317" t="n"/>
-      <c r="J16" s="317" t="n"/>
-      <c r="K16" s="317" t="n"/>
-      <c r="L16" s="317" t="n"/>
-      <c r="M16" s="317" t="n"/>
-      <c r="N16" s="317" t="n"/>
-      <c r="O16" s="317" t="n"/>
-      <c r="P16" s="317" t="n"/>
-      <c r="Q16" s="317" t="n"/>
-      <c r="R16" s="317" t="n"/>
-      <c r="S16" s="317" t="n"/>
-      <c r="T16" s="318" t="n"/>
-      <c r="U16" s="289" t="inlineStr">
+      <c r="B16" s="397" t="n"/>
+      <c r="C16" s="397" t="n"/>
+      <c r="D16" s="397" t="n"/>
+      <c r="E16" s="397" t="n"/>
+      <c r="F16" s="397" t="n"/>
+      <c r="G16" s="398" t="n"/>
+      <c r="H16" s="355" t="n"/>
+      <c r="I16" s="397" t="n"/>
+      <c r="J16" s="397" t="n"/>
+      <c r="K16" s="397" t="n"/>
+      <c r="L16" s="397" t="n"/>
+      <c r="M16" s="397" t="n"/>
+      <c r="N16" s="397" t="n"/>
+      <c r="O16" s="397" t="n"/>
+      <c r="P16" s="397" t="n"/>
+      <c r="Q16" s="397" t="n"/>
+      <c r="R16" s="397" t="n"/>
+      <c r="S16" s="397" t="n"/>
+      <c r="T16" s="398" t="n"/>
+      <c r="U16" s="356" t="inlineStr">
         <is>
           <t>Countermeasure / Trigger</t>
         </is>
       </c>
-      <c r="V16" s="317" t="n"/>
-      <c r="W16" s="317" t="n"/>
-      <c r="X16" s="317" t="n"/>
-      <c r="Y16" s="317" t="n"/>
-      <c r="Z16" s="317" t="n"/>
-      <c r="AA16" s="318" t="n"/>
-      <c r="AB16" s="290" t="n"/>
-      <c r="AC16" s="317" t="n"/>
-      <c r="AD16" s="317" t="n"/>
-      <c r="AE16" s="317" t="n"/>
-      <c r="AF16" s="317" t="n"/>
-      <c r="AG16" s="317" t="n"/>
-      <c r="AH16" s="317" t="n"/>
-      <c r="AI16" s="317" t="n"/>
-      <c r="AJ16" s="317" t="n"/>
-      <c r="AK16" s="317" t="n"/>
-      <c r="AL16" s="317" t="n"/>
-      <c r="AM16" s="317" t="n"/>
-      <c r="AN16" s="319" t="n"/>
+      <c r="V16" s="397" t="n"/>
+      <c r="W16" s="397" t="n"/>
+      <c r="X16" s="397" t="n"/>
+      <c r="Y16" s="397" t="n"/>
+      <c r="Z16" s="397" t="n"/>
+      <c r="AA16" s="398" t="n"/>
+      <c r="AB16" s="355" t="n"/>
+      <c r="AC16" s="397" t="n"/>
+      <c r="AD16" s="397" t="n"/>
+      <c r="AE16" s="397" t="n"/>
+      <c r="AF16" s="397" t="n"/>
+      <c r="AG16" s="397" t="n"/>
+      <c r="AH16" s="397" t="n"/>
+      <c r="AI16" s="397" t="n"/>
+      <c r="AJ16" s="397" t="n"/>
+      <c r="AK16" s="397" t="n"/>
+      <c r="AL16" s="397" t="n"/>
+      <c r="AM16" s="397" t="n"/>
+      <c r="AN16" s="398" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1" s="329">
-      <c r="A17" s="287" t="inlineStr">
+      <c r="A17" s="352" t="inlineStr">
         <is>
           <t>Related Requirement / Package</t>
         </is>
       </c>
-      <c r="B17" s="317" t="n"/>
-      <c r="C17" s="317" t="n"/>
-      <c r="D17" s="317" t="n"/>
-      <c r="E17" s="317" t="n"/>
-      <c r="F17" s="317" t="n"/>
-      <c r="G17" s="318" t="n"/>
-      <c r="H17" s="288" t="n"/>
-      <c r="I17" s="317" t="n"/>
-      <c r="J17" s="317" t="n"/>
-      <c r="K17" s="317" t="n"/>
-      <c r="L17" s="317" t="n"/>
-      <c r="M17" s="317" t="n"/>
-      <c r="N17" s="317" t="n"/>
-      <c r="O17" s="317" t="n"/>
-      <c r="P17" s="317" t="n"/>
-      <c r="Q17" s="317" t="n"/>
-      <c r="R17" s="317" t="n"/>
-      <c r="S17" s="317" t="n"/>
-      <c r="T17" s="318" t="n"/>
-      <c r="U17" s="289" t="inlineStr">
+      <c r="B17" s="397" t="n"/>
+      <c r="C17" s="397" t="n"/>
+      <c r="D17" s="397" t="n"/>
+      <c r="E17" s="397" t="n"/>
+      <c r="F17" s="397" t="n"/>
+      <c r="G17" s="398" t="n"/>
+      <c r="H17" s="355" t="n"/>
+      <c r="I17" s="397" t="n"/>
+      <c r="J17" s="397" t="n"/>
+      <c r="K17" s="397" t="n"/>
+      <c r="L17" s="397" t="n"/>
+      <c r="M17" s="397" t="n"/>
+      <c r="N17" s="397" t="n"/>
+      <c r="O17" s="397" t="n"/>
+      <c r="P17" s="397" t="n"/>
+      <c r="Q17" s="397" t="n"/>
+      <c r="R17" s="397" t="n"/>
+      <c r="S17" s="397" t="n"/>
+      <c r="T17" s="398" t="n"/>
+      <c r="U17" s="356" t="inlineStr">
         <is>
           <t>Customer Special Requirement (YES/NO)</t>
         </is>
       </c>
-      <c r="V17" s="317" t="n"/>
-      <c r="W17" s="317" t="n"/>
-      <c r="X17" s="317" t="n"/>
-      <c r="Y17" s="317" t="n"/>
-      <c r="Z17" s="317" t="n"/>
-      <c r="AA17" s="318" t="n"/>
-      <c r="AB17" s="290" t="n"/>
-      <c r="AC17" s="317" t="n"/>
-      <c r="AD17" s="317" t="n"/>
-      <c r="AE17" s="317" t="n"/>
-      <c r="AF17" s="317" t="n"/>
-      <c r="AG17" s="317" t="n"/>
-      <c r="AH17" s="317" t="n"/>
-      <c r="AI17" s="317" t="n"/>
-      <c r="AJ17" s="317" t="n"/>
-      <c r="AK17" s="317" t="n"/>
-      <c r="AL17" s="317" t="n"/>
-      <c r="AM17" s="317" t="n"/>
-      <c r="AN17" s="319" t="n"/>
+      <c r="V17" s="397" t="n"/>
+      <c r="W17" s="397" t="n"/>
+      <c r="X17" s="397" t="n"/>
+      <c r="Y17" s="397" t="n"/>
+      <c r="Z17" s="397" t="n"/>
+      <c r="AA17" s="398" t="n"/>
+      <c r="AB17" s="355" t="n"/>
+      <c r="AC17" s="397" t="n"/>
+      <c r="AD17" s="397" t="n"/>
+      <c r="AE17" s="397" t="n"/>
+      <c r="AF17" s="397" t="n"/>
+      <c r="AG17" s="397" t="n"/>
+      <c r="AH17" s="397" t="n"/>
+      <c r="AI17" s="397" t="n"/>
+      <c r="AJ17" s="397" t="n"/>
+      <c r="AK17" s="397" t="n"/>
+      <c r="AL17" s="397" t="n"/>
+      <c r="AM17" s="397" t="n"/>
+      <c r="AN17" s="398" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1" s="329">
-      <c r="A18" s="287" t="inlineStr">
+      <c r="A18" s="352" t="inlineStr">
         <is>
           <t>VERIFICATION / SCOPE DESCRIPTION</t>
         </is>
       </c>
-      <c r="B18" s="317" t="n"/>
-      <c r="C18" s="317" t="n"/>
-      <c r="D18" s="317" t="n"/>
-      <c r="E18" s="317" t="n"/>
-      <c r="F18" s="317" t="n"/>
-      <c r="G18" s="317" t="n"/>
-      <c r="H18" s="317" t="n"/>
-      <c r="I18" s="317" t="n"/>
-      <c r="J18" s="317" t="n"/>
-      <c r="K18" s="317" t="n"/>
-      <c r="L18" s="317" t="n"/>
-      <c r="M18" s="317" t="n"/>
-      <c r="N18" s="317" t="n"/>
-      <c r="O18" s="317" t="n"/>
-      <c r="P18" s="317" t="n"/>
-      <c r="Q18" s="317" t="n"/>
-      <c r="R18" s="317" t="n"/>
-      <c r="S18" s="317" t="n"/>
-      <c r="T18" s="317" t="n"/>
-      <c r="U18" s="317" t="n"/>
-      <c r="V18" s="317" t="n"/>
-      <c r="W18" s="317" t="n"/>
-      <c r="X18" s="317" t="n"/>
-      <c r="Y18" s="317" t="n"/>
-      <c r="Z18" s="317" t="n"/>
-      <c r="AA18" s="317" t="n"/>
-      <c r="AB18" s="317" t="n"/>
-      <c r="AC18" s="317" t="n"/>
-      <c r="AD18" s="317" t="n"/>
-      <c r="AE18" s="317" t="n"/>
-      <c r="AF18" s="317" t="n"/>
-      <c r="AG18" s="317" t="n"/>
-      <c r="AH18" s="317" t="n"/>
-      <c r="AI18" s="317" t="n"/>
-      <c r="AJ18" s="317" t="n"/>
-      <c r="AK18" s="317" t="n"/>
-      <c r="AL18" s="317" t="n"/>
-      <c r="AM18" s="317" t="n"/>
-      <c r="AN18" s="318" t="n"/>
+      <c r="B18" s="397" t="n"/>
+      <c r="C18" s="397" t="n"/>
+      <c r="D18" s="397" t="n"/>
+      <c r="E18" s="397" t="n"/>
+      <c r="F18" s="397" t="n"/>
+      <c r="G18" s="397" t="n"/>
+      <c r="H18" s="397" t="n"/>
+      <c r="I18" s="397" t="n"/>
+      <c r="J18" s="397" t="n"/>
+      <c r="K18" s="397" t="n"/>
+      <c r="L18" s="397" t="n"/>
+      <c r="M18" s="397" t="n"/>
+      <c r="N18" s="397" t="n"/>
+      <c r="O18" s="397" t="n"/>
+      <c r="P18" s="397" t="n"/>
+      <c r="Q18" s="397" t="n"/>
+      <c r="R18" s="397" t="n"/>
+      <c r="S18" s="397" t="n"/>
+      <c r="T18" s="397" t="n"/>
+      <c r="U18" s="397" t="n"/>
+      <c r="V18" s="397" t="n"/>
+      <c r="W18" s="397" t="n"/>
+      <c r="X18" s="397" t="n"/>
+      <c r="Y18" s="397" t="n"/>
+      <c r="Z18" s="397" t="n"/>
+      <c r="AA18" s="397" t="n"/>
+      <c r="AB18" s="397" t="n"/>
+      <c r="AC18" s="397" t="n"/>
+      <c r="AD18" s="397" t="n"/>
+      <c r="AE18" s="397" t="n"/>
+      <c r="AF18" s="397" t="n"/>
+      <c r="AG18" s="397" t="n"/>
+      <c r="AH18" s="397" t="n"/>
+      <c r="AI18" s="397" t="n"/>
+      <c r="AJ18" s="397" t="n"/>
+      <c r="AK18" s="397" t="n"/>
+      <c r="AL18" s="397" t="n"/>
+      <c r="AM18" s="397" t="n"/>
+      <c r="AN18" s="398" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1" s="329">
-      <c r="A19" s="291" t="n"/>
-      <c r="B19" s="320" t="n"/>
-      <c r="C19" s="320" t="n"/>
-      <c r="D19" s="320" t="n"/>
-      <c r="E19" s="320" t="n"/>
-      <c r="F19" s="320" t="n"/>
-      <c r="G19" s="320" t="n"/>
-      <c r="H19" s="320" t="n"/>
-      <c r="I19" s="320" t="n"/>
-      <c r="J19" s="320" t="n"/>
-      <c r="K19" s="320" t="n"/>
-      <c r="L19" s="320" t="n"/>
-      <c r="M19" s="320" t="n"/>
-      <c r="N19" s="320" t="n"/>
-      <c r="O19" s="320" t="n"/>
-      <c r="P19" s="320" t="n"/>
-      <c r="Q19" s="320" t="n"/>
-      <c r="R19" s="320" t="n"/>
-      <c r="S19" s="320" t="n"/>
-      <c r="T19" s="320" t="n"/>
-      <c r="U19" s="320" t="n"/>
-      <c r="V19" s="320" t="n"/>
-      <c r="W19" s="320" t="n"/>
-      <c r="X19" s="320" t="n"/>
-      <c r="Y19" s="320" t="n"/>
-      <c r="Z19" s="320" t="n"/>
-      <c r="AA19" s="320" t="n"/>
-      <c r="AB19" s="320" t="n"/>
-      <c r="AC19" s="320" t="n"/>
-      <c r="AD19" s="320" t="n"/>
-      <c r="AE19" s="320" t="n"/>
-      <c r="AF19" s="320" t="n"/>
-      <c r="AG19" s="320" t="n"/>
-      <c r="AH19" s="320" t="n"/>
-      <c r="AI19" s="320" t="n"/>
-      <c r="AJ19" s="320" t="n"/>
-      <c r="AK19" s="320" t="n"/>
-      <c r="AL19" s="320" t="n"/>
-      <c r="AM19" s="320" t="n"/>
-      <c r="AN19" s="321" t="n"/>
+      <c r="A19" s="355" t="n"/>
+      <c r="B19" s="399" t="n"/>
+      <c r="C19" s="399" t="n"/>
+      <c r="D19" s="399" t="n"/>
+      <c r="E19" s="399" t="n"/>
+      <c r="F19" s="399" t="n"/>
+      <c r="G19" s="399" t="n"/>
+      <c r="H19" s="399" t="n"/>
+      <c r="I19" s="399" t="n"/>
+      <c r="J19" s="399" t="n"/>
+      <c r="K19" s="399" t="n"/>
+      <c r="L19" s="399" t="n"/>
+      <c r="M19" s="399" t="n"/>
+      <c r="N19" s="399" t="n"/>
+      <c r="O19" s="399" t="n"/>
+      <c r="P19" s="399" t="n"/>
+      <c r="Q19" s="399" t="n"/>
+      <c r="R19" s="399" t="n"/>
+      <c r="S19" s="399" t="n"/>
+      <c r="T19" s="399" t="n"/>
+      <c r="U19" s="399" t="n"/>
+      <c r="V19" s="399" t="n"/>
+      <c r="W19" s="399" t="n"/>
+      <c r="X19" s="399" t="n"/>
+      <c r="Y19" s="399" t="n"/>
+      <c r="Z19" s="399" t="n"/>
+      <c r="AA19" s="399" t="n"/>
+      <c r="AB19" s="399" t="n"/>
+      <c r="AC19" s="399" t="n"/>
+      <c r="AD19" s="399" t="n"/>
+      <c r="AE19" s="399" t="n"/>
+      <c r="AF19" s="399" t="n"/>
+      <c r="AG19" s="399" t="n"/>
+      <c r="AH19" s="399" t="n"/>
+      <c r="AI19" s="399" t="n"/>
+      <c r="AJ19" s="399" t="n"/>
+      <c r="AK19" s="399" t="n"/>
+      <c r="AL19" s="399" t="n"/>
+      <c r="AM19" s="399" t="n"/>
+      <c r="AN19" s="400" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1" s="329">
-      <c r="A20" s="322" t="n"/>
-      <c r="B20" s="322" t="n"/>
-      <c r="C20" s="322" t="n"/>
-      <c r="D20" s="322" t="n"/>
-      <c r="E20" s="322" t="n"/>
-      <c r="F20" s="322" t="n"/>
-      <c r="G20" s="322" t="n"/>
-      <c r="H20" s="322" t="n"/>
-      <c r="I20" s="322" t="n"/>
-      <c r="J20" s="322" t="n"/>
-      <c r="K20" s="322" t="n"/>
-      <c r="L20" s="322" t="n"/>
-      <c r="M20" s="322" t="n"/>
-      <c r="N20" s="322" t="n"/>
-      <c r="O20" s="322" t="n"/>
-      <c r="P20" s="322" t="n"/>
-      <c r="Q20" s="322" t="n"/>
-      <c r="R20" s="322" t="n"/>
-      <c r="S20" s="322" t="n"/>
-      <c r="T20" s="322" t="n"/>
-      <c r="U20" s="322" t="n"/>
-      <c r="V20" s="322" t="n"/>
-      <c r="W20" s="322" t="n"/>
-      <c r="X20" s="322" t="n"/>
-      <c r="Y20" s="322" t="n"/>
-      <c r="Z20" s="322" t="n"/>
-      <c r="AA20" s="322" t="n"/>
-      <c r="AB20" s="322" t="n"/>
-      <c r="AC20" s="322" t="n"/>
-      <c r="AD20" s="322" t="n"/>
-      <c r="AE20" s="322" t="n"/>
-      <c r="AF20" s="322" t="n"/>
-      <c r="AG20" s="322" t="n"/>
-      <c r="AH20" s="322" t="n"/>
-      <c r="AI20" s="322" t="n"/>
-      <c r="AJ20" s="322" t="n"/>
-      <c r="AK20" s="322" t="n"/>
-      <c r="AL20" s="322" t="n"/>
-      <c r="AM20" s="322" t="n"/>
-      <c r="AN20" s="323" t="n"/>
+      <c r="A20" s="401" t="n"/>
+      <c r="B20" s="401" t="n"/>
+      <c r="C20" s="401" t="n"/>
+      <c r="D20" s="401" t="n"/>
+      <c r="E20" s="401" t="n"/>
+      <c r="F20" s="401" t="n"/>
+      <c r="G20" s="401" t="n"/>
+      <c r="H20" s="401" t="n"/>
+      <c r="I20" s="401" t="n"/>
+      <c r="J20" s="401" t="n"/>
+      <c r="K20" s="401" t="n"/>
+      <c r="L20" s="401" t="n"/>
+      <c r="M20" s="401" t="n"/>
+      <c r="N20" s="401" t="n"/>
+      <c r="O20" s="401" t="n"/>
+      <c r="P20" s="401" t="n"/>
+      <c r="Q20" s="401" t="n"/>
+      <c r="R20" s="401" t="n"/>
+      <c r="S20" s="401" t="n"/>
+      <c r="T20" s="401" t="n"/>
+      <c r="U20" s="401" t="n"/>
+      <c r="V20" s="401" t="n"/>
+      <c r="W20" s="401" t="n"/>
+      <c r="X20" s="401" t="n"/>
+      <c r="Y20" s="401" t="n"/>
+      <c r="Z20" s="401" t="n"/>
+      <c r="AA20" s="401" t="n"/>
+      <c r="AB20" s="401" t="n"/>
+      <c r="AC20" s="401" t="n"/>
+      <c r="AD20" s="401" t="n"/>
+      <c r="AE20" s="401" t="n"/>
+      <c r="AF20" s="401" t="n"/>
+      <c r="AG20" s="401" t="n"/>
+      <c r="AH20" s="401" t="n"/>
+      <c r="AI20" s="401" t="n"/>
+      <c r="AJ20" s="401" t="n"/>
+      <c r="AK20" s="401" t="n"/>
+      <c r="AL20" s="401" t="n"/>
+      <c r="AM20" s="401" t="n"/>
+      <c r="AN20" s="402" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1" s="329">
-      <c r="A21" s="287" t="inlineStr">
+      <c r="A21" s="352" t="inlineStr">
         <is>
           <t>OBSERVATION / CONTAINMENT / CERT CHECK</t>
         </is>
       </c>
-      <c r="B21" s="317" t="n"/>
-      <c r="C21" s="317" t="n"/>
-      <c r="D21" s="317" t="n"/>
-      <c r="E21" s="317" t="n"/>
-      <c r="F21" s="317" t="n"/>
-      <c r="G21" s="317" t="n"/>
-      <c r="H21" s="317" t="n"/>
-      <c r="I21" s="317" t="n"/>
-      <c r="J21" s="317" t="n"/>
-      <c r="K21" s="317" t="n"/>
-      <c r="L21" s="317" t="n"/>
-      <c r="M21" s="317" t="n"/>
-      <c r="N21" s="317" t="n"/>
-      <c r="O21" s="317" t="n"/>
-      <c r="P21" s="317" t="n"/>
-      <c r="Q21" s="317" t="n"/>
-      <c r="R21" s="317" t="n"/>
-      <c r="S21" s="317" t="n"/>
-      <c r="T21" s="317" t="n"/>
-      <c r="U21" s="317" t="n"/>
-      <c r="V21" s="317" t="n"/>
-      <c r="W21" s="317" t="n"/>
-      <c r="X21" s="317" t="n"/>
-      <c r="Y21" s="317" t="n"/>
-      <c r="Z21" s="317" t="n"/>
-      <c r="AA21" s="317" t="n"/>
-      <c r="AB21" s="317" t="n"/>
-      <c r="AC21" s="317" t="n"/>
-      <c r="AD21" s="317" t="n"/>
-      <c r="AE21" s="317" t="n"/>
-      <c r="AF21" s="317" t="n"/>
-      <c r="AG21" s="317" t="n"/>
-      <c r="AH21" s="317" t="n"/>
-      <c r="AI21" s="317" t="n"/>
-      <c r="AJ21" s="317" t="n"/>
-      <c r="AK21" s="317" t="n"/>
-      <c r="AL21" s="317" t="n"/>
-      <c r="AM21" s="317" t="n"/>
-      <c r="AN21" s="318" t="n"/>
+      <c r="B21" s="397" t="n"/>
+      <c r="C21" s="397" t="n"/>
+      <c r="D21" s="397" t="n"/>
+      <c r="E21" s="397" t="n"/>
+      <c r="F21" s="397" t="n"/>
+      <c r="G21" s="397" t="n"/>
+      <c r="H21" s="397" t="n"/>
+      <c r="I21" s="397" t="n"/>
+      <c r="J21" s="397" t="n"/>
+      <c r="K21" s="397" t="n"/>
+      <c r="L21" s="397" t="n"/>
+      <c r="M21" s="397" t="n"/>
+      <c r="N21" s="397" t="n"/>
+      <c r="O21" s="397" t="n"/>
+      <c r="P21" s="397" t="n"/>
+      <c r="Q21" s="397" t="n"/>
+      <c r="R21" s="397" t="n"/>
+      <c r="S21" s="397" t="n"/>
+      <c r="T21" s="397" t="n"/>
+      <c r="U21" s="397" t="n"/>
+      <c r="V21" s="397" t="n"/>
+      <c r="W21" s="397" t="n"/>
+      <c r="X21" s="397" t="n"/>
+      <c r="Y21" s="397" t="n"/>
+      <c r="Z21" s="397" t="n"/>
+      <c r="AA21" s="397" t="n"/>
+      <c r="AB21" s="397" t="n"/>
+      <c r="AC21" s="397" t="n"/>
+      <c r="AD21" s="397" t="n"/>
+      <c r="AE21" s="397" t="n"/>
+      <c r="AF21" s="397" t="n"/>
+      <c r="AG21" s="397" t="n"/>
+      <c r="AH21" s="397" t="n"/>
+      <c r="AI21" s="397" t="n"/>
+      <c r="AJ21" s="397" t="n"/>
+      <c r="AK21" s="397" t="n"/>
+      <c r="AL21" s="397" t="n"/>
+      <c r="AM21" s="397" t="n"/>
+      <c r="AN21" s="398" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1" s="329">
-      <c r="A22" s="291" t="n"/>
-      <c r="B22" s="320" t="n"/>
-      <c r="C22" s="320" t="n"/>
-      <c r="D22" s="320" t="n"/>
-      <c r="E22" s="320" t="n"/>
-      <c r="F22" s="320" t="n"/>
-      <c r="G22" s="320" t="n"/>
-      <c r="H22" s="320" t="n"/>
-      <c r="I22" s="320" t="n"/>
-      <c r="J22" s="320" t="n"/>
-      <c r="K22" s="320" t="n"/>
-      <c r="L22" s="320" t="n"/>
-      <c r="M22" s="320" t="n"/>
-      <c r="N22" s="320" t="n"/>
-      <c r="O22" s="320" t="n"/>
-      <c r="P22" s="320" t="n"/>
-      <c r="Q22" s="320" t="n"/>
-      <c r="R22" s="320" t="n"/>
-      <c r="S22" s="320" t="n"/>
-      <c r="T22" s="320" t="n"/>
-      <c r="U22" s="320" t="n"/>
-      <c r="V22" s="320" t="n"/>
-      <c r="W22" s="320" t="n"/>
-      <c r="X22" s="320" t="n"/>
-      <c r="Y22" s="320" t="n"/>
-      <c r="Z22" s="320" t="n"/>
-      <c r="AA22" s="320" t="n"/>
-      <c r="AB22" s="320" t="n"/>
-      <c r="AC22" s="320" t="n"/>
-      <c r="AD22" s="320" t="n"/>
-      <c r="AE22" s="320" t="n"/>
-      <c r="AF22" s="320" t="n"/>
-      <c r="AG22" s="320" t="n"/>
-      <c r="AH22" s="320" t="n"/>
-      <c r="AI22" s="320" t="n"/>
-      <c r="AJ22" s="320" t="n"/>
-      <c r="AK22" s="320" t="n"/>
-      <c r="AL22" s="320" t="n"/>
-      <c r="AM22" s="320" t="n"/>
-      <c r="AN22" s="321" t="n"/>
+      <c r="A22" s="355" t="n"/>
+      <c r="B22" s="399" t="n"/>
+      <c r="C22" s="399" t="n"/>
+      <c r="D22" s="399" t="n"/>
+      <c r="E22" s="399" t="n"/>
+      <c r="F22" s="399" t="n"/>
+      <c r="G22" s="399" t="n"/>
+      <c r="H22" s="399" t="n"/>
+      <c r="I22" s="399" t="n"/>
+      <c r="J22" s="399" t="n"/>
+      <c r="K22" s="399" t="n"/>
+      <c r="L22" s="399" t="n"/>
+      <c r="M22" s="399" t="n"/>
+      <c r="N22" s="399" t="n"/>
+      <c r="O22" s="399" t="n"/>
+      <c r="P22" s="399" t="n"/>
+      <c r="Q22" s="399" t="n"/>
+      <c r="R22" s="399" t="n"/>
+      <c r="S22" s="399" t="n"/>
+      <c r="T22" s="399" t="n"/>
+      <c r="U22" s="399" t="n"/>
+      <c r="V22" s="399" t="n"/>
+      <c r="W22" s="399" t="n"/>
+      <c r="X22" s="399" t="n"/>
+      <c r="Y22" s="399" t="n"/>
+      <c r="Z22" s="399" t="n"/>
+      <c r="AA22" s="399" t="n"/>
+      <c r="AB22" s="399" t="n"/>
+      <c r="AC22" s="399" t="n"/>
+      <c r="AD22" s="399" t="n"/>
+      <c r="AE22" s="399" t="n"/>
+      <c r="AF22" s="399" t="n"/>
+      <c r="AG22" s="399" t="n"/>
+      <c r="AH22" s="399" t="n"/>
+      <c r="AI22" s="399" t="n"/>
+      <c r="AJ22" s="399" t="n"/>
+      <c r="AK22" s="399" t="n"/>
+      <c r="AL22" s="399" t="n"/>
+      <c r="AM22" s="399" t="n"/>
+      <c r="AN22" s="400" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1" s="329">
-      <c r="A23" s="322" t="n"/>
-      <c r="B23" s="322" t="n"/>
-      <c r="C23" s="322" t="n"/>
-      <c r="D23" s="322" t="n"/>
-      <c r="E23" s="322" t="n"/>
-      <c r="F23" s="322" t="n"/>
-      <c r="G23" s="322" t="n"/>
-      <c r="H23" s="322" t="n"/>
-      <c r="I23" s="322" t="n"/>
-      <c r="J23" s="322" t="n"/>
-      <c r="K23" s="322" t="n"/>
-      <c r="L23" s="322" t="n"/>
-      <c r="M23" s="322" t="n"/>
-      <c r="N23" s="322" t="n"/>
-      <c r="O23" s="322" t="n"/>
-      <c r="P23" s="322" t="n"/>
-      <c r="Q23" s="322" t="n"/>
-      <c r="R23" s="322" t="n"/>
-      <c r="S23" s="322" t="n"/>
-      <c r="T23" s="322" t="n"/>
-      <c r="U23" s="322" t="n"/>
-      <c r="V23" s="322" t="n"/>
-      <c r="W23" s="322" t="n"/>
-      <c r="X23" s="322" t="n"/>
-      <c r="Y23" s="322" t="n"/>
-      <c r="Z23" s="322" t="n"/>
-      <c r="AA23" s="322" t="n"/>
-      <c r="AB23" s="322" t="n"/>
-      <c r="AC23" s="322" t="n"/>
-      <c r="AD23" s="322" t="n"/>
-      <c r="AE23" s="322" t="n"/>
-      <c r="AF23" s="322" t="n"/>
-      <c r="AG23" s="322" t="n"/>
-      <c r="AH23" s="322" t="n"/>
-      <c r="AI23" s="322" t="n"/>
-      <c r="AJ23" s="322" t="n"/>
-      <c r="AK23" s="322" t="n"/>
-      <c r="AL23" s="322" t="n"/>
-      <c r="AM23" s="322" t="n"/>
-      <c r="AN23" s="323" t="n"/>
+      <c r="A23" s="401" t="n"/>
+      <c r="B23" s="401" t="n"/>
+      <c r="C23" s="401" t="n"/>
+      <c r="D23" s="401" t="n"/>
+      <c r="E23" s="401" t="n"/>
+      <c r="F23" s="401" t="n"/>
+      <c r="G23" s="401" t="n"/>
+      <c r="H23" s="401" t="n"/>
+      <c r="I23" s="401" t="n"/>
+      <c r="J23" s="401" t="n"/>
+      <c r="K23" s="401" t="n"/>
+      <c r="L23" s="401" t="n"/>
+      <c r="M23" s="401" t="n"/>
+      <c r="N23" s="401" t="n"/>
+      <c r="O23" s="401" t="n"/>
+      <c r="P23" s="401" t="n"/>
+      <c r="Q23" s="401" t="n"/>
+      <c r="R23" s="401" t="n"/>
+      <c r="S23" s="401" t="n"/>
+      <c r="T23" s="401" t="n"/>
+      <c r="U23" s="401" t="n"/>
+      <c r="V23" s="401" t="n"/>
+      <c r="W23" s="401" t="n"/>
+      <c r="X23" s="401" t="n"/>
+      <c r="Y23" s="401" t="n"/>
+      <c r="Z23" s="401" t="n"/>
+      <c r="AA23" s="401" t="n"/>
+      <c r="AB23" s="401" t="n"/>
+      <c r="AC23" s="401" t="n"/>
+      <c r="AD23" s="401" t="n"/>
+      <c r="AE23" s="401" t="n"/>
+      <c r="AF23" s="401" t="n"/>
+      <c r="AG23" s="401" t="n"/>
+      <c r="AH23" s="401" t="n"/>
+      <c r="AI23" s="401" t="n"/>
+      <c r="AJ23" s="401" t="n"/>
+      <c r="AK23" s="401" t="n"/>
+      <c r="AL23" s="401" t="n"/>
+      <c r="AM23" s="401" t="n"/>
+      <c r="AN23" s="402" t="n"/>
     </row>
     <row r="24" ht="4" customHeight="1" s="329">
-      <c r="A24" s="293" t="n"/>
-      <c r="C24" s="294" t="n"/>
-      <c r="F24" s="303" t="n"/>
-      <c r="T24" s="304" t="n"/>
-      <c r="AF24" s="297" t="n"/>
-      <c r="AJ24" s="297" t="n"/>
-      <c r="AM24" s="298" t="n"/>
+      <c r="A24" s="362" t="n"/>
+      <c r="B24" s="350" t="n"/>
+      <c r="C24" s="363" t="n"/>
+      <c r="D24" s="350" t="n"/>
+      <c r="E24" s="350" t="n"/>
+      <c r="F24" s="364" t="n"/>
+      <c r="G24" s="350" t="n"/>
+      <c r="H24" s="350" t="n"/>
+      <c r="I24" s="350" t="n"/>
+      <c r="J24" s="350" t="n"/>
+      <c r="K24" s="350" t="n"/>
+      <c r="L24" s="350" t="n"/>
+      <c r="M24" s="350" t="n"/>
+      <c r="N24" s="350" t="n"/>
+      <c r="O24" s="350" t="n"/>
+      <c r="P24" s="350" t="n"/>
+      <c r="Q24" s="350" t="n"/>
+      <c r="R24" s="350" t="n"/>
+      <c r="S24" s="350" t="n"/>
+      <c r="T24" s="365" t="n"/>
+      <c r="U24" s="350" t="n"/>
+      <c r="V24" s="350" t="n"/>
+      <c r="W24" s="350" t="n"/>
+      <c r="X24" s="350" t="n"/>
+      <c r="Y24" s="350" t="n"/>
+      <c r="Z24" s="350" t="n"/>
+      <c r="AA24" s="350" t="n"/>
+      <c r="AB24" s="350" t="n"/>
+      <c r="AC24" s="350" t="n"/>
+      <c r="AD24" s="350" t="n"/>
+      <c r="AE24" s="350" t="n"/>
+      <c r="AF24" s="366" t="n"/>
+      <c r="AG24" s="350" t="n"/>
+      <c r="AH24" s="350" t="n"/>
+      <c r="AI24" s="350" t="n"/>
+      <c r="AJ24" s="366" t="n"/>
+      <c r="AK24" s="350" t="n"/>
+      <c r="AL24" s="350" t="n"/>
+      <c r="AM24" s="367" t="n"/>
+      <c r="AN24" s="350" t="n"/>
     </row>
-    <row r="25" ht="17" customHeight="1" s="329">
-      <c r="A25" s="284" t="inlineStr">
+    <row r="25" ht="20" customHeight="1" s="329">
+      <c r="A25" s="351" t="inlineStr">
         <is>
           <t xml:space="preserve">  3. IMPACT / CONTAINMENT / ACTIONS</t>
         </is>
       </c>
-      <c r="B25" s="285" t="n"/>
-      <c r="C25" s="285" t="n"/>
-      <c r="D25" s="285" t="n"/>
-      <c r="E25" s="285" t="n"/>
-      <c r="F25" s="285" t="n"/>
-      <c r="G25" s="285" t="n"/>
-      <c r="H25" s="285" t="n"/>
-      <c r="I25" s="285" t="n"/>
-      <c r="J25" s="285" t="n"/>
-      <c r="K25" s="285" t="n"/>
-      <c r="L25" s="285" t="n"/>
-      <c r="M25" s="285" t="n"/>
-      <c r="N25" s="285" t="n"/>
-      <c r="O25" s="285" t="n"/>
-      <c r="P25" s="285" t="n"/>
-      <c r="Q25" s="285" t="n"/>
-      <c r="R25" s="285" t="n"/>
-      <c r="S25" s="285" t="n"/>
-      <c r="T25" s="285" t="n"/>
-      <c r="U25" s="285" t="n"/>
-      <c r="V25" s="285" t="n"/>
-      <c r="W25" s="285" t="n"/>
-      <c r="X25" s="285" t="n"/>
-      <c r="Y25" s="285" t="n"/>
-      <c r="Z25" s="285" t="n"/>
-      <c r="AA25" s="285" t="n"/>
-      <c r="AB25" s="285" t="n"/>
-      <c r="AC25" s="285" t="n"/>
-      <c r="AD25" s="285" t="n"/>
-      <c r="AE25" s="285" t="n"/>
-      <c r="AF25" s="285" t="n"/>
-      <c r="AG25" s="285" t="n"/>
-      <c r="AH25" s="285" t="n"/>
-      <c r="AI25" s="285" t="n"/>
-      <c r="AJ25" s="285" t="n"/>
-      <c r="AK25" s="285" t="n"/>
-      <c r="AL25" s="285" t="n"/>
-      <c r="AM25" s="285" t="n"/>
-      <c r="AN25" s="286" t="n"/>
+      <c r="B25" s="397" t="n"/>
+      <c r="C25" s="397" t="n"/>
+      <c r="D25" s="397" t="n"/>
+      <c r="E25" s="397" t="n"/>
+      <c r="F25" s="397" t="n"/>
+      <c r="G25" s="397" t="n"/>
+      <c r="H25" s="397" t="n"/>
+      <c r="I25" s="397" t="n"/>
+      <c r="J25" s="397" t="n"/>
+      <c r="K25" s="397" t="n"/>
+      <c r="L25" s="397" t="n"/>
+      <c r="M25" s="397" t="n"/>
+      <c r="N25" s="397" t="n"/>
+      <c r="O25" s="397" t="n"/>
+      <c r="P25" s="397" t="n"/>
+      <c r="Q25" s="397" t="n"/>
+      <c r="R25" s="397" t="n"/>
+      <c r="S25" s="397" t="n"/>
+      <c r="T25" s="397" t="n"/>
+      <c r="U25" s="397" t="n"/>
+      <c r="V25" s="397" t="n"/>
+      <c r="W25" s="397" t="n"/>
+      <c r="X25" s="397" t="n"/>
+      <c r="Y25" s="397" t="n"/>
+      <c r="Z25" s="397" t="n"/>
+      <c r="AA25" s="397" t="n"/>
+      <c r="AB25" s="397" t="n"/>
+      <c r="AC25" s="397" t="n"/>
+      <c r="AD25" s="397" t="n"/>
+      <c r="AE25" s="397" t="n"/>
+      <c r="AF25" s="397" t="n"/>
+      <c r="AG25" s="397" t="n"/>
+      <c r="AH25" s="397" t="n"/>
+      <c r="AI25" s="397" t="n"/>
+      <c r="AJ25" s="397" t="n"/>
+      <c r="AK25" s="397" t="n"/>
+      <c r="AL25" s="397" t="n"/>
+      <c r="AM25" s="397" t="n"/>
+      <c r="AN25" s="398" t="n"/>
     </row>
-    <row r="26" ht="17" customHeight="1" s="329">
-      <c r="A26" s="299" t="inlineStr">
+    <row r="26" ht="20" customHeight="1" s="329">
+      <c r="A26" s="368" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B26" s="318" t="n"/>
-      <c r="C26" s="300" t="inlineStr">
+      <c r="B26" s="398" t="n"/>
+      <c r="C26" s="369" t="inlineStr">
         <is>
           <t>Cat.</t>
         </is>
       </c>
-      <c r="D26" s="317" t="n"/>
-      <c r="E26" s="318" t="n"/>
-      <c r="F26" s="300" t="inlineStr">
+      <c r="D26" s="397" t="n"/>
+      <c r="E26" s="398" t="n"/>
+      <c r="F26" s="369" t="inlineStr">
         <is>
           <t>Finding / Check</t>
         </is>
       </c>
-      <c r="G26" s="317" t="n"/>
-      <c r="H26" s="317" t="n"/>
-      <c r="I26" s="317" t="n"/>
-      <c r="J26" s="317" t="n"/>
-      <c r="K26" s="317" t="n"/>
-      <c r="L26" s="317" t="n"/>
-      <c r="M26" s="317" t="n"/>
-      <c r="N26" s="317" t="n"/>
-      <c r="O26" s="317" t="n"/>
-      <c r="P26" s="317" t="n"/>
-      <c r="Q26" s="317" t="n"/>
-      <c r="R26" s="317" t="n"/>
-      <c r="S26" s="318" t="n"/>
-      <c r="T26" s="300" t="inlineStr">
+      <c r="G26" s="397" t="n"/>
+      <c r="H26" s="397" t="n"/>
+      <c r="I26" s="397" t="n"/>
+      <c r="J26" s="397" t="n"/>
+      <c r="K26" s="397" t="n"/>
+      <c r="L26" s="397" t="n"/>
+      <c r="M26" s="397" t="n"/>
+      <c r="N26" s="397" t="n"/>
+      <c r="O26" s="397" t="n"/>
+      <c r="P26" s="397" t="n"/>
+      <c r="Q26" s="397" t="n"/>
+      <c r="R26" s="397" t="n"/>
+      <c r="S26" s="398" t="n"/>
+      <c r="T26" s="369" t="inlineStr">
         <is>
           <t>Evidence / Criteria</t>
         </is>
       </c>
-      <c r="U26" s="317" t="n"/>
-      <c r="V26" s="317" t="n"/>
-      <c r="W26" s="317" t="n"/>
-      <c r="X26" s="317" t="n"/>
-      <c r="Y26" s="317" t="n"/>
-      <c r="Z26" s="317" t="n"/>
-      <c r="AA26" s="317" t="n"/>
-      <c r="AB26" s="317" t="n"/>
-      <c r="AC26" s="317" t="n"/>
-      <c r="AD26" s="317" t="n"/>
-      <c r="AE26" s="318" t="n"/>
-      <c r="AF26" s="300" t="inlineStr">
+      <c r="U26" s="397" t="n"/>
+      <c r="V26" s="397" t="n"/>
+      <c r="W26" s="397" t="n"/>
+      <c r="X26" s="397" t="n"/>
+      <c r="Y26" s="397" t="n"/>
+      <c r="Z26" s="397" t="n"/>
+      <c r="AA26" s="397" t="n"/>
+      <c r="AB26" s="397" t="n"/>
+      <c r="AC26" s="397" t="n"/>
+      <c r="AD26" s="397" t="n"/>
+      <c r="AE26" s="398" t="n"/>
+      <c r="AF26" s="369" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="AG26" s="317" t="n"/>
-      <c r="AH26" s="317" t="n"/>
-      <c r="AI26" s="318" t="n"/>
-      <c r="AJ26" s="300" t="inlineStr">
+      <c r="AG26" s="397" t="n"/>
+      <c r="AH26" s="397" t="n"/>
+      <c r="AI26" s="398" t="n"/>
+      <c r="AJ26" s="369" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AK26" s="317" t="n"/>
-      <c r="AL26" s="318" t="n"/>
-      <c r="AM26" s="301" t="inlineStr">
+      <c r="AK26" s="397" t="n"/>
+      <c r="AL26" s="398" t="n"/>
+      <c r="AM26" s="369" t="inlineStr">
         <is>
           <t>Ref.</t>
         </is>
       </c>
-      <c r="AN26" s="319" t="n"/>
+      <c r="AN26" s="398" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1" s="329">
-      <c r="A27" s="293">
+      <c r="A27" s="370">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B27" s="323" t="n"/>
-      <c r="C27" s="302" t="inlineStr">
+      <c r="B27" s="402" t="n"/>
+      <c r="C27" s="371" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D27" s="322" t="n"/>
-      <c r="E27" s="323" t="n"/>
-      <c r="F27" s="303" t="n"/>
-      <c r="G27" s="322" t="n"/>
-      <c r="H27" s="322" t="n"/>
-      <c r="I27" s="322" t="n"/>
-      <c r="J27" s="322" t="n"/>
-      <c r="K27" s="322" t="n"/>
-      <c r="L27" s="322" t="n"/>
-      <c r="M27" s="322" t="n"/>
-      <c r="N27" s="322" t="n"/>
-      <c r="O27" s="322" t="n"/>
-      <c r="P27" s="322" t="n"/>
-      <c r="Q27" s="322" t="n"/>
-      <c r="R27" s="322" t="n"/>
-      <c r="S27" s="323" t="n"/>
-      <c r="T27" s="304" t="n"/>
-      <c r="U27" s="322" t="n"/>
-      <c r="V27" s="322" t="n"/>
-      <c r="W27" s="322" t="n"/>
-      <c r="X27" s="322" t="n"/>
-      <c r="Y27" s="322" t="n"/>
-      <c r="Z27" s="322" t="n"/>
-      <c r="AA27" s="322" t="n"/>
-      <c r="AB27" s="322" t="n"/>
-      <c r="AC27" s="322" t="n"/>
-      <c r="AD27" s="322" t="n"/>
-      <c r="AE27" s="323" t="n"/>
-      <c r="AF27" s="303" t="n"/>
-      <c r="AG27" s="322" t="n"/>
-      <c r="AH27" s="322" t="n"/>
-      <c r="AI27" s="323" t="n"/>
-      <c r="AJ27" s="303" t="n"/>
-      <c r="AK27" s="322" t="n"/>
-      <c r="AL27" s="323" t="n"/>
-      <c r="AM27" s="305" t="n"/>
-      <c r="AN27" s="324" t="n"/>
+      <c r="D27" s="401" t="n"/>
+      <c r="E27" s="402" t="n"/>
+      <c r="F27" s="372" t="n"/>
+      <c r="G27" s="401" t="n"/>
+      <c r="H27" s="401" t="n"/>
+      <c r="I27" s="401" t="n"/>
+      <c r="J27" s="401" t="n"/>
+      <c r="K27" s="401" t="n"/>
+      <c r="L27" s="401" t="n"/>
+      <c r="M27" s="401" t="n"/>
+      <c r="N27" s="401" t="n"/>
+      <c r="O27" s="401" t="n"/>
+      <c r="P27" s="401" t="n"/>
+      <c r="Q27" s="401" t="n"/>
+      <c r="R27" s="401" t="n"/>
+      <c r="S27" s="402" t="n"/>
+      <c r="T27" s="373" t="n"/>
+      <c r="U27" s="401" t="n"/>
+      <c r="V27" s="401" t="n"/>
+      <c r="W27" s="401" t="n"/>
+      <c r="X27" s="401" t="n"/>
+      <c r="Y27" s="401" t="n"/>
+      <c r="Z27" s="401" t="n"/>
+      <c r="AA27" s="401" t="n"/>
+      <c r="AB27" s="401" t="n"/>
+      <c r="AC27" s="401" t="n"/>
+      <c r="AD27" s="401" t="n"/>
+      <c r="AE27" s="402" t="n"/>
+      <c r="AF27" s="372" t="n"/>
+      <c r="AG27" s="401" t="n"/>
+      <c r="AH27" s="401" t="n"/>
+      <c r="AI27" s="402" t="n"/>
+      <c r="AJ27" s="372" t="n"/>
+      <c r="AK27" s="401" t="n"/>
+      <c r="AL27" s="402" t="n"/>
+      <c r="AM27" s="374" t="n"/>
+      <c r="AN27" s="402" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1" s="329">
-      <c r="A28" s="293">
+      <c r="A28" s="370">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B28" s="323" t="n"/>
-      <c r="C28" s="302" t="inlineStr">
+      <c r="B28" s="402" t="n"/>
+      <c r="C28" s="371" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D28" s="322" t="n"/>
-      <c r="E28" s="323" t="n"/>
-      <c r="F28" s="303" t="n"/>
-      <c r="G28" s="322" t="n"/>
-      <c r="H28" s="322" t="n"/>
-      <c r="I28" s="322" t="n"/>
-      <c r="J28" s="322" t="n"/>
-      <c r="K28" s="322" t="n"/>
-      <c r="L28" s="322" t="n"/>
-      <c r="M28" s="322" t="n"/>
-      <c r="N28" s="322" t="n"/>
-      <c r="O28" s="322" t="n"/>
-      <c r="P28" s="322" t="n"/>
-      <c r="Q28" s="322" t="n"/>
-      <c r="R28" s="322" t="n"/>
-      <c r="S28" s="323" t="n"/>
-      <c r="T28" s="304" t="n"/>
-      <c r="U28" s="322" t="n"/>
-      <c r="V28" s="322" t="n"/>
-      <c r="W28" s="322" t="n"/>
-      <c r="X28" s="322" t="n"/>
-      <c r="Y28" s="322" t="n"/>
-      <c r="Z28" s="322" t="n"/>
-      <c r="AA28" s="322" t="n"/>
-      <c r="AB28" s="322" t="n"/>
-      <c r="AC28" s="322" t="n"/>
-      <c r="AD28" s="322" t="n"/>
-      <c r="AE28" s="323" t="n"/>
-      <c r="AF28" s="303" t="n"/>
-      <c r="AG28" s="322" t="n"/>
-      <c r="AH28" s="322" t="n"/>
-      <c r="AI28" s="323" t="n"/>
-      <c r="AJ28" s="303" t="n"/>
-      <c r="AK28" s="322" t="n"/>
-      <c r="AL28" s="323" t="n"/>
-      <c r="AM28" s="305" t="n"/>
-      <c r="AN28" s="324" t="n"/>
+      <c r="D28" s="401" t="n"/>
+      <c r="E28" s="402" t="n"/>
+      <c r="F28" s="372" t="n"/>
+      <c r="G28" s="401" t="n"/>
+      <c r="H28" s="401" t="n"/>
+      <c r="I28" s="401" t="n"/>
+      <c r="J28" s="401" t="n"/>
+      <c r="K28" s="401" t="n"/>
+      <c r="L28" s="401" t="n"/>
+      <c r="M28" s="401" t="n"/>
+      <c r="N28" s="401" t="n"/>
+      <c r="O28" s="401" t="n"/>
+      <c r="P28" s="401" t="n"/>
+      <c r="Q28" s="401" t="n"/>
+      <c r="R28" s="401" t="n"/>
+      <c r="S28" s="402" t="n"/>
+      <c r="T28" s="373" t="n"/>
+      <c r="U28" s="401" t="n"/>
+      <c r="V28" s="401" t="n"/>
+      <c r="W28" s="401" t="n"/>
+      <c r="X28" s="401" t="n"/>
+      <c r="Y28" s="401" t="n"/>
+      <c r="Z28" s="401" t="n"/>
+      <c r="AA28" s="401" t="n"/>
+      <c r="AB28" s="401" t="n"/>
+      <c r="AC28" s="401" t="n"/>
+      <c r="AD28" s="401" t="n"/>
+      <c r="AE28" s="402" t="n"/>
+      <c r="AF28" s="372" t="n"/>
+      <c r="AG28" s="401" t="n"/>
+      <c r="AH28" s="401" t="n"/>
+      <c r="AI28" s="402" t="n"/>
+      <c r="AJ28" s="372" t="n"/>
+      <c r="AK28" s="401" t="n"/>
+      <c r="AL28" s="402" t="n"/>
+      <c r="AM28" s="374" t="n"/>
+      <c r="AN28" s="402" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1" s="329">
-      <c r="A29" s="293">
+      <c r="A29" s="370">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B29" s="323" t="n"/>
-      <c r="C29" s="302" t="inlineStr">
+      <c r="B29" s="402" t="n"/>
+      <c r="C29" s="371" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D29" s="322" t="n"/>
-      <c r="E29" s="323" t="n"/>
-      <c r="F29" s="303" t="n"/>
-      <c r="G29" s="322" t="n"/>
-      <c r="H29" s="322" t="n"/>
-      <c r="I29" s="322" t="n"/>
-      <c r="J29" s="322" t="n"/>
-      <c r="K29" s="322" t="n"/>
-      <c r="L29" s="322" t="n"/>
-      <c r="M29" s="322" t="n"/>
-      <c r="N29" s="322" t="n"/>
-      <c r="O29" s="322" t="n"/>
-      <c r="P29" s="322" t="n"/>
-      <c r="Q29" s="322" t="n"/>
-      <c r="R29" s="322" t="n"/>
-      <c r="S29" s="323" t="n"/>
-      <c r="T29" s="304" t="n"/>
-      <c r="U29" s="322" t="n"/>
-      <c r="V29" s="322" t="n"/>
-      <c r="W29" s="322" t="n"/>
-      <c r="X29" s="322" t="n"/>
-      <c r="Y29" s="322" t="n"/>
-      <c r="Z29" s="322" t="n"/>
-      <c r="AA29" s="322" t="n"/>
-      <c r="AB29" s="322" t="n"/>
-      <c r="AC29" s="322" t="n"/>
-      <c r="AD29" s="322" t="n"/>
-      <c r="AE29" s="323" t="n"/>
-      <c r="AF29" s="303" t="n"/>
-      <c r="AG29" s="322" t="n"/>
-      <c r="AH29" s="322" t="n"/>
-      <c r="AI29" s="323" t="n"/>
-      <c r="AJ29" s="303" t="n"/>
-      <c r="AK29" s="322" t="n"/>
-      <c r="AL29" s="323" t="n"/>
-      <c r="AM29" s="305" t="n"/>
-      <c r="AN29" s="324" t="n"/>
+      <c r="D29" s="401" t="n"/>
+      <c r="E29" s="402" t="n"/>
+      <c r="F29" s="372" t="n"/>
+      <c r="G29" s="401" t="n"/>
+      <c r="H29" s="401" t="n"/>
+      <c r="I29" s="401" t="n"/>
+      <c r="J29" s="401" t="n"/>
+      <c r="K29" s="401" t="n"/>
+      <c r="L29" s="401" t="n"/>
+      <c r="M29" s="401" t="n"/>
+      <c r="N29" s="401" t="n"/>
+      <c r="O29" s="401" t="n"/>
+      <c r="P29" s="401" t="n"/>
+      <c r="Q29" s="401" t="n"/>
+      <c r="R29" s="401" t="n"/>
+      <c r="S29" s="402" t="n"/>
+      <c r="T29" s="373" t="n"/>
+      <c r="U29" s="401" t="n"/>
+      <c r="V29" s="401" t="n"/>
+      <c r="W29" s="401" t="n"/>
+      <c r="X29" s="401" t="n"/>
+      <c r="Y29" s="401" t="n"/>
+      <c r="Z29" s="401" t="n"/>
+      <c r="AA29" s="401" t="n"/>
+      <c r="AB29" s="401" t="n"/>
+      <c r="AC29" s="401" t="n"/>
+      <c r="AD29" s="401" t="n"/>
+      <c r="AE29" s="402" t="n"/>
+      <c r="AF29" s="372" t="n"/>
+      <c r="AG29" s="401" t="n"/>
+      <c r="AH29" s="401" t="n"/>
+      <c r="AI29" s="402" t="n"/>
+      <c r="AJ29" s="372" t="n"/>
+      <c r="AK29" s="401" t="n"/>
+      <c r="AL29" s="402" t="n"/>
+      <c r="AM29" s="374" t="n"/>
+      <c r="AN29" s="402" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1" s="329">
-      <c r="A30" s="293">
+      <c r="A30" s="370">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B30" s="323" t="n"/>
-      <c r="C30" s="302" t="inlineStr">
+      <c r="B30" s="402" t="n"/>
+      <c r="C30" s="371" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D30" s="322" t="n"/>
-      <c r="E30" s="323" t="n"/>
-      <c r="F30" s="303" t="n"/>
-      <c r="G30" s="322" t="n"/>
-      <c r="H30" s="322" t="n"/>
-      <c r="I30" s="322" t="n"/>
-      <c r="J30" s="322" t="n"/>
-      <c r="K30" s="322" t="n"/>
-      <c r="L30" s="322" t="n"/>
-      <c r="M30" s="322" t="n"/>
-      <c r="N30" s="322" t="n"/>
-      <c r="O30" s="322" t="n"/>
-      <c r="P30" s="322" t="n"/>
-      <c r="Q30" s="322" t="n"/>
-      <c r="R30" s="322" t="n"/>
-      <c r="S30" s="323" t="n"/>
-      <c r="T30" s="304" t="n"/>
-      <c r="U30" s="322" t="n"/>
-      <c r="V30" s="322" t="n"/>
-      <c r="W30" s="322" t="n"/>
-      <c r="X30" s="322" t="n"/>
-      <c r="Y30" s="322" t="n"/>
-      <c r="Z30" s="322" t="n"/>
-      <c r="AA30" s="322" t="n"/>
-      <c r="AB30" s="322" t="n"/>
-      <c r="AC30" s="322" t="n"/>
-      <c r="AD30" s="322" t="n"/>
-      <c r="AE30" s="323" t="n"/>
-      <c r="AF30" s="303" t="n"/>
-      <c r="AG30" s="322" t="n"/>
-      <c r="AH30" s="322" t="n"/>
-      <c r="AI30" s="323" t="n"/>
-      <c r="AJ30" s="303" t="n"/>
-      <c r="AK30" s="322" t="n"/>
-      <c r="AL30" s="323" t="n"/>
-      <c r="AM30" s="305" t="n"/>
-      <c r="AN30" s="324" t="n"/>
+      <c r="D30" s="401" t="n"/>
+      <c r="E30" s="402" t="n"/>
+      <c r="F30" s="372" t="n"/>
+      <c r="G30" s="401" t="n"/>
+      <c r="H30" s="401" t="n"/>
+      <c r="I30" s="401" t="n"/>
+      <c r="J30" s="401" t="n"/>
+      <c r="K30" s="401" t="n"/>
+      <c r="L30" s="401" t="n"/>
+      <c r="M30" s="401" t="n"/>
+      <c r="N30" s="401" t="n"/>
+      <c r="O30" s="401" t="n"/>
+      <c r="P30" s="401" t="n"/>
+      <c r="Q30" s="401" t="n"/>
+      <c r="R30" s="401" t="n"/>
+      <c r="S30" s="402" t="n"/>
+      <c r="T30" s="373" t="n"/>
+      <c r="U30" s="401" t="n"/>
+      <c r="V30" s="401" t="n"/>
+      <c r="W30" s="401" t="n"/>
+      <c r="X30" s="401" t="n"/>
+      <c r="Y30" s="401" t="n"/>
+      <c r="Z30" s="401" t="n"/>
+      <c r="AA30" s="401" t="n"/>
+      <c r="AB30" s="401" t="n"/>
+      <c r="AC30" s="401" t="n"/>
+      <c r="AD30" s="401" t="n"/>
+      <c r="AE30" s="402" t="n"/>
+      <c r="AF30" s="372" t="n"/>
+      <c r="AG30" s="401" t="n"/>
+      <c r="AH30" s="401" t="n"/>
+      <c r="AI30" s="402" t="n"/>
+      <c r="AJ30" s="372" t="n"/>
+      <c r="AK30" s="401" t="n"/>
+      <c r="AL30" s="402" t="n"/>
+      <c r="AM30" s="374" t="n"/>
+      <c r="AN30" s="402" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1" s="329">
-      <c r="A31" s="293">
+      <c r="A31" s="370">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B31" s="323" t="n"/>
-      <c r="C31" s="302" t="inlineStr">
+      <c r="B31" s="402" t="n"/>
+      <c r="C31" s="371" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D31" s="322" t="n"/>
-      <c r="E31" s="323" t="n"/>
-      <c r="F31" s="303" t="n"/>
-      <c r="G31" s="322" t="n"/>
-      <c r="H31" s="322" t="n"/>
-      <c r="I31" s="322" t="n"/>
-      <c r="J31" s="322" t="n"/>
-      <c r="K31" s="322" t="n"/>
-      <c r="L31" s="322" t="n"/>
-      <c r="M31" s="322" t="n"/>
-      <c r="N31" s="322" t="n"/>
-      <c r="O31" s="322" t="n"/>
-      <c r="P31" s="322" t="n"/>
-      <c r="Q31" s="322" t="n"/>
-      <c r="R31" s="322" t="n"/>
-      <c r="S31" s="323" t="n"/>
-      <c r="T31" s="304" t="n"/>
-      <c r="U31" s="322" t="n"/>
-      <c r="V31" s="322" t="n"/>
-      <c r="W31" s="322" t="n"/>
-      <c r="X31" s="322" t="n"/>
-      <c r="Y31" s="322" t="n"/>
-      <c r="Z31" s="322" t="n"/>
-      <c r="AA31" s="322" t="n"/>
-      <c r="AB31" s="322" t="n"/>
-      <c r="AC31" s="322" t="n"/>
-      <c r="AD31" s="322" t="n"/>
-      <c r="AE31" s="323" t="n"/>
-      <c r="AF31" s="303" t="n"/>
-      <c r="AG31" s="322" t="n"/>
-      <c r="AH31" s="322" t="n"/>
-      <c r="AI31" s="323" t="n"/>
-      <c r="AJ31" s="303" t="n"/>
-      <c r="AK31" s="322" t="n"/>
-      <c r="AL31" s="323" t="n"/>
-      <c r="AM31" s="305" t="n"/>
-      <c r="AN31" s="324" t="n"/>
+      <c r="D31" s="401" t="n"/>
+      <c r="E31" s="402" t="n"/>
+      <c r="F31" s="372" t="n"/>
+      <c r="G31" s="401" t="n"/>
+      <c r="H31" s="401" t="n"/>
+      <c r="I31" s="401" t="n"/>
+      <c r="J31" s="401" t="n"/>
+      <c r="K31" s="401" t="n"/>
+      <c r="L31" s="401" t="n"/>
+      <c r="M31" s="401" t="n"/>
+      <c r="N31" s="401" t="n"/>
+      <c r="O31" s="401" t="n"/>
+      <c r="P31" s="401" t="n"/>
+      <c r="Q31" s="401" t="n"/>
+      <c r="R31" s="401" t="n"/>
+      <c r="S31" s="402" t="n"/>
+      <c r="T31" s="373" t="n"/>
+      <c r="U31" s="401" t="n"/>
+      <c r="V31" s="401" t="n"/>
+      <c r="W31" s="401" t="n"/>
+      <c r="X31" s="401" t="n"/>
+      <c r="Y31" s="401" t="n"/>
+      <c r="Z31" s="401" t="n"/>
+      <c r="AA31" s="401" t="n"/>
+      <c r="AB31" s="401" t="n"/>
+      <c r="AC31" s="401" t="n"/>
+      <c r="AD31" s="401" t="n"/>
+      <c r="AE31" s="402" t="n"/>
+      <c r="AF31" s="372" t="n"/>
+      <c r="AG31" s="401" t="n"/>
+      <c r="AH31" s="401" t="n"/>
+      <c r="AI31" s="402" t="n"/>
+      <c r="AJ31" s="372" t="n"/>
+      <c r="AK31" s="401" t="n"/>
+      <c r="AL31" s="402" t="n"/>
+      <c r="AM31" s="374" t="n"/>
+      <c r="AN31" s="402" t="n"/>
     </row>
     <row r="32" ht="20" customHeight="1" s="329">
-      <c r="A32" s="293">
+      <c r="A32" s="370">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B32" s="323" t="n"/>
-      <c r="C32" s="302" t="inlineStr">
+      <c r="B32" s="402" t="n"/>
+      <c r="C32" s="371" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D32" s="322" t="n"/>
-      <c r="E32" s="323" t="n"/>
-      <c r="F32" s="303" t="n"/>
-      <c r="G32" s="322" t="n"/>
-      <c r="H32" s="322" t="n"/>
-      <c r="I32" s="322" t="n"/>
-      <c r="J32" s="322" t="n"/>
-      <c r="K32" s="322" t="n"/>
-      <c r="L32" s="322" t="n"/>
-      <c r="M32" s="322" t="n"/>
-      <c r="N32" s="322" t="n"/>
-      <c r="O32" s="322" t="n"/>
-      <c r="P32" s="322" t="n"/>
-      <c r="Q32" s="322" t="n"/>
-      <c r="R32" s="322" t="n"/>
-      <c r="S32" s="323" t="n"/>
-      <c r="T32" s="304" t="n"/>
-      <c r="U32" s="322" t="n"/>
-      <c r="V32" s="322" t="n"/>
-      <c r="W32" s="322" t="n"/>
-      <c r="X32" s="322" t="n"/>
-      <c r="Y32" s="322" t="n"/>
-      <c r="Z32" s="322" t="n"/>
-      <c r="AA32" s="322" t="n"/>
-      <c r="AB32" s="322" t="n"/>
-      <c r="AC32" s="322" t="n"/>
-      <c r="AD32" s="322" t="n"/>
-      <c r="AE32" s="323" t="n"/>
-      <c r="AF32" s="303" t="n"/>
-      <c r="AG32" s="322" t="n"/>
-      <c r="AH32" s="322" t="n"/>
-      <c r="AI32" s="323" t="n"/>
-      <c r="AJ32" s="303" t="n"/>
-      <c r="AK32" s="322" t="n"/>
-      <c r="AL32" s="323" t="n"/>
-      <c r="AM32" s="305" t="n"/>
-      <c r="AN32" s="324" t="n"/>
+      <c r="D32" s="401" t="n"/>
+      <c r="E32" s="402" t="n"/>
+      <c r="F32" s="372" t="n"/>
+      <c r="G32" s="401" t="n"/>
+      <c r="H32" s="401" t="n"/>
+      <c r="I32" s="401" t="n"/>
+      <c r="J32" s="401" t="n"/>
+      <c r="K32" s="401" t="n"/>
+      <c r="L32" s="401" t="n"/>
+      <c r="M32" s="401" t="n"/>
+      <c r="N32" s="401" t="n"/>
+      <c r="O32" s="401" t="n"/>
+      <c r="P32" s="401" t="n"/>
+      <c r="Q32" s="401" t="n"/>
+      <c r="R32" s="401" t="n"/>
+      <c r="S32" s="402" t="n"/>
+      <c r="T32" s="373" t="n"/>
+      <c r="U32" s="401" t="n"/>
+      <c r="V32" s="401" t="n"/>
+      <c r="W32" s="401" t="n"/>
+      <c r="X32" s="401" t="n"/>
+      <c r="Y32" s="401" t="n"/>
+      <c r="Z32" s="401" t="n"/>
+      <c r="AA32" s="401" t="n"/>
+      <c r="AB32" s="401" t="n"/>
+      <c r="AC32" s="401" t="n"/>
+      <c r="AD32" s="401" t="n"/>
+      <c r="AE32" s="402" t="n"/>
+      <c r="AF32" s="372" t="n"/>
+      <c r="AG32" s="401" t="n"/>
+      <c r="AH32" s="401" t="n"/>
+      <c r="AI32" s="402" t="n"/>
+      <c r="AJ32" s="372" t="n"/>
+      <c r="AK32" s="401" t="n"/>
+      <c r="AL32" s="402" t="n"/>
+      <c r="AM32" s="374" t="n"/>
+      <c r="AN32" s="402" t="n"/>
     </row>
     <row r="33" ht="4" customHeight="1" s="329">
-      <c r="A33" s="284" t="n"/>
+      <c r="A33" s="357" t="n"/>
+      <c r="B33" s="350" t="n"/>
+      <c r="C33" s="350" t="n"/>
+      <c r="D33" s="350" t="n"/>
+      <c r="E33" s="350" t="n"/>
+      <c r="F33" s="350" t="n"/>
+      <c r="G33" s="350" t="n"/>
+      <c r="H33" s="350" t="n"/>
+      <c r="I33" s="350" t="n"/>
+      <c r="J33" s="350" t="n"/>
+      <c r="K33" s="350" t="n"/>
+      <c r="L33" s="350" t="n"/>
+      <c r="M33" s="350" t="n"/>
+      <c r="N33" s="350" t="n"/>
+      <c r="O33" s="350" t="n"/>
+      <c r="P33" s="350" t="n"/>
+      <c r="Q33" s="350" t="n"/>
+      <c r="R33" s="350" t="n"/>
+      <c r="S33" s="350" t="n"/>
+      <c r="T33" s="350" t="n"/>
+      <c r="U33" s="350" t="n"/>
+      <c r="V33" s="350" t="n"/>
+      <c r="W33" s="350" t="n"/>
+      <c r="X33" s="350" t="n"/>
+      <c r="Y33" s="350" t="n"/>
+      <c r="Z33" s="350" t="n"/>
+      <c r="AA33" s="350" t="n"/>
+      <c r="AB33" s="350" t="n"/>
+      <c r="AC33" s="350" t="n"/>
+      <c r="AD33" s="350" t="n"/>
+      <c r="AE33" s="350" t="n"/>
+      <c r="AF33" s="350" t="n"/>
+      <c r="AG33" s="350" t="n"/>
+      <c r="AH33" s="350" t="n"/>
+      <c r="AI33" s="350" t="n"/>
+      <c r="AJ33" s="350" t="n"/>
+      <c r="AK33" s="350" t="n"/>
+      <c r="AL33" s="350" t="n"/>
+      <c r="AM33" s="350" t="n"/>
+      <c r="AN33" s="350" t="n"/>
     </row>
-    <row r="34" ht="17" customHeight="1" s="329">
-      <c r="A34" s="284" t="inlineStr">
+    <row r="34" ht="20" customHeight="1" s="329">
+      <c r="A34" s="351" t="inlineStr">
         <is>
           <t xml:space="preserve">  4. FINAL DECISION / CLOSURE</t>
         </is>
       </c>
-      <c r="B34" s="285" t="n"/>
-      <c r="C34" s="285" t="n"/>
-      <c r="D34" s="285" t="n"/>
-      <c r="E34" s="285" t="n"/>
-      <c r="F34" s="285" t="n"/>
-      <c r="G34" s="285" t="n"/>
-      <c r="H34" s="285" t="n"/>
-      <c r="I34" s="285" t="n"/>
-      <c r="J34" s="285" t="n"/>
-      <c r="K34" s="285" t="n"/>
-      <c r="L34" s="285" t="n"/>
-      <c r="M34" s="285" t="n"/>
-      <c r="N34" s="285" t="n"/>
-      <c r="O34" s="285" t="n"/>
-      <c r="P34" s="285" t="n"/>
-      <c r="Q34" s="285" t="n"/>
-      <c r="R34" s="285" t="n"/>
-      <c r="S34" s="285" t="n"/>
-      <c r="T34" s="285" t="n"/>
-      <c r="U34" s="285" t="n"/>
-      <c r="V34" s="285" t="n"/>
-      <c r="W34" s="285" t="n"/>
-      <c r="X34" s="285" t="n"/>
-      <c r="Y34" s="285" t="n"/>
-      <c r="Z34" s="285" t="n"/>
-      <c r="AA34" s="285" t="n"/>
-      <c r="AB34" s="285" t="n"/>
-      <c r="AC34" s="285" t="n"/>
-      <c r="AD34" s="285" t="n"/>
-      <c r="AE34" s="285" t="n"/>
-      <c r="AF34" s="285" t="n"/>
-      <c r="AG34" s="285" t="n"/>
-      <c r="AH34" s="285" t="n"/>
-      <c r="AI34" s="285" t="n"/>
-      <c r="AJ34" s="285" t="n"/>
-      <c r="AK34" s="285" t="n"/>
-      <c r="AL34" s="285" t="n"/>
-      <c r="AM34" s="285" t="n"/>
-      <c r="AN34" s="286" t="n"/>
+      <c r="B34" s="397" t="n"/>
+      <c r="C34" s="397" t="n"/>
+      <c r="D34" s="397" t="n"/>
+      <c r="E34" s="397" t="n"/>
+      <c r="F34" s="397" t="n"/>
+      <c r="G34" s="397" t="n"/>
+      <c r="H34" s="397" t="n"/>
+      <c r="I34" s="397" t="n"/>
+      <c r="J34" s="397" t="n"/>
+      <c r="K34" s="397" t="n"/>
+      <c r="L34" s="397" t="n"/>
+      <c r="M34" s="397" t="n"/>
+      <c r="N34" s="397" t="n"/>
+      <c r="O34" s="397" t="n"/>
+      <c r="P34" s="397" t="n"/>
+      <c r="Q34" s="397" t="n"/>
+      <c r="R34" s="397" t="n"/>
+      <c r="S34" s="397" t="n"/>
+      <c r="T34" s="397" t="n"/>
+      <c r="U34" s="397" t="n"/>
+      <c r="V34" s="397" t="n"/>
+      <c r="W34" s="397" t="n"/>
+      <c r="X34" s="397" t="n"/>
+      <c r="Y34" s="397" t="n"/>
+      <c r="Z34" s="397" t="n"/>
+      <c r="AA34" s="397" t="n"/>
+      <c r="AB34" s="397" t="n"/>
+      <c r="AC34" s="397" t="n"/>
+      <c r="AD34" s="397" t="n"/>
+      <c r="AE34" s="397" t="n"/>
+      <c r="AF34" s="397" t="n"/>
+      <c r="AG34" s="397" t="n"/>
+      <c r="AH34" s="397" t="n"/>
+      <c r="AI34" s="397" t="n"/>
+      <c r="AJ34" s="397" t="n"/>
+      <c r="AK34" s="397" t="n"/>
+      <c r="AL34" s="397" t="n"/>
+      <c r="AM34" s="397" t="n"/>
+      <c r="AN34" s="398" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1" s="329">
-      <c r="A35" s="287" t="inlineStr">
+      <c r="A35" s="352" t="inlineStr">
         <is>
           <t>Final Decision</t>
         </is>
       </c>
-      <c r="B35" s="317" t="n"/>
-      <c r="C35" s="317" t="n"/>
-      <c r="D35" s="317" t="n"/>
-      <c r="E35" s="317" t="n"/>
-      <c r="F35" s="317" t="n"/>
-      <c r="G35" s="318" t="n"/>
-      <c r="H35" s="288" t="n"/>
-      <c r="I35" s="317" t="n"/>
-      <c r="J35" s="317" t="n"/>
-      <c r="K35" s="317" t="n"/>
-      <c r="L35" s="317" t="n"/>
-      <c r="M35" s="317" t="n"/>
-      <c r="N35" s="317" t="n"/>
-      <c r="O35" s="317" t="n"/>
-      <c r="P35" s="317" t="n"/>
-      <c r="Q35" s="317" t="n"/>
-      <c r="R35" s="317" t="n"/>
-      <c r="S35" s="317" t="n"/>
-      <c r="T35" s="318" t="n"/>
-      <c r="U35" s="289" t="inlineStr">
+      <c r="B35" s="397" t="n"/>
+      <c r="C35" s="397" t="n"/>
+      <c r="D35" s="397" t="n"/>
+      <c r="E35" s="397" t="n"/>
+      <c r="F35" s="397" t="n"/>
+      <c r="G35" s="398" t="n"/>
+      <c r="H35" s="355" t="n"/>
+      <c r="I35" s="397" t="n"/>
+      <c r="J35" s="397" t="n"/>
+      <c r="K35" s="397" t="n"/>
+      <c r="L35" s="397" t="n"/>
+      <c r="M35" s="397" t="n"/>
+      <c r="N35" s="397" t="n"/>
+      <c r="O35" s="397" t="n"/>
+      <c r="P35" s="397" t="n"/>
+      <c r="Q35" s="397" t="n"/>
+      <c r="R35" s="397" t="n"/>
+      <c r="S35" s="397" t="n"/>
+      <c r="T35" s="398" t="n"/>
+      <c r="U35" s="356" t="inlineStr">
         <is>
           <t>Reviewed by</t>
         </is>
       </c>
-      <c r="V35" s="317" t="n"/>
-      <c r="W35" s="317" t="n"/>
-      <c r="X35" s="317" t="n"/>
-      <c r="Y35" s="317" t="n"/>
-      <c r="Z35" s="317" t="n"/>
-      <c r="AA35" s="318" t="n"/>
-      <c r="AB35" s="290" t="n"/>
-      <c r="AC35" s="317" t="n"/>
-      <c r="AD35" s="317" t="n"/>
-      <c r="AE35" s="317" t="n"/>
-      <c r="AF35" s="317" t="n"/>
-      <c r="AG35" s="317" t="n"/>
-      <c r="AH35" s="317" t="n"/>
-      <c r="AI35" s="317" t="n"/>
-      <c r="AJ35" s="317" t="n"/>
-      <c r="AK35" s="317" t="n"/>
-      <c r="AL35" s="317" t="n"/>
-      <c r="AM35" s="317" t="n"/>
-      <c r="AN35" s="319" t="n"/>
+      <c r="V35" s="397" t="n"/>
+      <c r="W35" s="397" t="n"/>
+      <c r="X35" s="397" t="n"/>
+      <c r="Y35" s="397" t="n"/>
+      <c r="Z35" s="397" t="n"/>
+      <c r="AA35" s="398" t="n"/>
+      <c r="AB35" s="355" t="n"/>
+      <c r="AC35" s="397" t="n"/>
+      <c r="AD35" s="397" t="n"/>
+      <c r="AE35" s="397" t="n"/>
+      <c r="AF35" s="397" t="n"/>
+      <c r="AG35" s="397" t="n"/>
+      <c r="AH35" s="397" t="n"/>
+      <c r="AI35" s="397" t="n"/>
+      <c r="AJ35" s="397" t="n"/>
+      <c r="AK35" s="397" t="n"/>
+      <c r="AL35" s="397" t="n"/>
+      <c r="AM35" s="397" t="n"/>
+      <c r="AN35" s="398" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1" s="329">
-      <c r="A36" s="287" t="inlineStr">
+      <c r="A36" s="352" t="inlineStr">
         <is>
           <t>Containment Required (YES/NO)</t>
         </is>
       </c>
-      <c r="B36" s="317" t="n"/>
-      <c r="C36" s="317" t="n"/>
-      <c r="D36" s="317" t="n"/>
-      <c r="E36" s="317" t="n"/>
-      <c r="F36" s="317" t="n"/>
-      <c r="G36" s="318" t="n"/>
-      <c r="H36" s="288" t="n"/>
-      <c r="I36" s="317" t="n"/>
-      <c r="J36" s="317" t="n"/>
-      <c r="K36" s="317" t="n"/>
-      <c r="L36" s="317" t="n"/>
-      <c r="M36" s="317" t="n"/>
-      <c r="N36" s="317" t="n"/>
-      <c r="O36" s="317" t="n"/>
-      <c r="P36" s="317" t="n"/>
-      <c r="Q36" s="317" t="n"/>
-      <c r="R36" s="317" t="n"/>
-      <c r="S36" s="317" t="n"/>
-      <c r="T36" s="318" t="n"/>
-      <c r="U36" s="289" t="inlineStr">
+      <c r="B36" s="397" t="n"/>
+      <c r="C36" s="397" t="n"/>
+      <c r="D36" s="397" t="n"/>
+      <c r="E36" s="397" t="n"/>
+      <c r="F36" s="397" t="n"/>
+      <c r="G36" s="398" t="n"/>
+      <c r="H36" s="355" t="n"/>
+      <c r="I36" s="397" t="n"/>
+      <c r="J36" s="397" t="n"/>
+      <c r="K36" s="397" t="n"/>
+      <c r="L36" s="397" t="n"/>
+      <c r="M36" s="397" t="n"/>
+      <c r="N36" s="397" t="n"/>
+      <c r="O36" s="397" t="n"/>
+      <c r="P36" s="397" t="n"/>
+      <c r="Q36" s="397" t="n"/>
+      <c r="R36" s="397" t="n"/>
+      <c r="S36" s="397" t="n"/>
+      <c r="T36" s="398" t="n"/>
+      <c r="U36" s="356" t="inlineStr">
         <is>
           <t>Target Closeout</t>
         </is>
       </c>
-      <c r="V36" s="317" t="n"/>
-      <c r="W36" s="317" t="n"/>
-      <c r="X36" s="317" t="n"/>
-      <c r="Y36" s="317" t="n"/>
-      <c r="Z36" s="317" t="n"/>
-      <c r="AA36" s="318" t="n"/>
-      <c r="AB36" s="290" t="n"/>
-      <c r="AC36" s="317" t="n"/>
-      <c r="AD36" s="317" t="n"/>
-      <c r="AE36" s="317" t="n"/>
-      <c r="AF36" s="317" t="n"/>
-      <c r="AG36" s="317" t="n"/>
-      <c r="AH36" s="317" t="n"/>
-      <c r="AI36" s="317" t="n"/>
-      <c r="AJ36" s="317" t="n"/>
-      <c r="AK36" s="317" t="n"/>
-      <c r="AL36" s="317" t="n"/>
-      <c r="AM36" s="317" t="n"/>
-      <c r="AN36" s="319" t="n"/>
+      <c r="V36" s="397" t="n"/>
+      <c r="W36" s="397" t="n"/>
+      <c r="X36" s="397" t="n"/>
+      <c r="Y36" s="397" t="n"/>
+      <c r="Z36" s="397" t="n"/>
+      <c r="AA36" s="398" t="n"/>
+      <c r="AB36" s="355" t="n"/>
+      <c r="AC36" s="397" t="n"/>
+      <c r="AD36" s="397" t="n"/>
+      <c r="AE36" s="397" t="n"/>
+      <c r="AF36" s="397" t="n"/>
+      <c r="AG36" s="397" t="n"/>
+      <c r="AH36" s="397" t="n"/>
+      <c r="AI36" s="397" t="n"/>
+      <c r="AJ36" s="397" t="n"/>
+      <c r="AK36" s="397" t="n"/>
+      <c r="AL36" s="397" t="n"/>
+      <c r="AM36" s="397" t="n"/>
+      <c r="AN36" s="398" t="n"/>
     </row>
     <row r="37" ht="4" customHeight="1" s="329">
-      <c r="A37" s="293" t="n"/>
-      <c r="C37" s="303" t="n"/>
-      <c r="M37" s="303" t="n"/>
-      <c r="Y37" s="297" t="n"/>
-      <c r="AD37" s="297" t="n"/>
-      <c r="AI37" s="297" t="n"/>
-      <c r="AL37" s="306" t="n"/>
+      <c r="A37" s="362" t="n"/>
+      <c r="B37" s="350" t="n"/>
+      <c r="C37" s="364" t="n"/>
+      <c r="D37" s="350" t="n"/>
+      <c r="E37" s="350" t="n"/>
+      <c r="F37" s="350" t="n"/>
+      <c r="G37" s="350" t="n"/>
+      <c r="H37" s="350" t="n"/>
+      <c r="I37" s="350" t="n"/>
+      <c r="J37" s="350" t="n"/>
+      <c r="K37" s="350" t="n"/>
+      <c r="L37" s="350" t="n"/>
+      <c r="M37" s="364" t="n"/>
+      <c r="N37" s="350" t="n"/>
+      <c r="O37" s="350" t="n"/>
+      <c r="P37" s="350" t="n"/>
+      <c r="Q37" s="350" t="n"/>
+      <c r="R37" s="350" t="n"/>
+      <c r="S37" s="350" t="n"/>
+      <c r="T37" s="350" t="n"/>
+      <c r="U37" s="350" t="n"/>
+      <c r="V37" s="350" t="n"/>
+      <c r="W37" s="350" t="n"/>
+      <c r="X37" s="350" t="n"/>
+      <c r="Y37" s="366" t="n"/>
+      <c r="Z37" s="350" t="n"/>
+      <c r="AA37" s="350" t="n"/>
+      <c r="AB37" s="350" t="n"/>
+      <c r="AC37" s="350" t="n"/>
+      <c r="AD37" s="366" t="n"/>
+      <c r="AE37" s="350" t="n"/>
+      <c r="AF37" s="350" t="n"/>
+      <c r="AG37" s="350" t="n"/>
+      <c r="AH37" s="350" t="n"/>
+      <c r="AI37" s="366" t="n"/>
+      <c r="AJ37" s="350" t="n"/>
+      <c r="AK37" s="350" t="n"/>
+      <c r="AL37" s="366" t="n"/>
+      <c r="AM37" s="350" t="n"/>
+      <c r="AN37" s="350" t="n"/>
     </row>
-    <row r="38" ht="17" customHeight="1" s="329">
-      <c r="A38" s="284" t="inlineStr">
+    <row r="38" ht="20" customHeight="1" s="329">
+      <c r="A38" s="351" t="inlineStr">
         <is>
           <t xml:space="preserve">  5. APPROVAL / SIGN-OFF</t>
         </is>
       </c>
-      <c r="B38" s="285" t="n"/>
-      <c r="C38" s="285" t="n"/>
-      <c r="D38" s="285" t="n"/>
-      <c r="E38" s="285" t="n"/>
-      <c r="F38" s="285" t="n"/>
-      <c r="G38" s="285" t="n"/>
-      <c r="H38" s="285" t="n"/>
-      <c r="I38" s="285" t="n"/>
-      <c r="J38" s="285" t="n"/>
-      <c r="K38" s="285" t="n"/>
-      <c r="L38" s="285" t="n"/>
-      <c r="M38" s="285" t="n"/>
-      <c r="N38" s="285" t="n"/>
-      <c r="O38" s="285" t="n"/>
-      <c r="P38" s="285" t="n"/>
-      <c r="Q38" s="285" t="n"/>
-      <c r="R38" s="285" t="n"/>
-      <c r="S38" s="285" t="n"/>
-      <c r="T38" s="285" t="n"/>
-      <c r="U38" s="285" t="n"/>
-      <c r="V38" s="285" t="n"/>
-      <c r="W38" s="285" t="n"/>
-      <c r="X38" s="285" t="n"/>
-      <c r="Y38" s="285" t="n"/>
-      <c r="Z38" s="285" t="n"/>
-      <c r="AA38" s="285" t="n"/>
-      <c r="AB38" s="285" t="n"/>
-      <c r="AC38" s="285" t="n"/>
-      <c r="AD38" s="285" t="n"/>
-      <c r="AE38" s="285" t="n"/>
-      <c r="AF38" s="285" t="n"/>
-      <c r="AG38" s="285" t="n"/>
-      <c r="AH38" s="285" t="n"/>
-      <c r="AI38" s="285" t="n"/>
-      <c r="AJ38" s="285" t="n"/>
-      <c r="AK38" s="285" t="n"/>
-      <c r="AL38" s="285" t="n"/>
-      <c r="AM38" s="285" t="n"/>
-      <c r="AN38" s="286" t="n"/>
+      <c r="B38" s="397" t="n"/>
+      <c r="C38" s="397" t="n"/>
+      <c r="D38" s="397" t="n"/>
+      <c r="E38" s="397" t="n"/>
+      <c r="F38" s="397" t="n"/>
+      <c r="G38" s="397" t="n"/>
+      <c r="H38" s="397" t="n"/>
+      <c r="I38" s="397" t="n"/>
+      <c r="J38" s="397" t="n"/>
+      <c r="K38" s="397" t="n"/>
+      <c r="L38" s="397" t="n"/>
+      <c r="M38" s="397" t="n"/>
+      <c r="N38" s="397" t="n"/>
+      <c r="O38" s="397" t="n"/>
+      <c r="P38" s="397" t="n"/>
+      <c r="Q38" s="397" t="n"/>
+      <c r="R38" s="397" t="n"/>
+      <c r="S38" s="397" t="n"/>
+      <c r="T38" s="397" t="n"/>
+      <c r="U38" s="397" t="n"/>
+      <c r="V38" s="397" t="n"/>
+      <c r="W38" s="397" t="n"/>
+      <c r="X38" s="397" t="n"/>
+      <c r="Y38" s="397" t="n"/>
+      <c r="Z38" s="397" t="n"/>
+      <c r="AA38" s="397" t="n"/>
+      <c r="AB38" s="397" t="n"/>
+      <c r="AC38" s="397" t="n"/>
+      <c r="AD38" s="397" t="n"/>
+      <c r="AE38" s="397" t="n"/>
+      <c r="AF38" s="397" t="n"/>
+      <c r="AG38" s="397" t="n"/>
+      <c r="AH38" s="397" t="n"/>
+      <c r="AI38" s="397" t="n"/>
+      <c r="AJ38" s="397" t="n"/>
+      <c r="AK38" s="397" t="n"/>
+      <c r="AL38" s="397" t="n"/>
+      <c r="AM38" s="397" t="n"/>
+      <c r="AN38" s="398" t="n"/>
     </row>
-    <row r="39" ht="17" customHeight="1" s="329">
-      <c r="A39" s="325" t="inlineStr">
+    <row r="39" ht="20" customHeight="1" s="329">
+      <c r="A39" s="375" t="inlineStr">
         <is>
           <t>Prepared by</t>
         </is>
       </c>
-      <c r="B39" s="285" t="n"/>
-      <c r="C39" s="285" t="n"/>
-      <c r="D39" s="285" t="n"/>
-      <c r="E39" s="285" t="n"/>
-      <c r="F39" s="285" t="n"/>
-      <c r="G39" s="285" t="n"/>
-      <c r="H39" s="285" t="n"/>
-      <c r="I39" s="285" t="n"/>
-      <c r="J39" s="285" t="n"/>
-      <c r="K39" s="285" t="n"/>
-      <c r="L39" s="285" t="n"/>
-      <c r="M39" s="326" t="n"/>
-      <c r="N39" s="51" t="inlineStr">
+      <c r="B39" s="392" t="n"/>
+      <c r="C39" s="392" t="n"/>
+      <c r="D39" s="392" t="n"/>
+      <c r="E39" s="392" t="n"/>
+      <c r="F39" s="392" t="n"/>
+      <c r="G39" s="392" t="n"/>
+      <c r="H39" s="392" t="n"/>
+      <c r="I39" s="392" t="n"/>
+      <c r="J39" s="392" t="n"/>
+      <c r="K39" s="392" t="n"/>
+      <c r="L39" s="392" t="n"/>
+      <c r="M39" s="393" t="n"/>
+      <c r="N39" s="376" t="inlineStr">
         <is>
           <t>Reviewed by</t>
         </is>
       </c>
-      <c r="O39" s="285" t="n"/>
-      <c r="P39" s="285" t="n"/>
-      <c r="Q39" s="285" t="n"/>
-      <c r="R39" s="285" t="n"/>
-      <c r="S39" s="285" t="n"/>
-      <c r="T39" s="285" t="n"/>
-      <c r="U39" s="285" t="n"/>
-      <c r="V39" s="285" t="n"/>
-      <c r="W39" s="285" t="n"/>
-      <c r="X39" s="285" t="n"/>
-      <c r="Y39" s="285" t="n"/>
-      <c r="Z39" s="285" t="n"/>
-      <c r="AA39" s="307" t="inlineStr">
+      <c r="O39" s="392" t="n"/>
+      <c r="P39" s="392" t="n"/>
+      <c r="Q39" s="392" t="n"/>
+      <c r="R39" s="392" t="n"/>
+      <c r="S39" s="392" t="n"/>
+      <c r="T39" s="392" t="n"/>
+      <c r="U39" s="392" t="n"/>
+      <c r="V39" s="392" t="n"/>
+      <c r="W39" s="392" t="n"/>
+      <c r="X39" s="392" t="n"/>
+      <c r="Y39" s="392" t="n"/>
+      <c r="Z39" s="392" t="n"/>
+      <c r="AA39" s="377" t="inlineStr">
         <is>
           <t>Approved by</t>
         </is>
       </c>
-      <c r="AB39" s="285" t="n"/>
-      <c r="AC39" s="285" t="n"/>
-      <c r="AD39" s="285" t="n"/>
-      <c r="AE39" s="285" t="n"/>
-      <c r="AF39" s="285" t="n"/>
-      <c r="AG39" s="285" t="n"/>
-      <c r="AH39" s="285" t="n"/>
-      <c r="AI39" s="285" t="n"/>
-      <c r="AJ39" s="285" t="n"/>
-      <c r="AK39" s="285" t="n"/>
-      <c r="AL39" s="285" t="n"/>
-      <c r="AM39" s="285" t="n"/>
-      <c r="AN39" s="286" t="n"/>
+      <c r="AB39" s="392" t="n"/>
+      <c r="AC39" s="392" t="n"/>
+      <c r="AD39" s="392" t="n"/>
+      <c r="AE39" s="392" t="n"/>
+      <c r="AF39" s="392" t="n"/>
+      <c r="AG39" s="392" t="n"/>
+      <c r="AH39" s="392" t="n"/>
+      <c r="AI39" s="392" t="n"/>
+      <c r="AJ39" s="392" t="n"/>
+      <c r="AK39" s="392" t="n"/>
+      <c r="AL39" s="392" t="n"/>
+      <c r="AM39" s="392" t="n"/>
+      <c r="AN39" s="393" t="n"/>
     </row>
-    <row r="40" ht="26" customHeight="1" s="329">
-      <c r="A40" s="308" t="inlineStr">
+    <row r="40" ht="20" customHeight="1" s="329">
+      <c r="A40" s="378" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="B40" s="320" t="n"/>
-      <c r="C40" s="320" t="n"/>
-      <c r="D40" s="320" t="n"/>
-      <c r="E40" s="320" t="n"/>
-      <c r="F40" s="320" t="n"/>
-      <c r="G40" s="320" t="n"/>
-      <c r="H40" s="320" t="n"/>
-      <c r="I40" s="320" t="n"/>
-      <c r="J40" s="320" t="n"/>
-      <c r="K40" s="320" t="n"/>
-      <c r="L40" s="320" t="n"/>
-      <c r="M40" s="327" t="n"/>
-      <c r="N40" s="308" t="inlineStr">
+      <c r="B40" s="391" t="n"/>
+      <c r="C40" s="391" t="n"/>
+      <c r="D40" s="391" t="n"/>
+      <c r="E40" s="391" t="n"/>
+      <c r="F40" s="391" t="n"/>
+      <c r="G40" s="391" t="n"/>
+      <c r="H40" s="391" t="n"/>
+      <c r="I40" s="391" t="n"/>
+      <c r="J40" s="391" t="n"/>
+      <c r="K40" s="391" t="n"/>
+      <c r="L40" s="391" t="n"/>
+      <c r="M40" s="403" t="n"/>
+      <c r="N40" s="378" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="O40" s="320" t="n"/>
-      <c r="P40" s="320" t="n"/>
-      <c r="Q40" s="320" t="n"/>
-      <c r="R40" s="320" t="n"/>
-      <c r="S40" s="320" t="n"/>
-      <c r="T40" s="320" t="n"/>
-      <c r="U40" s="320" t="n"/>
-      <c r="V40" s="320" t="n"/>
-      <c r="W40" s="320" t="n"/>
-      <c r="X40" s="320" t="n"/>
-      <c r="Y40" s="320" t="n"/>
-      <c r="Z40" s="327" t="n"/>
-      <c r="AA40" s="308" t="inlineStr">
+      <c r="O40" s="391" t="n"/>
+      <c r="P40" s="391" t="n"/>
+      <c r="Q40" s="391" t="n"/>
+      <c r="R40" s="391" t="n"/>
+      <c r="S40" s="391" t="n"/>
+      <c r="T40" s="391" t="n"/>
+      <c r="U40" s="391" t="n"/>
+      <c r="V40" s="391" t="n"/>
+      <c r="W40" s="391" t="n"/>
+      <c r="X40" s="391" t="n"/>
+      <c r="Y40" s="391" t="n"/>
+      <c r="Z40" s="403" t="n"/>
+      <c r="AA40" s="378" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="AB40" s="320" t="n"/>
-      <c r="AC40" s="320" t="n"/>
-      <c r="AD40" s="320" t="n"/>
-      <c r="AE40" s="320" t="n"/>
-      <c r="AF40" s="320" t="n"/>
-      <c r="AG40" s="320" t="n"/>
-      <c r="AH40" s="320" t="n"/>
-      <c r="AI40" s="320" t="n"/>
-      <c r="AJ40" s="320" t="n"/>
-      <c r="AK40" s="320" t="n"/>
-      <c r="AL40" s="320" t="n"/>
-      <c r="AM40" s="320" t="n"/>
-      <c r="AN40" s="327" t="n"/>
+      <c r="AB40" s="391" t="n"/>
+      <c r="AC40" s="391" t="n"/>
+      <c r="AD40" s="391" t="n"/>
+      <c r="AE40" s="391" t="n"/>
+      <c r="AF40" s="391" t="n"/>
+      <c r="AG40" s="391" t="n"/>
+      <c r="AH40" s="391" t="n"/>
+      <c r="AI40" s="391" t="n"/>
+      <c r="AJ40" s="391" t="n"/>
+      <c r="AK40" s="391" t="n"/>
+      <c r="AL40" s="391" t="n"/>
+      <c r="AM40" s="391" t="n"/>
+      <c r="AN40" s="403" t="n"/>
     </row>
-    <row r="41" ht="26" customHeight="1" s="329">
-      <c r="A41" s="328" t="n"/>
-      <c r="M41" s="330" t="n"/>
-      <c r="N41" s="328" t="n"/>
-      <c r="Z41" s="330" t="n"/>
-      <c r="AA41" s="328" t="n"/>
-      <c r="AN41" s="330" t="n"/>
+    <row r="41" ht="20" customHeight="1" s="329">
+      <c r="A41" s="404" t="n"/>
+      <c r="B41" s="381" t="n"/>
+      <c r="C41" s="381" t="n"/>
+      <c r="D41" s="381" t="n"/>
+      <c r="E41" s="381" t="n"/>
+      <c r="F41" s="381" t="n"/>
+      <c r="G41" s="381" t="n"/>
+      <c r="H41" s="381" t="n"/>
+      <c r="I41" s="381" t="n"/>
+      <c r="J41" s="381" t="n"/>
+      <c r="K41" s="381" t="n"/>
+      <c r="L41" s="381" t="n"/>
+      <c r="M41" s="405" t="n"/>
+      <c r="N41" s="404" t="n"/>
+      <c r="O41" s="381" t="n"/>
+      <c r="P41" s="381" t="n"/>
+      <c r="Q41" s="381" t="n"/>
+      <c r="R41" s="381" t="n"/>
+      <c r="S41" s="381" t="n"/>
+      <c r="T41" s="381" t="n"/>
+      <c r="U41" s="381" t="n"/>
+      <c r="V41" s="381" t="n"/>
+      <c r="W41" s="381" t="n"/>
+      <c r="X41" s="381" t="n"/>
+      <c r="Y41" s="381" t="n"/>
+      <c r="Z41" s="405" t="n"/>
+      <c r="AA41" s="404" t="n"/>
+      <c r="AB41" s="381" t="n"/>
+      <c r="AC41" s="381" t="n"/>
+      <c r="AD41" s="381" t="n"/>
+      <c r="AE41" s="381" t="n"/>
+      <c r="AF41" s="381" t="n"/>
+      <c r="AG41" s="381" t="n"/>
+      <c r="AH41" s="381" t="n"/>
+      <c r="AI41" s="381" t="n"/>
+      <c r="AJ41" s="381" t="n"/>
+      <c r="AK41" s="381" t="n"/>
+      <c r="AL41" s="381" t="n"/>
+      <c r="AM41" s="381" t="n"/>
+      <c r="AN41" s="405" t="n"/>
     </row>
-    <row r="42" ht="26" customHeight="1" s="329">
-      <c r="A42" s="331" t="n"/>
-      <c r="B42" s="332" t="n"/>
-      <c r="C42" s="332" t="n"/>
-      <c r="D42" s="332" t="n"/>
-      <c r="E42" s="332" t="n"/>
-      <c r="F42" s="332" t="n"/>
-      <c r="G42" s="332" t="n"/>
-      <c r="H42" s="332" t="n"/>
-      <c r="I42" s="332" t="n"/>
-      <c r="J42" s="332" t="n"/>
-      <c r="K42" s="332" t="n"/>
-      <c r="L42" s="332" t="n"/>
-      <c r="M42" s="333" t="n"/>
-      <c r="N42" s="331" t="n"/>
-      <c r="O42" s="332" t="n"/>
-      <c r="P42" s="332" t="n"/>
-      <c r="Q42" s="332" t="n"/>
-      <c r="R42" s="332" t="n"/>
-      <c r="S42" s="332" t="n"/>
-      <c r="T42" s="332" t="n"/>
-      <c r="U42" s="332" t="n"/>
-      <c r="V42" s="332" t="n"/>
-      <c r="W42" s="332" t="n"/>
-      <c r="X42" s="332" t="n"/>
-      <c r="Y42" s="332" t="n"/>
-      <c r="Z42" s="333" t="n"/>
-      <c r="AA42" s="331" t="n"/>
-      <c r="AB42" s="332" t="n"/>
-      <c r="AC42" s="332" t="n"/>
-      <c r="AD42" s="332" t="n"/>
-      <c r="AE42" s="332" t="n"/>
-      <c r="AF42" s="332" t="n"/>
-      <c r="AG42" s="332" t="n"/>
-      <c r="AH42" s="332" t="n"/>
-      <c r="AI42" s="332" t="n"/>
-      <c r="AJ42" s="332" t="n"/>
-      <c r="AK42" s="332" t="n"/>
-      <c r="AL42" s="332" t="n"/>
-      <c r="AM42" s="332" t="n"/>
-      <c r="AN42" s="333" t="n"/>
+    <row r="42" ht="20" customHeight="1" s="329">
+      <c r="A42" s="406" t="n"/>
+      <c r="B42" s="401" t="n"/>
+      <c r="C42" s="401" t="n"/>
+      <c r="D42" s="401" t="n"/>
+      <c r="E42" s="401" t="n"/>
+      <c r="F42" s="401" t="n"/>
+      <c r="G42" s="401" t="n"/>
+      <c r="H42" s="401" t="n"/>
+      <c r="I42" s="401" t="n"/>
+      <c r="J42" s="401" t="n"/>
+      <c r="K42" s="401" t="n"/>
+      <c r="L42" s="401" t="n"/>
+      <c r="M42" s="402" t="n"/>
+      <c r="N42" s="406" t="n"/>
+      <c r="O42" s="401" t="n"/>
+      <c r="P42" s="401" t="n"/>
+      <c r="Q42" s="401" t="n"/>
+      <c r="R42" s="401" t="n"/>
+      <c r="S42" s="401" t="n"/>
+      <c r="T42" s="401" t="n"/>
+      <c r="U42" s="401" t="n"/>
+      <c r="V42" s="401" t="n"/>
+      <c r="W42" s="401" t="n"/>
+      <c r="X42" s="401" t="n"/>
+      <c r="Y42" s="401" t="n"/>
+      <c r="Z42" s="402" t="n"/>
+      <c r="AA42" s="406" t="n"/>
+      <c r="AB42" s="401" t="n"/>
+      <c r="AC42" s="401" t="n"/>
+      <c r="AD42" s="401" t="n"/>
+      <c r="AE42" s="401" t="n"/>
+      <c r="AF42" s="401" t="n"/>
+      <c r="AG42" s="401" t="n"/>
+      <c r="AH42" s="401" t="n"/>
+      <c r="AI42" s="401" t="n"/>
+      <c r="AJ42" s="401" t="n"/>
+      <c r="AK42" s="401" t="n"/>
+      <c r="AL42" s="401" t="n"/>
+      <c r="AM42" s="401" t="n"/>
+      <c r="AN42" s="402" t="n"/>
     </row>
     <row r="43" ht="4" customHeight="1" s="329">
-      <c r="A43" s="309" t="n"/>
-      <c r="N43" s="309" t="n"/>
-      <c r="AA43" s="309" t="n"/>
+      <c r="A43" s="384" t="n"/>
+      <c r="B43" s="350" t="n"/>
+      <c r="C43" s="350" t="n"/>
+      <c r="D43" s="350" t="n"/>
+      <c r="E43" s="350" t="n"/>
+      <c r="F43" s="350" t="n"/>
+      <c r="G43" s="350" t="n"/>
+      <c r="H43" s="350" t="n"/>
+      <c r="I43" s="350" t="n"/>
+      <c r="J43" s="350" t="n"/>
+      <c r="K43" s="350" t="n"/>
+      <c r="L43" s="350" t="n"/>
+      <c r="M43" s="350" t="n"/>
+      <c r="N43" s="384" t="n"/>
+      <c r="O43" s="350" t="n"/>
+      <c r="P43" s="350" t="n"/>
+      <c r="Q43" s="350" t="n"/>
+      <c r="R43" s="350" t="n"/>
+      <c r="S43" s="350" t="n"/>
+      <c r="T43" s="350" t="n"/>
+      <c r="U43" s="350" t="n"/>
+      <c r="V43" s="350" t="n"/>
+      <c r="W43" s="350" t="n"/>
+      <c r="X43" s="350" t="n"/>
+      <c r="Y43" s="350" t="n"/>
+      <c r="Z43" s="350" t="n"/>
+      <c r="AA43" s="384" t="n"/>
+      <c r="AB43" s="350" t="n"/>
+      <c r="AC43" s="350" t="n"/>
+      <c r="AD43" s="350" t="n"/>
+      <c r="AE43" s="350" t="n"/>
+      <c r="AF43" s="350" t="n"/>
+      <c r="AG43" s="350" t="n"/>
+      <c r="AH43" s="350" t="n"/>
+      <c r="AI43" s="350" t="n"/>
+      <c r="AJ43" s="350" t="n"/>
+      <c r="AK43" s="350" t="n"/>
+      <c r="AL43" s="350" t="n"/>
+      <c r="AM43" s="350" t="n"/>
+      <c r="AN43" s="350" t="n"/>
     </row>
-    <row r="44" ht="24" customHeight="1" s="329">
-      <c r="A44" s="310" t="inlineStr">
+    <row r="44" ht="20" customHeight="1" s="329">
+      <c r="A44" s="385" t="inlineStr">
         <is>
           <t>NOTICE: Use for outsourced incoming verification only. Normal receiving / put-away remains in FRM-701; abnormal hold / disposition goes to FRM-413.</t>
         </is>
       </c>
+      <c r="B44" s="381" t="n"/>
+      <c r="C44" s="381" t="n"/>
+      <c r="D44" s="381" t="n"/>
+      <c r="E44" s="381" t="n"/>
+      <c r="F44" s="381" t="n"/>
+      <c r="G44" s="381" t="n"/>
+      <c r="H44" s="381" t="n"/>
+      <c r="I44" s="381" t="n"/>
+      <c r="J44" s="381" t="n"/>
+      <c r="K44" s="381" t="n"/>
+      <c r="L44" s="381" t="n"/>
+      <c r="M44" s="381" t="n"/>
+      <c r="N44" s="381" t="n"/>
+      <c r="O44" s="381" t="n"/>
+      <c r="P44" s="381" t="n"/>
+      <c r="Q44" s="381" t="n"/>
+      <c r="R44" s="381" t="n"/>
+      <c r="S44" s="381" t="n"/>
+      <c r="T44" s="381" t="n"/>
+      <c r="U44" s="381" t="n"/>
+      <c r="V44" s="381" t="n"/>
+      <c r="W44" s="381" t="n"/>
+      <c r="X44" s="381" t="n"/>
+      <c r="Y44" s="381" t="n"/>
+      <c r="Z44" s="381" t="n"/>
+      <c r="AA44" s="381" t="n"/>
+      <c r="AB44" s="381" t="n"/>
+      <c r="AC44" s="381" t="n"/>
+      <c r="AD44" s="381" t="n"/>
+      <c r="AE44" s="381" t="n"/>
+      <c r="AF44" s="381" t="n"/>
+      <c r="AG44" s="381" t="n"/>
+      <c r="AH44" s="381" t="n"/>
+      <c r="AI44" s="381" t="n"/>
+      <c r="AJ44" s="381" t="n"/>
+      <c r="AK44" s="381" t="n"/>
+      <c r="AL44" s="381" t="n"/>
+      <c r="AM44" s="381" t="n"/>
+      <c r="AN44" s="381" t="n"/>
     </row>
     <row r="45" ht="26" customHeight="1" s="329"/>
     <row r="46" ht="4" customHeight="1" s="329"/>
@@ -6599,7 +7266,6 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6836,31 +7502,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:AN16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" style="329" min="1" max="1"/>
-    <col width="28" customWidth="1" style="329" min="2" max="2"/>
-    <col width="28" customWidth="1" style="329" min="3" max="3"/>
-    <col width="16" customWidth="1" style="329" min="4" max="4"/>
-    <col width="14" customWidth="1" style="329" min="5" max="5"/>
-    <col width="16" customWidth="1" style="329" min="6" max="6"/>
-    <col width="18" customWidth="1" style="329" min="7" max="7"/>
-    <col width="24" customWidth="1" style="329" min="8" max="8"/>
+    <col width="2.33" customWidth="1" style="329" min="1" max="1"/>
+    <col width="2.33" customWidth="1" style="329" min="2" max="2"/>
+    <col width="2.33" customWidth="1" style="329" min="3" max="3"/>
+    <col width="2.33" customWidth="1" style="329" min="4" max="4"/>
+    <col width="2.33" customWidth="1" style="329" min="5" max="5"/>
+    <col width="2.33" customWidth="1" style="329" min="6" max="6"/>
+    <col width="2.33" customWidth="1" style="329" min="7" max="7"/>
+    <col width="2.33" customWidth="1" style="329" min="8" max="8"/>
+    <col width="2.33" customWidth="1" style="329" min="9" max="9"/>
+    <col width="2.33" customWidth="1" style="329" min="10" max="10"/>
+    <col width="2.33" customWidth="1" style="329" min="11" max="11"/>
+    <col width="2.33" customWidth="1" style="329" min="12" max="12"/>
+    <col width="2.33" customWidth="1" style="329" min="13" max="13"/>
+    <col width="2.33" customWidth="1" style="329" min="14" max="14"/>
+    <col width="2.33" customWidth="1" style="329" min="15" max="15"/>
+    <col width="2.33" customWidth="1" style="329" min="16" max="16"/>
+    <col width="2.33" customWidth="1" style="329" min="17" max="17"/>
+    <col width="2.33" customWidth="1" style="329" min="18" max="18"/>
+    <col width="2.33" customWidth="1" style="329" min="19" max="19"/>
+    <col width="2.33" customWidth="1" style="329" min="20" max="20"/>
+    <col width="2.33" customWidth="1" style="329" min="21" max="21"/>
+    <col width="2.33" customWidth="1" style="329" min="22" max="22"/>
+    <col width="2.33" customWidth="1" style="329" min="23" max="23"/>
+    <col width="2.33" customWidth="1" style="329" min="24" max="24"/>
+    <col width="2.33" customWidth="1" style="329" min="25" max="25"/>
+    <col width="2.33" customWidth="1" style="329" min="26" max="26"/>
+    <col width="2.33" customWidth="1" style="329" min="27" max="27"/>
+    <col width="2.33" customWidth="1" style="329" min="28" max="28"/>
+    <col width="2.33" customWidth="1" style="329" min="29" max="29"/>
+    <col width="2.33" customWidth="1" style="329" min="30" max="30"/>
+    <col width="2.33" customWidth="1" style="329" min="31" max="31"/>
+    <col width="2.33" customWidth="1" style="329" min="32" max="32"/>
+    <col width="2.33" customWidth="1" style="329" min="33" max="33"/>
+    <col width="2.33" customWidth="1" style="329" min="34" max="34"/>
+    <col width="2.33" customWidth="1" style="329" min="35" max="35"/>
+    <col width="2.33" customWidth="1" style="329" min="36" max="36"/>
+    <col width="2.33" customWidth="1" style="329" min="37" max="37"/>
+    <col width="2.33" customWidth="1" style="329" min="38" max="38"/>
+    <col width="2.33" customWidth="1" style="329" min="39" max="39"/>
+    <col width="2.33" customWidth="1" style="329" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1" s="329">
-      <c r="A1" s="334" t="inlineStr">
+      <c r="A1" s="386" t="inlineStr">
         <is>
           <t>Actions / Containment</t>
         </is>
       </c>
-      <c r="B1" s="285" t="n"/>
-      <c r="C1" s="285" t="n"/>
-      <c r="D1" s="285" t="n"/>
-      <c r="E1" s="285" t="n"/>
-      <c r="F1" s="285" t="n"/>
-      <c r="G1" s="286" t="n"/>
+      <c r="B1" s="409" t="n"/>
+      <c r="C1" s="409" t="n"/>
+      <c r="D1" s="409" t="n"/>
+      <c r="E1" s="409" t="n"/>
+      <c r="F1" s="409" t="n"/>
+      <c r="G1" s="410" t="n"/>
+      <c r="H1" s="345" t="n"/>
+      <c r="I1" s="345" t="n"/>
+      <c r="J1" s="345" t="n"/>
+      <c r="K1" s="345" t="n"/>
+      <c r="L1" s="345" t="n"/>
+      <c r="M1" s="345" t="n"/>
+      <c r="N1" s="345" t="n"/>
+      <c r="O1" s="345" t="n"/>
+      <c r="P1" s="345" t="n"/>
+      <c r="Q1" s="345" t="n"/>
+      <c r="R1" s="345" t="n"/>
+      <c r="S1" s="345" t="n"/>
+      <c r="T1" s="345" t="n"/>
+      <c r="U1" s="345" t="n"/>
+      <c r="V1" s="345" t="n"/>
+      <c r="W1" s="345" t="n"/>
+      <c r="X1" s="345" t="n"/>
+      <c r="Y1" s="345" t="n"/>
+      <c r="Z1" s="345" t="n"/>
+      <c r="AA1" s="345" t="n"/>
+      <c r="AB1" s="345" t="n"/>
+      <c r="AC1" s="345" t="n"/>
+      <c r="AD1" s="345" t="n"/>
+      <c r="AE1" s="345" t="n"/>
+      <c r="AF1" s="345" t="n"/>
+      <c r="AG1" s="345" t="n"/>
+      <c r="AH1" s="345" t="n"/>
+      <c r="AI1" s="345" t="n"/>
+      <c r="AJ1" s="345" t="n"/>
+      <c r="AK1" s="345" t="n"/>
+      <c r="AL1" s="345" t="n"/>
+      <c r="AM1" s="345" t="n"/>
+      <c r="AN1" s="345" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1" s="329">
       <c r="A2" s="335" t="inlineStr">
@@ -6868,199 +7599,689 @@
           <t>Incoming verification event record for outsourced process returns and discrete disposition decisions.</t>
         </is>
       </c>
+      <c r="H2" s="345" t="n"/>
+      <c r="I2" s="345" t="n"/>
+      <c r="J2" s="345" t="n"/>
+      <c r="K2" s="345" t="n"/>
+      <c r="L2" s="345" t="n"/>
+      <c r="M2" s="345" t="n"/>
+      <c r="N2" s="345" t="n"/>
+      <c r="O2" s="345" t="n"/>
+      <c r="P2" s="345" t="n"/>
+      <c r="Q2" s="345" t="n"/>
+      <c r="R2" s="345" t="n"/>
+      <c r="S2" s="345" t="n"/>
+      <c r="T2" s="345" t="n"/>
+      <c r="U2" s="345" t="n"/>
+      <c r="V2" s="345" t="n"/>
+      <c r="W2" s="345" t="n"/>
+      <c r="X2" s="345" t="n"/>
+      <c r="Y2" s="345" t="n"/>
+      <c r="Z2" s="345" t="n"/>
+      <c r="AA2" s="345" t="n"/>
+      <c r="AB2" s="345" t="n"/>
+      <c r="AC2" s="345" t="n"/>
+      <c r="AD2" s="345" t="n"/>
+      <c r="AE2" s="345" t="n"/>
+      <c r="AF2" s="345" t="n"/>
+      <c r="AG2" s="345" t="n"/>
+      <c r="AH2" s="345" t="n"/>
+      <c r="AI2" s="345" t="n"/>
+      <c r="AJ2" s="345" t="n"/>
+      <c r="AK2" s="345" t="n"/>
+      <c r="AL2" s="345" t="n"/>
+      <c r="AM2" s="345" t="n"/>
+      <c r="AN2" s="345" t="n"/>
     </row>
-    <row r="3" ht="18" customHeight="1" s="329"/>
+    <row r="3" ht="18" customHeight="1" s="329">
+      <c r="A3" s="345" t="n"/>
+      <c r="B3" s="345" t="n"/>
+      <c r="C3" s="345" t="n"/>
+      <c r="D3" s="345" t="n"/>
+      <c r="E3" s="345" t="n"/>
+      <c r="F3" s="345" t="n"/>
+      <c r="G3" s="345" t="n"/>
+      <c r="H3" s="345" t="n"/>
+      <c r="I3" s="345" t="n"/>
+      <c r="J3" s="345" t="n"/>
+      <c r="K3" s="345" t="n"/>
+      <c r="L3" s="345" t="n"/>
+      <c r="M3" s="345" t="n"/>
+      <c r="N3" s="345" t="n"/>
+      <c r="O3" s="345" t="n"/>
+      <c r="P3" s="345" t="n"/>
+      <c r="Q3" s="345" t="n"/>
+      <c r="R3" s="345" t="n"/>
+      <c r="S3" s="345" t="n"/>
+      <c r="T3" s="345" t="n"/>
+      <c r="U3" s="345" t="n"/>
+      <c r="V3" s="345" t="n"/>
+      <c r="W3" s="345" t="n"/>
+      <c r="X3" s="345" t="n"/>
+      <c r="Y3" s="345" t="n"/>
+      <c r="Z3" s="345" t="n"/>
+      <c r="AA3" s="345" t="n"/>
+      <c r="AB3" s="345" t="n"/>
+      <c r="AC3" s="345" t="n"/>
+      <c r="AD3" s="345" t="n"/>
+      <c r="AE3" s="345" t="n"/>
+      <c r="AF3" s="345" t="n"/>
+      <c r="AG3" s="345" t="n"/>
+      <c r="AH3" s="345" t="n"/>
+      <c r="AI3" s="345" t="n"/>
+      <c r="AJ3" s="345" t="n"/>
+      <c r="AK3" s="345" t="n"/>
+      <c r="AL3" s="345" t="n"/>
+      <c r="AM3" s="345" t="n"/>
+      <c r="AN3" s="345" t="n"/>
+    </row>
     <row r="4" ht="20" customHeight="1" s="329">
-      <c r="A4" s="336" t="inlineStr">
+      <c r="A4" s="387" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="336" t="inlineStr">
+      <c r="B4" s="387" t="inlineStr">
         <is>
           <t>Issue / Finding</t>
         </is>
       </c>
-      <c r="C4" s="336" t="inlineStr">
+      <c r="C4" s="387" t="inlineStr">
         <is>
           <t>Required Action</t>
         </is>
       </c>
-      <c r="D4" s="336" t="inlineStr">
+      <c r="D4" s="387" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E4" s="336" t="inlineStr">
+      <c r="E4" s="387" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="F4" s="336" t="inlineStr">
+      <c r="F4" s="387" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G4" s="336" t="inlineStr">
+      <c r="G4" s="387" t="inlineStr">
         <is>
           <t>Evidence Ref</t>
         </is>
       </c>
-      <c r="H4" s="336" t="inlineStr">
+      <c r="H4" s="387" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
+      <c r="I4" s="345" t="n"/>
+      <c r="J4" s="345" t="n"/>
+      <c r="K4" s="345" t="n"/>
+      <c r="L4" s="345" t="n"/>
+      <c r="M4" s="345" t="n"/>
+      <c r="N4" s="345" t="n"/>
+      <c r="O4" s="345" t="n"/>
+      <c r="P4" s="345" t="n"/>
+      <c r="Q4" s="345" t="n"/>
+      <c r="R4" s="345" t="n"/>
+      <c r="S4" s="345" t="n"/>
+      <c r="T4" s="345" t="n"/>
+      <c r="U4" s="345" t="n"/>
+      <c r="V4" s="345" t="n"/>
+      <c r="W4" s="345" t="n"/>
+      <c r="X4" s="345" t="n"/>
+      <c r="Y4" s="345" t="n"/>
+      <c r="Z4" s="345" t="n"/>
+      <c r="AA4" s="345" t="n"/>
+      <c r="AB4" s="345" t="n"/>
+      <c r="AC4" s="345" t="n"/>
+      <c r="AD4" s="345" t="n"/>
+      <c r="AE4" s="345" t="n"/>
+      <c r="AF4" s="345" t="n"/>
+      <c r="AG4" s="345" t="n"/>
+      <c r="AH4" s="345" t="n"/>
+      <c r="AI4" s="345" t="n"/>
+      <c r="AJ4" s="345" t="n"/>
+      <c r="AK4" s="345" t="n"/>
+      <c r="AL4" s="345" t="n"/>
+      <c r="AM4" s="345" t="n"/>
+      <c r="AN4" s="345" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1" s="329">
-      <c r="A5" s="315">
+      <c r="A5" s="388">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B5" s="316" t="n"/>
-      <c r="C5" s="316" t="n"/>
-      <c r="D5" s="316" t="n"/>
-      <c r="E5" s="316" t="n"/>
-      <c r="F5" s="316" t="n"/>
-      <c r="G5" s="316" t="n"/>
-      <c r="H5" s="316" t="n"/>
+      <c r="B5" s="389" t="n"/>
+      <c r="C5" s="389" t="n"/>
+      <c r="D5" s="389" t="n"/>
+      <c r="E5" s="389" t="n"/>
+      <c r="F5" s="389" t="n"/>
+      <c r="G5" s="389" t="n"/>
+      <c r="H5" s="389" t="n"/>
+      <c r="I5" s="345" t="n"/>
+      <c r="J5" s="345" t="n"/>
+      <c r="K5" s="345" t="n"/>
+      <c r="L5" s="345" t="n"/>
+      <c r="M5" s="345" t="n"/>
+      <c r="N5" s="345" t="n"/>
+      <c r="O5" s="345" t="n"/>
+      <c r="P5" s="345" t="n"/>
+      <c r="Q5" s="345" t="n"/>
+      <c r="R5" s="345" t="n"/>
+      <c r="S5" s="345" t="n"/>
+      <c r="T5" s="345" t="n"/>
+      <c r="U5" s="345" t="n"/>
+      <c r="V5" s="345" t="n"/>
+      <c r="W5" s="345" t="n"/>
+      <c r="X5" s="345" t="n"/>
+      <c r="Y5" s="345" t="n"/>
+      <c r="Z5" s="345" t="n"/>
+      <c r="AA5" s="345" t="n"/>
+      <c r="AB5" s="345" t="n"/>
+      <c r="AC5" s="345" t="n"/>
+      <c r="AD5" s="345" t="n"/>
+      <c r="AE5" s="345" t="n"/>
+      <c r="AF5" s="345" t="n"/>
+      <c r="AG5" s="345" t="n"/>
+      <c r="AH5" s="345" t="n"/>
+      <c r="AI5" s="345" t="n"/>
+      <c r="AJ5" s="345" t="n"/>
+      <c r="AK5" s="345" t="n"/>
+      <c r="AL5" s="345" t="n"/>
+      <c r="AM5" s="345" t="n"/>
+      <c r="AN5" s="345" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1" s="329">
-      <c r="A6" s="315">
+      <c r="A6" s="388">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B6" s="316" t="n"/>
-      <c r="C6" s="316" t="n"/>
-      <c r="D6" s="316" t="n"/>
-      <c r="E6" s="316" t="n"/>
-      <c r="F6" s="316" t="n"/>
-      <c r="G6" s="316" t="n"/>
-      <c r="H6" s="316" t="n"/>
+      <c r="B6" s="389" t="n"/>
+      <c r="C6" s="389" t="n"/>
+      <c r="D6" s="389" t="n"/>
+      <c r="E6" s="389" t="n"/>
+      <c r="F6" s="389" t="n"/>
+      <c r="G6" s="389" t="n"/>
+      <c r="H6" s="389" t="n"/>
+      <c r="I6" s="345" t="n"/>
+      <c r="J6" s="345" t="n"/>
+      <c r="K6" s="345" t="n"/>
+      <c r="L6" s="345" t="n"/>
+      <c r="M6" s="345" t="n"/>
+      <c r="N6" s="345" t="n"/>
+      <c r="O6" s="345" t="n"/>
+      <c r="P6" s="345" t="n"/>
+      <c r="Q6" s="345" t="n"/>
+      <c r="R6" s="345" t="n"/>
+      <c r="S6" s="345" t="n"/>
+      <c r="T6" s="345" t="n"/>
+      <c r="U6" s="345" t="n"/>
+      <c r="V6" s="345" t="n"/>
+      <c r="W6" s="345" t="n"/>
+      <c r="X6" s="345" t="n"/>
+      <c r="Y6" s="345" t="n"/>
+      <c r="Z6" s="345" t="n"/>
+      <c r="AA6" s="345" t="n"/>
+      <c r="AB6" s="345" t="n"/>
+      <c r="AC6" s="345" t="n"/>
+      <c r="AD6" s="345" t="n"/>
+      <c r="AE6" s="345" t="n"/>
+      <c r="AF6" s="345" t="n"/>
+      <c r="AG6" s="345" t="n"/>
+      <c r="AH6" s="345" t="n"/>
+      <c r="AI6" s="345" t="n"/>
+      <c r="AJ6" s="345" t="n"/>
+      <c r="AK6" s="345" t="n"/>
+      <c r="AL6" s="345" t="n"/>
+      <c r="AM6" s="345" t="n"/>
+      <c r="AN6" s="345" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1" s="329">
-      <c r="A7" s="315">
+      <c r="A7" s="388">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B7" s="316" t="n"/>
-      <c r="C7" s="316" t="n"/>
-      <c r="D7" s="316" t="n"/>
-      <c r="E7" s="316" t="n"/>
-      <c r="F7" s="316" t="n"/>
-      <c r="G7" s="316" t="n"/>
-      <c r="H7" s="316" t="n"/>
+      <c r="B7" s="389" t="n"/>
+      <c r="C7" s="389" t="n"/>
+      <c r="D7" s="389" t="n"/>
+      <c r="E7" s="389" t="n"/>
+      <c r="F7" s="389" t="n"/>
+      <c r="G7" s="389" t="n"/>
+      <c r="H7" s="389" t="n"/>
+      <c r="I7" s="345" t="n"/>
+      <c r="J7" s="345" t="n"/>
+      <c r="K7" s="345" t="n"/>
+      <c r="L7" s="345" t="n"/>
+      <c r="M7" s="345" t="n"/>
+      <c r="N7" s="345" t="n"/>
+      <c r="O7" s="345" t="n"/>
+      <c r="P7" s="345" t="n"/>
+      <c r="Q7" s="345" t="n"/>
+      <c r="R7" s="345" t="n"/>
+      <c r="S7" s="345" t="n"/>
+      <c r="T7" s="345" t="n"/>
+      <c r="U7" s="345" t="n"/>
+      <c r="V7" s="345" t="n"/>
+      <c r="W7" s="345" t="n"/>
+      <c r="X7" s="345" t="n"/>
+      <c r="Y7" s="345" t="n"/>
+      <c r="Z7" s="345" t="n"/>
+      <c r="AA7" s="345" t="n"/>
+      <c r="AB7" s="345" t="n"/>
+      <c r="AC7" s="345" t="n"/>
+      <c r="AD7" s="345" t="n"/>
+      <c r="AE7" s="345" t="n"/>
+      <c r="AF7" s="345" t="n"/>
+      <c r="AG7" s="345" t="n"/>
+      <c r="AH7" s="345" t="n"/>
+      <c r="AI7" s="345" t="n"/>
+      <c r="AJ7" s="345" t="n"/>
+      <c r="AK7" s="345" t="n"/>
+      <c r="AL7" s="345" t="n"/>
+      <c r="AM7" s="345" t="n"/>
+      <c r="AN7" s="345" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1" s="329">
-      <c r="A8" s="315">
+      <c r="A8" s="352">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B8" s="316" t="n"/>
-      <c r="C8" s="316" t="n"/>
-      <c r="D8" s="316" t="n"/>
-      <c r="E8" s="316" t="n"/>
-      <c r="F8" s="316" t="n"/>
-      <c r="G8" s="316" t="n"/>
-      <c r="H8" s="316" t="n"/>
+      <c r="B8" s="390" t="n"/>
+      <c r="C8" s="390" t="n"/>
+      <c r="D8" s="390" t="n"/>
+      <c r="E8" s="390" t="n"/>
+      <c r="F8" s="390" t="n"/>
+      <c r="G8" s="390" t="n"/>
+      <c r="H8" s="390" t="n"/>
+      <c r="I8" s="381" t="n"/>
+      <c r="J8" s="381" t="n"/>
+      <c r="K8" s="381" t="n"/>
+      <c r="L8" s="381" t="n"/>
+      <c r="M8" s="381" t="n"/>
+      <c r="N8" s="381" t="n"/>
+      <c r="O8" s="381" t="n"/>
+      <c r="P8" s="381" t="n"/>
+      <c r="Q8" s="381" t="n"/>
+      <c r="R8" s="381" t="n"/>
+      <c r="S8" s="381" t="n"/>
+      <c r="T8" s="381" t="n"/>
+      <c r="U8" s="381" t="n"/>
+      <c r="V8" s="381" t="n"/>
+      <c r="W8" s="381" t="n"/>
+      <c r="X8" s="381" t="n"/>
+      <c r="Y8" s="381" t="n"/>
+      <c r="Z8" s="381" t="n"/>
+      <c r="AA8" s="381" t="n"/>
+      <c r="AB8" s="381" t="n"/>
+      <c r="AC8" s="381" t="n"/>
+      <c r="AD8" s="381" t="n"/>
+      <c r="AE8" s="381" t="n"/>
+      <c r="AF8" s="381" t="n"/>
+      <c r="AG8" s="381" t="n"/>
+      <c r="AH8" s="381" t="n"/>
+      <c r="AI8" s="381" t="n"/>
+      <c r="AJ8" s="381" t="n"/>
+      <c r="AK8" s="381" t="n"/>
+      <c r="AL8" s="381" t="n"/>
+      <c r="AM8" s="381" t="n"/>
+      <c r="AN8" s="381" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1" s="329">
-      <c r="A9" s="315">
+      <c r="A9" s="352">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B9" s="316" t="n"/>
-      <c r="C9" s="316" t="n"/>
-      <c r="D9" s="316" t="n"/>
-      <c r="E9" s="316" t="n"/>
-      <c r="F9" s="316" t="n"/>
-      <c r="G9" s="316" t="n"/>
-      <c r="H9" s="316" t="n"/>
+      <c r="B9" s="390" t="n"/>
+      <c r="C9" s="390" t="n"/>
+      <c r="D9" s="390" t="n"/>
+      <c r="E9" s="390" t="n"/>
+      <c r="F9" s="390" t="n"/>
+      <c r="G9" s="390" t="n"/>
+      <c r="H9" s="390" t="n"/>
+      <c r="I9" s="381" t="n"/>
+      <c r="J9" s="381" t="n"/>
+      <c r="K9" s="381" t="n"/>
+      <c r="L9" s="381" t="n"/>
+      <c r="M9" s="381" t="n"/>
+      <c r="N9" s="381" t="n"/>
+      <c r="O9" s="381" t="n"/>
+      <c r="P9" s="381" t="n"/>
+      <c r="Q9" s="381" t="n"/>
+      <c r="R9" s="381" t="n"/>
+      <c r="S9" s="381" t="n"/>
+      <c r="T9" s="381" t="n"/>
+      <c r="U9" s="381" t="n"/>
+      <c r="V9" s="381" t="n"/>
+      <c r="W9" s="381" t="n"/>
+      <c r="X9" s="381" t="n"/>
+      <c r="Y9" s="381" t="n"/>
+      <c r="Z9" s="381" t="n"/>
+      <c r="AA9" s="381" t="n"/>
+      <c r="AB9" s="381" t="n"/>
+      <c r="AC9" s="381" t="n"/>
+      <c r="AD9" s="381" t="n"/>
+      <c r="AE9" s="381" t="n"/>
+      <c r="AF9" s="381" t="n"/>
+      <c r="AG9" s="381" t="n"/>
+      <c r="AH9" s="381" t="n"/>
+      <c r="AI9" s="381" t="n"/>
+      <c r="AJ9" s="381" t="n"/>
+      <c r="AK9" s="381" t="n"/>
+      <c r="AL9" s="381" t="n"/>
+      <c r="AM9" s="381" t="n"/>
+      <c r="AN9" s="381" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1" s="329">
-      <c r="A10" s="315">
+      <c r="A10" s="352">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B10" s="316" t="n"/>
-      <c r="C10" s="316" t="n"/>
-      <c r="D10" s="316" t="n"/>
-      <c r="E10" s="316" t="n"/>
-      <c r="F10" s="316" t="n"/>
-      <c r="G10" s="316" t="n"/>
-      <c r="H10" s="316" t="n"/>
+      <c r="B10" s="390" t="n"/>
+      <c r="C10" s="390" t="n"/>
+      <c r="D10" s="390" t="n"/>
+      <c r="E10" s="390" t="n"/>
+      <c r="F10" s="390" t="n"/>
+      <c r="G10" s="390" t="n"/>
+      <c r="H10" s="390" t="n"/>
+      <c r="I10" s="381" t="n"/>
+      <c r="J10" s="381" t="n"/>
+      <c r="K10" s="381" t="n"/>
+      <c r="L10" s="381" t="n"/>
+      <c r="M10" s="381" t="n"/>
+      <c r="N10" s="381" t="n"/>
+      <c r="O10" s="381" t="n"/>
+      <c r="P10" s="381" t="n"/>
+      <c r="Q10" s="381" t="n"/>
+      <c r="R10" s="381" t="n"/>
+      <c r="S10" s="381" t="n"/>
+      <c r="T10" s="381" t="n"/>
+      <c r="U10" s="381" t="n"/>
+      <c r="V10" s="381" t="n"/>
+      <c r="W10" s="381" t="n"/>
+      <c r="X10" s="381" t="n"/>
+      <c r="Y10" s="381" t="n"/>
+      <c r="Z10" s="381" t="n"/>
+      <c r="AA10" s="381" t="n"/>
+      <c r="AB10" s="381" t="n"/>
+      <c r="AC10" s="381" t="n"/>
+      <c r="AD10" s="381" t="n"/>
+      <c r="AE10" s="381" t="n"/>
+      <c r="AF10" s="381" t="n"/>
+      <c r="AG10" s="381" t="n"/>
+      <c r="AH10" s="381" t="n"/>
+      <c r="AI10" s="381" t="n"/>
+      <c r="AJ10" s="381" t="n"/>
+      <c r="AK10" s="381" t="n"/>
+      <c r="AL10" s="381" t="n"/>
+      <c r="AM10" s="381" t="n"/>
+      <c r="AN10" s="381" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1" s="329">
-      <c r="A11" s="315">
+      <c r="A11" s="352">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B11" s="316" t="n"/>
-      <c r="C11" s="316" t="n"/>
-      <c r="D11" s="316" t="n"/>
-      <c r="E11" s="316" t="n"/>
-      <c r="F11" s="316" t="n"/>
-      <c r="G11" s="316" t="n"/>
-      <c r="H11" s="316" t="n"/>
+      <c r="B11" s="390" t="n"/>
+      <c r="C11" s="390" t="n"/>
+      <c r="D11" s="390" t="n"/>
+      <c r="E11" s="390" t="n"/>
+      <c r="F11" s="390" t="n"/>
+      <c r="G11" s="390" t="n"/>
+      <c r="H11" s="390" t="n"/>
+      <c r="I11" s="381" t="n"/>
+      <c r="J11" s="381" t="n"/>
+      <c r="K11" s="381" t="n"/>
+      <c r="L11" s="381" t="n"/>
+      <c r="M11" s="381" t="n"/>
+      <c r="N11" s="381" t="n"/>
+      <c r="O11" s="381" t="n"/>
+      <c r="P11" s="381" t="n"/>
+      <c r="Q11" s="381" t="n"/>
+      <c r="R11" s="381" t="n"/>
+      <c r="S11" s="381" t="n"/>
+      <c r="T11" s="381" t="n"/>
+      <c r="U11" s="381" t="n"/>
+      <c r="V11" s="381" t="n"/>
+      <c r="W11" s="381" t="n"/>
+      <c r="X11" s="381" t="n"/>
+      <c r="Y11" s="381" t="n"/>
+      <c r="Z11" s="381" t="n"/>
+      <c r="AA11" s="381" t="n"/>
+      <c r="AB11" s="381" t="n"/>
+      <c r="AC11" s="381" t="n"/>
+      <c r="AD11" s="381" t="n"/>
+      <c r="AE11" s="381" t="n"/>
+      <c r="AF11" s="381" t="n"/>
+      <c r="AG11" s="381" t="n"/>
+      <c r="AH11" s="381" t="n"/>
+      <c r="AI11" s="381" t="n"/>
+      <c r="AJ11" s="381" t="n"/>
+      <c r="AK11" s="381" t="n"/>
+      <c r="AL11" s="381" t="n"/>
+      <c r="AM11" s="381" t="n"/>
+      <c r="AN11" s="381" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1" s="329">
-      <c r="A12" s="315">
+      <c r="A12" s="352">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B12" s="316" t="n"/>
-      <c r="C12" s="316" t="n"/>
-      <c r="D12" s="316" t="n"/>
-      <c r="E12" s="316" t="n"/>
-      <c r="F12" s="316" t="n"/>
-      <c r="G12" s="316" t="n"/>
-      <c r="H12" s="316" t="n"/>
+      <c r="B12" s="390" t="n"/>
+      <c r="C12" s="390" t="n"/>
+      <c r="D12" s="390" t="n"/>
+      <c r="E12" s="390" t="n"/>
+      <c r="F12" s="390" t="n"/>
+      <c r="G12" s="390" t="n"/>
+      <c r="H12" s="390" t="n"/>
+      <c r="I12" s="381" t="n"/>
+      <c r="J12" s="381" t="n"/>
+      <c r="K12" s="381" t="n"/>
+      <c r="L12" s="381" t="n"/>
+      <c r="M12" s="381" t="n"/>
+      <c r="N12" s="381" t="n"/>
+      <c r="O12" s="381" t="n"/>
+      <c r="P12" s="381" t="n"/>
+      <c r="Q12" s="381" t="n"/>
+      <c r="R12" s="381" t="n"/>
+      <c r="S12" s="381" t="n"/>
+      <c r="T12" s="381" t="n"/>
+      <c r="U12" s="381" t="n"/>
+      <c r="V12" s="381" t="n"/>
+      <c r="W12" s="381" t="n"/>
+      <c r="X12" s="381" t="n"/>
+      <c r="Y12" s="381" t="n"/>
+      <c r="Z12" s="381" t="n"/>
+      <c r="AA12" s="381" t="n"/>
+      <c r="AB12" s="381" t="n"/>
+      <c r="AC12" s="381" t="n"/>
+      <c r="AD12" s="381" t="n"/>
+      <c r="AE12" s="381" t="n"/>
+      <c r="AF12" s="381" t="n"/>
+      <c r="AG12" s="381" t="n"/>
+      <c r="AH12" s="381" t="n"/>
+      <c r="AI12" s="381" t="n"/>
+      <c r="AJ12" s="381" t="n"/>
+      <c r="AK12" s="381" t="n"/>
+      <c r="AL12" s="381" t="n"/>
+      <c r="AM12" s="381" t="n"/>
+      <c r="AN12" s="381" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1" s="329">
-      <c r="A13" s="315">
+      <c r="A13" s="352">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B13" s="316" t="n"/>
-      <c r="C13" s="316" t="n"/>
-      <c r="D13" s="316" t="n"/>
-      <c r="E13" s="316" t="n"/>
-      <c r="F13" s="316" t="n"/>
-      <c r="G13" s="316" t="n"/>
-      <c r="H13" s="316" t="n"/>
+      <c r="B13" s="390" t="n"/>
+      <c r="C13" s="390" t="n"/>
+      <c r="D13" s="390" t="n"/>
+      <c r="E13" s="390" t="n"/>
+      <c r="F13" s="390" t="n"/>
+      <c r="G13" s="390" t="n"/>
+      <c r="H13" s="390" t="n"/>
+      <c r="I13" s="381" t="n"/>
+      <c r="J13" s="381" t="n"/>
+      <c r="K13" s="381" t="n"/>
+      <c r="L13" s="381" t="n"/>
+      <c r="M13" s="381" t="n"/>
+      <c r="N13" s="381" t="n"/>
+      <c r="O13" s="381" t="n"/>
+      <c r="P13" s="381" t="n"/>
+      <c r="Q13" s="381" t="n"/>
+      <c r="R13" s="381" t="n"/>
+      <c r="S13" s="381" t="n"/>
+      <c r="T13" s="381" t="n"/>
+      <c r="U13" s="381" t="n"/>
+      <c r="V13" s="381" t="n"/>
+      <c r="W13" s="381" t="n"/>
+      <c r="X13" s="381" t="n"/>
+      <c r="Y13" s="381" t="n"/>
+      <c r="Z13" s="381" t="n"/>
+      <c r="AA13" s="381" t="n"/>
+      <c r="AB13" s="381" t="n"/>
+      <c r="AC13" s="381" t="n"/>
+      <c r="AD13" s="381" t="n"/>
+      <c r="AE13" s="381" t="n"/>
+      <c r="AF13" s="381" t="n"/>
+      <c r="AG13" s="381" t="n"/>
+      <c r="AH13" s="381" t="n"/>
+      <c r="AI13" s="381" t="n"/>
+      <c r="AJ13" s="381" t="n"/>
+      <c r="AK13" s="381" t="n"/>
+      <c r="AL13" s="381" t="n"/>
+      <c r="AM13" s="381" t="n"/>
+      <c r="AN13" s="381" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1" s="329">
-      <c r="A14" s="315">
+      <c r="A14" s="352">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B14" s="316" t="n"/>
-      <c r="C14" s="316" t="n"/>
-      <c r="D14" s="316" t="n"/>
-      <c r="E14" s="316" t="n"/>
-      <c r="F14" s="316" t="n"/>
-      <c r="G14" s="316" t="n"/>
-      <c r="H14" s="316" t="n"/>
+      <c r="B14" s="390" t="n"/>
+      <c r="C14" s="390" t="n"/>
+      <c r="D14" s="390" t="n"/>
+      <c r="E14" s="390" t="n"/>
+      <c r="F14" s="390" t="n"/>
+      <c r="G14" s="390" t="n"/>
+      <c r="H14" s="390" t="n"/>
+      <c r="I14" s="381" t="n"/>
+      <c r="J14" s="381" t="n"/>
+      <c r="K14" s="381" t="n"/>
+      <c r="L14" s="381" t="n"/>
+      <c r="M14" s="381" t="n"/>
+      <c r="N14" s="381" t="n"/>
+      <c r="O14" s="381" t="n"/>
+      <c r="P14" s="381" t="n"/>
+      <c r="Q14" s="381" t="n"/>
+      <c r="R14" s="381" t="n"/>
+      <c r="S14" s="381" t="n"/>
+      <c r="T14" s="381" t="n"/>
+      <c r="U14" s="381" t="n"/>
+      <c r="V14" s="381" t="n"/>
+      <c r="W14" s="381" t="n"/>
+      <c r="X14" s="381" t="n"/>
+      <c r="Y14" s="381" t="n"/>
+      <c r="Z14" s="381" t="n"/>
+      <c r="AA14" s="381" t="n"/>
+      <c r="AB14" s="381" t="n"/>
+      <c r="AC14" s="381" t="n"/>
+      <c r="AD14" s="381" t="n"/>
+      <c r="AE14" s="381" t="n"/>
+      <c r="AF14" s="381" t="n"/>
+      <c r="AG14" s="381" t="n"/>
+      <c r="AH14" s="381" t="n"/>
+      <c r="AI14" s="381" t="n"/>
+      <c r="AJ14" s="381" t="n"/>
+      <c r="AK14" s="381" t="n"/>
+      <c r="AL14" s="381" t="n"/>
+      <c r="AM14" s="381" t="n"/>
+      <c r="AN14" s="381" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1" s="329">
-      <c r="A15" s="315" t="n"/>
-      <c r="B15" s="316" t="n"/>
-      <c r="C15" s="316" t="n"/>
-      <c r="D15" s="316" t="n"/>
-      <c r="E15" s="316" t="n"/>
-      <c r="F15" s="316" t="n"/>
-      <c r="G15" s="316" t="n"/>
-      <c r="H15" s="316" t="n"/>
+      <c r="A15" s="352" t="n"/>
+      <c r="B15" s="390" t="n"/>
+      <c r="C15" s="390" t="n"/>
+      <c r="D15" s="390" t="n"/>
+      <c r="E15" s="390" t="n"/>
+      <c r="F15" s="390" t="n"/>
+      <c r="G15" s="390" t="n"/>
+      <c r="H15" s="390" t="n"/>
+      <c r="I15" s="381" t="n"/>
+      <c r="J15" s="381" t="n"/>
+      <c r="K15" s="381" t="n"/>
+      <c r="L15" s="381" t="n"/>
+      <c r="M15" s="381" t="n"/>
+      <c r="N15" s="381" t="n"/>
+      <c r="O15" s="381" t="n"/>
+      <c r="P15" s="381" t="n"/>
+      <c r="Q15" s="381" t="n"/>
+      <c r="R15" s="381" t="n"/>
+      <c r="S15" s="381" t="n"/>
+      <c r="T15" s="381" t="n"/>
+      <c r="U15" s="381" t="n"/>
+      <c r="V15" s="381" t="n"/>
+      <c r="W15" s="381" t="n"/>
+      <c r="X15" s="381" t="n"/>
+      <c r="Y15" s="381" t="n"/>
+      <c r="Z15" s="381" t="n"/>
+      <c r="AA15" s="381" t="n"/>
+      <c r="AB15" s="381" t="n"/>
+      <c r="AC15" s="381" t="n"/>
+      <c r="AD15" s="381" t="n"/>
+      <c r="AE15" s="381" t="n"/>
+      <c r="AF15" s="381" t="n"/>
+      <c r="AG15" s="381" t="n"/>
+      <c r="AH15" s="381" t="n"/>
+      <c r="AI15" s="381" t="n"/>
+      <c r="AJ15" s="381" t="n"/>
+      <c r="AK15" s="381" t="n"/>
+      <c r="AL15" s="381" t="n"/>
+      <c r="AM15" s="381" t="n"/>
+      <c r="AN15" s="381" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1" s="329">
-      <c r="A16" s="315" t="n"/>
-      <c r="B16" s="316" t="n"/>
-      <c r="C16" s="316" t="n"/>
-      <c r="D16" s="316" t="n"/>
-      <c r="E16" s="316" t="n"/>
-      <c r="F16" s="316" t="n"/>
-      <c r="G16" s="316" t="n"/>
-      <c r="H16" s="316" t="n"/>
+      <c r="A16" s="352" t="n"/>
+      <c r="B16" s="390" t="n"/>
+      <c r="C16" s="390" t="n"/>
+      <c r="D16" s="390" t="n"/>
+      <c r="E16" s="390" t="n"/>
+      <c r="F16" s="390" t="n"/>
+      <c r="G16" s="390" t="n"/>
+      <c r="H16" s="390" t="n"/>
+      <c r="I16" s="381" t="n"/>
+      <c r="J16" s="381" t="n"/>
+      <c r="K16" s="381" t="n"/>
+      <c r="L16" s="381" t="n"/>
+      <c r="M16" s="381" t="n"/>
+      <c r="N16" s="381" t="n"/>
+      <c r="O16" s="381" t="n"/>
+      <c r="P16" s="381" t="n"/>
+      <c r="Q16" s="381" t="n"/>
+      <c r="R16" s="381" t="n"/>
+      <c r="S16" s="381" t="n"/>
+      <c r="T16" s="381" t="n"/>
+      <c r="U16" s="381" t="n"/>
+      <c r="V16" s="381" t="n"/>
+      <c r="W16" s="381" t="n"/>
+      <c r="X16" s="381" t="n"/>
+      <c r="Y16" s="381" t="n"/>
+      <c r="Z16" s="381" t="n"/>
+      <c r="AA16" s="381" t="n"/>
+      <c r="AB16" s="381" t="n"/>
+      <c r="AC16" s="381" t="n"/>
+      <c r="AD16" s="381" t="n"/>
+      <c r="AE16" s="381" t="n"/>
+      <c r="AF16" s="381" t="n"/>
+      <c r="AG16" s="381" t="n"/>
+      <c r="AH16" s="381" t="n"/>
+      <c r="AI16" s="381" t="n"/>
+      <c r="AJ16" s="381" t="n"/>
+      <c r="AK16" s="381" t="n"/>
+      <c r="AL16" s="381" t="n"/>
+      <c r="AM16" s="381" t="n"/>
+      <c r="AN16" s="381" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1" s="329"/>
     <row r="18" ht="20" customHeight="1" s="329"/>
@@ -7102,7 +8323,8 @@
       <formula1>=LISTS!$D$2:$D$11</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <tableParts count="2">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
@@ -7116,30 +8338,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:AN13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" style="329" min="1" max="1"/>
-    <col width="52" customWidth="1" style="329" min="2" max="2"/>
-    <col width="65" customWidth="1" style="329" min="3" max="3"/>
-    <col width="18" customWidth="1" style="329" min="4" max="4"/>
-    <col width="18" customWidth="1" style="329" min="5" max="5"/>
-    <col width="18" customWidth="1" style="329" min="6" max="6"/>
-    <col width="24" customWidth="1" style="329" min="7" max="7"/>
+    <col width="2.33" customWidth="1" style="329" min="1" max="1"/>
+    <col width="2.33" customWidth="1" style="329" min="2" max="2"/>
+    <col width="2.33" customWidth="1" style="329" min="3" max="3"/>
+    <col width="2.33" customWidth="1" style="329" min="4" max="4"/>
+    <col width="2.33" customWidth="1" style="329" min="5" max="5"/>
+    <col width="2.33" customWidth="1" style="329" min="6" max="6"/>
+    <col width="2.33" customWidth="1" style="329" min="7" max="7"/>
+    <col width="2.33" customWidth="1" style="329" min="8" max="8"/>
+    <col width="2.33" customWidth="1" style="329" min="9" max="9"/>
+    <col width="2.33" customWidth="1" style="329" min="10" max="10"/>
+    <col width="2.33" customWidth="1" style="329" min="11" max="11"/>
+    <col width="2.33" customWidth="1" style="329" min="12" max="12"/>
+    <col width="2.33" customWidth="1" style="329" min="13" max="13"/>
+    <col width="2.33" customWidth="1" style="329" min="14" max="14"/>
+    <col width="2.33" customWidth="1" style="329" min="15" max="15"/>
+    <col width="2.33" customWidth="1" style="329" min="16" max="16"/>
+    <col width="2.33" customWidth="1" style="329" min="17" max="17"/>
+    <col width="2.33" customWidth="1" style="329" min="18" max="18"/>
+    <col width="2.33" customWidth="1" style="329" min="19" max="19"/>
+    <col width="2.33" customWidth="1" style="329" min="20" max="20"/>
+    <col width="2.33" customWidth="1" style="329" min="21" max="21"/>
+    <col width="2.33" customWidth="1" style="329" min="22" max="22"/>
+    <col width="2.33" customWidth="1" style="329" min="23" max="23"/>
+    <col width="2.33" customWidth="1" style="329" min="24" max="24"/>
+    <col width="2.33" customWidth="1" style="329" min="25" max="25"/>
+    <col width="2.33" customWidth="1" style="329" min="26" max="26"/>
+    <col width="2.33" customWidth="1" style="329" min="27" max="27"/>
+    <col width="2.33" customWidth="1" style="329" min="28" max="28"/>
+    <col width="2.33" customWidth="1" style="329" min="29" max="29"/>
+    <col width="2.33" customWidth="1" style="329" min="30" max="30"/>
+    <col width="2.33" customWidth="1" style="329" min="31" max="31"/>
+    <col width="2.33" customWidth="1" style="329" min="32" max="32"/>
+    <col width="2.33" customWidth="1" style="329" min="33" max="33"/>
+    <col width="2.33" customWidth="1" style="329" min="34" max="34"/>
+    <col width="2.33" customWidth="1" style="329" min="35" max="35"/>
+    <col width="2.33" customWidth="1" style="329" min="36" max="36"/>
+    <col width="2.33" customWidth="1" style="329" min="37" max="37"/>
+    <col width="2.33" customWidth="1" style="329" min="38" max="38"/>
+    <col width="2.33" customWidth="1" style="329" min="39" max="39"/>
+    <col width="2.33" customWidth="1" style="329" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1" s="329">
-      <c r="A1" s="334" t="inlineStr">
+      <c r="A1" s="386" t="inlineStr">
         <is>
           <t>Upstream References / Import Guidance</t>
         </is>
       </c>
-      <c r="B1" s="285" t="n"/>
-      <c r="C1" s="285" t="n"/>
-      <c r="D1" s="285" t="n"/>
-      <c r="E1" s="285" t="n"/>
-      <c r="F1" s="285" t="n"/>
-      <c r="G1" s="286" t="n"/>
+      <c r="B1" s="409" t="n"/>
+      <c r="C1" s="409" t="n"/>
+      <c r="D1" s="409" t="n"/>
+      <c r="E1" s="409" t="n"/>
+      <c r="F1" s="409" t="n"/>
+      <c r="G1" s="410" t="n"/>
+      <c r="H1" s="345" t="n"/>
+      <c r="I1" s="345" t="n"/>
+      <c r="J1" s="345" t="n"/>
+      <c r="K1" s="345" t="n"/>
+      <c r="L1" s="345" t="n"/>
+      <c r="M1" s="345" t="n"/>
+      <c r="N1" s="345" t="n"/>
+      <c r="O1" s="345" t="n"/>
+      <c r="P1" s="345" t="n"/>
+      <c r="Q1" s="345" t="n"/>
+      <c r="R1" s="345" t="n"/>
+      <c r="S1" s="345" t="n"/>
+      <c r="T1" s="345" t="n"/>
+      <c r="U1" s="345" t="n"/>
+      <c r="V1" s="345" t="n"/>
+      <c r="W1" s="345" t="n"/>
+      <c r="X1" s="345" t="n"/>
+      <c r="Y1" s="345" t="n"/>
+      <c r="Z1" s="345" t="n"/>
+      <c r="AA1" s="345" t="n"/>
+      <c r="AB1" s="345" t="n"/>
+      <c r="AC1" s="345" t="n"/>
+      <c r="AD1" s="345" t="n"/>
+      <c r="AE1" s="345" t="n"/>
+      <c r="AF1" s="345" t="n"/>
+      <c r="AG1" s="345" t="n"/>
+      <c r="AH1" s="345" t="n"/>
+      <c r="AI1" s="345" t="n"/>
+      <c r="AJ1" s="345" t="n"/>
+      <c r="AK1" s="345" t="n"/>
+      <c r="AL1" s="345" t="n"/>
+      <c r="AM1" s="345" t="n"/>
+      <c r="AN1" s="345" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1" s="329">
       <c r="A2" s="335" t="inlineStr">
@@ -7147,181 +8435,625 @@
           <t>Incoming verification event record for outsourced process returns and discrete disposition decisions.</t>
         </is>
       </c>
+      <c r="H2" s="345" t="n"/>
+      <c r="I2" s="345" t="n"/>
+      <c r="J2" s="345" t="n"/>
+      <c r="K2" s="345" t="n"/>
+      <c r="L2" s="345" t="n"/>
+      <c r="M2" s="345" t="n"/>
+      <c r="N2" s="345" t="n"/>
+      <c r="O2" s="345" t="n"/>
+      <c r="P2" s="345" t="n"/>
+      <c r="Q2" s="345" t="n"/>
+      <c r="R2" s="345" t="n"/>
+      <c r="S2" s="345" t="n"/>
+      <c r="T2" s="345" t="n"/>
+      <c r="U2" s="345" t="n"/>
+      <c r="V2" s="345" t="n"/>
+      <c r="W2" s="345" t="n"/>
+      <c r="X2" s="345" t="n"/>
+      <c r="Y2" s="345" t="n"/>
+      <c r="Z2" s="345" t="n"/>
+      <c r="AA2" s="345" t="n"/>
+      <c r="AB2" s="345" t="n"/>
+      <c r="AC2" s="345" t="n"/>
+      <c r="AD2" s="345" t="n"/>
+      <c r="AE2" s="345" t="n"/>
+      <c r="AF2" s="345" t="n"/>
+      <c r="AG2" s="345" t="n"/>
+      <c r="AH2" s="345" t="n"/>
+      <c r="AI2" s="345" t="n"/>
+      <c r="AJ2" s="345" t="n"/>
+      <c r="AK2" s="345" t="n"/>
+      <c r="AL2" s="345" t="n"/>
+      <c r="AM2" s="345" t="n"/>
+      <c r="AN2" s="345" t="n"/>
     </row>
-    <row r="3" ht="18" customHeight="1" s="329"/>
+    <row r="3" ht="18" customHeight="1" s="329">
+      <c r="A3" s="345" t="n"/>
+      <c r="B3" s="345" t="n"/>
+      <c r="C3" s="345" t="n"/>
+      <c r="D3" s="345" t="n"/>
+      <c r="E3" s="345" t="n"/>
+      <c r="F3" s="345" t="n"/>
+      <c r="G3" s="345" t="n"/>
+      <c r="H3" s="345" t="n"/>
+      <c r="I3" s="345" t="n"/>
+      <c r="J3" s="345" t="n"/>
+      <c r="K3" s="345" t="n"/>
+      <c r="L3" s="345" t="n"/>
+      <c r="M3" s="345" t="n"/>
+      <c r="N3" s="345" t="n"/>
+      <c r="O3" s="345" t="n"/>
+      <c r="P3" s="345" t="n"/>
+      <c r="Q3" s="345" t="n"/>
+      <c r="R3" s="345" t="n"/>
+      <c r="S3" s="345" t="n"/>
+      <c r="T3" s="345" t="n"/>
+      <c r="U3" s="345" t="n"/>
+      <c r="V3" s="345" t="n"/>
+      <c r="W3" s="345" t="n"/>
+      <c r="X3" s="345" t="n"/>
+      <c r="Y3" s="345" t="n"/>
+      <c r="Z3" s="345" t="n"/>
+      <c r="AA3" s="345" t="n"/>
+      <c r="AB3" s="345" t="n"/>
+      <c r="AC3" s="345" t="n"/>
+      <c r="AD3" s="345" t="n"/>
+      <c r="AE3" s="345" t="n"/>
+      <c r="AF3" s="345" t="n"/>
+      <c r="AG3" s="345" t="n"/>
+      <c r="AH3" s="345" t="n"/>
+      <c r="AI3" s="345" t="n"/>
+      <c r="AJ3" s="345" t="n"/>
+      <c r="AK3" s="345" t="n"/>
+      <c r="AL3" s="345" t="n"/>
+      <c r="AM3" s="345" t="n"/>
+      <c r="AN3" s="345" t="n"/>
+    </row>
     <row r="4" ht="20" customHeight="1" s="329">
-      <c r="A4" s="336" t="inlineStr">
+      <c r="A4" s="387" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B4" s="336" t="inlineStr">
+      <c r="B4" s="387" t="inlineStr">
         <is>
           <t>Value / Reference</t>
         </is>
       </c>
-      <c r="C4" s="336" t="inlineStr">
+      <c r="C4" s="387" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
+      <c r="D4" s="345" t="n"/>
+      <c r="E4" s="345" t="n"/>
+      <c r="F4" s="345" t="n"/>
+      <c r="G4" s="345" t="n"/>
+      <c r="H4" s="345" t="n"/>
+      <c r="I4" s="345" t="n"/>
+      <c r="J4" s="345" t="n"/>
+      <c r="K4" s="345" t="n"/>
+      <c r="L4" s="345" t="n"/>
+      <c r="M4" s="345" t="n"/>
+      <c r="N4" s="345" t="n"/>
+      <c r="O4" s="345" t="n"/>
+      <c r="P4" s="345" t="n"/>
+      <c r="Q4" s="345" t="n"/>
+      <c r="R4" s="345" t="n"/>
+      <c r="S4" s="345" t="n"/>
+      <c r="T4" s="345" t="n"/>
+      <c r="U4" s="345" t="n"/>
+      <c r="V4" s="345" t="n"/>
+      <c r="W4" s="345" t="n"/>
+      <c r="X4" s="345" t="n"/>
+      <c r="Y4" s="345" t="n"/>
+      <c r="Z4" s="345" t="n"/>
+      <c r="AA4" s="345" t="n"/>
+      <c r="AB4" s="345" t="n"/>
+      <c r="AC4" s="345" t="n"/>
+      <c r="AD4" s="345" t="n"/>
+      <c r="AE4" s="345" t="n"/>
+      <c r="AF4" s="345" t="n"/>
+      <c r="AG4" s="345" t="n"/>
+      <c r="AH4" s="345" t="n"/>
+      <c r="AI4" s="345" t="n"/>
+      <c r="AJ4" s="345" t="n"/>
+      <c r="AK4" s="345" t="n"/>
+      <c r="AL4" s="345" t="n"/>
+      <c r="AM4" s="345" t="n"/>
+      <c r="AN4" s="345" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1" s="329">
-      <c r="A5" s="315" t="inlineStr">
+      <c r="A5" s="388" t="inlineStr">
         <is>
           <t>Source of Truth</t>
         </is>
       </c>
-      <c r="B5" s="316" t="inlineStr">
+      <c r="B5" s="389" t="inlineStr">
         <is>
           <t>Epicor transaction + M365 evidence</t>
         </is>
       </c>
-      <c r="C5" s="316" t="inlineStr">
+      <c r="C5" s="389" t="inlineStr">
         <is>
           <t>Do not duplicate ERP/M365/ANNEX master data.</t>
         </is>
       </c>
+      <c r="D5" s="345" t="n"/>
+      <c r="E5" s="345" t="n"/>
+      <c r="F5" s="345" t="n"/>
+      <c r="G5" s="345" t="n"/>
+      <c r="H5" s="345" t="n"/>
+      <c r="I5" s="345" t="n"/>
+      <c r="J5" s="345" t="n"/>
+      <c r="K5" s="345" t="n"/>
+      <c r="L5" s="345" t="n"/>
+      <c r="M5" s="345" t="n"/>
+      <c r="N5" s="345" t="n"/>
+      <c r="O5" s="345" t="n"/>
+      <c r="P5" s="345" t="n"/>
+      <c r="Q5" s="345" t="n"/>
+      <c r="R5" s="345" t="n"/>
+      <c r="S5" s="345" t="n"/>
+      <c r="T5" s="345" t="n"/>
+      <c r="U5" s="345" t="n"/>
+      <c r="V5" s="345" t="n"/>
+      <c r="W5" s="345" t="n"/>
+      <c r="X5" s="345" t="n"/>
+      <c r="Y5" s="345" t="n"/>
+      <c r="Z5" s="345" t="n"/>
+      <c r="AA5" s="345" t="n"/>
+      <c r="AB5" s="345" t="n"/>
+      <c r="AC5" s="345" t="n"/>
+      <c r="AD5" s="345" t="n"/>
+      <c r="AE5" s="345" t="n"/>
+      <c r="AF5" s="345" t="n"/>
+      <c r="AG5" s="345" t="n"/>
+      <c r="AH5" s="345" t="n"/>
+      <c r="AI5" s="345" t="n"/>
+      <c r="AJ5" s="345" t="n"/>
+      <c r="AK5" s="345" t="n"/>
+      <c r="AL5" s="345" t="n"/>
+      <c r="AM5" s="345" t="n"/>
+      <c r="AN5" s="345" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1" s="329">
-      <c r="A6" s="315" t="inlineStr">
+      <c r="A6" s="388" t="inlineStr">
         <is>
           <t>Cross-Reference Boundary</t>
         </is>
       </c>
-      <c r="B6" s="316" t="inlineStr">
+      <c r="B6" s="389" t="inlineStr">
         <is>
           <t>This form does not replace SOP-402; it records the evidence, data or decision required by that SOP.
 Rules, matrices, dictionaries, acceptance criteria and data definitions belong in ANNEX-PUR-001/002/003 + ANNEX-ENG-002; do not copy ANNEX content into the live data-entry body.
 System-of-record / source-of-truth boundary: Epicor transaction + M365 evidence. If the master data already live there, reference or import them; do not re-key without need.</t>
         </is>
       </c>
-      <c r="C6" s="316" t="inlineStr">
+      <c r="C6" s="389" t="inlineStr">
         <is>
           <t>This form does not replace SOP-402; it records the evidence, data or decision required by that SOP.
 Rules, matrices, dictionaries, acceptance criteria and data definitions belong in ANNEX-PUR-001/002/003 + ANNEX-ENG-002; do not copy ANNEX content into the live data-entry body.
 System-of-record / source-of-truth boundary: Epicor transaction + M365 evidence. If the master data already live there, reference or import them; do not re-key without need.</t>
         </is>
       </c>
+      <c r="D6" s="345" t="n"/>
+      <c r="E6" s="345" t="n"/>
+      <c r="F6" s="345" t="n"/>
+      <c r="G6" s="345" t="n"/>
+      <c r="H6" s="345" t="n"/>
+      <c r="I6" s="345" t="n"/>
+      <c r="J6" s="345" t="n"/>
+      <c r="K6" s="345" t="n"/>
+      <c r="L6" s="345" t="n"/>
+      <c r="M6" s="345" t="n"/>
+      <c r="N6" s="345" t="n"/>
+      <c r="O6" s="345" t="n"/>
+      <c r="P6" s="345" t="n"/>
+      <c r="Q6" s="345" t="n"/>
+      <c r="R6" s="345" t="n"/>
+      <c r="S6" s="345" t="n"/>
+      <c r="T6" s="345" t="n"/>
+      <c r="U6" s="345" t="n"/>
+      <c r="V6" s="345" t="n"/>
+      <c r="W6" s="345" t="n"/>
+      <c r="X6" s="345" t="n"/>
+      <c r="Y6" s="345" t="n"/>
+      <c r="Z6" s="345" t="n"/>
+      <c r="AA6" s="345" t="n"/>
+      <c r="AB6" s="345" t="n"/>
+      <c r="AC6" s="345" t="n"/>
+      <c r="AD6" s="345" t="n"/>
+      <c r="AE6" s="345" t="n"/>
+      <c r="AF6" s="345" t="n"/>
+      <c r="AG6" s="345" t="n"/>
+      <c r="AH6" s="345" t="n"/>
+      <c r="AI6" s="345" t="n"/>
+      <c r="AJ6" s="345" t="n"/>
+      <c r="AK6" s="345" t="n"/>
+      <c r="AL6" s="345" t="n"/>
+      <c r="AM6" s="345" t="n"/>
+      <c r="AN6" s="345" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1" s="329">
-      <c r="A7" s="315" t="inlineStr">
+      <c r="A7" s="388" t="inlineStr">
         <is>
           <t>SOP-402</t>
         </is>
       </c>
-      <c r="B7" s="316" t="inlineStr">
+      <c r="B7" s="389" t="inlineStr">
         <is>
           <t>SOP-402 — Xác minh vật liệu, truy xuất và phòng chống vật tư giả/không rõ nguồn gốc | HESEM QMS</t>
         </is>
       </c>
-      <c r="C7" s="316" t="inlineStr">
+      <c r="C7" s="389" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/01-SOPs/04-SOP-400/sop-402-material-verification-traceability-and-counterfeit-prevention.html</t>
         </is>
       </c>
+      <c r="D7" s="345" t="n"/>
+      <c r="E7" s="345" t="n"/>
+      <c r="F7" s="345" t="n"/>
+      <c r="G7" s="345" t="n"/>
+      <c r="H7" s="345" t="n"/>
+      <c r="I7" s="345" t="n"/>
+      <c r="J7" s="345" t="n"/>
+      <c r="K7" s="345" t="n"/>
+      <c r="L7" s="345" t="n"/>
+      <c r="M7" s="345" t="n"/>
+      <c r="N7" s="345" t="n"/>
+      <c r="O7" s="345" t="n"/>
+      <c r="P7" s="345" t="n"/>
+      <c r="Q7" s="345" t="n"/>
+      <c r="R7" s="345" t="n"/>
+      <c r="S7" s="345" t="n"/>
+      <c r="T7" s="345" t="n"/>
+      <c r="U7" s="345" t="n"/>
+      <c r="V7" s="345" t="n"/>
+      <c r="W7" s="345" t="n"/>
+      <c r="X7" s="345" t="n"/>
+      <c r="Y7" s="345" t="n"/>
+      <c r="Z7" s="345" t="n"/>
+      <c r="AA7" s="345" t="n"/>
+      <c r="AB7" s="345" t="n"/>
+      <c r="AC7" s="345" t="n"/>
+      <c r="AD7" s="345" t="n"/>
+      <c r="AE7" s="345" t="n"/>
+      <c r="AF7" s="345" t="n"/>
+      <c r="AG7" s="345" t="n"/>
+      <c r="AH7" s="345" t="n"/>
+      <c r="AI7" s="345" t="n"/>
+      <c r="AJ7" s="345" t="n"/>
+      <c r="AK7" s="345" t="n"/>
+      <c r="AL7" s="345" t="n"/>
+      <c r="AM7" s="345" t="n"/>
+      <c r="AN7" s="345" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1" s="329">
-      <c r="A8" s="315" t="inlineStr">
+      <c r="A8" s="352" t="inlineStr">
         <is>
           <t>ANNEX-PUR-001</t>
         </is>
       </c>
-      <c r="B8" s="316" t="inlineStr">
+      <c r="B8" s="390" t="inlineStr">
         <is>
           <t>ANNEX-PUR-001 — Mô hình rủi ro nhà cung cấp và phương pháp scorecard</t>
         </is>
       </c>
-      <c r="C8" s="316" t="inlineStr">
+      <c r="C8" s="390" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-001-supplier-risk-model-and-scorecard-method.html</t>
         </is>
       </c>
+      <c r="D8" s="381" t="n"/>
+      <c r="E8" s="381" t="n"/>
+      <c r="F8" s="381" t="n"/>
+      <c r="G8" s="381" t="n"/>
+      <c r="H8" s="381" t="n"/>
+      <c r="I8" s="381" t="n"/>
+      <c r="J8" s="381" t="n"/>
+      <c r="K8" s="381" t="n"/>
+      <c r="L8" s="381" t="n"/>
+      <c r="M8" s="381" t="n"/>
+      <c r="N8" s="381" t="n"/>
+      <c r="O8" s="381" t="n"/>
+      <c r="P8" s="381" t="n"/>
+      <c r="Q8" s="381" t="n"/>
+      <c r="R8" s="381" t="n"/>
+      <c r="S8" s="381" t="n"/>
+      <c r="T8" s="381" t="n"/>
+      <c r="U8" s="381" t="n"/>
+      <c r="V8" s="381" t="n"/>
+      <c r="W8" s="381" t="n"/>
+      <c r="X8" s="381" t="n"/>
+      <c r="Y8" s="381" t="n"/>
+      <c r="Z8" s="381" t="n"/>
+      <c r="AA8" s="381" t="n"/>
+      <c r="AB8" s="381" t="n"/>
+      <c r="AC8" s="381" t="n"/>
+      <c r="AD8" s="381" t="n"/>
+      <c r="AE8" s="381" t="n"/>
+      <c r="AF8" s="381" t="n"/>
+      <c r="AG8" s="381" t="n"/>
+      <c r="AH8" s="381" t="n"/>
+      <c r="AI8" s="381" t="n"/>
+      <c r="AJ8" s="381" t="n"/>
+      <c r="AK8" s="381" t="n"/>
+      <c r="AL8" s="381" t="n"/>
+      <c r="AM8" s="381" t="n"/>
+      <c r="AN8" s="381" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1" s="329">
-      <c r="A9" s="315" t="inlineStr">
+      <c r="A9" s="352" t="inlineStr">
         <is>
           <t>ANNEX-PUR-002</t>
         </is>
       </c>
-      <c r="B9" s="316" t="inlineStr">
+      <c r="B9" s="390" t="inlineStr">
         <is>
           <t>ANNEX-PUR-002 — Gói kiểm soát outsource / special process / cert flow-down</t>
         </is>
       </c>
-      <c r="C9" s="316" t="inlineStr">
+      <c r="C9" s="390" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-002-outsource-special-process-pack.html</t>
         </is>
       </c>
+      <c r="D9" s="381" t="n"/>
+      <c r="E9" s="381" t="n"/>
+      <c r="F9" s="381" t="n"/>
+      <c r="G9" s="381" t="n"/>
+      <c r="H9" s="381" t="n"/>
+      <c r="I9" s="381" t="n"/>
+      <c r="J9" s="381" t="n"/>
+      <c r="K9" s="381" t="n"/>
+      <c r="L9" s="381" t="n"/>
+      <c r="M9" s="381" t="n"/>
+      <c r="N9" s="381" t="n"/>
+      <c r="O9" s="381" t="n"/>
+      <c r="P9" s="381" t="n"/>
+      <c r="Q9" s="381" t="n"/>
+      <c r="R9" s="381" t="n"/>
+      <c r="S9" s="381" t="n"/>
+      <c r="T9" s="381" t="n"/>
+      <c r="U9" s="381" t="n"/>
+      <c r="V9" s="381" t="n"/>
+      <c r="W9" s="381" t="n"/>
+      <c r="X9" s="381" t="n"/>
+      <c r="Y9" s="381" t="n"/>
+      <c r="Z9" s="381" t="n"/>
+      <c r="AA9" s="381" t="n"/>
+      <c r="AB9" s="381" t="n"/>
+      <c r="AC9" s="381" t="n"/>
+      <c r="AD9" s="381" t="n"/>
+      <c r="AE9" s="381" t="n"/>
+      <c r="AF9" s="381" t="n"/>
+      <c r="AG9" s="381" t="n"/>
+      <c r="AH9" s="381" t="n"/>
+      <c r="AI9" s="381" t="n"/>
+      <c r="AJ9" s="381" t="n"/>
+      <c r="AK9" s="381" t="n"/>
+      <c r="AL9" s="381" t="n"/>
+      <c r="AM9" s="381" t="n"/>
+      <c r="AN9" s="381" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1" s="329">
-      <c r="A10" s="315" t="inlineStr">
+      <c r="A10" s="352" t="inlineStr">
         <is>
           <t>ANNEX-PUR-003</t>
         </is>
       </c>
-      <c r="B10" s="316" t="inlineStr">
+      <c r="B10" s="390" t="inlineStr">
         <is>
           <t>ANNEX-PUR-003 — Approved processor list, scope approval và rule tạm ngưng</t>
         </is>
       </c>
-      <c r="C10" s="316" t="inlineStr">
+      <c r="C10" s="390" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-003-approved-processor-list.html</t>
         </is>
       </c>
+      <c r="D10" s="381" t="n"/>
+      <c r="E10" s="381" t="n"/>
+      <c r="F10" s="381" t="n"/>
+      <c r="G10" s="381" t="n"/>
+      <c r="H10" s="381" t="n"/>
+      <c r="I10" s="381" t="n"/>
+      <c r="J10" s="381" t="n"/>
+      <c r="K10" s="381" t="n"/>
+      <c r="L10" s="381" t="n"/>
+      <c r="M10" s="381" t="n"/>
+      <c r="N10" s="381" t="n"/>
+      <c r="O10" s="381" t="n"/>
+      <c r="P10" s="381" t="n"/>
+      <c r="Q10" s="381" t="n"/>
+      <c r="R10" s="381" t="n"/>
+      <c r="S10" s="381" t="n"/>
+      <c r="T10" s="381" t="n"/>
+      <c r="U10" s="381" t="n"/>
+      <c r="V10" s="381" t="n"/>
+      <c r="W10" s="381" t="n"/>
+      <c r="X10" s="381" t="n"/>
+      <c r="Y10" s="381" t="n"/>
+      <c r="Z10" s="381" t="n"/>
+      <c r="AA10" s="381" t="n"/>
+      <c r="AB10" s="381" t="n"/>
+      <c r="AC10" s="381" t="n"/>
+      <c r="AD10" s="381" t="n"/>
+      <c r="AE10" s="381" t="n"/>
+      <c r="AF10" s="381" t="n"/>
+      <c r="AG10" s="381" t="n"/>
+      <c r="AH10" s="381" t="n"/>
+      <c r="AI10" s="381" t="n"/>
+      <c r="AJ10" s="381" t="n"/>
+      <c r="AK10" s="381" t="n"/>
+      <c r="AL10" s="381" t="n"/>
+      <c r="AM10" s="381" t="n"/>
+      <c r="AN10" s="381" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1" s="329">
-      <c r="A11" s="315" t="inlineStr">
+      <c r="A11" s="352" t="inlineStr">
         <is>
           <t>ANNEX-ENG-002</t>
         </is>
       </c>
-      <c r="B11" s="316" t="inlineStr">
+      <c r="B11" s="390" t="inlineStr">
         <is>
           <t>ANNEX-ENG-002 — Approved materials list, source restriction và rule thay thế</t>
         </is>
       </c>
-      <c r="C11" s="316" t="inlineStr">
+      <c r="C11" s="390" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-eng-002-approved-materials-list.html</t>
         </is>
       </c>
+      <c r="D11" s="381" t="n"/>
+      <c r="E11" s="381" t="n"/>
+      <c r="F11" s="381" t="n"/>
+      <c r="G11" s="381" t="n"/>
+      <c r="H11" s="381" t="n"/>
+      <c r="I11" s="381" t="n"/>
+      <c r="J11" s="381" t="n"/>
+      <c r="K11" s="381" t="n"/>
+      <c r="L11" s="381" t="n"/>
+      <c r="M11" s="381" t="n"/>
+      <c r="N11" s="381" t="n"/>
+      <c r="O11" s="381" t="n"/>
+      <c r="P11" s="381" t="n"/>
+      <c r="Q11" s="381" t="n"/>
+      <c r="R11" s="381" t="n"/>
+      <c r="S11" s="381" t="n"/>
+      <c r="T11" s="381" t="n"/>
+      <c r="U11" s="381" t="n"/>
+      <c r="V11" s="381" t="n"/>
+      <c r="W11" s="381" t="n"/>
+      <c r="X11" s="381" t="n"/>
+      <c r="Y11" s="381" t="n"/>
+      <c r="Z11" s="381" t="n"/>
+      <c r="AA11" s="381" t="n"/>
+      <c r="AB11" s="381" t="n"/>
+      <c r="AC11" s="381" t="n"/>
+      <c r="AD11" s="381" t="n"/>
+      <c r="AE11" s="381" t="n"/>
+      <c r="AF11" s="381" t="n"/>
+      <c r="AG11" s="381" t="n"/>
+      <c r="AH11" s="381" t="n"/>
+      <c r="AI11" s="381" t="n"/>
+      <c r="AJ11" s="381" t="n"/>
+      <c r="AK11" s="381" t="n"/>
+      <c r="AL11" s="381" t="n"/>
+      <c r="AM11" s="381" t="n"/>
+      <c r="AN11" s="381" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1" s="329">
-      <c r="A12" s="315" t="inlineStr">
+      <c r="A12" s="352" t="inlineStr">
         <is>
           <t>Open When</t>
         </is>
       </c>
-      <c r="B12" s="316" t="inlineStr">
+      <c r="B12" s="390" t="inlineStr">
         <is>
           <t>Open immediately when the event, request, issue, change, complaint, risk or incident is detected or formally raised.</t>
         </is>
       </c>
-      <c r="C12" s="316" t="inlineStr">
+      <c r="C12" s="390" t="inlineStr">
         <is>
           <t>Operational trigger</t>
         </is>
       </c>
+      <c r="D12" s="381" t="n"/>
+      <c r="E12" s="381" t="n"/>
+      <c r="F12" s="381" t="n"/>
+      <c r="G12" s="381" t="n"/>
+      <c r="H12" s="381" t="n"/>
+      <c r="I12" s="381" t="n"/>
+      <c r="J12" s="381" t="n"/>
+      <c r="K12" s="381" t="n"/>
+      <c r="L12" s="381" t="n"/>
+      <c r="M12" s="381" t="n"/>
+      <c r="N12" s="381" t="n"/>
+      <c r="O12" s="381" t="n"/>
+      <c r="P12" s="381" t="n"/>
+      <c r="Q12" s="381" t="n"/>
+      <c r="R12" s="381" t="n"/>
+      <c r="S12" s="381" t="n"/>
+      <c r="T12" s="381" t="n"/>
+      <c r="U12" s="381" t="n"/>
+      <c r="V12" s="381" t="n"/>
+      <c r="W12" s="381" t="n"/>
+      <c r="X12" s="381" t="n"/>
+      <c r="Y12" s="381" t="n"/>
+      <c r="Z12" s="381" t="n"/>
+      <c r="AA12" s="381" t="n"/>
+      <c r="AB12" s="381" t="n"/>
+      <c r="AC12" s="381" t="n"/>
+      <c r="AD12" s="381" t="n"/>
+      <c r="AE12" s="381" t="n"/>
+      <c r="AF12" s="381" t="n"/>
+      <c r="AG12" s="381" t="n"/>
+      <c r="AH12" s="381" t="n"/>
+      <c r="AI12" s="381" t="n"/>
+      <c r="AJ12" s="381" t="n"/>
+      <c r="AK12" s="381" t="n"/>
+      <c r="AL12" s="381" t="n"/>
+      <c r="AM12" s="381" t="n"/>
+      <c r="AN12" s="381" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1" s="329">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="381" t="inlineStr">
         <is>
           <t>Close When</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="381" t="inlineStr">
         <is>
           <t>Close when the final decision, final owner, final disposition and required follow-up actions are all recorded and the evidence package is complete.</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="381" t="inlineStr">
         <is>
           <t>Release / closure rule</t>
         </is>
       </c>
+      <c r="D13" s="381" t="n"/>
+      <c r="E13" s="381" t="n"/>
+      <c r="F13" s="381" t="n"/>
+      <c r="G13" s="381" t="n"/>
+      <c r="H13" s="381" t="n"/>
+      <c r="I13" s="381" t="n"/>
+      <c r="J13" s="381" t="n"/>
+      <c r="K13" s="381" t="n"/>
+      <c r="L13" s="381" t="n"/>
+      <c r="M13" s="381" t="n"/>
+      <c r="N13" s="381" t="n"/>
+      <c r="O13" s="381" t="n"/>
+      <c r="P13" s="381" t="n"/>
+      <c r="Q13" s="381" t="n"/>
+      <c r="R13" s="381" t="n"/>
+      <c r="S13" s="381" t="n"/>
+      <c r="T13" s="381" t="n"/>
+      <c r="U13" s="381" t="n"/>
+      <c r="V13" s="381" t="n"/>
+      <c r="W13" s="381" t="n"/>
+      <c r="X13" s="381" t="n"/>
+      <c r="Y13" s="381" t="n"/>
+      <c r="Z13" s="381" t="n"/>
+      <c r="AA13" s="381" t="n"/>
+      <c r="AB13" s="381" t="n"/>
+      <c r="AC13" s="381" t="n"/>
+      <c r="AD13" s="381" t="n"/>
+      <c r="AE13" s="381" t="n"/>
+      <c r="AF13" s="381" t="n"/>
+      <c r="AG13" s="381" t="n"/>
+      <c r="AH13" s="381" t="n"/>
+      <c r="AI13" s="381" t="n"/>
+      <c r="AJ13" s="381" t="n"/>
+      <c r="AK13" s="381" t="n"/>
+      <c r="AL13" s="381" t="n"/>
+      <c r="AM13" s="381" t="n"/>
+      <c r="AN13" s="381" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1" s="329"/>
     <row r="15" ht="20" customHeight="1" s="329"/>
@@ -7345,7 +9077,8 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -7355,30 +9088,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:AN13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" style="329" min="1" max="1"/>
-    <col width="52" customWidth="1" style="329" min="2" max="2"/>
-    <col width="65" customWidth="1" style="329" min="3" max="3"/>
-    <col width="18" customWidth="1" style="329" min="4" max="4"/>
-    <col width="18" customWidth="1" style="329" min="5" max="5"/>
-    <col width="18" customWidth="1" style="329" min="6" max="6"/>
-    <col width="24" customWidth="1" style="329" min="7" max="7"/>
+    <col width="2.33" customWidth="1" style="329" min="1" max="1"/>
+    <col width="2.33" customWidth="1" style="329" min="2" max="2"/>
+    <col width="2.33" customWidth="1" style="329" min="3" max="3"/>
+    <col width="2.33" customWidth="1" style="329" min="4" max="4"/>
+    <col width="2.33" customWidth="1" style="329" min="5" max="5"/>
+    <col width="2.33" customWidth="1" style="329" min="6" max="6"/>
+    <col width="2.33" customWidth="1" style="329" min="7" max="7"/>
+    <col width="2.33" customWidth="1" style="329" min="8" max="8"/>
+    <col width="2.33" customWidth="1" style="329" min="9" max="9"/>
+    <col width="2.33" customWidth="1" style="329" min="10" max="10"/>
+    <col width="2.33" customWidth="1" style="329" min="11" max="11"/>
+    <col width="2.33" customWidth="1" style="329" min="12" max="12"/>
+    <col width="2.33" customWidth="1" style="329" min="13" max="13"/>
+    <col width="2.33" customWidth="1" style="329" min="14" max="14"/>
+    <col width="2.33" customWidth="1" style="329" min="15" max="15"/>
+    <col width="2.33" customWidth="1" style="329" min="16" max="16"/>
+    <col width="2.33" customWidth="1" style="329" min="17" max="17"/>
+    <col width="2.33" customWidth="1" style="329" min="18" max="18"/>
+    <col width="2.33" customWidth="1" style="329" min="19" max="19"/>
+    <col width="2.33" customWidth="1" style="329" min="20" max="20"/>
+    <col width="2.33" customWidth="1" style="329" min="21" max="21"/>
+    <col width="2.33" customWidth="1" style="329" min="22" max="22"/>
+    <col width="2.33" customWidth="1" style="329" min="23" max="23"/>
+    <col width="2.33" customWidth="1" style="329" min="24" max="24"/>
+    <col width="2.33" customWidth="1" style="329" min="25" max="25"/>
+    <col width="2.33" customWidth="1" style="329" min="26" max="26"/>
+    <col width="2.33" customWidth="1" style="329" min="27" max="27"/>
+    <col width="2.33" customWidth="1" style="329" min="28" max="28"/>
+    <col width="2.33" customWidth="1" style="329" min="29" max="29"/>
+    <col width="2.33" customWidth="1" style="329" min="30" max="30"/>
+    <col width="2.33" customWidth="1" style="329" min="31" max="31"/>
+    <col width="2.33" customWidth="1" style="329" min="32" max="32"/>
+    <col width="2.33" customWidth="1" style="329" min="33" max="33"/>
+    <col width="2.33" customWidth="1" style="329" min="34" max="34"/>
+    <col width="2.33" customWidth="1" style="329" min="35" max="35"/>
+    <col width="2.33" customWidth="1" style="329" min="36" max="36"/>
+    <col width="2.33" customWidth="1" style="329" min="37" max="37"/>
+    <col width="2.33" customWidth="1" style="329" min="38" max="38"/>
+    <col width="2.33" customWidth="1" style="329" min="39" max="39"/>
+    <col width="2.33" customWidth="1" style="329" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1" s="329">
-      <c r="A1" s="334" t="inlineStr">
+      <c r="A1" s="386" t="inlineStr">
         <is>
           <t>Evidence Reference / Attachment Guidance</t>
         </is>
       </c>
-      <c r="B1" s="285" t="n"/>
-      <c r="C1" s="285" t="n"/>
-      <c r="D1" s="285" t="n"/>
-      <c r="E1" s="285" t="n"/>
-      <c r="F1" s="285" t="n"/>
-      <c r="G1" s="286" t="n"/>
+      <c r="B1" s="409" t="n"/>
+      <c r="C1" s="409" t="n"/>
+      <c r="D1" s="409" t="n"/>
+      <c r="E1" s="409" t="n"/>
+      <c r="F1" s="409" t="n"/>
+      <c r="G1" s="410" t="n"/>
+      <c r="H1" s="345" t="n"/>
+      <c r="I1" s="345" t="n"/>
+      <c r="J1" s="345" t="n"/>
+      <c r="K1" s="345" t="n"/>
+      <c r="L1" s="345" t="n"/>
+      <c r="M1" s="345" t="n"/>
+      <c r="N1" s="345" t="n"/>
+      <c r="O1" s="345" t="n"/>
+      <c r="P1" s="345" t="n"/>
+      <c r="Q1" s="345" t="n"/>
+      <c r="R1" s="345" t="n"/>
+      <c r="S1" s="345" t="n"/>
+      <c r="T1" s="345" t="n"/>
+      <c r="U1" s="345" t="n"/>
+      <c r="V1" s="345" t="n"/>
+      <c r="W1" s="345" t="n"/>
+      <c r="X1" s="345" t="n"/>
+      <c r="Y1" s="345" t="n"/>
+      <c r="Z1" s="345" t="n"/>
+      <c r="AA1" s="345" t="n"/>
+      <c r="AB1" s="345" t="n"/>
+      <c r="AC1" s="345" t="n"/>
+      <c r="AD1" s="345" t="n"/>
+      <c r="AE1" s="345" t="n"/>
+      <c r="AF1" s="345" t="n"/>
+      <c r="AG1" s="345" t="n"/>
+      <c r="AH1" s="345" t="n"/>
+      <c r="AI1" s="345" t="n"/>
+      <c r="AJ1" s="345" t="n"/>
+      <c r="AK1" s="345" t="n"/>
+      <c r="AL1" s="345" t="n"/>
+      <c r="AM1" s="345" t="n"/>
+      <c r="AN1" s="345" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1" s="329">
       <c r="A2" s="335" t="inlineStr">
@@ -7386,181 +9185,625 @@
           <t>Use controlled evidence package references; do not free-type vague placeholders.</t>
         </is>
       </c>
+      <c r="H2" s="345" t="n"/>
+      <c r="I2" s="345" t="n"/>
+      <c r="J2" s="345" t="n"/>
+      <c r="K2" s="345" t="n"/>
+      <c r="L2" s="345" t="n"/>
+      <c r="M2" s="345" t="n"/>
+      <c r="N2" s="345" t="n"/>
+      <c r="O2" s="345" t="n"/>
+      <c r="P2" s="345" t="n"/>
+      <c r="Q2" s="345" t="n"/>
+      <c r="R2" s="345" t="n"/>
+      <c r="S2" s="345" t="n"/>
+      <c r="T2" s="345" t="n"/>
+      <c r="U2" s="345" t="n"/>
+      <c r="V2" s="345" t="n"/>
+      <c r="W2" s="345" t="n"/>
+      <c r="X2" s="345" t="n"/>
+      <c r="Y2" s="345" t="n"/>
+      <c r="Z2" s="345" t="n"/>
+      <c r="AA2" s="345" t="n"/>
+      <c r="AB2" s="345" t="n"/>
+      <c r="AC2" s="345" t="n"/>
+      <c r="AD2" s="345" t="n"/>
+      <c r="AE2" s="345" t="n"/>
+      <c r="AF2" s="345" t="n"/>
+      <c r="AG2" s="345" t="n"/>
+      <c r="AH2" s="345" t="n"/>
+      <c r="AI2" s="345" t="n"/>
+      <c r="AJ2" s="345" t="n"/>
+      <c r="AK2" s="345" t="n"/>
+      <c r="AL2" s="345" t="n"/>
+      <c r="AM2" s="345" t="n"/>
+      <c r="AN2" s="345" t="n"/>
     </row>
-    <row r="3" ht="18" customHeight="1" s="329"/>
+    <row r="3" ht="18" customHeight="1" s="329">
+      <c r="A3" s="345" t="n"/>
+      <c r="B3" s="345" t="n"/>
+      <c r="C3" s="345" t="n"/>
+      <c r="D3" s="345" t="n"/>
+      <c r="E3" s="345" t="n"/>
+      <c r="F3" s="345" t="n"/>
+      <c r="G3" s="345" t="n"/>
+      <c r="H3" s="345" t="n"/>
+      <c r="I3" s="345" t="n"/>
+      <c r="J3" s="345" t="n"/>
+      <c r="K3" s="345" t="n"/>
+      <c r="L3" s="345" t="n"/>
+      <c r="M3" s="345" t="n"/>
+      <c r="N3" s="345" t="n"/>
+      <c r="O3" s="345" t="n"/>
+      <c r="P3" s="345" t="n"/>
+      <c r="Q3" s="345" t="n"/>
+      <c r="R3" s="345" t="n"/>
+      <c r="S3" s="345" t="n"/>
+      <c r="T3" s="345" t="n"/>
+      <c r="U3" s="345" t="n"/>
+      <c r="V3" s="345" t="n"/>
+      <c r="W3" s="345" t="n"/>
+      <c r="X3" s="345" t="n"/>
+      <c r="Y3" s="345" t="n"/>
+      <c r="Z3" s="345" t="n"/>
+      <c r="AA3" s="345" t="n"/>
+      <c r="AB3" s="345" t="n"/>
+      <c r="AC3" s="345" t="n"/>
+      <c r="AD3" s="345" t="n"/>
+      <c r="AE3" s="345" t="n"/>
+      <c r="AF3" s="345" t="n"/>
+      <c r="AG3" s="345" t="n"/>
+      <c r="AH3" s="345" t="n"/>
+      <c r="AI3" s="345" t="n"/>
+      <c r="AJ3" s="345" t="n"/>
+      <c r="AK3" s="345" t="n"/>
+      <c r="AL3" s="345" t="n"/>
+      <c r="AM3" s="345" t="n"/>
+      <c r="AN3" s="345" t="n"/>
+    </row>
     <row r="4" ht="20" customHeight="1" s="329">
-      <c r="A4" s="336" t="inlineStr">
+      <c r="A4" s="387" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B4" s="336" t="inlineStr">
+      <c r="B4" s="387" t="inlineStr">
         <is>
           <t>Value / Reference</t>
         </is>
       </c>
-      <c r="C4" s="336" t="inlineStr">
+      <c r="C4" s="387" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
+      <c r="D4" s="345" t="n"/>
+      <c r="E4" s="345" t="n"/>
+      <c r="F4" s="345" t="n"/>
+      <c r="G4" s="345" t="n"/>
+      <c r="H4" s="345" t="n"/>
+      <c r="I4" s="345" t="n"/>
+      <c r="J4" s="345" t="n"/>
+      <c r="K4" s="345" t="n"/>
+      <c r="L4" s="345" t="n"/>
+      <c r="M4" s="345" t="n"/>
+      <c r="N4" s="345" t="n"/>
+      <c r="O4" s="345" t="n"/>
+      <c r="P4" s="345" t="n"/>
+      <c r="Q4" s="345" t="n"/>
+      <c r="R4" s="345" t="n"/>
+      <c r="S4" s="345" t="n"/>
+      <c r="T4" s="345" t="n"/>
+      <c r="U4" s="345" t="n"/>
+      <c r="V4" s="345" t="n"/>
+      <c r="W4" s="345" t="n"/>
+      <c r="X4" s="345" t="n"/>
+      <c r="Y4" s="345" t="n"/>
+      <c r="Z4" s="345" t="n"/>
+      <c r="AA4" s="345" t="n"/>
+      <c r="AB4" s="345" t="n"/>
+      <c r="AC4" s="345" t="n"/>
+      <c r="AD4" s="345" t="n"/>
+      <c r="AE4" s="345" t="n"/>
+      <c r="AF4" s="345" t="n"/>
+      <c r="AG4" s="345" t="n"/>
+      <c r="AH4" s="345" t="n"/>
+      <c r="AI4" s="345" t="n"/>
+      <c r="AJ4" s="345" t="n"/>
+      <c r="AK4" s="345" t="n"/>
+      <c r="AL4" s="345" t="n"/>
+      <c r="AM4" s="345" t="n"/>
+      <c r="AN4" s="345" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1" s="329">
-      <c r="A5" s="315" t="inlineStr">
+      <c r="A5" s="388" t="inlineStr">
         <is>
           <t>Source of Truth</t>
         </is>
       </c>
-      <c r="B5" s="316" t="inlineStr">
+      <c r="B5" s="389" t="inlineStr">
         <is>
           <t>Epicor transaction + M365 evidence</t>
         </is>
       </c>
-      <c r="C5" s="316" t="inlineStr">
+      <c r="C5" s="389" t="inlineStr">
         <is>
           <t>Do not duplicate ERP/M365/ANNEX master data.</t>
         </is>
       </c>
+      <c r="D5" s="345" t="n"/>
+      <c r="E5" s="345" t="n"/>
+      <c r="F5" s="345" t="n"/>
+      <c r="G5" s="345" t="n"/>
+      <c r="H5" s="345" t="n"/>
+      <c r="I5" s="345" t="n"/>
+      <c r="J5" s="345" t="n"/>
+      <c r="K5" s="345" t="n"/>
+      <c r="L5" s="345" t="n"/>
+      <c r="M5" s="345" t="n"/>
+      <c r="N5" s="345" t="n"/>
+      <c r="O5" s="345" t="n"/>
+      <c r="P5" s="345" t="n"/>
+      <c r="Q5" s="345" t="n"/>
+      <c r="R5" s="345" t="n"/>
+      <c r="S5" s="345" t="n"/>
+      <c r="T5" s="345" t="n"/>
+      <c r="U5" s="345" t="n"/>
+      <c r="V5" s="345" t="n"/>
+      <c r="W5" s="345" t="n"/>
+      <c r="X5" s="345" t="n"/>
+      <c r="Y5" s="345" t="n"/>
+      <c r="Z5" s="345" t="n"/>
+      <c r="AA5" s="345" t="n"/>
+      <c r="AB5" s="345" t="n"/>
+      <c r="AC5" s="345" t="n"/>
+      <c r="AD5" s="345" t="n"/>
+      <c r="AE5" s="345" t="n"/>
+      <c r="AF5" s="345" t="n"/>
+      <c r="AG5" s="345" t="n"/>
+      <c r="AH5" s="345" t="n"/>
+      <c r="AI5" s="345" t="n"/>
+      <c r="AJ5" s="345" t="n"/>
+      <c r="AK5" s="345" t="n"/>
+      <c r="AL5" s="345" t="n"/>
+      <c r="AM5" s="345" t="n"/>
+      <c r="AN5" s="345" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1" s="329">
-      <c r="A6" s="315" t="inlineStr">
+      <c r="A6" s="388" t="inlineStr">
         <is>
           <t>Cross-Reference Boundary</t>
         </is>
       </c>
-      <c r="B6" s="316" t="inlineStr">
+      <c r="B6" s="389" t="inlineStr">
         <is>
           <t>This form does not replace SOP-402; it records the evidence, data or decision required by that SOP.
 Rules, matrices, dictionaries, acceptance criteria and data definitions belong in ANNEX-PUR-001/002/003 + ANNEX-ENG-002; do not copy ANNEX content into the live data-entry body.
 System-of-record / source-of-truth boundary: Epicor transaction + M365 evidence. If the master data already live there, reference or import them; do not re-key without need.</t>
         </is>
       </c>
-      <c r="C6" s="316" t="inlineStr">
+      <c r="C6" s="389" t="inlineStr">
         <is>
           <t>This form does not replace SOP-402; it records the evidence, data or decision required by that SOP.
 Rules, matrices, dictionaries, acceptance criteria and data definitions belong in ANNEX-PUR-001/002/003 + ANNEX-ENG-002; do not copy ANNEX content into the live data-entry body.
 System-of-record / source-of-truth boundary: Epicor transaction + M365 evidence. If the master data already live there, reference or import them; do not re-key without need.</t>
         </is>
       </c>
+      <c r="D6" s="345" t="n"/>
+      <c r="E6" s="345" t="n"/>
+      <c r="F6" s="345" t="n"/>
+      <c r="G6" s="345" t="n"/>
+      <c r="H6" s="345" t="n"/>
+      <c r="I6" s="345" t="n"/>
+      <c r="J6" s="345" t="n"/>
+      <c r="K6" s="345" t="n"/>
+      <c r="L6" s="345" t="n"/>
+      <c r="M6" s="345" t="n"/>
+      <c r="N6" s="345" t="n"/>
+      <c r="O6" s="345" t="n"/>
+      <c r="P6" s="345" t="n"/>
+      <c r="Q6" s="345" t="n"/>
+      <c r="R6" s="345" t="n"/>
+      <c r="S6" s="345" t="n"/>
+      <c r="T6" s="345" t="n"/>
+      <c r="U6" s="345" t="n"/>
+      <c r="V6" s="345" t="n"/>
+      <c r="W6" s="345" t="n"/>
+      <c r="X6" s="345" t="n"/>
+      <c r="Y6" s="345" t="n"/>
+      <c r="Z6" s="345" t="n"/>
+      <c r="AA6" s="345" t="n"/>
+      <c r="AB6" s="345" t="n"/>
+      <c r="AC6" s="345" t="n"/>
+      <c r="AD6" s="345" t="n"/>
+      <c r="AE6" s="345" t="n"/>
+      <c r="AF6" s="345" t="n"/>
+      <c r="AG6" s="345" t="n"/>
+      <c r="AH6" s="345" t="n"/>
+      <c r="AI6" s="345" t="n"/>
+      <c r="AJ6" s="345" t="n"/>
+      <c r="AK6" s="345" t="n"/>
+      <c r="AL6" s="345" t="n"/>
+      <c r="AM6" s="345" t="n"/>
+      <c r="AN6" s="345" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1" s="329">
-      <c r="A7" s="315" t="inlineStr">
+      <c r="A7" s="388" t="inlineStr">
         <is>
           <t>SOP-402</t>
         </is>
       </c>
-      <c r="B7" s="316" t="inlineStr">
+      <c r="B7" s="389" t="inlineStr">
         <is>
           <t>SOP-402 — Xác minh vật liệu, truy xuất và phòng chống vật tư giả/không rõ nguồn gốc | HESEM QMS</t>
         </is>
       </c>
-      <c r="C7" s="316" t="inlineStr">
+      <c r="C7" s="389" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/01-SOPs/04-SOP-400/sop-402-material-verification-traceability-and-counterfeit-prevention.html</t>
         </is>
       </c>
+      <c r="D7" s="345" t="n"/>
+      <c r="E7" s="345" t="n"/>
+      <c r="F7" s="345" t="n"/>
+      <c r="G7" s="345" t="n"/>
+      <c r="H7" s="345" t="n"/>
+      <c r="I7" s="345" t="n"/>
+      <c r="J7" s="345" t="n"/>
+      <c r="K7" s="345" t="n"/>
+      <c r="L7" s="345" t="n"/>
+      <c r="M7" s="345" t="n"/>
+      <c r="N7" s="345" t="n"/>
+      <c r="O7" s="345" t="n"/>
+      <c r="P7" s="345" t="n"/>
+      <c r="Q7" s="345" t="n"/>
+      <c r="R7" s="345" t="n"/>
+      <c r="S7" s="345" t="n"/>
+      <c r="T7" s="345" t="n"/>
+      <c r="U7" s="345" t="n"/>
+      <c r="V7" s="345" t="n"/>
+      <c r="W7" s="345" t="n"/>
+      <c r="X7" s="345" t="n"/>
+      <c r="Y7" s="345" t="n"/>
+      <c r="Z7" s="345" t="n"/>
+      <c r="AA7" s="345" t="n"/>
+      <c r="AB7" s="345" t="n"/>
+      <c r="AC7" s="345" t="n"/>
+      <c r="AD7" s="345" t="n"/>
+      <c r="AE7" s="345" t="n"/>
+      <c r="AF7" s="345" t="n"/>
+      <c r="AG7" s="345" t="n"/>
+      <c r="AH7" s="345" t="n"/>
+      <c r="AI7" s="345" t="n"/>
+      <c r="AJ7" s="345" t="n"/>
+      <c r="AK7" s="345" t="n"/>
+      <c r="AL7" s="345" t="n"/>
+      <c r="AM7" s="345" t="n"/>
+      <c r="AN7" s="345" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1" s="329">
-      <c r="A8" s="315" t="inlineStr">
+      <c r="A8" s="352" t="inlineStr">
         <is>
           <t>ANNEX-PUR-001</t>
         </is>
       </c>
-      <c r="B8" s="316" t="inlineStr">
+      <c r="B8" s="390" t="inlineStr">
         <is>
           <t>ANNEX-PUR-001 — Mô hình rủi ro nhà cung cấp và phương pháp scorecard</t>
         </is>
       </c>
-      <c r="C8" s="316" t="inlineStr">
+      <c r="C8" s="390" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-001-supplier-risk-model-and-scorecard-method.html</t>
         </is>
       </c>
+      <c r="D8" s="381" t="n"/>
+      <c r="E8" s="381" t="n"/>
+      <c r="F8" s="381" t="n"/>
+      <c r="G8" s="381" t="n"/>
+      <c r="H8" s="381" t="n"/>
+      <c r="I8" s="381" t="n"/>
+      <c r="J8" s="381" t="n"/>
+      <c r="K8" s="381" t="n"/>
+      <c r="L8" s="381" t="n"/>
+      <c r="M8" s="381" t="n"/>
+      <c r="N8" s="381" t="n"/>
+      <c r="O8" s="381" t="n"/>
+      <c r="P8" s="381" t="n"/>
+      <c r="Q8" s="381" t="n"/>
+      <c r="R8" s="381" t="n"/>
+      <c r="S8" s="381" t="n"/>
+      <c r="T8" s="381" t="n"/>
+      <c r="U8" s="381" t="n"/>
+      <c r="V8" s="381" t="n"/>
+      <c r="W8" s="381" t="n"/>
+      <c r="X8" s="381" t="n"/>
+      <c r="Y8" s="381" t="n"/>
+      <c r="Z8" s="381" t="n"/>
+      <c r="AA8" s="381" t="n"/>
+      <c r="AB8" s="381" t="n"/>
+      <c r="AC8" s="381" t="n"/>
+      <c r="AD8" s="381" t="n"/>
+      <c r="AE8" s="381" t="n"/>
+      <c r="AF8" s="381" t="n"/>
+      <c r="AG8" s="381" t="n"/>
+      <c r="AH8" s="381" t="n"/>
+      <c r="AI8" s="381" t="n"/>
+      <c r="AJ8" s="381" t="n"/>
+      <c r="AK8" s="381" t="n"/>
+      <c r="AL8" s="381" t="n"/>
+      <c r="AM8" s="381" t="n"/>
+      <c r="AN8" s="381" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1" s="329">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="381" t="inlineStr">
         <is>
           <t>ANNEX-PUR-002</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="381" t="inlineStr">
         <is>
           <t>ANNEX-PUR-002 — Gói kiểm soát outsource / special process / cert flow-down</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="381" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-002-outsource-special-process-pack.html</t>
         </is>
       </c>
+      <c r="D9" s="381" t="n"/>
+      <c r="E9" s="381" t="n"/>
+      <c r="F9" s="381" t="n"/>
+      <c r="G9" s="381" t="n"/>
+      <c r="H9" s="381" t="n"/>
+      <c r="I9" s="381" t="n"/>
+      <c r="J9" s="381" t="n"/>
+      <c r="K9" s="381" t="n"/>
+      <c r="L9" s="381" t="n"/>
+      <c r="M9" s="381" t="n"/>
+      <c r="N9" s="381" t="n"/>
+      <c r="O9" s="381" t="n"/>
+      <c r="P9" s="381" t="n"/>
+      <c r="Q9" s="381" t="n"/>
+      <c r="R9" s="381" t="n"/>
+      <c r="S9" s="381" t="n"/>
+      <c r="T9" s="381" t="n"/>
+      <c r="U9" s="381" t="n"/>
+      <c r="V9" s="381" t="n"/>
+      <c r="W9" s="381" t="n"/>
+      <c r="X9" s="381" t="n"/>
+      <c r="Y9" s="381" t="n"/>
+      <c r="Z9" s="381" t="n"/>
+      <c r="AA9" s="381" t="n"/>
+      <c r="AB9" s="381" t="n"/>
+      <c r="AC9" s="381" t="n"/>
+      <c r="AD9" s="381" t="n"/>
+      <c r="AE9" s="381" t="n"/>
+      <c r="AF9" s="381" t="n"/>
+      <c r="AG9" s="381" t="n"/>
+      <c r="AH9" s="381" t="n"/>
+      <c r="AI9" s="381" t="n"/>
+      <c r="AJ9" s="381" t="n"/>
+      <c r="AK9" s="381" t="n"/>
+      <c r="AL9" s="381" t="n"/>
+      <c r="AM9" s="381" t="n"/>
+      <c r="AN9" s="381" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1" s="329">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="381" t="inlineStr">
         <is>
           <t>ANNEX-PUR-003</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="381" t="inlineStr">
         <is>
           <t>ANNEX-PUR-003 — Approved processor list, scope approval và rule tạm ngưng</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="381" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-003-approved-processor-list.html</t>
         </is>
       </c>
+      <c r="D10" s="381" t="n"/>
+      <c r="E10" s="381" t="n"/>
+      <c r="F10" s="381" t="n"/>
+      <c r="G10" s="381" t="n"/>
+      <c r="H10" s="381" t="n"/>
+      <c r="I10" s="381" t="n"/>
+      <c r="J10" s="381" t="n"/>
+      <c r="K10" s="381" t="n"/>
+      <c r="L10" s="381" t="n"/>
+      <c r="M10" s="381" t="n"/>
+      <c r="N10" s="381" t="n"/>
+      <c r="O10" s="381" t="n"/>
+      <c r="P10" s="381" t="n"/>
+      <c r="Q10" s="381" t="n"/>
+      <c r="R10" s="381" t="n"/>
+      <c r="S10" s="381" t="n"/>
+      <c r="T10" s="381" t="n"/>
+      <c r="U10" s="381" t="n"/>
+      <c r="V10" s="381" t="n"/>
+      <c r="W10" s="381" t="n"/>
+      <c r="X10" s="381" t="n"/>
+      <c r="Y10" s="381" t="n"/>
+      <c r="Z10" s="381" t="n"/>
+      <c r="AA10" s="381" t="n"/>
+      <c r="AB10" s="381" t="n"/>
+      <c r="AC10" s="381" t="n"/>
+      <c r="AD10" s="381" t="n"/>
+      <c r="AE10" s="381" t="n"/>
+      <c r="AF10" s="381" t="n"/>
+      <c r="AG10" s="381" t="n"/>
+      <c r="AH10" s="381" t="n"/>
+      <c r="AI10" s="381" t="n"/>
+      <c r="AJ10" s="381" t="n"/>
+      <c r="AK10" s="381" t="n"/>
+      <c r="AL10" s="381" t="n"/>
+      <c r="AM10" s="381" t="n"/>
+      <c r="AN10" s="381" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1" s="329">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="381" t="inlineStr">
         <is>
           <t>ANNEX-ENG-002</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="381" t="inlineStr">
         <is>
           <t>ANNEX-ENG-002 — Approved materials list, source restriction và rule thay thế</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="381" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-eng-002-approved-materials-list.html</t>
         </is>
       </c>
+      <c r="D11" s="381" t="n"/>
+      <c r="E11" s="381" t="n"/>
+      <c r="F11" s="381" t="n"/>
+      <c r="G11" s="381" t="n"/>
+      <c r="H11" s="381" t="n"/>
+      <c r="I11" s="381" t="n"/>
+      <c r="J11" s="381" t="n"/>
+      <c r="K11" s="381" t="n"/>
+      <c r="L11" s="381" t="n"/>
+      <c r="M11" s="381" t="n"/>
+      <c r="N11" s="381" t="n"/>
+      <c r="O11" s="381" t="n"/>
+      <c r="P11" s="381" t="n"/>
+      <c r="Q11" s="381" t="n"/>
+      <c r="R11" s="381" t="n"/>
+      <c r="S11" s="381" t="n"/>
+      <c r="T11" s="381" t="n"/>
+      <c r="U11" s="381" t="n"/>
+      <c r="V11" s="381" t="n"/>
+      <c r="W11" s="381" t="n"/>
+      <c r="X11" s="381" t="n"/>
+      <c r="Y11" s="381" t="n"/>
+      <c r="Z11" s="381" t="n"/>
+      <c r="AA11" s="381" t="n"/>
+      <c r="AB11" s="381" t="n"/>
+      <c r="AC11" s="381" t="n"/>
+      <c r="AD11" s="381" t="n"/>
+      <c r="AE11" s="381" t="n"/>
+      <c r="AF11" s="381" t="n"/>
+      <c r="AG11" s="381" t="n"/>
+      <c r="AH11" s="381" t="n"/>
+      <c r="AI11" s="381" t="n"/>
+      <c r="AJ11" s="381" t="n"/>
+      <c r="AK11" s="381" t="n"/>
+      <c r="AL11" s="381" t="n"/>
+      <c r="AM11" s="381" t="n"/>
+      <c r="AN11" s="381" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1" s="329">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="381" t="inlineStr">
         <is>
           <t>Open When</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="381" t="inlineStr">
         <is>
           <t>Open immediately when the event, request, issue, change, complaint, risk or incident is detected or formally raised.</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="381" t="inlineStr">
         <is>
           <t>Operational trigger</t>
         </is>
       </c>
+      <c r="D12" s="381" t="n"/>
+      <c r="E12" s="381" t="n"/>
+      <c r="F12" s="381" t="n"/>
+      <c r="G12" s="381" t="n"/>
+      <c r="H12" s="381" t="n"/>
+      <c r="I12" s="381" t="n"/>
+      <c r="J12" s="381" t="n"/>
+      <c r="K12" s="381" t="n"/>
+      <c r="L12" s="381" t="n"/>
+      <c r="M12" s="381" t="n"/>
+      <c r="N12" s="381" t="n"/>
+      <c r="O12" s="381" t="n"/>
+      <c r="P12" s="381" t="n"/>
+      <c r="Q12" s="381" t="n"/>
+      <c r="R12" s="381" t="n"/>
+      <c r="S12" s="381" t="n"/>
+      <c r="T12" s="381" t="n"/>
+      <c r="U12" s="381" t="n"/>
+      <c r="V12" s="381" t="n"/>
+      <c r="W12" s="381" t="n"/>
+      <c r="X12" s="381" t="n"/>
+      <c r="Y12" s="381" t="n"/>
+      <c r="Z12" s="381" t="n"/>
+      <c r="AA12" s="381" t="n"/>
+      <c r="AB12" s="381" t="n"/>
+      <c r="AC12" s="381" t="n"/>
+      <c r="AD12" s="381" t="n"/>
+      <c r="AE12" s="381" t="n"/>
+      <c r="AF12" s="381" t="n"/>
+      <c r="AG12" s="381" t="n"/>
+      <c r="AH12" s="381" t="n"/>
+      <c r="AI12" s="381" t="n"/>
+      <c r="AJ12" s="381" t="n"/>
+      <c r="AK12" s="381" t="n"/>
+      <c r="AL12" s="381" t="n"/>
+      <c r="AM12" s="381" t="n"/>
+      <c r="AN12" s="381" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1" s="329">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="381" t="inlineStr">
         <is>
           <t>Close When</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="381" t="inlineStr">
         <is>
           <t>Close when the final decision, final owner, final disposition and required follow-up actions are all recorded and the evidence package is complete.</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="381" t="inlineStr">
         <is>
           <t>Release / closure rule</t>
         </is>
       </c>
+      <c r="D13" s="381" t="n"/>
+      <c r="E13" s="381" t="n"/>
+      <c r="F13" s="381" t="n"/>
+      <c r="G13" s="381" t="n"/>
+      <c r="H13" s="381" t="n"/>
+      <c r="I13" s="381" t="n"/>
+      <c r="J13" s="381" t="n"/>
+      <c r="K13" s="381" t="n"/>
+      <c r="L13" s="381" t="n"/>
+      <c r="M13" s="381" t="n"/>
+      <c r="N13" s="381" t="n"/>
+      <c r="O13" s="381" t="n"/>
+      <c r="P13" s="381" t="n"/>
+      <c r="Q13" s="381" t="n"/>
+      <c r="R13" s="381" t="n"/>
+      <c r="S13" s="381" t="n"/>
+      <c r="T13" s="381" t="n"/>
+      <c r="U13" s="381" t="n"/>
+      <c r="V13" s="381" t="n"/>
+      <c r="W13" s="381" t="n"/>
+      <c r="X13" s="381" t="n"/>
+      <c r="Y13" s="381" t="n"/>
+      <c r="Z13" s="381" t="n"/>
+      <c r="AA13" s="381" t="n"/>
+      <c r="AB13" s="381" t="n"/>
+      <c r="AC13" s="381" t="n"/>
+      <c r="AD13" s="381" t="n"/>
+      <c r="AE13" s="381" t="n"/>
+      <c r="AF13" s="381" t="n"/>
+      <c r="AG13" s="381" t="n"/>
+      <c r="AH13" s="381" t="n"/>
+      <c r="AI13" s="381" t="n"/>
+      <c r="AJ13" s="381" t="n"/>
+      <c r="AK13" s="381" t="n"/>
+      <c r="AL13" s="381" t="n"/>
+      <c r="AM13" s="381" t="n"/>
+      <c r="AN13" s="381" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1" s="329"/>
     <row r="15" ht="20" customHeight="1" s="329"/>
@@ -7584,6 +9827,7 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/04-Bieu-Mau/04-FRM-400/FRM-411_Outsourced_Process_Incoming_Verification.xlsx
+++ b/04-Bieu-Mau/04-FRM-400/FRM-411_Outsourced_Process_Incoming_Verification.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="81">
+  <fonts count="86">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -478,8 +478,35 @@
       <color theme="1"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000C2D48"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000C2D48"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="001565C0"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="007A8FA6"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00BBCCCC"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="47">
+  <fills count="52">
     <fill>
       <patternFill/>
     </fill>
@@ -711,8 +738,33 @@
         <fgColor rgb="007C3AED"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002C9CD7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E4F0F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001565C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F7FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000C2D48"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="293">
+  <borders count="321">
     <border>
       <left/>
       <right/>
@@ -3846,12 +3898,308 @@
         <color rgb="00C5D9E8"/>
       </bottom>
       <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="414">
+  <cellXfs count="526">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -4770,6 +5118,290 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="291" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="292" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="289" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="293" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="294" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="295" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="81" fillId="4" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="4" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="4" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="48" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="48" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="48" borderId="296" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="297" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="298" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="299" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="81" fillId="4" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="4" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="48" borderId="300" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="48" borderId="273" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="48" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="301" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="273" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="302" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="4" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="4" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="303" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="304" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="305" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="84" fillId="4" borderId="303" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="4" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="4" borderId="305" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="48" borderId="306" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="48" borderId="307" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="48" borderId="308" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="309" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="307" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="310" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="47" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="49" borderId="311" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="49" borderId="312" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="49" borderId="313" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="50" borderId="314" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="315" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="316" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="50" borderId="316" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="317" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="50" borderId="318" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="50" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="319" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="50" borderId="306" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="307" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="309" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="50" borderId="309" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="310" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="272" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="318" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="318" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="306" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="309" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="51" borderId="311" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="51" borderId="312" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="51" borderId="320" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="51" borderId="313" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="50" borderId="314" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="50" borderId="316" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="50" borderId="316" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="316" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="50" borderId="318" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="50" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="50" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="50" borderId="306" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="50" borderId="309" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="50" borderId="309" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="309" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="50" borderId="316" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="4" borderId="318" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="4" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="4" borderId="311" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="312" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="313" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="295" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="78" fillId="4" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="299" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="298" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="53" fillId="4" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="4" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="303" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="305" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="50" borderId="314" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="316" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="315" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="50" borderId="318" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="275" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="275" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="319" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="307" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="307" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="310" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="304" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="305" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="306" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="309" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="318" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -4843,6 +5475,126 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1303776" cy="376089"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1303776" cy="376089"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1303776" cy="376089"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1303776" cy="376089"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5103,573 +5855,636 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="329">
-      <c r="A1" s="337" t="n"/>
-      <c r="B1" s="408" t="n"/>
-      <c r="C1" s="408" t="n"/>
-      <c r="D1" s="408" t="n"/>
-      <c r="E1" s="408" t="n"/>
-      <c r="F1" s="408" t="n"/>
-      <c r="G1" s="408" t="n"/>
-      <c r="H1" s="408" t="n"/>
-      <c r="I1" s="339" t="inlineStr">
+      <c r="A1" s="414" t="n"/>
+      <c r="B1" s="415" t="n"/>
+      <c r="C1" s="415" t="n"/>
+      <c r="D1" s="415" t="n"/>
+      <c r="E1" s="415" t="n"/>
+      <c r="F1" s="415" t="n"/>
+      <c r="G1" s="415" t="n"/>
+      <c r="H1" s="416" t="n"/>
+      <c r="I1" s="417" t="inlineStr">
         <is>
           <t>Outsourced Process Incoming Verification</t>
         </is>
       </c>
-      <c r="J1" s="408" t="n"/>
-      <c r="K1" s="408" t="n"/>
-      <c r="L1" s="408" t="n"/>
-      <c r="M1" s="408" t="n"/>
-      <c r="N1" s="408" t="n"/>
-      <c r="O1" s="408" t="n"/>
-      <c r="P1" s="408" t="n"/>
-      <c r="Q1" s="408" t="n"/>
-      <c r="R1" s="408" t="n"/>
-      <c r="S1" s="408" t="n"/>
-      <c r="T1" s="408" t="n"/>
-      <c r="U1" s="408" t="n"/>
-      <c r="V1" s="408" t="n"/>
-      <c r="W1" s="408" t="n"/>
-      <c r="X1" s="408" t="n"/>
-      <c r="Y1" s="408" t="n"/>
-      <c r="Z1" s="408" t="n"/>
-      <c r="AA1" s="408" t="n"/>
-      <c r="AB1" s="408" t="n"/>
-      <c r="AC1" s="408" t="n"/>
-      <c r="AD1" s="408" t="n"/>
-      <c r="AE1" s="340" t="n"/>
-      <c r="AF1" s="409" t="n"/>
-      <c r="AG1" s="409" t="n"/>
-      <c r="AH1" s="410" t="n"/>
-      <c r="AI1" s="343" t="inlineStr">
+      <c r="J1" s="418" t="n"/>
+      <c r="K1" s="418" t="n"/>
+      <c r="L1" s="418" t="n"/>
+      <c r="M1" s="418" t="n"/>
+      <c r="N1" s="418" t="n"/>
+      <c r="O1" s="418" t="n"/>
+      <c r="P1" s="418" t="n"/>
+      <c r="Q1" s="418" t="n"/>
+      <c r="R1" s="418" t="n"/>
+      <c r="S1" s="418" t="n"/>
+      <c r="T1" s="418" t="n"/>
+      <c r="U1" s="418" t="n"/>
+      <c r="V1" s="418" t="n"/>
+      <c r="W1" s="418" t="n"/>
+      <c r="X1" s="418" t="n"/>
+      <c r="Y1" s="418" t="n"/>
+      <c r="Z1" s="418" t="n"/>
+      <c r="AA1" s="418" t="n"/>
+      <c r="AB1" s="418" t="n"/>
+      <c r="AC1" s="418" t="n"/>
+      <c r="AD1" s="419" t="n"/>
+      <c r="AE1" s="420" t="n"/>
+      <c r="AF1" s="421" t="n"/>
+      <c r="AG1" s="421" t="n"/>
+      <c r="AH1" s="422" t="n"/>
+      <c r="AI1" s="423" t="inlineStr">
         <is>
           <t>FRM-411</t>
         </is>
       </c>
-      <c r="AJ1" s="409" t="n"/>
-      <c r="AK1" s="409" t="n"/>
-      <c r="AL1" s="409" t="n"/>
-      <c r="AM1" s="409" t="n"/>
-      <c r="AN1" s="410" t="n"/>
+      <c r="AJ1" s="424" t="n"/>
+      <c r="AK1" s="424" t="n"/>
+      <c r="AL1" s="424" t="n"/>
+      <c r="AM1" s="424" t="n"/>
+      <c r="AN1" s="425" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1" s="329">
-      <c r="A2" s="411" t="n"/>
-      <c r="I2" s="411" t="n"/>
-      <c r="AE2" s="340" t="n"/>
-      <c r="AF2" s="409" t="n"/>
-      <c r="AG2" s="409" t="n"/>
-      <c r="AH2" s="410" t="n"/>
-      <c r="AI2" s="343" t="inlineStr">
+      <c r="A2" s="426" t="n"/>
+      <c r="B2" s="25" t="n"/>
+      <c r="C2" s="25" t="n"/>
+      <c r="D2" s="25" t="n"/>
+      <c r="E2" s="25" t="n"/>
+      <c r="F2" s="25" t="n"/>
+      <c r="G2" s="25" t="n"/>
+      <c r="H2" s="427" t="n"/>
+      <c r="I2" s="428" t="n"/>
+      <c r="J2" s="429" t="n"/>
+      <c r="K2" s="429" t="n"/>
+      <c r="L2" s="429" t="n"/>
+      <c r="M2" s="429" t="n"/>
+      <c r="N2" s="429" t="n"/>
+      <c r="O2" s="429" t="n"/>
+      <c r="P2" s="429" t="n"/>
+      <c r="Q2" s="429" t="n"/>
+      <c r="R2" s="429" t="n"/>
+      <c r="S2" s="429" t="n"/>
+      <c r="T2" s="429" t="n"/>
+      <c r="U2" s="429" t="n"/>
+      <c r="V2" s="429" t="n"/>
+      <c r="W2" s="429" t="n"/>
+      <c r="X2" s="429" t="n"/>
+      <c r="Y2" s="429" t="n"/>
+      <c r="Z2" s="429" t="n"/>
+      <c r="AA2" s="429" t="n"/>
+      <c r="AB2" s="429" t="n"/>
+      <c r="AC2" s="429" t="n"/>
+      <c r="AD2" s="430" t="n"/>
+      <c r="AE2" s="431" t="n"/>
+      <c r="AF2" s="432" t="n"/>
+      <c r="AG2" s="432" t="n"/>
+      <c r="AH2" s="433" t="n"/>
+      <c r="AI2" s="434" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AJ2" s="409" t="n"/>
-      <c r="AK2" s="409" t="n"/>
-      <c r="AL2" s="409" t="n"/>
-      <c r="AM2" s="409" t="n"/>
-      <c r="AN2" s="410" t="n"/>
+      <c r="AJ2" s="435" t="n"/>
+      <c r="AK2" s="435" t="n"/>
+      <c r="AL2" s="435" t="n"/>
+      <c r="AM2" s="435" t="n"/>
+      <c r="AN2" s="436" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1" s="329">
-      <c r="A3" s="411" t="n"/>
-      <c r="I3" s="412" t="n"/>
-      <c r="J3" s="413" t="n"/>
-      <c r="K3" s="413" t="n"/>
-      <c r="L3" s="413" t="n"/>
-      <c r="M3" s="413" t="n"/>
-      <c r="N3" s="413" t="n"/>
-      <c r="O3" s="413" t="n"/>
-      <c r="P3" s="413" t="n"/>
-      <c r="Q3" s="413" t="n"/>
-      <c r="R3" s="413" t="n"/>
-      <c r="S3" s="413" t="n"/>
-      <c r="T3" s="413" t="n"/>
-      <c r="U3" s="413" t="n"/>
-      <c r="V3" s="413" t="n"/>
-      <c r="W3" s="413" t="n"/>
-      <c r="X3" s="413" t="n"/>
-      <c r="Y3" s="413" t="n"/>
-      <c r="Z3" s="413" t="n"/>
-      <c r="AA3" s="413" t="n"/>
-      <c r="AB3" s="413" t="n"/>
-      <c r="AC3" s="413" t="n"/>
-      <c r="AD3" s="413" t="n"/>
-      <c r="AE3" s="340" t="n"/>
-      <c r="AF3" s="409" t="n"/>
-      <c r="AG3" s="409" t="n"/>
-      <c r="AH3" s="410" t="n"/>
-      <c r="AI3" s="343" t="inlineStr">
+      <c r="A3" s="426" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="427" t="n"/>
+      <c r="I3" s="428" t="n"/>
+      <c r="J3" s="429" t="n"/>
+      <c r="K3" s="429" t="n"/>
+      <c r="L3" s="429" t="n"/>
+      <c r="M3" s="429" t="n"/>
+      <c r="N3" s="429" t="n"/>
+      <c r="O3" s="429" t="n"/>
+      <c r="P3" s="429" t="n"/>
+      <c r="Q3" s="429" t="n"/>
+      <c r="R3" s="429" t="n"/>
+      <c r="S3" s="429" t="n"/>
+      <c r="T3" s="429" t="n"/>
+      <c r="U3" s="429" t="n"/>
+      <c r="V3" s="429" t="n"/>
+      <c r="W3" s="429" t="n"/>
+      <c r="X3" s="429" t="n"/>
+      <c r="Y3" s="429" t="n"/>
+      <c r="Z3" s="429" t="n"/>
+      <c r="AA3" s="429" t="n"/>
+      <c r="AB3" s="429" t="n"/>
+      <c r="AC3" s="429" t="n"/>
+      <c r="AD3" s="430" t="n"/>
+      <c r="AE3" s="431" t="n"/>
+      <c r="AF3" s="432" t="n"/>
+      <c r="AG3" s="432" t="n"/>
+      <c r="AH3" s="433" t="n"/>
+      <c r="AI3" s="434" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AJ3" s="409" t="n"/>
-      <c r="AK3" s="409" t="n"/>
-      <c r="AL3" s="409" t="n"/>
-      <c r="AM3" s="409" t="n"/>
-      <c r="AN3" s="410" t="n"/>
+      <c r="AJ3" s="435" t="n"/>
+      <c r="AK3" s="435" t="n"/>
+      <c r="AL3" s="435" t="n"/>
+      <c r="AM3" s="435" t="n"/>
+      <c r="AN3" s="436" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1" s="329">
-      <c r="A4" s="411" t="n"/>
-      <c r="I4" s="348" t="inlineStr">
+      <c r="A4" s="426" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="25" t="n"/>
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="427" t="n"/>
+      <c r="I4" s="437" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AE4" s="340" t="n"/>
-      <c r="AF4" s="409" t="n"/>
-      <c r="AG4" s="409" t="n"/>
-      <c r="AH4" s="410" t="n"/>
-      <c r="AI4" s="343" t="inlineStr">
+      <c r="J4" s="438" t="n"/>
+      <c r="K4" s="438" t="n"/>
+      <c r="L4" s="438" t="n"/>
+      <c r="M4" s="438" t="n"/>
+      <c r="N4" s="438" t="n"/>
+      <c r="O4" s="438" t="n"/>
+      <c r="P4" s="438" t="n"/>
+      <c r="Q4" s="438" t="n"/>
+      <c r="R4" s="438" t="n"/>
+      <c r="S4" s="438" t="n"/>
+      <c r="T4" s="438" t="n"/>
+      <c r="U4" s="438" t="n"/>
+      <c r="V4" s="438" t="n"/>
+      <c r="W4" s="438" t="n"/>
+      <c r="X4" s="438" t="n"/>
+      <c r="Y4" s="438" t="n"/>
+      <c r="Z4" s="438" t="n"/>
+      <c r="AA4" s="438" t="n"/>
+      <c r="AB4" s="438" t="n"/>
+      <c r="AC4" s="438" t="n"/>
+      <c r="AD4" s="439" t="n"/>
+      <c r="AE4" s="431" t="n"/>
+      <c r="AF4" s="432" t="n"/>
+      <c r="AG4" s="432" t="n"/>
+      <c r="AH4" s="433" t="n"/>
+      <c r="AI4" s="434" t="inlineStr">
         <is>
           <t>Purchasing + QA</t>
         </is>
       </c>
-      <c r="AJ4" s="409" t="n"/>
-      <c r="AK4" s="409" t="n"/>
-      <c r="AL4" s="409" t="n"/>
-      <c r="AM4" s="409" t="n"/>
-      <c r="AN4" s="410" t="n"/>
+      <c r="AJ4" s="435" t="n"/>
+      <c r="AK4" s="435" t="n"/>
+      <c r="AL4" s="435" t="n"/>
+      <c r="AM4" s="435" t="n"/>
+      <c r="AN4" s="436" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1" s="329">
-      <c r="A5" s="412" t="n"/>
-      <c r="B5" s="413" t="n"/>
-      <c r="C5" s="413" t="n"/>
-      <c r="D5" s="413" t="n"/>
-      <c r="E5" s="413" t="n"/>
-      <c r="F5" s="413" t="n"/>
-      <c r="G5" s="413" t="n"/>
-      <c r="H5" s="413" t="n"/>
-      <c r="I5" s="349" t="inlineStr">
+      <c r="A5" s="440" t="n"/>
+      <c r="B5" s="441" t="n"/>
+      <c r="C5" s="441" t="n"/>
+      <c r="D5" s="441" t="n"/>
+      <c r="E5" s="441" t="n"/>
+      <c r="F5" s="441" t="n"/>
+      <c r="G5" s="441" t="n"/>
+      <c r="H5" s="442" t="n"/>
+      <c r="I5" s="443" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="J5" s="413" t="n"/>
-      <c r="K5" s="413" t="n"/>
-      <c r="L5" s="413" t="n"/>
-      <c r="M5" s="413" t="n"/>
-      <c r="N5" s="413" t="n"/>
-      <c r="O5" s="413" t="n"/>
-      <c r="P5" s="413" t="n"/>
-      <c r="Q5" s="413" t="n"/>
-      <c r="R5" s="413" t="n"/>
-      <c r="S5" s="413" t="n"/>
-      <c r="T5" s="413" t="n"/>
-      <c r="U5" s="413" t="n"/>
-      <c r="V5" s="413" t="n"/>
-      <c r="W5" s="413" t="n"/>
-      <c r="X5" s="413" t="n"/>
-      <c r="Y5" s="413" t="n"/>
-      <c r="Z5" s="413" t="n"/>
-      <c r="AA5" s="413" t="n"/>
-      <c r="AB5" s="413" t="n"/>
-      <c r="AC5" s="413" t="n"/>
-      <c r="AD5" s="413" t="n"/>
-      <c r="AE5" s="340" t="n"/>
-      <c r="AF5" s="409" t="n"/>
-      <c r="AG5" s="409" t="n"/>
-      <c r="AH5" s="410" t="n"/>
-      <c r="AI5" s="343" t="inlineStr">
+      <c r="J5" s="444" t="n"/>
+      <c r="K5" s="444" t="n"/>
+      <c r="L5" s="444" t="n"/>
+      <c r="M5" s="444" t="n"/>
+      <c r="N5" s="444" t="n"/>
+      <c r="O5" s="444" t="n"/>
+      <c r="P5" s="444" t="n"/>
+      <c r="Q5" s="444" t="n"/>
+      <c r="R5" s="444" t="n"/>
+      <c r="S5" s="444" t="n"/>
+      <c r="T5" s="444" t="n"/>
+      <c r="U5" s="444" t="n"/>
+      <c r="V5" s="444" t="n"/>
+      <c r="W5" s="444" t="n"/>
+      <c r="X5" s="444" t="n"/>
+      <c r="Y5" s="444" t="n"/>
+      <c r="Z5" s="444" t="n"/>
+      <c r="AA5" s="444" t="n"/>
+      <c r="AB5" s="444" t="n"/>
+      <c r="AC5" s="444" t="n"/>
+      <c r="AD5" s="445" t="n"/>
+      <c r="AE5" s="446" t="n"/>
+      <c r="AF5" s="447" t="n"/>
+      <c r="AG5" s="447" t="n"/>
+      <c r="AH5" s="448" t="n"/>
+      <c r="AI5" s="449" t="inlineStr">
         <is>
           <t>General Manager</t>
         </is>
       </c>
-      <c r="AJ5" s="409" t="n"/>
-      <c r="AK5" s="409" t="n"/>
-      <c r="AL5" s="409" t="n"/>
-      <c r="AM5" s="409" t="n"/>
-      <c r="AN5" s="410" t="n"/>
+      <c r="AJ5" s="450" t="n"/>
+      <c r="AK5" s="450" t="n"/>
+      <c r="AL5" s="450" t="n"/>
+      <c r="AM5" s="450" t="n"/>
+      <c r="AN5" s="451" t="n"/>
     </row>
-    <row r="6" ht="4" customHeight="1" s="329">
-      <c r="A6" s="350" t="n"/>
-      <c r="B6" s="407" t="n"/>
-      <c r="C6" s="407" t="n"/>
-      <c r="D6" s="407" t="n"/>
-      <c r="E6" s="407" t="n"/>
-      <c r="F6" s="407" t="n"/>
-      <c r="G6" s="407" t="n"/>
-      <c r="H6" s="407" t="n"/>
-      <c r="I6" s="407" t="n"/>
-      <c r="J6" s="407" t="n"/>
-      <c r="K6" s="407" t="n"/>
-      <c r="L6" s="407" t="n"/>
-      <c r="M6" s="407" t="n"/>
-      <c r="N6" s="407" t="n"/>
-      <c r="O6" s="407" t="n"/>
-      <c r="P6" s="407" t="n"/>
-      <c r="Q6" s="407" t="n"/>
-      <c r="R6" s="407" t="n"/>
-      <c r="S6" s="407" t="n"/>
-      <c r="T6" s="407" t="n"/>
-      <c r="U6" s="407" t="n"/>
-      <c r="V6" s="407" t="n"/>
-      <c r="W6" s="407" t="n"/>
-      <c r="X6" s="407" t="n"/>
-      <c r="Y6" s="407" t="n"/>
-      <c r="Z6" s="407" t="n"/>
-      <c r="AA6" s="407" t="n"/>
-      <c r="AB6" s="407" t="n"/>
-      <c r="AC6" s="407" t="n"/>
-      <c r="AD6" s="407" t="n"/>
-      <c r="AE6" s="407" t="n"/>
-      <c r="AF6" s="407" t="n"/>
-      <c r="AG6" s="407" t="n"/>
-      <c r="AH6" s="407" t="n"/>
-      <c r="AI6" s="407" t="n"/>
-      <c r="AJ6" s="407" t="n"/>
-      <c r="AK6" s="407" t="n"/>
-      <c r="AL6" s="407" t="n"/>
-      <c r="AM6" s="407" t="n"/>
-      <c r="AN6" s="407" t="n"/>
+    <row r="6" ht="1.5" customHeight="1" s="329">
+      <c r="A6" s="452" t="n"/>
+      <c r="B6" s="452" t="n"/>
+      <c r="C6" s="452" t="n"/>
+      <c r="D6" s="452" t="n"/>
+      <c r="E6" s="452" t="n"/>
+      <c r="F6" s="452" t="n"/>
+      <c r="G6" s="452" t="n"/>
+      <c r="H6" s="452" t="n"/>
+      <c r="I6" s="452" t="n"/>
+      <c r="J6" s="452" t="n"/>
+      <c r="K6" s="452" t="n"/>
+      <c r="L6" s="452" t="n"/>
+      <c r="M6" s="452" t="n"/>
+      <c r="N6" s="452" t="n"/>
+      <c r="O6" s="452" t="n"/>
+      <c r="P6" s="452" t="n"/>
+      <c r="Q6" s="452" t="n"/>
+      <c r="R6" s="452" t="n"/>
+      <c r="S6" s="452" t="n"/>
+      <c r="T6" s="452" t="n"/>
+      <c r="U6" s="452" t="n"/>
+      <c r="V6" s="452" t="n"/>
+      <c r="W6" s="452" t="n"/>
+      <c r="X6" s="452" t="n"/>
+      <c r="Y6" s="452" t="n"/>
+      <c r="Z6" s="452" t="n"/>
+      <c r="AA6" s="452" t="n"/>
+      <c r="AB6" s="452" t="n"/>
+      <c r="AC6" s="452" t="n"/>
+      <c r="AD6" s="452" t="n"/>
+      <c r="AE6" s="452" t="n"/>
+      <c r="AF6" s="452" t="n"/>
+      <c r="AG6" s="452" t="n"/>
+      <c r="AH6" s="452" t="n"/>
+      <c r="AI6" s="452" t="n"/>
+      <c r="AJ6" s="452" t="n"/>
+      <c r="AK6" s="452" t="n"/>
+      <c r="AL6" s="452" t="n"/>
+      <c r="AM6" s="452" t="n"/>
+      <c r="AN6" s="452" t="n"/>
     </row>
-    <row r="7" ht="17" customHeight="1" s="329">
-      <c r="A7" s="351" t="inlineStr">
+    <row r="7" ht="18" customHeight="1" s="329">
+      <c r="A7" s="453" t="inlineStr">
         <is>
           <t xml:space="preserve">  1. REFERENCE INFORMATION</t>
         </is>
       </c>
-      <c r="B7" s="409" t="n"/>
-      <c r="C7" s="409" t="n"/>
-      <c r="D7" s="409" t="n"/>
-      <c r="E7" s="409" t="n"/>
-      <c r="F7" s="409" t="n"/>
-      <c r="G7" s="409" t="n"/>
-      <c r="H7" s="409" t="n"/>
-      <c r="I7" s="409" t="n"/>
-      <c r="J7" s="409" t="n"/>
-      <c r="K7" s="409" t="n"/>
-      <c r="L7" s="409" t="n"/>
-      <c r="M7" s="409" t="n"/>
-      <c r="N7" s="409" t="n"/>
-      <c r="O7" s="409" t="n"/>
-      <c r="P7" s="409" t="n"/>
-      <c r="Q7" s="409" t="n"/>
-      <c r="R7" s="409" t="n"/>
-      <c r="S7" s="409" t="n"/>
-      <c r="T7" s="409" t="n"/>
-      <c r="U7" s="409" t="n"/>
-      <c r="V7" s="409" t="n"/>
-      <c r="W7" s="409" t="n"/>
-      <c r="X7" s="409" t="n"/>
-      <c r="Y7" s="409" t="n"/>
-      <c r="Z7" s="409" t="n"/>
-      <c r="AA7" s="409" t="n"/>
-      <c r="AB7" s="409" t="n"/>
-      <c r="AC7" s="409" t="n"/>
-      <c r="AD7" s="409" t="n"/>
-      <c r="AE7" s="409" t="n"/>
-      <c r="AF7" s="409" t="n"/>
-      <c r="AG7" s="409" t="n"/>
-      <c r="AH7" s="409" t="n"/>
-      <c r="AI7" s="409" t="n"/>
-      <c r="AJ7" s="409" t="n"/>
-      <c r="AK7" s="409" t="n"/>
-      <c r="AL7" s="409" t="n"/>
-      <c r="AM7" s="409" t="n"/>
-      <c r="AN7" s="410" t="n"/>
+      <c r="B7" s="454" t="n"/>
+      <c r="C7" s="454" t="n"/>
+      <c r="D7" s="454" t="n"/>
+      <c r="E7" s="454" t="n"/>
+      <c r="F7" s="454" t="n"/>
+      <c r="G7" s="454" t="n"/>
+      <c r="H7" s="454" t="n"/>
+      <c r="I7" s="454" t="n"/>
+      <c r="J7" s="454" t="n"/>
+      <c r="K7" s="454" t="n"/>
+      <c r="L7" s="454" t="n"/>
+      <c r="M7" s="454" t="n"/>
+      <c r="N7" s="454" t="n"/>
+      <c r="O7" s="454" t="n"/>
+      <c r="P7" s="454" t="n"/>
+      <c r="Q7" s="454" t="n"/>
+      <c r="R7" s="454" t="n"/>
+      <c r="S7" s="454" t="n"/>
+      <c r="T7" s="454" t="n"/>
+      <c r="U7" s="454" t="n"/>
+      <c r="V7" s="454" t="n"/>
+      <c r="W7" s="454" t="n"/>
+      <c r="X7" s="454" t="n"/>
+      <c r="Y7" s="454" t="n"/>
+      <c r="Z7" s="454" t="n"/>
+      <c r="AA7" s="454" t="n"/>
+      <c r="AB7" s="454" t="n"/>
+      <c r="AC7" s="454" t="n"/>
+      <c r="AD7" s="454" t="n"/>
+      <c r="AE7" s="454" t="n"/>
+      <c r="AF7" s="454" t="n"/>
+      <c r="AG7" s="454" t="n"/>
+      <c r="AH7" s="454" t="n"/>
+      <c r="AI7" s="454" t="n"/>
+      <c r="AJ7" s="454" t="n"/>
+      <c r="AK7" s="454" t="n"/>
+      <c r="AL7" s="454" t="n"/>
+      <c r="AM7" s="454" t="n"/>
+      <c r="AN7" s="455" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1" s="329">
-      <c r="A8" s="352" t="inlineStr">
+      <c r="A8" s="456" t="inlineStr">
         <is>
           <t>Incoming Verification ID</t>
         </is>
       </c>
-      <c r="B8" s="397" t="n"/>
-      <c r="C8" s="397" t="n"/>
-      <c r="D8" s="397" t="n"/>
-      <c r="E8" s="397" t="n"/>
-      <c r="F8" s="397" t="n"/>
-      <c r="G8" s="398" t="n"/>
-      <c r="H8" s="355" t="n"/>
-      <c r="I8" s="397" t="n"/>
-      <c r="J8" s="397" t="n"/>
-      <c r="K8" s="397" t="n"/>
-      <c r="L8" s="397" t="n"/>
-      <c r="M8" s="397" t="n"/>
-      <c r="N8" s="397" t="n"/>
-      <c r="O8" s="397" t="n"/>
-      <c r="P8" s="397" t="n"/>
-      <c r="Q8" s="397" t="n"/>
-      <c r="R8" s="397" t="n"/>
-      <c r="S8" s="397" t="n"/>
-      <c r="T8" s="398" t="n"/>
-      <c r="U8" s="356" t="inlineStr">
+      <c r="B8" s="457" t="n"/>
+      <c r="C8" s="457" t="n"/>
+      <c r="D8" s="457" t="n"/>
+      <c r="E8" s="457" t="n"/>
+      <c r="F8" s="457" t="n"/>
+      <c r="G8" s="457" t="n"/>
+      <c r="H8" s="458" t="n"/>
+      <c r="I8" s="457" t="n"/>
+      <c r="J8" s="457" t="n"/>
+      <c r="K8" s="457" t="n"/>
+      <c r="L8" s="457" t="n"/>
+      <c r="M8" s="457" t="n"/>
+      <c r="N8" s="457" t="n"/>
+      <c r="O8" s="457" t="n"/>
+      <c r="P8" s="457" t="n"/>
+      <c r="Q8" s="457" t="n"/>
+      <c r="R8" s="457" t="n"/>
+      <c r="S8" s="457" t="n"/>
+      <c r="T8" s="457" t="n"/>
+      <c r="U8" s="459" t="inlineStr">
         <is>
           <t>Disposition Status</t>
         </is>
       </c>
-      <c r="V8" s="397" t="n"/>
-      <c r="W8" s="397" t="n"/>
-      <c r="X8" s="397" t="n"/>
-      <c r="Y8" s="397" t="n"/>
-      <c r="Z8" s="397" t="n"/>
-      <c r="AA8" s="398" t="n"/>
-      <c r="AB8" s="355" t="n"/>
-      <c r="AC8" s="397" t="n"/>
-      <c r="AD8" s="397" t="n"/>
-      <c r="AE8" s="397" t="n"/>
-      <c r="AF8" s="397" t="n"/>
-      <c r="AG8" s="397" t="n"/>
-      <c r="AH8" s="397" t="n"/>
-      <c r="AI8" s="397" t="n"/>
-      <c r="AJ8" s="397" t="n"/>
-      <c r="AK8" s="397" t="n"/>
-      <c r="AL8" s="397" t="n"/>
-      <c r="AM8" s="397" t="n"/>
-      <c r="AN8" s="398" t="n"/>
+      <c r="V8" s="457" t="n"/>
+      <c r="W8" s="457" t="n"/>
+      <c r="X8" s="457" t="n"/>
+      <c r="Y8" s="457" t="n"/>
+      <c r="Z8" s="457" t="n"/>
+      <c r="AA8" s="457" t="n"/>
+      <c r="AB8" s="458" t="n"/>
+      <c r="AC8" s="457" t="n"/>
+      <c r="AD8" s="457" t="n"/>
+      <c r="AE8" s="457" t="n"/>
+      <c r="AF8" s="457" t="n"/>
+      <c r="AG8" s="457" t="n"/>
+      <c r="AH8" s="457" t="n"/>
+      <c r="AI8" s="457" t="n"/>
+      <c r="AJ8" s="457" t="n"/>
+      <c r="AK8" s="457" t="n"/>
+      <c r="AL8" s="457" t="n"/>
+      <c r="AM8" s="457" t="n"/>
+      <c r="AN8" s="460" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1" s="329">
-      <c r="A9" s="352" t="inlineStr">
+      <c r="A9" s="461" t="inlineStr">
         <is>
           <t>Supplier / Processor / Cert</t>
         </is>
       </c>
-      <c r="B9" s="397" t="n"/>
-      <c r="C9" s="397" t="n"/>
-      <c r="D9" s="397" t="n"/>
-      <c r="E9" s="397" t="n"/>
-      <c r="F9" s="397" t="n"/>
-      <c r="G9" s="398" t="n"/>
-      <c r="H9" s="355" t="n"/>
-      <c r="I9" s="397" t="n"/>
-      <c r="J9" s="397" t="n"/>
-      <c r="K9" s="397" t="n"/>
-      <c r="L9" s="397" t="n"/>
-      <c r="M9" s="397" t="n"/>
-      <c r="N9" s="397" t="n"/>
-      <c r="O9" s="397" t="n"/>
-      <c r="P9" s="397" t="n"/>
-      <c r="Q9" s="397" t="n"/>
-      <c r="R9" s="397" t="n"/>
-      <c r="S9" s="397" t="n"/>
-      <c r="T9" s="398" t="n"/>
-      <c r="U9" s="356" t="inlineStr">
+      <c r="B9" s="341" t="n"/>
+      <c r="C9" s="341" t="n"/>
+      <c r="D9" s="341" t="n"/>
+      <c r="E9" s="341" t="n"/>
+      <c r="F9" s="341" t="n"/>
+      <c r="G9" s="341" t="n"/>
+      <c r="H9" s="462" t="n"/>
+      <c r="I9" s="341" t="n"/>
+      <c r="J9" s="341" t="n"/>
+      <c r="K9" s="341" t="n"/>
+      <c r="L9" s="341" t="n"/>
+      <c r="M9" s="341" t="n"/>
+      <c r="N9" s="341" t="n"/>
+      <c r="O9" s="341" t="n"/>
+      <c r="P9" s="341" t="n"/>
+      <c r="Q9" s="341" t="n"/>
+      <c r="R9" s="341" t="n"/>
+      <c r="S9" s="341" t="n"/>
+      <c r="T9" s="341" t="n"/>
+      <c r="U9" s="463" t="inlineStr">
         <is>
           <t>PO / Cert / Lot Ref</t>
         </is>
       </c>
-      <c r="V9" s="397" t="n"/>
-      <c r="W9" s="397" t="n"/>
-      <c r="X9" s="397" t="n"/>
-      <c r="Y9" s="397" t="n"/>
-      <c r="Z9" s="397" t="n"/>
-      <c r="AA9" s="398" t="n"/>
-      <c r="AB9" s="355" t="n"/>
-      <c r="AC9" s="397" t="n"/>
-      <c r="AD9" s="397" t="n"/>
-      <c r="AE9" s="397" t="n"/>
-      <c r="AF9" s="397" t="n"/>
-      <c r="AG9" s="397" t="n"/>
-      <c r="AH9" s="397" t="n"/>
-      <c r="AI9" s="397" t="n"/>
-      <c r="AJ9" s="397" t="n"/>
-      <c r="AK9" s="397" t="n"/>
-      <c r="AL9" s="397" t="n"/>
-      <c r="AM9" s="397" t="n"/>
-      <c r="AN9" s="398" t="n"/>
+      <c r="V9" s="341" t="n"/>
+      <c r="W9" s="341" t="n"/>
+      <c r="X9" s="341" t="n"/>
+      <c r="Y9" s="341" t="n"/>
+      <c r="Z9" s="341" t="n"/>
+      <c r="AA9" s="341" t="n"/>
+      <c r="AB9" s="462" t="n"/>
+      <c r="AC9" s="341" t="n"/>
+      <c r="AD9" s="341" t="n"/>
+      <c r="AE9" s="341" t="n"/>
+      <c r="AF9" s="341" t="n"/>
+      <c r="AG9" s="341" t="n"/>
+      <c r="AH9" s="341" t="n"/>
+      <c r="AI9" s="341" t="n"/>
+      <c r="AJ9" s="341" t="n"/>
+      <c r="AK9" s="341" t="n"/>
+      <c r="AL9" s="341" t="n"/>
+      <c r="AM9" s="341" t="n"/>
+      <c r="AN9" s="464" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1" s="329">
-      <c r="A10" s="352" t="inlineStr">
+      <c r="A10" s="461" t="inlineStr">
         <is>
           <t>Part / Lot / Qty</t>
         </is>
       </c>
-      <c r="B10" s="397" t="n"/>
-      <c r="C10" s="397" t="n"/>
-      <c r="D10" s="397" t="n"/>
-      <c r="E10" s="397" t="n"/>
-      <c r="F10" s="397" t="n"/>
-      <c r="G10" s="398" t="n"/>
-      <c r="H10" s="355" t="n"/>
-      <c r="I10" s="397" t="n"/>
-      <c r="J10" s="397" t="n"/>
-      <c r="K10" s="397" t="n"/>
-      <c r="L10" s="397" t="n"/>
-      <c r="M10" s="397" t="n"/>
-      <c r="N10" s="397" t="n"/>
-      <c r="O10" s="397" t="n"/>
-      <c r="P10" s="397" t="n"/>
-      <c r="Q10" s="397" t="n"/>
-      <c r="R10" s="397" t="n"/>
-      <c r="S10" s="397" t="n"/>
-      <c r="T10" s="398" t="n"/>
-      <c r="U10" s="356" t="inlineStr">
+      <c r="B10" s="341" t="n"/>
+      <c r="C10" s="341" t="n"/>
+      <c r="D10" s="341" t="n"/>
+      <c r="E10" s="341" t="n"/>
+      <c r="F10" s="341" t="n"/>
+      <c r="G10" s="341" t="n"/>
+      <c r="H10" s="462" t="n"/>
+      <c r="I10" s="341" t="n"/>
+      <c r="J10" s="341" t="n"/>
+      <c r="K10" s="341" t="n"/>
+      <c r="L10" s="341" t="n"/>
+      <c r="M10" s="341" t="n"/>
+      <c r="N10" s="341" t="n"/>
+      <c r="O10" s="341" t="n"/>
+      <c r="P10" s="341" t="n"/>
+      <c r="Q10" s="341" t="n"/>
+      <c r="R10" s="341" t="n"/>
+      <c r="S10" s="341" t="n"/>
+      <c r="T10" s="341" t="n"/>
+      <c r="U10" s="463" t="inlineStr">
         <is>
           <t>Supplier-Quality Owner</t>
         </is>
       </c>
-      <c r="V10" s="397" t="n"/>
-      <c r="W10" s="397" t="n"/>
-      <c r="X10" s="397" t="n"/>
-      <c r="Y10" s="397" t="n"/>
-      <c r="Z10" s="397" t="n"/>
-      <c r="AA10" s="398" t="n"/>
-      <c r="AB10" s="355" t="n"/>
-      <c r="AC10" s="397" t="n"/>
-      <c r="AD10" s="397" t="n"/>
-      <c r="AE10" s="397" t="n"/>
-      <c r="AF10" s="397" t="n"/>
-      <c r="AG10" s="397" t="n"/>
-      <c r="AH10" s="397" t="n"/>
-      <c r="AI10" s="397" t="n"/>
-      <c r="AJ10" s="397" t="n"/>
-      <c r="AK10" s="397" t="n"/>
-      <c r="AL10" s="397" t="n"/>
-      <c r="AM10" s="397" t="n"/>
-      <c r="AN10" s="398" t="n"/>
+      <c r="V10" s="341" t="n"/>
+      <c r="W10" s="341" t="n"/>
+      <c r="X10" s="341" t="n"/>
+      <c r="Y10" s="341" t="n"/>
+      <c r="Z10" s="341" t="n"/>
+      <c r="AA10" s="341" t="n"/>
+      <c r="AB10" s="462" t="n"/>
+      <c r="AC10" s="341" t="n"/>
+      <c r="AD10" s="341" t="n"/>
+      <c r="AE10" s="341" t="n"/>
+      <c r="AF10" s="341" t="n"/>
+      <c r="AG10" s="341" t="n"/>
+      <c r="AH10" s="341" t="n"/>
+      <c r="AI10" s="341" t="n"/>
+      <c r="AJ10" s="341" t="n"/>
+      <c r="AK10" s="341" t="n"/>
+      <c r="AL10" s="341" t="n"/>
+      <c r="AM10" s="341" t="n"/>
+      <c r="AN10" s="464" t="n"/>
     </row>
-    <row r="11" ht="20" customHeight="1" s="329">
-      <c r="A11" s="352" t="inlineStr">
+    <row r="11" ht="26" customHeight="1" s="329">
+      <c r="A11" s="461" t="inlineStr">
         <is>
           <t>Prepared by / Date-Time</t>
         </is>
       </c>
-      <c r="B11" s="392" t="n"/>
-      <c r="C11" s="392" t="n"/>
-      <c r="D11" s="392" t="n"/>
-      <c r="E11" s="392" t="n"/>
-      <c r="F11" s="392" t="n"/>
-      <c r="G11" s="393" t="n"/>
-      <c r="H11" s="355" t="n"/>
-      <c r="I11" s="392" t="n"/>
-      <c r="J11" s="392" t="n"/>
-      <c r="K11" s="392" t="n"/>
-      <c r="L11" s="392" t="n"/>
-      <c r="M11" s="392" t="n"/>
-      <c r="N11" s="392" t="n"/>
-      <c r="O11" s="392" t="n"/>
-      <c r="P11" s="392" t="n"/>
-      <c r="Q11" s="392" t="n"/>
-      <c r="R11" s="392" t="n"/>
-      <c r="S11" s="392" t="n"/>
-      <c r="T11" s="393" t="n"/>
-      <c r="U11" s="356" t="inlineStr">
+      <c r="B11" s="341" t="n"/>
+      <c r="C11" s="341" t="n"/>
+      <c r="D11" s="341" t="n"/>
+      <c r="E11" s="341" t="n"/>
+      <c r="F11" s="341" t="n"/>
+      <c r="G11" s="341" t="n"/>
+      <c r="H11" s="462" t="n"/>
+      <c r="I11" s="341" t="n"/>
+      <c r="J11" s="341" t="n"/>
+      <c r="K11" s="341" t="n"/>
+      <c r="L11" s="341" t="n"/>
+      <c r="M11" s="341" t="n"/>
+      <c r="N11" s="341" t="n"/>
+      <c r="O11" s="341" t="n"/>
+      <c r="P11" s="341" t="n"/>
+      <c r="Q11" s="341" t="n"/>
+      <c r="R11" s="341" t="n"/>
+      <c r="S11" s="341" t="n"/>
+      <c r="T11" s="341" t="n"/>
+      <c r="U11" s="463" t="inlineStr">
         <is>
           <t>Record Status</t>
         </is>
       </c>
-      <c r="V11" s="392" t="n"/>
-      <c r="W11" s="392" t="n"/>
-      <c r="X11" s="392" t="n"/>
-      <c r="Y11" s="392" t="n"/>
-      <c r="Z11" s="392" t="n"/>
-      <c r="AA11" s="393" t="n"/>
-      <c r="AB11" s="355" t="n"/>
-      <c r="AC11" s="392" t="n"/>
-      <c r="AD11" s="392" t="n"/>
-      <c r="AE11" s="392" t="n"/>
-      <c r="AF11" s="392" t="n"/>
-      <c r="AG11" s="392" t="n"/>
-      <c r="AH11" s="392" t="n"/>
-      <c r="AI11" s="392" t="n"/>
-      <c r="AJ11" s="392" t="n"/>
-      <c r="AK11" s="392" t="n"/>
-      <c r="AL11" s="392" t="n"/>
-      <c r="AM11" s="392" t="n"/>
-      <c r="AN11" s="393" t="n"/>
+      <c r="V11" s="341" t="n"/>
+      <c r="W11" s="341" t="n"/>
+      <c r="X11" s="341" t="n"/>
+      <c r="Y11" s="341" t="n"/>
+      <c r="Z11" s="341" t="n"/>
+      <c r="AA11" s="341" t="n"/>
+      <c r="AB11" s="462" t="n"/>
+      <c r="AC11" s="341" t="n"/>
+      <c r="AD11" s="341" t="n"/>
+      <c r="AE11" s="341" t="n"/>
+      <c r="AF11" s="341" t="n"/>
+      <c r="AG11" s="341" t="n"/>
+      <c r="AH11" s="341" t="n"/>
+      <c r="AI11" s="341" t="n"/>
+      <c r="AJ11" s="341" t="n"/>
+      <c r="AK11" s="341" t="n"/>
+      <c r="AL11" s="341" t="n"/>
+      <c r="AM11" s="341" t="n"/>
+      <c r="AN11" s="464" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1" s="329">
-      <c r="A12" s="352" t="inlineStr">
+      <c r="A12" s="461" t="inlineStr">
         <is>
           <t>Evidence Package Ref</t>
         </is>
       </c>
-      <c r="B12" s="397" t="n"/>
-      <c r="C12" s="397" t="n"/>
-      <c r="D12" s="397" t="n"/>
-      <c r="E12" s="397" t="n"/>
-      <c r="F12" s="397" t="n"/>
-      <c r="G12" s="398" t="n"/>
-      <c r="H12" s="355" t="n"/>
-      <c r="I12" s="397" t="n"/>
-      <c r="J12" s="397" t="n"/>
-      <c r="K12" s="397" t="n"/>
-      <c r="L12" s="397" t="n"/>
-      <c r="M12" s="397" t="n"/>
-      <c r="N12" s="397" t="n"/>
-      <c r="O12" s="397" t="n"/>
-      <c r="P12" s="397" t="n"/>
-      <c r="Q12" s="397" t="n"/>
-      <c r="R12" s="397" t="n"/>
-      <c r="S12" s="397" t="n"/>
-      <c r="T12" s="398" t="n"/>
-      <c r="U12" s="356" t="inlineStr">
+      <c r="B12" s="341" t="n"/>
+      <c r="C12" s="341" t="n"/>
+      <c r="D12" s="341" t="n"/>
+      <c r="E12" s="341" t="n"/>
+      <c r="F12" s="341" t="n"/>
+      <c r="G12" s="341" t="n"/>
+      <c r="H12" s="462" t="n"/>
+      <c r="I12" s="341" t="n"/>
+      <c r="J12" s="341" t="n"/>
+      <c r="K12" s="341" t="n"/>
+      <c r="L12" s="341" t="n"/>
+      <c r="M12" s="341" t="n"/>
+      <c r="N12" s="341" t="n"/>
+      <c r="O12" s="341" t="n"/>
+      <c r="P12" s="341" t="n"/>
+      <c r="Q12" s="341" t="n"/>
+      <c r="R12" s="341" t="n"/>
+      <c r="S12" s="341" t="n"/>
+      <c r="T12" s="341" t="n"/>
+      <c r="U12" s="463" t="inlineStr">
         <is>
           <t>Risk Level</t>
         </is>
       </c>
-      <c r="V12" s="397" t="n"/>
-      <c r="W12" s="397" t="n"/>
-      <c r="X12" s="397" t="n"/>
-      <c r="Y12" s="397" t="n"/>
-      <c r="Z12" s="397" t="n"/>
-      <c r="AA12" s="398" t="n"/>
-      <c r="AB12" s="355" t="n"/>
-      <c r="AC12" s="397" t="n"/>
-      <c r="AD12" s="397" t="n"/>
-      <c r="AE12" s="397" t="n"/>
-      <c r="AF12" s="397" t="n"/>
-      <c r="AG12" s="397" t="n"/>
-      <c r="AH12" s="397" t="n"/>
-      <c r="AI12" s="397" t="n"/>
-      <c r="AJ12" s="397" t="n"/>
-      <c r="AK12" s="397" t="n"/>
-      <c r="AL12" s="397" t="n"/>
-      <c r="AM12" s="397" t="n"/>
-      <c r="AN12" s="398" t="n"/>
+      <c r="V12" s="341" t="n"/>
+      <c r="W12" s="341" t="n"/>
+      <c r="X12" s="341" t="n"/>
+      <c r="Y12" s="341" t="n"/>
+      <c r="Z12" s="341" t="n"/>
+      <c r="AA12" s="341" t="n"/>
+      <c r="AB12" s="462" t="n"/>
+      <c r="AC12" s="341" t="n"/>
+      <c r="AD12" s="341" t="n"/>
+      <c r="AE12" s="341" t="n"/>
+      <c r="AF12" s="341" t="n"/>
+      <c r="AG12" s="341" t="n"/>
+      <c r="AH12" s="341" t="n"/>
+      <c r="AI12" s="341" t="n"/>
+      <c r="AJ12" s="341" t="n"/>
+      <c r="AK12" s="341" t="n"/>
+      <c r="AL12" s="341" t="n"/>
+      <c r="AM12" s="341" t="n"/>
+      <c r="AN12" s="464" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1" s="329">
-      <c r="A13" s="352" t="inlineStr">
+      <c r="A13" s="465" t="inlineStr">
         <is>
           <t>Method / Acceptance Ref</t>
         </is>
       </c>
-      <c r="B13" s="397" t="n"/>
-      <c r="C13" s="397" t="n"/>
-      <c r="D13" s="397" t="n"/>
-      <c r="E13" s="397" t="n"/>
-      <c r="F13" s="397" t="n"/>
-      <c r="G13" s="398" t="n"/>
-      <c r="H13" s="355" t="n"/>
-      <c r="I13" s="397" t="n"/>
-      <c r="J13" s="397" t="n"/>
-      <c r="K13" s="397" t="n"/>
-      <c r="L13" s="397" t="n"/>
-      <c r="M13" s="397" t="n"/>
-      <c r="N13" s="397" t="n"/>
-      <c r="O13" s="397" t="n"/>
-      <c r="P13" s="397" t="n"/>
-      <c r="Q13" s="397" t="n"/>
-      <c r="R13" s="397" t="n"/>
-      <c r="S13" s="397" t="n"/>
-      <c r="T13" s="398" t="n"/>
-      <c r="U13" s="356" t="inlineStr">
+      <c r="B13" s="466" t="n"/>
+      <c r="C13" s="466" t="n"/>
+      <c r="D13" s="466" t="n"/>
+      <c r="E13" s="466" t="n"/>
+      <c r="F13" s="466" t="n"/>
+      <c r="G13" s="466" t="n"/>
+      <c r="H13" s="467" t="n"/>
+      <c r="I13" s="466" t="n"/>
+      <c r="J13" s="466" t="n"/>
+      <c r="K13" s="466" t="n"/>
+      <c r="L13" s="466" t="n"/>
+      <c r="M13" s="466" t="n"/>
+      <c r="N13" s="466" t="n"/>
+      <c r="O13" s="466" t="n"/>
+      <c r="P13" s="466" t="n"/>
+      <c r="Q13" s="466" t="n"/>
+      <c r="R13" s="466" t="n"/>
+      <c r="S13" s="466" t="n"/>
+      <c r="T13" s="466" t="n"/>
+      <c r="U13" s="468" t="inlineStr">
         <is>
           <t>Affected Job Ref</t>
         </is>
       </c>
-      <c r="V13" s="397" t="n"/>
-      <c r="W13" s="397" t="n"/>
-      <c r="X13" s="397" t="n"/>
-      <c r="Y13" s="397" t="n"/>
-      <c r="Z13" s="397" t="n"/>
-      <c r="AA13" s="398" t="n"/>
-      <c r="AB13" s="355" t="n"/>
-      <c r="AC13" s="397" t="n"/>
-      <c r="AD13" s="397" t="n"/>
-      <c r="AE13" s="397" t="n"/>
-      <c r="AF13" s="397" t="n"/>
-      <c r="AG13" s="397" t="n"/>
-      <c r="AH13" s="397" t="n"/>
-      <c r="AI13" s="397" t="n"/>
-      <c r="AJ13" s="397" t="n"/>
-      <c r="AK13" s="397" t="n"/>
-      <c r="AL13" s="397" t="n"/>
-      <c r="AM13" s="397" t="n"/>
-      <c r="AN13" s="398" t="n"/>
+      <c r="V13" s="466" t="n"/>
+      <c r="W13" s="466" t="n"/>
+      <c r="X13" s="466" t="n"/>
+      <c r="Y13" s="466" t="n"/>
+      <c r="Z13" s="466" t="n"/>
+      <c r="AA13" s="466" t="n"/>
+      <c r="AB13" s="467" t="n"/>
+      <c r="AC13" s="466" t="n"/>
+      <c r="AD13" s="466" t="n"/>
+      <c r="AE13" s="466" t="n"/>
+      <c r="AF13" s="466" t="n"/>
+      <c r="AG13" s="466" t="n"/>
+      <c r="AH13" s="466" t="n"/>
+      <c r="AI13" s="466" t="n"/>
+      <c r="AJ13" s="466" t="n"/>
+      <c r="AK13" s="466" t="n"/>
+      <c r="AL13" s="466" t="n"/>
+      <c r="AM13" s="466" t="n"/>
+      <c r="AN13" s="469" t="n"/>
     </row>
-    <row r="14" ht="4" customHeight="1" s="329">
+    <row r="14" ht="3" customHeight="1" s="329">
       <c r="A14" s="357" t="n"/>
       <c r="B14" s="350" t="n"/>
       <c r="C14" s="350" t="n"/>
@@ -5711,413 +6526,413 @@
       <c r="AM14" s="350" t="n"/>
       <c r="AN14" s="350" t="n"/>
     </row>
-    <row r="15" ht="20" customHeight="1" s="329">
-      <c r="A15" s="351" t="inlineStr">
+    <row r="15" ht="18" customHeight="1" s="329">
+      <c r="A15" s="453" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. INCOMING VERIFICATION / FINDING DETAIL</t>
         </is>
       </c>
-      <c r="B15" s="397" t="n"/>
-      <c r="C15" s="397" t="n"/>
-      <c r="D15" s="397" t="n"/>
-      <c r="E15" s="397" t="n"/>
-      <c r="F15" s="397" t="n"/>
-      <c r="G15" s="397" t="n"/>
-      <c r="H15" s="397" t="n"/>
-      <c r="I15" s="397" t="n"/>
-      <c r="J15" s="397" t="n"/>
-      <c r="K15" s="397" t="n"/>
-      <c r="L15" s="397" t="n"/>
-      <c r="M15" s="397" t="n"/>
-      <c r="N15" s="397" t="n"/>
-      <c r="O15" s="397" t="n"/>
-      <c r="P15" s="397" t="n"/>
-      <c r="Q15" s="397" t="n"/>
-      <c r="R15" s="397" t="n"/>
-      <c r="S15" s="397" t="n"/>
-      <c r="T15" s="397" t="n"/>
-      <c r="U15" s="397" t="n"/>
-      <c r="V15" s="397" t="n"/>
-      <c r="W15" s="397" t="n"/>
-      <c r="X15" s="397" t="n"/>
-      <c r="Y15" s="397" t="n"/>
-      <c r="Z15" s="397" t="n"/>
-      <c r="AA15" s="397" t="n"/>
-      <c r="AB15" s="397" t="n"/>
-      <c r="AC15" s="397" t="n"/>
-      <c r="AD15" s="397" t="n"/>
-      <c r="AE15" s="397" t="n"/>
-      <c r="AF15" s="397" t="n"/>
-      <c r="AG15" s="397" t="n"/>
-      <c r="AH15" s="397" t="n"/>
-      <c r="AI15" s="397" t="n"/>
-      <c r="AJ15" s="397" t="n"/>
-      <c r="AK15" s="397" t="n"/>
-      <c r="AL15" s="397" t="n"/>
-      <c r="AM15" s="397" t="n"/>
-      <c r="AN15" s="398" t="n"/>
+      <c r="B15" s="454" t="n"/>
+      <c r="C15" s="454" t="n"/>
+      <c r="D15" s="454" t="n"/>
+      <c r="E15" s="454" t="n"/>
+      <c r="F15" s="454" t="n"/>
+      <c r="G15" s="454" t="n"/>
+      <c r="H15" s="454" t="n"/>
+      <c r="I15" s="454" t="n"/>
+      <c r="J15" s="454" t="n"/>
+      <c r="K15" s="454" t="n"/>
+      <c r="L15" s="454" t="n"/>
+      <c r="M15" s="454" t="n"/>
+      <c r="N15" s="454" t="n"/>
+      <c r="O15" s="454" t="n"/>
+      <c r="P15" s="454" t="n"/>
+      <c r="Q15" s="454" t="n"/>
+      <c r="R15" s="454" t="n"/>
+      <c r="S15" s="454" t="n"/>
+      <c r="T15" s="454" t="n"/>
+      <c r="U15" s="454" t="n"/>
+      <c r="V15" s="454" t="n"/>
+      <c r="W15" s="454" t="n"/>
+      <c r="X15" s="454" t="n"/>
+      <c r="Y15" s="454" t="n"/>
+      <c r="Z15" s="454" t="n"/>
+      <c r="AA15" s="454" t="n"/>
+      <c r="AB15" s="454" t="n"/>
+      <c r="AC15" s="454" t="n"/>
+      <c r="AD15" s="454" t="n"/>
+      <c r="AE15" s="454" t="n"/>
+      <c r="AF15" s="454" t="n"/>
+      <c r="AG15" s="454" t="n"/>
+      <c r="AH15" s="454" t="n"/>
+      <c r="AI15" s="454" t="n"/>
+      <c r="AJ15" s="454" t="n"/>
+      <c r="AK15" s="454" t="n"/>
+      <c r="AL15" s="454" t="n"/>
+      <c r="AM15" s="454" t="n"/>
+      <c r="AN15" s="455" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1" s="329">
-      <c r="A16" s="352" t="inlineStr">
+      <c r="A16" s="456" t="inlineStr">
         <is>
           <t>Risk Level</t>
         </is>
       </c>
-      <c r="B16" s="397" t="n"/>
-      <c r="C16" s="397" t="n"/>
-      <c r="D16" s="397" t="n"/>
-      <c r="E16" s="397" t="n"/>
-      <c r="F16" s="397" t="n"/>
-      <c r="G16" s="398" t="n"/>
-      <c r="H16" s="355" t="n"/>
-      <c r="I16" s="397" t="n"/>
-      <c r="J16" s="397" t="n"/>
-      <c r="K16" s="397" t="n"/>
-      <c r="L16" s="397" t="n"/>
-      <c r="M16" s="397" t="n"/>
-      <c r="N16" s="397" t="n"/>
-      <c r="O16" s="397" t="n"/>
-      <c r="P16" s="397" t="n"/>
-      <c r="Q16" s="397" t="n"/>
-      <c r="R16" s="397" t="n"/>
-      <c r="S16" s="397" t="n"/>
-      <c r="T16" s="398" t="n"/>
-      <c r="U16" s="356" t="inlineStr">
+      <c r="B16" s="457" t="n"/>
+      <c r="C16" s="457" t="n"/>
+      <c r="D16" s="457" t="n"/>
+      <c r="E16" s="457" t="n"/>
+      <c r="F16" s="457" t="n"/>
+      <c r="G16" s="457" t="n"/>
+      <c r="H16" s="458" t="n"/>
+      <c r="I16" s="457" t="n"/>
+      <c r="J16" s="457" t="n"/>
+      <c r="K16" s="457" t="n"/>
+      <c r="L16" s="457" t="n"/>
+      <c r="M16" s="457" t="n"/>
+      <c r="N16" s="457" t="n"/>
+      <c r="O16" s="457" t="n"/>
+      <c r="P16" s="457" t="n"/>
+      <c r="Q16" s="457" t="n"/>
+      <c r="R16" s="457" t="n"/>
+      <c r="S16" s="457" t="n"/>
+      <c r="T16" s="457" t="n"/>
+      <c r="U16" s="459" t="inlineStr">
         <is>
           <t>Countermeasure / Trigger</t>
         </is>
       </c>
-      <c r="V16" s="397" t="n"/>
-      <c r="W16" s="397" t="n"/>
-      <c r="X16" s="397" t="n"/>
-      <c r="Y16" s="397" t="n"/>
-      <c r="Z16" s="397" t="n"/>
-      <c r="AA16" s="398" t="n"/>
-      <c r="AB16" s="355" t="n"/>
-      <c r="AC16" s="397" t="n"/>
-      <c r="AD16" s="397" t="n"/>
-      <c r="AE16" s="397" t="n"/>
-      <c r="AF16" s="397" t="n"/>
-      <c r="AG16" s="397" t="n"/>
-      <c r="AH16" s="397" t="n"/>
-      <c r="AI16" s="397" t="n"/>
-      <c r="AJ16" s="397" t="n"/>
-      <c r="AK16" s="397" t="n"/>
-      <c r="AL16" s="397" t="n"/>
-      <c r="AM16" s="397" t="n"/>
-      <c r="AN16" s="398" t="n"/>
+      <c r="V16" s="457" t="n"/>
+      <c r="W16" s="457" t="n"/>
+      <c r="X16" s="457" t="n"/>
+      <c r="Y16" s="457" t="n"/>
+      <c r="Z16" s="457" t="n"/>
+      <c r="AA16" s="457" t="n"/>
+      <c r="AB16" s="458" t="n"/>
+      <c r="AC16" s="457" t="n"/>
+      <c r="AD16" s="457" t="n"/>
+      <c r="AE16" s="457" t="n"/>
+      <c r="AF16" s="457" t="n"/>
+      <c r="AG16" s="457" t="n"/>
+      <c r="AH16" s="457" t="n"/>
+      <c r="AI16" s="457" t="n"/>
+      <c r="AJ16" s="457" t="n"/>
+      <c r="AK16" s="457" t="n"/>
+      <c r="AL16" s="457" t="n"/>
+      <c r="AM16" s="457" t="n"/>
+      <c r="AN16" s="460" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1" s="329">
-      <c r="A17" s="352" t="inlineStr">
+      <c r="A17" s="461" t="inlineStr">
         <is>
           <t>Related Requirement / Package</t>
         </is>
       </c>
-      <c r="B17" s="397" t="n"/>
-      <c r="C17" s="397" t="n"/>
-      <c r="D17" s="397" t="n"/>
-      <c r="E17" s="397" t="n"/>
-      <c r="F17" s="397" t="n"/>
-      <c r="G17" s="398" t="n"/>
-      <c r="H17" s="355" t="n"/>
-      <c r="I17" s="397" t="n"/>
-      <c r="J17" s="397" t="n"/>
-      <c r="K17" s="397" t="n"/>
-      <c r="L17" s="397" t="n"/>
-      <c r="M17" s="397" t="n"/>
-      <c r="N17" s="397" t="n"/>
-      <c r="O17" s="397" t="n"/>
-      <c r="P17" s="397" t="n"/>
-      <c r="Q17" s="397" t="n"/>
-      <c r="R17" s="397" t="n"/>
-      <c r="S17" s="397" t="n"/>
-      <c r="T17" s="398" t="n"/>
-      <c r="U17" s="356" t="inlineStr">
+      <c r="B17" s="341" t="n"/>
+      <c r="C17" s="341" t="n"/>
+      <c r="D17" s="341" t="n"/>
+      <c r="E17" s="341" t="n"/>
+      <c r="F17" s="341" t="n"/>
+      <c r="G17" s="341" t="n"/>
+      <c r="H17" s="462" t="n"/>
+      <c r="I17" s="341" t="n"/>
+      <c r="J17" s="341" t="n"/>
+      <c r="K17" s="341" t="n"/>
+      <c r="L17" s="341" t="n"/>
+      <c r="M17" s="341" t="n"/>
+      <c r="N17" s="341" t="n"/>
+      <c r="O17" s="341" t="n"/>
+      <c r="P17" s="341" t="n"/>
+      <c r="Q17" s="341" t="n"/>
+      <c r="R17" s="341" t="n"/>
+      <c r="S17" s="341" t="n"/>
+      <c r="T17" s="341" t="n"/>
+      <c r="U17" s="463" t="inlineStr">
         <is>
           <t>Customer Special Requirement (YES/NO)</t>
         </is>
       </c>
-      <c r="V17" s="397" t="n"/>
-      <c r="W17" s="397" t="n"/>
-      <c r="X17" s="397" t="n"/>
-      <c r="Y17" s="397" t="n"/>
-      <c r="Z17" s="397" t="n"/>
-      <c r="AA17" s="398" t="n"/>
-      <c r="AB17" s="355" t="n"/>
-      <c r="AC17" s="397" t="n"/>
-      <c r="AD17" s="397" t="n"/>
-      <c r="AE17" s="397" t="n"/>
-      <c r="AF17" s="397" t="n"/>
-      <c r="AG17" s="397" t="n"/>
-      <c r="AH17" s="397" t="n"/>
-      <c r="AI17" s="397" t="n"/>
-      <c r="AJ17" s="397" t="n"/>
-      <c r="AK17" s="397" t="n"/>
-      <c r="AL17" s="397" t="n"/>
-      <c r="AM17" s="397" t="n"/>
-      <c r="AN17" s="398" t="n"/>
+      <c r="V17" s="341" t="n"/>
+      <c r="W17" s="341" t="n"/>
+      <c r="X17" s="341" t="n"/>
+      <c r="Y17" s="341" t="n"/>
+      <c r="Z17" s="341" t="n"/>
+      <c r="AA17" s="341" t="n"/>
+      <c r="AB17" s="462" t="n"/>
+      <c r="AC17" s="341" t="n"/>
+      <c r="AD17" s="341" t="n"/>
+      <c r="AE17" s="341" t="n"/>
+      <c r="AF17" s="341" t="n"/>
+      <c r="AG17" s="341" t="n"/>
+      <c r="AH17" s="341" t="n"/>
+      <c r="AI17" s="341" t="n"/>
+      <c r="AJ17" s="341" t="n"/>
+      <c r="AK17" s="341" t="n"/>
+      <c r="AL17" s="341" t="n"/>
+      <c r="AM17" s="341" t="n"/>
+      <c r="AN17" s="464" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1" s="329">
-      <c r="A18" s="352" t="inlineStr">
+      <c r="A18" s="461" t="inlineStr">
         <is>
           <t>VERIFICATION / SCOPE DESCRIPTION</t>
         </is>
       </c>
-      <c r="B18" s="397" t="n"/>
-      <c r="C18" s="397" t="n"/>
-      <c r="D18" s="397" t="n"/>
-      <c r="E18" s="397" t="n"/>
-      <c r="F18" s="397" t="n"/>
-      <c r="G18" s="397" t="n"/>
-      <c r="H18" s="397" t="n"/>
-      <c r="I18" s="397" t="n"/>
-      <c r="J18" s="397" t="n"/>
-      <c r="K18" s="397" t="n"/>
-      <c r="L18" s="397" t="n"/>
-      <c r="M18" s="397" t="n"/>
-      <c r="N18" s="397" t="n"/>
-      <c r="O18" s="397" t="n"/>
-      <c r="P18" s="397" t="n"/>
-      <c r="Q18" s="397" t="n"/>
-      <c r="R18" s="397" t="n"/>
-      <c r="S18" s="397" t="n"/>
-      <c r="T18" s="397" t="n"/>
-      <c r="U18" s="397" t="n"/>
-      <c r="V18" s="397" t="n"/>
-      <c r="W18" s="397" t="n"/>
-      <c r="X18" s="397" t="n"/>
-      <c r="Y18" s="397" t="n"/>
-      <c r="Z18" s="397" t="n"/>
-      <c r="AA18" s="397" t="n"/>
-      <c r="AB18" s="397" t="n"/>
-      <c r="AC18" s="397" t="n"/>
-      <c r="AD18" s="397" t="n"/>
-      <c r="AE18" s="397" t="n"/>
-      <c r="AF18" s="397" t="n"/>
-      <c r="AG18" s="397" t="n"/>
-      <c r="AH18" s="397" t="n"/>
-      <c r="AI18" s="397" t="n"/>
-      <c r="AJ18" s="397" t="n"/>
-      <c r="AK18" s="397" t="n"/>
-      <c r="AL18" s="397" t="n"/>
-      <c r="AM18" s="397" t="n"/>
-      <c r="AN18" s="398" t="n"/>
+      <c r="B18" s="341" t="n"/>
+      <c r="C18" s="341" t="n"/>
+      <c r="D18" s="341" t="n"/>
+      <c r="E18" s="341" t="n"/>
+      <c r="F18" s="341" t="n"/>
+      <c r="G18" s="341" t="n"/>
+      <c r="H18" s="470" t="n"/>
+      <c r="I18" s="341" t="n"/>
+      <c r="J18" s="341" t="n"/>
+      <c r="K18" s="341" t="n"/>
+      <c r="L18" s="341" t="n"/>
+      <c r="M18" s="341" t="n"/>
+      <c r="N18" s="341" t="n"/>
+      <c r="O18" s="341" t="n"/>
+      <c r="P18" s="341" t="n"/>
+      <c r="Q18" s="341" t="n"/>
+      <c r="R18" s="341" t="n"/>
+      <c r="S18" s="341" t="n"/>
+      <c r="T18" s="341" t="n"/>
+      <c r="U18" s="470" t="n"/>
+      <c r="V18" s="341" t="n"/>
+      <c r="W18" s="341" t="n"/>
+      <c r="X18" s="341" t="n"/>
+      <c r="Y18" s="341" t="n"/>
+      <c r="Z18" s="341" t="n"/>
+      <c r="AA18" s="341" t="n"/>
+      <c r="AB18" s="470" t="n"/>
+      <c r="AC18" s="341" t="n"/>
+      <c r="AD18" s="341" t="n"/>
+      <c r="AE18" s="341" t="n"/>
+      <c r="AF18" s="341" t="n"/>
+      <c r="AG18" s="341" t="n"/>
+      <c r="AH18" s="341" t="n"/>
+      <c r="AI18" s="341" t="n"/>
+      <c r="AJ18" s="341" t="n"/>
+      <c r="AK18" s="341" t="n"/>
+      <c r="AL18" s="341" t="n"/>
+      <c r="AM18" s="341" t="n"/>
+      <c r="AN18" s="464" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1" s="329">
-      <c r="A19" s="355" t="n"/>
-      <c r="B19" s="399" t="n"/>
-      <c r="C19" s="399" t="n"/>
-      <c r="D19" s="399" t="n"/>
-      <c r="E19" s="399" t="n"/>
-      <c r="F19" s="399" t="n"/>
-      <c r="G19" s="399" t="n"/>
-      <c r="H19" s="399" t="n"/>
-      <c r="I19" s="399" t="n"/>
-      <c r="J19" s="399" t="n"/>
-      <c r="K19" s="399" t="n"/>
-      <c r="L19" s="399" t="n"/>
-      <c r="M19" s="399" t="n"/>
-      <c r="N19" s="399" t="n"/>
-      <c r="O19" s="399" t="n"/>
-      <c r="P19" s="399" t="n"/>
-      <c r="Q19" s="399" t="n"/>
-      <c r="R19" s="399" t="n"/>
-      <c r="S19" s="399" t="n"/>
-      <c r="T19" s="399" t="n"/>
-      <c r="U19" s="399" t="n"/>
-      <c r="V19" s="399" t="n"/>
-      <c r="W19" s="399" t="n"/>
-      <c r="X19" s="399" t="n"/>
-      <c r="Y19" s="399" t="n"/>
-      <c r="Z19" s="399" t="n"/>
-      <c r="AA19" s="399" t="n"/>
-      <c r="AB19" s="399" t="n"/>
-      <c r="AC19" s="399" t="n"/>
-      <c r="AD19" s="399" t="n"/>
-      <c r="AE19" s="399" t="n"/>
-      <c r="AF19" s="399" t="n"/>
-      <c r="AG19" s="399" t="n"/>
-      <c r="AH19" s="399" t="n"/>
-      <c r="AI19" s="399" t="n"/>
-      <c r="AJ19" s="399" t="n"/>
-      <c r="AK19" s="399" t="n"/>
-      <c r="AL19" s="399" t="n"/>
-      <c r="AM19" s="399" t="n"/>
-      <c r="AN19" s="400" t="n"/>
+      <c r="A19" s="471" t="n"/>
+      <c r="B19" s="341" t="n"/>
+      <c r="C19" s="341" t="n"/>
+      <c r="D19" s="341" t="n"/>
+      <c r="E19" s="341" t="n"/>
+      <c r="F19" s="341" t="n"/>
+      <c r="G19" s="341" t="n"/>
+      <c r="H19" s="470" t="n"/>
+      <c r="I19" s="341" t="n"/>
+      <c r="J19" s="341" t="n"/>
+      <c r="K19" s="341" t="n"/>
+      <c r="L19" s="341" t="n"/>
+      <c r="M19" s="341" t="n"/>
+      <c r="N19" s="341" t="n"/>
+      <c r="O19" s="341" t="n"/>
+      <c r="P19" s="341" t="n"/>
+      <c r="Q19" s="341" t="n"/>
+      <c r="R19" s="341" t="n"/>
+      <c r="S19" s="341" t="n"/>
+      <c r="T19" s="341" t="n"/>
+      <c r="U19" s="470" t="n"/>
+      <c r="V19" s="341" t="n"/>
+      <c r="W19" s="341" t="n"/>
+      <c r="X19" s="341" t="n"/>
+      <c r="Y19" s="341" t="n"/>
+      <c r="Z19" s="341" t="n"/>
+      <c r="AA19" s="341" t="n"/>
+      <c r="AB19" s="470" t="n"/>
+      <c r="AC19" s="341" t="n"/>
+      <c r="AD19" s="341" t="n"/>
+      <c r="AE19" s="341" t="n"/>
+      <c r="AF19" s="341" t="n"/>
+      <c r="AG19" s="341" t="n"/>
+      <c r="AH19" s="341" t="n"/>
+      <c r="AI19" s="341" t="n"/>
+      <c r="AJ19" s="341" t="n"/>
+      <c r="AK19" s="341" t="n"/>
+      <c r="AL19" s="341" t="n"/>
+      <c r="AM19" s="341" t="n"/>
+      <c r="AN19" s="464" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1" s="329">
-      <c r="A20" s="401" t="n"/>
-      <c r="B20" s="401" t="n"/>
-      <c r="C20" s="401" t="n"/>
-      <c r="D20" s="401" t="n"/>
-      <c r="E20" s="401" t="n"/>
-      <c r="F20" s="401" t="n"/>
-      <c r="G20" s="401" t="n"/>
-      <c r="H20" s="401" t="n"/>
-      <c r="I20" s="401" t="n"/>
-      <c r="J20" s="401" t="n"/>
-      <c r="K20" s="401" t="n"/>
-      <c r="L20" s="401" t="n"/>
-      <c r="M20" s="401" t="n"/>
-      <c r="N20" s="401" t="n"/>
-      <c r="O20" s="401" t="n"/>
-      <c r="P20" s="401" t="n"/>
-      <c r="Q20" s="401" t="n"/>
-      <c r="R20" s="401" t="n"/>
-      <c r="S20" s="401" t="n"/>
-      <c r="T20" s="401" t="n"/>
-      <c r="U20" s="401" t="n"/>
-      <c r="V20" s="401" t="n"/>
-      <c r="W20" s="401" t="n"/>
-      <c r="X20" s="401" t="n"/>
-      <c r="Y20" s="401" t="n"/>
-      <c r="Z20" s="401" t="n"/>
-      <c r="AA20" s="401" t="n"/>
-      <c r="AB20" s="401" t="n"/>
-      <c r="AC20" s="401" t="n"/>
-      <c r="AD20" s="401" t="n"/>
-      <c r="AE20" s="401" t="n"/>
-      <c r="AF20" s="401" t="n"/>
-      <c r="AG20" s="401" t="n"/>
-      <c r="AH20" s="401" t="n"/>
-      <c r="AI20" s="401" t="n"/>
-      <c r="AJ20" s="401" t="n"/>
-      <c r="AK20" s="401" t="n"/>
-      <c r="AL20" s="401" t="n"/>
-      <c r="AM20" s="401" t="n"/>
-      <c r="AN20" s="402" t="n"/>
+      <c r="A20" s="472" t="n"/>
+      <c r="B20" s="341" t="n"/>
+      <c r="C20" s="341" t="n"/>
+      <c r="D20" s="341" t="n"/>
+      <c r="E20" s="341" t="n"/>
+      <c r="F20" s="341" t="n"/>
+      <c r="G20" s="341" t="n"/>
+      <c r="H20" s="470" t="n"/>
+      <c r="I20" s="341" t="n"/>
+      <c r="J20" s="341" t="n"/>
+      <c r="K20" s="341" t="n"/>
+      <c r="L20" s="341" t="n"/>
+      <c r="M20" s="341" t="n"/>
+      <c r="N20" s="341" t="n"/>
+      <c r="O20" s="341" t="n"/>
+      <c r="P20" s="341" t="n"/>
+      <c r="Q20" s="341" t="n"/>
+      <c r="R20" s="341" t="n"/>
+      <c r="S20" s="341" t="n"/>
+      <c r="T20" s="341" t="n"/>
+      <c r="U20" s="470" t="n"/>
+      <c r="V20" s="341" t="n"/>
+      <c r="W20" s="341" t="n"/>
+      <c r="X20" s="341" t="n"/>
+      <c r="Y20" s="341" t="n"/>
+      <c r="Z20" s="341" t="n"/>
+      <c r="AA20" s="341" t="n"/>
+      <c r="AB20" s="470" t="n"/>
+      <c r="AC20" s="341" t="n"/>
+      <c r="AD20" s="341" t="n"/>
+      <c r="AE20" s="341" t="n"/>
+      <c r="AF20" s="341" t="n"/>
+      <c r="AG20" s="341" t="n"/>
+      <c r="AH20" s="341" t="n"/>
+      <c r="AI20" s="341" t="n"/>
+      <c r="AJ20" s="341" t="n"/>
+      <c r="AK20" s="341" t="n"/>
+      <c r="AL20" s="341" t="n"/>
+      <c r="AM20" s="341" t="n"/>
+      <c r="AN20" s="464" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1" s="329">
-      <c r="A21" s="352" t="inlineStr">
+      <c r="A21" s="461" t="inlineStr">
         <is>
           <t>OBSERVATION / CONTAINMENT / CERT CHECK</t>
         </is>
       </c>
-      <c r="B21" s="397" t="n"/>
-      <c r="C21" s="397" t="n"/>
-      <c r="D21" s="397" t="n"/>
-      <c r="E21" s="397" t="n"/>
-      <c r="F21" s="397" t="n"/>
-      <c r="G21" s="397" t="n"/>
-      <c r="H21" s="397" t="n"/>
-      <c r="I21" s="397" t="n"/>
-      <c r="J21" s="397" t="n"/>
-      <c r="K21" s="397" t="n"/>
-      <c r="L21" s="397" t="n"/>
-      <c r="M21" s="397" t="n"/>
-      <c r="N21" s="397" t="n"/>
-      <c r="O21" s="397" t="n"/>
-      <c r="P21" s="397" t="n"/>
-      <c r="Q21" s="397" t="n"/>
-      <c r="R21" s="397" t="n"/>
-      <c r="S21" s="397" t="n"/>
-      <c r="T21" s="397" t="n"/>
-      <c r="U21" s="397" t="n"/>
-      <c r="V21" s="397" t="n"/>
-      <c r="W21" s="397" t="n"/>
-      <c r="X21" s="397" t="n"/>
-      <c r="Y21" s="397" t="n"/>
-      <c r="Z21" s="397" t="n"/>
-      <c r="AA21" s="397" t="n"/>
-      <c r="AB21" s="397" t="n"/>
-      <c r="AC21" s="397" t="n"/>
-      <c r="AD21" s="397" t="n"/>
-      <c r="AE21" s="397" t="n"/>
-      <c r="AF21" s="397" t="n"/>
-      <c r="AG21" s="397" t="n"/>
-      <c r="AH21" s="397" t="n"/>
-      <c r="AI21" s="397" t="n"/>
-      <c r="AJ21" s="397" t="n"/>
-      <c r="AK21" s="397" t="n"/>
-      <c r="AL21" s="397" t="n"/>
-      <c r="AM21" s="397" t="n"/>
-      <c r="AN21" s="398" t="n"/>
+      <c r="B21" s="341" t="n"/>
+      <c r="C21" s="341" t="n"/>
+      <c r="D21" s="341" t="n"/>
+      <c r="E21" s="341" t="n"/>
+      <c r="F21" s="341" t="n"/>
+      <c r="G21" s="341" t="n"/>
+      <c r="H21" s="470" t="n"/>
+      <c r="I21" s="341" t="n"/>
+      <c r="J21" s="341" t="n"/>
+      <c r="K21" s="341" t="n"/>
+      <c r="L21" s="341" t="n"/>
+      <c r="M21" s="341" t="n"/>
+      <c r="N21" s="341" t="n"/>
+      <c r="O21" s="341" t="n"/>
+      <c r="P21" s="341" t="n"/>
+      <c r="Q21" s="341" t="n"/>
+      <c r="R21" s="341" t="n"/>
+      <c r="S21" s="341" t="n"/>
+      <c r="T21" s="341" t="n"/>
+      <c r="U21" s="470" t="n"/>
+      <c r="V21" s="341" t="n"/>
+      <c r="W21" s="341" t="n"/>
+      <c r="X21" s="341" t="n"/>
+      <c r="Y21" s="341" t="n"/>
+      <c r="Z21" s="341" t="n"/>
+      <c r="AA21" s="341" t="n"/>
+      <c r="AB21" s="470" t="n"/>
+      <c r="AC21" s="341" t="n"/>
+      <c r="AD21" s="341" t="n"/>
+      <c r="AE21" s="341" t="n"/>
+      <c r="AF21" s="341" t="n"/>
+      <c r="AG21" s="341" t="n"/>
+      <c r="AH21" s="341" t="n"/>
+      <c r="AI21" s="341" t="n"/>
+      <c r="AJ21" s="341" t="n"/>
+      <c r="AK21" s="341" t="n"/>
+      <c r="AL21" s="341" t="n"/>
+      <c r="AM21" s="341" t="n"/>
+      <c r="AN21" s="464" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1" s="329">
-      <c r="A22" s="355" t="n"/>
-      <c r="B22" s="399" t="n"/>
-      <c r="C22" s="399" t="n"/>
-      <c r="D22" s="399" t="n"/>
-      <c r="E22" s="399" t="n"/>
-      <c r="F22" s="399" t="n"/>
-      <c r="G22" s="399" t="n"/>
-      <c r="H22" s="399" t="n"/>
-      <c r="I22" s="399" t="n"/>
-      <c r="J22" s="399" t="n"/>
-      <c r="K22" s="399" t="n"/>
-      <c r="L22" s="399" t="n"/>
-      <c r="M22" s="399" t="n"/>
-      <c r="N22" s="399" t="n"/>
-      <c r="O22" s="399" t="n"/>
-      <c r="P22" s="399" t="n"/>
-      <c r="Q22" s="399" t="n"/>
-      <c r="R22" s="399" t="n"/>
-      <c r="S22" s="399" t="n"/>
-      <c r="T22" s="399" t="n"/>
-      <c r="U22" s="399" t="n"/>
-      <c r="V22" s="399" t="n"/>
-      <c r="W22" s="399" t="n"/>
-      <c r="X22" s="399" t="n"/>
-      <c r="Y22" s="399" t="n"/>
-      <c r="Z22" s="399" t="n"/>
-      <c r="AA22" s="399" t="n"/>
-      <c r="AB22" s="399" t="n"/>
-      <c r="AC22" s="399" t="n"/>
-      <c r="AD22" s="399" t="n"/>
-      <c r="AE22" s="399" t="n"/>
-      <c r="AF22" s="399" t="n"/>
-      <c r="AG22" s="399" t="n"/>
-      <c r="AH22" s="399" t="n"/>
-      <c r="AI22" s="399" t="n"/>
-      <c r="AJ22" s="399" t="n"/>
-      <c r="AK22" s="399" t="n"/>
-      <c r="AL22" s="399" t="n"/>
-      <c r="AM22" s="399" t="n"/>
-      <c r="AN22" s="400" t="n"/>
+      <c r="A22" s="471" t="n"/>
+      <c r="B22" s="341" t="n"/>
+      <c r="C22" s="341" t="n"/>
+      <c r="D22" s="341" t="n"/>
+      <c r="E22" s="341" t="n"/>
+      <c r="F22" s="341" t="n"/>
+      <c r="G22" s="341" t="n"/>
+      <c r="H22" s="470" t="n"/>
+      <c r="I22" s="341" t="n"/>
+      <c r="J22" s="341" t="n"/>
+      <c r="K22" s="341" t="n"/>
+      <c r="L22" s="341" t="n"/>
+      <c r="M22" s="341" t="n"/>
+      <c r="N22" s="341" t="n"/>
+      <c r="O22" s="341" t="n"/>
+      <c r="P22" s="341" t="n"/>
+      <c r="Q22" s="341" t="n"/>
+      <c r="R22" s="341" t="n"/>
+      <c r="S22" s="341" t="n"/>
+      <c r="T22" s="341" t="n"/>
+      <c r="U22" s="470" t="n"/>
+      <c r="V22" s="341" t="n"/>
+      <c r="W22" s="341" t="n"/>
+      <c r="X22" s="341" t="n"/>
+      <c r="Y22" s="341" t="n"/>
+      <c r="Z22" s="341" t="n"/>
+      <c r="AA22" s="341" t="n"/>
+      <c r="AB22" s="470" t="n"/>
+      <c r="AC22" s="341" t="n"/>
+      <c r="AD22" s="341" t="n"/>
+      <c r="AE22" s="341" t="n"/>
+      <c r="AF22" s="341" t="n"/>
+      <c r="AG22" s="341" t="n"/>
+      <c r="AH22" s="341" t="n"/>
+      <c r="AI22" s="341" t="n"/>
+      <c r="AJ22" s="341" t="n"/>
+      <c r="AK22" s="341" t="n"/>
+      <c r="AL22" s="341" t="n"/>
+      <c r="AM22" s="341" t="n"/>
+      <c r="AN22" s="464" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1" s="329">
-      <c r="A23" s="401" t="n"/>
-      <c r="B23" s="401" t="n"/>
-      <c r="C23" s="401" t="n"/>
-      <c r="D23" s="401" t="n"/>
-      <c r="E23" s="401" t="n"/>
-      <c r="F23" s="401" t="n"/>
-      <c r="G23" s="401" t="n"/>
-      <c r="H23" s="401" t="n"/>
-      <c r="I23" s="401" t="n"/>
-      <c r="J23" s="401" t="n"/>
-      <c r="K23" s="401" t="n"/>
-      <c r="L23" s="401" t="n"/>
-      <c r="M23" s="401" t="n"/>
-      <c r="N23" s="401" t="n"/>
-      <c r="O23" s="401" t="n"/>
-      <c r="P23" s="401" t="n"/>
-      <c r="Q23" s="401" t="n"/>
-      <c r="R23" s="401" t="n"/>
-      <c r="S23" s="401" t="n"/>
-      <c r="T23" s="401" t="n"/>
-      <c r="U23" s="401" t="n"/>
-      <c r="V23" s="401" t="n"/>
-      <c r="W23" s="401" t="n"/>
-      <c r="X23" s="401" t="n"/>
-      <c r="Y23" s="401" t="n"/>
-      <c r="Z23" s="401" t="n"/>
-      <c r="AA23" s="401" t="n"/>
-      <c r="AB23" s="401" t="n"/>
-      <c r="AC23" s="401" t="n"/>
-      <c r="AD23" s="401" t="n"/>
-      <c r="AE23" s="401" t="n"/>
-      <c r="AF23" s="401" t="n"/>
-      <c r="AG23" s="401" t="n"/>
-      <c r="AH23" s="401" t="n"/>
-      <c r="AI23" s="401" t="n"/>
-      <c r="AJ23" s="401" t="n"/>
-      <c r="AK23" s="401" t="n"/>
-      <c r="AL23" s="401" t="n"/>
-      <c r="AM23" s="401" t="n"/>
-      <c r="AN23" s="402" t="n"/>
+      <c r="A23" s="473" t="n"/>
+      <c r="B23" s="466" t="n"/>
+      <c r="C23" s="466" t="n"/>
+      <c r="D23" s="466" t="n"/>
+      <c r="E23" s="466" t="n"/>
+      <c r="F23" s="466" t="n"/>
+      <c r="G23" s="466" t="n"/>
+      <c r="H23" s="474" t="n"/>
+      <c r="I23" s="466" t="n"/>
+      <c r="J23" s="466" t="n"/>
+      <c r="K23" s="466" t="n"/>
+      <c r="L23" s="466" t="n"/>
+      <c r="M23" s="466" t="n"/>
+      <c r="N23" s="466" t="n"/>
+      <c r="O23" s="466" t="n"/>
+      <c r="P23" s="466" t="n"/>
+      <c r="Q23" s="466" t="n"/>
+      <c r="R23" s="466" t="n"/>
+      <c r="S23" s="466" t="n"/>
+      <c r="T23" s="466" t="n"/>
+      <c r="U23" s="474" t="n"/>
+      <c r="V23" s="466" t="n"/>
+      <c r="W23" s="466" t="n"/>
+      <c r="X23" s="466" t="n"/>
+      <c r="Y23" s="466" t="n"/>
+      <c r="Z23" s="466" t="n"/>
+      <c r="AA23" s="466" t="n"/>
+      <c r="AB23" s="474" t="n"/>
+      <c r="AC23" s="466" t="n"/>
+      <c r="AD23" s="466" t="n"/>
+      <c r="AE23" s="466" t="n"/>
+      <c r="AF23" s="466" t="n"/>
+      <c r="AG23" s="466" t="n"/>
+      <c r="AH23" s="466" t="n"/>
+      <c r="AI23" s="466" t="n"/>
+      <c r="AJ23" s="466" t="n"/>
+      <c r="AK23" s="466" t="n"/>
+      <c r="AL23" s="466" t="n"/>
+      <c r="AM23" s="466" t="n"/>
+      <c r="AN23" s="469" t="n"/>
     </row>
-    <row r="24" ht="4" customHeight="1" s="329">
+    <row r="24" ht="3" customHeight="1" s="329">
       <c r="A24" s="362" t="n"/>
       <c r="B24" s="350" t="n"/>
       <c r="C24" s="363" t="n"/>
@@ -6159,417 +6974,417 @@
       <c r="AM24" s="367" t="n"/>
       <c r="AN24" s="350" t="n"/>
     </row>
-    <row r="25" ht="20" customHeight="1" s="329">
-      <c r="A25" s="351" t="inlineStr">
+    <row r="25" ht="18" customHeight="1" s="329">
+      <c r="A25" s="453" t="inlineStr">
         <is>
           <t xml:space="preserve">  3. IMPACT / CONTAINMENT / ACTIONS</t>
         </is>
       </c>
-      <c r="B25" s="397" t="n"/>
-      <c r="C25" s="397" t="n"/>
-      <c r="D25" s="397" t="n"/>
-      <c r="E25" s="397" t="n"/>
-      <c r="F25" s="397" t="n"/>
-      <c r="G25" s="397" t="n"/>
-      <c r="H25" s="397" t="n"/>
-      <c r="I25" s="397" t="n"/>
-      <c r="J25" s="397" t="n"/>
-      <c r="K25" s="397" t="n"/>
-      <c r="L25" s="397" t="n"/>
-      <c r="M25" s="397" t="n"/>
-      <c r="N25" s="397" t="n"/>
-      <c r="O25" s="397" t="n"/>
-      <c r="P25" s="397" t="n"/>
-      <c r="Q25" s="397" t="n"/>
-      <c r="R25" s="397" t="n"/>
-      <c r="S25" s="397" t="n"/>
-      <c r="T25" s="397" t="n"/>
-      <c r="U25" s="397" t="n"/>
-      <c r="V25" s="397" t="n"/>
-      <c r="W25" s="397" t="n"/>
-      <c r="X25" s="397" t="n"/>
-      <c r="Y25" s="397" t="n"/>
-      <c r="Z25" s="397" t="n"/>
-      <c r="AA25" s="397" t="n"/>
-      <c r="AB25" s="397" t="n"/>
-      <c r="AC25" s="397" t="n"/>
-      <c r="AD25" s="397" t="n"/>
-      <c r="AE25" s="397" t="n"/>
-      <c r="AF25" s="397" t="n"/>
-      <c r="AG25" s="397" t="n"/>
-      <c r="AH25" s="397" t="n"/>
-      <c r="AI25" s="397" t="n"/>
-      <c r="AJ25" s="397" t="n"/>
-      <c r="AK25" s="397" t="n"/>
-      <c r="AL25" s="397" t="n"/>
-      <c r="AM25" s="397" t="n"/>
-      <c r="AN25" s="398" t="n"/>
+      <c r="B25" s="454" t="n"/>
+      <c r="C25" s="454" t="n"/>
+      <c r="D25" s="454" t="n"/>
+      <c r="E25" s="454" t="n"/>
+      <c r="F25" s="454" t="n"/>
+      <c r="G25" s="454" t="n"/>
+      <c r="H25" s="454" t="n"/>
+      <c r="I25" s="454" t="n"/>
+      <c r="J25" s="454" t="n"/>
+      <c r="K25" s="454" t="n"/>
+      <c r="L25" s="454" t="n"/>
+      <c r="M25" s="454" t="n"/>
+      <c r="N25" s="454" t="n"/>
+      <c r="O25" s="454" t="n"/>
+      <c r="P25" s="454" t="n"/>
+      <c r="Q25" s="454" t="n"/>
+      <c r="R25" s="454" t="n"/>
+      <c r="S25" s="454" t="n"/>
+      <c r="T25" s="454" t="n"/>
+      <c r="U25" s="454" t="n"/>
+      <c r="V25" s="454" t="n"/>
+      <c r="W25" s="454" t="n"/>
+      <c r="X25" s="454" t="n"/>
+      <c r="Y25" s="454" t="n"/>
+      <c r="Z25" s="454" t="n"/>
+      <c r="AA25" s="454" t="n"/>
+      <c r="AB25" s="454" t="n"/>
+      <c r="AC25" s="454" t="n"/>
+      <c r="AD25" s="454" t="n"/>
+      <c r="AE25" s="454" t="n"/>
+      <c r="AF25" s="454" t="n"/>
+      <c r="AG25" s="454" t="n"/>
+      <c r="AH25" s="454" t="n"/>
+      <c r="AI25" s="454" t="n"/>
+      <c r="AJ25" s="454" t="n"/>
+      <c r="AK25" s="454" t="n"/>
+      <c r="AL25" s="454" t="n"/>
+      <c r="AM25" s="454" t="n"/>
+      <c r="AN25" s="455" t="n"/>
     </row>
-    <row r="26" ht="20" customHeight="1" s="329">
-      <c r="A26" s="368" t="inlineStr">
+    <row r="26" ht="18" customHeight="1" s="329">
+      <c r="A26" s="475" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B26" s="398" t="n"/>
-      <c r="C26" s="369" t="inlineStr">
+      <c r="B26" s="476" t="n"/>
+      <c r="C26" s="477" t="inlineStr">
         <is>
           <t>Cat.</t>
         </is>
       </c>
-      <c r="D26" s="397" t="n"/>
-      <c r="E26" s="398" t="n"/>
-      <c r="F26" s="369" t="inlineStr">
+      <c r="D26" s="476" t="n"/>
+      <c r="E26" s="476" t="n"/>
+      <c r="F26" s="477" t="inlineStr">
         <is>
           <t>Finding / Check</t>
         </is>
       </c>
-      <c r="G26" s="397" t="n"/>
-      <c r="H26" s="397" t="n"/>
-      <c r="I26" s="397" t="n"/>
-      <c r="J26" s="397" t="n"/>
-      <c r="K26" s="397" t="n"/>
-      <c r="L26" s="397" t="n"/>
-      <c r="M26" s="397" t="n"/>
-      <c r="N26" s="397" t="n"/>
-      <c r="O26" s="397" t="n"/>
-      <c r="P26" s="397" t="n"/>
-      <c r="Q26" s="397" t="n"/>
-      <c r="R26" s="397" t="n"/>
-      <c r="S26" s="398" t="n"/>
-      <c r="T26" s="369" t="inlineStr">
+      <c r="G26" s="476" t="n"/>
+      <c r="H26" s="476" t="n"/>
+      <c r="I26" s="476" t="n"/>
+      <c r="J26" s="476" t="n"/>
+      <c r="K26" s="476" t="n"/>
+      <c r="L26" s="476" t="n"/>
+      <c r="M26" s="476" t="n"/>
+      <c r="N26" s="476" t="n"/>
+      <c r="O26" s="476" t="n"/>
+      <c r="P26" s="476" t="n"/>
+      <c r="Q26" s="476" t="n"/>
+      <c r="R26" s="476" t="n"/>
+      <c r="S26" s="476" t="n"/>
+      <c r="T26" s="477" t="inlineStr">
         <is>
           <t>Evidence / Criteria</t>
         </is>
       </c>
-      <c r="U26" s="397" t="n"/>
-      <c r="V26" s="397" t="n"/>
-      <c r="W26" s="397" t="n"/>
-      <c r="X26" s="397" t="n"/>
-      <c r="Y26" s="397" t="n"/>
-      <c r="Z26" s="397" t="n"/>
-      <c r="AA26" s="397" t="n"/>
-      <c r="AB26" s="397" t="n"/>
-      <c r="AC26" s="397" t="n"/>
-      <c r="AD26" s="397" t="n"/>
-      <c r="AE26" s="398" t="n"/>
-      <c r="AF26" s="369" t="inlineStr">
+      <c r="U26" s="476" t="n"/>
+      <c r="V26" s="476" t="n"/>
+      <c r="W26" s="476" t="n"/>
+      <c r="X26" s="476" t="n"/>
+      <c r="Y26" s="476" t="n"/>
+      <c r="Z26" s="476" t="n"/>
+      <c r="AA26" s="476" t="n"/>
+      <c r="AB26" s="476" t="n"/>
+      <c r="AC26" s="476" t="n"/>
+      <c r="AD26" s="476" t="n"/>
+      <c r="AE26" s="476" t="n"/>
+      <c r="AF26" s="477" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="AG26" s="397" t="n"/>
-      <c r="AH26" s="397" t="n"/>
-      <c r="AI26" s="398" t="n"/>
-      <c r="AJ26" s="369" t="inlineStr">
+      <c r="AG26" s="476" t="n"/>
+      <c r="AH26" s="476" t="n"/>
+      <c r="AI26" s="476" t="n"/>
+      <c r="AJ26" s="477" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AK26" s="397" t="n"/>
-      <c r="AL26" s="398" t="n"/>
-      <c r="AM26" s="369" t="inlineStr">
+      <c r="AK26" s="476" t="n"/>
+      <c r="AL26" s="476" t="n"/>
+      <c r="AM26" s="477" t="inlineStr">
         <is>
           <t>Ref.</t>
         </is>
       </c>
-      <c r="AN26" s="398" t="n"/>
+      <c r="AN26" s="478" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1" s="329">
-      <c r="A27" s="370">
+      <c r="A27" s="479">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B27" s="402" t="n"/>
-      <c r="C27" s="371" t="inlineStr">
+      <c r="B27" s="457" t="n"/>
+      <c r="C27" s="480" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D27" s="401" t="n"/>
-      <c r="E27" s="402" t="n"/>
-      <c r="F27" s="372" t="n"/>
-      <c r="G27" s="401" t="n"/>
-      <c r="H27" s="401" t="n"/>
-      <c r="I27" s="401" t="n"/>
-      <c r="J27" s="401" t="n"/>
-      <c r="K27" s="401" t="n"/>
-      <c r="L27" s="401" t="n"/>
-      <c r="M27" s="401" t="n"/>
-      <c r="N27" s="401" t="n"/>
-      <c r="O27" s="401" t="n"/>
-      <c r="P27" s="401" t="n"/>
-      <c r="Q27" s="401" t="n"/>
-      <c r="R27" s="401" t="n"/>
-      <c r="S27" s="402" t="n"/>
-      <c r="T27" s="373" t="n"/>
-      <c r="U27" s="401" t="n"/>
-      <c r="V27" s="401" t="n"/>
-      <c r="W27" s="401" t="n"/>
-      <c r="X27" s="401" t="n"/>
-      <c r="Y27" s="401" t="n"/>
-      <c r="Z27" s="401" t="n"/>
-      <c r="AA27" s="401" t="n"/>
-      <c r="AB27" s="401" t="n"/>
-      <c r="AC27" s="401" t="n"/>
-      <c r="AD27" s="401" t="n"/>
-      <c r="AE27" s="402" t="n"/>
-      <c r="AF27" s="372" t="n"/>
-      <c r="AG27" s="401" t="n"/>
-      <c r="AH27" s="401" t="n"/>
-      <c r="AI27" s="402" t="n"/>
-      <c r="AJ27" s="372" t="n"/>
-      <c r="AK27" s="401" t="n"/>
-      <c r="AL27" s="402" t="n"/>
-      <c r="AM27" s="374" t="n"/>
-      <c r="AN27" s="402" t="n"/>
+      <c r="D27" s="457" t="n"/>
+      <c r="E27" s="457" t="n"/>
+      <c r="F27" s="458" t="n"/>
+      <c r="G27" s="457" t="n"/>
+      <c r="H27" s="457" t="n"/>
+      <c r="I27" s="457" t="n"/>
+      <c r="J27" s="457" t="n"/>
+      <c r="K27" s="457" t="n"/>
+      <c r="L27" s="457" t="n"/>
+      <c r="M27" s="457" t="n"/>
+      <c r="N27" s="457" t="n"/>
+      <c r="O27" s="457" t="n"/>
+      <c r="P27" s="457" t="n"/>
+      <c r="Q27" s="457" t="n"/>
+      <c r="R27" s="457" t="n"/>
+      <c r="S27" s="457" t="n"/>
+      <c r="T27" s="481" t="n"/>
+      <c r="U27" s="457" t="n"/>
+      <c r="V27" s="457" t="n"/>
+      <c r="W27" s="457" t="n"/>
+      <c r="X27" s="457" t="n"/>
+      <c r="Y27" s="457" t="n"/>
+      <c r="Z27" s="457" t="n"/>
+      <c r="AA27" s="457" t="n"/>
+      <c r="AB27" s="457" t="n"/>
+      <c r="AC27" s="457" t="n"/>
+      <c r="AD27" s="457" t="n"/>
+      <c r="AE27" s="457" t="n"/>
+      <c r="AF27" s="458" t="n"/>
+      <c r="AG27" s="457" t="n"/>
+      <c r="AH27" s="457" t="n"/>
+      <c r="AI27" s="457" t="n"/>
+      <c r="AJ27" s="458" t="n"/>
+      <c r="AK27" s="457" t="n"/>
+      <c r="AL27" s="457" t="n"/>
+      <c r="AM27" s="482" t="n"/>
+      <c r="AN27" s="460" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1" s="329">
-      <c r="A28" s="370">
+      <c r="A28" s="483">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B28" s="402" t="n"/>
-      <c r="C28" s="371" t="inlineStr">
+      <c r="B28" s="341" t="n"/>
+      <c r="C28" s="484" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D28" s="401" t="n"/>
-      <c r="E28" s="402" t="n"/>
-      <c r="F28" s="372" t="n"/>
-      <c r="G28" s="401" t="n"/>
-      <c r="H28" s="401" t="n"/>
-      <c r="I28" s="401" t="n"/>
-      <c r="J28" s="401" t="n"/>
-      <c r="K28" s="401" t="n"/>
-      <c r="L28" s="401" t="n"/>
-      <c r="M28" s="401" t="n"/>
-      <c r="N28" s="401" t="n"/>
-      <c r="O28" s="401" t="n"/>
-      <c r="P28" s="401" t="n"/>
-      <c r="Q28" s="401" t="n"/>
-      <c r="R28" s="401" t="n"/>
-      <c r="S28" s="402" t="n"/>
-      <c r="T28" s="373" t="n"/>
-      <c r="U28" s="401" t="n"/>
-      <c r="V28" s="401" t="n"/>
-      <c r="W28" s="401" t="n"/>
-      <c r="X28" s="401" t="n"/>
-      <c r="Y28" s="401" t="n"/>
-      <c r="Z28" s="401" t="n"/>
-      <c r="AA28" s="401" t="n"/>
-      <c r="AB28" s="401" t="n"/>
-      <c r="AC28" s="401" t="n"/>
-      <c r="AD28" s="401" t="n"/>
-      <c r="AE28" s="402" t="n"/>
-      <c r="AF28" s="372" t="n"/>
-      <c r="AG28" s="401" t="n"/>
-      <c r="AH28" s="401" t="n"/>
-      <c r="AI28" s="402" t="n"/>
-      <c r="AJ28" s="372" t="n"/>
-      <c r="AK28" s="401" t="n"/>
-      <c r="AL28" s="402" t="n"/>
-      <c r="AM28" s="374" t="n"/>
-      <c r="AN28" s="402" t="n"/>
+      <c r="D28" s="341" t="n"/>
+      <c r="E28" s="341" t="n"/>
+      <c r="F28" s="462" t="n"/>
+      <c r="G28" s="341" t="n"/>
+      <c r="H28" s="341" t="n"/>
+      <c r="I28" s="341" t="n"/>
+      <c r="J28" s="341" t="n"/>
+      <c r="K28" s="341" t="n"/>
+      <c r="L28" s="341" t="n"/>
+      <c r="M28" s="341" t="n"/>
+      <c r="N28" s="341" t="n"/>
+      <c r="O28" s="341" t="n"/>
+      <c r="P28" s="341" t="n"/>
+      <c r="Q28" s="341" t="n"/>
+      <c r="R28" s="341" t="n"/>
+      <c r="S28" s="341" t="n"/>
+      <c r="T28" s="485" t="n"/>
+      <c r="U28" s="341" t="n"/>
+      <c r="V28" s="341" t="n"/>
+      <c r="W28" s="341" t="n"/>
+      <c r="X28" s="341" t="n"/>
+      <c r="Y28" s="341" t="n"/>
+      <c r="Z28" s="341" t="n"/>
+      <c r="AA28" s="341" t="n"/>
+      <c r="AB28" s="341" t="n"/>
+      <c r="AC28" s="341" t="n"/>
+      <c r="AD28" s="341" t="n"/>
+      <c r="AE28" s="341" t="n"/>
+      <c r="AF28" s="462" t="n"/>
+      <c r="AG28" s="341" t="n"/>
+      <c r="AH28" s="341" t="n"/>
+      <c r="AI28" s="341" t="n"/>
+      <c r="AJ28" s="462" t="n"/>
+      <c r="AK28" s="341" t="n"/>
+      <c r="AL28" s="341" t="n"/>
+      <c r="AM28" s="486" t="n"/>
+      <c r="AN28" s="464" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1" s="329">
-      <c r="A29" s="370">
+      <c r="A29" s="483">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B29" s="402" t="n"/>
-      <c r="C29" s="371" t="inlineStr">
+      <c r="B29" s="341" t="n"/>
+      <c r="C29" s="484" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D29" s="401" t="n"/>
-      <c r="E29" s="402" t="n"/>
-      <c r="F29" s="372" t="n"/>
-      <c r="G29" s="401" t="n"/>
-      <c r="H29" s="401" t="n"/>
-      <c r="I29" s="401" t="n"/>
-      <c r="J29" s="401" t="n"/>
-      <c r="K29" s="401" t="n"/>
-      <c r="L29" s="401" t="n"/>
-      <c r="M29" s="401" t="n"/>
-      <c r="N29" s="401" t="n"/>
-      <c r="O29" s="401" t="n"/>
-      <c r="P29" s="401" t="n"/>
-      <c r="Q29" s="401" t="n"/>
-      <c r="R29" s="401" t="n"/>
-      <c r="S29" s="402" t="n"/>
-      <c r="T29" s="373" t="n"/>
-      <c r="U29" s="401" t="n"/>
-      <c r="V29" s="401" t="n"/>
-      <c r="W29" s="401" t="n"/>
-      <c r="X29" s="401" t="n"/>
-      <c r="Y29" s="401" t="n"/>
-      <c r="Z29" s="401" t="n"/>
-      <c r="AA29" s="401" t="n"/>
-      <c r="AB29" s="401" t="n"/>
-      <c r="AC29" s="401" t="n"/>
-      <c r="AD29" s="401" t="n"/>
-      <c r="AE29" s="402" t="n"/>
-      <c r="AF29" s="372" t="n"/>
-      <c r="AG29" s="401" t="n"/>
-      <c r="AH29" s="401" t="n"/>
-      <c r="AI29" s="402" t="n"/>
-      <c r="AJ29" s="372" t="n"/>
-      <c r="AK29" s="401" t="n"/>
-      <c r="AL29" s="402" t="n"/>
-      <c r="AM29" s="374" t="n"/>
-      <c r="AN29" s="402" t="n"/>
+      <c r="D29" s="341" t="n"/>
+      <c r="E29" s="341" t="n"/>
+      <c r="F29" s="462" t="n"/>
+      <c r="G29" s="341" t="n"/>
+      <c r="H29" s="341" t="n"/>
+      <c r="I29" s="341" t="n"/>
+      <c r="J29" s="341" t="n"/>
+      <c r="K29" s="341" t="n"/>
+      <c r="L29" s="341" t="n"/>
+      <c r="M29" s="341" t="n"/>
+      <c r="N29" s="341" t="n"/>
+      <c r="O29" s="341" t="n"/>
+      <c r="P29" s="341" t="n"/>
+      <c r="Q29" s="341" t="n"/>
+      <c r="R29" s="341" t="n"/>
+      <c r="S29" s="341" t="n"/>
+      <c r="T29" s="485" t="n"/>
+      <c r="U29" s="341" t="n"/>
+      <c r="V29" s="341" t="n"/>
+      <c r="W29" s="341" t="n"/>
+      <c r="X29" s="341" t="n"/>
+      <c r="Y29" s="341" t="n"/>
+      <c r="Z29" s="341" t="n"/>
+      <c r="AA29" s="341" t="n"/>
+      <c r="AB29" s="341" t="n"/>
+      <c r="AC29" s="341" t="n"/>
+      <c r="AD29" s="341" t="n"/>
+      <c r="AE29" s="341" t="n"/>
+      <c r="AF29" s="462" t="n"/>
+      <c r="AG29" s="341" t="n"/>
+      <c r="AH29" s="341" t="n"/>
+      <c r="AI29" s="341" t="n"/>
+      <c r="AJ29" s="462" t="n"/>
+      <c r="AK29" s="341" t="n"/>
+      <c r="AL29" s="341" t="n"/>
+      <c r="AM29" s="486" t="n"/>
+      <c r="AN29" s="464" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1" s="329">
-      <c r="A30" s="370">
+      <c r="A30" s="483">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B30" s="402" t="n"/>
-      <c r="C30" s="371" t="inlineStr">
+      <c r="B30" s="341" t="n"/>
+      <c r="C30" s="484" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D30" s="401" t="n"/>
-      <c r="E30" s="402" t="n"/>
-      <c r="F30" s="372" t="n"/>
-      <c r="G30" s="401" t="n"/>
-      <c r="H30" s="401" t="n"/>
-      <c r="I30" s="401" t="n"/>
-      <c r="J30" s="401" t="n"/>
-      <c r="K30" s="401" t="n"/>
-      <c r="L30" s="401" t="n"/>
-      <c r="M30" s="401" t="n"/>
-      <c r="N30" s="401" t="n"/>
-      <c r="O30" s="401" t="n"/>
-      <c r="P30" s="401" t="n"/>
-      <c r="Q30" s="401" t="n"/>
-      <c r="R30" s="401" t="n"/>
-      <c r="S30" s="402" t="n"/>
-      <c r="T30" s="373" t="n"/>
-      <c r="U30" s="401" t="n"/>
-      <c r="V30" s="401" t="n"/>
-      <c r="W30" s="401" t="n"/>
-      <c r="X30" s="401" t="n"/>
-      <c r="Y30" s="401" t="n"/>
-      <c r="Z30" s="401" t="n"/>
-      <c r="AA30" s="401" t="n"/>
-      <c r="AB30" s="401" t="n"/>
-      <c r="AC30" s="401" t="n"/>
-      <c r="AD30" s="401" t="n"/>
-      <c r="AE30" s="402" t="n"/>
-      <c r="AF30" s="372" t="n"/>
-      <c r="AG30" s="401" t="n"/>
-      <c r="AH30" s="401" t="n"/>
-      <c r="AI30" s="402" t="n"/>
-      <c r="AJ30" s="372" t="n"/>
-      <c r="AK30" s="401" t="n"/>
-      <c r="AL30" s="402" t="n"/>
-      <c r="AM30" s="374" t="n"/>
-      <c r="AN30" s="402" t="n"/>
+      <c r="D30" s="341" t="n"/>
+      <c r="E30" s="341" t="n"/>
+      <c r="F30" s="462" t="n"/>
+      <c r="G30" s="341" t="n"/>
+      <c r="H30" s="341" t="n"/>
+      <c r="I30" s="341" t="n"/>
+      <c r="J30" s="341" t="n"/>
+      <c r="K30" s="341" t="n"/>
+      <c r="L30" s="341" t="n"/>
+      <c r="M30" s="341" t="n"/>
+      <c r="N30" s="341" t="n"/>
+      <c r="O30" s="341" t="n"/>
+      <c r="P30" s="341" t="n"/>
+      <c r="Q30" s="341" t="n"/>
+      <c r="R30" s="341" t="n"/>
+      <c r="S30" s="341" t="n"/>
+      <c r="T30" s="485" t="n"/>
+      <c r="U30" s="341" t="n"/>
+      <c r="V30" s="341" t="n"/>
+      <c r="W30" s="341" t="n"/>
+      <c r="X30" s="341" t="n"/>
+      <c r="Y30" s="341" t="n"/>
+      <c r="Z30" s="341" t="n"/>
+      <c r="AA30" s="341" t="n"/>
+      <c r="AB30" s="341" t="n"/>
+      <c r="AC30" s="341" t="n"/>
+      <c r="AD30" s="341" t="n"/>
+      <c r="AE30" s="341" t="n"/>
+      <c r="AF30" s="462" t="n"/>
+      <c r="AG30" s="341" t="n"/>
+      <c r="AH30" s="341" t="n"/>
+      <c r="AI30" s="341" t="n"/>
+      <c r="AJ30" s="462" t="n"/>
+      <c r="AK30" s="341" t="n"/>
+      <c r="AL30" s="341" t="n"/>
+      <c r="AM30" s="486" t="n"/>
+      <c r="AN30" s="464" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1" s="329">
-      <c r="A31" s="370">
+      <c r="A31" s="483">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B31" s="402" t="n"/>
-      <c r="C31" s="371" t="inlineStr">
+      <c r="B31" s="341" t="n"/>
+      <c r="C31" s="484" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D31" s="401" t="n"/>
-      <c r="E31" s="402" t="n"/>
-      <c r="F31" s="372" t="n"/>
-      <c r="G31" s="401" t="n"/>
-      <c r="H31" s="401" t="n"/>
-      <c r="I31" s="401" t="n"/>
-      <c r="J31" s="401" t="n"/>
-      <c r="K31" s="401" t="n"/>
-      <c r="L31" s="401" t="n"/>
-      <c r="M31" s="401" t="n"/>
-      <c r="N31" s="401" t="n"/>
-      <c r="O31" s="401" t="n"/>
-      <c r="P31" s="401" t="n"/>
-      <c r="Q31" s="401" t="n"/>
-      <c r="R31" s="401" t="n"/>
-      <c r="S31" s="402" t="n"/>
-      <c r="T31" s="373" t="n"/>
-      <c r="U31" s="401" t="n"/>
-      <c r="V31" s="401" t="n"/>
-      <c r="W31" s="401" t="n"/>
-      <c r="X31" s="401" t="n"/>
-      <c r="Y31" s="401" t="n"/>
-      <c r="Z31" s="401" t="n"/>
-      <c r="AA31" s="401" t="n"/>
-      <c r="AB31" s="401" t="n"/>
-      <c r="AC31" s="401" t="n"/>
-      <c r="AD31" s="401" t="n"/>
-      <c r="AE31" s="402" t="n"/>
-      <c r="AF31" s="372" t="n"/>
-      <c r="AG31" s="401" t="n"/>
-      <c r="AH31" s="401" t="n"/>
-      <c r="AI31" s="402" t="n"/>
-      <c r="AJ31" s="372" t="n"/>
-      <c r="AK31" s="401" t="n"/>
-      <c r="AL31" s="402" t="n"/>
-      <c r="AM31" s="374" t="n"/>
-      <c r="AN31" s="402" t="n"/>
+      <c r="D31" s="341" t="n"/>
+      <c r="E31" s="341" t="n"/>
+      <c r="F31" s="462" t="n"/>
+      <c r="G31" s="341" t="n"/>
+      <c r="H31" s="341" t="n"/>
+      <c r="I31" s="341" t="n"/>
+      <c r="J31" s="341" t="n"/>
+      <c r="K31" s="341" t="n"/>
+      <c r="L31" s="341" t="n"/>
+      <c r="M31" s="341" t="n"/>
+      <c r="N31" s="341" t="n"/>
+      <c r="O31" s="341" t="n"/>
+      <c r="P31" s="341" t="n"/>
+      <c r="Q31" s="341" t="n"/>
+      <c r="R31" s="341" t="n"/>
+      <c r="S31" s="341" t="n"/>
+      <c r="T31" s="485" t="n"/>
+      <c r="U31" s="341" t="n"/>
+      <c r="V31" s="341" t="n"/>
+      <c r="W31" s="341" t="n"/>
+      <c r="X31" s="341" t="n"/>
+      <c r="Y31" s="341" t="n"/>
+      <c r="Z31" s="341" t="n"/>
+      <c r="AA31" s="341" t="n"/>
+      <c r="AB31" s="341" t="n"/>
+      <c r="AC31" s="341" t="n"/>
+      <c r="AD31" s="341" t="n"/>
+      <c r="AE31" s="341" t="n"/>
+      <c r="AF31" s="462" t="n"/>
+      <c r="AG31" s="341" t="n"/>
+      <c r="AH31" s="341" t="n"/>
+      <c r="AI31" s="341" t="n"/>
+      <c r="AJ31" s="462" t="n"/>
+      <c r="AK31" s="341" t="n"/>
+      <c r="AL31" s="341" t="n"/>
+      <c r="AM31" s="486" t="n"/>
+      <c r="AN31" s="464" t="n"/>
     </row>
     <row r="32" ht="20" customHeight="1" s="329">
-      <c r="A32" s="370">
+      <c r="A32" s="487">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B32" s="402" t="n"/>
-      <c r="C32" s="371" t="inlineStr">
+      <c r="B32" s="466" t="n"/>
+      <c r="C32" s="488" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D32" s="401" t="n"/>
-      <c r="E32" s="402" t="n"/>
-      <c r="F32" s="372" t="n"/>
-      <c r="G32" s="401" t="n"/>
-      <c r="H32" s="401" t="n"/>
-      <c r="I32" s="401" t="n"/>
-      <c r="J32" s="401" t="n"/>
-      <c r="K32" s="401" t="n"/>
-      <c r="L32" s="401" t="n"/>
-      <c r="M32" s="401" t="n"/>
-      <c r="N32" s="401" t="n"/>
-      <c r="O32" s="401" t="n"/>
-      <c r="P32" s="401" t="n"/>
-      <c r="Q32" s="401" t="n"/>
-      <c r="R32" s="401" t="n"/>
-      <c r="S32" s="402" t="n"/>
-      <c r="T32" s="373" t="n"/>
-      <c r="U32" s="401" t="n"/>
-      <c r="V32" s="401" t="n"/>
-      <c r="W32" s="401" t="n"/>
-      <c r="X32" s="401" t="n"/>
-      <c r="Y32" s="401" t="n"/>
-      <c r="Z32" s="401" t="n"/>
-      <c r="AA32" s="401" t="n"/>
-      <c r="AB32" s="401" t="n"/>
-      <c r="AC32" s="401" t="n"/>
-      <c r="AD32" s="401" t="n"/>
-      <c r="AE32" s="402" t="n"/>
-      <c r="AF32" s="372" t="n"/>
-      <c r="AG32" s="401" t="n"/>
-      <c r="AH32" s="401" t="n"/>
-      <c r="AI32" s="402" t="n"/>
-      <c r="AJ32" s="372" t="n"/>
-      <c r="AK32" s="401" t="n"/>
-      <c r="AL32" s="402" t="n"/>
-      <c r="AM32" s="374" t="n"/>
-      <c r="AN32" s="402" t="n"/>
+      <c r="D32" s="466" t="n"/>
+      <c r="E32" s="466" t="n"/>
+      <c r="F32" s="467" t="n"/>
+      <c r="G32" s="466" t="n"/>
+      <c r="H32" s="466" t="n"/>
+      <c r="I32" s="466" t="n"/>
+      <c r="J32" s="466" t="n"/>
+      <c r="K32" s="466" t="n"/>
+      <c r="L32" s="466" t="n"/>
+      <c r="M32" s="466" t="n"/>
+      <c r="N32" s="466" t="n"/>
+      <c r="O32" s="466" t="n"/>
+      <c r="P32" s="466" t="n"/>
+      <c r="Q32" s="466" t="n"/>
+      <c r="R32" s="466" t="n"/>
+      <c r="S32" s="466" t="n"/>
+      <c r="T32" s="489" t="n"/>
+      <c r="U32" s="466" t="n"/>
+      <c r="V32" s="466" t="n"/>
+      <c r="W32" s="466" t="n"/>
+      <c r="X32" s="466" t="n"/>
+      <c r="Y32" s="466" t="n"/>
+      <c r="Z32" s="466" t="n"/>
+      <c r="AA32" s="466" t="n"/>
+      <c r="AB32" s="466" t="n"/>
+      <c r="AC32" s="466" t="n"/>
+      <c r="AD32" s="466" t="n"/>
+      <c r="AE32" s="466" t="n"/>
+      <c r="AF32" s="467" t="n"/>
+      <c r="AG32" s="466" t="n"/>
+      <c r="AH32" s="466" t="n"/>
+      <c r="AI32" s="466" t="n"/>
+      <c r="AJ32" s="467" t="n"/>
+      <c r="AK32" s="466" t="n"/>
+      <c r="AL32" s="466" t="n"/>
+      <c r="AM32" s="490" t="n"/>
+      <c r="AN32" s="469" t="n"/>
     </row>
-    <row r="33" ht="4" customHeight="1" s="329">
+    <row r="33" ht="3" customHeight="1" s="329">
       <c r="A33" s="357" t="n"/>
       <c r="B33" s="350" t="n"/>
       <c r="C33" s="350" t="n"/>
@@ -6611,153 +7426,153 @@
       <c r="AM33" s="350" t="n"/>
       <c r="AN33" s="350" t="n"/>
     </row>
-    <row r="34" ht="20" customHeight="1" s="329">
-      <c r="A34" s="351" t="inlineStr">
+    <row r="34" ht="18" customHeight="1" s="329">
+      <c r="A34" s="453" t="inlineStr">
         <is>
           <t xml:space="preserve">  4. FINAL DECISION / CLOSURE</t>
         </is>
       </c>
-      <c r="B34" s="397" t="n"/>
-      <c r="C34" s="397" t="n"/>
-      <c r="D34" s="397" t="n"/>
-      <c r="E34" s="397" t="n"/>
-      <c r="F34" s="397" t="n"/>
-      <c r="G34" s="397" t="n"/>
-      <c r="H34" s="397" t="n"/>
-      <c r="I34" s="397" t="n"/>
-      <c r="J34" s="397" t="n"/>
-      <c r="K34" s="397" t="n"/>
-      <c r="L34" s="397" t="n"/>
-      <c r="M34" s="397" t="n"/>
-      <c r="N34" s="397" t="n"/>
-      <c r="O34" s="397" t="n"/>
-      <c r="P34" s="397" t="n"/>
-      <c r="Q34" s="397" t="n"/>
-      <c r="R34" s="397" t="n"/>
-      <c r="S34" s="397" t="n"/>
-      <c r="T34" s="397" t="n"/>
-      <c r="U34" s="397" t="n"/>
-      <c r="V34" s="397" t="n"/>
-      <c r="W34" s="397" t="n"/>
-      <c r="X34" s="397" t="n"/>
-      <c r="Y34" s="397" t="n"/>
-      <c r="Z34" s="397" t="n"/>
-      <c r="AA34" s="397" t="n"/>
-      <c r="AB34" s="397" t="n"/>
-      <c r="AC34" s="397" t="n"/>
-      <c r="AD34" s="397" t="n"/>
-      <c r="AE34" s="397" t="n"/>
-      <c r="AF34" s="397" t="n"/>
-      <c r="AG34" s="397" t="n"/>
-      <c r="AH34" s="397" t="n"/>
-      <c r="AI34" s="397" t="n"/>
-      <c r="AJ34" s="397" t="n"/>
-      <c r="AK34" s="397" t="n"/>
-      <c r="AL34" s="397" t="n"/>
-      <c r="AM34" s="397" t="n"/>
-      <c r="AN34" s="398" t="n"/>
+      <c r="B34" s="454" t="n"/>
+      <c r="C34" s="454" t="n"/>
+      <c r="D34" s="454" t="n"/>
+      <c r="E34" s="454" t="n"/>
+      <c r="F34" s="454" t="n"/>
+      <c r="G34" s="454" t="n"/>
+      <c r="H34" s="454" t="n"/>
+      <c r="I34" s="454" t="n"/>
+      <c r="J34" s="454" t="n"/>
+      <c r="K34" s="454" t="n"/>
+      <c r="L34" s="454" t="n"/>
+      <c r="M34" s="454" t="n"/>
+      <c r="N34" s="454" t="n"/>
+      <c r="O34" s="454" t="n"/>
+      <c r="P34" s="454" t="n"/>
+      <c r="Q34" s="454" t="n"/>
+      <c r="R34" s="454" t="n"/>
+      <c r="S34" s="454" t="n"/>
+      <c r="T34" s="454" t="n"/>
+      <c r="U34" s="454" t="n"/>
+      <c r="V34" s="454" t="n"/>
+      <c r="W34" s="454" t="n"/>
+      <c r="X34" s="454" t="n"/>
+      <c r="Y34" s="454" t="n"/>
+      <c r="Z34" s="454" t="n"/>
+      <c r="AA34" s="454" t="n"/>
+      <c r="AB34" s="454" t="n"/>
+      <c r="AC34" s="454" t="n"/>
+      <c r="AD34" s="454" t="n"/>
+      <c r="AE34" s="454" t="n"/>
+      <c r="AF34" s="454" t="n"/>
+      <c r="AG34" s="454" t="n"/>
+      <c r="AH34" s="454" t="n"/>
+      <c r="AI34" s="454" t="n"/>
+      <c r="AJ34" s="454" t="n"/>
+      <c r="AK34" s="454" t="n"/>
+      <c r="AL34" s="454" t="n"/>
+      <c r="AM34" s="454" t="n"/>
+      <c r="AN34" s="455" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1" s="329">
-      <c r="A35" s="352" t="inlineStr">
+      <c r="A35" s="456" t="inlineStr">
         <is>
           <t>Final Decision</t>
         </is>
       </c>
-      <c r="B35" s="397" t="n"/>
-      <c r="C35" s="397" t="n"/>
-      <c r="D35" s="397" t="n"/>
-      <c r="E35" s="397" t="n"/>
-      <c r="F35" s="397" t="n"/>
-      <c r="G35" s="398" t="n"/>
-      <c r="H35" s="355" t="n"/>
-      <c r="I35" s="397" t="n"/>
-      <c r="J35" s="397" t="n"/>
-      <c r="K35" s="397" t="n"/>
-      <c r="L35" s="397" t="n"/>
-      <c r="M35" s="397" t="n"/>
-      <c r="N35" s="397" t="n"/>
-      <c r="O35" s="397" t="n"/>
-      <c r="P35" s="397" t="n"/>
-      <c r="Q35" s="397" t="n"/>
-      <c r="R35" s="397" t="n"/>
-      <c r="S35" s="397" t="n"/>
-      <c r="T35" s="398" t="n"/>
-      <c r="U35" s="356" t="inlineStr">
+      <c r="B35" s="457" t="n"/>
+      <c r="C35" s="457" t="n"/>
+      <c r="D35" s="457" t="n"/>
+      <c r="E35" s="457" t="n"/>
+      <c r="F35" s="457" t="n"/>
+      <c r="G35" s="457" t="n"/>
+      <c r="H35" s="458" t="n"/>
+      <c r="I35" s="457" t="n"/>
+      <c r="J35" s="457" t="n"/>
+      <c r="K35" s="457" t="n"/>
+      <c r="L35" s="457" t="n"/>
+      <c r="M35" s="457" t="n"/>
+      <c r="N35" s="457" t="n"/>
+      <c r="O35" s="457" t="n"/>
+      <c r="P35" s="457" t="n"/>
+      <c r="Q35" s="457" t="n"/>
+      <c r="R35" s="457" t="n"/>
+      <c r="S35" s="457" t="n"/>
+      <c r="T35" s="457" t="n"/>
+      <c r="U35" s="459" t="inlineStr">
         <is>
           <t>Reviewed by</t>
         </is>
       </c>
-      <c r="V35" s="397" t="n"/>
-      <c r="W35" s="397" t="n"/>
-      <c r="X35" s="397" t="n"/>
-      <c r="Y35" s="397" t="n"/>
-      <c r="Z35" s="397" t="n"/>
-      <c r="AA35" s="398" t="n"/>
-      <c r="AB35" s="355" t="n"/>
-      <c r="AC35" s="397" t="n"/>
-      <c r="AD35" s="397" t="n"/>
-      <c r="AE35" s="397" t="n"/>
-      <c r="AF35" s="397" t="n"/>
-      <c r="AG35" s="397" t="n"/>
-      <c r="AH35" s="397" t="n"/>
-      <c r="AI35" s="397" t="n"/>
-      <c r="AJ35" s="397" t="n"/>
-      <c r="AK35" s="397" t="n"/>
-      <c r="AL35" s="397" t="n"/>
-      <c r="AM35" s="397" t="n"/>
-      <c r="AN35" s="398" t="n"/>
+      <c r="V35" s="457" t="n"/>
+      <c r="W35" s="457" t="n"/>
+      <c r="X35" s="457" t="n"/>
+      <c r="Y35" s="457" t="n"/>
+      <c r="Z35" s="457" t="n"/>
+      <c r="AA35" s="457" t="n"/>
+      <c r="AB35" s="458" t="n"/>
+      <c r="AC35" s="457" t="n"/>
+      <c r="AD35" s="457" t="n"/>
+      <c r="AE35" s="457" t="n"/>
+      <c r="AF35" s="457" t="n"/>
+      <c r="AG35" s="457" t="n"/>
+      <c r="AH35" s="457" t="n"/>
+      <c r="AI35" s="457" t="n"/>
+      <c r="AJ35" s="457" t="n"/>
+      <c r="AK35" s="457" t="n"/>
+      <c r="AL35" s="457" t="n"/>
+      <c r="AM35" s="457" t="n"/>
+      <c r="AN35" s="460" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1" s="329">
-      <c r="A36" s="352" t="inlineStr">
+      <c r="A36" s="465" t="inlineStr">
         <is>
           <t>Containment Required (YES/NO)</t>
         </is>
       </c>
-      <c r="B36" s="397" t="n"/>
-      <c r="C36" s="397" t="n"/>
-      <c r="D36" s="397" t="n"/>
-      <c r="E36" s="397" t="n"/>
-      <c r="F36" s="397" t="n"/>
-      <c r="G36" s="398" t="n"/>
-      <c r="H36" s="355" t="n"/>
-      <c r="I36" s="397" t="n"/>
-      <c r="J36" s="397" t="n"/>
-      <c r="K36" s="397" t="n"/>
-      <c r="L36" s="397" t="n"/>
-      <c r="M36" s="397" t="n"/>
-      <c r="N36" s="397" t="n"/>
-      <c r="O36" s="397" t="n"/>
-      <c r="P36" s="397" t="n"/>
-      <c r="Q36" s="397" t="n"/>
-      <c r="R36" s="397" t="n"/>
-      <c r="S36" s="397" t="n"/>
-      <c r="T36" s="398" t="n"/>
-      <c r="U36" s="356" t="inlineStr">
+      <c r="B36" s="466" t="n"/>
+      <c r="C36" s="466" t="n"/>
+      <c r="D36" s="466" t="n"/>
+      <c r="E36" s="466" t="n"/>
+      <c r="F36" s="466" t="n"/>
+      <c r="G36" s="466" t="n"/>
+      <c r="H36" s="467" t="n"/>
+      <c r="I36" s="466" t="n"/>
+      <c r="J36" s="466" t="n"/>
+      <c r="K36" s="466" t="n"/>
+      <c r="L36" s="466" t="n"/>
+      <c r="M36" s="466" t="n"/>
+      <c r="N36" s="466" t="n"/>
+      <c r="O36" s="466" t="n"/>
+      <c r="P36" s="466" t="n"/>
+      <c r="Q36" s="466" t="n"/>
+      <c r="R36" s="466" t="n"/>
+      <c r="S36" s="466" t="n"/>
+      <c r="T36" s="466" t="n"/>
+      <c r="U36" s="468" t="inlineStr">
         <is>
           <t>Target Closeout</t>
         </is>
       </c>
-      <c r="V36" s="397" t="n"/>
-      <c r="W36" s="397" t="n"/>
-      <c r="X36" s="397" t="n"/>
-      <c r="Y36" s="397" t="n"/>
-      <c r="Z36" s="397" t="n"/>
-      <c r="AA36" s="398" t="n"/>
-      <c r="AB36" s="355" t="n"/>
-      <c r="AC36" s="397" t="n"/>
-      <c r="AD36" s="397" t="n"/>
-      <c r="AE36" s="397" t="n"/>
-      <c r="AF36" s="397" t="n"/>
-      <c r="AG36" s="397" t="n"/>
-      <c r="AH36" s="397" t="n"/>
-      <c r="AI36" s="397" t="n"/>
-      <c r="AJ36" s="397" t="n"/>
-      <c r="AK36" s="397" t="n"/>
-      <c r="AL36" s="397" t="n"/>
-      <c r="AM36" s="397" t="n"/>
-      <c r="AN36" s="398" t="n"/>
+      <c r="V36" s="466" t="n"/>
+      <c r="W36" s="466" t="n"/>
+      <c r="X36" s="466" t="n"/>
+      <c r="Y36" s="466" t="n"/>
+      <c r="Z36" s="466" t="n"/>
+      <c r="AA36" s="466" t="n"/>
+      <c r="AB36" s="467" t="n"/>
+      <c r="AC36" s="466" t="n"/>
+      <c r="AD36" s="466" t="n"/>
+      <c r="AE36" s="466" t="n"/>
+      <c r="AF36" s="466" t="n"/>
+      <c r="AG36" s="466" t="n"/>
+      <c r="AH36" s="466" t="n"/>
+      <c r="AI36" s="466" t="n"/>
+      <c r="AJ36" s="466" t="n"/>
+      <c r="AK36" s="466" t="n"/>
+      <c r="AL36" s="466" t="n"/>
+      <c r="AM36" s="466" t="n"/>
+      <c r="AN36" s="469" t="n"/>
     </row>
-    <row r="37" ht="4" customHeight="1" s="329">
+    <row r="37" ht="3" customHeight="1" s="329">
       <c r="A37" s="362" t="n"/>
       <c r="B37" s="350" t="n"/>
       <c r="C37" s="364" t="n"/>
@@ -6799,245 +7614,245 @@
       <c r="AM37" s="350" t="n"/>
       <c r="AN37" s="350" t="n"/>
     </row>
-    <row r="38" ht="20" customHeight="1" s="329">
-      <c r="A38" s="351" t="inlineStr">
+    <row r="38" ht="18" customHeight="1" s="329">
+      <c r="A38" s="453" t="inlineStr">
         <is>
           <t xml:space="preserve">  5. APPROVAL / SIGN-OFF</t>
         </is>
       </c>
-      <c r="B38" s="397" t="n"/>
-      <c r="C38" s="397" t="n"/>
-      <c r="D38" s="397" t="n"/>
-      <c r="E38" s="397" t="n"/>
-      <c r="F38" s="397" t="n"/>
-      <c r="G38" s="397" t="n"/>
-      <c r="H38" s="397" t="n"/>
-      <c r="I38" s="397" t="n"/>
-      <c r="J38" s="397" t="n"/>
-      <c r="K38" s="397" t="n"/>
-      <c r="L38" s="397" t="n"/>
-      <c r="M38" s="397" t="n"/>
-      <c r="N38" s="397" t="n"/>
-      <c r="O38" s="397" t="n"/>
-      <c r="P38" s="397" t="n"/>
-      <c r="Q38" s="397" t="n"/>
-      <c r="R38" s="397" t="n"/>
-      <c r="S38" s="397" t="n"/>
-      <c r="T38" s="397" t="n"/>
-      <c r="U38" s="397" t="n"/>
-      <c r="V38" s="397" t="n"/>
-      <c r="W38" s="397" t="n"/>
-      <c r="X38" s="397" t="n"/>
-      <c r="Y38" s="397" t="n"/>
-      <c r="Z38" s="397" t="n"/>
-      <c r="AA38" s="397" t="n"/>
-      <c r="AB38" s="397" t="n"/>
-      <c r="AC38" s="397" t="n"/>
-      <c r="AD38" s="397" t="n"/>
-      <c r="AE38" s="397" t="n"/>
-      <c r="AF38" s="397" t="n"/>
-      <c r="AG38" s="397" t="n"/>
-      <c r="AH38" s="397" t="n"/>
-      <c r="AI38" s="397" t="n"/>
-      <c r="AJ38" s="397" t="n"/>
-      <c r="AK38" s="397" t="n"/>
-      <c r="AL38" s="397" t="n"/>
-      <c r="AM38" s="397" t="n"/>
-      <c r="AN38" s="398" t="n"/>
+      <c r="B38" s="454" t="n"/>
+      <c r="C38" s="454" t="n"/>
+      <c r="D38" s="454" t="n"/>
+      <c r="E38" s="454" t="n"/>
+      <c r="F38" s="454" t="n"/>
+      <c r="G38" s="454" t="n"/>
+      <c r="H38" s="454" t="n"/>
+      <c r="I38" s="454" t="n"/>
+      <c r="J38" s="454" t="n"/>
+      <c r="K38" s="454" t="n"/>
+      <c r="L38" s="454" t="n"/>
+      <c r="M38" s="454" t="n"/>
+      <c r="N38" s="454" t="n"/>
+      <c r="O38" s="454" t="n"/>
+      <c r="P38" s="454" t="n"/>
+      <c r="Q38" s="454" t="n"/>
+      <c r="R38" s="454" t="n"/>
+      <c r="S38" s="454" t="n"/>
+      <c r="T38" s="454" t="n"/>
+      <c r="U38" s="454" t="n"/>
+      <c r="V38" s="454" t="n"/>
+      <c r="W38" s="454" t="n"/>
+      <c r="X38" s="454" t="n"/>
+      <c r="Y38" s="454" t="n"/>
+      <c r="Z38" s="454" t="n"/>
+      <c r="AA38" s="454" t="n"/>
+      <c r="AB38" s="454" t="n"/>
+      <c r="AC38" s="454" t="n"/>
+      <c r="AD38" s="454" t="n"/>
+      <c r="AE38" s="454" t="n"/>
+      <c r="AF38" s="454" t="n"/>
+      <c r="AG38" s="454" t="n"/>
+      <c r="AH38" s="454" t="n"/>
+      <c r="AI38" s="454" t="n"/>
+      <c r="AJ38" s="454" t="n"/>
+      <c r="AK38" s="454" t="n"/>
+      <c r="AL38" s="454" t="n"/>
+      <c r="AM38" s="454" t="n"/>
+      <c r="AN38" s="455" t="n"/>
     </row>
-    <row r="39" ht="20" customHeight="1" s="329">
-      <c r="A39" s="375" t="inlineStr">
+    <row r="39" ht="26" customHeight="1" s="329">
+      <c r="A39" s="479" t="inlineStr">
         <is>
           <t>Prepared by</t>
         </is>
       </c>
-      <c r="B39" s="392" t="n"/>
-      <c r="C39" s="392" t="n"/>
-      <c r="D39" s="392" t="n"/>
-      <c r="E39" s="392" t="n"/>
-      <c r="F39" s="392" t="n"/>
-      <c r="G39" s="392" t="n"/>
-      <c r="H39" s="392" t="n"/>
-      <c r="I39" s="392" t="n"/>
-      <c r="J39" s="392" t="n"/>
-      <c r="K39" s="392" t="n"/>
-      <c r="L39" s="392" t="n"/>
-      <c r="M39" s="393" t="n"/>
-      <c r="N39" s="376" t="inlineStr">
+      <c r="B39" s="457" t="n"/>
+      <c r="C39" s="457" t="n"/>
+      <c r="D39" s="457" t="n"/>
+      <c r="E39" s="457" t="n"/>
+      <c r="F39" s="457" t="n"/>
+      <c r="G39" s="457" t="n"/>
+      <c r="H39" s="457" t="n"/>
+      <c r="I39" s="457" t="n"/>
+      <c r="J39" s="457" t="n"/>
+      <c r="K39" s="457" t="n"/>
+      <c r="L39" s="457" t="n"/>
+      <c r="M39" s="457" t="n"/>
+      <c r="N39" s="491" t="inlineStr">
         <is>
           <t>Reviewed by</t>
         </is>
       </c>
-      <c r="O39" s="392" t="n"/>
-      <c r="P39" s="392" t="n"/>
-      <c r="Q39" s="392" t="n"/>
-      <c r="R39" s="392" t="n"/>
-      <c r="S39" s="392" t="n"/>
-      <c r="T39" s="392" t="n"/>
-      <c r="U39" s="392" t="n"/>
-      <c r="V39" s="392" t="n"/>
-      <c r="W39" s="392" t="n"/>
-      <c r="X39" s="392" t="n"/>
-      <c r="Y39" s="392" t="n"/>
-      <c r="Z39" s="392" t="n"/>
-      <c r="AA39" s="377" t="inlineStr">
+      <c r="O39" s="457" t="n"/>
+      <c r="P39" s="457" t="n"/>
+      <c r="Q39" s="457" t="n"/>
+      <c r="R39" s="457" t="n"/>
+      <c r="S39" s="457" t="n"/>
+      <c r="T39" s="457" t="n"/>
+      <c r="U39" s="457" t="n"/>
+      <c r="V39" s="457" t="n"/>
+      <c r="W39" s="457" t="n"/>
+      <c r="X39" s="457" t="n"/>
+      <c r="Y39" s="457" t="n"/>
+      <c r="Z39" s="457" t="n"/>
+      <c r="AA39" s="491" t="inlineStr">
         <is>
           <t>Approved by</t>
         </is>
       </c>
-      <c r="AB39" s="392" t="n"/>
-      <c r="AC39" s="392" t="n"/>
-      <c r="AD39" s="392" t="n"/>
-      <c r="AE39" s="392" t="n"/>
-      <c r="AF39" s="392" t="n"/>
-      <c r="AG39" s="392" t="n"/>
-      <c r="AH39" s="392" t="n"/>
-      <c r="AI39" s="392" t="n"/>
-      <c r="AJ39" s="392" t="n"/>
-      <c r="AK39" s="392" t="n"/>
-      <c r="AL39" s="392" t="n"/>
-      <c r="AM39" s="392" t="n"/>
-      <c r="AN39" s="393" t="n"/>
+      <c r="AB39" s="457" t="n"/>
+      <c r="AC39" s="457" t="n"/>
+      <c r="AD39" s="457" t="n"/>
+      <c r="AE39" s="457" t="n"/>
+      <c r="AF39" s="457" t="n"/>
+      <c r="AG39" s="457" t="n"/>
+      <c r="AH39" s="457" t="n"/>
+      <c r="AI39" s="457" t="n"/>
+      <c r="AJ39" s="457" t="n"/>
+      <c r="AK39" s="457" t="n"/>
+      <c r="AL39" s="457" t="n"/>
+      <c r="AM39" s="457" t="n"/>
+      <c r="AN39" s="460" t="n"/>
     </row>
-    <row r="40" ht="20" customHeight="1" s="329">
-      <c r="A40" s="378" t="inlineStr">
+    <row r="40" ht="26" customHeight="1" s="329">
+      <c r="A40" s="492" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="B40" s="391" t="n"/>
-      <c r="C40" s="391" t="n"/>
-      <c r="D40" s="391" t="n"/>
-      <c r="E40" s="391" t="n"/>
-      <c r="F40" s="391" t="n"/>
-      <c r="G40" s="391" t="n"/>
-      <c r="H40" s="391" t="n"/>
-      <c r="I40" s="391" t="n"/>
-      <c r="J40" s="391" t="n"/>
-      <c r="K40" s="391" t="n"/>
-      <c r="L40" s="391" t="n"/>
-      <c r="M40" s="403" t="n"/>
-      <c r="N40" s="378" t="inlineStr">
+      <c r="B40" s="341" t="n"/>
+      <c r="C40" s="341" t="n"/>
+      <c r="D40" s="341" t="n"/>
+      <c r="E40" s="341" t="n"/>
+      <c r="F40" s="341" t="n"/>
+      <c r="G40" s="341" t="n"/>
+      <c r="H40" s="341" t="n"/>
+      <c r="I40" s="341" t="n"/>
+      <c r="J40" s="341" t="n"/>
+      <c r="K40" s="341" t="n"/>
+      <c r="L40" s="341" t="n"/>
+      <c r="M40" s="341" t="n"/>
+      <c r="N40" s="493" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="O40" s="391" t="n"/>
-      <c r="P40" s="391" t="n"/>
-      <c r="Q40" s="391" t="n"/>
-      <c r="R40" s="391" t="n"/>
-      <c r="S40" s="391" t="n"/>
-      <c r="T40" s="391" t="n"/>
-      <c r="U40" s="391" t="n"/>
-      <c r="V40" s="391" t="n"/>
-      <c r="W40" s="391" t="n"/>
-      <c r="X40" s="391" t="n"/>
-      <c r="Y40" s="391" t="n"/>
-      <c r="Z40" s="403" t="n"/>
-      <c r="AA40" s="378" t="inlineStr">
+      <c r="O40" s="341" t="n"/>
+      <c r="P40" s="341" t="n"/>
+      <c r="Q40" s="341" t="n"/>
+      <c r="R40" s="341" t="n"/>
+      <c r="S40" s="341" t="n"/>
+      <c r="T40" s="341" t="n"/>
+      <c r="U40" s="341" t="n"/>
+      <c r="V40" s="341" t="n"/>
+      <c r="W40" s="341" t="n"/>
+      <c r="X40" s="341" t="n"/>
+      <c r="Y40" s="341" t="n"/>
+      <c r="Z40" s="341" t="n"/>
+      <c r="AA40" s="493" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="AB40" s="391" t="n"/>
-      <c r="AC40" s="391" t="n"/>
-      <c r="AD40" s="391" t="n"/>
-      <c r="AE40" s="391" t="n"/>
-      <c r="AF40" s="391" t="n"/>
-      <c r="AG40" s="391" t="n"/>
-      <c r="AH40" s="391" t="n"/>
-      <c r="AI40" s="391" t="n"/>
-      <c r="AJ40" s="391" t="n"/>
-      <c r="AK40" s="391" t="n"/>
-      <c r="AL40" s="391" t="n"/>
-      <c r="AM40" s="391" t="n"/>
-      <c r="AN40" s="403" t="n"/>
+      <c r="AB40" s="341" t="n"/>
+      <c r="AC40" s="341" t="n"/>
+      <c r="AD40" s="341" t="n"/>
+      <c r="AE40" s="341" t="n"/>
+      <c r="AF40" s="341" t="n"/>
+      <c r="AG40" s="341" t="n"/>
+      <c r="AH40" s="341" t="n"/>
+      <c r="AI40" s="341" t="n"/>
+      <c r="AJ40" s="341" t="n"/>
+      <c r="AK40" s="341" t="n"/>
+      <c r="AL40" s="341" t="n"/>
+      <c r="AM40" s="341" t="n"/>
+      <c r="AN40" s="464" t="n"/>
     </row>
     <row r="41" ht="20" customHeight="1" s="329">
-      <c r="A41" s="404" t="n"/>
-      <c r="B41" s="381" t="n"/>
-      <c r="C41" s="381" t="n"/>
-      <c r="D41" s="381" t="n"/>
-      <c r="E41" s="381" t="n"/>
-      <c r="F41" s="381" t="n"/>
-      <c r="G41" s="381" t="n"/>
-      <c r="H41" s="381" t="n"/>
-      <c r="I41" s="381" t="n"/>
-      <c r="J41" s="381" t="n"/>
-      <c r="K41" s="381" t="n"/>
-      <c r="L41" s="381" t="n"/>
-      <c r="M41" s="405" t="n"/>
-      <c r="N41" s="404" t="n"/>
-      <c r="O41" s="381" t="n"/>
-      <c r="P41" s="381" t="n"/>
-      <c r="Q41" s="381" t="n"/>
-      <c r="R41" s="381" t="n"/>
-      <c r="S41" s="381" t="n"/>
-      <c r="T41" s="381" t="n"/>
-      <c r="U41" s="381" t="n"/>
-      <c r="V41" s="381" t="n"/>
-      <c r="W41" s="381" t="n"/>
-      <c r="X41" s="381" t="n"/>
-      <c r="Y41" s="381" t="n"/>
-      <c r="Z41" s="405" t="n"/>
-      <c r="AA41" s="404" t="n"/>
-      <c r="AB41" s="381" t="n"/>
-      <c r="AC41" s="381" t="n"/>
-      <c r="AD41" s="381" t="n"/>
-      <c r="AE41" s="381" t="n"/>
-      <c r="AF41" s="381" t="n"/>
-      <c r="AG41" s="381" t="n"/>
-      <c r="AH41" s="381" t="n"/>
-      <c r="AI41" s="381" t="n"/>
-      <c r="AJ41" s="381" t="n"/>
-      <c r="AK41" s="381" t="n"/>
-      <c r="AL41" s="381" t="n"/>
-      <c r="AM41" s="381" t="n"/>
-      <c r="AN41" s="405" t="n"/>
+      <c r="A41" s="472" t="n"/>
+      <c r="B41" s="341" t="n"/>
+      <c r="C41" s="341" t="n"/>
+      <c r="D41" s="341" t="n"/>
+      <c r="E41" s="341" t="n"/>
+      <c r="F41" s="341" t="n"/>
+      <c r="G41" s="341" t="n"/>
+      <c r="H41" s="341" t="n"/>
+      <c r="I41" s="341" t="n"/>
+      <c r="J41" s="341" t="n"/>
+      <c r="K41" s="341" t="n"/>
+      <c r="L41" s="341" t="n"/>
+      <c r="M41" s="341" t="n"/>
+      <c r="N41" s="470" t="n"/>
+      <c r="O41" s="341" t="n"/>
+      <c r="P41" s="341" t="n"/>
+      <c r="Q41" s="341" t="n"/>
+      <c r="R41" s="341" t="n"/>
+      <c r="S41" s="341" t="n"/>
+      <c r="T41" s="341" t="n"/>
+      <c r="U41" s="341" t="n"/>
+      <c r="V41" s="341" t="n"/>
+      <c r="W41" s="341" t="n"/>
+      <c r="X41" s="341" t="n"/>
+      <c r="Y41" s="341" t="n"/>
+      <c r="Z41" s="341" t="n"/>
+      <c r="AA41" s="470" t="n"/>
+      <c r="AB41" s="341" t="n"/>
+      <c r="AC41" s="341" t="n"/>
+      <c r="AD41" s="341" t="n"/>
+      <c r="AE41" s="341" t="n"/>
+      <c r="AF41" s="341" t="n"/>
+      <c r="AG41" s="341" t="n"/>
+      <c r="AH41" s="341" t="n"/>
+      <c r="AI41" s="341" t="n"/>
+      <c r="AJ41" s="341" t="n"/>
+      <c r="AK41" s="341" t="n"/>
+      <c r="AL41" s="341" t="n"/>
+      <c r="AM41" s="341" t="n"/>
+      <c r="AN41" s="464" t="n"/>
     </row>
     <row r="42" ht="20" customHeight="1" s="329">
-      <c r="A42" s="406" t="n"/>
-      <c r="B42" s="401" t="n"/>
-      <c r="C42" s="401" t="n"/>
-      <c r="D42" s="401" t="n"/>
-      <c r="E42" s="401" t="n"/>
-      <c r="F42" s="401" t="n"/>
-      <c r="G42" s="401" t="n"/>
-      <c r="H42" s="401" t="n"/>
-      <c r="I42" s="401" t="n"/>
-      <c r="J42" s="401" t="n"/>
-      <c r="K42" s="401" t="n"/>
-      <c r="L42" s="401" t="n"/>
-      <c r="M42" s="402" t="n"/>
-      <c r="N42" s="406" t="n"/>
-      <c r="O42" s="401" t="n"/>
-      <c r="P42" s="401" t="n"/>
-      <c r="Q42" s="401" t="n"/>
-      <c r="R42" s="401" t="n"/>
-      <c r="S42" s="401" t="n"/>
-      <c r="T42" s="401" t="n"/>
-      <c r="U42" s="401" t="n"/>
-      <c r="V42" s="401" t="n"/>
-      <c r="W42" s="401" t="n"/>
-      <c r="X42" s="401" t="n"/>
-      <c r="Y42" s="401" t="n"/>
-      <c r="Z42" s="402" t="n"/>
-      <c r="AA42" s="406" t="n"/>
-      <c r="AB42" s="401" t="n"/>
-      <c r="AC42" s="401" t="n"/>
-      <c r="AD42" s="401" t="n"/>
-      <c r="AE42" s="401" t="n"/>
-      <c r="AF42" s="401" t="n"/>
-      <c r="AG42" s="401" t="n"/>
-      <c r="AH42" s="401" t="n"/>
-      <c r="AI42" s="401" t="n"/>
-      <c r="AJ42" s="401" t="n"/>
-      <c r="AK42" s="401" t="n"/>
-      <c r="AL42" s="401" t="n"/>
-      <c r="AM42" s="401" t="n"/>
-      <c r="AN42" s="402" t="n"/>
+      <c r="A42" s="473" t="n"/>
+      <c r="B42" s="466" t="n"/>
+      <c r="C42" s="466" t="n"/>
+      <c r="D42" s="466" t="n"/>
+      <c r="E42" s="466" t="n"/>
+      <c r="F42" s="466" t="n"/>
+      <c r="G42" s="466" t="n"/>
+      <c r="H42" s="466" t="n"/>
+      <c r="I42" s="466" t="n"/>
+      <c r="J42" s="466" t="n"/>
+      <c r="K42" s="466" t="n"/>
+      <c r="L42" s="466" t="n"/>
+      <c r="M42" s="466" t="n"/>
+      <c r="N42" s="474" t="n"/>
+      <c r="O42" s="466" t="n"/>
+      <c r="P42" s="466" t="n"/>
+      <c r="Q42" s="466" t="n"/>
+      <c r="R42" s="466" t="n"/>
+      <c r="S42" s="466" t="n"/>
+      <c r="T42" s="466" t="n"/>
+      <c r="U42" s="466" t="n"/>
+      <c r="V42" s="466" t="n"/>
+      <c r="W42" s="466" t="n"/>
+      <c r="X42" s="466" t="n"/>
+      <c r="Y42" s="466" t="n"/>
+      <c r="Z42" s="466" t="n"/>
+      <c r="AA42" s="474" t="n"/>
+      <c r="AB42" s="466" t="n"/>
+      <c r="AC42" s="466" t="n"/>
+      <c r="AD42" s="466" t="n"/>
+      <c r="AE42" s="466" t="n"/>
+      <c r="AF42" s="466" t="n"/>
+      <c r="AG42" s="466" t="n"/>
+      <c r="AH42" s="466" t="n"/>
+      <c r="AI42" s="466" t="n"/>
+      <c r="AJ42" s="466" t="n"/>
+      <c r="AK42" s="466" t="n"/>
+      <c r="AL42" s="466" t="n"/>
+      <c r="AM42" s="466" t="n"/>
+      <c r="AN42" s="469" t="n"/>
     </row>
-    <row r="43" ht="4" customHeight="1" s="329">
+    <row r="43" ht="3" customHeight="1" s="329">
       <c r="A43" s="384" t="n"/>
       <c r="B43" s="350" t="n"/>
       <c r="C43" s="350" t="n"/>
@@ -7080,56 +7895,56 @@
       <c r="AN43" s="350" t="n"/>
     </row>
     <row r="44" ht="20" customHeight="1" s="329">
-      <c r="A44" s="385" t="inlineStr">
+      <c r="A44" s="494" t="inlineStr">
         <is>
           <t>NOTICE: Use for outsourced incoming verification only. Normal receiving / put-away remains in FRM-701; abnormal hold / disposition goes to FRM-413.</t>
         </is>
       </c>
-      <c r="B44" s="381" t="n"/>
-      <c r="C44" s="381" t="n"/>
-      <c r="D44" s="381" t="n"/>
-      <c r="E44" s="381" t="n"/>
-      <c r="F44" s="381" t="n"/>
-      <c r="G44" s="381" t="n"/>
-      <c r="H44" s="381" t="n"/>
-      <c r="I44" s="381" t="n"/>
-      <c r="J44" s="381" t="n"/>
-      <c r="K44" s="381" t="n"/>
-      <c r="L44" s="381" t="n"/>
-      <c r="M44" s="381" t="n"/>
-      <c r="N44" s="381" t="n"/>
-      <c r="O44" s="381" t="n"/>
-      <c r="P44" s="381" t="n"/>
-      <c r="Q44" s="381" t="n"/>
-      <c r="R44" s="381" t="n"/>
-      <c r="S44" s="381" t="n"/>
-      <c r="T44" s="381" t="n"/>
-      <c r="U44" s="381" t="n"/>
-      <c r="V44" s="381" t="n"/>
-      <c r="W44" s="381" t="n"/>
-      <c r="X44" s="381" t="n"/>
-      <c r="Y44" s="381" t="n"/>
-      <c r="Z44" s="381" t="n"/>
-      <c r="AA44" s="381" t="n"/>
-      <c r="AB44" s="381" t="n"/>
-      <c r="AC44" s="381" t="n"/>
-      <c r="AD44" s="381" t="n"/>
-      <c r="AE44" s="381" t="n"/>
-      <c r="AF44" s="381" t="n"/>
-      <c r="AG44" s="381" t="n"/>
-      <c r="AH44" s="381" t="n"/>
-      <c r="AI44" s="381" t="n"/>
-      <c r="AJ44" s="381" t="n"/>
-      <c r="AK44" s="381" t="n"/>
-      <c r="AL44" s="381" t="n"/>
-      <c r="AM44" s="381" t="n"/>
-      <c r="AN44" s="381" t="n"/>
+      <c r="B44" s="495" t="n"/>
+      <c r="C44" s="495" t="n"/>
+      <c r="D44" s="495" t="n"/>
+      <c r="E44" s="495" t="n"/>
+      <c r="F44" s="495" t="n"/>
+      <c r="G44" s="495" t="n"/>
+      <c r="H44" s="495" t="n"/>
+      <c r="I44" s="495" t="n"/>
+      <c r="J44" s="495" t="n"/>
+      <c r="K44" s="495" t="n"/>
+      <c r="L44" s="495" t="n"/>
+      <c r="M44" s="495" t="n"/>
+      <c r="N44" s="495" t="n"/>
+      <c r="O44" s="495" t="n"/>
+      <c r="P44" s="495" t="n"/>
+      <c r="Q44" s="495" t="n"/>
+      <c r="R44" s="495" t="n"/>
+      <c r="S44" s="495" t="n"/>
+      <c r="T44" s="495" t="n"/>
+      <c r="U44" s="495" t="n"/>
+      <c r="V44" s="495" t="n"/>
+      <c r="W44" s="495" t="n"/>
+      <c r="X44" s="495" t="n"/>
+      <c r="Y44" s="495" t="n"/>
+      <c r="Z44" s="495" t="n"/>
+      <c r="AA44" s="495" t="n"/>
+      <c r="AB44" s="495" t="n"/>
+      <c r="AC44" s="495" t="n"/>
+      <c r="AD44" s="495" t="n"/>
+      <c r="AE44" s="495" t="n"/>
+      <c r="AF44" s="495" t="n"/>
+      <c r="AG44" s="495" t="n"/>
+      <c r="AH44" s="495" t="n"/>
+      <c r="AI44" s="495" t="n"/>
+      <c r="AJ44" s="495" t="n"/>
+      <c r="AK44" s="495" t="n"/>
+      <c r="AL44" s="495" t="n"/>
+      <c r="AM44" s="495" t="n"/>
+      <c r="AN44" s="496" t="n"/>
     </row>
     <row r="45" ht="26" customHeight="1" s="329"/>
     <row r="46" ht="4" customHeight="1" s="329"/>
     <row r="47" ht="24" customHeight="1" s="329"/>
   </sheetData>
-  <mergeCells count="120">
+  <mergeCells count="119">
     <mergeCell ref="AM26:AN26"/>
     <mergeCell ref="A17:G17"/>
     <mergeCell ref="A21:AN21"/>
@@ -7155,7 +7970,6 @@
     <mergeCell ref="F31:S31"/>
     <mergeCell ref="T30:AE30"/>
     <mergeCell ref="F28:S28"/>
-    <mergeCell ref="A6:AN6"/>
     <mergeCell ref="A22:AN23"/>
     <mergeCell ref="T29:AE29"/>
     <mergeCell ref="AI1:AN1"/>
@@ -7266,6 +8080,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7424,7 +8239,7 @@
           <t>PROD</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="345" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -7433,12 +8248,12 @@
       <c r="G5" s="266" t="n"/>
     </row>
     <row r="6">
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="345" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="345" t="inlineStr">
         <is>
           <t>INEFFECTIVE</t>
         </is>
@@ -7447,12 +8262,12 @@
       <c r="G6" s="266" t="n"/>
     </row>
     <row r="7">
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="345" t="inlineStr">
         <is>
           <t>PUR</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="345" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -7460,7 +8275,7 @@
       <c r="F7" s="266" t="n"/>
     </row>
     <row r="8">
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="345" t="inlineStr">
         <is>
           <t>WHS</t>
         </is>
@@ -7468,7 +8283,7 @@
       <c r="F8" s="266" t="n"/>
     </row>
     <row r="9">
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="345" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
@@ -7476,7 +8291,7 @@
       <c r="F9" s="266" t="n"/>
     </row>
     <row r="10">
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="345" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
@@ -7484,7 +8299,7 @@
       <c r="F10" s="266" t="n"/>
     </row>
     <row r="11">
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="345" t="inlineStr">
         <is>
           <t>MGT</t>
         </is>
@@ -7547,741 +8362,747 @@
     <col width="2.33" customWidth="1" style="329" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="329">
-      <c r="A1" s="386" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" s="329">
+      <c r="A1" s="497" t="inlineStr">
         <is>
           <t>Actions / Containment</t>
         </is>
       </c>
-      <c r="B1" s="409" t="n"/>
-      <c r="C1" s="409" t="n"/>
-      <c r="D1" s="409" t="n"/>
-      <c r="E1" s="409" t="n"/>
-      <c r="F1" s="409" t="n"/>
-      <c r="G1" s="410" t="n"/>
-      <c r="H1" s="345" t="n"/>
-      <c r="I1" s="345" t="n"/>
-      <c r="J1" s="345" t="n"/>
-      <c r="K1" s="345" t="n"/>
-      <c r="L1" s="345" t="n"/>
-      <c r="M1" s="345" t="n"/>
-      <c r="N1" s="345" t="n"/>
-      <c r="O1" s="345" t="n"/>
-      <c r="P1" s="345" t="n"/>
-      <c r="Q1" s="345" t="n"/>
-      <c r="R1" s="345" t="n"/>
-      <c r="S1" s="345" t="n"/>
-      <c r="T1" s="345" t="n"/>
-      <c r="U1" s="345" t="n"/>
-      <c r="V1" s="345" t="n"/>
-      <c r="W1" s="345" t="n"/>
-      <c r="X1" s="345" t="n"/>
-      <c r="Y1" s="345" t="n"/>
-      <c r="Z1" s="345" t="n"/>
-      <c r="AA1" s="345" t="n"/>
-      <c r="AB1" s="345" t="n"/>
-      <c r="AC1" s="345" t="n"/>
-      <c r="AD1" s="345" t="n"/>
-      <c r="AE1" s="345" t="n"/>
-      <c r="AF1" s="345" t="n"/>
-      <c r="AG1" s="345" t="n"/>
-      <c r="AH1" s="345" t="n"/>
-      <c r="AI1" s="345" t="n"/>
-      <c r="AJ1" s="345" t="n"/>
-      <c r="AK1" s="345" t="n"/>
-      <c r="AL1" s="345" t="n"/>
-      <c r="AM1" s="345" t="n"/>
-      <c r="AN1" s="345" t="n"/>
+      <c r="B1" s="415" t="n"/>
+      <c r="C1" s="415" t="n"/>
+      <c r="D1" s="415" t="n"/>
+      <c r="E1" s="415" t="n"/>
+      <c r="F1" s="415" t="n"/>
+      <c r="G1" s="415" t="n"/>
+      <c r="H1" s="498" t="n"/>
+      <c r="I1" s="417" t="n"/>
+      <c r="J1" s="418" t="n"/>
+      <c r="K1" s="418" t="n"/>
+      <c r="L1" s="418" t="n"/>
+      <c r="M1" s="418" t="n"/>
+      <c r="N1" s="418" t="n"/>
+      <c r="O1" s="418" t="n"/>
+      <c r="P1" s="418" t="n"/>
+      <c r="Q1" s="418" t="n"/>
+      <c r="R1" s="418" t="n"/>
+      <c r="S1" s="418" t="n"/>
+      <c r="T1" s="418" t="n"/>
+      <c r="U1" s="418" t="n"/>
+      <c r="V1" s="418" t="n"/>
+      <c r="W1" s="418" t="n"/>
+      <c r="X1" s="418" t="n"/>
+      <c r="Y1" s="418" t="n"/>
+      <c r="Z1" s="418" t="n"/>
+      <c r="AA1" s="418" t="n"/>
+      <c r="AB1" s="418" t="n"/>
+      <c r="AC1" s="418" t="n"/>
+      <c r="AD1" s="419" t="n"/>
+      <c r="AE1" s="420" t="n"/>
+      <c r="AF1" s="421" t="n"/>
+      <c r="AG1" s="421" t="n"/>
+      <c r="AH1" s="422" t="n"/>
+      <c r="AI1" s="423" t="n"/>
+      <c r="AJ1" s="424" t="n"/>
+      <c r="AK1" s="424" t="n"/>
+      <c r="AL1" s="424" t="n"/>
+      <c r="AM1" s="424" t="n"/>
+      <c r="AN1" s="425" t="n"/>
     </row>
-    <row r="2" ht="18" customHeight="1" s="329">
-      <c r="A2" s="335" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="329">
+      <c r="A2" s="499" t="inlineStr">
         <is>
           <t>Incoming verification event record for outsourced process returns and discrete disposition decisions.</t>
         </is>
       </c>
-      <c r="H2" s="345" t="n"/>
-      <c r="I2" s="345" t="n"/>
-      <c r="J2" s="345" t="n"/>
-      <c r="K2" s="345" t="n"/>
-      <c r="L2" s="345" t="n"/>
-      <c r="M2" s="345" t="n"/>
-      <c r="N2" s="345" t="n"/>
-      <c r="O2" s="345" t="n"/>
-      <c r="P2" s="345" t="n"/>
-      <c r="Q2" s="345" t="n"/>
-      <c r="R2" s="345" t="n"/>
-      <c r="S2" s="345" t="n"/>
-      <c r="T2" s="345" t="n"/>
-      <c r="U2" s="345" t="n"/>
-      <c r="V2" s="345" t="n"/>
-      <c r="W2" s="345" t="n"/>
-      <c r="X2" s="345" t="n"/>
-      <c r="Y2" s="345" t="n"/>
-      <c r="Z2" s="345" t="n"/>
-      <c r="AA2" s="345" t="n"/>
-      <c r="AB2" s="345" t="n"/>
-      <c r="AC2" s="345" t="n"/>
-      <c r="AD2" s="345" t="n"/>
-      <c r="AE2" s="345" t="n"/>
-      <c r="AF2" s="345" t="n"/>
-      <c r="AG2" s="345" t="n"/>
-      <c r="AH2" s="345" t="n"/>
-      <c r="AI2" s="345" t="n"/>
-      <c r="AJ2" s="345" t="n"/>
-      <c r="AK2" s="345" t="n"/>
-      <c r="AL2" s="345" t="n"/>
-      <c r="AM2" s="345" t="n"/>
-      <c r="AN2" s="345" t="n"/>
+      <c r="B2" s="25" t="n"/>
+      <c r="C2" s="25" t="n"/>
+      <c r="D2" s="25" t="n"/>
+      <c r="E2" s="25" t="n"/>
+      <c r="F2" s="25" t="n"/>
+      <c r="G2" s="25" t="n"/>
+      <c r="H2" s="500" t="n"/>
+      <c r="I2" s="428" t="n"/>
+      <c r="J2" s="429" t="n"/>
+      <c r="K2" s="429" t="n"/>
+      <c r="L2" s="429" t="n"/>
+      <c r="M2" s="429" t="n"/>
+      <c r="N2" s="429" t="n"/>
+      <c r="O2" s="429" t="n"/>
+      <c r="P2" s="429" t="n"/>
+      <c r="Q2" s="429" t="n"/>
+      <c r="R2" s="429" t="n"/>
+      <c r="S2" s="429" t="n"/>
+      <c r="T2" s="429" t="n"/>
+      <c r="U2" s="429" t="n"/>
+      <c r="V2" s="429" t="n"/>
+      <c r="W2" s="429" t="n"/>
+      <c r="X2" s="429" t="n"/>
+      <c r="Y2" s="429" t="n"/>
+      <c r="Z2" s="429" t="n"/>
+      <c r="AA2" s="429" t="n"/>
+      <c r="AB2" s="429" t="n"/>
+      <c r="AC2" s="429" t="n"/>
+      <c r="AD2" s="430" t="n"/>
+      <c r="AE2" s="431" t="n"/>
+      <c r="AF2" s="432" t="n"/>
+      <c r="AG2" s="432" t="n"/>
+      <c r="AH2" s="433" t="n"/>
+      <c r="AI2" s="434" t="n"/>
+      <c r="AJ2" s="435" t="n"/>
+      <c r="AK2" s="435" t="n"/>
+      <c r="AL2" s="435" t="n"/>
+      <c r="AM2" s="435" t="n"/>
+      <c r="AN2" s="436" t="n"/>
     </row>
-    <row r="3" ht="18" customHeight="1" s="329">
-      <c r="A3" s="345" t="n"/>
-      <c r="B3" s="345" t="n"/>
-      <c r="C3" s="345" t="n"/>
-      <c r="D3" s="345" t="n"/>
-      <c r="E3" s="345" t="n"/>
-      <c r="F3" s="345" t="n"/>
-      <c r="G3" s="345" t="n"/>
-      <c r="H3" s="345" t="n"/>
-      <c r="I3" s="345" t="n"/>
-      <c r="J3" s="345" t="n"/>
-      <c r="K3" s="345" t="n"/>
-      <c r="L3" s="345" t="n"/>
-      <c r="M3" s="345" t="n"/>
-      <c r="N3" s="345" t="n"/>
-      <c r="O3" s="345" t="n"/>
-      <c r="P3" s="345" t="n"/>
-      <c r="Q3" s="345" t="n"/>
-      <c r="R3" s="345" t="n"/>
-      <c r="S3" s="345" t="n"/>
-      <c r="T3" s="345" t="n"/>
-      <c r="U3" s="345" t="n"/>
-      <c r="V3" s="345" t="n"/>
-      <c r="W3" s="345" t="n"/>
-      <c r="X3" s="345" t="n"/>
-      <c r="Y3" s="345" t="n"/>
-      <c r="Z3" s="345" t="n"/>
-      <c r="AA3" s="345" t="n"/>
-      <c r="AB3" s="345" t="n"/>
-      <c r="AC3" s="345" t="n"/>
-      <c r="AD3" s="345" t="n"/>
-      <c r="AE3" s="345" t="n"/>
-      <c r="AF3" s="345" t="n"/>
-      <c r="AG3" s="345" t="n"/>
-      <c r="AH3" s="345" t="n"/>
-      <c r="AI3" s="345" t="n"/>
-      <c r="AJ3" s="345" t="n"/>
-      <c r="AK3" s="345" t="n"/>
-      <c r="AL3" s="345" t="n"/>
-      <c r="AM3" s="345" t="n"/>
-      <c r="AN3" s="345" t="n"/>
+    <row r="3" ht="15" customHeight="1" s="329">
+      <c r="A3" s="501" t="n"/>
+      <c r="B3" s="502" t="n"/>
+      <c r="C3" s="502" t="n"/>
+      <c r="D3" s="502" t="n"/>
+      <c r="E3" s="502" t="n"/>
+      <c r="F3" s="502" t="n"/>
+      <c r="G3" s="502" t="n"/>
+      <c r="H3" s="500" t="n"/>
+      <c r="I3" s="428" t="n"/>
+      <c r="J3" s="429" t="n"/>
+      <c r="K3" s="429" t="n"/>
+      <c r="L3" s="429" t="n"/>
+      <c r="M3" s="429" t="n"/>
+      <c r="N3" s="429" t="n"/>
+      <c r="O3" s="429" t="n"/>
+      <c r="P3" s="429" t="n"/>
+      <c r="Q3" s="429" t="n"/>
+      <c r="R3" s="429" t="n"/>
+      <c r="S3" s="429" t="n"/>
+      <c r="T3" s="429" t="n"/>
+      <c r="U3" s="429" t="n"/>
+      <c r="V3" s="429" t="n"/>
+      <c r="W3" s="429" t="n"/>
+      <c r="X3" s="429" t="n"/>
+      <c r="Y3" s="429" t="n"/>
+      <c r="Z3" s="429" t="n"/>
+      <c r="AA3" s="429" t="n"/>
+      <c r="AB3" s="429" t="n"/>
+      <c r="AC3" s="429" t="n"/>
+      <c r="AD3" s="430" t="n"/>
+      <c r="AE3" s="431" t="n"/>
+      <c r="AF3" s="432" t="n"/>
+      <c r="AG3" s="432" t="n"/>
+      <c r="AH3" s="433" t="n"/>
+      <c r="AI3" s="434" t="n"/>
+      <c r="AJ3" s="435" t="n"/>
+      <c r="AK3" s="435" t="n"/>
+      <c r="AL3" s="435" t="n"/>
+      <c r="AM3" s="435" t="n"/>
+      <c r="AN3" s="436" t="n"/>
     </row>
-    <row r="4" ht="20" customHeight="1" s="329">
-      <c r="A4" s="387" t="inlineStr">
+    <row r="4" ht="15" customHeight="1" s="329">
+      <c r="A4" s="503" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="387" t="inlineStr">
+      <c r="B4" s="504" t="inlineStr">
         <is>
           <t>Issue / Finding</t>
         </is>
       </c>
-      <c r="C4" s="387" t="inlineStr">
+      <c r="C4" s="504" t="inlineStr">
         <is>
           <t>Required Action</t>
         </is>
       </c>
-      <c r="D4" s="387" t="inlineStr">
+      <c r="D4" s="504" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E4" s="387" t="inlineStr">
+      <c r="E4" s="504" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="F4" s="387" t="inlineStr">
+      <c r="F4" s="504" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G4" s="387" t="inlineStr">
+      <c r="G4" s="504" t="inlineStr">
         <is>
           <t>Evidence Ref</t>
         </is>
       </c>
-      <c r="H4" s="387" t="inlineStr">
+      <c r="H4" s="505" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="I4" s="345" t="n"/>
-      <c r="J4" s="345" t="n"/>
-      <c r="K4" s="345" t="n"/>
-      <c r="L4" s="345" t="n"/>
-      <c r="M4" s="345" t="n"/>
-      <c r="N4" s="345" t="n"/>
-      <c r="O4" s="345" t="n"/>
-      <c r="P4" s="345" t="n"/>
-      <c r="Q4" s="345" t="n"/>
-      <c r="R4" s="345" t="n"/>
-      <c r="S4" s="345" t="n"/>
-      <c r="T4" s="345" t="n"/>
-      <c r="U4" s="345" t="n"/>
-      <c r="V4" s="345" t="n"/>
-      <c r="W4" s="345" t="n"/>
-      <c r="X4" s="345" t="n"/>
-      <c r="Y4" s="345" t="n"/>
-      <c r="Z4" s="345" t="n"/>
-      <c r="AA4" s="345" t="n"/>
-      <c r="AB4" s="345" t="n"/>
-      <c r="AC4" s="345" t="n"/>
-      <c r="AD4" s="345" t="n"/>
-      <c r="AE4" s="345" t="n"/>
-      <c r="AF4" s="345" t="n"/>
-      <c r="AG4" s="345" t="n"/>
-      <c r="AH4" s="345" t="n"/>
-      <c r="AI4" s="345" t="n"/>
-      <c r="AJ4" s="345" t="n"/>
-      <c r="AK4" s="345" t="n"/>
-      <c r="AL4" s="345" t="n"/>
-      <c r="AM4" s="345" t="n"/>
-      <c r="AN4" s="345" t="n"/>
+      <c r="I4" s="437" t="n"/>
+      <c r="J4" s="438" t="n"/>
+      <c r="K4" s="438" t="n"/>
+      <c r="L4" s="438" t="n"/>
+      <c r="M4" s="438" t="n"/>
+      <c r="N4" s="438" t="n"/>
+      <c r="O4" s="438" t="n"/>
+      <c r="P4" s="438" t="n"/>
+      <c r="Q4" s="438" t="n"/>
+      <c r="R4" s="438" t="n"/>
+      <c r="S4" s="438" t="n"/>
+      <c r="T4" s="438" t="n"/>
+      <c r="U4" s="438" t="n"/>
+      <c r="V4" s="438" t="n"/>
+      <c r="W4" s="438" t="n"/>
+      <c r="X4" s="438" t="n"/>
+      <c r="Y4" s="438" t="n"/>
+      <c r="Z4" s="438" t="n"/>
+      <c r="AA4" s="438" t="n"/>
+      <c r="AB4" s="438" t="n"/>
+      <c r="AC4" s="438" t="n"/>
+      <c r="AD4" s="439" t="n"/>
+      <c r="AE4" s="431" t="n"/>
+      <c r="AF4" s="432" t="n"/>
+      <c r="AG4" s="432" t="n"/>
+      <c r="AH4" s="433" t="n"/>
+      <c r="AI4" s="434" t="n"/>
+      <c r="AJ4" s="435" t="n"/>
+      <c r="AK4" s="435" t="n"/>
+      <c r="AL4" s="435" t="n"/>
+      <c r="AM4" s="435" t="n"/>
+      <c r="AN4" s="436" t="n"/>
     </row>
-    <row r="5" ht="20" customHeight="1" s="329">
-      <c r="A5" s="388">
+    <row r="5" ht="15" customHeight="1" s="329">
+      <c r="A5" s="506">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B5" s="389" t="n"/>
-      <c r="C5" s="389" t="n"/>
-      <c r="D5" s="389" t="n"/>
-      <c r="E5" s="389" t="n"/>
-      <c r="F5" s="389" t="n"/>
-      <c r="G5" s="389" t="n"/>
-      <c r="H5" s="389" t="n"/>
-      <c r="I5" s="345" t="n"/>
-      <c r="J5" s="345" t="n"/>
-      <c r="K5" s="345" t="n"/>
-      <c r="L5" s="345" t="n"/>
-      <c r="M5" s="345" t="n"/>
-      <c r="N5" s="345" t="n"/>
-      <c r="O5" s="345" t="n"/>
-      <c r="P5" s="345" t="n"/>
-      <c r="Q5" s="345" t="n"/>
-      <c r="R5" s="345" t="n"/>
-      <c r="S5" s="345" t="n"/>
-      <c r="T5" s="345" t="n"/>
-      <c r="U5" s="345" t="n"/>
-      <c r="V5" s="345" t="n"/>
-      <c r="W5" s="345" t="n"/>
-      <c r="X5" s="345" t="n"/>
-      <c r="Y5" s="345" t="n"/>
-      <c r="Z5" s="345" t="n"/>
-      <c r="AA5" s="345" t="n"/>
-      <c r="AB5" s="345" t="n"/>
-      <c r="AC5" s="345" t="n"/>
-      <c r="AD5" s="345" t="n"/>
-      <c r="AE5" s="345" t="n"/>
-      <c r="AF5" s="345" t="n"/>
-      <c r="AG5" s="345" t="n"/>
-      <c r="AH5" s="345" t="n"/>
-      <c r="AI5" s="345" t="n"/>
-      <c r="AJ5" s="345" t="n"/>
-      <c r="AK5" s="345" t="n"/>
-      <c r="AL5" s="345" t="n"/>
-      <c r="AM5" s="345" t="n"/>
-      <c r="AN5" s="345" t="n"/>
+      <c r="B5" s="507" t="n"/>
+      <c r="C5" s="507" t="n"/>
+      <c r="D5" s="507" t="n"/>
+      <c r="E5" s="507" t="n"/>
+      <c r="F5" s="507" t="n"/>
+      <c r="G5" s="507" t="n"/>
+      <c r="H5" s="508" t="n"/>
+      <c r="I5" s="443" t="n"/>
+      <c r="J5" s="444" t="n"/>
+      <c r="K5" s="444" t="n"/>
+      <c r="L5" s="444" t="n"/>
+      <c r="M5" s="444" t="n"/>
+      <c r="N5" s="444" t="n"/>
+      <c r="O5" s="444" t="n"/>
+      <c r="P5" s="444" t="n"/>
+      <c r="Q5" s="444" t="n"/>
+      <c r="R5" s="444" t="n"/>
+      <c r="S5" s="444" t="n"/>
+      <c r="T5" s="444" t="n"/>
+      <c r="U5" s="444" t="n"/>
+      <c r="V5" s="444" t="n"/>
+      <c r="W5" s="444" t="n"/>
+      <c r="X5" s="444" t="n"/>
+      <c r="Y5" s="444" t="n"/>
+      <c r="Z5" s="444" t="n"/>
+      <c r="AA5" s="444" t="n"/>
+      <c r="AB5" s="444" t="n"/>
+      <c r="AC5" s="444" t="n"/>
+      <c r="AD5" s="445" t="n"/>
+      <c r="AE5" s="446" t="n"/>
+      <c r="AF5" s="447" t="n"/>
+      <c r="AG5" s="447" t="n"/>
+      <c r="AH5" s="448" t="n"/>
+      <c r="AI5" s="449" t="n"/>
+      <c r="AJ5" s="450" t="n"/>
+      <c r="AK5" s="450" t="n"/>
+      <c r="AL5" s="450" t="n"/>
+      <c r="AM5" s="450" t="n"/>
+      <c r="AN5" s="451" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1" s="329">
-      <c r="A6" s="388">
+      <c r="A6" s="509">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B6" s="389" t="n"/>
-      <c r="C6" s="389" t="n"/>
-      <c r="D6" s="389" t="n"/>
-      <c r="E6" s="389" t="n"/>
-      <c r="F6" s="389" t="n"/>
-      <c r="G6" s="389" t="n"/>
-      <c r="H6" s="389" t="n"/>
-      <c r="I6" s="345" t="n"/>
-      <c r="J6" s="345" t="n"/>
-      <c r="K6" s="345" t="n"/>
-      <c r="L6" s="345" t="n"/>
-      <c r="M6" s="345" t="n"/>
-      <c r="N6" s="345" t="n"/>
-      <c r="O6" s="345" t="n"/>
-      <c r="P6" s="345" t="n"/>
-      <c r="Q6" s="345" t="n"/>
-      <c r="R6" s="345" t="n"/>
-      <c r="S6" s="345" t="n"/>
-      <c r="T6" s="345" t="n"/>
-      <c r="U6" s="345" t="n"/>
-      <c r="V6" s="345" t="n"/>
-      <c r="W6" s="345" t="n"/>
-      <c r="X6" s="345" t="n"/>
-      <c r="Y6" s="345" t="n"/>
-      <c r="Z6" s="345" t="n"/>
-      <c r="AA6" s="345" t="n"/>
-      <c r="AB6" s="345" t="n"/>
-      <c r="AC6" s="345" t="n"/>
-      <c r="AD6" s="345" t="n"/>
-      <c r="AE6" s="345" t="n"/>
-      <c r="AF6" s="345" t="n"/>
-      <c r="AG6" s="345" t="n"/>
-      <c r="AH6" s="345" t="n"/>
-      <c r="AI6" s="345" t="n"/>
-      <c r="AJ6" s="345" t="n"/>
-      <c r="AK6" s="345" t="n"/>
-      <c r="AL6" s="345" t="n"/>
-      <c r="AM6" s="345" t="n"/>
-      <c r="AN6" s="345" t="n"/>
+      <c r="B6" s="510" t="n"/>
+      <c r="C6" s="511" t="n"/>
+      <c r="D6" s="511" t="n"/>
+      <c r="E6" s="511" t="n"/>
+      <c r="F6" s="511" t="n"/>
+      <c r="G6" s="511" t="n"/>
+      <c r="H6" s="511" t="n"/>
+      <c r="I6" s="457" t="n"/>
+      <c r="J6" s="457" t="n"/>
+      <c r="K6" s="457" t="n"/>
+      <c r="L6" s="457" t="n"/>
+      <c r="M6" s="457" t="n"/>
+      <c r="N6" s="457" t="n"/>
+      <c r="O6" s="457" t="n"/>
+      <c r="P6" s="457" t="n"/>
+      <c r="Q6" s="457" t="n"/>
+      <c r="R6" s="457" t="n"/>
+      <c r="S6" s="457" t="n"/>
+      <c r="T6" s="457" t="n"/>
+      <c r="U6" s="457" t="n"/>
+      <c r="V6" s="457" t="n"/>
+      <c r="W6" s="457" t="n"/>
+      <c r="X6" s="457" t="n"/>
+      <c r="Y6" s="457" t="n"/>
+      <c r="Z6" s="457" t="n"/>
+      <c r="AA6" s="457" t="n"/>
+      <c r="AB6" s="457" t="n"/>
+      <c r="AC6" s="457" t="n"/>
+      <c r="AD6" s="457" t="n"/>
+      <c r="AE6" s="457" t="n"/>
+      <c r="AF6" s="457" t="n"/>
+      <c r="AG6" s="457" t="n"/>
+      <c r="AH6" s="457" t="n"/>
+      <c r="AI6" s="457" t="n"/>
+      <c r="AJ6" s="457" t="n"/>
+      <c r="AK6" s="457" t="n"/>
+      <c r="AL6" s="457" t="n"/>
+      <c r="AM6" s="457" t="n"/>
+      <c r="AN6" s="460" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1" s="329">
-      <c r="A7" s="388">
+      <c r="A7" s="512">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B7" s="389" t="n"/>
-      <c r="C7" s="389" t="n"/>
-      <c r="D7" s="389" t="n"/>
-      <c r="E7" s="389" t="n"/>
-      <c r="F7" s="389" t="n"/>
-      <c r="G7" s="389" t="n"/>
-      <c r="H7" s="389" t="n"/>
-      <c r="I7" s="345" t="n"/>
-      <c r="J7" s="345" t="n"/>
-      <c r="K7" s="345" t="n"/>
-      <c r="L7" s="345" t="n"/>
-      <c r="M7" s="345" t="n"/>
-      <c r="N7" s="345" t="n"/>
-      <c r="O7" s="345" t="n"/>
-      <c r="P7" s="345" t="n"/>
-      <c r="Q7" s="345" t="n"/>
-      <c r="R7" s="345" t="n"/>
-      <c r="S7" s="345" t="n"/>
-      <c r="T7" s="345" t="n"/>
-      <c r="U7" s="345" t="n"/>
-      <c r="V7" s="345" t="n"/>
-      <c r="W7" s="345" t="n"/>
-      <c r="X7" s="345" t="n"/>
-      <c r="Y7" s="345" t="n"/>
-      <c r="Z7" s="345" t="n"/>
-      <c r="AA7" s="345" t="n"/>
-      <c r="AB7" s="345" t="n"/>
-      <c r="AC7" s="345" t="n"/>
-      <c r="AD7" s="345" t="n"/>
-      <c r="AE7" s="345" t="n"/>
-      <c r="AF7" s="345" t="n"/>
-      <c r="AG7" s="345" t="n"/>
-      <c r="AH7" s="345" t="n"/>
-      <c r="AI7" s="345" t="n"/>
-      <c r="AJ7" s="345" t="n"/>
-      <c r="AK7" s="345" t="n"/>
-      <c r="AL7" s="345" t="n"/>
-      <c r="AM7" s="345" t="n"/>
-      <c r="AN7" s="345" t="n"/>
+      <c r="B7" s="513" t="n"/>
+      <c r="C7" s="514" t="n"/>
+      <c r="D7" s="514" t="n"/>
+      <c r="E7" s="514" t="n"/>
+      <c r="F7" s="514" t="n"/>
+      <c r="G7" s="514" t="n"/>
+      <c r="H7" s="514" t="n"/>
+      <c r="I7" s="341" t="n"/>
+      <c r="J7" s="341" t="n"/>
+      <c r="K7" s="341" t="n"/>
+      <c r="L7" s="341" t="n"/>
+      <c r="M7" s="341" t="n"/>
+      <c r="N7" s="341" t="n"/>
+      <c r="O7" s="341" t="n"/>
+      <c r="P7" s="341" t="n"/>
+      <c r="Q7" s="341" t="n"/>
+      <c r="R7" s="341" t="n"/>
+      <c r="S7" s="341" t="n"/>
+      <c r="T7" s="341" t="n"/>
+      <c r="U7" s="341" t="n"/>
+      <c r="V7" s="341" t="n"/>
+      <c r="W7" s="341" t="n"/>
+      <c r="X7" s="341" t="n"/>
+      <c r="Y7" s="341" t="n"/>
+      <c r="Z7" s="341" t="n"/>
+      <c r="AA7" s="341" t="n"/>
+      <c r="AB7" s="341" t="n"/>
+      <c r="AC7" s="341" t="n"/>
+      <c r="AD7" s="341" t="n"/>
+      <c r="AE7" s="341" t="n"/>
+      <c r="AF7" s="341" t="n"/>
+      <c r="AG7" s="341" t="n"/>
+      <c r="AH7" s="341" t="n"/>
+      <c r="AI7" s="341" t="n"/>
+      <c r="AJ7" s="341" t="n"/>
+      <c r="AK7" s="341" t="n"/>
+      <c r="AL7" s="341" t="n"/>
+      <c r="AM7" s="341" t="n"/>
+      <c r="AN7" s="464" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1" s="329">
-      <c r="A8" s="352">
+      <c r="A8" s="461">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B8" s="390" t="n"/>
-      <c r="C8" s="390" t="n"/>
-      <c r="D8" s="390" t="n"/>
-      <c r="E8" s="390" t="n"/>
-      <c r="F8" s="390" t="n"/>
-      <c r="G8" s="390" t="n"/>
-      <c r="H8" s="390" t="n"/>
-      <c r="I8" s="381" t="n"/>
-      <c r="J8" s="381" t="n"/>
-      <c r="K8" s="381" t="n"/>
-      <c r="L8" s="381" t="n"/>
-      <c r="M8" s="381" t="n"/>
-      <c r="N8" s="381" t="n"/>
-      <c r="O8" s="381" t="n"/>
-      <c r="P8" s="381" t="n"/>
-      <c r="Q8" s="381" t="n"/>
-      <c r="R8" s="381" t="n"/>
-      <c r="S8" s="381" t="n"/>
-      <c r="T8" s="381" t="n"/>
-      <c r="U8" s="381" t="n"/>
-      <c r="V8" s="381" t="n"/>
-      <c r="W8" s="381" t="n"/>
-      <c r="X8" s="381" t="n"/>
-      <c r="Y8" s="381" t="n"/>
-      <c r="Z8" s="381" t="n"/>
-      <c r="AA8" s="381" t="n"/>
-      <c r="AB8" s="381" t="n"/>
-      <c r="AC8" s="381" t="n"/>
-      <c r="AD8" s="381" t="n"/>
-      <c r="AE8" s="381" t="n"/>
-      <c r="AF8" s="381" t="n"/>
-      <c r="AG8" s="381" t="n"/>
-      <c r="AH8" s="381" t="n"/>
-      <c r="AI8" s="381" t="n"/>
-      <c r="AJ8" s="381" t="n"/>
-      <c r="AK8" s="381" t="n"/>
-      <c r="AL8" s="381" t="n"/>
-      <c r="AM8" s="381" t="n"/>
-      <c r="AN8" s="381" t="n"/>
+      <c r="B8" s="462" t="n"/>
+      <c r="C8" s="515" t="n"/>
+      <c r="D8" s="515" t="n"/>
+      <c r="E8" s="515" t="n"/>
+      <c r="F8" s="515" t="n"/>
+      <c r="G8" s="515" t="n"/>
+      <c r="H8" s="515" t="n"/>
+      <c r="I8" s="353" t="n"/>
+      <c r="J8" s="353" t="n"/>
+      <c r="K8" s="353" t="n"/>
+      <c r="L8" s="353" t="n"/>
+      <c r="M8" s="353" t="n"/>
+      <c r="N8" s="353" t="n"/>
+      <c r="O8" s="353" t="n"/>
+      <c r="P8" s="353" t="n"/>
+      <c r="Q8" s="353" t="n"/>
+      <c r="R8" s="353" t="n"/>
+      <c r="S8" s="353" t="n"/>
+      <c r="T8" s="353" t="n"/>
+      <c r="U8" s="353" t="n"/>
+      <c r="V8" s="353" t="n"/>
+      <c r="W8" s="353" t="n"/>
+      <c r="X8" s="353" t="n"/>
+      <c r="Y8" s="353" t="n"/>
+      <c r="Z8" s="353" t="n"/>
+      <c r="AA8" s="353" t="n"/>
+      <c r="AB8" s="353" t="n"/>
+      <c r="AC8" s="353" t="n"/>
+      <c r="AD8" s="353" t="n"/>
+      <c r="AE8" s="353" t="n"/>
+      <c r="AF8" s="353" t="n"/>
+      <c r="AG8" s="353" t="n"/>
+      <c r="AH8" s="353" t="n"/>
+      <c r="AI8" s="353" t="n"/>
+      <c r="AJ8" s="353" t="n"/>
+      <c r="AK8" s="353" t="n"/>
+      <c r="AL8" s="353" t="n"/>
+      <c r="AM8" s="353" t="n"/>
+      <c r="AN8" s="516" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1" s="329">
-      <c r="A9" s="352">
+      <c r="A9" s="461">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B9" s="390" t="n"/>
-      <c r="C9" s="390" t="n"/>
-      <c r="D9" s="390" t="n"/>
-      <c r="E9" s="390" t="n"/>
-      <c r="F9" s="390" t="n"/>
-      <c r="G9" s="390" t="n"/>
-      <c r="H9" s="390" t="n"/>
-      <c r="I9" s="381" t="n"/>
-      <c r="J9" s="381" t="n"/>
-      <c r="K9" s="381" t="n"/>
-      <c r="L9" s="381" t="n"/>
-      <c r="M9" s="381" t="n"/>
-      <c r="N9" s="381" t="n"/>
-      <c r="O9" s="381" t="n"/>
-      <c r="P9" s="381" t="n"/>
-      <c r="Q9" s="381" t="n"/>
-      <c r="R9" s="381" t="n"/>
-      <c r="S9" s="381" t="n"/>
-      <c r="T9" s="381" t="n"/>
-      <c r="U9" s="381" t="n"/>
-      <c r="V9" s="381" t="n"/>
-      <c r="W9" s="381" t="n"/>
-      <c r="X9" s="381" t="n"/>
-      <c r="Y9" s="381" t="n"/>
-      <c r="Z9" s="381" t="n"/>
-      <c r="AA9" s="381" t="n"/>
-      <c r="AB9" s="381" t="n"/>
-      <c r="AC9" s="381" t="n"/>
-      <c r="AD9" s="381" t="n"/>
-      <c r="AE9" s="381" t="n"/>
-      <c r="AF9" s="381" t="n"/>
-      <c r="AG9" s="381" t="n"/>
-      <c r="AH9" s="381" t="n"/>
-      <c r="AI9" s="381" t="n"/>
-      <c r="AJ9" s="381" t="n"/>
-      <c r="AK9" s="381" t="n"/>
-      <c r="AL9" s="381" t="n"/>
-      <c r="AM9" s="381" t="n"/>
-      <c r="AN9" s="381" t="n"/>
+      <c r="B9" s="462" t="n"/>
+      <c r="C9" s="515" t="n"/>
+      <c r="D9" s="515" t="n"/>
+      <c r="E9" s="515" t="n"/>
+      <c r="F9" s="515" t="n"/>
+      <c r="G9" s="515" t="n"/>
+      <c r="H9" s="515" t="n"/>
+      <c r="I9" s="353" t="n"/>
+      <c r="J9" s="353" t="n"/>
+      <c r="K9" s="353" t="n"/>
+      <c r="L9" s="353" t="n"/>
+      <c r="M9" s="353" t="n"/>
+      <c r="N9" s="353" t="n"/>
+      <c r="O9" s="353" t="n"/>
+      <c r="P9" s="353" t="n"/>
+      <c r="Q9" s="353" t="n"/>
+      <c r="R9" s="353" t="n"/>
+      <c r="S9" s="353" t="n"/>
+      <c r="T9" s="353" t="n"/>
+      <c r="U9" s="353" t="n"/>
+      <c r="V9" s="353" t="n"/>
+      <c r="W9" s="353" t="n"/>
+      <c r="X9" s="353" t="n"/>
+      <c r="Y9" s="353" t="n"/>
+      <c r="Z9" s="353" t="n"/>
+      <c r="AA9" s="353" t="n"/>
+      <c r="AB9" s="353" t="n"/>
+      <c r="AC9" s="353" t="n"/>
+      <c r="AD9" s="353" t="n"/>
+      <c r="AE9" s="353" t="n"/>
+      <c r="AF9" s="353" t="n"/>
+      <c r="AG9" s="353" t="n"/>
+      <c r="AH9" s="353" t="n"/>
+      <c r="AI9" s="353" t="n"/>
+      <c r="AJ9" s="353" t="n"/>
+      <c r="AK9" s="353" t="n"/>
+      <c r="AL9" s="353" t="n"/>
+      <c r="AM9" s="353" t="n"/>
+      <c r="AN9" s="516" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1" s="329">
-      <c r="A10" s="352">
+      <c r="A10" s="461">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B10" s="390" t="n"/>
-      <c r="C10" s="390" t="n"/>
-      <c r="D10" s="390" t="n"/>
-      <c r="E10" s="390" t="n"/>
-      <c r="F10" s="390" t="n"/>
-      <c r="G10" s="390" t="n"/>
-      <c r="H10" s="390" t="n"/>
-      <c r="I10" s="381" t="n"/>
-      <c r="J10" s="381" t="n"/>
-      <c r="K10" s="381" t="n"/>
-      <c r="L10" s="381" t="n"/>
-      <c r="M10" s="381" t="n"/>
-      <c r="N10" s="381" t="n"/>
-      <c r="O10" s="381" t="n"/>
-      <c r="P10" s="381" t="n"/>
-      <c r="Q10" s="381" t="n"/>
-      <c r="R10" s="381" t="n"/>
-      <c r="S10" s="381" t="n"/>
-      <c r="T10" s="381" t="n"/>
-      <c r="U10" s="381" t="n"/>
-      <c r="V10" s="381" t="n"/>
-      <c r="W10" s="381" t="n"/>
-      <c r="X10" s="381" t="n"/>
-      <c r="Y10" s="381" t="n"/>
-      <c r="Z10" s="381" t="n"/>
-      <c r="AA10" s="381" t="n"/>
-      <c r="AB10" s="381" t="n"/>
-      <c r="AC10" s="381" t="n"/>
-      <c r="AD10" s="381" t="n"/>
-      <c r="AE10" s="381" t="n"/>
-      <c r="AF10" s="381" t="n"/>
-      <c r="AG10" s="381" t="n"/>
-      <c r="AH10" s="381" t="n"/>
-      <c r="AI10" s="381" t="n"/>
-      <c r="AJ10" s="381" t="n"/>
-      <c r="AK10" s="381" t="n"/>
-      <c r="AL10" s="381" t="n"/>
-      <c r="AM10" s="381" t="n"/>
-      <c r="AN10" s="381" t="n"/>
+      <c r="B10" s="462" t="n"/>
+      <c r="C10" s="515" t="n"/>
+      <c r="D10" s="515" t="n"/>
+      <c r="E10" s="515" t="n"/>
+      <c r="F10" s="515" t="n"/>
+      <c r="G10" s="515" t="n"/>
+      <c r="H10" s="515" t="n"/>
+      <c r="I10" s="353" t="n"/>
+      <c r="J10" s="353" t="n"/>
+      <c r="K10" s="353" t="n"/>
+      <c r="L10" s="353" t="n"/>
+      <c r="M10" s="353" t="n"/>
+      <c r="N10" s="353" t="n"/>
+      <c r="O10" s="353" t="n"/>
+      <c r="P10" s="353" t="n"/>
+      <c r="Q10" s="353" t="n"/>
+      <c r="R10" s="353" t="n"/>
+      <c r="S10" s="353" t="n"/>
+      <c r="T10" s="353" t="n"/>
+      <c r="U10" s="353" t="n"/>
+      <c r="V10" s="353" t="n"/>
+      <c r="W10" s="353" t="n"/>
+      <c r="X10" s="353" t="n"/>
+      <c r="Y10" s="353" t="n"/>
+      <c r="Z10" s="353" t="n"/>
+      <c r="AA10" s="353" t="n"/>
+      <c r="AB10" s="353" t="n"/>
+      <c r="AC10" s="353" t="n"/>
+      <c r="AD10" s="353" t="n"/>
+      <c r="AE10" s="353" t="n"/>
+      <c r="AF10" s="353" t="n"/>
+      <c r="AG10" s="353" t="n"/>
+      <c r="AH10" s="353" t="n"/>
+      <c r="AI10" s="353" t="n"/>
+      <c r="AJ10" s="353" t="n"/>
+      <c r="AK10" s="353" t="n"/>
+      <c r="AL10" s="353" t="n"/>
+      <c r="AM10" s="353" t="n"/>
+      <c r="AN10" s="516" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1" s="329">
-      <c r="A11" s="352">
+      <c r="A11" s="461">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B11" s="390" t="n"/>
-      <c r="C11" s="390" t="n"/>
-      <c r="D11" s="390" t="n"/>
-      <c r="E11" s="390" t="n"/>
-      <c r="F11" s="390" t="n"/>
-      <c r="G11" s="390" t="n"/>
-      <c r="H11" s="390" t="n"/>
-      <c r="I11" s="381" t="n"/>
-      <c r="J11" s="381" t="n"/>
-      <c r="K11" s="381" t="n"/>
-      <c r="L11" s="381" t="n"/>
-      <c r="M11" s="381" t="n"/>
-      <c r="N11" s="381" t="n"/>
-      <c r="O11" s="381" t="n"/>
-      <c r="P11" s="381" t="n"/>
-      <c r="Q11" s="381" t="n"/>
-      <c r="R11" s="381" t="n"/>
-      <c r="S11" s="381" t="n"/>
-      <c r="T11" s="381" t="n"/>
-      <c r="U11" s="381" t="n"/>
-      <c r="V11" s="381" t="n"/>
-      <c r="W11" s="381" t="n"/>
-      <c r="X11" s="381" t="n"/>
-      <c r="Y11" s="381" t="n"/>
-      <c r="Z11" s="381" t="n"/>
-      <c r="AA11" s="381" t="n"/>
-      <c r="AB11" s="381" t="n"/>
-      <c r="AC11" s="381" t="n"/>
-      <c r="AD11" s="381" t="n"/>
-      <c r="AE11" s="381" t="n"/>
-      <c r="AF11" s="381" t="n"/>
-      <c r="AG11" s="381" t="n"/>
-      <c r="AH11" s="381" t="n"/>
-      <c r="AI11" s="381" t="n"/>
-      <c r="AJ11" s="381" t="n"/>
-      <c r="AK11" s="381" t="n"/>
-      <c r="AL11" s="381" t="n"/>
-      <c r="AM11" s="381" t="n"/>
-      <c r="AN11" s="381" t="n"/>
+      <c r="B11" s="462" t="n"/>
+      <c r="C11" s="515" t="n"/>
+      <c r="D11" s="515" t="n"/>
+      <c r="E11" s="515" t="n"/>
+      <c r="F11" s="515" t="n"/>
+      <c r="G11" s="515" t="n"/>
+      <c r="H11" s="515" t="n"/>
+      <c r="I11" s="353" t="n"/>
+      <c r="J11" s="353" t="n"/>
+      <c r="K11" s="353" t="n"/>
+      <c r="L11" s="353" t="n"/>
+      <c r="M11" s="353" t="n"/>
+      <c r="N11" s="353" t="n"/>
+      <c r="O11" s="353" t="n"/>
+      <c r="P11" s="353" t="n"/>
+      <c r="Q11" s="353" t="n"/>
+      <c r="R11" s="353" t="n"/>
+      <c r="S11" s="353" t="n"/>
+      <c r="T11" s="353" t="n"/>
+      <c r="U11" s="353" t="n"/>
+      <c r="V11" s="353" t="n"/>
+      <c r="W11" s="353" t="n"/>
+      <c r="X11" s="353" t="n"/>
+      <c r="Y11" s="353" t="n"/>
+      <c r="Z11" s="353" t="n"/>
+      <c r="AA11" s="353" t="n"/>
+      <c r="AB11" s="353" t="n"/>
+      <c r="AC11" s="353" t="n"/>
+      <c r="AD11" s="353" t="n"/>
+      <c r="AE11" s="353" t="n"/>
+      <c r="AF11" s="353" t="n"/>
+      <c r="AG11" s="353" t="n"/>
+      <c r="AH11" s="353" t="n"/>
+      <c r="AI11" s="353" t="n"/>
+      <c r="AJ11" s="353" t="n"/>
+      <c r="AK11" s="353" t="n"/>
+      <c r="AL11" s="353" t="n"/>
+      <c r="AM11" s="353" t="n"/>
+      <c r="AN11" s="516" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1" s="329">
-      <c r="A12" s="352">
+      <c r="A12" s="461">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B12" s="390" t="n"/>
-      <c r="C12" s="390" t="n"/>
-      <c r="D12" s="390" t="n"/>
-      <c r="E12" s="390" t="n"/>
-      <c r="F12" s="390" t="n"/>
-      <c r="G12" s="390" t="n"/>
-      <c r="H12" s="390" t="n"/>
-      <c r="I12" s="381" t="n"/>
-      <c r="J12" s="381" t="n"/>
-      <c r="K12" s="381" t="n"/>
-      <c r="L12" s="381" t="n"/>
-      <c r="M12" s="381" t="n"/>
-      <c r="N12" s="381" t="n"/>
-      <c r="O12" s="381" t="n"/>
-      <c r="P12" s="381" t="n"/>
-      <c r="Q12" s="381" t="n"/>
-      <c r="R12" s="381" t="n"/>
-      <c r="S12" s="381" t="n"/>
-      <c r="T12" s="381" t="n"/>
-      <c r="U12" s="381" t="n"/>
-      <c r="V12" s="381" t="n"/>
-      <c r="W12" s="381" t="n"/>
-      <c r="X12" s="381" t="n"/>
-      <c r="Y12" s="381" t="n"/>
-      <c r="Z12" s="381" t="n"/>
-      <c r="AA12" s="381" t="n"/>
-      <c r="AB12" s="381" t="n"/>
-      <c r="AC12" s="381" t="n"/>
-      <c r="AD12" s="381" t="n"/>
-      <c r="AE12" s="381" t="n"/>
-      <c r="AF12" s="381" t="n"/>
-      <c r="AG12" s="381" t="n"/>
-      <c r="AH12" s="381" t="n"/>
-      <c r="AI12" s="381" t="n"/>
-      <c r="AJ12" s="381" t="n"/>
-      <c r="AK12" s="381" t="n"/>
-      <c r="AL12" s="381" t="n"/>
-      <c r="AM12" s="381" t="n"/>
-      <c r="AN12" s="381" t="n"/>
+      <c r="B12" s="462" t="n"/>
+      <c r="C12" s="515" t="n"/>
+      <c r="D12" s="515" t="n"/>
+      <c r="E12" s="515" t="n"/>
+      <c r="F12" s="515" t="n"/>
+      <c r="G12" s="515" t="n"/>
+      <c r="H12" s="515" t="n"/>
+      <c r="I12" s="353" t="n"/>
+      <c r="J12" s="353" t="n"/>
+      <c r="K12" s="353" t="n"/>
+      <c r="L12" s="353" t="n"/>
+      <c r="M12" s="353" t="n"/>
+      <c r="N12" s="353" t="n"/>
+      <c r="O12" s="353" t="n"/>
+      <c r="P12" s="353" t="n"/>
+      <c r="Q12" s="353" t="n"/>
+      <c r="R12" s="353" t="n"/>
+      <c r="S12" s="353" t="n"/>
+      <c r="T12" s="353" t="n"/>
+      <c r="U12" s="353" t="n"/>
+      <c r="V12" s="353" t="n"/>
+      <c r="W12" s="353" t="n"/>
+      <c r="X12" s="353" t="n"/>
+      <c r="Y12" s="353" t="n"/>
+      <c r="Z12" s="353" t="n"/>
+      <c r="AA12" s="353" t="n"/>
+      <c r="AB12" s="353" t="n"/>
+      <c r="AC12" s="353" t="n"/>
+      <c r="AD12" s="353" t="n"/>
+      <c r="AE12" s="353" t="n"/>
+      <c r="AF12" s="353" t="n"/>
+      <c r="AG12" s="353" t="n"/>
+      <c r="AH12" s="353" t="n"/>
+      <c r="AI12" s="353" t="n"/>
+      <c r="AJ12" s="353" t="n"/>
+      <c r="AK12" s="353" t="n"/>
+      <c r="AL12" s="353" t="n"/>
+      <c r="AM12" s="353" t="n"/>
+      <c r="AN12" s="516" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1" s="329">
-      <c r="A13" s="352">
+      <c r="A13" s="461">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B13" s="390" t="n"/>
-      <c r="C13" s="390" t="n"/>
-      <c r="D13" s="390" t="n"/>
-      <c r="E13" s="390" t="n"/>
-      <c r="F13" s="390" t="n"/>
-      <c r="G13" s="390" t="n"/>
-      <c r="H13" s="390" t="n"/>
-      <c r="I13" s="381" t="n"/>
-      <c r="J13" s="381" t="n"/>
-      <c r="K13" s="381" t="n"/>
-      <c r="L13" s="381" t="n"/>
-      <c r="M13" s="381" t="n"/>
-      <c r="N13" s="381" t="n"/>
-      <c r="O13" s="381" t="n"/>
-      <c r="P13" s="381" t="n"/>
-      <c r="Q13" s="381" t="n"/>
-      <c r="R13" s="381" t="n"/>
-      <c r="S13" s="381" t="n"/>
-      <c r="T13" s="381" t="n"/>
-      <c r="U13" s="381" t="n"/>
-      <c r="V13" s="381" t="n"/>
-      <c r="W13" s="381" t="n"/>
-      <c r="X13" s="381" t="n"/>
-      <c r="Y13" s="381" t="n"/>
-      <c r="Z13" s="381" t="n"/>
-      <c r="AA13" s="381" t="n"/>
-      <c r="AB13" s="381" t="n"/>
-      <c r="AC13" s="381" t="n"/>
-      <c r="AD13" s="381" t="n"/>
-      <c r="AE13" s="381" t="n"/>
-      <c r="AF13" s="381" t="n"/>
-      <c r="AG13" s="381" t="n"/>
-      <c r="AH13" s="381" t="n"/>
-      <c r="AI13" s="381" t="n"/>
-      <c r="AJ13" s="381" t="n"/>
-      <c r="AK13" s="381" t="n"/>
-      <c r="AL13" s="381" t="n"/>
-      <c r="AM13" s="381" t="n"/>
-      <c r="AN13" s="381" t="n"/>
+      <c r="B13" s="462" t="n"/>
+      <c r="C13" s="515" t="n"/>
+      <c r="D13" s="515" t="n"/>
+      <c r="E13" s="515" t="n"/>
+      <c r="F13" s="515" t="n"/>
+      <c r="G13" s="515" t="n"/>
+      <c r="H13" s="515" t="n"/>
+      <c r="I13" s="353" t="n"/>
+      <c r="J13" s="353" t="n"/>
+      <c r="K13" s="353" t="n"/>
+      <c r="L13" s="353" t="n"/>
+      <c r="M13" s="353" t="n"/>
+      <c r="N13" s="353" t="n"/>
+      <c r="O13" s="353" t="n"/>
+      <c r="P13" s="353" t="n"/>
+      <c r="Q13" s="353" t="n"/>
+      <c r="R13" s="353" t="n"/>
+      <c r="S13" s="353" t="n"/>
+      <c r="T13" s="353" t="n"/>
+      <c r="U13" s="353" t="n"/>
+      <c r="V13" s="353" t="n"/>
+      <c r="W13" s="353" t="n"/>
+      <c r="X13" s="353" t="n"/>
+      <c r="Y13" s="353" t="n"/>
+      <c r="Z13" s="353" t="n"/>
+      <c r="AA13" s="353" t="n"/>
+      <c r="AB13" s="353" t="n"/>
+      <c r="AC13" s="353" t="n"/>
+      <c r="AD13" s="353" t="n"/>
+      <c r="AE13" s="353" t="n"/>
+      <c r="AF13" s="353" t="n"/>
+      <c r="AG13" s="353" t="n"/>
+      <c r="AH13" s="353" t="n"/>
+      <c r="AI13" s="353" t="n"/>
+      <c r="AJ13" s="353" t="n"/>
+      <c r="AK13" s="353" t="n"/>
+      <c r="AL13" s="353" t="n"/>
+      <c r="AM13" s="353" t="n"/>
+      <c r="AN13" s="516" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1" s="329">
-      <c r="A14" s="352">
+      <c r="A14" s="461">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B14" s="390" t="n"/>
-      <c r="C14" s="390" t="n"/>
-      <c r="D14" s="390" t="n"/>
-      <c r="E14" s="390" t="n"/>
-      <c r="F14" s="390" t="n"/>
-      <c r="G14" s="390" t="n"/>
-      <c r="H14" s="390" t="n"/>
-      <c r="I14" s="381" t="n"/>
-      <c r="J14" s="381" t="n"/>
-      <c r="K14" s="381" t="n"/>
-      <c r="L14" s="381" t="n"/>
-      <c r="M14" s="381" t="n"/>
-      <c r="N14" s="381" t="n"/>
-      <c r="O14" s="381" t="n"/>
-      <c r="P14" s="381" t="n"/>
-      <c r="Q14" s="381" t="n"/>
-      <c r="R14" s="381" t="n"/>
-      <c r="S14" s="381" t="n"/>
-      <c r="T14" s="381" t="n"/>
-      <c r="U14" s="381" t="n"/>
-      <c r="V14" s="381" t="n"/>
-      <c r="W14" s="381" t="n"/>
-      <c r="X14" s="381" t="n"/>
-      <c r="Y14" s="381" t="n"/>
-      <c r="Z14" s="381" t="n"/>
-      <c r="AA14" s="381" t="n"/>
-      <c r="AB14" s="381" t="n"/>
-      <c r="AC14" s="381" t="n"/>
-      <c r="AD14" s="381" t="n"/>
-      <c r="AE14" s="381" t="n"/>
-      <c r="AF14" s="381" t="n"/>
-      <c r="AG14" s="381" t="n"/>
-      <c r="AH14" s="381" t="n"/>
-      <c r="AI14" s="381" t="n"/>
-      <c r="AJ14" s="381" t="n"/>
-      <c r="AK14" s="381" t="n"/>
-      <c r="AL14" s="381" t="n"/>
-      <c r="AM14" s="381" t="n"/>
-      <c r="AN14" s="381" t="n"/>
+      <c r="B14" s="462" t="n"/>
+      <c r="C14" s="515" t="n"/>
+      <c r="D14" s="515" t="n"/>
+      <c r="E14" s="515" t="n"/>
+      <c r="F14" s="515" t="n"/>
+      <c r="G14" s="515" t="n"/>
+      <c r="H14" s="515" t="n"/>
+      <c r="I14" s="353" t="n"/>
+      <c r="J14" s="353" t="n"/>
+      <c r="K14" s="353" t="n"/>
+      <c r="L14" s="353" t="n"/>
+      <c r="M14" s="353" t="n"/>
+      <c r="N14" s="353" t="n"/>
+      <c r="O14" s="353" t="n"/>
+      <c r="P14" s="353" t="n"/>
+      <c r="Q14" s="353" t="n"/>
+      <c r="R14" s="353" t="n"/>
+      <c r="S14" s="353" t="n"/>
+      <c r="T14" s="353" t="n"/>
+      <c r="U14" s="353" t="n"/>
+      <c r="V14" s="353" t="n"/>
+      <c r="W14" s="353" t="n"/>
+      <c r="X14" s="353" t="n"/>
+      <c r="Y14" s="353" t="n"/>
+      <c r="Z14" s="353" t="n"/>
+      <c r="AA14" s="353" t="n"/>
+      <c r="AB14" s="353" t="n"/>
+      <c r="AC14" s="353" t="n"/>
+      <c r="AD14" s="353" t="n"/>
+      <c r="AE14" s="353" t="n"/>
+      <c r="AF14" s="353" t="n"/>
+      <c r="AG14" s="353" t="n"/>
+      <c r="AH14" s="353" t="n"/>
+      <c r="AI14" s="353" t="n"/>
+      <c r="AJ14" s="353" t="n"/>
+      <c r="AK14" s="353" t="n"/>
+      <c r="AL14" s="353" t="n"/>
+      <c r="AM14" s="353" t="n"/>
+      <c r="AN14" s="516" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1" s="329">
-      <c r="A15" s="352" t="n"/>
-      <c r="B15" s="390" t="n"/>
-      <c r="C15" s="390" t="n"/>
-      <c r="D15" s="390" t="n"/>
-      <c r="E15" s="390" t="n"/>
-      <c r="F15" s="390" t="n"/>
-      <c r="G15" s="390" t="n"/>
-      <c r="H15" s="390" t="n"/>
-      <c r="I15" s="381" t="n"/>
-      <c r="J15" s="381" t="n"/>
-      <c r="K15" s="381" t="n"/>
-      <c r="L15" s="381" t="n"/>
-      <c r="M15" s="381" t="n"/>
-      <c r="N15" s="381" t="n"/>
-      <c r="O15" s="381" t="n"/>
-      <c r="P15" s="381" t="n"/>
-      <c r="Q15" s="381" t="n"/>
-      <c r="R15" s="381" t="n"/>
-      <c r="S15" s="381" t="n"/>
-      <c r="T15" s="381" t="n"/>
-      <c r="U15" s="381" t="n"/>
-      <c r="V15" s="381" t="n"/>
-      <c r="W15" s="381" t="n"/>
-      <c r="X15" s="381" t="n"/>
-      <c r="Y15" s="381" t="n"/>
-      <c r="Z15" s="381" t="n"/>
-      <c r="AA15" s="381" t="n"/>
-      <c r="AB15" s="381" t="n"/>
-      <c r="AC15" s="381" t="n"/>
-      <c r="AD15" s="381" t="n"/>
-      <c r="AE15" s="381" t="n"/>
-      <c r="AF15" s="381" t="n"/>
-      <c r="AG15" s="381" t="n"/>
-      <c r="AH15" s="381" t="n"/>
-      <c r="AI15" s="381" t="n"/>
-      <c r="AJ15" s="381" t="n"/>
-      <c r="AK15" s="381" t="n"/>
-      <c r="AL15" s="381" t="n"/>
-      <c r="AM15" s="381" t="n"/>
-      <c r="AN15" s="381" t="n"/>
+      <c r="A15" s="461" t="n"/>
+      <c r="B15" s="462" t="n"/>
+      <c r="C15" s="515" t="n"/>
+      <c r="D15" s="515" t="n"/>
+      <c r="E15" s="515" t="n"/>
+      <c r="F15" s="515" t="n"/>
+      <c r="G15" s="515" t="n"/>
+      <c r="H15" s="515" t="n"/>
+      <c r="I15" s="353" t="n"/>
+      <c r="J15" s="353" t="n"/>
+      <c r="K15" s="353" t="n"/>
+      <c r="L15" s="353" t="n"/>
+      <c r="M15" s="353" t="n"/>
+      <c r="N15" s="353" t="n"/>
+      <c r="O15" s="353" t="n"/>
+      <c r="P15" s="353" t="n"/>
+      <c r="Q15" s="353" t="n"/>
+      <c r="R15" s="353" t="n"/>
+      <c r="S15" s="353" t="n"/>
+      <c r="T15" s="353" t="n"/>
+      <c r="U15" s="353" t="n"/>
+      <c r="V15" s="353" t="n"/>
+      <c r="W15" s="353" t="n"/>
+      <c r="X15" s="353" t="n"/>
+      <c r="Y15" s="353" t="n"/>
+      <c r="Z15" s="353" t="n"/>
+      <c r="AA15" s="353" t="n"/>
+      <c r="AB15" s="353" t="n"/>
+      <c r="AC15" s="353" t="n"/>
+      <c r="AD15" s="353" t="n"/>
+      <c r="AE15" s="353" t="n"/>
+      <c r="AF15" s="353" t="n"/>
+      <c r="AG15" s="353" t="n"/>
+      <c r="AH15" s="353" t="n"/>
+      <c r="AI15" s="353" t="n"/>
+      <c r="AJ15" s="353" t="n"/>
+      <c r="AK15" s="353" t="n"/>
+      <c r="AL15" s="353" t="n"/>
+      <c r="AM15" s="353" t="n"/>
+      <c r="AN15" s="516" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1" s="329">
-      <c r="A16" s="352" t="n"/>
-      <c r="B16" s="390" t="n"/>
-      <c r="C16" s="390" t="n"/>
-      <c r="D16" s="390" t="n"/>
-      <c r="E16" s="390" t="n"/>
-      <c r="F16" s="390" t="n"/>
-      <c r="G16" s="390" t="n"/>
-      <c r="H16" s="390" t="n"/>
-      <c r="I16" s="381" t="n"/>
-      <c r="J16" s="381" t="n"/>
-      <c r="K16" s="381" t="n"/>
-      <c r="L16" s="381" t="n"/>
-      <c r="M16" s="381" t="n"/>
-      <c r="N16" s="381" t="n"/>
-      <c r="O16" s="381" t="n"/>
-      <c r="P16" s="381" t="n"/>
-      <c r="Q16" s="381" t="n"/>
-      <c r="R16" s="381" t="n"/>
-      <c r="S16" s="381" t="n"/>
-      <c r="T16" s="381" t="n"/>
-      <c r="U16" s="381" t="n"/>
-      <c r="V16" s="381" t="n"/>
-      <c r="W16" s="381" t="n"/>
-      <c r="X16" s="381" t="n"/>
-      <c r="Y16" s="381" t="n"/>
-      <c r="Z16" s="381" t="n"/>
-      <c r="AA16" s="381" t="n"/>
-      <c r="AB16" s="381" t="n"/>
-      <c r="AC16" s="381" t="n"/>
-      <c r="AD16" s="381" t="n"/>
-      <c r="AE16" s="381" t="n"/>
-      <c r="AF16" s="381" t="n"/>
-      <c r="AG16" s="381" t="n"/>
-      <c r="AH16" s="381" t="n"/>
-      <c r="AI16" s="381" t="n"/>
-      <c r="AJ16" s="381" t="n"/>
-      <c r="AK16" s="381" t="n"/>
-      <c r="AL16" s="381" t="n"/>
-      <c r="AM16" s="381" t="n"/>
-      <c r="AN16" s="381" t="n"/>
+      <c r="A16" s="465" t="n"/>
+      <c r="B16" s="467" t="n"/>
+      <c r="C16" s="517" t="n"/>
+      <c r="D16" s="517" t="n"/>
+      <c r="E16" s="517" t="n"/>
+      <c r="F16" s="517" t="n"/>
+      <c r="G16" s="517" t="n"/>
+      <c r="H16" s="517" t="n"/>
+      <c r="I16" s="518" t="n"/>
+      <c r="J16" s="518" t="n"/>
+      <c r="K16" s="518" t="n"/>
+      <c r="L16" s="518" t="n"/>
+      <c r="M16" s="518" t="n"/>
+      <c r="N16" s="518" t="n"/>
+      <c r="O16" s="518" t="n"/>
+      <c r="P16" s="518" t="n"/>
+      <c r="Q16" s="518" t="n"/>
+      <c r="R16" s="518" t="n"/>
+      <c r="S16" s="518" t="n"/>
+      <c r="T16" s="518" t="n"/>
+      <c r="U16" s="518" t="n"/>
+      <c r="V16" s="518" t="n"/>
+      <c r="W16" s="518" t="n"/>
+      <c r="X16" s="518" t="n"/>
+      <c r="Y16" s="518" t="n"/>
+      <c r="Z16" s="518" t="n"/>
+      <c r="AA16" s="518" t="n"/>
+      <c r="AB16" s="518" t="n"/>
+      <c r="AC16" s="518" t="n"/>
+      <c r="AD16" s="518" t="n"/>
+      <c r="AE16" s="518" t="n"/>
+      <c r="AF16" s="518" t="n"/>
+      <c r="AG16" s="518" t="n"/>
+      <c r="AH16" s="518" t="n"/>
+      <c r="AI16" s="518" t="n"/>
+      <c r="AJ16" s="518" t="n"/>
+      <c r="AK16" s="518" t="n"/>
+      <c r="AL16" s="518" t="n"/>
+      <c r="AM16" s="518" t="n"/>
+      <c r="AN16" s="519" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1" s="329"/>
     <row r="18" ht="20" customHeight="1" s="329"/>
@@ -8325,9 +9146,10 @@
   </dataValidations>
   <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <tableParts count="2">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
@@ -8383,677 +9205,683 @@
     <col width="2.33" customWidth="1" style="329" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="329">
-      <c r="A1" s="386" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" s="329">
+      <c r="A1" s="497" t="inlineStr">
         <is>
           <t>Upstream References / Import Guidance</t>
         </is>
       </c>
-      <c r="B1" s="409" t="n"/>
-      <c r="C1" s="409" t="n"/>
-      <c r="D1" s="409" t="n"/>
-      <c r="E1" s="409" t="n"/>
-      <c r="F1" s="409" t="n"/>
-      <c r="G1" s="410" t="n"/>
-      <c r="H1" s="345" t="n"/>
-      <c r="I1" s="345" t="n"/>
-      <c r="J1" s="345" t="n"/>
-      <c r="K1" s="345" t="n"/>
-      <c r="L1" s="345" t="n"/>
-      <c r="M1" s="345" t="n"/>
-      <c r="N1" s="345" t="n"/>
-      <c r="O1" s="345" t="n"/>
-      <c r="P1" s="345" t="n"/>
-      <c r="Q1" s="345" t="n"/>
-      <c r="R1" s="345" t="n"/>
-      <c r="S1" s="345" t="n"/>
-      <c r="T1" s="345" t="n"/>
-      <c r="U1" s="345" t="n"/>
-      <c r="V1" s="345" t="n"/>
-      <c r="W1" s="345" t="n"/>
-      <c r="X1" s="345" t="n"/>
-      <c r="Y1" s="345" t="n"/>
-      <c r="Z1" s="345" t="n"/>
-      <c r="AA1" s="345" t="n"/>
-      <c r="AB1" s="345" t="n"/>
-      <c r="AC1" s="345" t="n"/>
-      <c r="AD1" s="345" t="n"/>
-      <c r="AE1" s="345" t="n"/>
-      <c r="AF1" s="345" t="n"/>
-      <c r="AG1" s="345" t="n"/>
-      <c r="AH1" s="345" t="n"/>
-      <c r="AI1" s="345" t="n"/>
-      <c r="AJ1" s="345" t="n"/>
-      <c r="AK1" s="345" t="n"/>
-      <c r="AL1" s="345" t="n"/>
-      <c r="AM1" s="345" t="n"/>
-      <c r="AN1" s="345" t="n"/>
+      <c r="B1" s="415" t="n"/>
+      <c r="C1" s="415" t="n"/>
+      <c r="D1" s="415" t="n"/>
+      <c r="E1" s="415" t="n"/>
+      <c r="F1" s="415" t="n"/>
+      <c r="G1" s="415" t="n"/>
+      <c r="H1" s="498" t="n"/>
+      <c r="I1" s="417" t="n"/>
+      <c r="J1" s="418" t="n"/>
+      <c r="K1" s="418" t="n"/>
+      <c r="L1" s="418" t="n"/>
+      <c r="M1" s="418" t="n"/>
+      <c r="N1" s="418" t="n"/>
+      <c r="O1" s="418" t="n"/>
+      <c r="P1" s="418" t="n"/>
+      <c r="Q1" s="418" t="n"/>
+      <c r="R1" s="418" t="n"/>
+      <c r="S1" s="418" t="n"/>
+      <c r="T1" s="418" t="n"/>
+      <c r="U1" s="418" t="n"/>
+      <c r="V1" s="418" t="n"/>
+      <c r="W1" s="418" t="n"/>
+      <c r="X1" s="418" t="n"/>
+      <c r="Y1" s="418" t="n"/>
+      <c r="Z1" s="418" t="n"/>
+      <c r="AA1" s="418" t="n"/>
+      <c r="AB1" s="418" t="n"/>
+      <c r="AC1" s="418" t="n"/>
+      <c r="AD1" s="419" t="n"/>
+      <c r="AE1" s="420" t="n"/>
+      <c r="AF1" s="421" t="n"/>
+      <c r="AG1" s="421" t="n"/>
+      <c r="AH1" s="422" t="n"/>
+      <c r="AI1" s="423" t="n"/>
+      <c r="AJ1" s="424" t="n"/>
+      <c r="AK1" s="424" t="n"/>
+      <c r="AL1" s="424" t="n"/>
+      <c r="AM1" s="424" t="n"/>
+      <c r="AN1" s="425" t="n"/>
     </row>
-    <row r="2" ht="18" customHeight="1" s="329">
-      <c r="A2" s="335" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="329">
+      <c r="A2" s="499" t="inlineStr">
         <is>
           <t>Incoming verification event record for outsourced process returns and discrete disposition decisions.</t>
         </is>
       </c>
-      <c r="H2" s="345" t="n"/>
-      <c r="I2" s="345" t="n"/>
-      <c r="J2" s="345" t="n"/>
-      <c r="K2" s="345" t="n"/>
-      <c r="L2" s="345" t="n"/>
-      <c r="M2" s="345" t="n"/>
-      <c r="N2" s="345" t="n"/>
-      <c r="O2" s="345" t="n"/>
-      <c r="P2" s="345" t="n"/>
-      <c r="Q2" s="345" t="n"/>
-      <c r="R2" s="345" t="n"/>
-      <c r="S2" s="345" t="n"/>
-      <c r="T2" s="345" t="n"/>
-      <c r="U2" s="345" t="n"/>
-      <c r="V2" s="345" t="n"/>
-      <c r="W2" s="345" t="n"/>
-      <c r="X2" s="345" t="n"/>
-      <c r="Y2" s="345" t="n"/>
-      <c r="Z2" s="345" t="n"/>
-      <c r="AA2" s="345" t="n"/>
-      <c r="AB2" s="345" t="n"/>
-      <c r="AC2" s="345" t="n"/>
-      <c r="AD2" s="345" t="n"/>
-      <c r="AE2" s="345" t="n"/>
-      <c r="AF2" s="345" t="n"/>
-      <c r="AG2" s="345" t="n"/>
-      <c r="AH2" s="345" t="n"/>
-      <c r="AI2" s="345" t="n"/>
-      <c r="AJ2" s="345" t="n"/>
-      <c r="AK2" s="345" t="n"/>
-      <c r="AL2" s="345" t="n"/>
-      <c r="AM2" s="345" t="n"/>
-      <c r="AN2" s="345" t="n"/>
+      <c r="B2" s="25" t="n"/>
+      <c r="C2" s="25" t="n"/>
+      <c r="D2" s="25" t="n"/>
+      <c r="E2" s="25" t="n"/>
+      <c r="F2" s="25" t="n"/>
+      <c r="G2" s="25" t="n"/>
+      <c r="H2" s="500" t="n"/>
+      <c r="I2" s="428" t="n"/>
+      <c r="J2" s="429" t="n"/>
+      <c r="K2" s="429" t="n"/>
+      <c r="L2" s="429" t="n"/>
+      <c r="M2" s="429" t="n"/>
+      <c r="N2" s="429" t="n"/>
+      <c r="O2" s="429" t="n"/>
+      <c r="P2" s="429" t="n"/>
+      <c r="Q2" s="429" t="n"/>
+      <c r="R2" s="429" t="n"/>
+      <c r="S2" s="429" t="n"/>
+      <c r="T2" s="429" t="n"/>
+      <c r="U2" s="429" t="n"/>
+      <c r="V2" s="429" t="n"/>
+      <c r="W2" s="429" t="n"/>
+      <c r="X2" s="429" t="n"/>
+      <c r="Y2" s="429" t="n"/>
+      <c r="Z2" s="429" t="n"/>
+      <c r="AA2" s="429" t="n"/>
+      <c r="AB2" s="429" t="n"/>
+      <c r="AC2" s="429" t="n"/>
+      <c r="AD2" s="430" t="n"/>
+      <c r="AE2" s="431" t="n"/>
+      <c r="AF2" s="432" t="n"/>
+      <c r="AG2" s="432" t="n"/>
+      <c r="AH2" s="433" t="n"/>
+      <c r="AI2" s="434" t="n"/>
+      <c r="AJ2" s="435" t="n"/>
+      <c r="AK2" s="435" t="n"/>
+      <c r="AL2" s="435" t="n"/>
+      <c r="AM2" s="435" t="n"/>
+      <c r="AN2" s="436" t="n"/>
     </row>
-    <row r="3" ht="18" customHeight="1" s="329">
-      <c r="A3" s="345" t="n"/>
-      <c r="B3" s="345" t="n"/>
-      <c r="C3" s="345" t="n"/>
-      <c r="D3" s="345" t="n"/>
-      <c r="E3" s="345" t="n"/>
-      <c r="F3" s="345" t="n"/>
-      <c r="G3" s="345" t="n"/>
-      <c r="H3" s="345" t="n"/>
-      <c r="I3" s="345" t="n"/>
-      <c r="J3" s="345" t="n"/>
-      <c r="K3" s="345" t="n"/>
-      <c r="L3" s="345" t="n"/>
-      <c r="M3" s="345" t="n"/>
-      <c r="N3" s="345" t="n"/>
-      <c r="O3" s="345" t="n"/>
-      <c r="P3" s="345" t="n"/>
-      <c r="Q3" s="345" t="n"/>
-      <c r="R3" s="345" t="n"/>
-      <c r="S3" s="345" t="n"/>
-      <c r="T3" s="345" t="n"/>
-      <c r="U3" s="345" t="n"/>
-      <c r="V3" s="345" t="n"/>
-      <c r="W3" s="345" t="n"/>
-      <c r="X3" s="345" t="n"/>
-      <c r="Y3" s="345" t="n"/>
-      <c r="Z3" s="345" t="n"/>
-      <c r="AA3" s="345" t="n"/>
-      <c r="AB3" s="345" t="n"/>
-      <c r="AC3" s="345" t="n"/>
-      <c r="AD3" s="345" t="n"/>
-      <c r="AE3" s="345" t="n"/>
-      <c r="AF3" s="345" t="n"/>
-      <c r="AG3" s="345" t="n"/>
-      <c r="AH3" s="345" t="n"/>
-      <c r="AI3" s="345" t="n"/>
-      <c r="AJ3" s="345" t="n"/>
-      <c r="AK3" s="345" t="n"/>
-      <c r="AL3" s="345" t="n"/>
-      <c r="AM3" s="345" t="n"/>
-      <c r="AN3" s="345" t="n"/>
+    <row r="3" ht="15" customHeight="1" s="329">
+      <c r="A3" s="501" t="n"/>
+      <c r="B3" s="502" t="n"/>
+      <c r="C3" s="502" t="n"/>
+      <c r="D3" s="502" t="n"/>
+      <c r="E3" s="502" t="n"/>
+      <c r="F3" s="502" t="n"/>
+      <c r="G3" s="502" t="n"/>
+      <c r="H3" s="500" t="n"/>
+      <c r="I3" s="428" t="n"/>
+      <c r="J3" s="429" t="n"/>
+      <c r="K3" s="429" t="n"/>
+      <c r="L3" s="429" t="n"/>
+      <c r="M3" s="429" t="n"/>
+      <c r="N3" s="429" t="n"/>
+      <c r="O3" s="429" t="n"/>
+      <c r="P3" s="429" t="n"/>
+      <c r="Q3" s="429" t="n"/>
+      <c r="R3" s="429" t="n"/>
+      <c r="S3" s="429" t="n"/>
+      <c r="T3" s="429" t="n"/>
+      <c r="U3" s="429" t="n"/>
+      <c r="V3" s="429" t="n"/>
+      <c r="W3" s="429" t="n"/>
+      <c r="X3" s="429" t="n"/>
+      <c r="Y3" s="429" t="n"/>
+      <c r="Z3" s="429" t="n"/>
+      <c r="AA3" s="429" t="n"/>
+      <c r="AB3" s="429" t="n"/>
+      <c r="AC3" s="429" t="n"/>
+      <c r="AD3" s="430" t="n"/>
+      <c r="AE3" s="431" t="n"/>
+      <c r="AF3" s="432" t="n"/>
+      <c r="AG3" s="432" t="n"/>
+      <c r="AH3" s="433" t="n"/>
+      <c r="AI3" s="434" t="n"/>
+      <c r="AJ3" s="435" t="n"/>
+      <c r="AK3" s="435" t="n"/>
+      <c r="AL3" s="435" t="n"/>
+      <c r="AM3" s="435" t="n"/>
+      <c r="AN3" s="436" t="n"/>
     </row>
-    <row r="4" ht="20" customHeight="1" s="329">
-      <c r="A4" s="387" t="inlineStr">
+    <row r="4" ht="15" customHeight="1" s="329">
+      <c r="A4" s="503" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B4" s="387" t="inlineStr">
+      <c r="B4" s="504" t="inlineStr">
         <is>
           <t>Value / Reference</t>
         </is>
       </c>
-      <c r="C4" s="387" t="inlineStr">
+      <c r="C4" s="504" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="D4" s="345" t="n"/>
-      <c r="E4" s="345" t="n"/>
-      <c r="F4" s="345" t="n"/>
-      <c r="G4" s="345" t="n"/>
-      <c r="H4" s="345" t="n"/>
-      <c r="I4" s="345" t="n"/>
-      <c r="J4" s="345" t="n"/>
-      <c r="K4" s="345" t="n"/>
-      <c r="L4" s="345" t="n"/>
-      <c r="M4" s="345" t="n"/>
-      <c r="N4" s="345" t="n"/>
-      <c r="O4" s="345" t="n"/>
-      <c r="P4" s="345" t="n"/>
-      <c r="Q4" s="345" t="n"/>
-      <c r="R4" s="345" t="n"/>
-      <c r="S4" s="345" t="n"/>
-      <c r="T4" s="345" t="n"/>
-      <c r="U4" s="345" t="n"/>
-      <c r="V4" s="345" t="n"/>
-      <c r="W4" s="345" t="n"/>
-      <c r="X4" s="345" t="n"/>
-      <c r="Y4" s="345" t="n"/>
-      <c r="Z4" s="345" t="n"/>
-      <c r="AA4" s="345" t="n"/>
-      <c r="AB4" s="345" t="n"/>
-      <c r="AC4" s="345" t="n"/>
-      <c r="AD4" s="345" t="n"/>
-      <c r="AE4" s="345" t="n"/>
-      <c r="AF4" s="345" t="n"/>
-      <c r="AG4" s="345" t="n"/>
-      <c r="AH4" s="345" t="n"/>
-      <c r="AI4" s="345" t="n"/>
-      <c r="AJ4" s="345" t="n"/>
-      <c r="AK4" s="345" t="n"/>
-      <c r="AL4" s="345" t="n"/>
-      <c r="AM4" s="345" t="n"/>
-      <c r="AN4" s="345" t="n"/>
+      <c r="D4" s="502" t="n"/>
+      <c r="E4" s="502" t="n"/>
+      <c r="F4" s="502" t="n"/>
+      <c r="G4" s="502" t="n"/>
+      <c r="H4" s="500" t="n"/>
+      <c r="I4" s="437" t="n"/>
+      <c r="J4" s="438" t="n"/>
+      <c r="K4" s="438" t="n"/>
+      <c r="L4" s="438" t="n"/>
+      <c r="M4" s="438" t="n"/>
+      <c r="N4" s="438" t="n"/>
+      <c r="O4" s="438" t="n"/>
+      <c r="P4" s="438" t="n"/>
+      <c r="Q4" s="438" t="n"/>
+      <c r="R4" s="438" t="n"/>
+      <c r="S4" s="438" t="n"/>
+      <c r="T4" s="438" t="n"/>
+      <c r="U4" s="438" t="n"/>
+      <c r="V4" s="438" t="n"/>
+      <c r="W4" s="438" t="n"/>
+      <c r="X4" s="438" t="n"/>
+      <c r="Y4" s="438" t="n"/>
+      <c r="Z4" s="438" t="n"/>
+      <c r="AA4" s="438" t="n"/>
+      <c r="AB4" s="438" t="n"/>
+      <c r="AC4" s="438" t="n"/>
+      <c r="AD4" s="439" t="n"/>
+      <c r="AE4" s="431" t="n"/>
+      <c r="AF4" s="432" t="n"/>
+      <c r="AG4" s="432" t="n"/>
+      <c r="AH4" s="433" t="n"/>
+      <c r="AI4" s="434" t="n"/>
+      <c r="AJ4" s="435" t="n"/>
+      <c r="AK4" s="435" t="n"/>
+      <c r="AL4" s="435" t="n"/>
+      <c r="AM4" s="435" t="n"/>
+      <c r="AN4" s="436" t="n"/>
     </row>
-    <row r="5" ht="20" customHeight="1" s="329">
-      <c r="A5" s="388" t="inlineStr">
+    <row r="5" ht="15" customHeight="1" s="329">
+      <c r="A5" s="506" t="inlineStr">
         <is>
           <t>Source of Truth</t>
         </is>
       </c>
-      <c r="B5" s="389" t="inlineStr">
+      <c r="B5" s="507" t="inlineStr">
         <is>
           <t>Epicor transaction + M365 evidence</t>
         </is>
       </c>
-      <c r="C5" s="389" t="inlineStr">
+      <c r="C5" s="507" t="inlineStr">
         <is>
           <t>Do not duplicate ERP/M365/ANNEX master data.</t>
         </is>
       </c>
-      <c r="D5" s="345" t="n"/>
-      <c r="E5" s="345" t="n"/>
-      <c r="F5" s="345" t="n"/>
-      <c r="G5" s="345" t="n"/>
-      <c r="H5" s="345" t="n"/>
-      <c r="I5" s="345" t="n"/>
-      <c r="J5" s="345" t="n"/>
-      <c r="K5" s="345" t="n"/>
-      <c r="L5" s="345" t="n"/>
-      <c r="M5" s="345" t="n"/>
-      <c r="N5" s="345" t="n"/>
-      <c r="O5" s="345" t="n"/>
-      <c r="P5" s="345" t="n"/>
-      <c r="Q5" s="345" t="n"/>
-      <c r="R5" s="345" t="n"/>
-      <c r="S5" s="345" t="n"/>
-      <c r="T5" s="345" t="n"/>
-      <c r="U5" s="345" t="n"/>
-      <c r="V5" s="345" t="n"/>
-      <c r="W5" s="345" t="n"/>
-      <c r="X5" s="345" t="n"/>
-      <c r="Y5" s="345" t="n"/>
-      <c r="Z5" s="345" t="n"/>
-      <c r="AA5" s="345" t="n"/>
-      <c r="AB5" s="345" t="n"/>
-      <c r="AC5" s="345" t="n"/>
-      <c r="AD5" s="345" t="n"/>
-      <c r="AE5" s="345" t="n"/>
-      <c r="AF5" s="345" t="n"/>
-      <c r="AG5" s="345" t="n"/>
-      <c r="AH5" s="345" t="n"/>
-      <c r="AI5" s="345" t="n"/>
-      <c r="AJ5" s="345" t="n"/>
-      <c r="AK5" s="345" t="n"/>
-      <c r="AL5" s="345" t="n"/>
-      <c r="AM5" s="345" t="n"/>
-      <c r="AN5" s="345" t="n"/>
+      <c r="D5" s="520" t="n"/>
+      <c r="E5" s="520" t="n"/>
+      <c r="F5" s="520" t="n"/>
+      <c r="G5" s="520" t="n"/>
+      <c r="H5" s="521" t="n"/>
+      <c r="I5" s="443" t="n"/>
+      <c r="J5" s="444" t="n"/>
+      <c r="K5" s="444" t="n"/>
+      <c r="L5" s="444" t="n"/>
+      <c r="M5" s="444" t="n"/>
+      <c r="N5" s="444" t="n"/>
+      <c r="O5" s="444" t="n"/>
+      <c r="P5" s="444" t="n"/>
+      <c r="Q5" s="444" t="n"/>
+      <c r="R5" s="444" t="n"/>
+      <c r="S5" s="444" t="n"/>
+      <c r="T5" s="444" t="n"/>
+      <c r="U5" s="444" t="n"/>
+      <c r="V5" s="444" t="n"/>
+      <c r="W5" s="444" t="n"/>
+      <c r="X5" s="444" t="n"/>
+      <c r="Y5" s="444" t="n"/>
+      <c r="Z5" s="444" t="n"/>
+      <c r="AA5" s="444" t="n"/>
+      <c r="AB5" s="444" t="n"/>
+      <c r="AC5" s="444" t="n"/>
+      <c r="AD5" s="445" t="n"/>
+      <c r="AE5" s="446" t="n"/>
+      <c r="AF5" s="447" t="n"/>
+      <c r="AG5" s="447" t="n"/>
+      <c r="AH5" s="448" t="n"/>
+      <c r="AI5" s="449" t="n"/>
+      <c r="AJ5" s="450" t="n"/>
+      <c r="AK5" s="450" t="n"/>
+      <c r="AL5" s="450" t="n"/>
+      <c r="AM5" s="450" t="n"/>
+      <c r="AN5" s="451" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1" s="329">
-      <c r="A6" s="388" t="inlineStr">
+      <c r="A6" s="509" t="inlineStr">
         <is>
           <t>Cross-Reference Boundary</t>
         </is>
       </c>
-      <c r="B6" s="389" t="inlineStr">
+      <c r="B6" s="510" t="inlineStr">
         <is>
           <t>This form does not replace SOP-402; it records the evidence, data or decision required by that SOP.
 Rules, matrices, dictionaries, acceptance criteria and data definitions belong in ANNEX-PUR-001/002/003 + ANNEX-ENG-002; do not copy ANNEX content into the live data-entry body.
 System-of-record / source-of-truth boundary: Epicor transaction + M365 evidence. If the master data already live there, reference or import them; do not re-key without need.</t>
         </is>
       </c>
-      <c r="C6" s="389" t="inlineStr">
+      <c r="C6" s="511" t="inlineStr">
         <is>
           <t>This form does not replace SOP-402; it records the evidence, data or decision required by that SOP.
 Rules, matrices, dictionaries, acceptance criteria and data definitions belong in ANNEX-PUR-001/002/003 + ANNEX-ENG-002; do not copy ANNEX content into the live data-entry body.
 System-of-record / source-of-truth boundary: Epicor transaction + M365 evidence. If the master data already live there, reference or import them; do not re-key without need.</t>
         </is>
       </c>
-      <c r="D6" s="345" t="n"/>
-      <c r="E6" s="345" t="n"/>
-      <c r="F6" s="345" t="n"/>
-      <c r="G6" s="345" t="n"/>
-      <c r="H6" s="345" t="n"/>
-      <c r="I6" s="345" t="n"/>
-      <c r="J6" s="345" t="n"/>
-      <c r="K6" s="345" t="n"/>
-      <c r="L6" s="345" t="n"/>
-      <c r="M6" s="345" t="n"/>
-      <c r="N6" s="345" t="n"/>
-      <c r="O6" s="345" t="n"/>
-      <c r="P6" s="345" t="n"/>
-      <c r="Q6" s="345" t="n"/>
-      <c r="R6" s="345" t="n"/>
-      <c r="S6" s="345" t="n"/>
-      <c r="T6" s="345" t="n"/>
-      <c r="U6" s="345" t="n"/>
-      <c r="V6" s="345" t="n"/>
-      <c r="W6" s="345" t="n"/>
-      <c r="X6" s="345" t="n"/>
-      <c r="Y6" s="345" t="n"/>
-      <c r="Z6" s="345" t="n"/>
-      <c r="AA6" s="345" t="n"/>
-      <c r="AB6" s="345" t="n"/>
-      <c r="AC6" s="345" t="n"/>
-      <c r="AD6" s="345" t="n"/>
-      <c r="AE6" s="345" t="n"/>
-      <c r="AF6" s="345" t="n"/>
-      <c r="AG6" s="345" t="n"/>
-      <c r="AH6" s="345" t="n"/>
-      <c r="AI6" s="345" t="n"/>
-      <c r="AJ6" s="345" t="n"/>
-      <c r="AK6" s="345" t="n"/>
-      <c r="AL6" s="345" t="n"/>
-      <c r="AM6" s="345" t="n"/>
-      <c r="AN6" s="345" t="n"/>
+      <c r="D6" s="457" t="n"/>
+      <c r="E6" s="457" t="n"/>
+      <c r="F6" s="457" t="n"/>
+      <c r="G6" s="457" t="n"/>
+      <c r="H6" s="457" t="n"/>
+      <c r="I6" s="457" t="n"/>
+      <c r="J6" s="457" t="n"/>
+      <c r="K6" s="457" t="n"/>
+      <c r="L6" s="457" t="n"/>
+      <c r="M6" s="457" t="n"/>
+      <c r="N6" s="457" t="n"/>
+      <c r="O6" s="457" t="n"/>
+      <c r="P6" s="457" t="n"/>
+      <c r="Q6" s="457" t="n"/>
+      <c r="R6" s="457" t="n"/>
+      <c r="S6" s="457" t="n"/>
+      <c r="T6" s="457" t="n"/>
+      <c r="U6" s="457" t="n"/>
+      <c r="V6" s="457" t="n"/>
+      <c r="W6" s="457" t="n"/>
+      <c r="X6" s="457" t="n"/>
+      <c r="Y6" s="457" t="n"/>
+      <c r="Z6" s="457" t="n"/>
+      <c r="AA6" s="457" t="n"/>
+      <c r="AB6" s="457" t="n"/>
+      <c r="AC6" s="457" t="n"/>
+      <c r="AD6" s="457" t="n"/>
+      <c r="AE6" s="457" t="n"/>
+      <c r="AF6" s="457" t="n"/>
+      <c r="AG6" s="457" t="n"/>
+      <c r="AH6" s="457" t="n"/>
+      <c r="AI6" s="457" t="n"/>
+      <c r="AJ6" s="457" t="n"/>
+      <c r="AK6" s="457" t="n"/>
+      <c r="AL6" s="457" t="n"/>
+      <c r="AM6" s="457" t="n"/>
+      <c r="AN6" s="460" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1" s="329">
-      <c r="A7" s="388" t="inlineStr">
+      <c r="A7" s="512" t="inlineStr">
         <is>
           <t>SOP-402</t>
         </is>
       </c>
-      <c r="B7" s="389" t="inlineStr">
+      <c r="B7" s="513" t="inlineStr">
         <is>
           <t>SOP-402 — Xác minh vật liệu, truy xuất và phòng chống vật tư giả/không rõ nguồn gốc | HESEM QMS</t>
         </is>
       </c>
-      <c r="C7" s="389" t="inlineStr">
+      <c r="C7" s="514" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/01-SOPs/04-SOP-400/sop-402-material-verification-traceability-and-counterfeit-prevention.html</t>
         </is>
       </c>
-      <c r="D7" s="345" t="n"/>
-      <c r="E7" s="345" t="n"/>
-      <c r="F7" s="345" t="n"/>
-      <c r="G7" s="345" t="n"/>
-      <c r="H7" s="345" t="n"/>
-      <c r="I7" s="345" t="n"/>
-      <c r="J7" s="345" t="n"/>
-      <c r="K7" s="345" t="n"/>
-      <c r="L7" s="345" t="n"/>
-      <c r="M7" s="345" t="n"/>
-      <c r="N7" s="345" t="n"/>
-      <c r="O7" s="345" t="n"/>
-      <c r="P7" s="345" t="n"/>
-      <c r="Q7" s="345" t="n"/>
-      <c r="R7" s="345" t="n"/>
-      <c r="S7" s="345" t="n"/>
-      <c r="T7" s="345" t="n"/>
-      <c r="U7" s="345" t="n"/>
-      <c r="V7" s="345" t="n"/>
-      <c r="W7" s="345" t="n"/>
-      <c r="X7" s="345" t="n"/>
-      <c r="Y7" s="345" t="n"/>
-      <c r="Z7" s="345" t="n"/>
-      <c r="AA7" s="345" t="n"/>
-      <c r="AB7" s="345" t="n"/>
-      <c r="AC7" s="345" t="n"/>
-      <c r="AD7" s="345" t="n"/>
-      <c r="AE7" s="345" t="n"/>
-      <c r="AF7" s="345" t="n"/>
-      <c r="AG7" s="345" t="n"/>
-      <c r="AH7" s="345" t="n"/>
-      <c r="AI7" s="345" t="n"/>
-      <c r="AJ7" s="345" t="n"/>
-      <c r="AK7" s="345" t="n"/>
-      <c r="AL7" s="345" t="n"/>
-      <c r="AM7" s="345" t="n"/>
-      <c r="AN7" s="345" t="n"/>
+      <c r="D7" s="341" t="n"/>
+      <c r="E7" s="341" t="n"/>
+      <c r="F7" s="341" t="n"/>
+      <c r="G7" s="341" t="n"/>
+      <c r="H7" s="341" t="n"/>
+      <c r="I7" s="341" t="n"/>
+      <c r="J7" s="341" t="n"/>
+      <c r="K7" s="341" t="n"/>
+      <c r="L7" s="341" t="n"/>
+      <c r="M7" s="341" t="n"/>
+      <c r="N7" s="341" t="n"/>
+      <c r="O7" s="341" t="n"/>
+      <c r="P7" s="341" t="n"/>
+      <c r="Q7" s="341" t="n"/>
+      <c r="R7" s="341" t="n"/>
+      <c r="S7" s="341" t="n"/>
+      <c r="T7" s="341" t="n"/>
+      <c r="U7" s="341" t="n"/>
+      <c r="V7" s="341" t="n"/>
+      <c r="W7" s="341" t="n"/>
+      <c r="X7" s="341" t="n"/>
+      <c r="Y7" s="341" t="n"/>
+      <c r="Z7" s="341" t="n"/>
+      <c r="AA7" s="341" t="n"/>
+      <c r="AB7" s="341" t="n"/>
+      <c r="AC7" s="341" t="n"/>
+      <c r="AD7" s="341" t="n"/>
+      <c r="AE7" s="341" t="n"/>
+      <c r="AF7" s="341" t="n"/>
+      <c r="AG7" s="341" t="n"/>
+      <c r="AH7" s="341" t="n"/>
+      <c r="AI7" s="341" t="n"/>
+      <c r="AJ7" s="341" t="n"/>
+      <c r="AK7" s="341" t="n"/>
+      <c r="AL7" s="341" t="n"/>
+      <c r="AM7" s="341" t="n"/>
+      <c r="AN7" s="464" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1" s="329">
-      <c r="A8" s="352" t="inlineStr">
+      <c r="A8" s="461" t="inlineStr">
         <is>
           <t>ANNEX-PUR-001</t>
         </is>
       </c>
-      <c r="B8" s="390" t="inlineStr">
+      <c r="B8" s="462" t="inlineStr">
         <is>
           <t>ANNEX-PUR-001 — Mô hình rủi ro nhà cung cấp và phương pháp scorecard</t>
         </is>
       </c>
-      <c r="C8" s="390" t="inlineStr">
+      <c r="C8" s="515" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-001-supplier-risk-model-and-scorecard-method.html</t>
         </is>
       </c>
-      <c r="D8" s="381" t="n"/>
-      <c r="E8" s="381" t="n"/>
-      <c r="F8" s="381" t="n"/>
-      <c r="G8" s="381" t="n"/>
-      <c r="H8" s="381" t="n"/>
-      <c r="I8" s="381" t="n"/>
-      <c r="J8" s="381" t="n"/>
-      <c r="K8" s="381" t="n"/>
-      <c r="L8" s="381" t="n"/>
-      <c r="M8" s="381" t="n"/>
-      <c r="N8" s="381" t="n"/>
-      <c r="O8" s="381" t="n"/>
-      <c r="P8" s="381" t="n"/>
-      <c r="Q8" s="381" t="n"/>
-      <c r="R8" s="381" t="n"/>
-      <c r="S8" s="381" t="n"/>
-      <c r="T8" s="381" t="n"/>
-      <c r="U8" s="381" t="n"/>
-      <c r="V8" s="381" t="n"/>
-      <c r="W8" s="381" t="n"/>
-      <c r="X8" s="381" t="n"/>
-      <c r="Y8" s="381" t="n"/>
-      <c r="Z8" s="381" t="n"/>
-      <c r="AA8" s="381" t="n"/>
-      <c r="AB8" s="381" t="n"/>
-      <c r="AC8" s="381" t="n"/>
-      <c r="AD8" s="381" t="n"/>
-      <c r="AE8" s="381" t="n"/>
-      <c r="AF8" s="381" t="n"/>
-      <c r="AG8" s="381" t="n"/>
-      <c r="AH8" s="381" t="n"/>
-      <c r="AI8" s="381" t="n"/>
-      <c r="AJ8" s="381" t="n"/>
-      <c r="AK8" s="381" t="n"/>
-      <c r="AL8" s="381" t="n"/>
-      <c r="AM8" s="381" t="n"/>
-      <c r="AN8" s="381" t="n"/>
+      <c r="D8" s="353" t="n"/>
+      <c r="E8" s="353" t="n"/>
+      <c r="F8" s="353" t="n"/>
+      <c r="G8" s="353" t="n"/>
+      <c r="H8" s="353" t="n"/>
+      <c r="I8" s="353" t="n"/>
+      <c r="J8" s="353" t="n"/>
+      <c r="K8" s="353" t="n"/>
+      <c r="L8" s="353" t="n"/>
+      <c r="M8" s="353" t="n"/>
+      <c r="N8" s="353" t="n"/>
+      <c r="O8" s="353" t="n"/>
+      <c r="P8" s="353" t="n"/>
+      <c r="Q8" s="353" t="n"/>
+      <c r="R8" s="353" t="n"/>
+      <c r="S8" s="353" t="n"/>
+      <c r="T8" s="353" t="n"/>
+      <c r="U8" s="353" t="n"/>
+      <c r="V8" s="353" t="n"/>
+      <c r="W8" s="353" t="n"/>
+      <c r="X8" s="353" t="n"/>
+      <c r="Y8" s="353" t="n"/>
+      <c r="Z8" s="353" t="n"/>
+      <c r="AA8" s="353" t="n"/>
+      <c r="AB8" s="353" t="n"/>
+      <c r="AC8" s="353" t="n"/>
+      <c r="AD8" s="353" t="n"/>
+      <c r="AE8" s="353" t="n"/>
+      <c r="AF8" s="353" t="n"/>
+      <c r="AG8" s="353" t="n"/>
+      <c r="AH8" s="353" t="n"/>
+      <c r="AI8" s="353" t="n"/>
+      <c r="AJ8" s="353" t="n"/>
+      <c r="AK8" s="353" t="n"/>
+      <c r="AL8" s="353" t="n"/>
+      <c r="AM8" s="353" t="n"/>
+      <c r="AN8" s="516" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1" s="329">
-      <c r="A9" s="352" t="inlineStr">
+      <c r="A9" s="461" t="inlineStr">
         <is>
           <t>ANNEX-PUR-002</t>
         </is>
       </c>
-      <c r="B9" s="390" t="inlineStr">
+      <c r="B9" s="462" t="inlineStr">
         <is>
           <t>ANNEX-PUR-002 — Gói kiểm soát outsource / special process / cert flow-down</t>
         </is>
       </c>
-      <c r="C9" s="390" t="inlineStr">
+      <c r="C9" s="515" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-002-outsource-special-process-pack.html</t>
         </is>
       </c>
-      <c r="D9" s="381" t="n"/>
-      <c r="E9" s="381" t="n"/>
-      <c r="F9" s="381" t="n"/>
-      <c r="G9" s="381" t="n"/>
-      <c r="H9" s="381" t="n"/>
-      <c r="I9" s="381" t="n"/>
-      <c r="J9" s="381" t="n"/>
-      <c r="K9" s="381" t="n"/>
-      <c r="L9" s="381" t="n"/>
-      <c r="M9" s="381" t="n"/>
-      <c r="N9" s="381" t="n"/>
-      <c r="O9" s="381" t="n"/>
-      <c r="P9" s="381" t="n"/>
-      <c r="Q9" s="381" t="n"/>
-      <c r="R9" s="381" t="n"/>
-      <c r="S9" s="381" t="n"/>
-      <c r="T9" s="381" t="n"/>
-      <c r="U9" s="381" t="n"/>
-      <c r="V9" s="381" t="n"/>
-      <c r="W9" s="381" t="n"/>
-      <c r="X9" s="381" t="n"/>
-      <c r="Y9" s="381" t="n"/>
-      <c r="Z9" s="381" t="n"/>
-      <c r="AA9" s="381" t="n"/>
-      <c r="AB9" s="381" t="n"/>
-      <c r="AC9" s="381" t="n"/>
-      <c r="AD9" s="381" t="n"/>
-      <c r="AE9" s="381" t="n"/>
-      <c r="AF9" s="381" t="n"/>
-      <c r="AG9" s="381" t="n"/>
-      <c r="AH9" s="381" t="n"/>
-      <c r="AI9" s="381" t="n"/>
-      <c r="AJ9" s="381" t="n"/>
-      <c r="AK9" s="381" t="n"/>
-      <c r="AL9" s="381" t="n"/>
-      <c r="AM9" s="381" t="n"/>
-      <c r="AN9" s="381" t="n"/>
+      <c r="D9" s="353" t="n"/>
+      <c r="E9" s="353" t="n"/>
+      <c r="F9" s="353" t="n"/>
+      <c r="G9" s="353" t="n"/>
+      <c r="H9" s="353" t="n"/>
+      <c r="I9" s="353" t="n"/>
+      <c r="J9" s="353" t="n"/>
+      <c r="K9" s="353" t="n"/>
+      <c r="L9" s="353" t="n"/>
+      <c r="M9" s="353" t="n"/>
+      <c r="N9" s="353" t="n"/>
+      <c r="O9" s="353" t="n"/>
+      <c r="P9" s="353" t="n"/>
+      <c r="Q9" s="353" t="n"/>
+      <c r="R9" s="353" t="n"/>
+      <c r="S9" s="353" t="n"/>
+      <c r="T9" s="353" t="n"/>
+      <c r="U9" s="353" t="n"/>
+      <c r="V9" s="353" t="n"/>
+      <c r="W9" s="353" t="n"/>
+      <c r="X9" s="353" t="n"/>
+      <c r="Y9" s="353" t="n"/>
+      <c r="Z9" s="353" t="n"/>
+      <c r="AA9" s="353" t="n"/>
+      <c r="AB9" s="353" t="n"/>
+      <c r="AC9" s="353" t="n"/>
+      <c r="AD9" s="353" t="n"/>
+      <c r="AE9" s="353" t="n"/>
+      <c r="AF9" s="353" t="n"/>
+      <c r="AG9" s="353" t="n"/>
+      <c r="AH9" s="353" t="n"/>
+      <c r="AI9" s="353" t="n"/>
+      <c r="AJ9" s="353" t="n"/>
+      <c r="AK9" s="353" t="n"/>
+      <c r="AL9" s="353" t="n"/>
+      <c r="AM9" s="353" t="n"/>
+      <c r="AN9" s="516" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1" s="329">
-      <c r="A10" s="352" t="inlineStr">
+      <c r="A10" s="461" t="inlineStr">
         <is>
           <t>ANNEX-PUR-003</t>
         </is>
       </c>
-      <c r="B10" s="390" t="inlineStr">
+      <c r="B10" s="462" t="inlineStr">
         <is>
           <t>ANNEX-PUR-003 — Approved processor list, scope approval và rule tạm ngưng</t>
         </is>
       </c>
-      <c r="C10" s="390" t="inlineStr">
+      <c r="C10" s="515" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-003-approved-processor-list.html</t>
         </is>
       </c>
-      <c r="D10" s="381" t="n"/>
-      <c r="E10" s="381" t="n"/>
-      <c r="F10" s="381" t="n"/>
-      <c r="G10" s="381" t="n"/>
-      <c r="H10" s="381" t="n"/>
-      <c r="I10" s="381" t="n"/>
-      <c r="J10" s="381" t="n"/>
-      <c r="K10" s="381" t="n"/>
-      <c r="L10" s="381" t="n"/>
-      <c r="M10" s="381" t="n"/>
-      <c r="N10" s="381" t="n"/>
-      <c r="O10" s="381" t="n"/>
-      <c r="P10" s="381" t="n"/>
-      <c r="Q10" s="381" t="n"/>
-      <c r="R10" s="381" t="n"/>
-      <c r="S10" s="381" t="n"/>
-      <c r="T10" s="381" t="n"/>
-      <c r="U10" s="381" t="n"/>
-      <c r="V10" s="381" t="n"/>
-      <c r="W10" s="381" t="n"/>
-      <c r="X10" s="381" t="n"/>
-      <c r="Y10" s="381" t="n"/>
-      <c r="Z10" s="381" t="n"/>
-      <c r="AA10" s="381" t="n"/>
-      <c r="AB10" s="381" t="n"/>
-      <c r="AC10" s="381" t="n"/>
-      <c r="AD10" s="381" t="n"/>
-      <c r="AE10" s="381" t="n"/>
-      <c r="AF10" s="381" t="n"/>
-      <c r="AG10" s="381" t="n"/>
-      <c r="AH10" s="381" t="n"/>
-      <c r="AI10" s="381" t="n"/>
-      <c r="AJ10" s="381" t="n"/>
-      <c r="AK10" s="381" t="n"/>
-      <c r="AL10" s="381" t="n"/>
-      <c r="AM10" s="381" t="n"/>
-      <c r="AN10" s="381" t="n"/>
+      <c r="D10" s="353" t="n"/>
+      <c r="E10" s="353" t="n"/>
+      <c r="F10" s="353" t="n"/>
+      <c r="G10" s="353" t="n"/>
+      <c r="H10" s="353" t="n"/>
+      <c r="I10" s="353" t="n"/>
+      <c r="J10" s="353" t="n"/>
+      <c r="K10" s="353" t="n"/>
+      <c r="L10" s="353" t="n"/>
+      <c r="M10" s="353" t="n"/>
+      <c r="N10" s="353" t="n"/>
+      <c r="O10" s="353" t="n"/>
+      <c r="P10" s="353" t="n"/>
+      <c r="Q10" s="353" t="n"/>
+      <c r="R10" s="353" t="n"/>
+      <c r="S10" s="353" t="n"/>
+      <c r="T10" s="353" t="n"/>
+      <c r="U10" s="353" t="n"/>
+      <c r="V10" s="353" t="n"/>
+      <c r="W10" s="353" t="n"/>
+      <c r="X10" s="353" t="n"/>
+      <c r="Y10" s="353" t="n"/>
+      <c r="Z10" s="353" t="n"/>
+      <c r="AA10" s="353" t="n"/>
+      <c r="AB10" s="353" t="n"/>
+      <c r="AC10" s="353" t="n"/>
+      <c r="AD10" s="353" t="n"/>
+      <c r="AE10" s="353" t="n"/>
+      <c r="AF10" s="353" t="n"/>
+      <c r="AG10" s="353" t="n"/>
+      <c r="AH10" s="353" t="n"/>
+      <c r="AI10" s="353" t="n"/>
+      <c r="AJ10" s="353" t="n"/>
+      <c r="AK10" s="353" t="n"/>
+      <c r="AL10" s="353" t="n"/>
+      <c r="AM10" s="353" t="n"/>
+      <c r="AN10" s="516" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1" s="329">
-      <c r="A11" s="352" t="inlineStr">
+      <c r="A11" s="461" t="inlineStr">
         <is>
           <t>ANNEX-ENG-002</t>
         </is>
       </c>
-      <c r="B11" s="390" t="inlineStr">
+      <c r="B11" s="462" t="inlineStr">
         <is>
           <t>ANNEX-ENG-002 — Approved materials list, source restriction và rule thay thế</t>
         </is>
       </c>
-      <c r="C11" s="390" t="inlineStr">
+      <c r="C11" s="515" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-eng-002-approved-materials-list.html</t>
         </is>
       </c>
-      <c r="D11" s="381" t="n"/>
-      <c r="E11" s="381" t="n"/>
-      <c r="F11" s="381" t="n"/>
-      <c r="G11" s="381" t="n"/>
-      <c r="H11" s="381" t="n"/>
-      <c r="I11" s="381" t="n"/>
-      <c r="J11" s="381" t="n"/>
-      <c r="K11" s="381" t="n"/>
-      <c r="L11" s="381" t="n"/>
-      <c r="M11" s="381" t="n"/>
-      <c r="N11" s="381" t="n"/>
-      <c r="O11" s="381" t="n"/>
-      <c r="P11" s="381" t="n"/>
-      <c r="Q11" s="381" t="n"/>
-      <c r="R11" s="381" t="n"/>
-      <c r="S11" s="381" t="n"/>
-      <c r="T11" s="381" t="n"/>
-      <c r="U11" s="381" t="n"/>
-      <c r="V11" s="381" t="n"/>
-      <c r="W11" s="381" t="n"/>
-      <c r="X11" s="381" t="n"/>
-      <c r="Y11" s="381" t="n"/>
-      <c r="Z11" s="381" t="n"/>
-      <c r="AA11" s="381" t="n"/>
-      <c r="AB11" s="381" t="n"/>
-      <c r="AC11" s="381" t="n"/>
-      <c r="AD11" s="381" t="n"/>
-      <c r="AE11" s="381" t="n"/>
-      <c r="AF11" s="381" t="n"/>
-      <c r="AG11" s="381" t="n"/>
-      <c r="AH11" s="381" t="n"/>
-      <c r="AI11" s="381" t="n"/>
-      <c r="AJ11" s="381" t="n"/>
-      <c r="AK11" s="381" t="n"/>
-      <c r="AL11" s="381" t="n"/>
-      <c r="AM11" s="381" t="n"/>
-      <c r="AN11" s="381" t="n"/>
+      <c r="D11" s="353" t="n"/>
+      <c r="E11" s="353" t="n"/>
+      <c r="F11" s="353" t="n"/>
+      <c r="G11" s="353" t="n"/>
+      <c r="H11" s="353" t="n"/>
+      <c r="I11" s="353" t="n"/>
+      <c r="J11" s="353" t="n"/>
+      <c r="K11" s="353" t="n"/>
+      <c r="L11" s="353" t="n"/>
+      <c r="M11" s="353" t="n"/>
+      <c r="N11" s="353" t="n"/>
+      <c r="O11" s="353" t="n"/>
+      <c r="P11" s="353" t="n"/>
+      <c r="Q11" s="353" t="n"/>
+      <c r="R11" s="353" t="n"/>
+      <c r="S11" s="353" t="n"/>
+      <c r="T11" s="353" t="n"/>
+      <c r="U11" s="353" t="n"/>
+      <c r="V11" s="353" t="n"/>
+      <c r="W11" s="353" t="n"/>
+      <c r="X11" s="353" t="n"/>
+      <c r="Y11" s="353" t="n"/>
+      <c r="Z11" s="353" t="n"/>
+      <c r="AA11" s="353" t="n"/>
+      <c r="AB11" s="353" t="n"/>
+      <c r="AC11" s="353" t="n"/>
+      <c r="AD11" s="353" t="n"/>
+      <c r="AE11" s="353" t="n"/>
+      <c r="AF11" s="353" t="n"/>
+      <c r="AG11" s="353" t="n"/>
+      <c r="AH11" s="353" t="n"/>
+      <c r="AI11" s="353" t="n"/>
+      <c r="AJ11" s="353" t="n"/>
+      <c r="AK11" s="353" t="n"/>
+      <c r="AL11" s="353" t="n"/>
+      <c r="AM11" s="353" t="n"/>
+      <c r="AN11" s="516" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1" s="329">
-      <c r="A12" s="352" t="inlineStr">
+      <c r="A12" s="461" t="inlineStr">
         <is>
           <t>Open When</t>
         </is>
       </c>
-      <c r="B12" s="390" t="inlineStr">
+      <c r="B12" s="462" t="inlineStr">
         <is>
           <t>Open immediately when the event, request, issue, change, complaint, risk or incident is detected or formally raised.</t>
         </is>
       </c>
-      <c r="C12" s="390" t="inlineStr">
+      <c r="C12" s="515" t="inlineStr">
         <is>
           <t>Operational trigger</t>
         </is>
       </c>
-      <c r="D12" s="381" t="n"/>
-      <c r="E12" s="381" t="n"/>
-      <c r="F12" s="381" t="n"/>
-      <c r="G12" s="381" t="n"/>
-      <c r="H12" s="381" t="n"/>
-      <c r="I12" s="381" t="n"/>
-      <c r="J12" s="381" t="n"/>
-      <c r="K12" s="381" t="n"/>
-      <c r="L12" s="381" t="n"/>
-      <c r="M12" s="381" t="n"/>
-      <c r="N12" s="381" t="n"/>
-      <c r="O12" s="381" t="n"/>
-      <c r="P12" s="381" t="n"/>
-      <c r="Q12" s="381" t="n"/>
-      <c r="R12" s="381" t="n"/>
-      <c r="S12" s="381" t="n"/>
-      <c r="T12" s="381" t="n"/>
-      <c r="U12" s="381" t="n"/>
-      <c r="V12" s="381" t="n"/>
-      <c r="W12" s="381" t="n"/>
-      <c r="X12" s="381" t="n"/>
-      <c r="Y12" s="381" t="n"/>
-      <c r="Z12" s="381" t="n"/>
-      <c r="AA12" s="381" t="n"/>
-      <c r="AB12" s="381" t="n"/>
-      <c r="AC12" s="381" t="n"/>
-      <c r="AD12" s="381" t="n"/>
-      <c r="AE12" s="381" t="n"/>
-      <c r="AF12" s="381" t="n"/>
-      <c r="AG12" s="381" t="n"/>
-      <c r="AH12" s="381" t="n"/>
-      <c r="AI12" s="381" t="n"/>
-      <c r="AJ12" s="381" t="n"/>
-      <c r="AK12" s="381" t="n"/>
-      <c r="AL12" s="381" t="n"/>
-      <c r="AM12" s="381" t="n"/>
-      <c r="AN12" s="381" t="n"/>
+      <c r="D12" s="353" t="n"/>
+      <c r="E12" s="353" t="n"/>
+      <c r="F12" s="353" t="n"/>
+      <c r="G12" s="353" t="n"/>
+      <c r="H12" s="353" t="n"/>
+      <c r="I12" s="353" t="n"/>
+      <c r="J12" s="353" t="n"/>
+      <c r="K12" s="353" t="n"/>
+      <c r="L12" s="353" t="n"/>
+      <c r="M12" s="353" t="n"/>
+      <c r="N12" s="353" t="n"/>
+      <c r="O12" s="353" t="n"/>
+      <c r="P12" s="353" t="n"/>
+      <c r="Q12" s="353" t="n"/>
+      <c r="R12" s="353" t="n"/>
+      <c r="S12" s="353" t="n"/>
+      <c r="T12" s="353" t="n"/>
+      <c r="U12" s="353" t="n"/>
+      <c r="V12" s="353" t="n"/>
+      <c r="W12" s="353" t="n"/>
+      <c r="X12" s="353" t="n"/>
+      <c r="Y12" s="353" t="n"/>
+      <c r="Z12" s="353" t="n"/>
+      <c r="AA12" s="353" t="n"/>
+      <c r="AB12" s="353" t="n"/>
+      <c r="AC12" s="353" t="n"/>
+      <c r="AD12" s="353" t="n"/>
+      <c r="AE12" s="353" t="n"/>
+      <c r="AF12" s="353" t="n"/>
+      <c r="AG12" s="353" t="n"/>
+      <c r="AH12" s="353" t="n"/>
+      <c r="AI12" s="353" t="n"/>
+      <c r="AJ12" s="353" t="n"/>
+      <c r="AK12" s="353" t="n"/>
+      <c r="AL12" s="353" t="n"/>
+      <c r="AM12" s="353" t="n"/>
+      <c r="AN12" s="516" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1" s="329">
-      <c r="A13" s="381" t="inlineStr">
+      <c r="A13" s="522" t="inlineStr">
         <is>
           <t>Close When</t>
         </is>
       </c>
-      <c r="B13" s="381" t="inlineStr">
+      <c r="B13" s="523" t="inlineStr">
         <is>
           <t>Close when the final decision, final owner, final disposition and required follow-up actions are all recorded and the evidence package is complete.</t>
         </is>
       </c>
-      <c r="C13" s="381" t="inlineStr">
+      <c r="C13" s="518" t="inlineStr">
         <is>
           <t>Release / closure rule</t>
         </is>
       </c>
-      <c r="D13" s="381" t="n"/>
-      <c r="E13" s="381" t="n"/>
-      <c r="F13" s="381" t="n"/>
-      <c r="G13" s="381" t="n"/>
-      <c r="H13" s="381" t="n"/>
-      <c r="I13" s="381" t="n"/>
-      <c r="J13" s="381" t="n"/>
-      <c r="K13" s="381" t="n"/>
-      <c r="L13" s="381" t="n"/>
-      <c r="M13" s="381" t="n"/>
-      <c r="N13" s="381" t="n"/>
-      <c r="O13" s="381" t="n"/>
-      <c r="P13" s="381" t="n"/>
-      <c r="Q13" s="381" t="n"/>
-      <c r="R13" s="381" t="n"/>
-      <c r="S13" s="381" t="n"/>
-      <c r="T13" s="381" t="n"/>
-      <c r="U13" s="381" t="n"/>
-      <c r="V13" s="381" t="n"/>
-      <c r="W13" s="381" t="n"/>
-      <c r="X13" s="381" t="n"/>
-      <c r="Y13" s="381" t="n"/>
-      <c r="Z13" s="381" t="n"/>
-      <c r="AA13" s="381" t="n"/>
-      <c r="AB13" s="381" t="n"/>
-      <c r="AC13" s="381" t="n"/>
-      <c r="AD13" s="381" t="n"/>
-      <c r="AE13" s="381" t="n"/>
-      <c r="AF13" s="381" t="n"/>
-      <c r="AG13" s="381" t="n"/>
-      <c r="AH13" s="381" t="n"/>
-      <c r="AI13" s="381" t="n"/>
-      <c r="AJ13" s="381" t="n"/>
-      <c r="AK13" s="381" t="n"/>
-      <c r="AL13" s="381" t="n"/>
-      <c r="AM13" s="381" t="n"/>
-      <c r="AN13" s="381" t="n"/>
+      <c r="D13" s="518" t="n"/>
+      <c r="E13" s="518" t="n"/>
+      <c r="F13" s="518" t="n"/>
+      <c r="G13" s="518" t="n"/>
+      <c r="H13" s="518" t="n"/>
+      <c r="I13" s="518" t="n"/>
+      <c r="J13" s="518" t="n"/>
+      <c r="K13" s="518" t="n"/>
+      <c r="L13" s="518" t="n"/>
+      <c r="M13" s="518" t="n"/>
+      <c r="N13" s="518" t="n"/>
+      <c r="O13" s="518" t="n"/>
+      <c r="P13" s="518" t="n"/>
+      <c r="Q13" s="518" t="n"/>
+      <c r="R13" s="518" t="n"/>
+      <c r="S13" s="518" t="n"/>
+      <c r="T13" s="518" t="n"/>
+      <c r="U13" s="518" t="n"/>
+      <c r="V13" s="518" t="n"/>
+      <c r="W13" s="518" t="n"/>
+      <c r="X13" s="518" t="n"/>
+      <c r="Y13" s="518" t="n"/>
+      <c r="Z13" s="518" t="n"/>
+      <c r="AA13" s="518" t="n"/>
+      <c r="AB13" s="518" t="n"/>
+      <c r="AC13" s="518" t="n"/>
+      <c r="AD13" s="518" t="n"/>
+      <c r="AE13" s="518" t="n"/>
+      <c r="AF13" s="518" t="n"/>
+      <c r="AG13" s="518" t="n"/>
+      <c r="AH13" s="518" t="n"/>
+      <c r="AI13" s="518" t="n"/>
+      <c r="AJ13" s="518" t="n"/>
+      <c r="AK13" s="518" t="n"/>
+      <c r="AL13" s="518" t="n"/>
+      <c r="AM13" s="518" t="n"/>
+      <c r="AN13" s="519" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1" s="329"/>
     <row r="15" ht="20" customHeight="1" s="329"/>
@@ -9079,6 +9907,7 @@
   </mergeCells>
   <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -9133,677 +9962,683 @@
     <col width="2.33" customWidth="1" style="329" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="329">
-      <c r="A1" s="386" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" s="329">
+      <c r="A1" s="497" t="inlineStr">
         <is>
           <t>Evidence Reference / Attachment Guidance</t>
         </is>
       </c>
-      <c r="B1" s="409" t="n"/>
-      <c r="C1" s="409" t="n"/>
-      <c r="D1" s="409" t="n"/>
-      <c r="E1" s="409" t="n"/>
-      <c r="F1" s="409" t="n"/>
-      <c r="G1" s="410" t="n"/>
-      <c r="H1" s="345" t="n"/>
-      <c r="I1" s="345" t="n"/>
-      <c r="J1" s="345" t="n"/>
-      <c r="K1" s="345" t="n"/>
-      <c r="L1" s="345" t="n"/>
-      <c r="M1" s="345" t="n"/>
-      <c r="N1" s="345" t="n"/>
-      <c r="O1" s="345" t="n"/>
-      <c r="P1" s="345" t="n"/>
-      <c r="Q1" s="345" t="n"/>
-      <c r="R1" s="345" t="n"/>
-      <c r="S1" s="345" t="n"/>
-      <c r="T1" s="345" t="n"/>
-      <c r="U1" s="345" t="n"/>
-      <c r="V1" s="345" t="n"/>
-      <c r="W1" s="345" t="n"/>
-      <c r="X1" s="345" t="n"/>
-      <c r="Y1" s="345" t="n"/>
-      <c r="Z1" s="345" t="n"/>
-      <c r="AA1" s="345" t="n"/>
-      <c r="AB1" s="345" t="n"/>
-      <c r="AC1" s="345" t="n"/>
-      <c r="AD1" s="345" t="n"/>
-      <c r="AE1" s="345" t="n"/>
-      <c r="AF1" s="345" t="n"/>
-      <c r="AG1" s="345" t="n"/>
-      <c r="AH1" s="345" t="n"/>
-      <c r="AI1" s="345" t="n"/>
-      <c r="AJ1" s="345" t="n"/>
-      <c r="AK1" s="345" t="n"/>
-      <c r="AL1" s="345" t="n"/>
-      <c r="AM1" s="345" t="n"/>
-      <c r="AN1" s="345" t="n"/>
+      <c r="B1" s="415" t="n"/>
+      <c r="C1" s="415" t="n"/>
+      <c r="D1" s="415" t="n"/>
+      <c r="E1" s="415" t="n"/>
+      <c r="F1" s="415" t="n"/>
+      <c r="G1" s="415" t="n"/>
+      <c r="H1" s="498" t="n"/>
+      <c r="I1" s="417" t="n"/>
+      <c r="J1" s="418" t="n"/>
+      <c r="K1" s="418" t="n"/>
+      <c r="L1" s="418" t="n"/>
+      <c r="M1" s="418" t="n"/>
+      <c r="N1" s="418" t="n"/>
+      <c r="O1" s="418" t="n"/>
+      <c r="P1" s="418" t="n"/>
+      <c r="Q1" s="418" t="n"/>
+      <c r="R1" s="418" t="n"/>
+      <c r="S1" s="418" t="n"/>
+      <c r="T1" s="418" t="n"/>
+      <c r="U1" s="418" t="n"/>
+      <c r="V1" s="418" t="n"/>
+      <c r="W1" s="418" t="n"/>
+      <c r="X1" s="418" t="n"/>
+      <c r="Y1" s="418" t="n"/>
+      <c r="Z1" s="418" t="n"/>
+      <c r="AA1" s="418" t="n"/>
+      <c r="AB1" s="418" t="n"/>
+      <c r="AC1" s="418" t="n"/>
+      <c r="AD1" s="419" t="n"/>
+      <c r="AE1" s="420" t="n"/>
+      <c r="AF1" s="421" t="n"/>
+      <c r="AG1" s="421" t="n"/>
+      <c r="AH1" s="422" t="n"/>
+      <c r="AI1" s="423" t="n"/>
+      <c r="AJ1" s="424" t="n"/>
+      <c r="AK1" s="424" t="n"/>
+      <c r="AL1" s="424" t="n"/>
+      <c r="AM1" s="424" t="n"/>
+      <c r="AN1" s="425" t="n"/>
     </row>
-    <row r="2" ht="18" customHeight="1" s="329">
-      <c r="A2" s="335" t="inlineStr">
+    <row r="2" ht="15" customHeight="1" s="329">
+      <c r="A2" s="499" t="inlineStr">
         <is>
           <t>Use controlled evidence package references; do not free-type vague placeholders.</t>
         </is>
       </c>
-      <c r="H2" s="345" t="n"/>
-      <c r="I2" s="345" t="n"/>
-      <c r="J2" s="345" t="n"/>
-      <c r="K2" s="345" t="n"/>
-      <c r="L2" s="345" t="n"/>
-      <c r="M2" s="345" t="n"/>
-      <c r="N2" s="345" t="n"/>
-      <c r="O2" s="345" t="n"/>
-      <c r="P2" s="345" t="n"/>
-      <c r="Q2" s="345" t="n"/>
-      <c r="R2" s="345" t="n"/>
-      <c r="S2" s="345" t="n"/>
-      <c r="T2" s="345" t="n"/>
-      <c r="U2" s="345" t="n"/>
-      <c r="V2" s="345" t="n"/>
-      <c r="W2" s="345" t="n"/>
-      <c r="X2" s="345" t="n"/>
-      <c r="Y2" s="345" t="n"/>
-      <c r="Z2" s="345" t="n"/>
-      <c r="AA2" s="345" t="n"/>
-      <c r="AB2" s="345" t="n"/>
-      <c r="AC2" s="345" t="n"/>
-      <c r="AD2" s="345" t="n"/>
-      <c r="AE2" s="345" t="n"/>
-      <c r="AF2" s="345" t="n"/>
-      <c r="AG2" s="345" t="n"/>
-      <c r="AH2" s="345" t="n"/>
-      <c r="AI2" s="345" t="n"/>
-      <c r="AJ2" s="345" t="n"/>
-      <c r="AK2" s="345" t="n"/>
-      <c r="AL2" s="345" t="n"/>
-      <c r="AM2" s="345" t="n"/>
-      <c r="AN2" s="345" t="n"/>
+      <c r="B2" s="25" t="n"/>
+      <c r="C2" s="25" t="n"/>
+      <c r="D2" s="25" t="n"/>
+      <c r="E2" s="25" t="n"/>
+      <c r="F2" s="25" t="n"/>
+      <c r="G2" s="25" t="n"/>
+      <c r="H2" s="500" t="n"/>
+      <c r="I2" s="428" t="n"/>
+      <c r="J2" s="429" t="n"/>
+      <c r="K2" s="429" t="n"/>
+      <c r="L2" s="429" t="n"/>
+      <c r="M2" s="429" t="n"/>
+      <c r="N2" s="429" t="n"/>
+      <c r="O2" s="429" t="n"/>
+      <c r="P2" s="429" t="n"/>
+      <c r="Q2" s="429" t="n"/>
+      <c r="R2" s="429" t="n"/>
+      <c r="S2" s="429" t="n"/>
+      <c r="T2" s="429" t="n"/>
+      <c r="U2" s="429" t="n"/>
+      <c r="V2" s="429" t="n"/>
+      <c r="W2" s="429" t="n"/>
+      <c r="X2" s="429" t="n"/>
+      <c r="Y2" s="429" t="n"/>
+      <c r="Z2" s="429" t="n"/>
+      <c r="AA2" s="429" t="n"/>
+      <c r="AB2" s="429" t="n"/>
+      <c r="AC2" s="429" t="n"/>
+      <c r="AD2" s="430" t="n"/>
+      <c r="AE2" s="431" t="n"/>
+      <c r="AF2" s="432" t="n"/>
+      <c r="AG2" s="432" t="n"/>
+      <c r="AH2" s="433" t="n"/>
+      <c r="AI2" s="434" t="n"/>
+      <c r="AJ2" s="435" t="n"/>
+      <c r="AK2" s="435" t="n"/>
+      <c r="AL2" s="435" t="n"/>
+      <c r="AM2" s="435" t="n"/>
+      <c r="AN2" s="436" t="n"/>
     </row>
-    <row r="3" ht="18" customHeight="1" s="329">
-      <c r="A3" s="345" t="n"/>
-      <c r="B3" s="345" t="n"/>
-      <c r="C3" s="345" t="n"/>
-      <c r="D3" s="345" t="n"/>
-      <c r="E3" s="345" t="n"/>
-      <c r="F3" s="345" t="n"/>
-      <c r="G3" s="345" t="n"/>
-      <c r="H3" s="345" t="n"/>
-      <c r="I3" s="345" t="n"/>
-      <c r="J3" s="345" t="n"/>
-      <c r="K3" s="345" t="n"/>
-      <c r="L3" s="345" t="n"/>
-      <c r="M3" s="345" t="n"/>
-      <c r="N3" s="345" t="n"/>
-      <c r="O3" s="345" t="n"/>
-      <c r="P3" s="345" t="n"/>
-      <c r="Q3" s="345" t="n"/>
-      <c r="R3" s="345" t="n"/>
-      <c r="S3" s="345" t="n"/>
-      <c r="T3" s="345" t="n"/>
-      <c r="U3" s="345" t="n"/>
-      <c r="V3" s="345" t="n"/>
-      <c r="W3" s="345" t="n"/>
-      <c r="X3" s="345" t="n"/>
-      <c r="Y3" s="345" t="n"/>
-      <c r="Z3" s="345" t="n"/>
-      <c r="AA3" s="345" t="n"/>
-      <c r="AB3" s="345" t="n"/>
-      <c r="AC3" s="345" t="n"/>
-      <c r="AD3" s="345" t="n"/>
-      <c r="AE3" s="345" t="n"/>
-      <c r="AF3" s="345" t="n"/>
-      <c r="AG3" s="345" t="n"/>
-      <c r="AH3" s="345" t="n"/>
-      <c r="AI3" s="345" t="n"/>
-      <c r="AJ3" s="345" t="n"/>
-      <c r="AK3" s="345" t="n"/>
-      <c r="AL3" s="345" t="n"/>
-      <c r="AM3" s="345" t="n"/>
-      <c r="AN3" s="345" t="n"/>
+    <row r="3" ht="15" customHeight="1" s="329">
+      <c r="A3" s="501" t="n"/>
+      <c r="B3" s="502" t="n"/>
+      <c r="C3" s="502" t="n"/>
+      <c r="D3" s="502" t="n"/>
+      <c r="E3" s="502" t="n"/>
+      <c r="F3" s="502" t="n"/>
+      <c r="G3" s="502" t="n"/>
+      <c r="H3" s="500" t="n"/>
+      <c r="I3" s="428" t="n"/>
+      <c r="J3" s="429" t="n"/>
+      <c r="K3" s="429" t="n"/>
+      <c r="L3" s="429" t="n"/>
+      <c r="M3" s="429" t="n"/>
+      <c r="N3" s="429" t="n"/>
+      <c r="O3" s="429" t="n"/>
+      <c r="P3" s="429" t="n"/>
+      <c r="Q3" s="429" t="n"/>
+      <c r="R3" s="429" t="n"/>
+      <c r="S3" s="429" t="n"/>
+      <c r="T3" s="429" t="n"/>
+      <c r="U3" s="429" t="n"/>
+      <c r="V3" s="429" t="n"/>
+      <c r="W3" s="429" t="n"/>
+      <c r="X3" s="429" t="n"/>
+      <c r="Y3" s="429" t="n"/>
+      <c r="Z3" s="429" t="n"/>
+      <c r="AA3" s="429" t="n"/>
+      <c r="AB3" s="429" t="n"/>
+      <c r="AC3" s="429" t="n"/>
+      <c r="AD3" s="430" t="n"/>
+      <c r="AE3" s="431" t="n"/>
+      <c r="AF3" s="432" t="n"/>
+      <c r="AG3" s="432" t="n"/>
+      <c r="AH3" s="433" t="n"/>
+      <c r="AI3" s="434" t="n"/>
+      <c r="AJ3" s="435" t="n"/>
+      <c r="AK3" s="435" t="n"/>
+      <c r="AL3" s="435" t="n"/>
+      <c r="AM3" s="435" t="n"/>
+      <c r="AN3" s="436" t="n"/>
     </row>
-    <row r="4" ht="20" customHeight="1" s="329">
-      <c r="A4" s="387" t="inlineStr">
+    <row r="4" ht="15" customHeight="1" s="329">
+      <c r="A4" s="503" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B4" s="387" t="inlineStr">
+      <c r="B4" s="504" t="inlineStr">
         <is>
           <t>Value / Reference</t>
         </is>
       </c>
-      <c r="C4" s="387" t="inlineStr">
+      <c r="C4" s="504" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="D4" s="345" t="n"/>
-      <c r="E4" s="345" t="n"/>
-      <c r="F4" s="345" t="n"/>
-      <c r="G4" s="345" t="n"/>
-      <c r="H4" s="345" t="n"/>
-      <c r="I4" s="345" t="n"/>
-      <c r="J4" s="345" t="n"/>
-      <c r="K4" s="345" t="n"/>
-      <c r="L4" s="345" t="n"/>
-      <c r="M4" s="345" t="n"/>
-      <c r="N4" s="345" t="n"/>
-      <c r="O4" s="345" t="n"/>
-      <c r="P4" s="345" t="n"/>
-      <c r="Q4" s="345" t="n"/>
-      <c r="R4" s="345" t="n"/>
-      <c r="S4" s="345" t="n"/>
-      <c r="T4" s="345" t="n"/>
-      <c r="U4" s="345" t="n"/>
-      <c r="V4" s="345" t="n"/>
-      <c r="W4" s="345" t="n"/>
-      <c r="X4" s="345" t="n"/>
-      <c r="Y4" s="345" t="n"/>
-      <c r="Z4" s="345" t="n"/>
-      <c r="AA4" s="345" t="n"/>
-      <c r="AB4" s="345" t="n"/>
-      <c r="AC4" s="345" t="n"/>
-      <c r="AD4" s="345" t="n"/>
-      <c r="AE4" s="345" t="n"/>
-      <c r="AF4" s="345" t="n"/>
-      <c r="AG4" s="345" t="n"/>
-      <c r="AH4" s="345" t="n"/>
-      <c r="AI4" s="345" t="n"/>
-      <c r="AJ4" s="345" t="n"/>
-      <c r="AK4" s="345" t="n"/>
-      <c r="AL4" s="345" t="n"/>
-      <c r="AM4" s="345" t="n"/>
-      <c r="AN4" s="345" t="n"/>
+      <c r="D4" s="502" t="n"/>
+      <c r="E4" s="502" t="n"/>
+      <c r="F4" s="502" t="n"/>
+      <c r="G4" s="502" t="n"/>
+      <c r="H4" s="500" t="n"/>
+      <c r="I4" s="437" t="n"/>
+      <c r="J4" s="438" t="n"/>
+      <c r="K4" s="438" t="n"/>
+      <c r="L4" s="438" t="n"/>
+      <c r="M4" s="438" t="n"/>
+      <c r="N4" s="438" t="n"/>
+      <c r="O4" s="438" t="n"/>
+      <c r="P4" s="438" t="n"/>
+      <c r="Q4" s="438" t="n"/>
+      <c r="R4" s="438" t="n"/>
+      <c r="S4" s="438" t="n"/>
+      <c r="T4" s="438" t="n"/>
+      <c r="U4" s="438" t="n"/>
+      <c r="V4" s="438" t="n"/>
+      <c r="W4" s="438" t="n"/>
+      <c r="X4" s="438" t="n"/>
+      <c r="Y4" s="438" t="n"/>
+      <c r="Z4" s="438" t="n"/>
+      <c r="AA4" s="438" t="n"/>
+      <c r="AB4" s="438" t="n"/>
+      <c r="AC4" s="438" t="n"/>
+      <c r="AD4" s="439" t="n"/>
+      <c r="AE4" s="431" t="n"/>
+      <c r="AF4" s="432" t="n"/>
+      <c r="AG4" s="432" t="n"/>
+      <c r="AH4" s="433" t="n"/>
+      <c r="AI4" s="434" t="n"/>
+      <c r="AJ4" s="435" t="n"/>
+      <c r="AK4" s="435" t="n"/>
+      <c r="AL4" s="435" t="n"/>
+      <c r="AM4" s="435" t="n"/>
+      <c r="AN4" s="436" t="n"/>
     </row>
-    <row r="5" ht="20" customHeight="1" s="329">
-      <c r="A5" s="388" t="inlineStr">
+    <row r="5" ht="15" customHeight="1" s="329">
+      <c r="A5" s="506" t="inlineStr">
         <is>
           <t>Source of Truth</t>
         </is>
       </c>
-      <c r="B5" s="389" t="inlineStr">
+      <c r="B5" s="507" t="inlineStr">
         <is>
           <t>Epicor transaction + M365 evidence</t>
         </is>
       </c>
-      <c r="C5" s="389" t="inlineStr">
+      <c r="C5" s="507" t="inlineStr">
         <is>
           <t>Do not duplicate ERP/M365/ANNEX master data.</t>
         </is>
       </c>
-      <c r="D5" s="345" t="n"/>
-      <c r="E5" s="345" t="n"/>
-      <c r="F5" s="345" t="n"/>
-      <c r="G5" s="345" t="n"/>
-      <c r="H5" s="345" t="n"/>
-      <c r="I5" s="345" t="n"/>
-      <c r="J5" s="345" t="n"/>
-      <c r="K5" s="345" t="n"/>
-      <c r="L5" s="345" t="n"/>
-      <c r="M5" s="345" t="n"/>
-      <c r="N5" s="345" t="n"/>
-      <c r="O5" s="345" t="n"/>
-      <c r="P5" s="345" t="n"/>
-      <c r="Q5" s="345" t="n"/>
-      <c r="R5" s="345" t="n"/>
-      <c r="S5" s="345" t="n"/>
-      <c r="T5" s="345" t="n"/>
-      <c r="U5" s="345" t="n"/>
-      <c r="V5" s="345" t="n"/>
-      <c r="W5" s="345" t="n"/>
-      <c r="X5" s="345" t="n"/>
-      <c r="Y5" s="345" t="n"/>
-      <c r="Z5" s="345" t="n"/>
-      <c r="AA5" s="345" t="n"/>
-      <c r="AB5" s="345" t="n"/>
-      <c r="AC5" s="345" t="n"/>
-      <c r="AD5" s="345" t="n"/>
-      <c r="AE5" s="345" t="n"/>
-      <c r="AF5" s="345" t="n"/>
-      <c r="AG5" s="345" t="n"/>
-      <c r="AH5" s="345" t="n"/>
-      <c r="AI5" s="345" t="n"/>
-      <c r="AJ5" s="345" t="n"/>
-      <c r="AK5" s="345" t="n"/>
-      <c r="AL5" s="345" t="n"/>
-      <c r="AM5" s="345" t="n"/>
-      <c r="AN5" s="345" t="n"/>
+      <c r="D5" s="520" t="n"/>
+      <c r="E5" s="520" t="n"/>
+      <c r="F5" s="520" t="n"/>
+      <c r="G5" s="520" t="n"/>
+      <c r="H5" s="521" t="n"/>
+      <c r="I5" s="443" t="n"/>
+      <c r="J5" s="444" t="n"/>
+      <c r="K5" s="444" t="n"/>
+      <c r="L5" s="444" t="n"/>
+      <c r="M5" s="444" t="n"/>
+      <c r="N5" s="444" t="n"/>
+      <c r="O5" s="444" t="n"/>
+      <c r="P5" s="444" t="n"/>
+      <c r="Q5" s="444" t="n"/>
+      <c r="R5" s="444" t="n"/>
+      <c r="S5" s="444" t="n"/>
+      <c r="T5" s="444" t="n"/>
+      <c r="U5" s="444" t="n"/>
+      <c r="V5" s="444" t="n"/>
+      <c r="W5" s="444" t="n"/>
+      <c r="X5" s="444" t="n"/>
+      <c r="Y5" s="444" t="n"/>
+      <c r="Z5" s="444" t="n"/>
+      <c r="AA5" s="444" t="n"/>
+      <c r="AB5" s="444" t="n"/>
+      <c r="AC5" s="444" t="n"/>
+      <c r="AD5" s="445" t="n"/>
+      <c r="AE5" s="446" t="n"/>
+      <c r="AF5" s="447" t="n"/>
+      <c r="AG5" s="447" t="n"/>
+      <c r="AH5" s="448" t="n"/>
+      <c r="AI5" s="449" t="n"/>
+      <c r="AJ5" s="450" t="n"/>
+      <c r="AK5" s="450" t="n"/>
+      <c r="AL5" s="450" t="n"/>
+      <c r="AM5" s="450" t="n"/>
+      <c r="AN5" s="451" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1" s="329">
-      <c r="A6" s="388" t="inlineStr">
+      <c r="A6" s="509" t="inlineStr">
         <is>
           <t>Cross-Reference Boundary</t>
         </is>
       </c>
-      <c r="B6" s="389" t="inlineStr">
+      <c r="B6" s="510" t="inlineStr">
         <is>
           <t>This form does not replace SOP-402; it records the evidence, data or decision required by that SOP.
 Rules, matrices, dictionaries, acceptance criteria and data definitions belong in ANNEX-PUR-001/002/003 + ANNEX-ENG-002; do not copy ANNEX content into the live data-entry body.
 System-of-record / source-of-truth boundary: Epicor transaction + M365 evidence. If the master data already live there, reference or import them; do not re-key without need.</t>
         </is>
       </c>
-      <c r="C6" s="389" t="inlineStr">
+      <c r="C6" s="511" t="inlineStr">
         <is>
           <t>This form does not replace SOP-402; it records the evidence, data or decision required by that SOP.
 Rules, matrices, dictionaries, acceptance criteria and data definitions belong in ANNEX-PUR-001/002/003 + ANNEX-ENG-002; do not copy ANNEX content into the live data-entry body.
 System-of-record / source-of-truth boundary: Epicor transaction + M365 evidence. If the master data already live there, reference or import them; do not re-key without need.</t>
         </is>
       </c>
-      <c r="D6" s="345" t="n"/>
-      <c r="E6" s="345" t="n"/>
-      <c r="F6" s="345" t="n"/>
-      <c r="G6" s="345" t="n"/>
-      <c r="H6" s="345" t="n"/>
-      <c r="I6" s="345" t="n"/>
-      <c r="J6" s="345" t="n"/>
-      <c r="K6" s="345" t="n"/>
-      <c r="L6" s="345" t="n"/>
-      <c r="M6" s="345" t="n"/>
-      <c r="N6" s="345" t="n"/>
-      <c r="O6" s="345" t="n"/>
-      <c r="P6" s="345" t="n"/>
-      <c r="Q6" s="345" t="n"/>
-      <c r="R6" s="345" t="n"/>
-      <c r="S6" s="345" t="n"/>
-      <c r="T6" s="345" t="n"/>
-      <c r="U6" s="345" t="n"/>
-      <c r="V6" s="345" t="n"/>
-      <c r="W6" s="345" t="n"/>
-      <c r="X6" s="345" t="n"/>
-      <c r="Y6" s="345" t="n"/>
-      <c r="Z6" s="345" t="n"/>
-      <c r="AA6" s="345" t="n"/>
-      <c r="AB6" s="345" t="n"/>
-      <c r="AC6" s="345" t="n"/>
-      <c r="AD6" s="345" t="n"/>
-      <c r="AE6" s="345" t="n"/>
-      <c r="AF6" s="345" t="n"/>
-      <c r="AG6" s="345" t="n"/>
-      <c r="AH6" s="345" t="n"/>
-      <c r="AI6" s="345" t="n"/>
-      <c r="AJ6" s="345" t="n"/>
-      <c r="AK6" s="345" t="n"/>
-      <c r="AL6" s="345" t="n"/>
-      <c r="AM6" s="345" t="n"/>
-      <c r="AN6" s="345" t="n"/>
+      <c r="D6" s="457" t="n"/>
+      <c r="E6" s="457" t="n"/>
+      <c r="F6" s="457" t="n"/>
+      <c r="G6" s="457" t="n"/>
+      <c r="H6" s="457" t="n"/>
+      <c r="I6" s="457" t="n"/>
+      <c r="J6" s="457" t="n"/>
+      <c r="K6" s="457" t="n"/>
+      <c r="L6" s="457" t="n"/>
+      <c r="M6" s="457" t="n"/>
+      <c r="N6" s="457" t="n"/>
+      <c r="O6" s="457" t="n"/>
+      <c r="P6" s="457" t="n"/>
+      <c r="Q6" s="457" t="n"/>
+      <c r="R6" s="457" t="n"/>
+      <c r="S6" s="457" t="n"/>
+      <c r="T6" s="457" t="n"/>
+      <c r="U6" s="457" t="n"/>
+      <c r="V6" s="457" t="n"/>
+      <c r="W6" s="457" t="n"/>
+      <c r="X6" s="457" t="n"/>
+      <c r="Y6" s="457" t="n"/>
+      <c r="Z6" s="457" t="n"/>
+      <c r="AA6" s="457" t="n"/>
+      <c r="AB6" s="457" t="n"/>
+      <c r="AC6" s="457" t="n"/>
+      <c r="AD6" s="457" t="n"/>
+      <c r="AE6" s="457" t="n"/>
+      <c r="AF6" s="457" t="n"/>
+      <c r="AG6" s="457" t="n"/>
+      <c r="AH6" s="457" t="n"/>
+      <c r="AI6" s="457" t="n"/>
+      <c r="AJ6" s="457" t="n"/>
+      <c r="AK6" s="457" t="n"/>
+      <c r="AL6" s="457" t="n"/>
+      <c r="AM6" s="457" t="n"/>
+      <c r="AN6" s="460" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1" s="329">
-      <c r="A7" s="388" t="inlineStr">
+      <c r="A7" s="512" t="inlineStr">
         <is>
           <t>SOP-402</t>
         </is>
       </c>
-      <c r="B7" s="389" t="inlineStr">
+      <c r="B7" s="513" t="inlineStr">
         <is>
           <t>SOP-402 — Xác minh vật liệu, truy xuất và phòng chống vật tư giả/không rõ nguồn gốc | HESEM QMS</t>
         </is>
       </c>
-      <c r="C7" s="389" t="inlineStr">
+      <c r="C7" s="514" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/01-SOPs/04-SOP-400/sop-402-material-verification-traceability-and-counterfeit-prevention.html</t>
         </is>
       </c>
-      <c r="D7" s="345" t="n"/>
-      <c r="E7" s="345" t="n"/>
-      <c r="F7" s="345" t="n"/>
-      <c r="G7" s="345" t="n"/>
-      <c r="H7" s="345" t="n"/>
-      <c r="I7" s="345" t="n"/>
-      <c r="J7" s="345" t="n"/>
-      <c r="K7" s="345" t="n"/>
-      <c r="L7" s="345" t="n"/>
-      <c r="M7" s="345" t="n"/>
-      <c r="N7" s="345" t="n"/>
-      <c r="O7" s="345" t="n"/>
-      <c r="P7" s="345" t="n"/>
-      <c r="Q7" s="345" t="n"/>
-      <c r="R7" s="345" t="n"/>
-      <c r="S7" s="345" t="n"/>
-      <c r="T7" s="345" t="n"/>
-      <c r="U7" s="345" t="n"/>
-      <c r="V7" s="345" t="n"/>
-      <c r="W7" s="345" t="n"/>
-      <c r="X7" s="345" t="n"/>
-      <c r="Y7" s="345" t="n"/>
-      <c r="Z7" s="345" t="n"/>
-      <c r="AA7" s="345" t="n"/>
-      <c r="AB7" s="345" t="n"/>
-      <c r="AC7" s="345" t="n"/>
-      <c r="AD7" s="345" t="n"/>
-      <c r="AE7" s="345" t="n"/>
-      <c r="AF7" s="345" t="n"/>
-      <c r="AG7" s="345" t="n"/>
-      <c r="AH7" s="345" t="n"/>
-      <c r="AI7" s="345" t="n"/>
-      <c r="AJ7" s="345" t="n"/>
-      <c r="AK7" s="345" t="n"/>
-      <c r="AL7" s="345" t="n"/>
-      <c r="AM7" s="345" t="n"/>
-      <c r="AN7" s="345" t="n"/>
+      <c r="D7" s="341" t="n"/>
+      <c r="E7" s="341" t="n"/>
+      <c r="F7" s="341" t="n"/>
+      <c r="G7" s="341" t="n"/>
+      <c r="H7" s="341" t="n"/>
+      <c r="I7" s="341" t="n"/>
+      <c r="J7" s="341" t="n"/>
+      <c r="K7" s="341" t="n"/>
+      <c r="L7" s="341" t="n"/>
+      <c r="M7" s="341" t="n"/>
+      <c r="N7" s="341" t="n"/>
+      <c r="O7" s="341" t="n"/>
+      <c r="P7" s="341" t="n"/>
+      <c r="Q7" s="341" t="n"/>
+      <c r="R7" s="341" t="n"/>
+      <c r="S7" s="341" t="n"/>
+      <c r="T7" s="341" t="n"/>
+      <c r="U7" s="341" t="n"/>
+      <c r="V7" s="341" t="n"/>
+      <c r="W7" s="341" t="n"/>
+      <c r="X7" s="341" t="n"/>
+      <c r="Y7" s="341" t="n"/>
+      <c r="Z7" s="341" t="n"/>
+      <c r="AA7" s="341" t="n"/>
+      <c r="AB7" s="341" t="n"/>
+      <c r="AC7" s="341" t="n"/>
+      <c r="AD7" s="341" t="n"/>
+      <c r="AE7" s="341" t="n"/>
+      <c r="AF7" s="341" t="n"/>
+      <c r="AG7" s="341" t="n"/>
+      <c r="AH7" s="341" t="n"/>
+      <c r="AI7" s="341" t="n"/>
+      <c r="AJ7" s="341" t="n"/>
+      <c r="AK7" s="341" t="n"/>
+      <c r="AL7" s="341" t="n"/>
+      <c r="AM7" s="341" t="n"/>
+      <c r="AN7" s="464" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1" s="329">
-      <c r="A8" s="352" t="inlineStr">
+      <c r="A8" s="461" t="inlineStr">
         <is>
           <t>ANNEX-PUR-001</t>
         </is>
       </c>
-      <c r="B8" s="390" t="inlineStr">
+      <c r="B8" s="462" t="inlineStr">
         <is>
           <t>ANNEX-PUR-001 — Mô hình rủi ro nhà cung cấp và phương pháp scorecard</t>
         </is>
       </c>
-      <c r="C8" s="390" t="inlineStr">
+      <c r="C8" s="515" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-001-supplier-risk-model-and-scorecard-method.html</t>
         </is>
       </c>
-      <c r="D8" s="381" t="n"/>
-      <c r="E8" s="381" t="n"/>
-      <c r="F8" s="381" t="n"/>
-      <c r="G8" s="381" t="n"/>
-      <c r="H8" s="381" t="n"/>
-      <c r="I8" s="381" t="n"/>
-      <c r="J8" s="381" t="n"/>
-      <c r="K8" s="381" t="n"/>
-      <c r="L8" s="381" t="n"/>
-      <c r="M8" s="381" t="n"/>
-      <c r="N8" s="381" t="n"/>
-      <c r="O8" s="381" t="n"/>
-      <c r="P8" s="381" t="n"/>
-      <c r="Q8" s="381" t="n"/>
-      <c r="R8" s="381" t="n"/>
-      <c r="S8" s="381" t="n"/>
-      <c r="T8" s="381" t="n"/>
-      <c r="U8" s="381" t="n"/>
-      <c r="V8" s="381" t="n"/>
-      <c r="W8" s="381" t="n"/>
-      <c r="X8" s="381" t="n"/>
-      <c r="Y8" s="381" t="n"/>
-      <c r="Z8" s="381" t="n"/>
-      <c r="AA8" s="381" t="n"/>
-      <c r="AB8" s="381" t="n"/>
-      <c r="AC8" s="381" t="n"/>
-      <c r="AD8" s="381" t="n"/>
-      <c r="AE8" s="381" t="n"/>
-      <c r="AF8" s="381" t="n"/>
-      <c r="AG8" s="381" t="n"/>
-      <c r="AH8" s="381" t="n"/>
-      <c r="AI8" s="381" t="n"/>
-      <c r="AJ8" s="381" t="n"/>
-      <c r="AK8" s="381" t="n"/>
-      <c r="AL8" s="381" t="n"/>
-      <c r="AM8" s="381" t="n"/>
-      <c r="AN8" s="381" t="n"/>
+      <c r="D8" s="353" t="n"/>
+      <c r="E8" s="353" t="n"/>
+      <c r="F8" s="353" t="n"/>
+      <c r="G8" s="353" t="n"/>
+      <c r="H8" s="353" t="n"/>
+      <c r="I8" s="353" t="n"/>
+      <c r="J8" s="353" t="n"/>
+      <c r="K8" s="353" t="n"/>
+      <c r="L8" s="353" t="n"/>
+      <c r="M8" s="353" t="n"/>
+      <c r="N8" s="353" t="n"/>
+      <c r="O8" s="353" t="n"/>
+      <c r="P8" s="353" t="n"/>
+      <c r="Q8" s="353" t="n"/>
+      <c r="R8" s="353" t="n"/>
+      <c r="S8" s="353" t="n"/>
+      <c r="T8" s="353" t="n"/>
+      <c r="U8" s="353" t="n"/>
+      <c r="V8" s="353" t="n"/>
+      <c r="W8" s="353" t="n"/>
+      <c r="X8" s="353" t="n"/>
+      <c r="Y8" s="353" t="n"/>
+      <c r="Z8" s="353" t="n"/>
+      <c r="AA8" s="353" t="n"/>
+      <c r="AB8" s="353" t="n"/>
+      <c r="AC8" s="353" t="n"/>
+      <c r="AD8" s="353" t="n"/>
+      <c r="AE8" s="353" t="n"/>
+      <c r="AF8" s="353" t="n"/>
+      <c r="AG8" s="353" t="n"/>
+      <c r="AH8" s="353" t="n"/>
+      <c r="AI8" s="353" t="n"/>
+      <c r="AJ8" s="353" t="n"/>
+      <c r="AK8" s="353" t="n"/>
+      <c r="AL8" s="353" t="n"/>
+      <c r="AM8" s="353" t="n"/>
+      <c r="AN8" s="516" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1" s="329">
-      <c r="A9" s="381" t="inlineStr">
+      <c r="A9" s="524" t="inlineStr">
         <is>
           <t>ANNEX-PUR-002</t>
         </is>
       </c>
-      <c r="B9" s="381" t="inlineStr">
+      <c r="B9" s="525" t="inlineStr">
         <is>
           <t>ANNEX-PUR-002 — Gói kiểm soát outsource / special process / cert flow-down</t>
         </is>
       </c>
-      <c r="C9" s="381" t="inlineStr">
+      <c r="C9" s="353" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-002-outsource-special-process-pack.html</t>
         </is>
       </c>
-      <c r="D9" s="381" t="n"/>
-      <c r="E9" s="381" t="n"/>
-      <c r="F9" s="381" t="n"/>
-      <c r="G9" s="381" t="n"/>
-      <c r="H9" s="381" t="n"/>
-      <c r="I9" s="381" t="n"/>
-      <c r="J9" s="381" t="n"/>
-      <c r="K9" s="381" t="n"/>
-      <c r="L9" s="381" t="n"/>
-      <c r="M9" s="381" t="n"/>
-      <c r="N9" s="381" t="n"/>
-      <c r="O9" s="381" t="n"/>
-      <c r="P9" s="381" t="n"/>
-      <c r="Q9" s="381" t="n"/>
-      <c r="R9" s="381" t="n"/>
-      <c r="S9" s="381" t="n"/>
-      <c r="T9" s="381" t="n"/>
-      <c r="U9" s="381" t="n"/>
-      <c r="V9" s="381" t="n"/>
-      <c r="W9" s="381" t="n"/>
-      <c r="X9" s="381" t="n"/>
-      <c r="Y9" s="381" t="n"/>
-      <c r="Z9" s="381" t="n"/>
-      <c r="AA9" s="381" t="n"/>
-      <c r="AB9" s="381" t="n"/>
-      <c r="AC9" s="381" t="n"/>
-      <c r="AD9" s="381" t="n"/>
-      <c r="AE9" s="381" t="n"/>
-      <c r="AF9" s="381" t="n"/>
-      <c r="AG9" s="381" t="n"/>
-      <c r="AH9" s="381" t="n"/>
-      <c r="AI9" s="381" t="n"/>
-      <c r="AJ9" s="381" t="n"/>
-      <c r="AK9" s="381" t="n"/>
-      <c r="AL9" s="381" t="n"/>
-      <c r="AM9" s="381" t="n"/>
-      <c r="AN9" s="381" t="n"/>
+      <c r="D9" s="353" t="n"/>
+      <c r="E9" s="353" t="n"/>
+      <c r="F9" s="353" t="n"/>
+      <c r="G9" s="353" t="n"/>
+      <c r="H9" s="353" t="n"/>
+      <c r="I9" s="353" t="n"/>
+      <c r="J9" s="353" t="n"/>
+      <c r="K9" s="353" t="n"/>
+      <c r="L9" s="353" t="n"/>
+      <c r="M9" s="353" t="n"/>
+      <c r="N9" s="353" t="n"/>
+      <c r="O9" s="353" t="n"/>
+      <c r="P9" s="353" t="n"/>
+      <c r="Q9" s="353" t="n"/>
+      <c r="R9" s="353" t="n"/>
+      <c r="S9" s="353" t="n"/>
+      <c r="T9" s="353" t="n"/>
+      <c r="U9" s="353" t="n"/>
+      <c r="V9" s="353" t="n"/>
+      <c r="W9" s="353" t="n"/>
+      <c r="X9" s="353" t="n"/>
+      <c r="Y9" s="353" t="n"/>
+      <c r="Z9" s="353" t="n"/>
+      <c r="AA9" s="353" t="n"/>
+      <c r="AB9" s="353" t="n"/>
+      <c r="AC9" s="353" t="n"/>
+      <c r="AD9" s="353" t="n"/>
+      <c r="AE9" s="353" t="n"/>
+      <c r="AF9" s="353" t="n"/>
+      <c r="AG9" s="353" t="n"/>
+      <c r="AH9" s="353" t="n"/>
+      <c r="AI9" s="353" t="n"/>
+      <c r="AJ9" s="353" t="n"/>
+      <c r="AK9" s="353" t="n"/>
+      <c r="AL9" s="353" t="n"/>
+      <c r="AM9" s="353" t="n"/>
+      <c r="AN9" s="516" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1" s="329">
-      <c r="A10" s="381" t="inlineStr">
+      <c r="A10" s="524" t="inlineStr">
         <is>
           <t>ANNEX-PUR-003</t>
         </is>
       </c>
-      <c r="B10" s="381" t="inlineStr">
+      <c r="B10" s="525" t="inlineStr">
         <is>
           <t>ANNEX-PUR-003 — Approved processor list, scope approval và rule tạm ngưng</t>
         </is>
       </c>
-      <c r="C10" s="381" t="inlineStr">
+      <c r="C10" s="353" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-003-approved-processor-list.html</t>
         </is>
       </c>
-      <c r="D10" s="381" t="n"/>
-      <c r="E10" s="381" t="n"/>
-      <c r="F10" s="381" t="n"/>
-      <c r="G10" s="381" t="n"/>
-      <c r="H10" s="381" t="n"/>
-      <c r="I10" s="381" t="n"/>
-      <c r="J10" s="381" t="n"/>
-      <c r="K10" s="381" t="n"/>
-      <c r="L10" s="381" t="n"/>
-      <c r="M10" s="381" t="n"/>
-      <c r="N10" s="381" t="n"/>
-      <c r="O10" s="381" t="n"/>
-      <c r="P10" s="381" t="n"/>
-      <c r="Q10" s="381" t="n"/>
-      <c r="R10" s="381" t="n"/>
-      <c r="S10" s="381" t="n"/>
-      <c r="T10" s="381" t="n"/>
-      <c r="U10" s="381" t="n"/>
-      <c r="V10" s="381" t="n"/>
-      <c r="W10" s="381" t="n"/>
-      <c r="X10" s="381" t="n"/>
-      <c r="Y10" s="381" t="n"/>
-      <c r="Z10" s="381" t="n"/>
-      <c r="AA10" s="381" t="n"/>
-      <c r="AB10" s="381" t="n"/>
-      <c r="AC10" s="381" t="n"/>
-      <c r="AD10" s="381" t="n"/>
-      <c r="AE10" s="381" t="n"/>
-      <c r="AF10" s="381" t="n"/>
-      <c r="AG10" s="381" t="n"/>
-      <c r="AH10" s="381" t="n"/>
-      <c r="AI10" s="381" t="n"/>
-      <c r="AJ10" s="381" t="n"/>
-      <c r="AK10" s="381" t="n"/>
-      <c r="AL10" s="381" t="n"/>
-      <c r="AM10" s="381" t="n"/>
-      <c r="AN10" s="381" t="n"/>
+      <c r="D10" s="353" t="n"/>
+      <c r="E10" s="353" t="n"/>
+      <c r="F10" s="353" t="n"/>
+      <c r="G10" s="353" t="n"/>
+      <c r="H10" s="353" t="n"/>
+      <c r="I10" s="353" t="n"/>
+      <c r="J10" s="353" t="n"/>
+      <c r="K10" s="353" t="n"/>
+      <c r="L10" s="353" t="n"/>
+      <c r="M10" s="353" t="n"/>
+      <c r="N10" s="353" t="n"/>
+      <c r="O10" s="353" t="n"/>
+      <c r="P10" s="353" t="n"/>
+      <c r="Q10" s="353" t="n"/>
+      <c r="R10" s="353" t="n"/>
+      <c r="S10" s="353" t="n"/>
+      <c r="T10" s="353" t="n"/>
+      <c r="U10" s="353" t="n"/>
+      <c r="V10" s="353" t="n"/>
+      <c r="W10" s="353" t="n"/>
+      <c r="X10" s="353" t="n"/>
+      <c r="Y10" s="353" t="n"/>
+      <c r="Z10" s="353" t="n"/>
+      <c r="AA10" s="353" t="n"/>
+      <c r="AB10" s="353" t="n"/>
+      <c r="AC10" s="353" t="n"/>
+      <c r="AD10" s="353" t="n"/>
+      <c r="AE10" s="353" t="n"/>
+      <c r="AF10" s="353" t="n"/>
+      <c r="AG10" s="353" t="n"/>
+      <c r="AH10" s="353" t="n"/>
+      <c r="AI10" s="353" t="n"/>
+      <c r="AJ10" s="353" t="n"/>
+      <c r="AK10" s="353" t="n"/>
+      <c r="AL10" s="353" t="n"/>
+      <c r="AM10" s="353" t="n"/>
+      <c r="AN10" s="516" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1" s="329">
-      <c r="A11" s="381" t="inlineStr">
+      <c r="A11" s="524" t="inlineStr">
         <is>
           <t>ANNEX-ENG-002</t>
         </is>
       </c>
-      <c r="B11" s="381" t="inlineStr">
+      <c r="B11" s="525" t="inlineStr">
         <is>
           <t>ANNEX-ENG-002 — Approved materials list, source restriction và rule thay thế</t>
         </is>
       </c>
-      <c r="C11" s="381" t="inlineStr">
+      <c r="C11" s="353" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-eng-002-approved-materials-list.html</t>
         </is>
       </c>
-      <c r="D11" s="381" t="n"/>
-      <c r="E11" s="381" t="n"/>
-      <c r="F11" s="381" t="n"/>
-      <c r="G11" s="381" t="n"/>
-      <c r="H11" s="381" t="n"/>
-      <c r="I11" s="381" t="n"/>
-      <c r="J11" s="381" t="n"/>
-      <c r="K11" s="381" t="n"/>
-      <c r="L11" s="381" t="n"/>
-      <c r="M11" s="381" t="n"/>
-      <c r="N11" s="381" t="n"/>
-      <c r="O11" s="381" t="n"/>
-      <c r="P11" s="381" t="n"/>
-      <c r="Q11" s="381" t="n"/>
-      <c r="R11" s="381" t="n"/>
-      <c r="S11" s="381" t="n"/>
-      <c r="T11" s="381" t="n"/>
-      <c r="U11" s="381" t="n"/>
-      <c r="V11" s="381" t="n"/>
-      <c r="W11" s="381" t="n"/>
-      <c r="X11" s="381" t="n"/>
-      <c r="Y11" s="381" t="n"/>
-      <c r="Z11" s="381" t="n"/>
-      <c r="AA11" s="381" t="n"/>
-      <c r="AB11" s="381" t="n"/>
-      <c r="AC11" s="381" t="n"/>
-      <c r="AD11" s="381" t="n"/>
-      <c r="AE11" s="381" t="n"/>
-      <c r="AF11" s="381" t="n"/>
-      <c r="AG11" s="381" t="n"/>
-      <c r="AH11" s="381" t="n"/>
-      <c r="AI11" s="381" t="n"/>
-      <c r="AJ11" s="381" t="n"/>
-      <c r="AK11" s="381" t="n"/>
-      <c r="AL11" s="381" t="n"/>
-      <c r="AM11" s="381" t="n"/>
-      <c r="AN11" s="381" t="n"/>
+      <c r="D11" s="353" t="n"/>
+      <c r="E11" s="353" t="n"/>
+      <c r="F11" s="353" t="n"/>
+      <c r="G11" s="353" t="n"/>
+      <c r="H11" s="353" t="n"/>
+      <c r="I11" s="353" t="n"/>
+      <c r="J11" s="353" t="n"/>
+      <c r="K11" s="353" t="n"/>
+      <c r="L11" s="353" t="n"/>
+      <c r="M11" s="353" t="n"/>
+      <c r="N11" s="353" t="n"/>
+      <c r="O11" s="353" t="n"/>
+      <c r="P11" s="353" t="n"/>
+      <c r="Q11" s="353" t="n"/>
+      <c r="R11" s="353" t="n"/>
+      <c r="S11" s="353" t="n"/>
+      <c r="T11" s="353" t="n"/>
+      <c r="U11" s="353" t="n"/>
+      <c r="V11" s="353" t="n"/>
+      <c r="W11" s="353" t="n"/>
+      <c r="X11" s="353" t="n"/>
+      <c r="Y11" s="353" t="n"/>
+      <c r="Z11" s="353" t="n"/>
+      <c r="AA11" s="353" t="n"/>
+      <c r="AB11" s="353" t="n"/>
+      <c r="AC11" s="353" t="n"/>
+      <c r="AD11" s="353" t="n"/>
+      <c r="AE11" s="353" t="n"/>
+      <c r="AF11" s="353" t="n"/>
+      <c r="AG11" s="353" t="n"/>
+      <c r="AH11" s="353" t="n"/>
+      <c r="AI11" s="353" t="n"/>
+      <c r="AJ11" s="353" t="n"/>
+      <c r="AK11" s="353" t="n"/>
+      <c r="AL11" s="353" t="n"/>
+      <c r="AM11" s="353" t="n"/>
+      <c r="AN11" s="516" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1" s="329">
-      <c r="A12" s="381" t="inlineStr">
+      <c r="A12" s="524" t="inlineStr">
         <is>
           <t>Open When</t>
         </is>
       </c>
-      <c r="B12" s="381" t="inlineStr">
+      <c r="B12" s="525" t="inlineStr">
         <is>
           <t>Open immediately when the event, request, issue, change, complaint, risk or incident is detected or formally raised.</t>
         </is>
       </c>
-      <c r="C12" s="381" t="inlineStr">
+      <c r="C12" s="353" t="inlineStr">
         <is>
           <t>Operational trigger</t>
         </is>
       </c>
-      <c r="D12" s="381" t="n"/>
-      <c r="E12" s="381" t="n"/>
-      <c r="F12" s="381" t="n"/>
-      <c r="G12" s="381" t="n"/>
-      <c r="H12" s="381" t="n"/>
-      <c r="I12" s="381" t="n"/>
-      <c r="J12" s="381" t="n"/>
-      <c r="K12" s="381" t="n"/>
-      <c r="L12" s="381" t="n"/>
-      <c r="M12" s="381" t="n"/>
-      <c r="N12" s="381" t="n"/>
-      <c r="O12" s="381" t="n"/>
-      <c r="P12" s="381" t="n"/>
-      <c r="Q12" s="381" t="n"/>
-      <c r="R12" s="381" t="n"/>
-      <c r="S12" s="381" t="n"/>
-      <c r="T12" s="381" t="n"/>
-      <c r="U12" s="381" t="n"/>
-      <c r="V12" s="381" t="n"/>
-      <c r="W12" s="381" t="n"/>
-      <c r="X12" s="381" t="n"/>
-      <c r="Y12" s="381" t="n"/>
-      <c r="Z12" s="381" t="n"/>
-      <c r="AA12" s="381" t="n"/>
-      <c r="AB12" s="381" t="n"/>
-      <c r="AC12" s="381" t="n"/>
-      <c r="AD12" s="381" t="n"/>
-      <c r="AE12" s="381" t="n"/>
-      <c r="AF12" s="381" t="n"/>
-      <c r="AG12" s="381" t="n"/>
-      <c r="AH12" s="381" t="n"/>
-      <c r="AI12" s="381" t="n"/>
-      <c r="AJ12" s="381" t="n"/>
-      <c r="AK12" s="381" t="n"/>
-      <c r="AL12" s="381" t="n"/>
-      <c r="AM12" s="381" t="n"/>
-      <c r="AN12" s="381" t="n"/>
+      <c r="D12" s="353" t="n"/>
+      <c r="E12" s="353" t="n"/>
+      <c r="F12" s="353" t="n"/>
+      <c r="G12" s="353" t="n"/>
+      <c r="H12" s="353" t="n"/>
+      <c r="I12" s="353" t="n"/>
+      <c r="J12" s="353" t="n"/>
+      <c r="K12" s="353" t="n"/>
+      <c r="L12" s="353" t="n"/>
+      <c r="M12" s="353" t="n"/>
+      <c r="N12" s="353" t="n"/>
+      <c r="O12" s="353" t="n"/>
+      <c r="P12" s="353" t="n"/>
+      <c r="Q12" s="353" t="n"/>
+      <c r="R12" s="353" t="n"/>
+      <c r="S12" s="353" t="n"/>
+      <c r="T12" s="353" t="n"/>
+      <c r="U12" s="353" t="n"/>
+      <c r="V12" s="353" t="n"/>
+      <c r="W12" s="353" t="n"/>
+      <c r="X12" s="353" t="n"/>
+      <c r="Y12" s="353" t="n"/>
+      <c r="Z12" s="353" t="n"/>
+      <c r="AA12" s="353" t="n"/>
+      <c r="AB12" s="353" t="n"/>
+      <c r="AC12" s="353" t="n"/>
+      <c r="AD12" s="353" t="n"/>
+      <c r="AE12" s="353" t="n"/>
+      <c r="AF12" s="353" t="n"/>
+      <c r="AG12" s="353" t="n"/>
+      <c r="AH12" s="353" t="n"/>
+      <c r="AI12" s="353" t="n"/>
+      <c r="AJ12" s="353" t="n"/>
+      <c r="AK12" s="353" t="n"/>
+      <c r="AL12" s="353" t="n"/>
+      <c r="AM12" s="353" t="n"/>
+      <c r="AN12" s="516" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1" s="329">
-      <c r="A13" s="381" t="inlineStr">
+      <c r="A13" s="522" t="inlineStr">
         <is>
           <t>Close When</t>
         </is>
       </c>
-      <c r="B13" s="381" t="inlineStr">
+      <c r="B13" s="523" t="inlineStr">
         <is>
           <t>Close when the final decision, final owner, final disposition and required follow-up actions are all recorded and the evidence package is complete.</t>
         </is>
       </c>
-      <c r="C13" s="381" t="inlineStr">
+      <c r="C13" s="518" t="inlineStr">
         <is>
           <t>Release / closure rule</t>
         </is>
       </c>
-      <c r="D13" s="381" t="n"/>
-      <c r="E13" s="381" t="n"/>
-      <c r="F13" s="381" t="n"/>
-      <c r="G13" s="381" t="n"/>
-      <c r="H13" s="381" t="n"/>
-      <c r="I13" s="381" t="n"/>
-      <c r="J13" s="381" t="n"/>
-      <c r="K13" s="381" t="n"/>
-      <c r="L13" s="381" t="n"/>
-      <c r="M13" s="381" t="n"/>
-      <c r="N13" s="381" t="n"/>
-      <c r="O13" s="381" t="n"/>
-      <c r="P13" s="381" t="n"/>
-      <c r="Q13" s="381" t="n"/>
-      <c r="R13" s="381" t="n"/>
-      <c r="S13" s="381" t="n"/>
-      <c r="T13" s="381" t="n"/>
-      <c r="U13" s="381" t="n"/>
-      <c r="V13" s="381" t="n"/>
-      <c r="W13" s="381" t="n"/>
-      <c r="X13" s="381" t="n"/>
-      <c r="Y13" s="381" t="n"/>
-      <c r="Z13" s="381" t="n"/>
-      <c r="AA13" s="381" t="n"/>
-      <c r="AB13" s="381" t="n"/>
-      <c r="AC13" s="381" t="n"/>
-      <c r="AD13" s="381" t="n"/>
-      <c r="AE13" s="381" t="n"/>
-      <c r="AF13" s="381" t="n"/>
-      <c r="AG13" s="381" t="n"/>
-      <c r="AH13" s="381" t="n"/>
-      <c r="AI13" s="381" t="n"/>
-      <c r="AJ13" s="381" t="n"/>
-      <c r="AK13" s="381" t="n"/>
-      <c r="AL13" s="381" t="n"/>
-      <c r="AM13" s="381" t="n"/>
-      <c r="AN13" s="381" t="n"/>
+      <c r="D13" s="518" t="n"/>
+      <c r="E13" s="518" t="n"/>
+      <c r="F13" s="518" t="n"/>
+      <c r="G13" s="518" t="n"/>
+      <c r="H13" s="518" t="n"/>
+      <c r="I13" s="518" t="n"/>
+      <c r="J13" s="518" t="n"/>
+      <c r="K13" s="518" t="n"/>
+      <c r="L13" s="518" t="n"/>
+      <c r="M13" s="518" t="n"/>
+      <c r="N13" s="518" t="n"/>
+      <c r="O13" s="518" t="n"/>
+      <c r="P13" s="518" t="n"/>
+      <c r="Q13" s="518" t="n"/>
+      <c r="R13" s="518" t="n"/>
+      <c r="S13" s="518" t="n"/>
+      <c r="T13" s="518" t="n"/>
+      <c r="U13" s="518" t="n"/>
+      <c r="V13" s="518" t="n"/>
+      <c r="W13" s="518" t="n"/>
+      <c r="X13" s="518" t="n"/>
+      <c r="Y13" s="518" t="n"/>
+      <c r="Z13" s="518" t="n"/>
+      <c r="AA13" s="518" t="n"/>
+      <c r="AB13" s="518" t="n"/>
+      <c r="AC13" s="518" t="n"/>
+      <c r="AD13" s="518" t="n"/>
+      <c r="AE13" s="518" t="n"/>
+      <c r="AF13" s="518" t="n"/>
+      <c r="AG13" s="518" t="n"/>
+      <c r="AH13" s="518" t="n"/>
+      <c r="AI13" s="518" t="n"/>
+      <c r="AJ13" s="518" t="n"/>
+      <c r="AK13" s="518" t="n"/>
+      <c r="AL13" s="518" t="n"/>
+      <c r="AM13" s="518" t="n"/>
+      <c r="AN13" s="519" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1" s="329"/>
     <row r="15" ht="20" customHeight="1" s="329"/>
@@ -9829,5 +10664,6 @@
   </mergeCells>
   <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/04-Bieu-Mau/04-FRM-400/FRM-411_Outsourced_Process_Incoming_Verification.xlsx
+++ b/04-Bieu-Mau/04-FRM-400/FRM-411_Outsourced_Process_Incoming_Verification.xlsx
@@ -764,7 +764,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="321">
+  <borders count="354">
     <border>
       <left/>
       <right/>
@@ -4194,12 +4194,403 @@
       <bottom style="medium">
         <color rgb="002C9CD7"/>
       </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="526">
+  <cellXfs count="569">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -5400,6 +5791,93 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="335" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="322" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="323" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="81" fillId="4" borderId="332" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="48" borderId="351" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="352" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="339" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="333" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="331" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="48" borderId="334" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="285" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="348" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="326" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="83" fillId="4" borderId="330" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="353" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="342" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="343" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="84" fillId="4" borderId="341" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="48" borderId="346" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="340" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="347" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="349" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="350" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="49" borderId="335" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="336" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="324" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="328" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="344" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="345" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="329" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="327" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="349" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="50" borderId="325" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="325" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="337" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="338" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="51" borderId="321" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="344" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="329" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="349" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="50" borderId="344" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="4" borderId="329" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="4" borderId="335" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5500,6 +5978,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5530,6 +6011,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5560,6 +6044,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5590,6 +6077,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5809,7 +6299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AN44"/>
+  <dimension ref="A1:CU44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.329999923706055" customWidth="1" style="329" min="1" max="1"/>
@@ -5855,246 +6345,168 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="329">
-      <c r="A1" s="414" t="n"/>
-      <c r="B1" s="415" t="n"/>
-      <c r="C1" s="415" t="n"/>
-      <c r="D1" s="415" t="n"/>
-      <c r="E1" s="415" t="n"/>
-      <c r="F1" s="415" t="n"/>
-      <c r="G1" s="415" t="n"/>
-      <c r="H1" s="416" t="n"/>
-      <c r="I1" s="417" t="inlineStr">
+      <c r="A1" s="526" t="n"/>
+      <c r="B1" s="527" t="n"/>
+      <c r="C1" s="527" t="n"/>
+      <c r="D1" s="527" t="n"/>
+      <c r="E1" s="527" t="n"/>
+      <c r="F1" s="527" t="n"/>
+      <c r="G1" s="527" t="n"/>
+      <c r="H1" s="528" t="n"/>
+      <c r="I1" s="529" t="inlineStr">
         <is>
           <t>Outsourced Process Incoming Verification</t>
         </is>
       </c>
-      <c r="J1" s="418" t="n"/>
-      <c r="K1" s="418" t="n"/>
-      <c r="L1" s="418" t="n"/>
-      <c r="M1" s="418" t="n"/>
-      <c r="N1" s="418" t="n"/>
-      <c r="O1" s="418" t="n"/>
-      <c r="P1" s="418" t="n"/>
-      <c r="Q1" s="418" t="n"/>
-      <c r="R1" s="418" t="n"/>
-      <c r="S1" s="418" t="n"/>
-      <c r="T1" s="418" t="n"/>
-      <c r="U1" s="418" t="n"/>
-      <c r="V1" s="418" t="n"/>
-      <c r="W1" s="418" t="n"/>
-      <c r="X1" s="418" t="n"/>
-      <c r="Y1" s="418" t="n"/>
-      <c r="Z1" s="418" t="n"/>
-      <c r="AA1" s="418" t="n"/>
-      <c r="AB1" s="418" t="n"/>
-      <c r="AC1" s="418" t="n"/>
-      <c r="AD1" s="419" t="n"/>
-      <c r="AE1" s="420" t="n"/>
-      <c r="AF1" s="421" t="n"/>
-      <c r="AG1" s="421" t="n"/>
-      <c r="AH1" s="422" t="n"/>
-      <c r="AI1" s="423" t="inlineStr">
+      <c r="J1" s="527" t="n"/>
+      <c r="K1" s="527" t="n"/>
+      <c r="L1" s="527" t="n"/>
+      <c r="M1" s="527" t="n"/>
+      <c r="N1" s="527" t="n"/>
+      <c r="O1" s="527" t="n"/>
+      <c r="P1" s="527" t="n"/>
+      <c r="Q1" s="527" t="n"/>
+      <c r="R1" s="527" t="n"/>
+      <c r="S1" s="527" t="n"/>
+      <c r="T1" s="527" t="n"/>
+      <c r="U1" s="527" t="n"/>
+      <c r="V1" s="527" t="n"/>
+      <c r="W1" s="527" t="n"/>
+      <c r="X1" s="527" t="n"/>
+      <c r="Y1" s="527" t="n"/>
+      <c r="Z1" s="527" t="n"/>
+      <c r="AA1" s="527" t="n"/>
+      <c r="AB1" s="527" t="n"/>
+      <c r="AC1" s="527" t="n"/>
+      <c r="AD1" s="528" t="n"/>
+      <c r="AE1" s="530" t="n"/>
+      <c r="AF1" s="527" t="n"/>
+      <c r="AG1" s="527" t="n"/>
+      <c r="AH1" s="531" t="n"/>
+      <c r="AI1" s="532" t="inlineStr">
         <is>
           <t>FRM-411</t>
         </is>
       </c>
-      <c r="AJ1" s="424" t="n"/>
-      <c r="AK1" s="424" t="n"/>
-      <c r="AL1" s="424" t="n"/>
-      <c r="AM1" s="424" t="n"/>
-      <c r="AN1" s="425" t="n"/>
+      <c r="AJ1" s="527" t="n"/>
+      <c r="AK1" s="527" t="n"/>
+      <c r="AL1" s="527" t="n"/>
+      <c r="AM1" s="527" t="n"/>
+      <c r="AN1" s="528" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1" s="329">
-      <c r="A2" s="426" t="n"/>
-      <c r="B2" s="25" t="n"/>
-      <c r="C2" s="25" t="n"/>
-      <c r="D2" s="25" t="n"/>
-      <c r="E2" s="25" t="n"/>
-      <c r="F2" s="25" t="n"/>
-      <c r="G2" s="25" t="n"/>
-      <c r="H2" s="427" t="n"/>
-      <c r="I2" s="428" t="n"/>
-      <c r="J2" s="429" t="n"/>
-      <c r="K2" s="429" t="n"/>
-      <c r="L2" s="429" t="n"/>
-      <c r="M2" s="429" t="n"/>
-      <c r="N2" s="429" t="n"/>
-      <c r="O2" s="429" t="n"/>
-      <c r="P2" s="429" t="n"/>
-      <c r="Q2" s="429" t="n"/>
-      <c r="R2" s="429" t="n"/>
-      <c r="S2" s="429" t="n"/>
-      <c r="T2" s="429" t="n"/>
-      <c r="U2" s="429" t="n"/>
-      <c r="V2" s="429" t="n"/>
-      <c r="W2" s="429" t="n"/>
-      <c r="X2" s="429" t="n"/>
-      <c r="Y2" s="429" t="n"/>
-      <c r="Z2" s="429" t="n"/>
-      <c r="AA2" s="429" t="n"/>
-      <c r="AB2" s="429" t="n"/>
-      <c r="AC2" s="429" t="n"/>
-      <c r="AD2" s="430" t="n"/>
-      <c r="AE2" s="431" t="n"/>
-      <c r="AF2" s="432" t="n"/>
-      <c r="AG2" s="432" t="n"/>
-      <c r="AH2" s="433" t="n"/>
-      <c r="AI2" s="434" t="inlineStr">
+      <c r="A2" s="533" t="n"/>
+      <c r="H2" s="534" t="n"/>
+      <c r="I2" s="533" t="n"/>
+      <c r="AD2" s="534" t="n"/>
+      <c r="AE2" s="535" t="n"/>
+      <c r="AF2" s="408" t="n"/>
+      <c r="AG2" s="408" t="n"/>
+      <c r="AH2" s="536" t="n"/>
+      <c r="AI2" s="537" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AJ2" s="435" t="n"/>
-      <c r="AK2" s="435" t="n"/>
-      <c r="AL2" s="435" t="n"/>
-      <c r="AM2" s="435" t="n"/>
-      <c r="AN2" s="436" t="n"/>
+      <c r="AJ2" s="408" t="n"/>
+      <c r="AK2" s="408" t="n"/>
+      <c r="AL2" s="408" t="n"/>
+      <c r="AM2" s="408" t="n"/>
+      <c r="AN2" s="538" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1" s="329">
-      <c r="A3" s="426" t="n"/>
-      <c r="B3" s="25" t="n"/>
-      <c r="C3" s="25" t="n"/>
-      <c r="D3" s="25" t="n"/>
-      <c r="E3" s="25" t="n"/>
-      <c r="F3" s="25" t="n"/>
-      <c r="G3" s="25" t="n"/>
-      <c r="H3" s="427" t="n"/>
-      <c r="I3" s="428" t="n"/>
-      <c r="J3" s="429" t="n"/>
-      <c r="K3" s="429" t="n"/>
-      <c r="L3" s="429" t="n"/>
-      <c r="M3" s="429" t="n"/>
-      <c r="N3" s="429" t="n"/>
-      <c r="O3" s="429" t="n"/>
-      <c r="P3" s="429" t="n"/>
-      <c r="Q3" s="429" t="n"/>
-      <c r="R3" s="429" t="n"/>
-      <c r="S3" s="429" t="n"/>
-      <c r="T3" s="429" t="n"/>
-      <c r="U3" s="429" t="n"/>
-      <c r="V3" s="429" t="n"/>
-      <c r="W3" s="429" t="n"/>
-      <c r="X3" s="429" t="n"/>
-      <c r="Y3" s="429" t="n"/>
-      <c r="Z3" s="429" t="n"/>
-      <c r="AA3" s="429" t="n"/>
-      <c r="AB3" s="429" t="n"/>
-      <c r="AC3" s="429" t="n"/>
-      <c r="AD3" s="430" t="n"/>
-      <c r="AE3" s="431" t="n"/>
-      <c r="AF3" s="432" t="n"/>
-      <c r="AG3" s="432" t="n"/>
-      <c r="AH3" s="433" t="n"/>
-      <c r="AI3" s="434" t="inlineStr">
+      <c r="A3" s="533" t="n"/>
+      <c r="H3" s="534" t="n"/>
+      <c r="I3" s="533" t="n"/>
+      <c r="AD3" s="534" t="n"/>
+      <c r="AE3" s="535" t="n"/>
+      <c r="AF3" s="408" t="n"/>
+      <c r="AG3" s="408" t="n"/>
+      <c r="AH3" s="536" t="n"/>
+      <c r="AI3" s="537" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AJ3" s="435" t="n"/>
-      <c r="AK3" s="435" t="n"/>
-      <c r="AL3" s="435" t="n"/>
-      <c r="AM3" s="435" t="n"/>
-      <c r="AN3" s="436" t="n"/>
+      <c r="AJ3" s="408" t="n"/>
+      <c r="AK3" s="408" t="n"/>
+      <c r="AL3" s="408" t="n"/>
+      <c r="AM3" s="408" t="n"/>
+      <c r="AN3" s="538" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1" s="329">
-      <c r="A4" s="426" t="n"/>
-      <c r="B4" s="25" t="n"/>
-      <c r="C4" s="25" t="n"/>
-      <c r="D4" s="25" t="n"/>
-      <c r="E4" s="25" t="n"/>
-      <c r="F4" s="25" t="n"/>
-      <c r="G4" s="25" t="n"/>
-      <c r="H4" s="427" t="n"/>
-      <c r="I4" s="437" t="inlineStr">
+      <c r="A4" s="533" t="n"/>
+      <c r="H4" s="534" t="n"/>
+      <c r="I4" s="539" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="J4" s="438" t="n"/>
-      <c r="K4" s="438" t="n"/>
-      <c r="L4" s="438" t="n"/>
-      <c r="M4" s="438" t="n"/>
-      <c r="N4" s="438" t="n"/>
-      <c r="O4" s="438" t="n"/>
-      <c r="P4" s="438" t="n"/>
-      <c r="Q4" s="438" t="n"/>
-      <c r="R4" s="438" t="n"/>
-      <c r="S4" s="438" t="n"/>
-      <c r="T4" s="438" t="n"/>
-      <c r="U4" s="438" t="n"/>
-      <c r="V4" s="438" t="n"/>
-      <c r="W4" s="438" t="n"/>
-      <c r="X4" s="438" t="n"/>
-      <c r="Y4" s="438" t="n"/>
-      <c r="Z4" s="438" t="n"/>
-      <c r="AA4" s="438" t="n"/>
-      <c r="AB4" s="438" t="n"/>
-      <c r="AC4" s="438" t="n"/>
-      <c r="AD4" s="439" t="n"/>
-      <c r="AE4" s="431" t="n"/>
-      <c r="AF4" s="432" t="n"/>
-      <c r="AG4" s="432" t="n"/>
-      <c r="AH4" s="433" t="n"/>
-      <c r="AI4" s="434" t="inlineStr">
+      <c r="AD4" s="534" t="n"/>
+      <c r="AE4" s="535" t="n"/>
+      <c r="AF4" s="408" t="n"/>
+      <c r="AG4" s="408" t="n"/>
+      <c r="AH4" s="536" t="n"/>
+      <c r="AI4" s="537" t="inlineStr">
         <is>
           <t>Purchasing + QA</t>
         </is>
       </c>
-      <c r="AJ4" s="435" t="n"/>
-      <c r="AK4" s="435" t="n"/>
-      <c r="AL4" s="435" t="n"/>
-      <c r="AM4" s="435" t="n"/>
-      <c r="AN4" s="436" t="n"/>
+      <c r="AJ4" s="408" t="n"/>
+      <c r="AK4" s="408" t="n"/>
+      <c r="AL4" s="408" t="n"/>
+      <c r="AM4" s="408" t="n"/>
+      <c r="AN4" s="538" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1" s="329">
-      <c r="A5" s="440" t="n"/>
-      <c r="B5" s="441" t="n"/>
-      <c r="C5" s="441" t="n"/>
-      <c r="D5" s="441" t="n"/>
-      <c r="E5" s="441" t="n"/>
-      <c r="F5" s="441" t="n"/>
-      <c r="G5" s="441" t="n"/>
-      <c r="H5" s="442" t="n"/>
-      <c r="I5" s="443" t="inlineStr">
+      <c r="A5" s="540" t="n"/>
+      <c r="B5" s="541" t="n"/>
+      <c r="C5" s="541" t="n"/>
+      <c r="D5" s="541" t="n"/>
+      <c r="E5" s="541" t="n"/>
+      <c r="F5" s="541" t="n"/>
+      <c r="G5" s="541" t="n"/>
+      <c r="H5" s="542" t="n"/>
+      <c r="I5" s="543" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="J5" s="444" t="n"/>
-      <c r="K5" s="444" t="n"/>
-      <c r="L5" s="444" t="n"/>
-      <c r="M5" s="444" t="n"/>
-      <c r="N5" s="444" t="n"/>
-      <c r="O5" s="444" t="n"/>
-      <c r="P5" s="444" t="n"/>
-      <c r="Q5" s="444" t="n"/>
-      <c r="R5" s="444" t="n"/>
-      <c r="S5" s="444" t="n"/>
-      <c r="T5" s="444" t="n"/>
-      <c r="U5" s="444" t="n"/>
-      <c r="V5" s="444" t="n"/>
-      <c r="W5" s="444" t="n"/>
-      <c r="X5" s="444" t="n"/>
-      <c r="Y5" s="444" t="n"/>
-      <c r="Z5" s="444" t="n"/>
-      <c r="AA5" s="444" t="n"/>
-      <c r="AB5" s="444" t="n"/>
-      <c r="AC5" s="444" t="n"/>
-      <c r="AD5" s="445" t="n"/>
-      <c r="AE5" s="446" t="n"/>
-      <c r="AF5" s="447" t="n"/>
-      <c r="AG5" s="447" t="n"/>
-      <c r="AH5" s="448" t="n"/>
-      <c r="AI5" s="449" t="inlineStr">
+      <c r="J5" s="541" t="n"/>
+      <c r="K5" s="541" t="n"/>
+      <c r="L5" s="541" t="n"/>
+      <c r="M5" s="541" t="n"/>
+      <c r="N5" s="541" t="n"/>
+      <c r="O5" s="541" t="n"/>
+      <c r="P5" s="541" t="n"/>
+      <c r="Q5" s="541" t="n"/>
+      <c r="R5" s="541" t="n"/>
+      <c r="S5" s="541" t="n"/>
+      <c r="T5" s="541" t="n"/>
+      <c r="U5" s="541" t="n"/>
+      <c r="V5" s="541" t="n"/>
+      <c r="W5" s="541" t="n"/>
+      <c r="X5" s="541" t="n"/>
+      <c r="Y5" s="541" t="n"/>
+      <c r="Z5" s="541" t="n"/>
+      <c r="AA5" s="541" t="n"/>
+      <c r="AB5" s="541" t="n"/>
+      <c r="AC5" s="541" t="n"/>
+      <c r="AD5" s="542" t="n"/>
+      <c r="AE5" s="544" t="n"/>
+      <c r="AF5" s="545" t="n"/>
+      <c r="AG5" s="545" t="n"/>
+      <c r="AH5" s="546" t="n"/>
+      <c r="AI5" s="547" t="inlineStr">
         <is>
           <t>General Manager</t>
         </is>
       </c>
-      <c r="AJ5" s="450" t="n"/>
-      <c r="AK5" s="450" t="n"/>
-      <c r="AL5" s="450" t="n"/>
-      <c r="AM5" s="450" t="n"/>
-      <c r="AN5" s="451" t="n"/>
+      <c r="AJ5" s="545" t="n"/>
+      <c r="AK5" s="545" t="n"/>
+      <c r="AL5" s="545" t="n"/>
+      <c r="AM5" s="545" t="n"/>
+      <c r="AN5" s="548" t="n"/>
     </row>
     <row r="6" ht="1.5" customHeight="1" s="329">
       <c r="A6" s="452" t="n"/>
@@ -6139,50 +6551,50 @@
       <c r="AN6" s="452" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1" s="329">
-      <c r="A7" s="453" t="inlineStr">
+      <c r="A7" s="549" t="inlineStr">
         <is>
           <t xml:space="preserve">  1. REFERENCE INFORMATION</t>
         </is>
       </c>
-      <c r="B7" s="454" t="n"/>
-      <c r="C7" s="454" t="n"/>
-      <c r="D7" s="454" t="n"/>
-      <c r="E7" s="454" t="n"/>
-      <c r="F7" s="454" t="n"/>
-      <c r="G7" s="454" t="n"/>
-      <c r="H7" s="454" t="n"/>
-      <c r="I7" s="454" t="n"/>
-      <c r="J7" s="454" t="n"/>
-      <c r="K7" s="454" t="n"/>
-      <c r="L7" s="454" t="n"/>
-      <c r="M7" s="454" t="n"/>
-      <c r="N7" s="454" t="n"/>
-      <c r="O7" s="454" t="n"/>
-      <c r="P7" s="454" t="n"/>
-      <c r="Q7" s="454" t="n"/>
-      <c r="R7" s="454" t="n"/>
-      <c r="S7" s="454" t="n"/>
-      <c r="T7" s="454" t="n"/>
-      <c r="U7" s="454" t="n"/>
-      <c r="V7" s="454" t="n"/>
-      <c r="W7" s="454" t="n"/>
-      <c r="X7" s="454" t="n"/>
-      <c r="Y7" s="454" t="n"/>
-      <c r="Z7" s="454" t="n"/>
-      <c r="AA7" s="454" t="n"/>
-      <c r="AB7" s="454" t="n"/>
-      <c r="AC7" s="454" t="n"/>
-      <c r="AD7" s="454" t="n"/>
-      <c r="AE7" s="454" t="n"/>
-      <c r="AF7" s="454" t="n"/>
-      <c r="AG7" s="454" t="n"/>
-      <c r="AH7" s="454" t="n"/>
-      <c r="AI7" s="454" t="n"/>
-      <c r="AJ7" s="454" t="n"/>
-      <c r="AK7" s="454" t="n"/>
-      <c r="AL7" s="454" t="n"/>
-      <c r="AM7" s="454" t="n"/>
-      <c r="AN7" s="455" t="n"/>
+      <c r="B7" s="550" t="n"/>
+      <c r="C7" s="550" t="n"/>
+      <c r="D7" s="550" t="n"/>
+      <c r="E7" s="550" t="n"/>
+      <c r="F7" s="550" t="n"/>
+      <c r="G7" s="550" t="n"/>
+      <c r="H7" s="550" t="n"/>
+      <c r="I7" s="550" t="n"/>
+      <c r="J7" s="550" t="n"/>
+      <c r="K7" s="550" t="n"/>
+      <c r="L7" s="550" t="n"/>
+      <c r="M7" s="550" t="n"/>
+      <c r="N7" s="550" t="n"/>
+      <c r="O7" s="550" t="n"/>
+      <c r="P7" s="550" t="n"/>
+      <c r="Q7" s="550" t="n"/>
+      <c r="R7" s="550" t="n"/>
+      <c r="S7" s="550" t="n"/>
+      <c r="T7" s="550" t="n"/>
+      <c r="U7" s="550" t="n"/>
+      <c r="V7" s="550" t="n"/>
+      <c r="W7" s="550" t="n"/>
+      <c r="X7" s="550" t="n"/>
+      <c r="Y7" s="550" t="n"/>
+      <c r="Z7" s="550" t="n"/>
+      <c r="AA7" s="550" t="n"/>
+      <c r="AB7" s="550" t="n"/>
+      <c r="AC7" s="550" t="n"/>
+      <c r="AD7" s="550" t="n"/>
+      <c r="AE7" s="550" t="n"/>
+      <c r="AF7" s="550" t="n"/>
+      <c r="AG7" s="550" t="n"/>
+      <c r="AH7" s="550" t="n"/>
+      <c r="AI7" s="550" t="n"/>
+      <c r="AJ7" s="550" t="n"/>
+      <c r="AK7" s="550" t="n"/>
+      <c r="AL7" s="550" t="n"/>
+      <c r="AM7" s="550" t="n"/>
+      <c r="AN7" s="551" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1" s="329">
       <c r="A8" s="456" t="inlineStr">
@@ -6190,49 +6602,49 @@
           <t>Incoming Verification ID</t>
         </is>
       </c>
-      <c r="B8" s="457" t="n"/>
-      <c r="C8" s="457" t="n"/>
-      <c r="D8" s="457" t="n"/>
-      <c r="E8" s="457" t="n"/>
-      <c r="F8" s="457" t="n"/>
-      <c r="G8" s="457" t="n"/>
+      <c r="B8" s="552" t="n"/>
+      <c r="C8" s="552" t="n"/>
+      <c r="D8" s="552" t="n"/>
+      <c r="E8" s="552" t="n"/>
+      <c r="F8" s="552" t="n"/>
+      <c r="G8" s="552" t="n"/>
       <c r="H8" s="458" t="n"/>
-      <c r="I8" s="457" t="n"/>
-      <c r="J8" s="457" t="n"/>
-      <c r="K8" s="457" t="n"/>
-      <c r="L8" s="457" t="n"/>
-      <c r="M8" s="457" t="n"/>
-      <c r="N8" s="457" t="n"/>
-      <c r="O8" s="457" t="n"/>
-      <c r="P8" s="457" t="n"/>
-      <c r="Q8" s="457" t="n"/>
-      <c r="R8" s="457" t="n"/>
-      <c r="S8" s="457" t="n"/>
-      <c r="T8" s="457" t="n"/>
+      <c r="I8" s="552" t="n"/>
+      <c r="J8" s="552" t="n"/>
+      <c r="K8" s="552" t="n"/>
+      <c r="L8" s="552" t="n"/>
+      <c r="M8" s="552" t="n"/>
+      <c r="N8" s="552" t="n"/>
+      <c r="O8" s="552" t="n"/>
+      <c r="P8" s="552" t="n"/>
+      <c r="Q8" s="552" t="n"/>
+      <c r="R8" s="552" t="n"/>
+      <c r="S8" s="552" t="n"/>
+      <c r="T8" s="552" t="n"/>
       <c r="U8" s="459" t="inlineStr">
         <is>
           <t>Disposition Status</t>
         </is>
       </c>
-      <c r="V8" s="457" t="n"/>
-      <c r="W8" s="457" t="n"/>
-      <c r="X8" s="457" t="n"/>
-      <c r="Y8" s="457" t="n"/>
-      <c r="Z8" s="457" t="n"/>
-      <c r="AA8" s="457" t="n"/>
-      <c r="AB8" s="458" t="n"/>
-      <c r="AC8" s="457" t="n"/>
-      <c r="AD8" s="457" t="n"/>
-      <c r="AE8" s="457" t="n"/>
-      <c r="AF8" s="457" t="n"/>
-      <c r="AG8" s="457" t="n"/>
-      <c r="AH8" s="457" t="n"/>
-      <c r="AI8" s="457" t="n"/>
-      <c r="AJ8" s="457" t="n"/>
-      <c r="AK8" s="457" t="n"/>
-      <c r="AL8" s="457" t="n"/>
-      <c r="AM8" s="457" t="n"/>
-      <c r="AN8" s="460" t="n"/>
+      <c r="V8" s="552" t="n"/>
+      <c r="W8" s="552" t="n"/>
+      <c r="X8" s="552" t="n"/>
+      <c r="Y8" s="552" t="n"/>
+      <c r="Z8" s="552" t="n"/>
+      <c r="AA8" s="552" t="n"/>
+      <c r="AB8" s="553" t="n"/>
+      <c r="AC8" s="552" t="n"/>
+      <c r="AD8" s="552" t="n"/>
+      <c r="AE8" s="552" t="n"/>
+      <c r="AF8" s="552" t="n"/>
+      <c r="AG8" s="552" t="n"/>
+      <c r="AH8" s="552" t="n"/>
+      <c r="AI8" s="552" t="n"/>
+      <c r="AJ8" s="552" t="n"/>
+      <c r="AK8" s="552" t="n"/>
+      <c r="AL8" s="552" t="n"/>
+      <c r="AM8" s="552" t="n"/>
+      <c r="AN8" s="554" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1" s="329">
       <c r="A9" s="461" t="inlineStr">
@@ -6240,49 +6652,49 @@
           <t>Supplier / Processor / Cert</t>
         </is>
       </c>
-      <c r="B9" s="341" t="n"/>
-      <c r="C9" s="341" t="n"/>
-      <c r="D9" s="341" t="n"/>
-      <c r="E9" s="341" t="n"/>
-      <c r="F9" s="341" t="n"/>
-      <c r="G9" s="341" t="n"/>
+      <c r="B9" s="409" t="n"/>
+      <c r="C9" s="409" t="n"/>
+      <c r="D9" s="409" t="n"/>
+      <c r="E9" s="409" t="n"/>
+      <c r="F9" s="409" t="n"/>
+      <c r="G9" s="409" t="n"/>
       <c r="H9" s="462" t="n"/>
-      <c r="I9" s="341" t="n"/>
-      <c r="J9" s="341" t="n"/>
-      <c r="K9" s="341" t="n"/>
-      <c r="L9" s="341" t="n"/>
-      <c r="M9" s="341" t="n"/>
-      <c r="N9" s="341" t="n"/>
-      <c r="O9" s="341" t="n"/>
-      <c r="P9" s="341" t="n"/>
-      <c r="Q9" s="341" t="n"/>
-      <c r="R9" s="341" t="n"/>
-      <c r="S9" s="341" t="n"/>
-      <c r="T9" s="341" t="n"/>
+      <c r="I9" s="409" t="n"/>
+      <c r="J9" s="409" t="n"/>
+      <c r="K9" s="409" t="n"/>
+      <c r="L9" s="409" t="n"/>
+      <c r="M9" s="409" t="n"/>
+      <c r="N9" s="409" t="n"/>
+      <c r="O9" s="409" t="n"/>
+      <c r="P9" s="409" t="n"/>
+      <c r="Q9" s="409" t="n"/>
+      <c r="R9" s="409" t="n"/>
+      <c r="S9" s="409" t="n"/>
+      <c r="T9" s="409" t="n"/>
       <c r="U9" s="463" t="inlineStr">
         <is>
           <t>PO / Cert / Lot Ref</t>
         </is>
       </c>
-      <c r="V9" s="341" t="n"/>
-      <c r="W9" s="341" t="n"/>
-      <c r="X9" s="341" t="n"/>
-      <c r="Y9" s="341" t="n"/>
-      <c r="Z9" s="341" t="n"/>
-      <c r="AA9" s="341" t="n"/>
-      <c r="AB9" s="462" t="n"/>
-      <c r="AC9" s="341" t="n"/>
-      <c r="AD9" s="341" t="n"/>
-      <c r="AE9" s="341" t="n"/>
-      <c r="AF9" s="341" t="n"/>
-      <c r="AG9" s="341" t="n"/>
-      <c r="AH9" s="341" t="n"/>
-      <c r="AI9" s="341" t="n"/>
-      <c r="AJ9" s="341" t="n"/>
-      <c r="AK9" s="341" t="n"/>
-      <c r="AL9" s="341" t="n"/>
-      <c r="AM9" s="341" t="n"/>
-      <c r="AN9" s="464" t="n"/>
+      <c r="V9" s="409" t="n"/>
+      <c r="W9" s="409" t="n"/>
+      <c r="X9" s="409" t="n"/>
+      <c r="Y9" s="409" t="n"/>
+      <c r="Z9" s="409" t="n"/>
+      <c r="AA9" s="409" t="n"/>
+      <c r="AB9" s="555" t="n"/>
+      <c r="AC9" s="409" t="n"/>
+      <c r="AD9" s="409" t="n"/>
+      <c r="AE9" s="409" t="n"/>
+      <c r="AF9" s="409" t="n"/>
+      <c r="AG9" s="409" t="n"/>
+      <c r="AH9" s="409" t="n"/>
+      <c r="AI9" s="409" t="n"/>
+      <c r="AJ9" s="409" t="n"/>
+      <c r="AK9" s="409" t="n"/>
+      <c r="AL9" s="409" t="n"/>
+      <c r="AM9" s="409" t="n"/>
+      <c r="AN9" s="556" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1" s="329">
       <c r="A10" s="461" t="inlineStr">
@@ -6290,49 +6702,49 @@
           <t>Part / Lot / Qty</t>
         </is>
       </c>
-      <c r="B10" s="341" t="n"/>
-      <c r="C10" s="341" t="n"/>
-      <c r="D10" s="341" t="n"/>
-      <c r="E10" s="341" t="n"/>
-      <c r="F10" s="341" t="n"/>
-      <c r="G10" s="341" t="n"/>
+      <c r="B10" s="409" t="n"/>
+      <c r="C10" s="409" t="n"/>
+      <c r="D10" s="409" t="n"/>
+      <c r="E10" s="409" t="n"/>
+      <c r="F10" s="409" t="n"/>
+      <c r="G10" s="409" t="n"/>
       <c r="H10" s="462" t="n"/>
-      <c r="I10" s="341" t="n"/>
-      <c r="J10" s="341" t="n"/>
-      <c r="K10" s="341" t="n"/>
-      <c r="L10" s="341" t="n"/>
-      <c r="M10" s="341" t="n"/>
-      <c r="N10" s="341" t="n"/>
-      <c r="O10" s="341" t="n"/>
-      <c r="P10" s="341" t="n"/>
-      <c r="Q10" s="341" t="n"/>
-      <c r="R10" s="341" t="n"/>
-      <c r="S10" s="341" t="n"/>
-      <c r="T10" s="341" t="n"/>
+      <c r="I10" s="409" t="n"/>
+      <c r="J10" s="409" t="n"/>
+      <c r="K10" s="409" t="n"/>
+      <c r="L10" s="409" t="n"/>
+      <c r="M10" s="409" t="n"/>
+      <c r="N10" s="409" t="n"/>
+      <c r="O10" s="409" t="n"/>
+      <c r="P10" s="409" t="n"/>
+      <c r="Q10" s="409" t="n"/>
+      <c r="R10" s="409" t="n"/>
+      <c r="S10" s="409" t="n"/>
+      <c r="T10" s="409" t="n"/>
       <c r="U10" s="463" t="inlineStr">
         <is>
           <t>Supplier-Quality Owner</t>
         </is>
       </c>
-      <c r="V10" s="341" t="n"/>
-      <c r="W10" s="341" t="n"/>
-      <c r="X10" s="341" t="n"/>
-      <c r="Y10" s="341" t="n"/>
-      <c r="Z10" s="341" t="n"/>
-      <c r="AA10" s="341" t="n"/>
-      <c r="AB10" s="462" t="n"/>
-      <c r="AC10" s="341" t="n"/>
-      <c r="AD10" s="341" t="n"/>
-      <c r="AE10" s="341" t="n"/>
-      <c r="AF10" s="341" t="n"/>
-      <c r="AG10" s="341" t="n"/>
-      <c r="AH10" s="341" t="n"/>
-      <c r="AI10" s="341" t="n"/>
-      <c r="AJ10" s="341" t="n"/>
-      <c r="AK10" s="341" t="n"/>
-      <c r="AL10" s="341" t="n"/>
-      <c r="AM10" s="341" t="n"/>
-      <c r="AN10" s="464" t="n"/>
+      <c r="V10" s="409" t="n"/>
+      <c r="W10" s="409" t="n"/>
+      <c r="X10" s="409" t="n"/>
+      <c r="Y10" s="409" t="n"/>
+      <c r="Z10" s="409" t="n"/>
+      <c r="AA10" s="409" t="n"/>
+      <c r="AB10" s="555" t="n"/>
+      <c r="AC10" s="409" t="n"/>
+      <c r="AD10" s="409" t="n"/>
+      <c r="AE10" s="409" t="n"/>
+      <c r="AF10" s="409" t="n"/>
+      <c r="AG10" s="409" t="n"/>
+      <c r="AH10" s="409" t="n"/>
+      <c r="AI10" s="409" t="n"/>
+      <c r="AJ10" s="409" t="n"/>
+      <c r="AK10" s="409" t="n"/>
+      <c r="AL10" s="409" t="n"/>
+      <c r="AM10" s="409" t="n"/>
+      <c r="AN10" s="556" t="n"/>
     </row>
     <row r="11" ht="26" customHeight="1" s="329">
       <c r="A11" s="461" t="inlineStr">
@@ -6340,49 +6752,49 @@
           <t>Prepared by / Date-Time</t>
         </is>
       </c>
-      <c r="B11" s="341" t="n"/>
-      <c r="C11" s="341" t="n"/>
-      <c r="D11" s="341" t="n"/>
-      <c r="E11" s="341" t="n"/>
-      <c r="F11" s="341" t="n"/>
-      <c r="G11" s="341" t="n"/>
+      <c r="B11" s="409" t="n"/>
+      <c r="C11" s="409" t="n"/>
+      <c r="D11" s="409" t="n"/>
+      <c r="E11" s="409" t="n"/>
+      <c r="F11" s="409" t="n"/>
+      <c r="G11" s="409" t="n"/>
       <c r="H11" s="462" t="n"/>
-      <c r="I11" s="341" t="n"/>
-      <c r="J11" s="341" t="n"/>
-      <c r="K11" s="341" t="n"/>
-      <c r="L11" s="341" t="n"/>
-      <c r="M11" s="341" t="n"/>
-      <c r="N11" s="341" t="n"/>
-      <c r="O11" s="341" t="n"/>
-      <c r="P11" s="341" t="n"/>
-      <c r="Q11" s="341" t="n"/>
-      <c r="R11" s="341" t="n"/>
-      <c r="S11" s="341" t="n"/>
-      <c r="T11" s="341" t="n"/>
+      <c r="I11" s="409" t="n"/>
+      <c r="J11" s="409" t="n"/>
+      <c r="K11" s="409" t="n"/>
+      <c r="L11" s="409" t="n"/>
+      <c r="M11" s="409" t="n"/>
+      <c r="N11" s="409" t="n"/>
+      <c r="O11" s="409" t="n"/>
+      <c r="P11" s="409" t="n"/>
+      <c r="Q11" s="409" t="n"/>
+      <c r="R11" s="409" t="n"/>
+      <c r="S11" s="409" t="n"/>
+      <c r="T11" s="409" t="n"/>
       <c r="U11" s="463" t="inlineStr">
         <is>
           <t>Record Status</t>
         </is>
       </c>
-      <c r="V11" s="341" t="n"/>
-      <c r="W11" s="341" t="n"/>
-      <c r="X11" s="341" t="n"/>
-      <c r="Y11" s="341" t="n"/>
-      <c r="Z11" s="341" t="n"/>
-      <c r="AA11" s="341" t="n"/>
-      <c r="AB11" s="462" t="n"/>
-      <c r="AC11" s="341" t="n"/>
-      <c r="AD11" s="341" t="n"/>
-      <c r="AE11" s="341" t="n"/>
-      <c r="AF11" s="341" t="n"/>
-      <c r="AG11" s="341" t="n"/>
-      <c r="AH11" s="341" t="n"/>
-      <c r="AI11" s="341" t="n"/>
-      <c r="AJ11" s="341" t="n"/>
-      <c r="AK11" s="341" t="n"/>
-      <c r="AL11" s="341" t="n"/>
-      <c r="AM11" s="341" t="n"/>
-      <c r="AN11" s="464" t="n"/>
+      <c r="V11" s="409" t="n"/>
+      <c r="W11" s="409" t="n"/>
+      <c r="X11" s="409" t="n"/>
+      <c r="Y11" s="409" t="n"/>
+      <c r="Z11" s="409" t="n"/>
+      <c r="AA11" s="409" t="n"/>
+      <c r="AB11" s="555" t="n"/>
+      <c r="AC11" s="409" t="n"/>
+      <c r="AD11" s="409" t="n"/>
+      <c r="AE11" s="409" t="n"/>
+      <c r="AF11" s="409" t="n"/>
+      <c r="AG11" s="409" t="n"/>
+      <c r="AH11" s="409" t="n"/>
+      <c r="AI11" s="409" t="n"/>
+      <c r="AJ11" s="409" t="n"/>
+      <c r="AK11" s="409" t="n"/>
+      <c r="AL11" s="409" t="n"/>
+      <c r="AM11" s="409" t="n"/>
+      <c r="AN11" s="556" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1" s="329">
       <c r="A12" s="461" t="inlineStr">
@@ -6390,49 +6802,49 @@
           <t>Evidence Package Ref</t>
         </is>
       </c>
-      <c r="B12" s="341" t="n"/>
-      <c r="C12" s="341" t="n"/>
-      <c r="D12" s="341" t="n"/>
-      <c r="E12" s="341" t="n"/>
-      <c r="F12" s="341" t="n"/>
-      <c r="G12" s="341" t="n"/>
+      <c r="B12" s="409" t="n"/>
+      <c r="C12" s="409" t="n"/>
+      <c r="D12" s="409" t="n"/>
+      <c r="E12" s="409" t="n"/>
+      <c r="F12" s="409" t="n"/>
+      <c r="G12" s="409" t="n"/>
       <c r="H12" s="462" t="n"/>
-      <c r="I12" s="341" t="n"/>
-      <c r="J12" s="341" t="n"/>
-      <c r="K12" s="341" t="n"/>
-      <c r="L12" s="341" t="n"/>
-      <c r="M12" s="341" t="n"/>
-      <c r="N12" s="341" t="n"/>
-      <c r="O12" s="341" t="n"/>
-      <c r="P12" s="341" t="n"/>
-      <c r="Q12" s="341" t="n"/>
-      <c r="R12" s="341" t="n"/>
-      <c r="S12" s="341" t="n"/>
-      <c r="T12" s="341" t="n"/>
+      <c r="I12" s="409" t="n"/>
+      <c r="J12" s="409" t="n"/>
+      <c r="K12" s="409" t="n"/>
+      <c r="L12" s="409" t="n"/>
+      <c r="M12" s="409" t="n"/>
+      <c r="N12" s="409" t="n"/>
+      <c r="O12" s="409" t="n"/>
+      <c r="P12" s="409" t="n"/>
+      <c r="Q12" s="409" t="n"/>
+      <c r="R12" s="409" t="n"/>
+      <c r="S12" s="409" t="n"/>
+      <c r="T12" s="409" t="n"/>
       <c r="U12" s="463" t="inlineStr">
         <is>
           <t>Risk Level</t>
         </is>
       </c>
-      <c r="V12" s="341" t="n"/>
-      <c r="W12" s="341" t="n"/>
-      <c r="X12" s="341" t="n"/>
-      <c r="Y12" s="341" t="n"/>
-      <c r="Z12" s="341" t="n"/>
-      <c r="AA12" s="341" t="n"/>
-      <c r="AB12" s="462" t="n"/>
-      <c r="AC12" s="341" t="n"/>
-      <c r="AD12" s="341" t="n"/>
-      <c r="AE12" s="341" t="n"/>
-      <c r="AF12" s="341" t="n"/>
-      <c r="AG12" s="341" t="n"/>
-      <c r="AH12" s="341" t="n"/>
-      <c r="AI12" s="341" t="n"/>
-      <c r="AJ12" s="341" t="n"/>
-      <c r="AK12" s="341" t="n"/>
-      <c r="AL12" s="341" t="n"/>
-      <c r="AM12" s="341" t="n"/>
-      <c r="AN12" s="464" t="n"/>
+      <c r="V12" s="409" t="n"/>
+      <c r="W12" s="409" t="n"/>
+      <c r="X12" s="409" t="n"/>
+      <c r="Y12" s="409" t="n"/>
+      <c r="Z12" s="409" t="n"/>
+      <c r="AA12" s="409" t="n"/>
+      <c r="AB12" s="555" t="n"/>
+      <c r="AC12" s="409" t="n"/>
+      <c r="AD12" s="409" t="n"/>
+      <c r="AE12" s="409" t="n"/>
+      <c r="AF12" s="409" t="n"/>
+      <c r="AG12" s="409" t="n"/>
+      <c r="AH12" s="409" t="n"/>
+      <c r="AI12" s="409" t="n"/>
+      <c r="AJ12" s="409" t="n"/>
+      <c r="AK12" s="409" t="n"/>
+      <c r="AL12" s="409" t="n"/>
+      <c r="AM12" s="409" t="n"/>
+      <c r="AN12" s="556" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1" s="329">
       <c r="A13" s="465" t="inlineStr">
@@ -6440,49 +6852,49 @@
           <t>Method / Acceptance Ref</t>
         </is>
       </c>
-      <c r="B13" s="466" t="n"/>
-      <c r="C13" s="466" t="n"/>
-      <c r="D13" s="466" t="n"/>
-      <c r="E13" s="466" t="n"/>
-      <c r="F13" s="466" t="n"/>
-      <c r="G13" s="466" t="n"/>
+      <c r="B13" s="545" t="n"/>
+      <c r="C13" s="545" t="n"/>
+      <c r="D13" s="545" t="n"/>
+      <c r="E13" s="545" t="n"/>
+      <c r="F13" s="545" t="n"/>
+      <c r="G13" s="545" t="n"/>
       <c r="H13" s="467" t="n"/>
-      <c r="I13" s="466" t="n"/>
-      <c r="J13" s="466" t="n"/>
-      <c r="K13" s="466" t="n"/>
-      <c r="L13" s="466" t="n"/>
-      <c r="M13" s="466" t="n"/>
-      <c r="N13" s="466" t="n"/>
-      <c r="O13" s="466" t="n"/>
-      <c r="P13" s="466" t="n"/>
-      <c r="Q13" s="466" t="n"/>
-      <c r="R13" s="466" t="n"/>
-      <c r="S13" s="466" t="n"/>
-      <c r="T13" s="466" t="n"/>
+      <c r="I13" s="545" t="n"/>
+      <c r="J13" s="545" t="n"/>
+      <c r="K13" s="545" t="n"/>
+      <c r="L13" s="545" t="n"/>
+      <c r="M13" s="545" t="n"/>
+      <c r="N13" s="545" t="n"/>
+      <c r="O13" s="545" t="n"/>
+      <c r="P13" s="545" t="n"/>
+      <c r="Q13" s="545" t="n"/>
+      <c r="R13" s="545" t="n"/>
+      <c r="S13" s="545" t="n"/>
+      <c r="T13" s="545" t="n"/>
       <c r="U13" s="468" t="inlineStr">
         <is>
           <t>Affected Job Ref</t>
         </is>
       </c>
-      <c r="V13" s="466" t="n"/>
-      <c r="W13" s="466" t="n"/>
-      <c r="X13" s="466" t="n"/>
-      <c r="Y13" s="466" t="n"/>
-      <c r="Z13" s="466" t="n"/>
-      <c r="AA13" s="466" t="n"/>
-      <c r="AB13" s="467" t="n"/>
-      <c r="AC13" s="466" t="n"/>
-      <c r="AD13" s="466" t="n"/>
-      <c r="AE13" s="466" t="n"/>
-      <c r="AF13" s="466" t="n"/>
-      <c r="AG13" s="466" t="n"/>
-      <c r="AH13" s="466" t="n"/>
-      <c r="AI13" s="466" t="n"/>
-      <c r="AJ13" s="466" t="n"/>
-      <c r="AK13" s="466" t="n"/>
-      <c r="AL13" s="466" t="n"/>
-      <c r="AM13" s="466" t="n"/>
-      <c r="AN13" s="469" t="n"/>
+      <c r="V13" s="545" t="n"/>
+      <c r="W13" s="545" t="n"/>
+      <c r="X13" s="545" t="n"/>
+      <c r="Y13" s="545" t="n"/>
+      <c r="Z13" s="545" t="n"/>
+      <c r="AA13" s="545" t="n"/>
+      <c r="AB13" s="557" t="n"/>
+      <c r="AC13" s="545" t="n"/>
+      <c r="AD13" s="545" t="n"/>
+      <c r="AE13" s="545" t="n"/>
+      <c r="AF13" s="545" t="n"/>
+      <c r="AG13" s="545" t="n"/>
+      <c r="AH13" s="545" t="n"/>
+      <c r="AI13" s="545" t="n"/>
+      <c r="AJ13" s="545" t="n"/>
+      <c r="AK13" s="545" t="n"/>
+      <c r="AL13" s="545" t="n"/>
+      <c r="AM13" s="545" t="n"/>
+      <c r="AN13" s="548" t="n"/>
     </row>
     <row r="14" ht="3" customHeight="1" s="329">
       <c r="A14" s="357" t="n"/>
@@ -6527,50 +6939,50 @@
       <c r="AN14" s="350" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1" s="329">
-      <c r="A15" s="453" t="inlineStr">
+      <c r="A15" s="549" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. INCOMING VERIFICATION / FINDING DETAIL</t>
         </is>
       </c>
-      <c r="B15" s="454" t="n"/>
-      <c r="C15" s="454" t="n"/>
-      <c r="D15" s="454" t="n"/>
-      <c r="E15" s="454" t="n"/>
-      <c r="F15" s="454" t="n"/>
-      <c r="G15" s="454" t="n"/>
-      <c r="H15" s="454" t="n"/>
-      <c r="I15" s="454" t="n"/>
-      <c r="J15" s="454" t="n"/>
-      <c r="K15" s="454" t="n"/>
-      <c r="L15" s="454" t="n"/>
-      <c r="M15" s="454" t="n"/>
-      <c r="N15" s="454" t="n"/>
-      <c r="O15" s="454" t="n"/>
-      <c r="P15" s="454" t="n"/>
-      <c r="Q15" s="454" t="n"/>
-      <c r="R15" s="454" t="n"/>
-      <c r="S15" s="454" t="n"/>
-      <c r="T15" s="454" t="n"/>
-      <c r="U15" s="454" t="n"/>
-      <c r="V15" s="454" t="n"/>
-      <c r="W15" s="454" t="n"/>
-      <c r="X15" s="454" t="n"/>
-      <c r="Y15" s="454" t="n"/>
-      <c r="Z15" s="454" t="n"/>
-      <c r="AA15" s="454" t="n"/>
-      <c r="AB15" s="454" t="n"/>
-      <c r="AC15" s="454" t="n"/>
-      <c r="AD15" s="454" t="n"/>
-      <c r="AE15" s="454" t="n"/>
-      <c r="AF15" s="454" t="n"/>
-      <c r="AG15" s="454" t="n"/>
-      <c r="AH15" s="454" t="n"/>
-      <c r="AI15" s="454" t="n"/>
-      <c r="AJ15" s="454" t="n"/>
-      <c r="AK15" s="454" t="n"/>
-      <c r="AL15" s="454" t="n"/>
-      <c r="AM15" s="454" t="n"/>
-      <c r="AN15" s="455" t="n"/>
+      <c r="B15" s="550" t="n"/>
+      <c r="C15" s="550" t="n"/>
+      <c r="D15" s="550" t="n"/>
+      <c r="E15" s="550" t="n"/>
+      <c r="F15" s="550" t="n"/>
+      <c r="G15" s="550" t="n"/>
+      <c r="H15" s="550" t="n"/>
+      <c r="I15" s="550" t="n"/>
+      <c r="J15" s="550" t="n"/>
+      <c r="K15" s="550" t="n"/>
+      <c r="L15" s="550" t="n"/>
+      <c r="M15" s="550" t="n"/>
+      <c r="N15" s="550" t="n"/>
+      <c r="O15" s="550" t="n"/>
+      <c r="P15" s="550" t="n"/>
+      <c r="Q15" s="550" t="n"/>
+      <c r="R15" s="550" t="n"/>
+      <c r="S15" s="550" t="n"/>
+      <c r="T15" s="550" t="n"/>
+      <c r="U15" s="550" t="n"/>
+      <c r="V15" s="550" t="n"/>
+      <c r="W15" s="550" t="n"/>
+      <c r="X15" s="550" t="n"/>
+      <c r="Y15" s="550" t="n"/>
+      <c r="Z15" s="550" t="n"/>
+      <c r="AA15" s="550" t="n"/>
+      <c r="AB15" s="550" t="n"/>
+      <c r="AC15" s="550" t="n"/>
+      <c r="AD15" s="550" t="n"/>
+      <c r="AE15" s="550" t="n"/>
+      <c r="AF15" s="550" t="n"/>
+      <c r="AG15" s="550" t="n"/>
+      <c r="AH15" s="550" t="n"/>
+      <c r="AI15" s="550" t="n"/>
+      <c r="AJ15" s="550" t="n"/>
+      <c r="AK15" s="550" t="n"/>
+      <c r="AL15" s="550" t="n"/>
+      <c r="AM15" s="550" t="n"/>
+      <c r="AN15" s="551" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1" s="329">
       <c r="A16" s="456" t="inlineStr">
@@ -6578,49 +6990,49 @@
           <t>Risk Level</t>
         </is>
       </c>
-      <c r="B16" s="457" t="n"/>
-      <c r="C16" s="457" t="n"/>
-      <c r="D16" s="457" t="n"/>
-      <c r="E16" s="457" t="n"/>
-      <c r="F16" s="457" t="n"/>
-      <c r="G16" s="457" t="n"/>
+      <c r="B16" s="552" t="n"/>
+      <c r="C16" s="552" t="n"/>
+      <c r="D16" s="552" t="n"/>
+      <c r="E16" s="552" t="n"/>
+      <c r="F16" s="552" t="n"/>
+      <c r="G16" s="552" t="n"/>
       <c r="H16" s="458" t="n"/>
-      <c r="I16" s="457" t="n"/>
-      <c r="J16" s="457" t="n"/>
-      <c r="K16" s="457" t="n"/>
-      <c r="L16" s="457" t="n"/>
-      <c r="M16" s="457" t="n"/>
-      <c r="N16" s="457" t="n"/>
-      <c r="O16" s="457" t="n"/>
-      <c r="P16" s="457" t="n"/>
-      <c r="Q16" s="457" t="n"/>
-      <c r="R16" s="457" t="n"/>
-      <c r="S16" s="457" t="n"/>
-      <c r="T16" s="457" t="n"/>
+      <c r="I16" s="552" t="n"/>
+      <c r="J16" s="552" t="n"/>
+      <c r="K16" s="552" t="n"/>
+      <c r="L16" s="552" t="n"/>
+      <c r="M16" s="552" t="n"/>
+      <c r="N16" s="552" t="n"/>
+      <c r="O16" s="552" t="n"/>
+      <c r="P16" s="552" t="n"/>
+      <c r="Q16" s="552" t="n"/>
+      <c r="R16" s="552" t="n"/>
+      <c r="S16" s="552" t="n"/>
+      <c r="T16" s="552" t="n"/>
       <c r="U16" s="459" t="inlineStr">
         <is>
           <t>Countermeasure / Trigger</t>
         </is>
       </c>
-      <c r="V16" s="457" t="n"/>
-      <c r="W16" s="457" t="n"/>
-      <c r="X16" s="457" t="n"/>
-      <c r="Y16" s="457" t="n"/>
-      <c r="Z16" s="457" t="n"/>
-      <c r="AA16" s="457" t="n"/>
-      <c r="AB16" s="458" t="n"/>
-      <c r="AC16" s="457" t="n"/>
-      <c r="AD16" s="457" t="n"/>
-      <c r="AE16" s="457" t="n"/>
-      <c r="AF16" s="457" t="n"/>
-      <c r="AG16" s="457" t="n"/>
-      <c r="AH16" s="457" t="n"/>
-      <c r="AI16" s="457" t="n"/>
-      <c r="AJ16" s="457" t="n"/>
-      <c r="AK16" s="457" t="n"/>
-      <c r="AL16" s="457" t="n"/>
-      <c r="AM16" s="457" t="n"/>
-      <c r="AN16" s="460" t="n"/>
+      <c r="V16" s="552" t="n"/>
+      <c r="W16" s="552" t="n"/>
+      <c r="X16" s="552" t="n"/>
+      <c r="Y16" s="552" t="n"/>
+      <c r="Z16" s="552" t="n"/>
+      <c r="AA16" s="552" t="n"/>
+      <c r="AB16" s="553" t="n"/>
+      <c r="AC16" s="552" t="n"/>
+      <c r="AD16" s="552" t="n"/>
+      <c r="AE16" s="552" t="n"/>
+      <c r="AF16" s="552" t="n"/>
+      <c r="AG16" s="552" t="n"/>
+      <c r="AH16" s="552" t="n"/>
+      <c r="AI16" s="552" t="n"/>
+      <c r="AJ16" s="552" t="n"/>
+      <c r="AK16" s="552" t="n"/>
+      <c r="AL16" s="552" t="n"/>
+      <c r="AM16" s="552" t="n"/>
+      <c r="AN16" s="554" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1" s="329">
       <c r="A17" s="461" t="inlineStr">
@@ -6628,309 +7040,309 @@
           <t>Related Requirement / Package</t>
         </is>
       </c>
-      <c r="B17" s="341" t="n"/>
-      <c r="C17" s="341" t="n"/>
-      <c r="D17" s="341" t="n"/>
-      <c r="E17" s="341" t="n"/>
-      <c r="F17" s="341" t="n"/>
-      <c r="G17" s="341" t="n"/>
+      <c r="B17" s="409" t="n"/>
+      <c r="C17" s="409" t="n"/>
+      <c r="D17" s="409" t="n"/>
+      <c r="E17" s="409" t="n"/>
+      <c r="F17" s="409" t="n"/>
+      <c r="G17" s="409" t="n"/>
       <c r="H17" s="462" t="n"/>
-      <c r="I17" s="341" t="n"/>
-      <c r="J17" s="341" t="n"/>
-      <c r="K17" s="341" t="n"/>
-      <c r="L17" s="341" t="n"/>
-      <c r="M17" s="341" t="n"/>
-      <c r="N17" s="341" t="n"/>
-      <c r="O17" s="341" t="n"/>
-      <c r="P17" s="341" t="n"/>
-      <c r="Q17" s="341" t="n"/>
-      <c r="R17" s="341" t="n"/>
-      <c r="S17" s="341" t="n"/>
-      <c r="T17" s="341" t="n"/>
+      <c r="I17" s="409" t="n"/>
+      <c r="J17" s="409" t="n"/>
+      <c r="K17" s="409" t="n"/>
+      <c r="L17" s="409" t="n"/>
+      <c r="M17" s="409" t="n"/>
+      <c r="N17" s="409" t="n"/>
+      <c r="O17" s="409" t="n"/>
+      <c r="P17" s="409" t="n"/>
+      <c r="Q17" s="409" t="n"/>
+      <c r="R17" s="409" t="n"/>
+      <c r="S17" s="409" t="n"/>
+      <c r="T17" s="409" t="n"/>
       <c r="U17" s="463" t="inlineStr">
         <is>
           <t>Customer Special Requirement (YES/NO)</t>
         </is>
       </c>
-      <c r="V17" s="341" t="n"/>
-      <c r="W17" s="341" t="n"/>
-      <c r="X17" s="341" t="n"/>
-      <c r="Y17" s="341" t="n"/>
-      <c r="Z17" s="341" t="n"/>
-      <c r="AA17" s="341" t="n"/>
-      <c r="AB17" s="462" t="n"/>
-      <c r="AC17" s="341" t="n"/>
-      <c r="AD17" s="341" t="n"/>
-      <c r="AE17" s="341" t="n"/>
-      <c r="AF17" s="341" t="n"/>
-      <c r="AG17" s="341" t="n"/>
-      <c r="AH17" s="341" t="n"/>
-      <c r="AI17" s="341" t="n"/>
-      <c r="AJ17" s="341" t="n"/>
-      <c r="AK17" s="341" t="n"/>
-      <c r="AL17" s="341" t="n"/>
-      <c r="AM17" s="341" t="n"/>
-      <c r="AN17" s="464" t="n"/>
+      <c r="V17" s="409" t="n"/>
+      <c r="W17" s="409" t="n"/>
+      <c r="X17" s="409" t="n"/>
+      <c r="Y17" s="409" t="n"/>
+      <c r="Z17" s="409" t="n"/>
+      <c r="AA17" s="409" t="n"/>
+      <c r="AB17" s="555" t="n"/>
+      <c r="AC17" s="409" t="n"/>
+      <c r="AD17" s="409" t="n"/>
+      <c r="AE17" s="409" t="n"/>
+      <c r="AF17" s="409" t="n"/>
+      <c r="AG17" s="409" t="n"/>
+      <c r="AH17" s="409" t="n"/>
+      <c r="AI17" s="409" t="n"/>
+      <c r="AJ17" s="409" t="n"/>
+      <c r="AK17" s="409" t="n"/>
+      <c r="AL17" s="409" t="n"/>
+      <c r="AM17" s="409" t="n"/>
+      <c r="AN17" s="556" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1" s="329">
-      <c r="A18" s="461" t="inlineStr">
+      <c r="A18" s="558" t="inlineStr">
         <is>
           <t>VERIFICATION / SCOPE DESCRIPTION</t>
         </is>
       </c>
-      <c r="B18" s="341" t="n"/>
-      <c r="C18" s="341" t="n"/>
-      <c r="D18" s="341" t="n"/>
-      <c r="E18" s="341" t="n"/>
-      <c r="F18" s="341" t="n"/>
-      <c r="G18" s="341" t="n"/>
-      <c r="H18" s="470" t="n"/>
-      <c r="I18" s="341" t="n"/>
-      <c r="J18" s="341" t="n"/>
-      <c r="K18" s="341" t="n"/>
-      <c r="L18" s="341" t="n"/>
-      <c r="M18" s="341" t="n"/>
-      <c r="N18" s="341" t="n"/>
-      <c r="O18" s="341" t="n"/>
-      <c r="P18" s="341" t="n"/>
-      <c r="Q18" s="341" t="n"/>
-      <c r="R18" s="341" t="n"/>
-      <c r="S18" s="341" t="n"/>
-      <c r="T18" s="341" t="n"/>
-      <c r="U18" s="470" t="n"/>
-      <c r="V18" s="341" t="n"/>
-      <c r="W18" s="341" t="n"/>
-      <c r="X18" s="341" t="n"/>
-      <c r="Y18" s="341" t="n"/>
-      <c r="Z18" s="341" t="n"/>
-      <c r="AA18" s="341" t="n"/>
-      <c r="AB18" s="470" t="n"/>
-      <c r="AC18" s="341" t="n"/>
-      <c r="AD18" s="341" t="n"/>
-      <c r="AE18" s="341" t="n"/>
-      <c r="AF18" s="341" t="n"/>
-      <c r="AG18" s="341" t="n"/>
-      <c r="AH18" s="341" t="n"/>
-      <c r="AI18" s="341" t="n"/>
-      <c r="AJ18" s="341" t="n"/>
-      <c r="AK18" s="341" t="n"/>
-      <c r="AL18" s="341" t="n"/>
-      <c r="AM18" s="341" t="n"/>
-      <c r="AN18" s="464" t="n"/>
+      <c r="B18" s="409" t="n"/>
+      <c r="C18" s="409" t="n"/>
+      <c r="D18" s="409" t="n"/>
+      <c r="E18" s="409" t="n"/>
+      <c r="F18" s="409" t="n"/>
+      <c r="G18" s="409" t="n"/>
+      <c r="H18" s="409" t="n"/>
+      <c r="I18" s="409" t="n"/>
+      <c r="J18" s="409" t="n"/>
+      <c r="K18" s="409" t="n"/>
+      <c r="L18" s="409" t="n"/>
+      <c r="M18" s="409" t="n"/>
+      <c r="N18" s="409" t="n"/>
+      <c r="O18" s="409" t="n"/>
+      <c r="P18" s="409" t="n"/>
+      <c r="Q18" s="409" t="n"/>
+      <c r="R18" s="409" t="n"/>
+      <c r="S18" s="409" t="n"/>
+      <c r="T18" s="409" t="n"/>
+      <c r="U18" s="409" t="n"/>
+      <c r="V18" s="409" t="n"/>
+      <c r="W18" s="409" t="n"/>
+      <c r="X18" s="409" t="n"/>
+      <c r="Y18" s="409" t="n"/>
+      <c r="Z18" s="409" t="n"/>
+      <c r="AA18" s="409" t="n"/>
+      <c r="AB18" s="409" t="n"/>
+      <c r="AC18" s="409" t="n"/>
+      <c r="AD18" s="409" t="n"/>
+      <c r="AE18" s="409" t="n"/>
+      <c r="AF18" s="409" t="n"/>
+      <c r="AG18" s="409" t="n"/>
+      <c r="AH18" s="409" t="n"/>
+      <c r="AI18" s="409" t="n"/>
+      <c r="AJ18" s="409" t="n"/>
+      <c r="AK18" s="409" t="n"/>
+      <c r="AL18" s="409" t="n"/>
+      <c r="AM18" s="409" t="n"/>
+      <c r="AN18" s="556" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1" s="329">
-      <c r="A19" s="471" t="n"/>
-      <c r="B19" s="341" t="n"/>
-      <c r="C19" s="341" t="n"/>
-      <c r="D19" s="341" t="n"/>
-      <c r="E19" s="341" t="n"/>
-      <c r="F19" s="341" t="n"/>
-      <c r="G19" s="341" t="n"/>
-      <c r="H19" s="470" t="n"/>
-      <c r="I19" s="341" t="n"/>
-      <c r="J19" s="341" t="n"/>
-      <c r="K19" s="341" t="n"/>
-      <c r="L19" s="341" t="n"/>
-      <c r="M19" s="341" t="n"/>
-      <c r="N19" s="341" t="n"/>
-      <c r="O19" s="341" t="n"/>
-      <c r="P19" s="341" t="n"/>
-      <c r="Q19" s="341" t="n"/>
-      <c r="R19" s="341" t="n"/>
-      <c r="S19" s="341" t="n"/>
-      <c r="T19" s="341" t="n"/>
-      <c r="U19" s="470" t="n"/>
-      <c r="V19" s="341" t="n"/>
-      <c r="W19" s="341" t="n"/>
-      <c r="X19" s="341" t="n"/>
-      <c r="Y19" s="341" t="n"/>
-      <c r="Z19" s="341" t="n"/>
-      <c r="AA19" s="341" t="n"/>
-      <c r="AB19" s="470" t="n"/>
-      <c r="AC19" s="341" t="n"/>
-      <c r="AD19" s="341" t="n"/>
-      <c r="AE19" s="341" t="n"/>
-      <c r="AF19" s="341" t="n"/>
-      <c r="AG19" s="341" t="n"/>
-      <c r="AH19" s="341" t="n"/>
-      <c r="AI19" s="341" t="n"/>
-      <c r="AJ19" s="341" t="n"/>
-      <c r="AK19" s="341" t="n"/>
-      <c r="AL19" s="341" t="n"/>
-      <c r="AM19" s="341" t="n"/>
-      <c r="AN19" s="464" t="n"/>
+      <c r="A19" s="559" t="n"/>
+      <c r="B19" s="408" t="n"/>
+      <c r="C19" s="408" t="n"/>
+      <c r="D19" s="408" t="n"/>
+      <c r="E19" s="408" t="n"/>
+      <c r="F19" s="408" t="n"/>
+      <c r="G19" s="408" t="n"/>
+      <c r="H19" s="408" t="n"/>
+      <c r="I19" s="408" t="n"/>
+      <c r="J19" s="408" t="n"/>
+      <c r="K19" s="408" t="n"/>
+      <c r="L19" s="408" t="n"/>
+      <c r="M19" s="408" t="n"/>
+      <c r="N19" s="408" t="n"/>
+      <c r="O19" s="408" t="n"/>
+      <c r="P19" s="408" t="n"/>
+      <c r="Q19" s="408" t="n"/>
+      <c r="R19" s="408" t="n"/>
+      <c r="S19" s="408" t="n"/>
+      <c r="T19" s="408" t="n"/>
+      <c r="U19" s="408" t="n"/>
+      <c r="V19" s="408" t="n"/>
+      <c r="W19" s="408" t="n"/>
+      <c r="X19" s="408" t="n"/>
+      <c r="Y19" s="408" t="n"/>
+      <c r="Z19" s="408" t="n"/>
+      <c r="AA19" s="408" t="n"/>
+      <c r="AB19" s="408" t="n"/>
+      <c r="AC19" s="408" t="n"/>
+      <c r="AD19" s="408" t="n"/>
+      <c r="AE19" s="408" t="n"/>
+      <c r="AF19" s="408" t="n"/>
+      <c r="AG19" s="408" t="n"/>
+      <c r="AH19" s="408" t="n"/>
+      <c r="AI19" s="408" t="n"/>
+      <c r="AJ19" s="408" t="n"/>
+      <c r="AK19" s="408" t="n"/>
+      <c r="AL19" s="408" t="n"/>
+      <c r="AM19" s="408" t="n"/>
+      <c r="AN19" s="538" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1" s="329">
-      <c r="A20" s="472" t="n"/>
-      <c r="B20" s="341" t="n"/>
-      <c r="C20" s="341" t="n"/>
-      <c r="D20" s="341" t="n"/>
-      <c r="E20" s="341" t="n"/>
-      <c r="F20" s="341" t="n"/>
-      <c r="G20" s="341" t="n"/>
-      <c r="H20" s="470" t="n"/>
-      <c r="I20" s="341" t="n"/>
-      <c r="J20" s="341" t="n"/>
-      <c r="K20" s="341" t="n"/>
-      <c r="L20" s="341" t="n"/>
-      <c r="M20" s="341" t="n"/>
-      <c r="N20" s="341" t="n"/>
-      <c r="O20" s="341" t="n"/>
-      <c r="P20" s="341" t="n"/>
-      <c r="Q20" s="341" t="n"/>
-      <c r="R20" s="341" t="n"/>
-      <c r="S20" s="341" t="n"/>
-      <c r="T20" s="341" t="n"/>
-      <c r="U20" s="470" t="n"/>
-      <c r="V20" s="341" t="n"/>
-      <c r="W20" s="341" t="n"/>
-      <c r="X20" s="341" t="n"/>
-      <c r="Y20" s="341" t="n"/>
-      <c r="Z20" s="341" t="n"/>
-      <c r="AA20" s="341" t="n"/>
-      <c r="AB20" s="470" t="n"/>
-      <c r="AC20" s="341" t="n"/>
-      <c r="AD20" s="341" t="n"/>
-      <c r="AE20" s="341" t="n"/>
-      <c r="AF20" s="341" t="n"/>
-      <c r="AG20" s="341" t="n"/>
-      <c r="AH20" s="341" t="n"/>
-      <c r="AI20" s="341" t="n"/>
-      <c r="AJ20" s="341" t="n"/>
-      <c r="AK20" s="341" t="n"/>
-      <c r="AL20" s="341" t="n"/>
-      <c r="AM20" s="341" t="n"/>
-      <c r="AN20" s="464" t="n"/>
+      <c r="A20" s="560" t="n"/>
+      <c r="B20" s="413" t="n"/>
+      <c r="C20" s="413" t="n"/>
+      <c r="D20" s="413" t="n"/>
+      <c r="E20" s="413" t="n"/>
+      <c r="F20" s="413" t="n"/>
+      <c r="G20" s="413" t="n"/>
+      <c r="H20" s="413" t="n"/>
+      <c r="I20" s="413" t="n"/>
+      <c r="J20" s="413" t="n"/>
+      <c r="K20" s="413" t="n"/>
+      <c r="L20" s="413" t="n"/>
+      <c r="M20" s="413" t="n"/>
+      <c r="N20" s="413" t="n"/>
+      <c r="O20" s="413" t="n"/>
+      <c r="P20" s="413" t="n"/>
+      <c r="Q20" s="413" t="n"/>
+      <c r="R20" s="413" t="n"/>
+      <c r="S20" s="413" t="n"/>
+      <c r="T20" s="413" t="n"/>
+      <c r="U20" s="413" t="n"/>
+      <c r="V20" s="413" t="n"/>
+      <c r="W20" s="413" t="n"/>
+      <c r="X20" s="413" t="n"/>
+      <c r="Y20" s="413" t="n"/>
+      <c r="Z20" s="413" t="n"/>
+      <c r="AA20" s="413" t="n"/>
+      <c r="AB20" s="413" t="n"/>
+      <c r="AC20" s="413" t="n"/>
+      <c r="AD20" s="413" t="n"/>
+      <c r="AE20" s="413" t="n"/>
+      <c r="AF20" s="413" t="n"/>
+      <c r="AG20" s="413" t="n"/>
+      <c r="AH20" s="413" t="n"/>
+      <c r="AI20" s="413" t="n"/>
+      <c r="AJ20" s="413" t="n"/>
+      <c r="AK20" s="413" t="n"/>
+      <c r="AL20" s="413" t="n"/>
+      <c r="AM20" s="413" t="n"/>
+      <c r="AN20" s="561" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1" s="329">
-      <c r="A21" s="461" t="inlineStr">
+      <c r="A21" s="558" t="inlineStr">
         <is>
           <t>OBSERVATION / CONTAINMENT / CERT CHECK</t>
         </is>
       </c>
-      <c r="B21" s="341" t="n"/>
-      <c r="C21" s="341" t="n"/>
-      <c r="D21" s="341" t="n"/>
-      <c r="E21" s="341" t="n"/>
-      <c r="F21" s="341" t="n"/>
-      <c r="G21" s="341" t="n"/>
-      <c r="H21" s="470" t="n"/>
-      <c r="I21" s="341" t="n"/>
-      <c r="J21" s="341" t="n"/>
-      <c r="K21" s="341" t="n"/>
-      <c r="L21" s="341" t="n"/>
-      <c r="M21" s="341" t="n"/>
-      <c r="N21" s="341" t="n"/>
-      <c r="O21" s="341" t="n"/>
-      <c r="P21" s="341" t="n"/>
-      <c r="Q21" s="341" t="n"/>
-      <c r="R21" s="341" t="n"/>
-      <c r="S21" s="341" t="n"/>
-      <c r="T21" s="341" t="n"/>
-      <c r="U21" s="470" t="n"/>
-      <c r="V21" s="341" t="n"/>
-      <c r="W21" s="341" t="n"/>
-      <c r="X21" s="341" t="n"/>
-      <c r="Y21" s="341" t="n"/>
-      <c r="Z21" s="341" t="n"/>
-      <c r="AA21" s="341" t="n"/>
-      <c r="AB21" s="470" t="n"/>
-      <c r="AC21" s="341" t="n"/>
-      <c r="AD21" s="341" t="n"/>
-      <c r="AE21" s="341" t="n"/>
-      <c r="AF21" s="341" t="n"/>
-      <c r="AG21" s="341" t="n"/>
-      <c r="AH21" s="341" t="n"/>
-      <c r="AI21" s="341" t="n"/>
-      <c r="AJ21" s="341" t="n"/>
-      <c r="AK21" s="341" t="n"/>
-      <c r="AL21" s="341" t="n"/>
-      <c r="AM21" s="341" t="n"/>
-      <c r="AN21" s="464" t="n"/>
+      <c r="B21" s="409" t="n"/>
+      <c r="C21" s="409" t="n"/>
+      <c r="D21" s="409" t="n"/>
+      <c r="E21" s="409" t="n"/>
+      <c r="F21" s="409" t="n"/>
+      <c r="G21" s="409" t="n"/>
+      <c r="H21" s="409" t="n"/>
+      <c r="I21" s="409" t="n"/>
+      <c r="J21" s="409" t="n"/>
+      <c r="K21" s="409" t="n"/>
+      <c r="L21" s="409" t="n"/>
+      <c r="M21" s="409" t="n"/>
+      <c r="N21" s="409" t="n"/>
+      <c r="O21" s="409" t="n"/>
+      <c r="P21" s="409" t="n"/>
+      <c r="Q21" s="409" t="n"/>
+      <c r="R21" s="409" t="n"/>
+      <c r="S21" s="409" t="n"/>
+      <c r="T21" s="409" t="n"/>
+      <c r="U21" s="409" t="n"/>
+      <c r="V21" s="409" t="n"/>
+      <c r="W21" s="409" t="n"/>
+      <c r="X21" s="409" t="n"/>
+      <c r="Y21" s="409" t="n"/>
+      <c r="Z21" s="409" t="n"/>
+      <c r="AA21" s="409" t="n"/>
+      <c r="AB21" s="409" t="n"/>
+      <c r="AC21" s="409" t="n"/>
+      <c r="AD21" s="409" t="n"/>
+      <c r="AE21" s="409" t="n"/>
+      <c r="AF21" s="409" t="n"/>
+      <c r="AG21" s="409" t="n"/>
+      <c r="AH21" s="409" t="n"/>
+      <c r="AI21" s="409" t="n"/>
+      <c r="AJ21" s="409" t="n"/>
+      <c r="AK21" s="409" t="n"/>
+      <c r="AL21" s="409" t="n"/>
+      <c r="AM21" s="409" t="n"/>
+      <c r="AN21" s="556" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1" s="329">
-      <c r="A22" s="471" t="n"/>
-      <c r="B22" s="341" t="n"/>
-      <c r="C22" s="341" t="n"/>
-      <c r="D22" s="341" t="n"/>
-      <c r="E22" s="341" t="n"/>
-      <c r="F22" s="341" t="n"/>
-      <c r="G22" s="341" t="n"/>
-      <c r="H22" s="470" t="n"/>
-      <c r="I22" s="341" t="n"/>
-      <c r="J22" s="341" t="n"/>
-      <c r="K22" s="341" t="n"/>
-      <c r="L22" s="341" t="n"/>
-      <c r="M22" s="341" t="n"/>
-      <c r="N22" s="341" t="n"/>
-      <c r="O22" s="341" t="n"/>
-      <c r="P22" s="341" t="n"/>
-      <c r="Q22" s="341" t="n"/>
-      <c r="R22" s="341" t="n"/>
-      <c r="S22" s="341" t="n"/>
-      <c r="T22" s="341" t="n"/>
-      <c r="U22" s="470" t="n"/>
-      <c r="V22" s="341" t="n"/>
-      <c r="W22" s="341" t="n"/>
-      <c r="X22" s="341" t="n"/>
-      <c r="Y22" s="341" t="n"/>
-      <c r="Z22" s="341" t="n"/>
-      <c r="AA22" s="341" t="n"/>
-      <c r="AB22" s="470" t="n"/>
-      <c r="AC22" s="341" t="n"/>
-      <c r="AD22" s="341" t="n"/>
-      <c r="AE22" s="341" t="n"/>
-      <c r="AF22" s="341" t="n"/>
-      <c r="AG22" s="341" t="n"/>
-      <c r="AH22" s="341" t="n"/>
-      <c r="AI22" s="341" t="n"/>
-      <c r="AJ22" s="341" t="n"/>
-      <c r="AK22" s="341" t="n"/>
-      <c r="AL22" s="341" t="n"/>
-      <c r="AM22" s="341" t="n"/>
-      <c r="AN22" s="464" t="n"/>
+      <c r="A22" s="559" t="n"/>
+      <c r="B22" s="408" t="n"/>
+      <c r="C22" s="408" t="n"/>
+      <c r="D22" s="408" t="n"/>
+      <c r="E22" s="408" t="n"/>
+      <c r="F22" s="408" t="n"/>
+      <c r="G22" s="408" t="n"/>
+      <c r="H22" s="408" t="n"/>
+      <c r="I22" s="408" t="n"/>
+      <c r="J22" s="408" t="n"/>
+      <c r="K22" s="408" t="n"/>
+      <c r="L22" s="408" t="n"/>
+      <c r="M22" s="408" t="n"/>
+      <c r="N22" s="408" t="n"/>
+      <c r="O22" s="408" t="n"/>
+      <c r="P22" s="408" t="n"/>
+      <c r="Q22" s="408" t="n"/>
+      <c r="R22" s="408" t="n"/>
+      <c r="S22" s="408" t="n"/>
+      <c r="T22" s="408" t="n"/>
+      <c r="U22" s="408" t="n"/>
+      <c r="V22" s="408" t="n"/>
+      <c r="W22" s="408" t="n"/>
+      <c r="X22" s="408" t="n"/>
+      <c r="Y22" s="408" t="n"/>
+      <c r="Z22" s="408" t="n"/>
+      <c r="AA22" s="408" t="n"/>
+      <c r="AB22" s="408" t="n"/>
+      <c r="AC22" s="408" t="n"/>
+      <c r="AD22" s="408" t="n"/>
+      <c r="AE22" s="408" t="n"/>
+      <c r="AF22" s="408" t="n"/>
+      <c r="AG22" s="408" t="n"/>
+      <c r="AH22" s="408" t="n"/>
+      <c r="AI22" s="408" t="n"/>
+      <c r="AJ22" s="408" t="n"/>
+      <c r="AK22" s="408" t="n"/>
+      <c r="AL22" s="408" t="n"/>
+      <c r="AM22" s="408" t="n"/>
+      <c r="AN22" s="538" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1" s="329">
-      <c r="A23" s="473" t="n"/>
-      <c r="B23" s="466" t="n"/>
-      <c r="C23" s="466" t="n"/>
-      <c r="D23" s="466" t="n"/>
-      <c r="E23" s="466" t="n"/>
-      <c r="F23" s="466" t="n"/>
-      <c r="G23" s="466" t="n"/>
-      <c r="H23" s="474" t="n"/>
-      <c r="I23" s="466" t="n"/>
-      <c r="J23" s="466" t="n"/>
-      <c r="K23" s="466" t="n"/>
-      <c r="L23" s="466" t="n"/>
-      <c r="M23" s="466" t="n"/>
-      <c r="N23" s="466" t="n"/>
-      <c r="O23" s="466" t="n"/>
-      <c r="P23" s="466" t="n"/>
-      <c r="Q23" s="466" t="n"/>
-      <c r="R23" s="466" t="n"/>
-      <c r="S23" s="466" t="n"/>
-      <c r="T23" s="466" t="n"/>
-      <c r="U23" s="474" t="n"/>
-      <c r="V23" s="466" t="n"/>
-      <c r="W23" s="466" t="n"/>
-      <c r="X23" s="466" t="n"/>
-      <c r="Y23" s="466" t="n"/>
-      <c r="Z23" s="466" t="n"/>
-      <c r="AA23" s="466" t="n"/>
-      <c r="AB23" s="474" t="n"/>
-      <c r="AC23" s="466" t="n"/>
-      <c r="AD23" s="466" t="n"/>
-      <c r="AE23" s="466" t="n"/>
-      <c r="AF23" s="466" t="n"/>
-      <c r="AG23" s="466" t="n"/>
-      <c r="AH23" s="466" t="n"/>
-      <c r="AI23" s="466" t="n"/>
-      <c r="AJ23" s="466" t="n"/>
-      <c r="AK23" s="466" t="n"/>
-      <c r="AL23" s="466" t="n"/>
-      <c r="AM23" s="466" t="n"/>
-      <c r="AN23" s="469" t="n"/>
+      <c r="A23" s="560" t="n"/>
+      <c r="B23" s="413" t="n"/>
+      <c r="C23" s="413" t="n"/>
+      <c r="D23" s="413" t="n"/>
+      <c r="E23" s="413" t="n"/>
+      <c r="F23" s="413" t="n"/>
+      <c r="G23" s="413" t="n"/>
+      <c r="H23" s="413" t="n"/>
+      <c r="I23" s="413" t="n"/>
+      <c r="J23" s="413" t="n"/>
+      <c r="K23" s="413" t="n"/>
+      <c r="L23" s="413" t="n"/>
+      <c r="M23" s="413" t="n"/>
+      <c r="N23" s="413" t="n"/>
+      <c r="O23" s="413" t="n"/>
+      <c r="P23" s="413" t="n"/>
+      <c r="Q23" s="413" t="n"/>
+      <c r="R23" s="413" t="n"/>
+      <c r="S23" s="413" t="n"/>
+      <c r="T23" s="413" t="n"/>
+      <c r="U23" s="413" t="n"/>
+      <c r="V23" s="413" t="n"/>
+      <c r="W23" s="413" t="n"/>
+      <c r="X23" s="413" t="n"/>
+      <c r="Y23" s="413" t="n"/>
+      <c r="Z23" s="413" t="n"/>
+      <c r="AA23" s="413" t="n"/>
+      <c r="AB23" s="413" t="n"/>
+      <c r="AC23" s="413" t="n"/>
+      <c r="AD23" s="413" t="n"/>
+      <c r="AE23" s="413" t="n"/>
+      <c r="AF23" s="413" t="n"/>
+      <c r="AG23" s="413" t="n"/>
+      <c r="AH23" s="413" t="n"/>
+      <c r="AI23" s="413" t="n"/>
+      <c r="AJ23" s="413" t="n"/>
+      <c r="AK23" s="413" t="n"/>
+      <c r="AL23" s="413" t="n"/>
+      <c r="AM23" s="413" t="n"/>
+      <c r="AN23" s="561" t="n"/>
     </row>
     <row r="24" ht="3" customHeight="1" s="329">
       <c r="A24" s="362" t="n"/>
@@ -6975,50 +7387,50 @@
       <c r="AN24" s="350" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1" s="329">
-      <c r="A25" s="453" t="inlineStr">
+      <c r="A25" s="549" t="inlineStr">
         <is>
           <t xml:space="preserve">  3. IMPACT / CONTAINMENT / ACTIONS</t>
         </is>
       </c>
-      <c r="B25" s="454" t="n"/>
-      <c r="C25" s="454" t="n"/>
-      <c r="D25" s="454" t="n"/>
-      <c r="E25" s="454" t="n"/>
-      <c r="F25" s="454" t="n"/>
-      <c r="G25" s="454" t="n"/>
-      <c r="H25" s="454" t="n"/>
-      <c r="I25" s="454" t="n"/>
-      <c r="J25" s="454" t="n"/>
-      <c r="K25" s="454" t="n"/>
-      <c r="L25" s="454" t="n"/>
-      <c r="M25" s="454" t="n"/>
-      <c r="N25" s="454" t="n"/>
-      <c r="O25" s="454" t="n"/>
-      <c r="P25" s="454" t="n"/>
-      <c r="Q25" s="454" t="n"/>
-      <c r="R25" s="454" t="n"/>
-      <c r="S25" s="454" t="n"/>
-      <c r="T25" s="454" t="n"/>
-      <c r="U25" s="454" t="n"/>
-      <c r="V25" s="454" t="n"/>
-      <c r="W25" s="454" t="n"/>
-      <c r="X25" s="454" t="n"/>
-      <c r="Y25" s="454" t="n"/>
-      <c r="Z25" s="454" t="n"/>
-      <c r="AA25" s="454" t="n"/>
-      <c r="AB25" s="454" t="n"/>
-      <c r="AC25" s="454" t="n"/>
-      <c r="AD25" s="454" t="n"/>
-      <c r="AE25" s="454" t="n"/>
-      <c r="AF25" s="454" t="n"/>
-      <c r="AG25" s="454" t="n"/>
-      <c r="AH25" s="454" t="n"/>
-      <c r="AI25" s="454" t="n"/>
-      <c r="AJ25" s="454" t="n"/>
-      <c r="AK25" s="454" t="n"/>
-      <c r="AL25" s="454" t="n"/>
-      <c r="AM25" s="454" t="n"/>
-      <c r="AN25" s="455" t="n"/>
+      <c r="B25" s="550" t="n"/>
+      <c r="C25" s="550" t="n"/>
+      <c r="D25" s="550" t="n"/>
+      <c r="E25" s="550" t="n"/>
+      <c r="F25" s="550" t="n"/>
+      <c r="G25" s="550" t="n"/>
+      <c r="H25" s="550" t="n"/>
+      <c r="I25" s="550" t="n"/>
+      <c r="J25" s="550" t="n"/>
+      <c r="K25" s="550" t="n"/>
+      <c r="L25" s="550" t="n"/>
+      <c r="M25" s="550" t="n"/>
+      <c r="N25" s="550" t="n"/>
+      <c r="O25" s="550" t="n"/>
+      <c r="P25" s="550" t="n"/>
+      <c r="Q25" s="550" t="n"/>
+      <c r="R25" s="550" t="n"/>
+      <c r="S25" s="550" t="n"/>
+      <c r="T25" s="550" t="n"/>
+      <c r="U25" s="550" t="n"/>
+      <c r="V25" s="550" t="n"/>
+      <c r="W25" s="550" t="n"/>
+      <c r="X25" s="550" t="n"/>
+      <c r="Y25" s="550" t="n"/>
+      <c r="Z25" s="550" t="n"/>
+      <c r="AA25" s="550" t="n"/>
+      <c r="AB25" s="550" t="n"/>
+      <c r="AC25" s="550" t="n"/>
+      <c r="AD25" s="550" t="n"/>
+      <c r="AE25" s="550" t="n"/>
+      <c r="AF25" s="550" t="n"/>
+      <c r="AG25" s="550" t="n"/>
+      <c r="AH25" s="550" t="n"/>
+      <c r="AI25" s="550" t="n"/>
+      <c r="AJ25" s="550" t="n"/>
+      <c r="AK25" s="550" t="n"/>
+      <c r="AL25" s="550" t="n"/>
+      <c r="AM25" s="550" t="n"/>
+      <c r="AN25" s="551" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1" s="329">
       <c r="A26" s="475" t="inlineStr">
@@ -7026,363 +7438,363 @@
           <t>#</t>
         </is>
       </c>
-      <c r="B26" s="476" t="n"/>
+      <c r="B26" s="550" t="n"/>
       <c r="C26" s="477" t="inlineStr">
         <is>
           <t>Cat.</t>
         </is>
       </c>
-      <c r="D26" s="476" t="n"/>
-      <c r="E26" s="476" t="n"/>
+      <c r="D26" s="550" t="n"/>
+      <c r="E26" s="550" t="n"/>
       <c r="F26" s="477" t="inlineStr">
         <is>
           <t>Finding / Check</t>
         </is>
       </c>
-      <c r="G26" s="476" t="n"/>
-      <c r="H26" s="476" t="n"/>
-      <c r="I26" s="476" t="n"/>
-      <c r="J26" s="476" t="n"/>
-      <c r="K26" s="476" t="n"/>
-      <c r="L26" s="476" t="n"/>
-      <c r="M26" s="476" t="n"/>
-      <c r="N26" s="476" t="n"/>
-      <c r="O26" s="476" t="n"/>
-      <c r="P26" s="476" t="n"/>
-      <c r="Q26" s="476" t="n"/>
-      <c r="R26" s="476" t="n"/>
-      <c r="S26" s="476" t="n"/>
+      <c r="G26" s="550" t="n"/>
+      <c r="H26" s="550" t="n"/>
+      <c r="I26" s="550" t="n"/>
+      <c r="J26" s="550" t="n"/>
+      <c r="K26" s="550" t="n"/>
+      <c r="L26" s="550" t="n"/>
+      <c r="M26" s="550" t="n"/>
+      <c r="N26" s="550" t="n"/>
+      <c r="O26" s="550" t="n"/>
+      <c r="P26" s="550" t="n"/>
+      <c r="Q26" s="550" t="n"/>
+      <c r="R26" s="550" t="n"/>
+      <c r="S26" s="550" t="n"/>
       <c r="T26" s="477" t="inlineStr">
         <is>
           <t>Evidence / Criteria</t>
         </is>
       </c>
-      <c r="U26" s="476" t="n"/>
-      <c r="V26" s="476" t="n"/>
-      <c r="W26" s="476" t="n"/>
-      <c r="X26" s="476" t="n"/>
-      <c r="Y26" s="476" t="n"/>
-      <c r="Z26" s="476" t="n"/>
-      <c r="AA26" s="476" t="n"/>
-      <c r="AB26" s="476" t="n"/>
-      <c r="AC26" s="476" t="n"/>
-      <c r="AD26" s="476" t="n"/>
-      <c r="AE26" s="476" t="n"/>
+      <c r="U26" s="550" t="n"/>
+      <c r="V26" s="550" t="n"/>
+      <c r="W26" s="550" t="n"/>
+      <c r="X26" s="550" t="n"/>
+      <c r="Y26" s="550" t="n"/>
+      <c r="Z26" s="550" t="n"/>
+      <c r="AA26" s="550" t="n"/>
+      <c r="AB26" s="550" t="n"/>
+      <c r="AC26" s="550" t="n"/>
+      <c r="AD26" s="550" t="n"/>
+      <c r="AE26" s="550" t="n"/>
       <c r="AF26" s="477" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="AG26" s="476" t="n"/>
-      <c r="AH26" s="476" t="n"/>
-      <c r="AI26" s="476" t="n"/>
+      <c r="AG26" s="550" t="n"/>
+      <c r="AH26" s="550" t="n"/>
+      <c r="AI26" s="550" t="n"/>
       <c r="AJ26" s="477" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AK26" s="476" t="n"/>
-      <c r="AL26" s="476" t="n"/>
-      <c r="AM26" s="477" t="inlineStr">
+      <c r="AK26" s="550" t="n"/>
+      <c r="AL26" s="550" t="n"/>
+      <c r="AM26" s="562" t="inlineStr">
         <is>
           <t>Ref.</t>
         </is>
       </c>
-      <c r="AN26" s="478" t="n"/>
+      <c r="AN26" s="551" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1" s="329">
       <c r="A27" s="479">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B27" s="457" t="n"/>
+      <c r="B27" s="552" t="n"/>
       <c r="C27" s="480" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D27" s="457" t="n"/>
-      <c r="E27" s="457" t="n"/>
+      <c r="D27" s="552" t="n"/>
+      <c r="E27" s="552" t="n"/>
       <c r="F27" s="458" t="n"/>
-      <c r="G27" s="457" t="n"/>
-      <c r="H27" s="457" t="n"/>
-      <c r="I27" s="457" t="n"/>
-      <c r="J27" s="457" t="n"/>
-      <c r="K27" s="457" t="n"/>
-      <c r="L27" s="457" t="n"/>
-      <c r="M27" s="457" t="n"/>
-      <c r="N27" s="457" t="n"/>
-      <c r="O27" s="457" t="n"/>
-      <c r="P27" s="457" t="n"/>
-      <c r="Q27" s="457" t="n"/>
-      <c r="R27" s="457" t="n"/>
-      <c r="S27" s="457" t="n"/>
+      <c r="G27" s="552" t="n"/>
+      <c r="H27" s="552" t="n"/>
+      <c r="I27" s="552" t="n"/>
+      <c r="J27" s="552" t="n"/>
+      <c r="K27" s="552" t="n"/>
+      <c r="L27" s="552" t="n"/>
+      <c r="M27" s="552" t="n"/>
+      <c r="N27" s="552" t="n"/>
+      <c r="O27" s="552" t="n"/>
+      <c r="P27" s="552" t="n"/>
+      <c r="Q27" s="552" t="n"/>
+      <c r="R27" s="552" t="n"/>
+      <c r="S27" s="552" t="n"/>
       <c r="T27" s="481" t="n"/>
-      <c r="U27" s="457" t="n"/>
-      <c r="V27" s="457" t="n"/>
-      <c r="W27" s="457" t="n"/>
-      <c r="X27" s="457" t="n"/>
-      <c r="Y27" s="457" t="n"/>
-      <c r="Z27" s="457" t="n"/>
-      <c r="AA27" s="457" t="n"/>
-      <c r="AB27" s="457" t="n"/>
-      <c r="AC27" s="457" t="n"/>
-      <c r="AD27" s="457" t="n"/>
-      <c r="AE27" s="457" t="n"/>
+      <c r="U27" s="552" t="n"/>
+      <c r="V27" s="552" t="n"/>
+      <c r="W27" s="552" t="n"/>
+      <c r="X27" s="552" t="n"/>
+      <c r="Y27" s="552" t="n"/>
+      <c r="Z27" s="552" t="n"/>
+      <c r="AA27" s="552" t="n"/>
+      <c r="AB27" s="552" t="n"/>
+      <c r="AC27" s="552" t="n"/>
+      <c r="AD27" s="552" t="n"/>
+      <c r="AE27" s="552" t="n"/>
       <c r="AF27" s="458" t="n"/>
-      <c r="AG27" s="457" t="n"/>
-      <c r="AH27" s="457" t="n"/>
-      <c r="AI27" s="457" t="n"/>
+      <c r="AG27" s="552" t="n"/>
+      <c r="AH27" s="552" t="n"/>
+      <c r="AI27" s="552" t="n"/>
       <c r="AJ27" s="458" t="n"/>
-      <c r="AK27" s="457" t="n"/>
-      <c r="AL27" s="457" t="n"/>
-      <c r="AM27" s="482" t="n"/>
-      <c r="AN27" s="460" t="n"/>
+      <c r="AK27" s="552" t="n"/>
+      <c r="AL27" s="552" t="n"/>
+      <c r="AM27" s="563" t="n"/>
+      <c r="AN27" s="554" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1" s="329">
       <c r="A28" s="483">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B28" s="341" t="n"/>
+      <c r="B28" s="409" t="n"/>
       <c r="C28" s="484" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D28" s="341" t="n"/>
-      <c r="E28" s="341" t="n"/>
+      <c r="D28" s="409" t="n"/>
+      <c r="E28" s="409" t="n"/>
       <c r="F28" s="462" t="n"/>
-      <c r="G28" s="341" t="n"/>
-      <c r="H28" s="341" t="n"/>
-      <c r="I28" s="341" t="n"/>
-      <c r="J28" s="341" t="n"/>
-      <c r="K28" s="341" t="n"/>
-      <c r="L28" s="341" t="n"/>
-      <c r="M28" s="341" t="n"/>
-      <c r="N28" s="341" t="n"/>
-      <c r="O28" s="341" t="n"/>
-      <c r="P28" s="341" t="n"/>
-      <c r="Q28" s="341" t="n"/>
-      <c r="R28" s="341" t="n"/>
-      <c r="S28" s="341" t="n"/>
+      <c r="G28" s="409" t="n"/>
+      <c r="H28" s="409" t="n"/>
+      <c r="I28" s="409" t="n"/>
+      <c r="J28" s="409" t="n"/>
+      <c r="K28" s="409" t="n"/>
+      <c r="L28" s="409" t="n"/>
+      <c r="M28" s="409" t="n"/>
+      <c r="N28" s="409" t="n"/>
+      <c r="O28" s="409" t="n"/>
+      <c r="P28" s="409" t="n"/>
+      <c r="Q28" s="409" t="n"/>
+      <c r="R28" s="409" t="n"/>
+      <c r="S28" s="409" t="n"/>
       <c r="T28" s="485" t="n"/>
-      <c r="U28" s="341" t="n"/>
-      <c r="V28" s="341" t="n"/>
-      <c r="W28" s="341" t="n"/>
-      <c r="X28" s="341" t="n"/>
-      <c r="Y28" s="341" t="n"/>
-      <c r="Z28" s="341" t="n"/>
-      <c r="AA28" s="341" t="n"/>
-      <c r="AB28" s="341" t="n"/>
-      <c r="AC28" s="341" t="n"/>
-      <c r="AD28" s="341" t="n"/>
-      <c r="AE28" s="341" t="n"/>
+      <c r="U28" s="409" t="n"/>
+      <c r="V28" s="409" t="n"/>
+      <c r="W28" s="409" t="n"/>
+      <c r="X28" s="409" t="n"/>
+      <c r="Y28" s="409" t="n"/>
+      <c r="Z28" s="409" t="n"/>
+      <c r="AA28" s="409" t="n"/>
+      <c r="AB28" s="409" t="n"/>
+      <c r="AC28" s="409" t="n"/>
+      <c r="AD28" s="409" t="n"/>
+      <c r="AE28" s="409" t="n"/>
       <c r="AF28" s="462" t="n"/>
-      <c r="AG28" s="341" t="n"/>
-      <c r="AH28" s="341" t="n"/>
-      <c r="AI28" s="341" t="n"/>
+      <c r="AG28" s="409" t="n"/>
+      <c r="AH28" s="409" t="n"/>
+      <c r="AI28" s="409" t="n"/>
       <c r="AJ28" s="462" t="n"/>
-      <c r="AK28" s="341" t="n"/>
-      <c r="AL28" s="341" t="n"/>
-      <c r="AM28" s="486" t="n"/>
-      <c r="AN28" s="464" t="n"/>
+      <c r="AK28" s="409" t="n"/>
+      <c r="AL28" s="409" t="n"/>
+      <c r="AM28" s="564" t="n"/>
+      <c r="AN28" s="556" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1" s="329">
       <c r="A29" s="483">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B29" s="341" t="n"/>
+      <c r="B29" s="409" t="n"/>
       <c r="C29" s="484" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D29" s="341" t="n"/>
-      <c r="E29" s="341" t="n"/>
+      <c r="D29" s="409" t="n"/>
+      <c r="E29" s="409" t="n"/>
       <c r="F29" s="462" t="n"/>
-      <c r="G29" s="341" t="n"/>
-      <c r="H29" s="341" t="n"/>
-      <c r="I29" s="341" t="n"/>
-      <c r="J29" s="341" t="n"/>
-      <c r="K29" s="341" t="n"/>
-      <c r="L29" s="341" t="n"/>
-      <c r="M29" s="341" t="n"/>
-      <c r="N29" s="341" t="n"/>
-      <c r="O29" s="341" t="n"/>
-      <c r="P29" s="341" t="n"/>
-      <c r="Q29" s="341" t="n"/>
-      <c r="R29" s="341" t="n"/>
-      <c r="S29" s="341" t="n"/>
+      <c r="G29" s="409" t="n"/>
+      <c r="H29" s="409" t="n"/>
+      <c r="I29" s="409" t="n"/>
+      <c r="J29" s="409" t="n"/>
+      <c r="K29" s="409" t="n"/>
+      <c r="L29" s="409" t="n"/>
+      <c r="M29" s="409" t="n"/>
+      <c r="N29" s="409" t="n"/>
+      <c r="O29" s="409" t="n"/>
+      <c r="P29" s="409" t="n"/>
+      <c r="Q29" s="409" t="n"/>
+      <c r="R29" s="409" t="n"/>
+      <c r="S29" s="409" t="n"/>
       <c r="T29" s="485" t="n"/>
-      <c r="U29" s="341" t="n"/>
-      <c r="V29" s="341" t="n"/>
-      <c r="W29" s="341" t="n"/>
-      <c r="X29" s="341" t="n"/>
-      <c r="Y29" s="341" t="n"/>
-      <c r="Z29" s="341" t="n"/>
-      <c r="AA29" s="341" t="n"/>
-      <c r="AB29" s="341" t="n"/>
-      <c r="AC29" s="341" t="n"/>
-      <c r="AD29" s="341" t="n"/>
-      <c r="AE29" s="341" t="n"/>
+      <c r="U29" s="409" t="n"/>
+      <c r="V29" s="409" t="n"/>
+      <c r="W29" s="409" t="n"/>
+      <c r="X29" s="409" t="n"/>
+      <c r="Y29" s="409" t="n"/>
+      <c r="Z29" s="409" t="n"/>
+      <c r="AA29" s="409" t="n"/>
+      <c r="AB29" s="409" t="n"/>
+      <c r="AC29" s="409" t="n"/>
+      <c r="AD29" s="409" t="n"/>
+      <c r="AE29" s="409" t="n"/>
       <c r="AF29" s="462" t="n"/>
-      <c r="AG29" s="341" t="n"/>
-      <c r="AH29" s="341" t="n"/>
-      <c r="AI29" s="341" t="n"/>
+      <c r="AG29" s="409" t="n"/>
+      <c r="AH29" s="409" t="n"/>
+      <c r="AI29" s="409" t="n"/>
       <c r="AJ29" s="462" t="n"/>
-      <c r="AK29" s="341" t="n"/>
-      <c r="AL29" s="341" t="n"/>
-      <c r="AM29" s="486" t="n"/>
-      <c r="AN29" s="464" t="n"/>
+      <c r="AK29" s="409" t="n"/>
+      <c r="AL29" s="409" t="n"/>
+      <c r="AM29" s="564" t="n"/>
+      <c r="AN29" s="556" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1" s="329">
       <c r="A30" s="483">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B30" s="341" t="n"/>
+      <c r="B30" s="409" t="n"/>
       <c r="C30" s="484" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D30" s="341" t="n"/>
-      <c r="E30" s="341" t="n"/>
+      <c r="D30" s="409" t="n"/>
+      <c r="E30" s="409" t="n"/>
       <c r="F30" s="462" t="n"/>
-      <c r="G30" s="341" t="n"/>
-      <c r="H30" s="341" t="n"/>
-      <c r="I30" s="341" t="n"/>
-      <c r="J30" s="341" t="n"/>
-      <c r="K30" s="341" t="n"/>
-      <c r="L30" s="341" t="n"/>
-      <c r="M30" s="341" t="n"/>
-      <c r="N30" s="341" t="n"/>
-      <c r="O30" s="341" t="n"/>
-      <c r="P30" s="341" t="n"/>
-      <c r="Q30" s="341" t="n"/>
-      <c r="R30" s="341" t="n"/>
-      <c r="S30" s="341" t="n"/>
+      <c r="G30" s="409" t="n"/>
+      <c r="H30" s="409" t="n"/>
+      <c r="I30" s="409" t="n"/>
+      <c r="J30" s="409" t="n"/>
+      <c r="K30" s="409" t="n"/>
+      <c r="L30" s="409" t="n"/>
+      <c r="M30" s="409" t="n"/>
+      <c r="N30" s="409" t="n"/>
+      <c r="O30" s="409" t="n"/>
+      <c r="P30" s="409" t="n"/>
+      <c r="Q30" s="409" t="n"/>
+      <c r="R30" s="409" t="n"/>
+      <c r="S30" s="409" t="n"/>
       <c r="T30" s="485" t="n"/>
-      <c r="U30" s="341" t="n"/>
-      <c r="V30" s="341" t="n"/>
-      <c r="W30" s="341" t="n"/>
-      <c r="X30" s="341" t="n"/>
-      <c r="Y30" s="341" t="n"/>
-      <c r="Z30" s="341" t="n"/>
-      <c r="AA30" s="341" t="n"/>
-      <c r="AB30" s="341" t="n"/>
-      <c r="AC30" s="341" t="n"/>
-      <c r="AD30" s="341" t="n"/>
-      <c r="AE30" s="341" t="n"/>
+      <c r="U30" s="409" t="n"/>
+      <c r="V30" s="409" t="n"/>
+      <c r="W30" s="409" t="n"/>
+      <c r="X30" s="409" t="n"/>
+      <c r="Y30" s="409" t="n"/>
+      <c r="Z30" s="409" t="n"/>
+      <c r="AA30" s="409" t="n"/>
+      <c r="AB30" s="409" t="n"/>
+      <c r="AC30" s="409" t="n"/>
+      <c r="AD30" s="409" t="n"/>
+      <c r="AE30" s="409" t="n"/>
       <c r="AF30" s="462" t="n"/>
-      <c r="AG30" s="341" t="n"/>
-      <c r="AH30" s="341" t="n"/>
-      <c r="AI30" s="341" t="n"/>
+      <c r="AG30" s="409" t="n"/>
+      <c r="AH30" s="409" t="n"/>
+      <c r="AI30" s="409" t="n"/>
       <c r="AJ30" s="462" t="n"/>
-      <c r="AK30" s="341" t="n"/>
-      <c r="AL30" s="341" t="n"/>
-      <c r="AM30" s="486" t="n"/>
-      <c r="AN30" s="464" t="n"/>
+      <c r="AK30" s="409" t="n"/>
+      <c r="AL30" s="409" t="n"/>
+      <c r="AM30" s="564" t="n"/>
+      <c r="AN30" s="556" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1" s="329">
       <c r="A31" s="483">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B31" s="341" t="n"/>
+      <c r="B31" s="409" t="n"/>
       <c r="C31" s="484" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D31" s="341" t="n"/>
-      <c r="E31" s="341" t="n"/>
+      <c r="D31" s="409" t="n"/>
+      <c r="E31" s="409" t="n"/>
       <c r="F31" s="462" t="n"/>
-      <c r="G31" s="341" t="n"/>
-      <c r="H31" s="341" t="n"/>
-      <c r="I31" s="341" t="n"/>
-      <c r="J31" s="341" t="n"/>
-      <c r="K31" s="341" t="n"/>
-      <c r="L31" s="341" t="n"/>
-      <c r="M31" s="341" t="n"/>
-      <c r="N31" s="341" t="n"/>
-      <c r="O31" s="341" t="n"/>
-      <c r="P31" s="341" t="n"/>
-      <c r="Q31" s="341" t="n"/>
-      <c r="R31" s="341" t="n"/>
-      <c r="S31" s="341" t="n"/>
+      <c r="G31" s="409" t="n"/>
+      <c r="H31" s="409" t="n"/>
+      <c r="I31" s="409" t="n"/>
+      <c r="J31" s="409" t="n"/>
+      <c r="K31" s="409" t="n"/>
+      <c r="L31" s="409" t="n"/>
+      <c r="M31" s="409" t="n"/>
+      <c r="N31" s="409" t="n"/>
+      <c r="O31" s="409" t="n"/>
+      <c r="P31" s="409" t="n"/>
+      <c r="Q31" s="409" t="n"/>
+      <c r="R31" s="409" t="n"/>
+      <c r="S31" s="409" t="n"/>
       <c r="T31" s="485" t="n"/>
-      <c r="U31" s="341" t="n"/>
-      <c r="V31" s="341" t="n"/>
-      <c r="W31" s="341" t="n"/>
-      <c r="X31" s="341" t="n"/>
-      <c r="Y31" s="341" t="n"/>
-      <c r="Z31" s="341" t="n"/>
-      <c r="AA31" s="341" t="n"/>
-      <c r="AB31" s="341" t="n"/>
-      <c r="AC31" s="341" t="n"/>
-      <c r="AD31" s="341" t="n"/>
-      <c r="AE31" s="341" t="n"/>
+      <c r="U31" s="409" t="n"/>
+      <c r="V31" s="409" t="n"/>
+      <c r="W31" s="409" t="n"/>
+      <c r="X31" s="409" t="n"/>
+      <c r="Y31" s="409" t="n"/>
+      <c r="Z31" s="409" t="n"/>
+      <c r="AA31" s="409" t="n"/>
+      <c r="AB31" s="409" t="n"/>
+      <c r="AC31" s="409" t="n"/>
+      <c r="AD31" s="409" t="n"/>
+      <c r="AE31" s="409" t="n"/>
       <c r="AF31" s="462" t="n"/>
-      <c r="AG31" s="341" t="n"/>
-      <c r="AH31" s="341" t="n"/>
-      <c r="AI31" s="341" t="n"/>
+      <c r="AG31" s="409" t="n"/>
+      <c r="AH31" s="409" t="n"/>
+      <c r="AI31" s="409" t="n"/>
       <c r="AJ31" s="462" t="n"/>
-      <c r="AK31" s="341" t="n"/>
-      <c r="AL31" s="341" t="n"/>
-      <c r="AM31" s="486" t="n"/>
-      <c r="AN31" s="464" t="n"/>
+      <c r="AK31" s="409" t="n"/>
+      <c r="AL31" s="409" t="n"/>
+      <c r="AM31" s="564" t="n"/>
+      <c r="AN31" s="556" t="n"/>
     </row>
     <row r="32" ht="20" customHeight="1" s="329">
       <c r="A32" s="487">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B32" s="466" t="n"/>
+      <c r="B32" s="545" t="n"/>
       <c r="C32" s="488" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D32" s="466" t="n"/>
-      <c r="E32" s="466" t="n"/>
+      <c r="D32" s="545" t="n"/>
+      <c r="E32" s="545" t="n"/>
       <c r="F32" s="467" t="n"/>
-      <c r="G32" s="466" t="n"/>
-      <c r="H32" s="466" t="n"/>
-      <c r="I32" s="466" t="n"/>
-      <c r="J32" s="466" t="n"/>
-      <c r="K32" s="466" t="n"/>
-      <c r="L32" s="466" t="n"/>
-      <c r="M32" s="466" t="n"/>
-      <c r="N32" s="466" t="n"/>
-      <c r="O32" s="466" t="n"/>
-      <c r="P32" s="466" t="n"/>
-      <c r="Q32" s="466" t="n"/>
-      <c r="R32" s="466" t="n"/>
-      <c r="S32" s="466" t="n"/>
+      <c r="G32" s="545" t="n"/>
+      <c r="H32" s="545" t="n"/>
+      <c r="I32" s="545" t="n"/>
+      <c r="J32" s="545" t="n"/>
+      <c r="K32" s="545" t="n"/>
+      <c r="L32" s="545" t="n"/>
+      <c r="M32" s="545" t="n"/>
+      <c r="N32" s="545" t="n"/>
+      <c r="O32" s="545" t="n"/>
+      <c r="P32" s="545" t="n"/>
+      <c r="Q32" s="545" t="n"/>
+      <c r="R32" s="545" t="n"/>
+      <c r="S32" s="545" t="n"/>
       <c r="T32" s="489" t="n"/>
-      <c r="U32" s="466" t="n"/>
-      <c r="V32" s="466" t="n"/>
-      <c r="W32" s="466" t="n"/>
-      <c r="X32" s="466" t="n"/>
-      <c r="Y32" s="466" t="n"/>
-      <c r="Z32" s="466" t="n"/>
-      <c r="AA32" s="466" t="n"/>
-      <c r="AB32" s="466" t="n"/>
-      <c r="AC32" s="466" t="n"/>
-      <c r="AD32" s="466" t="n"/>
-      <c r="AE32" s="466" t="n"/>
+      <c r="U32" s="545" t="n"/>
+      <c r="V32" s="545" t="n"/>
+      <c r="W32" s="545" t="n"/>
+      <c r="X32" s="545" t="n"/>
+      <c r="Y32" s="545" t="n"/>
+      <c r="Z32" s="545" t="n"/>
+      <c r="AA32" s="545" t="n"/>
+      <c r="AB32" s="545" t="n"/>
+      <c r="AC32" s="545" t="n"/>
+      <c r="AD32" s="545" t="n"/>
+      <c r="AE32" s="545" t="n"/>
       <c r="AF32" s="467" t="n"/>
-      <c r="AG32" s="466" t="n"/>
-      <c r="AH32" s="466" t="n"/>
-      <c r="AI32" s="466" t="n"/>
+      <c r="AG32" s="545" t="n"/>
+      <c r="AH32" s="545" t="n"/>
+      <c r="AI32" s="545" t="n"/>
       <c r="AJ32" s="467" t="n"/>
-      <c r="AK32" s="466" t="n"/>
-      <c r="AL32" s="466" t="n"/>
-      <c r="AM32" s="490" t="n"/>
-      <c r="AN32" s="469" t="n"/>
+      <c r="AK32" s="545" t="n"/>
+      <c r="AL32" s="545" t="n"/>
+      <c r="AM32" s="565" t="n"/>
+      <c r="AN32" s="548" t="n"/>
     </row>
     <row r="33" ht="3" customHeight="1" s="329">
       <c r="A33" s="357" t="n"/>
@@ -7427,50 +7839,50 @@
       <c r="AN33" s="350" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1" s="329">
-      <c r="A34" s="453" t="inlineStr">
+      <c r="A34" s="549" t="inlineStr">
         <is>
           <t xml:space="preserve">  4. FINAL DECISION / CLOSURE</t>
         </is>
       </c>
-      <c r="B34" s="454" t="n"/>
-      <c r="C34" s="454" t="n"/>
-      <c r="D34" s="454" t="n"/>
-      <c r="E34" s="454" t="n"/>
-      <c r="F34" s="454" t="n"/>
-      <c r="G34" s="454" t="n"/>
-      <c r="H34" s="454" t="n"/>
-      <c r="I34" s="454" t="n"/>
-      <c r="J34" s="454" t="n"/>
-      <c r="K34" s="454" t="n"/>
-      <c r="L34" s="454" t="n"/>
-      <c r="M34" s="454" t="n"/>
-      <c r="N34" s="454" t="n"/>
-      <c r="O34" s="454" t="n"/>
-      <c r="P34" s="454" t="n"/>
-      <c r="Q34" s="454" t="n"/>
-      <c r="R34" s="454" t="n"/>
-      <c r="S34" s="454" t="n"/>
-      <c r="T34" s="454" t="n"/>
-      <c r="U34" s="454" t="n"/>
-      <c r="V34" s="454" t="n"/>
-      <c r="W34" s="454" t="n"/>
-      <c r="X34" s="454" t="n"/>
-      <c r="Y34" s="454" t="n"/>
-      <c r="Z34" s="454" t="n"/>
-      <c r="AA34" s="454" t="n"/>
-      <c r="AB34" s="454" t="n"/>
-      <c r="AC34" s="454" t="n"/>
-      <c r="AD34" s="454" t="n"/>
-      <c r="AE34" s="454" t="n"/>
-      <c r="AF34" s="454" t="n"/>
-      <c r="AG34" s="454" t="n"/>
-      <c r="AH34" s="454" t="n"/>
-      <c r="AI34" s="454" t="n"/>
-      <c r="AJ34" s="454" t="n"/>
-      <c r="AK34" s="454" t="n"/>
-      <c r="AL34" s="454" t="n"/>
-      <c r="AM34" s="454" t="n"/>
-      <c r="AN34" s="455" t="n"/>
+      <c r="B34" s="550" t="n"/>
+      <c r="C34" s="550" t="n"/>
+      <c r="D34" s="550" t="n"/>
+      <c r="E34" s="550" t="n"/>
+      <c r="F34" s="550" t="n"/>
+      <c r="G34" s="550" t="n"/>
+      <c r="H34" s="550" t="n"/>
+      <c r="I34" s="550" t="n"/>
+      <c r="J34" s="550" t="n"/>
+      <c r="K34" s="550" t="n"/>
+      <c r="L34" s="550" t="n"/>
+      <c r="M34" s="550" t="n"/>
+      <c r="N34" s="550" t="n"/>
+      <c r="O34" s="550" t="n"/>
+      <c r="P34" s="550" t="n"/>
+      <c r="Q34" s="550" t="n"/>
+      <c r="R34" s="550" t="n"/>
+      <c r="S34" s="550" t="n"/>
+      <c r="T34" s="550" t="n"/>
+      <c r="U34" s="550" t="n"/>
+      <c r="V34" s="550" t="n"/>
+      <c r="W34" s="550" t="n"/>
+      <c r="X34" s="550" t="n"/>
+      <c r="Y34" s="550" t="n"/>
+      <c r="Z34" s="550" t="n"/>
+      <c r="AA34" s="550" t="n"/>
+      <c r="AB34" s="550" t="n"/>
+      <c r="AC34" s="550" t="n"/>
+      <c r="AD34" s="550" t="n"/>
+      <c r="AE34" s="550" t="n"/>
+      <c r="AF34" s="550" t="n"/>
+      <c r="AG34" s="550" t="n"/>
+      <c r="AH34" s="550" t="n"/>
+      <c r="AI34" s="550" t="n"/>
+      <c r="AJ34" s="550" t="n"/>
+      <c r="AK34" s="550" t="n"/>
+      <c r="AL34" s="550" t="n"/>
+      <c r="AM34" s="550" t="n"/>
+      <c r="AN34" s="551" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1" s="329">
       <c r="A35" s="456" t="inlineStr">
@@ -7478,49 +7890,49 @@
           <t>Final Decision</t>
         </is>
       </c>
-      <c r="B35" s="457" t="n"/>
-      <c r="C35" s="457" t="n"/>
-      <c r="D35" s="457" t="n"/>
-      <c r="E35" s="457" t="n"/>
-      <c r="F35" s="457" t="n"/>
-      <c r="G35" s="457" t="n"/>
+      <c r="B35" s="552" t="n"/>
+      <c r="C35" s="552" t="n"/>
+      <c r="D35" s="552" t="n"/>
+      <c r="E35" s="552" t="n"/>
+      <c r="F35" s="552" t="n"/>
+      <c r="G35" s="552" t="n"/>
       <c r="H35" s="458" t="n"/>
-      <c r="I35" s="457" t="n"/>
-      <c r="J35" s="457" t="n"/>
-      <c r="K35" s="457" t="n"/>
-      <c r="L35" s="457" t="n"/>
-      <c r="M35" s="457" t="n"/>
-      <c r="N35" s="457" t="n"/>
-      <c r="O35" s="457" t="n"/>
-      <c r="P35" s="457" t="n"/>
-      <c r="Q35" s="457" t="n"/>
-      <c r="R35" s="457" t="n"/>
-      <c r="S35" s="457" t="n"/>
-      <c r="T35" s="457" t="n"/>
+      <c r="I35" s="552" t="n"/>
+      <c r="J35" s="552" t="n"/>
+      <c r="K35" s="552" t="n"/>
+      <c r="L35" s="552" t="n"/>
+      <c r="M35" s="552" t="n"/>
+      <c r="N35" s="552" t="n"/>
+      <c r="O35" s="552" t="n"/>
+      <c r="P35" s="552" t="n"/>
+      <c r="Q35" s="552" t="n"/>
+      <c r="R35" s="552" t="n"/>
+      <c r="S35" s="552" t="n"/>
+      <c r="T35" s="552" t="n"/>
       <c r="U35" s="459" t="inlineStr">
         <is>
           <t>Reviewed by</t>
         </is>
       </c>
-      <c r="V35" s="457" t="n"/>
-      <c r="W35" s="457" t="n"/>
-      <c r="X35" s="457" t="n"/>
-      <c r="Y35" s="457" t="n"/>
-      <c r="Z35" s="457" t="n"/>
-      <c r="AA35" s="457" t="n"/>
-      <c r="AB35" s="458" t="n"/>
-      <c r="AC35" s="457" t="n"/>
-      <c r="AD35" s="457" t="n"/>
-      <c r="AE35" s="457" t="n"/>
-      <c r="AF35" s="457" t="n"/>
-      <c r="AG35" s="457" t="n"/>
-      <c r="AH35" s="457" t="n"/>
-      <c r="AI35" s="457" t="n"/>
-      <c r="AJ35" s="457" t="n"/>
-      <c r="AK35" s="457" t="n"/>
-      <c r="AL35" s="457" t="n"/>
-      <c r="AM35" s="457" t="n"/>
-      <c r="AN35" s="460" t="n"/>
+      <c r="V35" s="552" t="n"/>
+      <c r="W35" s="552" t="n"/>
+      <c r="X35" s="552" t="n"/>
+      <c r="Y35" s="552" t="n"/>
+      <c r="Z35" s="552" t="n"/>
+      <c r="AA35" s="552" t="n"/>
+      <c r="AB35" s="553" t="n"/>
+      <c r="AC35" s="552" t="n"/>
+      <c r="AD35" s="552" t="n"/>
+      <c r="AE35" s="552" t="n"/>
+      <c r="AF35" s="552" t="n"/>
+      <c r="AG35" s="552" t="n"/>
+      <c r="AH35" s="552" t="n"/>
+      <c r="AI35" s="552" t="n"/>
+      <c r="AJ35" s="552" t="n"/>
+      <c r="AK35" s="552" t="n"/>
+      <c r="AL35" s="552" t="n"/>
+      <c r="AM35" s="552" t="n"/>
+      <c r="AN35" s="554" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1" s="329">
       <c r="A36" s="465" t="inlineStr">
@@ -7528,49 +7940,49 @@
           <t>Containment Required (YES/NO)</t>
         </is>
       </c>
-      <c r="B36" s="466" t="n"/>
-      <c r="C36" s="466" t="n"/>
-      <c r="D36" s="466" t="n"/>
-      <c r="E36" s="466" t="n"/>
-      <c r="F36" s="466" t="n"/>
-      <c r="G36" s="466" t="n"/>
+      <c r="B36" s="545" t="n"/>
+      <c r="C36" s="545" t="n"/>
+      <c r="D36" s="545" t="n"/>
+      <c r="E36" s="545" t="n"/>
+      <c r="F36" s="545" t="n"/>
+      <c r="G36" s="545" t="n"/>
       <c r="H36" s="467" t="n"/>
-      <c r="I36" s="466" t="n"/>
-      <c r="J36" s="466" t="n"/>
-      <c r="K36" s="466" t="n"/>
-      <c r="L36" s="466" t="n"/>
-      <c r="M36" s="466" t="n"/>
-      <c r="N36" s="466" t="n"/>
-      <c r="O36" s="466" t="n"/>
-      <c r="P36" s="466" t="n"/>
-      <c r="Q36" s="466" t="n"/>
-      <c r="R36" s="466" t="n"/>
-      <c r="S36" s="466" t="n"/>
-      <c r="T36" s="466" t="n"/>
+      <c r="I36" s="545" t="n"/>
+      <c r="J36" s="545" t="n"/>
+      <c r="K36" s="545" t="n"/>
+      <c r="L36" s="545" t="n"/>
+      <c r="M36" s="545" t="n"/>
+      <c r="N36" s="545" t="n"/>
+      <c r="O36" s="545" t="n"/>
+      <c r="P36" s="545" t="n"/>
+      <c r="Q36" s="545" t="n"/>
+      <c r="R36" s="545" t="n"/>
+      <c r="S36" s="545" t="n"/>
+      <c r="T36" s="545" t="n"/>
       <c r="U36" s="468" t="inlineStr">
         <is>
           <t>Target Closeout</t>
         </is>
       </c>
-      <c r="V36" s="466" t="n"/>
-      <c r="W36" s="466" t="n"/>
-      <c r="X36" s="466" t="n"/>
-      <c r="Y36" s="466" t="n"/>
-      <c r="Z36" s="466" t="n"/>
-      <c r="AA36" s="466" t="n"/>
-      <c r="AB36" s="467" t="n"/>
-      <c r="AC36" s="466" t="n"/>
-      <c r="AD36" s="466" t="n"/>
-      <c r="AE36" s="466" t="n"/>
-      <c r="AF36" s="466" t="n"/>
-      <c r="AG36" s="466" t="n"/>
-      <c r="AH36" s="466" t="n"/>
-      <c r="AI36" s="466" t="n"/>
-      <c r="AJ36" s="466" t="n"/>
-      <c r="AK36" s="466" t="n"/>
-      <c r="AL36" s="466" t="n"/>
-      <c r="AM36" s="466" t="n"/>
-      <c r="AN36" s="469" t="n"/>
+      <c r="V36" s="545" t="n"/>
+      <c r="W36" s="545" t="n"/>
+      <c r="X36" s="545" t="n"/>
+      <c r="Y36" s="545" t="n"/>
+      <c r="Z36" s="545" t="n"/>
+      <c r="AA36" s="545" t="n"/>
+      <c r="AB36" s="557" t="n"/>
+      <c r="AC36" s="545" t="n"/>
+      <c r="AD36" s="545" t="n"/>
+      <c r="AE36" s="545" t="n"/>
+      <c r="AF36" s="545" t="n"/>
+      <c r="AG36" s="545" t="n"/>
+      <c r="AH36" s="545" t="n"/>
+      <c r="AI36" s="545" t="n"/>
+      <c r="AJ36" s="545" t="n"/>
+      <c r="AK36" s="545" t="n"/>
+      <c r="AL36" s="545" t="n"/>
+      <c r="AM36" s="545" t="n"/>
+      <c r="AN36" s="548" t="n"/>
     </row>
     <row r="37" ht="3" customHeight="1" s="329">
       <c r="A37" s="362" t="n"/>
@@ -7615,50 +8027,50 @@
       <c r="AN37" s="350" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1" s="329">
-      <c r="A38" s="453" t="inlineStr">
+      <c r="A38" s="549" t="inlineStr">
         <is>
           <t xml:space="preserve">  5. APPROVAL / SIGN-OFF</t>
         </is>
       </c>
-      <c r="B38" s="454" t="n"/>
-      <c r="C38" s="454" t="n"/>
-      <c r="D38" s="454" t="n"/>
-      <c r="E38" s="454" t="n"/>
-      <c r="F38" s="454" t="n"/>
-      <c r="G38" s="454" t="n"/>
-      <c r="H38" s="454" t="n"/>
-      <c r="I38" s="454" t="n"/>
-      <c r="J38" s="454" t="n"/>
-      <c r="K38" s="454" t="n"/>
-      <c r="L38" s="454" t="n"/>
-      <c r="M38" s="454" t="n"/>
-      <c r="N38" s="454" t="n"/>
-      <c r="O38" s="454" t="n"/>
-      <c r="P38" s="454" t="n"/>
-      <c r="Q38" s="454" t="n"/>
-      <c r="R38" s="454" t="n"/>
-      <c r="S38" s="454" t="n"/>
-      <c r="T38" s="454" t="n"/>
-      <c r="U38" s="454" t="n"/>
-      <c r="V38" s="454" t="n"/>
-      <c r="W38" s="454" t="n"/>
-      <c r="X38" s="454" t="n"/>
-      <c r="Y38" s="454" t="n"/>
-      <c r="Z38" s="454" t="n"/>
-      <c r="AA38" s="454" t="n"/>
-      <c r="AB38" s="454" t="n"/>
-      <c r="AC38" s="454" t="n"/>
-      <c r="AD38" s="454" t="n"/>
-      <c r="AE38" s="454" t="n"/>
-      <c r="AF38" s="454" t="n"/>
-      <c r="AG38" s="454" t="n"/>
-      <c r="AH38" s="454" t="n"/>
-      <c r="AI38" s="454" t="n"/>
-      <c r="AJ38" s="454" t="n"/>
-      <c r="AK38" s="454" t="n"/>
-      <c r="AL38" s="454" t="n"/>
-      <c r="AM38" s="454" t="n"/>
-      <c r="AN38" s="455" t="n"/>
+      <c r="B38" s="550" t="n"/>
+      <c r="C38" s="550" t="n"/>
+      <c r="D38" s="550" t="n"/>
+      <c r="E38" s="550" t="n"/>
+      <c r="F38" s="550" t="n"/>
+      <c r="G38" s="550" t="n"/>
+      <c r="H38" s="550" t="n"/>
+      <c r="I38" s="550" t="n"/>
+      <c r="J38" s="550" t="n"/>
+      <c r="K38" s="550" t="n"/>
+      <c r="L38" s="550" t="n"/>
+      <c r="M38" s="550" t="n"/>
+      <c r="N38" s="550" t="n"/>
+      <c r="O38" s="550" t="n"/>
+      <c r="P38" s="550" t="n"/>
+      <c r="Q38" s="550" t="n"/>
+      <c r="R38" s="550" t="n"/>
+      <c r="S38" s="550" t="n"/>
+      <c r="T38" s="550" t="n"/>
+      <c r="U38" s="550" t="n"/>
+      <c r="V38" s="550" t="n"/>
+      <c r="W38" s="550" t="n"/>
+      <c r="X38" s="550" t="n"/>
+      <c r="Y38" s="550" t="n"/>
+      <c r="Z38" s="550" t="n"/>
+      <c r="AA38" s="550" t="n"/>
+      <c r="AB38" s="550" t="n"/>
+      <c r="AC38" s="550" t="n"/>
+      <c r="AD38" s="550" t="n"/>
+      <c r="AE38" s="550" t="n"/>
+      <c r="AF38" s="550" t="n"/>
+      <c r="AG38" s="550" t="n"/>
+      <c r="AH38" s="550" t="n"/>
+      <c r="AI38" s="550" t="n"/>
+      <c r="AJ38" s="550" t="n"/>
+      <c r="AK38" s="550" t="n"/>
+      <c r="AL38" s="550" t="n"/>
+      <c r="AM38" s="550" t="n"/>
+      <c r="AN38" s="551" t="n"/>
     </row>
     <row r="39" ht="26" customHeight="1" s="329">
       <c r="A39" s="479" t="inlineStr">
@@ -7666,53 +8078,53 @@
           <t>Prepared by</t>
         </is>
       </c>
-      <c r="B39" s="457" t="n"/>
-      <c r="C39" s="457" t="n"/>
-      <c r="D39" s="457" t="n"/>
-      <c r="E39" s="457" t="n"/>
-      <c r="F39" s="457" t="n"/>
-      <c r="G39" s="457" t="n"/>
-      <c r="H39" s="457" t="n"/>
-      <c r="I39" s="457" t="n"/>
-      <c r="J39" s="457" t="n"/>
-      <c r="K39" s="457" t="n"/>
-      <c r="L39" s="457" t="n"/>
-      <c r="M39" s="457" t="n"/>
+      <c r="B39" s="552" t="n"/>
+      <c r="C39" s="552" t="n"/>
+      <c r="D39" s="552" t="n"/>
+      <c r="E39" s="552" t="n"/>
+      <c r="F39" s="552" t="n"/>
+      <c r="G39" s="552" t="n"/>
+      <c r="H39" s="552" t="n"/>
+      <c r="I39" s="552" t="n"/>
+      <c r="J39" s="552" t="n"/>
+      <c r="K39" s="552" t="n"/>
+      <c r="L39" s="552" t="n"/>
+      <c r="M39" s="552" t="n"/>
       <c r="N39" s="491" t="inlineStr">
         <is>
           <t>Reviewed by</t>
         </is>
       </c>
-      <c r="O39" s="457" t="n"/>
-      <c r="P39" s="457" t="n"/>
-      <c r="Q39" s="457" t="n"/>
-      <c r="R39" s="457" t="n"/>
-      <c r="S39" s="457" t="n"/>
-      <c r="T39" s="457" t="n"/>
-      <c r="U39" s="457" t="n"/>
-      <c r="V39" s="457" t="n"/>
-      <c r="W39" s="457" t="n"/>
-      <c r="X39" s="457" t="n"/>
-      <c r="Y39" s="457" t="n"/>
-      <c r="Z39" s="457" t="n"/>
-      <c r="AA39" s="491" t="inlineStr">
+      <c r="O39" s="552" t="n"/>
+      <c r="P39" s="552" t="n"/>
+      <c r="Q39" s="552" t="n"/>
+      <c r="R39" s="552" t="n"/>
+      <c r="S39" s="552" t="n"/>
+      <c r="T39" s="552" t="n"/>
+      <c r="U39" s="552" t="n"/>
+      <c r="V39" s="552" t="n"/>
+      <c r="W39" s="552" t="n"/>
+      <c r="X39" s="552" t="n"/>
+      <c r="Y39" s="552" t="n"/>
+      <c r="Z39" s="552" t="n"/>
+      <c r="AA39" s="566" t="inlineStr">
         <is>
           <t>Approved by</t>
         </is>
       </c>
-      <c r="AB39" s="457" t="n"/>
-      <c r="AC39" s="457" t="n"/>
-      <c r="AD39" s="457" t="n"/>
-      <c r="AE39" s="457" t="n"/>
-      <c r="AF39" s="457" t="n"/>
-      <c r="AG39" s="457" t="n"/>
-      <c r="AH39" s="457" t="n"/>
-      <c r="AI39" s="457" t="n"/>
-      <c r="AJ39" s="457" t="n"/>
-      <c r="AK39" s="457" t="n"/>
-      <c r="AL39" s="457" t="n"/>
-      <c r="AM39" s="457" t="n"/>
-      <c r="AN39" s="460" t="n"/>
+      <c r="AB39" s="552" t="n"/>
+      <c r="AC39" s="552" t="n"/>
+      <c r="AD39" s="552" t="n"/>
+      <c r="AE39" s="552" t="n"/>
+      <c r="AF39" s="552" t="n"/>
+      <c r="AG39" s="552" t="n"/>
+      <c r="AH39" s="552" t="n"/>
+      <c r="AI39" s="552" t="n"/>
+      <c r="AJ39" s="552" t="n"/>
+      <c r="AK39" s="552" t="n"/>
+      <c r="AL39" s="552" t="n"/>
+      <c r="AM39" s="552" t="n"/>
+      <c r="AN39" s="554" t="n"/>
     </row>
     <row r="40" ht="26" customHeight="1" s="329">
       <c r="A40" s="492" t="inlineStr">
@@ -7720,137 +8132,101 @@
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="B40" s="341" t="n"/>
-      <c r="C40" s="341" t="n"/>
-      <c r="D40" s="341" t="n"/>
-      <c r="E40" s="341" t="n"/>
-      <c r="F40" s="341" t="n"/>
-      <c r="G40" s="341" t="n"/>
-      <c r="H40" s="341" t="n"/>
-      <c r="I40" s="341" t="n"/>
-      <c r="J40" s="341" t="n"/>
-      <c r="K40" s="341" t="n"/>
-      <c r="L40" s="341" t="n"/>
-      <c r="M40" s="341" t="n"/>
+      <c r="B40" s="408" t="n"/>
+      <c r="C40" s="408" t="n"/>
+      <c r="D40" s="408" t="n"/>
+      <c r="E40" s="408" t="n"/>
+      <c r="F40" s="408" t="n"/>
+      <c r="G40" s="408" t="n"/>
+      <c r="H40" s="408" t="n"/>
+      <c r="I40" s="408" t="n"/>
+      <c r="J40" s="408" t="n"/>
+      <c r="K40" s="408" t="n"/>
+      <c r="L40" s="408" t="n"/>
+      <c r="M40" s="408" t="n"/>
       <c r="N40" s="493" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="O40" s="341" t="n"/>
-      <c r="P40" s="341" t="n"/>
-      <c r="Q40" s="341" t="n"/>
-      <c r="R40" s="341" t="n"/>
-      <c r="S40" s="341" t="n"/>
-      <c r="T40" s="341" t="n"/>
-      <c r="U40" s="341" t="n"/>
-      <c r="V40" s="341" t="n"/>
-      <c r="W40" s="341" t="n"/>
-      <c r="X40" s="341" t="n"/>
-      <c r="Y40" s="341" t="n"/>
-      <c r="Z40" s="341" t="n"/>
-      <c r="AA40" s="493" t="inlineStr">
+      <c r="O40" s="408" t="n"/>
+      <c r="P40" s="408" t="n"/>
+      <c r="Q40" s="408" t="n"/>
+      <c r="R40" s="408" t="n"/>
+      <c r="S40" s="408" t="n"/>
+      <c r="T40" s="408" t="n"/>
+      <c r="U40" s="408" t="n"/>
+      <c r="V40" s="408" t="n"/>
+      <c r="W40" s="408" t="n"/>
+      <c r="X40" s="408" t="n"/>
+      <c r="Y40" s="408" t="n"/>
+      <c r="Z40" s="408" t="n"/>
+      <c r="AA40" s="567" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="AB40" s="341" t="n"/>
-      <c r="AC40" s="341" t="n"/>
-      <c r="AD40" s="341" t="n"/>
-      <c r="AE40" s="341" t="n"/>
-      <c r="AF40" s="341" t="n"/>
-      <c r="AG40" s="341" t="n"/>
-      <c r="AH40" s="341" t="n"/>
-      <c r="AI40" s="341" t="n"/>
-      <c r="AJ40" s="341" t="n"/>
-      <c r="AK40" s="341" t="n"/>
-      <c r="AL40" s="341" t="n"/>
-      <c r="AM40" s="341" t="n"/>
-      <c r="AN40" s="464" t="n"/>
+      <c r="AB40" s="408" t="n"/>
+      <c r="AC40" s="408" t="n"/>
+      <c r="AD40" s="408" t="n"/>
+      <c r="AE40" s="408" t="n"/>
+      <c r="AF40" s="408" t="n"/>
+      <c r="AG40" s="408" t="n"/>
+      <c r="AH40" s="408" t="n"/>
+      <c r="AI40" s="408" t="n"/>
+      <c r="AJ40" s="408" t="n"/>
+      <c r="AK40" s="408" t="n"/>
+      <c r="AL40" s="408" t="n"/>
+      <c r="AM40" s="408" t="n"/>
+      <c r="AN40" s="538" t="n"/>
     </row>
     <row r="41" ht="20" customHeight="1" s="329">
-      <c r="A41" s="472" t="n"/>
-      <c r="B41" s="341" t="n"/>
-      <c r="C41" s="341" t="n"/>
-      <c r="D41" s="341" t="n"/>
-      <c r="E41" s="341" t="n"/>
-      <c r="F41" s="341" t="n"/>
-      <c r="G41" s="341" t="n"/>
-      <c r="H41" s="341" t="n"/>
-      <c r="I41" s="341" t="n"/>
-      <c r="J41" s="341" t="n"/>
-      <c r="K41" s="341" t="n"/>
-      <c r="L41" s="341" t="n"/>
-      <c r="M41" s="341" t="n"/>
-      <c r="N41" s="470" t="n"/>
-      <c r="O41" s="341" t="n"/>
-      <c r="P41" s="341" t="n"/>
-      <c r="Q41" s="341" t="n"/>
-      <c r="R41" s="341" t="n"/>
-      <c r="S41" s="341" t="n"/>
-      <c r="T41" s="341" t="n"/>
-      <c r="U41" s="341" t="n"/>
-      <c r="V41" s="341" t="n"/>
-      <c r="W41" s="341" t="n"/>
-      <c r="X41" s="341" t="n"/>
-      <c r="Y41" s="341" t="n"/>
-      <c r="Z41" s="341" t="n"/>
-      <c r="AA41" s="470" t="n"/>
-      <c r="AB41" s="341" t="n"/>
-      <c r="AC41" s="341" t="n"/>
-      <c r="AD41" s="341" t="n"/>
-      <c r="AE41" s="341" t="n"/>
-      <c r="AF41" s="341" t="n"/>
-      <c r="AG41" s="341" t="n"/>
-      <c r="AH41" s="341" t="n"/>
-      <c r="AI41" s="341" t="n"/>
-      <c r="AJ41" s="341" t="n"/>
-      <c r="AK41" s="341" t="n"/>
-      <c r="AL41" s="341" t="n"/>
-      <c r="AM41" s="341" t="n"/>
-      <c r="AN41" s="464" t="n"/>
+      <c r="A41" s="533" t="n"/>
+      <c r="N41" s="411" t="n"/>
+      <c r="AA41" s="411" t="n"/>
+      <c r="AN41" s="534" t="n"/>
     </row>
     <row r="42" ht="20" customHeight="1" s="329">
-      <c r="A42" s="473" t="n"/>
-      <c r="B42" s="466" t="n"/>
-      <c r="C42" s="466" t="n"/>
-      <c r="D42" s="466" t="n"/>
-      <c r="E42" s="466" t="n"/>
-      <c r="F42" s="466" t="n"/>
-      <c r="G42" s="466" t="n"/>
-      <c r="H42" s="466" t="n"/>
-      <c r="I42" s="466" t="n"/>
-      <c r="J42" s="466" t="n"/>
-      <c r="K42" s="466" t="n"/>
-      <c r="L42" s="466" t="n"/>
-      <c r="M42" s="466" t="n"/>
-      <c r="N42" s="474" t="n"/>
-      <c r="O42" s="466" t="n"/>
-      <c r="P42" s="466" t="n"/>
-      <c r="Q42" s="466" t="n"/>
-      <c r="R42" s="466" t="n"/>
-      <c r="S42" s="466" t="n"/>
-      <c r="T42" s="466" t="n"/>
-      <c r="U42" s="466" t="n"/>
-      <c r="V42" s="466" t="n"/>
-      <c r="W42" s="466" t="n"/>
-      <c r="X42" s="466" t="n"/>
-      <c r="Y42" s="466" t="n"/>
-      <c r="Z42" s="466" t="n"/>
-      <c r="AA42" s="474" t="n"/>
-      <c r="AB42" s="466" t="n"/>
-      <c r="AC42" s="466" t="n"/>
-      <c r="AD42" s="466" t="n"/>
-      <c r="AE42" s="466" t="n"/>
-      <c r="AF42" s="466" t="n"/>
-      <c r="AG42" s="466" t="n"/>
-      <c r="AH42" s="466" t="n"/>
-      <c r="AI42" s="466" t="n"/>
-      <c r="AJ42" s="466" t="n"/>
-      <c r="AK42" s="466" t="n"/>
-      <c r="AL42" s="466" t="n"/>
-      <c r="AM42" s="466" t="n"/>
-      <c r="AN42" s="469" t="n"/>
+      <c r="A42" s="560" t="n"/>
+      <c r="B42" s="413" t="n"/>
+      <c r="C42" s="413" t="n"/>
+      <c r="D42" s="413" t="n"/>
+      <c r="E42" s="413" t="n"/>
+      <c r="F42" s="413" t="n"/>
+      <c r="G42" s="413" t="n"/>
+      <c r="H42" s="413" t="n"/>
+      <c r="I42" s="413" t="n"/>
+      <c r="J42" s="413" t="n"/>
+      <c r="K42" s="413" t="n"/>
+      <c r="L42" s="413" t="n"/>
+      <c r="M42" s="413" t="n"/>
+      <c r="N42" s="412" t="n"/>
+      <c r="O42" s="413" t="n"/>
+      <c r="P42" s="413" t="n"/>
+      <c r="Q42" s="413" t="n"/>
+      <c r="R42" s="413" t="n"/>
+      <c r="S42" s="413" t="n"/>
+      <c r="T42" s="413" t="n"/>
+      <c r="U42" s="413" t="n"/>
+      <c r="V42" s="413" t="n"/>
+      <c r="W42" s="413" t="n"/>
+      <c r="X42" s="413" t="n"/>
+      <c r="Y42" s="413" t="n"/>
+      <c r="Z42" s="413" t="n"/>
+      <c r="AA42" s="412" t="n"/>
+      <c r="AB42" s="413" t="n"/>
+      <c r="AC42" s="413" t="n"/>
+      <c r="AD42" s="413" t="n"/>
+      <c r="AE42" s="413" t="n"/>
+      <c r="AF42" s="413" t="n"/>
+      <c r="AG42" s="413" t="n"/>
+      <c r="AH42" s="413" t="n"/>
+      <c r="AI42" s="413" t="n"/>
+      <c r="AJ42" s="413" t="n"/>
+      <c r="AK42" s="413" t="n"/>
+      <c r="AL42" s="413" t="n"/>
+      <c r="AM42" s="413" t="n"/>
+      <c r="AN42" s="561" t="n"/>
     </row>
     <row r="43" ht="3" customHeight="1" s="329">
       <c r="A43" s="384" t="n"/>
@@ -7895,50 +8271,50 @@
       <c r="AN43" s="350" t="n"/>
     </row>
     <row r="44" ht="20" customHeight="1" s="329">
-      <c r="A44" s="494" t="inlineStr">
+      <c r="A44" s="568" t="inlineStr">
         <is>
           <t>NOTICE: Use for outsourced incoming verification only. Normal receiving / put-away remains in FRM-701; abnormal hold / disposition goes to FRM-413.</t>
         </is>
       </c>
-      <c r="B44" s="495" t="n"/>
-      <c r="C44" s="495" t="n"/>
-      <c r="D44" s="495" t="n"/>
-      <c r="E44" s="495" t="n"/>
-      <c r="F44" s="495" t="n"/>
-      <c r="G44" s="495" t="n"/>
-      <c r="H44" s="495" t="n"/>
-      <c r="I44" s="495" t="n"/>
-      <c r="J44" s="495" t="n"/>
-      <c r="K44" s="495" t="n"/>
-      <c r="L44" s="495" t="n"/>
-      <c r="M44" s="495" t="n"/>
-      <c r="N44" s="495" t="n"/>
-      <c r="O44" s="495" t="n"/>
-      <c r="P44" s="495" t="n"/>
-      <c r="Q44" s="495" t="n"/>
-      <c r="R44" s="495" t="n"/>
-      <c r="S44" s="495" t="n"/>
-      <c r="T44" s="495" t="n"/>
-      <c r="U44" s="495" t="n"/>
-      <c r="V44" s="495" t="n"/>
-      <c r="W44" s="495" t="n"/>
-      <c r="X44" s="495" t="n"/>
-      <c r="Y44" s="495" t="n"/>
-      <c r="Z44" s="495" t="n"/>
-      <c r="AA44" s="495" t="n"/>
-      <c r="AB44" s="495" t="n"/>
-      <c r="AC44" s="495" t="n"/>
-      <c r="AD44" s="495" t="n"/>
-      <c r="AE44" s="495" t="n"/>
-      <c r="AF44" s="495" t="n"/>
-      <c r="AG44" s="495" t="n"/>
-      <c r="AH44" s="495" t="n"/>
-      <c r="AI44" s="495" t="n"/>
-      <c r="AJ44" s="495" t="n"/>
-      <c r="AK44" s="495" t="n"/>
-      <c r="AL44" s="495" t="n"/>
-      <c r="AM44" s="495" t="n"/>
-      <c r="AN44" s="496" t="n"/>
+      <c r="B44" s="550" t="n"/>
+      <c r="C44" s="550" t="n"/>
+      <c r="D44" s="550" t="n"/>
+      <c r="E44" s="550" t="n"/>
+      <c r="F44" s="550" t="n"/>
+      <c r="G44" s="550" t="n"/>
+      <c r="H44" s="550" t="n"/>
+      <c r="I44" s="550" t="n"/>
+      <c r="J44" s="550" t="n"/>
+      <c r="K44" s="550" t="n"/>
+      <c r="L44" s="550" t="n"/>
+      <c r="M44" s="550" t="n"/>
+      <c r="N44" s="550" t="n"/>
+      <c r="O44" s="550" t="n"/>
+      <c r="P44" s="550" t="n"/>
+      <c r="Q44" s="550" t="n"/>
+      <c r="R44" s="550" t="n"/>
+      <c r="S44" s="550" t="n"/>
+      <c r="T44" s="550" t="n"/>
+      <c r="U44" s="550" t="n"/>
+      <c r="V44" s="550" t="n"/>
+      <c r="W44" s="550" t="n"/>
+      <c r="X44" s="550" t="n"/>
+      <c r="Y44" s="550" t="n"/>
+      <c r="Z44" s="550" t="n"/>
+      <c r="AA44" s="550" t="n"/>
+      <c r="AB44" s="550" t="n"/>
+      <c r="AC44" s="550" t="n"/>
+      <c r="AD44" s="550" t="n"/>
+      <c r="AE44" s="550" t="n"/>
+      <c r="AF44" s="550" t="n"/>
+      <c r="AG44" s="550" t="n"/>
+      <c r="AH44" s="550" t="n"/>
+      <c r="AI44" s="550" t="n"/>
+      <c r="AJ44" s="550" t="n"/>
+      <c r="AK44" s="550" t="n"/>
+      <c r="AL44" s="550" t="n"/>
+      <c r="AM44" s="550" t="n"/>
+      <c r="AN44" s="551" t="n"/>
     </row>
     <row r="45" ht="26" customHeight="1" s="329"/>
     <row r="46" ht="4" customHeight="1" s="329"/>
@@ -8090,7 +8466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:CU11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="329" min="1" max="1"/>
@@ -8317,7 +8693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN16"/>
+  <dimension ref="A1:CU16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" style="329" min="1" max="1"/>
@@ -8368,12 +8744,12 @@
           <t>Actions / Containment</t>
         </is>
       </c>
-      <c r="B1" s="415" t="n"/>
-      <c r="C1" s="415" t="n"/>
-      <c r="D1" s="415" t="n"/>
-      <c r="E1" s="415" t="n"/>
-      <c r="F1" s="415" t="n"/>
-      <c r="G1" s="415" t="n"/>
+      <c r="B1" s="527" t="n"/>
+      <c r="C1" s="527" t="n"/>
+      <c r="D1" s="527" t="n"/>
+      <c r="E1" s="527" t="n"/>
+      <c r="F1" s="527" t="n"/>
+      <c r="G1" s="527" t="n"/>
       <c r="H1" s="498" t="n"/>
       <c r="I1" s="417" t="n"/>
       <c r="J1" s="418" t="n"/>
@@ -8414,12 +8790,6 @@
           <t>Incoming verification event record for outsourced process returns and discrete disposition decisions.</t>
         </is>
       </c>
-      <c r="B2" s="25" t="n"/>
-      <c r="C2" s="25" t="n"/>
-      <c r="D2" s="25" t="n"/>
-      <c r="E2" s="25" t="n"/>
-      <c r="F2" s="25" t="n"/>
-      <c r="G2" s="25" t="n"/>
       <c r="H2" s="500" t="n"/>
       <c r="I2" s="428" t="n"/>
       <c r="J2" s="429" t="n"/>
@@ -9160,7 +9530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN13"/>
+  <dimension ref="A1:CU13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" style="329" min="1" max="1"/>
@@ -9211,12 +9581,12 @@
           <t>Upstream References / Import Guidance</t>
         </is>
       </c>
-      <c r="B1" s="415" t="n"/>
-      <c r="C1" s="415" t="n"/>
-      <c r="D1" s="415" t="n"/>
-      <c r="E1" s="415" t="n"/>
-      <c r="F1" s="415" t="n"/>
-      <c r="G1" s="415" t="n"/>
+      <c r="B1" s="527" t="n"/>
+      <c r="C1" s="527" t="n"/>
+      <c r="D1" s="527" t="n"/>
+      <c r="E1" s="527" t="n"/>
+      <c r="F1" s="527" t="n"/>
+      <c r="G1" s="527" t="n"/>
       <c r="H1" s="498" t="n"/>
       <c r="I1" s="417" t="n"/>
       <c r="J1" s="418" t="n"/>
@@ -9257,12 +9627,6 @@
           <t>Incoming verification event record for outsourced process returns and discrete disposition decisions.</t>
         </is>
       </c>
-      <c r="B2" s="25" t="n"/>
-      <c r="C2" s="25" t="n"/>
-      <c r="D2" s="25" t="n"/>
-      <c r="E2" s="25" t="n"/>
-      <c r="F2" s="25" t="n"/>
-      <c r="G2" s="25" t="n"/>
       <c r="H2" s="500" t="n"/>
       <c r="I2" s="428" t="n"/>
       <c r="J2" s="429" t="n"/>
@@ -9917,7 +10281,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN13"/>
+  <dimension ref="A1:CU13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" style="329" min="1" max="1"/>
@@ -9968,12 +10332,12 @@
           <t>Evidence Reference / Attachment Guidance</t>
         </is>
       </c>
-      <c r="B1" s="415" t="n"/>
-      <c r="C1" s="415" t="n"/>
-      <c r="D1" s="415" t="n"/>
-      <c r="E1" s="415" t="n"/>
-      <c r="F1" s="415" t="n"/>
-      <c r="G1" s="415" t="n"/>
+      <c r="B1" s="527" t="n"/>
+      <c r="C1" s="527" t="n"/>
+      <c r="D1" s="527" t="n"/>
+      <c r="E1" s="527" t="n"/>
+      <c r="F1" s="527" t="n"/>
+      <c r="G1" s="527" t="n"/>
       <c r="H1" s="498" t="n"/>
       <c r="I1" s="417" t="n"/>
       <c r="J1" s="418" t="n"/>
@@ -10014,12 +10378,6 @@
           <t>Use controlled evidence package references; do not free-type vague placeholders.</t>
         </is>
       </c>
-      <c r="B2" s="25" t="n"/>
-      <c r="C2" s="25" t="n"/>
-      <c r="D2" s="25" t="n"/>
-      <c r="E2" s="25" t="n"/>
-      <c r="F2" s="25" t="n"/>
-      <c r="G2" s="25" t="n"/>
       <c r="H2" s="500" t="n"/>
       <c r="I2" s="428" t="n"/>
       <c r="J2" s="429" t="n"/>

--- a/04-Bieu-Mau/04-FRM-400/FRM-411_Outsourced_Process_Incoming_Verification.xlsx
+++ b/04-Bieu-Mau/04-FRM-400/FRM-411_Outsourced_Process_Incoming_Verification.xlsx
@@ -4,10 +4,10 @@
   <workbookPr/>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INCOMING_VERIFY" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ACTIONS" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_IMPORT" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVIDENCE_REF" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="2" state="veryHidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ACTIONS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_IMPORT" sheetId="4" state="veryHidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVIDENCE_REF" sheetId="5" state="veryHidden" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'INCOMING_VERIFY'!$A$1:$AN$44</definedName>
@@ -6299,7 +6299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CU44"/>
+  <dimension ref="A1:AN44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.329999923706055" customWidth="1" style="329" min="1" max="1"/>
@@ -8466,7 +8466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="329" min="1" max="1"/>
@@ -8693,7 +8693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU16"/>
+  <dimension ref="A1:AN16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" style="329" min="1" max="1"/>
@@ -9530,7 +9530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU13"/>
+  <dimension ref="A1:AN13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" style="329" min="1" max="1"/>
@@ -10281,7 +10281,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU13"/>
+  <dimension ref="A1:AN13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" style="329" min="1" max="1"/>

--- a/04-Bieu-Mau/04-FRM-400/FRM-411_Outsourced_Process_Incoming_Verification.xlsx
+++ b/04-Bieu-Mau/04-FRM-400/FRM-411_Outsourced_Process_Incoming_Verification.xlsx
@@ -15,10 +15,368 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="117">
+  <si>
+    <t>  1. REFERENCE INFORMATION</t>
+  </si>
+  <si>
+    <t>  2. INCOMING VERIFICATION / FINDING DETAIL</t>
+  </si>
+  <si>
+    <t>  3. IMPACT / CONTAINMENT / ACTIONS</t>
+  </si>
+  <si>
+    <t>  4. FINAL DECISION / CLOSURE</t>
+  </si>
+  <si>
+    <t>  5. APPROVAL / SIGN-OFF</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>=ROW()-ROW($A$27)+1</t>
+  </si>
+  <si>
+    <t>=ROW()-ROW($A$5)+1</t>
+  </si>
+  <si>
+    <t>ACTION_STATUS</t>
+  </si>
+  <si>
+    <t>ANNEX-ENG-002</t>
+  </si>
+  <si>
+    <t>ANNEX-ENG-002 — Approved materials list, source restriction và rule thay thế</t>
+  </si>
+  <si>
+    <t>ANNEX-PUR-001</t>
+  </si>
+  <si>
+    <t>ANNEX-PUR-001 — Mô hình rủi ro nhà cung cấp và phương pháp scorecard</t>
+  </si>
+  <si>
+    <t>ANNEX-PUR-002</t>
+  </si>
+  <si>
+    <t>ANNEX-PUR-002 — Gói kiểm soát outsource / special process / cert flow-down</t>
+  </si>
+  <si>
+    <t>ANNEX-PUR-003</t>
+  </si>
+  <si>
+    <t>ANNEX-PUR-003 — Approved processor list, scope approval và rule tạm ngưng</t>
+  </si>
+  <si>
+    <t>APPROVED</t>
+  </si>
+  <si>
+    <t>Actions / Containment</t>
+  </si>
+  <si>
+    <t>Affected Job Ref</t>
+  </si>
+  <si>
+    <t>Approved by</t>
+  </si>
+  <si>
+    <t>CLOSED</t>
+  </si>
+  <si>
+    <t>CONDITIONAL</t>
+  </si>
+  <si>
+    <t>CRITICAL</t>
+  </si>
+  <si>
+    <t>Cat.</t>
+  </si>
+  <si>
+    <t>Close When</t>
+  </si>
+  <si>
+    <t>Close when the final decision, final owner, final disposition and required follow-up actions are all recorded and the evidence package is complete.</t>
+  </si>
+  <si>
+    <t>Containment Required (YES/NO)</t>
+  </si>
+  <si>
+    <t>Countermeasure / Trigger</t>
+  </si>
+  <si>
+    <t>Cross-Reference Boundary</t>
+  </si>
+  <si>
+    <t>Customer Special Requirement (YES/NO)</t>
+  </si>
+  <si>
+    <t>DISPOSITION_GATE</t>
+  </si>
+  <si>
+    <t>Disposition Status</t>
+  </si>
+  <si>
+    <t>Do not duplicate ERP/M365/ANNEX master data.</t>
+  </si>
+  <si>
+    <t>Due Date</t>
+  </si>
+  <si>
+    <t>ENG</t>
+  </si>
+  <si>
+    <t>Epicor transaction + M365 evidence</t>
+  </si>
+  <si>
+    <t>Evidence / Criteria</t>
+  </si>
+  <si>
+    <t>Evidence Package Ref</t>
+  </si>
+  <si>
+    <t>Evidence Ref</t>
+  </si>
+  <si>
+    <t>Evidence Reference / Attachment Guidance</t>
+  </si>
+  <si>
+    <t>FRM-411</t>
+  </si>
+  <si>
+    <t>Field</t>
+  </si>
+  <si>
+    <t>Final Decision</t>
+  </si>
+  <si>
+    <t>Finding / Check</t>
+  </si>
+  <si>
+    <t>General Manager</t>
+  </si>
+  <si>
+    <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
+  </si>
+  <si>
+    <t>HIGH</t>
+  </si>
+  <si>
+    <t>HOLD</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
+    <t>IN PROGRESS</t>
+  </si>
+  <si>
+    <t>INEFFECTIVE</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>Incoming Verification ID</t>
+  </si>
+  <si>
+    <t>Incoming verification event record for outsourced process returns and discrete disposition decisions.</t>
+  </si>
+  <si>
+    <t>Issue / Finding</t>
+  </si>
+  <si>
+    <t>LOW</t>
+  </si>
+  <si>
+    <t>MEDIUM</t>
+  </si>
+  <si>
+    <t>MGT</t>
+  </si>
+  <si>
+    <t>MONITORING</t>
+  </si>
+  <si>
+    <t>Method / Acceptance Ref</t>
+  </si>
+  <si>
+    <t>NOTICE: Use for outsourced incoming verification only. Normal receiving / put-away remains in FRM-701; abnormal hold / disposition goes to FRM-413.</t>
+  </si>
+  <si>
+    <t>Name / Signature / Date</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>OBSERVATION / CONTAINMENT / CERT CHECK</t>
+  </si>
+  <si>
+    <t>OPEN</t>
+  </si>
+  <si>
+    <t>OVERDUE</t>
+  </si>
+  <si>
+    <t>OWNER_DEPT</t>
+  </si>
+  <si>
+    <t>Open When</t>
+  </si>
+  <si>
+    <t>Open immediately when the event, request, issue, change, complaint, risk or incident is detected or formally raised.</t>
+  </si>
+  <si>
+    <t>Operational trigger</t>
+  </si>
+  <si>
+    <t>Outsourced Process Incoming Verification</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>PLANNING</t>
+  </si>
+  <si>
+    <t>PO / Cert / Lot Ref</t>
+  </si>
+  <si>
+    <t>PROD</t>
+  </si>
+  <si>
+    <t>PUR</t>
+  </si>
+  <si>
+    <t>Part / Lot / Qty</t>
+  </si>
+  <si>
+    <t>Prepared by</t>
+  </si>
+  <si>
+    <t>Prepared by / Date-Time</t>
+  </si>
+  <si>
+    <t>Purchasing + QA</t>
+  </si>
+  <si>
+    <t>QA</t>
+  </si>
+  <si>
+    <t>Quality Management System · Controlled Document</t>
+  </si>
+  <si>
+    <t>REJECT</t>
+  </si>
+  <si>
+    <t>RISK</t>
+  </si>
+  <si>
+    <t>Record Status</t>
+  </si>
+  <si>
+    <t>Ref.</t>
+  </si>
+  <si>
+    <t>Related Requirement / Package</t>
+  </si>
+  <si>
+    <t>Release / closure rule</t>
+  </si>
+  <si>
+    <t>Required Action</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>Reviewed by</t>
+  </si>
+  <si>
+    <t>Risk Level</t>
+  </si>
+  <si>
+    <t>SALES</t>
+  </si>
+  <si>
+    <t>SOP-402</t>
+  </si>
+  <si>
+    <t>SOP-402 — Xác minh vật liệu, truy xuất và phòng chống vật tư giả/không rõ nguồn gốc | HESEM QMS</t>
+  </si>
+  <si>
+    <t>STATUS</t>
+  </si>
+  <si>
+    <t>Source of Truth</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Supplier / Processor / Cert</t>
+  </si>
+  <si>
+    <t>Supplier-Quality Owner</t>
+  </si>
+  <si>
+    <t>Target Closeout</t>
+  </si>
+  <si>
+    <t>This form does not replace SOP-402; it records the evidence, data or decision required by that SOP.
+Rules, matrices, dictionaries, acceptance criteria and data definitions belong in ANNEX-PUR-001/002/003 + ANNEX-ENG-002; do not copy ANNEX content into the live data-entry body.
+System-of-record / source-of-truth boundary: Epicor transaction + M365 evidence. If the master data already live there, reference or import them; do not re-key without need.</t>
+  </si>
+  <si>
+    <t>Upstream References / Import Guidance</t>
+  </si>
+  <si>
+    <t>Use controlled evidence package references; do not free-type vague placeholders.</t>
+  </si>
+  <si>
+    <t>V0</t>
+  </si>
+  <si>
+    <t>VERIFICATION / SCOPE DESCRIPTION</t>
+  </si>
+  <si>
+    <t>VERIFIED</t>
+  </si>
+  <si>
+    <t>Value / Reference</t>
+  </si>
+  <si>
+    <t>WHS</t>
+  </si>
+  <si>
+    <t>YYYY-MM-DD</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/01-SOPs/04-SOP-400/sop-402-material-verification-traceability-and-counterfeit-prevention.html</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-eng-002-approved-materials-list.html</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-001-supplier-risk-model-and-scorecard-method.html</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-002-outsource-special-process-pack.html</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-003-approved-processor-list.html</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="86">
+  <fonts count="87">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -505,8 +863,13 @@
       <color rgb="00BBCCCC"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="007B4F00"/>
+      <sz val="7"/>
+    </font>
   </fonts>
-  <fills count="52">
+  <fills count="53">
     <fill>
       <patternFill/>
     </fill>
@@ -763,8 +1126,13 @@
         <fgColor rgb="000C2D48"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="354">
+  <borders count="357">
     <border>
       <left/>
       <right/>
@@ -4585,12 +4953,46 @@
         <color rgb="002C9CD7"/>
       </bottom>
       <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00F9A825"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="569">
+  <cellXfs count="572">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -5878,6 +6280,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="80" fillId="4" borderId="335" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="52" borderId="354" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="52" borderId="355" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="52" borderId="356" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -8271,50 +8682,50 @@
       <c r="AN43" s="350" t="n"/>
     </row>
     <row r="44" ht="20" customHeight="1" s="329">
-      <c r="A44" s="568" t="inlineStr">
+      <c r="A44" s="569" t="inlineStr">
         <is>
           <t>NOTICE: Use for outsourced incoming verification only. Normal receiving / put-away remains in FRM-701; abnormal hold / disposition goes to FRM-413.</t>
         </is>
       </c>
-      <c r="B44" s="550" t="n"/>
-      <c r="C44" s="550" t="n"/>
-      <c r="D44" s="550" t="n"/>
-      <c r="E44" s="550" t="n"/>
-      <c r="F44" s="550" t="n"/>
-      <c r="G44" s="550" t="n"/>
-      <c r="H44" s="550" t="n"/>
-      <c r="I44" s="550" t="n"/>
-      <c r="J44" s="550" t="n"/>
-      <c r="K44" s="550" t="n"/>
-      <c r="L44" s="550" t="n"/>
-      <c r="M44" s="550" t="n"/>
-      <c r="N44" s="550" t="n"/>
-      <c r="O44" s="550" t="n"/>
-      <c r="P44" s="550" t="n"/>
-      <c r="Q44" s="550" t="n"/>
-      <c r="R44" s="550" t="n"/>
-      <c r="S44" s="550" t="n"/>
-      <c r="T44" s="550" t="n"/>
-      <c r="U44" s="550" t="n"/>
-      <c r="V44" s="550" t="n"/>
-      <c r="W44" s="550" t="n"/>
-      <c r="X44" s="550" t="n"/>
-      <c r="Y44" s="550" t="n"/>
-      <c r="Z44" s="550" t="n"/>
-      <c r="AA44" s="550" t="n"/>
-      <c r="AB44" s="550" t="n"/>
-      <c r="AC44" s="550" t="n"/>
-      <c r="AD44" s="550" t="n"/>
-      <c r="AE44" s="550" t="n"/>
-      <c r="AF44" s="550" t="n"/>
-      <c r="AG44" s="550" t="n"/>
-      <c r="AH44" s="550" t="n"/>
-      <c r="AI44" s="550" t="n"/>
-      <c r="AJ44" s="550" t="n"/>
-      <c r="AK44" s="550" t="n"/>
-      <c r="AL44" s="550" t="n"/>
-      <c r="AM44" s="550" t="n"/>
-      <c r="AN44" s="551" t="n"/>
+      <c r="B44" s="570" t="n"/>
+      <c r="C44" s="570" t="n"/>
+      <c r="D44" s="570" t="n"/>
+      <c r="E44" s="570" t="n"/>
+      <c r="F44" s="570" t="n"/>
+      <c r="G44" s="570" t="n"/>
+      <c r="H44" s="570" t="n"/>
+      <c r="I44" s="570" t="n"/>
+      <c r="J44" s="570" t="n"/>
+      <c r="K44" s="570" t="n"/>
+      <c r="L44" s="570" t="n"/>
+      <c r="M44" s="570" t="n"/>
+      <c r="N44" s="570" t="n"/>
+      <c r="O44" s="570" t="n"/>
+      <c r="P44" s="570" t="n"/>
+      <c r="Q44" s="570" t="n"/>
+      <c r="R44" s="570" t="n"/>
+      <c r="S44" s="570" t="n"/>
+      <c r="T44" s="570" t="n"/>
+      <c r="U44" s="570" t="n"/>
+      <c r="V44" s="570" t="n"/>
+      <c r="W44" s="570" t="n"/>
+      <c r="X44" s="570" t="n"/>
+      <c r="Y44" s="570" t="n"/>
+      <c r="Z44" s="570" t="n"/>
+      <c r="AA44" s="570" t="n"/>
+      <c r="AB44" s="570" t="n"/>
+      <c r="AC44" s="570" t="n"/>
+      <c r="AD44" s="570" t="n"/>
+      <c r="AE44" s="570" t="n"/>
+      <c r="AF44" s="570" t="n"/>
+      <c r="AG44" s="570" t="n"/>
+      <c r="AH44" s="570" t="n"/>
+      <c r="AI44" s="570" t="n"/>
+      <c r="AJ44" s="570" t="n"/>
+      <c r="AK44" s="570" t="n"/>
+      <c r="AL44" s="570" t="n"/>
+      <c r="AM44" s="570" t="n"/>
+      <c r="AN44" s="571" t="n"/>
     </row>
     <row r="45" ht="26" customHeight="1" s="329"/>
     <row r="46" ht="4" customHeight="1" s="329"/>

--- a/04-Bieu-Mau/04-FRM-400/FRM-411_Outsourced_Process_Incoming_Verification.xlsx
+++ b/04-Bieu-Mau/04-FRM-400/FRM-411_Outsourced_Process_Incoming_Verification.xlsx
@@ -6,8 +6,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INCOMING_VERIFY" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="2" state="veryHidden" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ACTIONS" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_IMPORT" sheetId="4" state="veryHidden" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVIDENCE_REF" sheetId="5" state="veryHidden" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'INCOMING_VERIFY'!$A$1:$AN$44</definedName>
@@ -16,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
   <si>
     <t>  1. REFERENCE INFORMATION</t>
   </si>
@@ -39,40 +37,16 @@
     <t>=ROW()-ROW($A$27)+1</t>
   </si>
   <si>
-    <t>=ROW()-ROW($A$5)+1</t>
+    <t>=ROW()-ROW($A$9)+1</t>
+  </si>
+  <si>
+    <t>ACTION TRACKER</t>
   </si>
   <si>
     <t>ACTION_STATUS</t>
   </si>
   <si>
-    <t>ANNEX-ENG-002</t>
-  </si>
-  <si>
-    <t>ANNEX-ENG-002 — Approved materials list, source restriction và rule thay thế</t>
-  </si>
-  <si>
-    <t>ANNEX-PUR-001</t>
-  </si>
-  <si>
-    <t>ANNEX-PUR-001 — Mô hình rủi ro nhà cung cấp và phương pháp scorecard</t>
-  </si>
-  <si>
-    <t>ANNEX-PUR-002</t>
-  </si>
-  <si>
-    <t>ANNEX-PUR-002 — Gói kiểm soát outsource / special process / cert flow-down</t>
-  </si>
-  <si>
-    <t>ANNEX-PUR-003</t>
-  </si>
-  <si>
-    <t>ANNEX-PUR-003 — Approved processor list, scope approval và rule tạm ngưng</t>
-  </si>
-  <si>
     <t>APPROVED</t>
-  </si>
-  <si>
-    <t>Actions / Containment</t>
   </si>
   <si>
     <t>Affected Job Ref</t>
@@ -93,19 +67,10 @@
     <t>Cat.</t>
   </si>
   <si>
-    <t>Close When</t>
-  </si>
-  <si>
-    <t>Close when the final decision, final owner, final disposition and required follow-up actions are all recorded and the evidence package is complete.</t>
-  </si>
-  <si>
     <t>Containment Required (YES/NO)</t>
   </si>
   <si>
     <t>Countermeasure / Trigger</t>
-  </si>
-  <si>
-    <t>Cross-Reference Boundary</t>
   </si>
   <si>
     <t>Customer Special Requirement (YES/NO)</t>
@@ -117,34 +82,16 @@
     <t>Disposition Status</t>
   </si>
   <si>
-    <t>Do not duplicate ERP/M365/ANNEX master data.</t>
-  </si>
-  <si>
     <t>Due Date</t>
   </si>
   <si>
     <t>ENG</t>
   </si>
   <si>
-    <t>Epicor transaction + M365 evidence</t>
-  </si>
-  <si>
     <t>Evidence / Criteria</t>
   </si>
   <si>
-    <t>Evidence Package Ref</t>
-  </si>
-  <si>
-    <t>Evidence Ref</t>
-  </si>
-  <si>
-    <t>Evidence Reference / Attachment Guidance</t>
-  </si>
-  <si>
     <t>FRM-411</t>
-  </si>
-  <si>
-    <t>Field</t>
   </si>
   <si>
     <t>Final Decision</t>
@@ -180,10 +127,7 @@
     <t>Incoming Verification ID</t>
   </si>
   <si>
-    <t>Incoming verification event record for outsourced process returns and discrete disposition decisions.</t>
-  </si>
-  <si>
-    <t>Issue / Finding</t>
+    <t>Issue / Requirement</t>
   </si>
   <si>
     <t>LOW</t>
@@ -207,9 +151,6 @@
     <t>Name / Signature / Date</t>
   </si>
   <si>
-    <t>Notes</t>
-  </si>
-  <si>
     <t>OBSERVATION / CONTAINMENT / CERT CHECK</t>
   </si>
   <si>
@@ -220,15 +161,6 @@
   </si>
   <si>
     <t>OWNER_DEPT</t>
-  </si>
-  <si>
-    <t>Open When</t>
-  </si>
-  <si>
-    <t>Open immediately when the event, request, issue, change, complaint, risk or incident is detected or formally raised.</t>
-  </si>
-  <si>
-    <t>Operational trigger</t>
   </si>
   <si>
     <t>Outsourced Process Incoming Verification</t>
@@ -258,6 +190,9 @@
     <t>Prepared by / Date-Time</t>
   </si>
   <si>
+    <t>Process Cert Matches Spec?</t>
+  </si>
+  <si>
     <t>Purchasing + QA</t>
   </si>
   <si>
@@ -282,9 +217,6 @@
     <t>Related Requirement / Package</t>
   </si>
   <si>
-    <t>Release / closure rule</t>
-  </si>
-  <si>
     <t>Required Action</t>
   </si>
   <si>
@@ -300,16 +232,7 @@
     <t>SALES</t>
   </si>
   <si>
-    <t>SOP-402</t>
-  </si>
-  <si>
-    <t>SOP-402 — Xác minh vật liệu, truy xuất và phòng chống vật tư giả/không rõ nguồn gốc | HESEM QMS</t>
-  </si>
-  <si>
     <t>STATUS</t>
-  </si>
-  <si>
-    <t>Source of Truth</t>
   </si>
   <si>
     <t>Status</t>
@@ -324,17 +247,6 @@
     <t>Target Closeout</t>
   </si>
   <si>
-    <t>This form does not replace SOP-402; it records the evidence, data or decision required by that SOP.
-Rules, matrices, dictionaries, acceptance criteria and data definitions belong in ANNEX-PUR-001/002/003 + ANNEX-ENG-002; do not copy ANNEX content into the live data-entry body.
-System-of-record / source-of-truth boundary: Epicor transaction + M365 evidence. If the master data already live there, reference or import them; do not re-key without need.</t>
-  </si>
-  <si>
-    <t>Upstream References / Import Guidance</t>
-  </si>
-  <si>
-    <t>Use controlled evidence package references; do not free-type vague placeholders.</t>
-  </si>
-  <si>
     <t>V0</t>
   </si>
   <si>
@@ -344,28 +256,16 @@
     <t>VERIFIED</t>
   </si>
   <si>
-    <t>Value / Reference</t>
+    <t>Verified by</t>
+  </si>
+  <si>
+    <t>Visual Inspection Result</t>
   </si>
   <si>
     <t>WHS</t>
   </si>
   <si>
     <t>YYYY-MM-DD</t>
-  </si>
-  <si>
-    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/01-SOPs/04-SOP-400/sop-402-material-verification-traceability-and-counterfeit-prevention.html</t>
-  </si>
-  <si>
-    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-eng-002-approved-materials-list.html</t>
-  </si>
-  <si>
-    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-001-supplier-risk-model-and-scorecard-method.html</t>
-  </si>
-  <si>
-    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-002-outsource-special-process-pack.html</t>
-  </si>
-  <si>
-    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-003-approved-processor-list.html</t>
   </si>
   <si>
     <t>—</t>
@@ -376,7 +276,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="87">
+  <fonts count="89">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -868,8 +768,17 @@
       <color rgb="007B4F00"/>
       <sz val="7"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="53">
+  <fills count="54">
     <fill>
       <patternFill/>
     </fill>
@@ -1131,8 +1040,13 @@
         <fgColor rgb="00FFF8E1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7FBFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="357">
+  <borders count="368">
     <border>
       <left/>
       <right/>
@@ -4986,13 +4900,152 @@
       </top>
       <bottom style="thin">
         <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00F9A825"/>
+      </left>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="572">
+  <cellXfs count="620">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -6290,6 +6343,112 @@
     </xf>
     <xf numFmtId="0" fontId="86" fillId="52" borderId="356" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="52" borderId="357" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="360" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="361" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="312" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="313" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="84" fillId="50" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="51" borderId="311" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="362" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="53" fillId="51" borderId="320" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="312" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="313" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="4" borderId="318" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="276" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="275" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="319" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="53" borderId="318" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="276" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="53" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="275" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="319" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="53" borderId="306" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="308" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="53" borderId="309" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="307" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="310" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="53" fillId="51" borderId="367" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="365" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="53" fillId="51" borderId="364" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="51" borderId="321" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="4" borderId="366" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="329" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="53" borderId="366" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="53" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="53" borderId="329" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="53" borderId="346" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="53" borderId="363" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="53" borderId="349" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="47" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="4" borderId="318" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="53" borderId="318" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="53" borderId="306" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="4" borderId="366" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="53" borderId="366" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="53" borderId="346" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6429,59 +6588,21 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>1</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1303776" cy="376089"/>
+    <ext cx="523875" cy="523875"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1303776" cy="376089"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -7210,7 +7331,7 @@
     <row r="12" ht="20" customHeight="1" s="329">
       <c r="A12" s="461" t="inlineStr">
         <is>
-          <t>Evidence Package Ref</t>
+          <t>Process Cert Matches Spec?</t>
         </is>
       </c>
       <c r="B12" s="409" t="n"/>
@@ -7234,7 +7355,7 @@
       <c r="T12" s="409" t="n"/>
       <c r="U12" s="463" t="inlineStr">
         <is>
-          <t>Risk Level</t>
+          <t>Visual Inspection Result</t>
         </is>
       </c>
       <c r="V12" s="409" t="n"/>
@@ -9104,7 +9225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN16"/>
+  <dimension ref="A1:AN50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" style="329" min="1" max="1"/>
@@ -9150,769 +9271,2215 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="329">
-      <c r="A1" s="497" t="inlineStr">
-        <is>
-          <t>Actions / Containment</t>
-        </is>
-      </c>
+      <c r="A1" s="526" t="n"/>
       <c r="B1" s="527" t="n"/>
       <c r="C1" s="527" t="n"/>
       <c r="D1" s="527" t="n"/>
       <c r="E1" s="527" t="n"/>
       <c r="F1" s="527" t="n"/>
       <c r="G1" s="527" t="n"/>
-      <c r="H1" s="498" t="n"/>
-      <c r="I1" s="417" t="n"/>
-      <c r="J1" s="418" t="n"/>
-      <c r="K1" s="418" t="n"/>
-      <c r="L1" s="418" t="n"/>
-      <c r="M1" s="418" t="n"/>
-      <c r="N1" s="418" t="n"/>
-      <c r="O1" s="418" t="n"/>
-      <c r="P1" s="418" t="n"/>
-      <c r="Q1" s="418" t="n"/>
-      <c r="R1" s="418" t="n"/>
-      <c r="S1" s="418" t="n"/>
-      <c r="T1" s="418" t="n"/>
-      <c r="U1" s="418" t="n"/>
-      <c r="V1" s="418" t="n"/>
-      <c r="W1" s="418" t="n"/>
-      <c r="X1" s="418" t="n"/>
-      <c r="Y1" s="418" t="n"/>
-      <c r="Z1" s="418" t="n"/>
-      <c r="AA1" s="418" t="n"/>
-      <c r="AB1" s="418" t="n"/>
-      <c r="AC1" s="418" t="n"/>
-      <c r="AD1" s="419" t="n"/>
-      <c r="AE1" s="420" t="n"/>
-      <c r="AF1" s="421" t="n"/>
-      <c r="AG1" s="421" t="n"/>
-      <c r="AH1" s="422" t="n"/>
-      <c r="AI1" s="423" t="n"/>
-      <c r="AJ1" s="424" t="n"/>
-      <c r="AK1" s="424" t="n"/>
-      <c r="AL1" s="424" t="n"/>
-      <c r="AM1" s="424" t="n"/>
-      <c r="AN1" s="425" t="n"/>
+      <c r="H1" s="528" t="n"/>
+      <c r="I1" s="529" t="inlineStr">
+        <is>
+          <t>Outsourced Process Incoming Verification</t>
+        </is>
+      </c>
+      <c r="J1" s="527" t="n"/>
+      <c r="K1" s="527" t="n"/>
+      <c r="L1" s="527" t="n"/>
+      <c r="M1" s="527" t="n"/>
+      <c r="N1" s="527" t="n"/>
+      <c r="O1" s="527" t="n"/>
+      <c r="P1" s="527" t="n"/>
+      <c r="Q1" s="527" t="n"/>
+      <c r="R1" s="527" t="n"/>
+      <c r="S1" s="527" t="n"/>
+      <c r="T1" s="527" t="n"/>
+      <c r="U1" s="527" t="n"/>
+      <c r="V1" s="527" t="n"/>
+      <c r="W1" s="527" t="n"/>
+      <c r="X1" s="527" t="n"/>
+      <c r="Y1" s="527" t="n"/>
+      <c r="Z1" s="527" t="n"/>
+      <c r="AA1" s="527" t="n"/>
+      <c r="AB1" s="527" t="n"/>
+      <c r="AC1" s="527" t="n"/>
+      <c r="AD1" s="528" t="n"/>
+      <c r="AE1" s="530" t="n"/>
+      <c r="AF1" s="527" t="n"/>
+      <c r="AG1" s="527" t="n"/>
+      <c r="AH1" s="531" t="n"/>
+      <c r="AI1" s="532" t="inlineStr">
+        <is>
+          <t>FRM-411</t>
+        </is>
+      </c>
+      <c r="AJ1" s="527" t="n"/>
+      <c r="AK1" s="527" t="n"/>
+      <c r="AL1" s="527" t="n"/>
+      <c r="AM1" s="527" t="n"/>
+      <c r="AN1" s="528" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1" s="329">
-      <c r="A2" s="499" t="inlineStr">
+      <c r="A2" s="533" t="n"/>
+      <c r="H2" s="534" t="n"/>
+      <c r="I2" s="533" t="n"/>
+      <c r="AD2" s="534" t="n"/>
+      <c r="AE2" s="535" t="n"/>
+      <c r="AF2" s="408" t="n"/>
+      <c r="AG2" s="408" t="n"/>
+      <c r="AH2" s="536" t="n"/>
+      <c r="AI2" s="537" t="inlineStr">
         <is>
-          <t>Incoming verification event record for outsourced process returns and discrete disposition decisions.</t>
+          <t>V0</t>
         </is>
       </c>
-      <c r="H2" s="500" t="n"/>
-      <c r="I2" s="428" t="n"/>
-      <c r="J2" s="429" t="n"/>
-      <c r="K2" s="429" t="n"/>
-      <c r="L2" s="429" t="n"/>
-      <c r="M2" s="429" t="n"/>
-      <c r="N2" s="429" t="n"/>
-      <c r="O2" s="429" t="n"/>
-      <c r="P2" s="429" t="n"/>
-      <c r="Q2" s="429" t="n"/>
-      <c r="R2" s="429" t="n"/>
-      <c r="S2" s="429" t="n"/>
-      <c r="T2" s="429" t="n"/>
-      <c r="U2" s="429" t="n"/>
-      <c r="V2" s="429" t="n"/>
-      <c r="W2" s="429" t="n"/>
-      <c r="X2" s="429" t="n"/>
-      <c r="Y2" s="429" t="n"/>
-      <c r="Z2" s="429" t="n"/>
-      <c r="AA2" s="429" t="n"/>
-      <c r="AB2" s="429" t="n"/>
-      <c r="AC2" s="429" t="n"/>
-      <c r="AD2" s="430" t="n"/>
-      <c r="AE2" s="431" t="n"/>
-      <c r="AF2" s="432" t="n"/>
-      <c r="AG2" s="432" t="n"/>
-      <c r="AH2" s="433" t="n"/>
-      <c r="AI2" s="434" t="n"/>
-      <c r="AJ2" s="435" t="n"/>
-      <c r="AK2" s="435" t="n"/>
-      <c r="AL2" s="435" t="n"/>
-      <c r="AM2" s="435" t="n"/>
-      <c r="AN2" s="436" t="n"/>
+      <c r="AJ2" s="408" t="n"/>
+      <c r="AK2" s="408" t="n"/>
+      <c r="AL2" s="408" t="n"/>
+      <c r="AM2" s="408" t="n"/>
+      <c r="AN2" s="538" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1" s="329">
-      <c r="A3" s="501" t="n"/>
-      <c r="B3" s="502" t="n"/>
-      <c r="C3" s="502" t="n"/>
-      <c r="D3" s="502" t="n"/>
-      <c r="E3" s="502" t="n"/>
-      <c r="F3" s="502" t="n"/>
-      <c r="G3" s="502" t="n"/>
-      <c r="H3" s="500" t="n"/>
-      <c r="I3" s="428" t="n"/>
-      <c r="J3" s="429" t="n"/>
-      <c r="K3" s="429" t="n"/>
-      <c r="L3" s="429" t="n"/>
-      <c r="M3" s="429" t="n"/>
-      <c r="N3" s="429" t="n"/>
-      <c r="O3" s="429" t="n"/>
-      <c r="P3" s="429" t="n"/>
-      <c r="Q3" s="429" t="n"/>
-      <c r="R3" s="429" t="n"/>
-      <c r="S3" s="429" t="n"/>
-      <c r="T3" s="429" t="n"/>
-      <c r="U3" s="429" t="n"/>
-      <c r="V3" s="429" t="n"/>
-      <c r="W3" s="429" t="n"/>
-      <c r="X3" s="429" t="n"/>
-      <c r="Y3" s="429" t="n"/>
-      <c r="Z3" s="429" t="n"/>
-      <c r="AA3" s="429" t="n"/>
-      <c r="AB3" s="429" t="n"/>
-      <c r="AC3" s="429" t="n"/>
-      <c r="AD3" s="430" t="n"/>
-      <c r="AE3" s="431" t="n"/>
-      <c r="AF3" s="432" t="n"/>
-      <c r="AG3" s="432" t="n"/>
-      <c r="AH3" s="433" t="n"/>
-      <c r="AI3" s="434" t="n"/>
-      <c r="AJ3" s="435" t="n"/>
-      <c r="AK3" s="435" t="n"/>
-      <c r="AL3" s="435" t="n"/>
-      <c r="AM3" s="435" t="n"/>
-      <c r="AN3" s="436" t="n"/>
+      <c r="A3" s="533" t="n"/>
+      <c r="H3" s="534" t="n"/>
+      <c r="I3" s="533" t="n"/>
+      <c r="AD3" s="534" t="n"/>
+      <c r="AE3" s="535" t="n"/>
+      <c r="AF3" s="408" t="n"/>
+      <c r="AG3" s="408" t="n"/>
+      <c r="AH3" s="536" t="n"/>
+      <c r="AI3" s="537" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
+      <c r="AJ3" s="408" t="n"/>
+      <c r="AK3" s="408" t="n"/>
+      <c r="AL3" s="408" t="n"/>
+      <c r="AM3" s="408" t="n"/>
+      <c r="AN3" s="538" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1" s="329">
-      <c r="A4" s="503" t="inlineStr">
+      <c r="A4" s="533" t="n"/>
+      <c r="H4" s="534" t="n"/>
+      <c r="I4" s="539" t="inlineStr">
+        <is>
+          <t>Quality Management System · Controlled Document</t>
+        </is>
+      </c>
+      <c r="AD4" s="534" t="n"/>
+      <c r="AE4" s="535" t="n"/>
+      <c r="AF4" s="408" t="n"/>
+      <c r="AG4" s="408" t="n"/>
+      <c r="AH4" s="536" t="n"/>
+      <c r="AI4" s="537" t="inlineStr">
+        <is>
+          <t>Purchasing + QA</t>
+        </is>
+      </c>
+      <c r="AJ4" s="408" t="n"/>
+      <c r="AK4" s="408" t="n"/>
+      <c r="AL4" s="408" t="n"/>
+      <c r="AM4" s="408" t="n"/>
+      <c r="AN4" s="538" t="n"/>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="329">
+      <c r="A5" s="540" t="n"/>
+      <c r="B5" s="541" t="n"/>
+      <c r="C5" s="541" t="n"/>
+      <c r="D5" s="541" t="n"/>
+      <c r="E5" s="541" t="n"/>
+      <c r="F5" s="541" t="n"/>
+      <c r="G5" s="541" t="n"/>
+      <c r="H5" s="542" t="n"/>
+      <c r="I5" s="543" t="inlineStr">
+        <is>
+          <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
+        </is>
+      </c>
+      <c r="J5" s="541" t="n"/>
+      <c r="K5" s="541" t="n"/>
+      <c r="L5" s="541" t="n"/>
+      <c r="M5" s="541" t="n"/>
+      <c r="N5" s="541" t="n"/>
+      <c r="O5" s="541" t="n"/>
+      <c r="P5" s="541" t="n"/>
+      <c r="Q5" s="541" t="n"/>
+      <c r="R5" s="541" t="n"/>
+      <c r="S5" s="541" t="n"/>
+      <c r="T5" s="541" t="n"/>
+      <c r="U5" s="541" t="n"/>
+      <c r="V5" s="541" t="n"/>
+      <c r="W5" s="541" t="n"/>
+      <c r="X5" s="541" t="n"/>
+      <c r="Y5" s="541" t="n"/>
+      <c r="Z5" s="541" t="n"/>
+      <c r="AA5" s="541" t="n"/>
+      <c r="AB5" s="541" t="n"/>
+      <c r="AC5" s="541" t="n"/>
+      <c r="AD5" s="542" t="n"/>
+      <c r="AE5" s="544" t="n"/>
+      <c r="AF5" s="545" t="n"/>
+      <c r="AG5" s="545" t="n"/>
+      <c r="AH5" s="546" t="n"/>
+      <c r="AI5" s="547" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="AJ5" s="545" t="n"/>
+      <c r="AK5" s="545" t="n"/>
+      <c r="AL5" s="545" t="n"/>
+      <c r="AM5" s="545" t="n"/>
+      <c r="AN5" s="548" t="n"/>
+    </row>
+    <row r="6" ht="1.5" customHeight="1" s="329">
+      <c r="A6" s="612" t="n"/>
+      <c r="B6" s="612" t="n"/>
+      <c r="C6" s="612" t="n"/>
+      <c r="D6" s="612" t="n"/>
+      <c r="E6" s="612" t="n"/>
+      <c r="F6" s="612" t="n"/>
+      <c r="G6" s="612" t="n"/>
+      <c r="H6" s="612" t="n"/>
+      <c r="I6" s="612" t="n"/>
+      <c r="J6" s="612" t="n"/>
+      <c r="K6" s="612" t="n"/>
+      <c r="L6" s="612" t="n"/>
+      <c r="M6" s="612" t="n"/>
+      <c r="N6" s="612" t="n"/>
+      <c r="O6" s="612" t="n"/>
+      <c r="P6" s="612" t="n"/>
+      <c r="Q6" s="612" t="n"/>
+      <c r="R6" s="612" t="n"/>
+      <c r="S6" s="612" t="n"/>
+      <c r="T6" s="612" t="n"/>
+      <c r="U6" s="612" t="n"/>
+      <c r="V6" s="612" t="n"/>
+      <c r="W6" s="612" t="n"/>
+      <c r="X6" s="612" t="n"/>
+      <c r="Y6" s="612" t="n"/>
+      <c r="Z6" s="612" t="n"/>
+      <c r="AA6" s="612" t="n"/>
+      <c r="AB6" s="612" t="n"/>
+      <c r="AC6" s="612" t="n"/>
+      <c r="AD6" s="612" t="n"/>
+      <c r="AE6" s="612" t="n"/>
+      <c r="AF6" s="612" t="n"/>
+      <c r="AG6" s="612" t="n"/>
+      <c r="AH6" s="612" t="n"/>
+      <c r="AI6" s="612" t="n"/>
+      <c r="AJ6" s="612" t="n"/>
+      <c r="AK6" s="612" t="n"/>
+      <c r="AL6" s="612" t="n"/>
+      <c r="AM6" s="612" t="n"/>
+      <c r="AN6" s="612" t="n"/>
+    </row>
+    <row r="7" ht="18" customHeight="1" s="329">
+      <c r="A7" s="549" t="inlineStr">
+        <is>
+          <t>ACTION TRACKER</t>
+        </is>
+      </c>
+      <c r="B7" s="550" t="n"/>
+      <c r="C7" s="550" t="n"/>
+      <c r="D7" s="550" t="n"/>
+      <c r="E7" s="550" t="n"/>
+      <c r="F7" s="550" t="n"/>
+      <c r="G7" s="550" t="n"/>
+      <c r="H7" s="550" t="n"/>
+      <c r="I7" s="550" t="n"/>
+      <c r="J7" s="550" t="n"/>
+      <c r="K7" s="550" t="n"/>
+      <c r="L7" s="550" t="n"/>
+      <c r="M7" s="550" t="n"/>
+      <c r="N7" s="550" t="n"/>
+      <c r="O7" s="550" t="n"/>
+      <c r="P7" s="550" t="n"/>
+      <c r="Q7" s="550" t="n"/>
+      <c r="R7" s="550" t="n"/>
+      <c r="S7" s="550" t="n"/>
+      <c r="T7" s="550" t="n"/>
+      <c r="U7" s="550" t="n"/>
+      <c r="V7" s="550" t="n"/>
+      <c r="W7" s="550" t="n"/>
+      <c r="X7" s="550" t="n"/>
+      <c r="Y7" s="550" t="n"/>
+      <c r="Z7" s="550" t="n"/>
+      <c r="AA7" s="550" t="n"/>
+      <c r="AB7" s="550" t="n"/>
+      <c r="AC7" s="550" t="n"/>
+      <c r="AD7" s="550" t="n"/>
+      <c r="AE7" s="550" t="n"/>
+      <c r="AF7" s="550" t="n"/>
+      <c r="AG7" s="550" t="n"/>
+      <c r="AH7" s="550" t="n"/>
+      <c r="AI7" s="550" t="n"/>
+      <c r="AJ7" s="550" t="n"/>
+      <c r="AK7" s="550" t="n"/>
+      <c r="AL7" s="550" t="n"/>
+      <c r="AM7" s="550" t="n"/>
+      <c r="AN7" s="551" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1" s="329">
+      <c r="A8" s="599" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="504" t="inlineStr">
+      <c r="B8" s="600" t="n"/>
+      <c r="C8" s="601" t="inlineStr">
         <is>
-          <t>Issue / Finding</t>
+          <t>Issue / Requirement</t>
         </is>
       </c>
-      <c r="C4" s="504" t="inlineStr">
+      <c r="D8" s="550" t="n"/>
+      <c r="E8" s="550" t="n"/>
+      <c r="F8" s="550" t="n"/>
+      <c r="G8" s="550" t="n"/>
+      <c r="H8" s="550" t="n"/>
+      <c r="I8" s="550" t="n"/>
+      <c r="J8" s="550" t="n"/>
+      <c r="K8" s="550" t="n"/>
+      <c r="L8" s="600" t="n"/>
+      <c r="M8" s="601" t="inlineStr">
         <is>
           <t>Required Action</t>
         </is>
       </c>
-      <c r="D4" s="504" t="inlineStr">
+      <c r="N8" s="550" t="n"/>
+      <c r="O8" s="550" t="n"/>
+      <c r="P8" s="550" t="n"/>
+      <c r="Q8" s="550" t="n"/>
+      <c r="R8" s="550" t="n"/>
+      <c r="S8" s="550" t="n"/>
+      <c r="T8" s="550" t="n"/>
+      <c r="U8" s="550" t="n"/>
+      <c r="V8" s="550" t="n"/>
+      <c r="W8" s="550" t="n"/>
+      <c r="X8" s="600" t="n"/>
+      <c r="Y8" s="601" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E4" s="504" t="inlineStr">
+      <c r="Z8" s="550" t="n"/>
+      <c r="AA8" s="550" t="n"/>
+      <c r="AB8" s="550" t="n"/>
+      <c r="AC8" s="600" t="n"/>
+      <c r="AD8" s="601" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="F4" s="504" t="inlineStr">
+      <c r="AE8" s="550" t="n"/>
+      <c r="AF8" s="550" t="n"/>
+      <c r="AG8" s="550" t="n"/>
+      <c r="AH8" s="600" t="n"/>
+      <c r="AI8" s="601" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G4" s="504" t="inlineStr">
+      <c r="AJ8" s="550" t="n"/>
+      <c r="AK8" s="600" t="n"/>
+      <c r="AL8" s="602" t="inlineStr">
         <is>
-          <t>Evidence Ref</t>
+          <t>Verified by</t>
         </is>
       </c>
-      <c r="H4" s="505" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="I4" s="437" t="n"/>
-      <c r="J4" s="438" t="n"/>
-      <c r="K4" s="438" t="n"/>
-      <c r="L4" s="438" t="n"/>
-      <c r="M4" s="438" t="n"/>
-      <c r="N4" s="438" t="n"/>
-      <c r="O4" s="438" t="n"/>
-      <c r="P4" s="438" t="n"/>
-      <c r="Q4" s="438" t="n"/>
-      <c r="R4" s="438" t="n"/>
-      <c r="S4" s="438" t="n"/>
-      <c r="T4" s="438" t="n"/>
-      <c r="U4" s="438" t="n"/>
-      <c r="V4" s="438" t="n"/>
-      <c r="W4" s="438" t="n"/>
-      <c r="X4" s="438" t="n"/>
-      <c r="Y4" s="438" t="n"/>
-      <c r="Z4" s="438" t="n"/>
-      <c r="AA4" s="438" t="n"/>
-      <c r="AB4" s="438" t="n"/>
-      <c r="AC4" s="438" t="n"/>
-      <c r="AD4" s="439" t="n"/>
-      <c r="AE4" s="431" t="n"/>
-      <c r="AF4" s="432" t="n"/>
-      <c r="AG4" s="432" t="n"/>
-      <c r="AH4" s="433" t="n"/>
-      <c r="AI4" s="434" t="n"/>
-      <c r="AJ4" s="435" t="n"/>
-      <c r="AK4" s="435" t="n"/>
-      <c r="AL4" s="435" t="n"/>
-      <c r="AM4" s="435" t="n"/>
-      <c r="AN4" s="436" t="n"/>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="329">
-      <c r="A5" s="506">
-        <f>ROW()-ROW($A$5)+1</f>
-        <v/>
-      </c>
-      <c r="B5" s="507" t="n"/>
-      <c r="C5" s="507" t="n"/>
-      <c r="D5" s="507" t="n"/>
-      <c r="E5" s="507" t="n"/>
-      <c r="F5" s="507" t="n"/>
-      <c r="G5" s="507" t="n"/>
-      <c r="H5" s="508" t="n"/>
-      <c r="I5" s="443" t="n"/>
-      <c r="J5" s="444" t="n"/>
-      <c r="K5" s="444" t="n"/>
-      <c r="L5" s="444" t="n"/>
-      <c r="M5" s="444" t="n"/>
-      <c r="N5" s="444" t="n"/>
-      <c r="O5" s="444" t="n"/>
-      <c r="P5" s="444" t="n"/>
-      <c r="Q5" s="444" t="n"/>
-      <c r="R5" s="444" t="n"/>
-      <c r="S5" s="444" t="n"/>
-      <c r="T5" s="444" t="n"/>
-      <c r="U5" s="444" t="n"/>
-      <c r="V5" s="444" t="n"/>
-      <c r="W5" s="444" t="n"/>
-      <c r="X5" s="444" t="n"/>
-      <c r="Y5" s="444" t="n"/>
-      <c r="Z5" s="444" t="n"/>
-      <c r="AA5" s="444" t="n"/>
-      <c r="AB5" s="444" t="n"/>
-      <c r="AC5" s="444" t="n"/>
-      <c r="AD5" s="445" t="n"/>
-      <c r="AE5" s="446" t="n"/>
-      <c r="AF5" s="447" t="n"/>
-      <c r="AG5" s="447" t="n"/>
-      <c r="AH5" s="448" t="n"/>
-      <c r="AI5" s="449" t="n"/>
-      <c r="AJ5" s="450" t="n"/>
-      <c r="AK5" s="450" t="n"/>
-      <c r="AL5" s="450" t="n"/>
-      <c r="AM5" s="450" t="n"/>
-      <c r="AN5" s="451" t="n"/>
-    </row>
-    <row r="6" ht="20" customHeight="1" s="329">
-      <c r="A6" s="509">
-        <f>ROW()-ROW($A$5)+1</f>
-        <v/>
-      </c>
-      <c r="B6" s="510" t="n"/>
-      <c r="C6" s="511" t="n"/>
-      <c r="D6" s="511" t="n"/>
-      <c r="E6" s="511" t="n"/>
-      <c r="F6" s="511" t="n"/>
-      <c r="G6" s="511" t="n"/>
-      <c r="H6" s="511" t="n"/>
-      <c r="I6" s="457" t="n"/>
-      <c r="J6" s="457" t="n"/>
-      <c r="K6" s="457" t="n"/>
-      <c r="L6" s="457" t="n"/>
-      <c r="M6" s="457" t="n"/>
-      <c r="N6" s="457" t="n"/>
-      <c r="O6" s="457" t="n"/>
-      <c r="P6" s="457" t="n"/>
-      <c r="Q6" s="457" t="n"/>
-      <c r="R6" s="457" t="n"/>
-      <c r="S6" s="457" t="n"/>
-      <c r="T6" s="457" t="n"/>
-      <c r="U6" s="457" t="n"/>
-      <c r="V6" s="457" t="n"/>
-      <c r="W6" s="457" t="n"/>
-      <c r="X6" s="457" t="n"/>
-      <c r="Y6" s="457" t="n"/>
-      <c r="Z6" s="457" t="n"/>
-      <c r="AA6" s="457" t="n"/>
-      <c r="AB6" s="457" t="n"/>
-      <c r="AC6" s="457" t="n"/>
-      <c r="AD6" s="457" t="n"/>
-      <c r="AE6" s="457" t="n"/>
-      <c r="AF6" s="457" t="n"/>
-      <c r="AG6" s="457" t="n"/>
-      <c r="AH6" s="457" t="n"/>
-      <c r="AI6" s="457" t="n"/>
-      <c r="AJ6" s="457" t="n"/>
-      <c r="AK6" s="457" t="n"/>
-      <c r="AL6" s="457" t="n"/>
-      <c r="AM6" s="457" t="n"/>
-      <c r="AN6" s="460" t="n"/>
-    </row>
-    <row r="7" ht="20" customHeight="1" s="329">
-      <c r="A7" s="512">
-        <f>ROW()-ROW($A$5)+1</f>
-        <v/>
-      </c>
-      <c r="B7" s="513" t="n"/>
-      <c r="C7" s="514" t="n"/>
-      <c r="D7" s="514" t="n"/>
-      <c r="E7" s="514" t="n"/>
-      <c r="F7" s="514" t="n"/>
-      <c r="G7" s="514" t="n"/>
-      <c r="H7" s="514" t="n"/>
-      <c r="I7" s="341" t="n"/>
-      <c r="J7" s="341" t="n"/>
-      <c r="K7" s="341" t="n"/>
-      <c r="L7" s="341" t="n"/>
-      <c r="M7" s="341" t="n"/>
-      <c r="N7" s="341" t="n"/>
-      <c r="O7" s="341" t="n"/>
-      <c r="P7" s="341" t="n"/>
-      <c r="Q7" s="341" t="n"/>
-      <c r="R7" s="341" t="n"/>
-      <c r="S7" s="341" t="n"/>
-      <c r="T7" s="341" t="n"/>
-      <c r="U7" s="341" t="n"/>
-      <c r="V7" s="341" t="n"/>
-      <c r="W7" s="341" t="n"/>
-      <c r="X7" s="341" t="n"/>
-      <c r="Y7" s="341" t="n"/>
-      <c r="Z7" s="341" t="n"/>
-      <c r="AA7" s="341" t="n"/>
-      <c r="AB7" s="341" t="n"/>
-      <c r="AC7" s="341" t="n"/>
-      <c r="AD7" s="341" t="n"/>
-      <c r="AE7" s="341" t="n"/>
-      <c r="AF7" s="341" t="n"/>
-      <c r="AG7" s="341" t="n"/>
-      <c r="AH7" s="341" t="n"/>
-      <c r="AI7" s="341" t="n"/>
-      <c r="AJ7" s="341" t="n"/>
-      <c r="AK7" s="341" t="n"/>
-      <c r="AL7" s="341" t="n"/>
-      <c r="AM7" s="341" t="n"/>
-      <c r="AN7" s="464" t="n"/>
-    </row>
-    <row r="8" ht="20" customHeight="1" s="329">
-      <c r="A8" s="461">
-        <f>ROW()-ROW($A$5)+1</f>
-        <v/>
-      </c>
-      <c r="B8" s="462" t="n"/>
-      <c r="C8" s="515" t="n"/>
-      <c r="D8" s="515" t="n"/>
-      <c r="E8" s="515" t="n"/>
-      <c r="F8" s="515" t="n"/>
-      <c r="G8" s="515" t="n"/>
-      <c r="H8" s="515" t="n"/>
-      <c r="I8" s="353" t="n"/>
-      <c r="J8" s="353" t="n"/>
-      <c r="K8" s="353" t="n"/>
-      <c r="L8" s="353" t="n"/>
-      <c r="M8" s="353" t="n"/>
-      <c r="N8" s="353" t="n"/>
-      <c r="O8" s="353" t="n"/>
-      <c r="P8" s="353" t="n"/>
-      <c r="Q8" s="353" t="n"/>
-      <c r="R8" s="353" t="n"/>
-      <c r="S8" s="353" t="n"/>
-      <c r="T8" s="353" t="n"/>
-      <c r="U8" s="353" t="n"/>
-      <c r="V8" s="353" t="n"/>
-      <c r="W8" s="353" t="n"/>
-      <c r="X8" s="353" t="n"/>
-      <c r="Y8" s="353" t="n"/>
-      <c r="Z8" s="353" t="n"/>
-      <c r="AA8" s="353" t="n"/>
-      <c r="AB8" s="353" t="n"/>
-      <c r="AC8" s="353" t="n"/>
-      <c r="AD8" s="353" t="n"/>
-      <c r="AE8" s="353" t="n"/>
-      <c r="AF8" s="353" t="n"/>
-      <c r="AG8" s="353" t="n"/>
-      <c r="AH8" s="353" t="n"/>
-      <c r="AI8" s="353" t="n"/>
-      <c r="AJ8" s="353" t="n"/>
-      <c r="AK8" s="353" t="n"/>
-      <c r="AL8" s="353" t="n"/>
-      <c r="AM8" s="353" t="n"/>
-      <c r="AN8" s="516" t="n"/>
+      <c r="AM8" s="550" t="n"/>
+      <c r="AN8" s="551" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1" s="329">
-      <c r="A9" s="461">
-        <f>ROW()-ROW($A$5)+1</f>
+      <c r="A9" s="617">
+        <f>ROW()-ROW($A$9)+1</f>
         <v/>
       </c>
-      <c r="B9" s="462" t="n"/>
-      <c r="C9" s="515" t="n"/>
-      <c r="D9" s="515" t="n"/>
-      <c r="E9" s="515" t="n"/>
-      <c r="F9" s="515" t="n"/>
-      <c r="G9" s="515" t="n"/>
-      <c r="H9" s="515" t="n"/>
-      <c r="I9" s="353" t="n"/>
-      <c r="J9" s="353" t="n"/>
-      <c r="K9" s="353" t="n"/>
-      <c r="L9" s="353" t="n"/>
-      <c r="M9" s="353" t="n"/>
-      <c r="N9" s="353" t="n"/>
-      <c r="O9" s="353" t="n"/>
-      <c r="P9" s="353" t="n"/>
-      <c r="Q9" s="353" t="n"/>
-      <c r="R9" s="353" t="n"/>
-      <c r="S9" s="353" t="n"/>
-      <c r="T9" s="353" t="n"/>
-      <c r="U9" s="353" t="n"/>
-      <c r="V9" s="353" t="n"/>
-      <c r="W9" s="353" t="n"/>
-      <c r="X9" s="353" t="n"/>
-      <c r="Y9" s="353" t="n"/>
-      <c r="Z9" s="353" t="n"/>
-      <c r="AA9" s="353" t="n"/>
-      <c r="AB9" s="353" t="n"/>
-      <c r="AC9" s="353" t="n"/>
-      <c r="AD9" s="353" t="n"/>
-      <c r="AE9" s="353" t="n"/>
-      <c r="AF9" s="353" t="n"/>
-      <c r="AG9" s="353" t="n"/>
-      <c r="AH9" s="353" t="n"/>
-      <c r="AI9" s="353" t="n"/>
-      <c r="AJ9" s="353" t="n"/>
-      <c r="AK9" s="353" t="n"/>
-      <c r="AL9" s="353" t="n"/>
-      <c r="AM9" s="353" t="n"/>
-      <c r="AN9" s="516" t="n"/>
+      <c r="B9" s="410" t="n"/>
+      <c r="C9" s="604" t="n"/>
+      <c r="D9" s="409" t="n"/>
+      <c r="E9" s="409" t="n"/>
+      <c r="F9" s="409" t="n"/>
+      <c r="G9" s="409" t="n"/>
+      <c r="H9" s="409" t="n"/>
+      <c r="I9" s="409" t="n"/>
+      <c r="J9" s="409" t="n"/>
+      <c r="K9" s="409" t="n"/>
+      <c r="L9" s="410" t="n"/>
+      <c r="M9" s="604" t="n"/>
+      <c r="N9" s="409" t="n"/>
+      <c r="O9" s="409" t="n"/>
+      <c r="P9" s="409" t="n"/>
+      <c r="Q9" s="409" t="n"/>
+      <c r="R9" s="409" t="n"/>
+      <c r="S9" s="409" t="n"/>
+      <c r="T9" s="409" t="n"/>
+      <c r="U9" s="409" t="n"/>
+      <c r="V9" s="409" t="n"/>
+      <c r="W9" s="409" t="n"/>
+      <c r="X9" s="410" t="n"/>
+      <c r="Y9" s="604" t="n"/>
+      <c r="Z9" s="409" t="n"/>
+      <c r="AA9" s="409" t="n"/>
+      <c r="AB9" s="409" t="n"/>
+      <c r="AC9" s="410" t="n"/>
+      <c r="AD9" s="604" t="n"/>
+      <c r="AE9" s="409" t="n"/>
+      <c r="AF9" s="409" t="n"/>
+      <c r="AG9" s="409" t="n"/>
+      <c r="AH9" s="410" t="n"/>
+      <c r="AI9" s="604" t="n"/>
+      <c r="AJ9" s="409" t="n"/>
+      <c r="AK9" s="410" t="n"/>
+      <c r="AL9" s="605" t="n"/>
+      <c r="AM9" s="409" t="n"/>
+      <c r="AN9" s="556" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1" s="329">
-      <c r="A10" s="461">
-        <f>ROW()-ROW($A$5)+1</f>
+      <c r="A10" s="618">
+        <f>ROW()-ROW($A$9)+1</f>
         <v/>
       </c>
-      <c r="B10" s="462" t="n"/>
-      <c r="C10" s="515" t="n"/>
-      <c r="D10" s="515" t="n"/>
-      <c r="E10" s="515" t="n"/>
-      <c r="F10" s="515" t="n"/>
-      <c r="G10" s="515" t="n"/>
-      <c r="H10" s="515" t="n"/>
-      <c r="I10" s="353" t="n"/>
-      <c r="J10" s="353" t="n"/>
-      <c r="K10" s="353" t="n"/>
-      <c r="L10" s="353" t="n"/>
-      <c r="M10" s="353" t="n"/>
-      <c r="N10" s="353" t="n"/>
-      <c r="O10" s="353" t="n"/>
-      <c r="P10" s="353" t="n"/>
-      <c r="Q10" s="353" t="n"/>
-      <c r="R10" s="353" t="n"/>
-      <c r="S10" s="353" t="n"/>
-      <c r="T10" s="353" t="n"/>
-      <c r="U10" s="353" t="n"/>
-      <c r="V10" s="353" t="n"/>
-      <c r="W10" s="353" t="n"/>
-      <c r="X10" s="353" t="n"/>
-      <c r="Y10" s="353" t="n"/>
-      <c r="Z10" s="353" t="n"/>
-      <c r="AA10" s="353" t="n"/>
-      <c r="AB10" s="353" t="n"/>
-      <c r="AC10" s="353" t="n"/>
-      <c r="AD10" s="353" t="n"/>
-      <c r="AE10" s="353" t="n"/>
-      <c r="AF10" s="353" t="n"/>
-      <c r="AG10" s="353" t="n"/>
-      <c r="AH10" s="353" t="n"/>
-      <c r="AI10" s="353" t="n"/>
-      <c r="AJ10" s="353" t="n"/>
-      <c r="AK10" s="353" t="n"/>
-      <c r="AL10" s="353" t="n"/>
-      <c r="AM10" s="353" t="n"/>
-      <c r="AN10" s="516" t="n"/>
+      <c r="B10" s="410" t="n"/>
+      <c r="C10" s="607" t="n"/>
+      <c r="D10" s="409" t="n"/>
+      <c r="E10" s="409" t="n"/>
+      <c r="F10" s="409" t="n"/>
+      <c r="G10" s="409" t="n"/>
+      <c r="H10" s="409" t="n"/>
+      <c r="I10" s="409" t="n"/>
+      <c r="J10" s="409" t="n"/>
+      <c r="K10" s="409" t="n"/>
+      <c r="L10" s="410" t="n"/>
+      <c r="M10" s="607" t="n"/>
+      <c r="N10" s="409" t="n"/>
+      <c r="O10" s="409" t="n"/>
+      <c r="P10" s="409" t="n"/>
+      <c r="Q10" s="409" t="n"/>
+      <c r="R10" s="409" t="n"/>
+      <c r="S10" s="409" t="n"/>
+      <c r="T10" s="409" t="n"/>
+      <c r="U10" s="409" t="n"/>
+      <c r="V10" s="409" t="n"/>
+      <c r="W10" s="409" t="n"/>
+      <c r="X10" s="410" t="n"/>
+      <c r="Y10" s="607" t="n"/>
+      <c r="Z10" s="409" t="n"/>
+      <c r="AA10" s="409" t="n"/>
+      <c r="AB10" s="409" t="n"/>
+      <c r="AC10" s="410" t="n"/>
+      <c r="AD10" s="607" t="n"/>
+      <c r="AE10" s="409" t="n"/>
+      <c r="AF10" s="409" t="n"/>
+      <c r="AG10" s="409" t="n"/>
+      <c r="AH10" s="410" t="n"/>
+      <c r="AI10" s="607" t="n"/>
+      <c r="AJ10" s="409" t="n"/>
+      <c r="AK10" s="410" t="n"/>
+      <c r="AL10" s="608" t="n"/>
+      <c r="AM10" s="409" t="n"/>
+      <c r="AN10" s="556" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1" s="329">
-      <c r="A11" s="461">
-        <f>ROW()-ROW($A$5)+1</f>
+      <c r="A11" s="617">
+        <f>ROW()-ROW($A$9)+1</f>
         <v/>
       </c>
-      <c r="B11" s="462" t="n"/>
-      <c r="C11" s="515" t="n"/>
-      <c r="D11" s="515" t="n"/>
-      <c r="E11" s="515" t="n"/>
-      <c r="F11" s="515" t="n"/>
-      <c r="G11" s="515" t="n"/>
-      <c r="H11" s="515" t="n"/>
-      <c r="I11" s="353" t="n"/>
-      <c r="J11" s="353" t="n"/>
-      <c r="K11" s="353" t="n"/>
-      <c r="L11" s="353" t="n"/>
-      <c r="M11" s="353" t="n"/>
-      <c r="N11" s="353" t="n"/>
-      <c r="O11" s="353" t="n"/>
-      <c r="P11" s="353" t="n"/>
-      <c r="Q11" s="353" t="n"/>
-      <c r="R11" s="353" t="n"/>
-      <c r="S11" s="353" t="n"/>
-      <c r="T11" s="353" t="n"/>
-      <c r="U11" s="353" t="n"/>
-      <c r="V11" s="353" t="n"/>
-      <c r="W11" s="353" t="n"/>
-      <c r="X11" s="353" t="n"/>
-      <c r="Y11" s="353" t="n"/>
-      <c r="Z11" s="353" t="n"/>
-      <c r="AA11" s="353" t="n"/>
-      <c r="AB11" s="353" t="n"/>
-      <c r="AC11" s="353" t="n"/>
-      <c r="AD11" s="353" t="n"/>
-      <c r="AE11" s="353" t="n"/>
-      <c r="AF11" s="353" t="n"/>
-      <c r="AG11" s="353" t="n"/>
-      <c r="AH11" s="353" t="n"/>
-      <c r="AI11" s="353" t="n"/>
-      <c r="AJ11" s="353" t="n"/>
-      <c r="AK11" s="353" t="n"/>
-      <c r="AL11" s="353" t="n"/>
-      <c r="AM11" s="353" t="n"/>
-      <c r="AN11" s="516" t="n"/>
+      <c r="B11" s="410" t="n"/>
+      <c r="C11" s="604" t="n"/>
+      <c r="D11" s="409" t="n"/>
+      <c r="E11" s="409" t="n"/>
+      <c r="F11" s="409" t="n"/>
+      <c r="G11" s="409" t="n"/>
+      <c r="H11" s="409" t="n"/>
+      <c r="I11" s="409" t="n"/>
+      <c r="J11" s="409" t="n"/>
+      <c r="K11" s="409" t="n"/>
+      <c r="L11" s="410" t="n"/>
+      <c r="M11" s="604" t="n"/>
+      <c r="N11" s="409" t="n"/>
+      <c r="O11" s="409" t="n"/>
+      <c r="P11" s="409" t="n"/>
+      <c r="Q11" s="409" t="n"/>
+      <c r="R11" s="409" t="n"/>
+      <c r="S11" s="409" t="n"/>
+      <c r="T11" s="409" t="n"/>
+      <c r="U11" s="409" t="n"/>
+      <c r="V11" s="409" t="n"/>
+      <c r="W11" s="409" t="n"/>
+      <c r="X11" s="410" t="n"/>
+      <c r="Y11" s="604" t="n"/>
+      <c r="Z11" s="409" t="n"/>
+      <c r="AA11" s="409" t="n"/>
+      <c r="AB11" s="409" t="n"/>
+      <c r="AC11" s="410" t="n"/>
+      <c r="AD11" s="604" t="n"/>
+      <c r="AE11" s="409" t="n"/>
+      <c r="AF11" s="409" t="n"/>
+      <c r="AG11" s="409" t="n"/>
+      <c r="AH11" s="410" t="n"/>
+      <c r="AI11" s="604" t="n"/>
+      <c r="AJ11" s="409" t="n"/>
+      <c r="AK11" s="410" t="n"/>
+      <c r="AL11" s="605" t="n"/>
+      <c r="AM11" s="409" t="n"/>
+      <c r="AN11" s="556" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1" s="329">
-      <c r="A12" s="461">
-        <f>ROW()-ROW($A$5)+1</f>
+      <c r="A12" s="618">
+        <f>ROW()-ROW($A$9)+1</f>
         <v/>
       </c>
-      <c r="B12" s="462" t="n"/>
-      <c r="C12" s="515" t="n"/>
-      <c r="D12" s="515" t="n"/>
-      <c r="E12" s="515" t="n"/>
-      <c r="F12" s="515" t="n"/>
-      <c r="G12" s="515" t="n"/>
-      <c r="H12" s="515" t="n"/>
-      <c r="I12" s="353" t="n"/>
-      <c r="J12" s="353" t="n"/>
-      <c r="K12" s="353" t="n"/>
-      <c r="L12" s="353" t="n"/>
-      <c r="M12" s="353" t="n"/>
-      <c r="N12" s="353" t="n"/>
-      <c r="O12" s="353" t="n"/>
-      <c r="P12" s="353" t="n"/>
-      <c r="Q12" s="353" t="n"/>
-      <c r="R12" s="353" t="n"/>
-      <c r="S12" s="353" t="n"/>
-      <c r="T12" s="353" t="n"/>
-      <c r="U12" s="353" t="n"/>
-      <c r="V12" s="353" t="n"/>
-      <c r="W12" s="353" t="n"/>
-      <c r="X12" s="353" t="n"/>
-      <c r="Y12" s="353" t="n"/>
-      <c r="Z12" s="353" t="n"/>
-      <c r="AA12" s="353" t="n"/>
-      <c r="AB12" s="353" t="n"/>
-      <c r="AC12" s="353" t="n"/>
-      <c r="AD12" s="353" t="n"/>
-      <c r="AE12" s="353" t="n"/>
-      <c r="AF12" s="353" t="n"/>
-      <c r="AG12" s="353" t="n"/>
-      <c r="AH12" s="353" t="n"/>
-      <c r="AI12" s="353" t="n"/>
-      <c r="AJ12" s="353" t="n"/>
-      <c r="AK12" s="353" t="n"/>
-      <c r="AL12" s="353" t="n"/>
-      <c r="AM12" s="353" t="n"/>
-      <c r="AN12" s="516" t="n"/>
+      <c r="B12" s="410" t="n"/>
+      <c r="C12" s="607" t="n"/>
+      <c r="D12" s="409" t="n"/>
+      <c r="E12" s="409" t="n"/>
+      <c r="F12" s="409" t="n"/>
+      <c r="G12" s="409" t="n"/>
+      <c r="H12" s="409" t="n"/>
+      <c r="I12" s="409" t="n"/>
+      <c r="J12" s="409" t="n"/>
+      <c r="K12" s="409" t="n"/>
+      <c r="L12" s="410" t="n"/>
+      <c r="M12" s="607" t="n"/>
+      <c r="N12" s="409" t="n"/>
+      <c r="O12" s="409" t="n"/>
+      <c r="P12" s="409" t="n"/>
+      <c r="Q12" s="409" t="n"/>
+      <c r="R12" s="409" t="n"/>
+      <c r="S12" s="409" t="n"/>
+      <c r="T12" s="409" t="n"/>
+      <c r="U12" s="409" t="n"/>
+      <c r="V12" s="409" t="n"/>
+      <c r="W12" s="409" t="n"/>
+      <c r="X12" s="410" t="n"/>
+      <c r="Y12" s="607" t="n"/>
+      <c r="Z12" s="409" t="n"/>
+      <c r="AA12" s="409" t="n"/>
+      <c r="AB12" s="409" t="n"/>
+      <c r="AC12" s="410" t="n"/>
+      <c r="AD12" s="607" t="n"/>
+      <c r="AE12" s="409" t="n"/>
+      <c r="AF12" s="409" t="n"/>
+      <c r="AG12" s="409" t="n"/>
+      <c r="AH12" s="410" t="n"/>
+      <c r="AI12" s="607" t="n"/>
+      <c r="AJ12" s="409" t="n"/>
+      <c r="AK12" s="410" t="n"/>
+      <c r="AL12" s="608" t="n"/>
+      <c r="AM12" s="409" t="n"/>
+      <c r="AN12" s="556" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1" s="329">
-      <c r="A13" s="461">
-        <f>ROW()-ROW($A$5)+1</f>
+      <c r="A13" s="617">
+        <f>ROW()-ROW($A$9)+1</f>
         <v/>
       </c>
-      <c r="B13" s="462" t="n"/>
-      <c r="C13" s="515" t="n"/>
-      <c r="D13" s="515" t="n"/>
-      <c r="E13" s="515" t="n"/>
-      <c r="F13" s="515" t="n"/>
-      <c r="G13" s="515" t="n"/>
-      <c r="H13" s="515" t="n"/>
-      <c r="I13" s="353" t="n"/>
-      <c r="J13" s="353" t="n"/>
-      <c r="K13" s="353" t="n"/>
-      <c r="L13" s="353" t="n"/>
-      <c r="M13" s="353" t="n"/>
-      <c r="N13" s="353" t="n"/>
-      <c r="O13" s="353" t="n"/>
-      <c r="P13" s="353" t="n"/>
-      <c r="Q13" s="353" t="n"/>
-      <c r="R13" s="353" t="n"/>
-      <c r="S13" s="353" t="n"/>
-      <c r="T13" s="353" t="n"/>
-      <c r="U13" s="353" t="n"/>
-      <c r="V13" s="353" t="n"/>
-      <c r="W13" s="353" t="n"/>
-      <c r="X13" s="353" t="n"/>
-      <c r="Y13" s="353" t="n"/>
-      <c r="Z13" s="353" t="n"/>
-      <c r="AA13" s="353" t="n"/>
-      <c r="AB13" s="353" t="n"/>
-      <c r="AC13" s="353" t="n"/>
-      <c r="AD13" s="353" t="n"/>
-      <c r="AE13" s="353" t="n"/>
-      <c r="AF13" s="353" t="n"/>
-      <c r="AG13" s="353" t="n"/>
-      <c r="AH13" s="353" t="n"/>
-      <c r="AI13" s="353" t="n"/>
-      <c r="AJ13" s="353" t="n"/>
-      <c r="AK13" s="353" t="n"/>
-      <c r="AL13" s="353" t="n"/>
-      <c r="AM13" s="353" t="n"/>
-      <c r="AN13" s="516" t="n"/>
+      <c r="B13" s="410" t="n"/>
+      <c r="C13" s="604" t="n"/>
+      <c r="D13" s="409" t="n"/>
+      <c r="E13" s="409" t="n"/>
+      <c r="F13" s="409" t="n"/>
+      <c r="G13" s="409" t="n"/>
+      <c r="H13" s="409" t="n"/>
+      <c r="I13" s="409" t="n"/>
+      <c r="J13" s="409" t="n"/>
+      <c r="K13" s="409" t="n"/>
+      <c r="L13" s="410" t="n"/>
+      <c r="M13" s="604" t="n"/>
+      <c r="N13" s="409" t="n"/>
+      <c r="O13" s="409" t="n"/>
+      <c r="P13" s="409" t="n"/>
+      <c r="Q13" s="409" t="n"/>
+      <c r="R13" s="409" t="n"/>
+      <c r="S13" s="409" t="n"/>
+      <c r="T13" s="409" t="n"/>
+      <c r="U13" s="409" t="n"/>
+      <c r="V13" s="409" t="n"/>
+      <c r="W13" s="409" t="n"/>
+      <c r="X13" s="410" t="n"/>
+      <c r="Y13" s="604" t="n"/>
+      <c r="Z13" s="409" t="n"/>
+      <c r="AA13" s="409" t="n"/>
+      <c r="AB13" s="409" t="n"/>
+      <c r="AC13" s="410" t="n"/>
+      <c r="AD13" s="604" t="n"/>
+      <c r="AE13" s="409" t="n"/>
+      <c r="AF13" s="409" t="n"/>
+      <c r="AG13" s="409" t="n"/>
+      <c r="AH13" s="410" t="n"/>
+      <c r="AI13" s="604" t="n"/>
+      <c r="AJ13" s="409" t="n"/>
+      <c r="AK13" s="410" t="n"/>
+      <c r="AL13" s="605" t="n"/>
+      <c r="AM13" s="409" t="n"/>
+      <c r="AN13" s="556" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1" s="329">
-      <c r="A14" s="461">
-        <f>ROW()-ROW($A$5)+1</f>
+      <c r="A14" s="618">
+        <f>ROW()-ROW($A$9)+1</f>
         <v/>
       </c>
-      <c r="B14" s="462" t="n"/>
-      <c r="C14" s="515" t="n"/>
-      <c r="D14" s="515" t="n"/>
-      <c r="E14" s="515" t="n"/>
-      <c r="F14" s="515" t="n"/>
-      <c r="G14" s="515" t="n"/>
-      <c r="H14" s="515" t="n"/>
-      <c r="I14" s="353" t="n"/>
-      <c r="J14" s="353" t="n"/>
-      <c r="K14" s="353" t="n"/>
-      <c r="L14" s="353" t="n"/>
-      <c r="M14" s="353" t="n"/>
-      <c r="N14" s="353" t="n"/>
-      <c r="O14" s="353" t="n"/>
-      <c r="P14" s="353" t="n"/>
-      <c r="Q14" s="353" t="n"/>
-      <c r="R14" s="353" t="n"/>
-      <c r="S14" s="353" t="n"/>
-      <c r="T14" s="353" t="n"/>
-      <c r="U14" s="353" t="n"/>
-      <c r="V14" s="353" t="n"/>
-      <c r="W14" s="353" t="n"/>
-      <c r="X14" s="353" t="n"/>
-      <c r="Y14" s="353" t="n"/>
-      <c r="Z14" s="353" t="n"/>
-      <c r="AA14" s="353" t="n"/>
-      <c r="AB14" s="353" t="n"/>
-      <c r="AC14" s="353" t="n"/>
-      <c r="AD14" s="353" t="n"/>
-      <c r="AE14" s="353" t="n"/>
-      <c r="AF14" s="353" t="n"/>
-      <c r="AG14" s="353" t="n"/>
-      <c r="AH14" s="353" t="n"/>
-      <c r="AI14" s="353" t="n"/>
-      <c r="AJ14" s="353" t="n"/>
-      <c r="AK14" s="353" t="n"/>
-      <c r="AL14" s="353" t="n"/>
-      <c r="AM14" s="353" t="n"/>
-      <c r="AN14" s="516" t="n"/>
+      <c r="B14" s="410" t="n"/>
+      <c r="C14" s="607" t="n"/>
+      <c r="D14" s="409" t="n"/>
+      <c r="E14" s="409" t="n"/>
+      <c r="F14" s="409" t="n"/>
+      <c r="G14" s="409" t="n"/>
+      <c r="H14" s="409" t="n"/>
+      <c r="I14" s="409" t="n"/>
+      <c r="J14" s="409" t="n"/>
+      <c r="K14" s="409" t="n"/>
+      <c r="L14" s="410" t="n"/>
+      <c r="M14" s="607" t="n"/>
+      <c r="N14" s="409" t="n"/>
+      <c r="O14" s="409" t="n"/>
+      <c r="P14" s="409" t="n"/>
+      <c r="Q14" s="409" t="n"/>
+      <c r="R14" s="409" t="n"/>
+      <c r="S14" s="409" t="n"/>
+      <c r="T14" s="409" t="n"/>
+      <c r="U14" s="409" t="n"/>
+      <c r="V14" s="409" t="n"/>
+      <c r="W14" s="409" t="n"/>
+      <c r="X14" s="410" t="n"/>
+      <c r="Y14" s="607" t="n"/>
+      <c r="Z14" s="409" t="n"/>
+      <c r="AA14" s="409" t="n"/>
+      <c r="AB14" s="409" t="n"/>
+      <c r="AC14" s="410" t="n"/>
+      <c r="AD14" s="607" t="n"/>
+      <c r="AE14" s="409" t="n"/>
+      <c r="AF14" s="409" t="n"/>
+      <c r="AG14" s="409" t="n"/>
+      <c r="AH14" s="410" t="n"/>
+      <c r="AI14" s="607" t="n"/>
+      <c r="AJ14" s="409" t="n"/>
+      <c r="AK14" s="410" t="n"/>
+      <c r="AL14" s="608" t="n"/>
+      <c r="AM14" s="409" t="n"/>
+      <c r="AN14" s="556" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1" s="329">
-      <c r="A15" s="461" t="n"/>
-      <c r="B15" s="462" t="n"/>
-      <c r="C15" s="515" t="n"/>
-      <c r="D15" s="515" t="n"/>
-      <c r="E15" s="515" t="n"/>
-      <c r="F15" s="515" t="n"/>
-      <c r="G15" s="515" t="n"/>
-      <c r="H15" s="515" t="n"/>
-      <c r="I15" s="353" t="n"/>
-      <c r="J15" s="353" t="n"/>
-      <c r="K15" s="353" t="n"/>
-      <c r="L15" s="353" t="n"/>
-      <c r="M15" s="353" t="n"/>
-      <c r="N15" s="353" t="n"/>
-      <c r="O15" s="353" t="n"/>
-      <c r="P15" s="353" t="n"/>
-      <c r="Q15" s="353" t="n"/>
-      <c r="R15" s="353" t="n"/>
-      <c r="S15" s="353" t="n"/>
-      <c r="T15" s="353" t="n"/>
-      <c r="U15" s="353" t="n"/>
-      <c r="V15" s="353" t="n"/>
-      <c r="W15" s="353" t="n"/>
-      <c r="X15" s="353" t="n"/>
-      <c r="Y15" s="353" t="n"/>
-      <c r="Z15" s="353" t="n"/>
-      <c r="AA15" s="353" t="n"/>
-      <c r="AB15" s="353" t="n"/>
-      <c r="AC15" s="353" t="n"/>
-      <c r="AD15" s="353" t="n"/>
-      <c r="AE15" s="353" t="n"/>
-      <c r="AF15" s="353" t="n"/>
-      <c r="AG15" s="353" t="n"/>
-      <c r="AH15" s="353" t="n"/>
-      <c r="AI15" s="353" t="n"/>
-      <c r="AJ15" s="353" t="n"/>
-      <c r="AK15" s="353" t="n"/>
-      <c r="AL15" s="353" t="n"/>
-      <c r="AM15" s="353" t="n"/>
-      <c r="AN15" s="516" t="n"/>
+      <c r="A15" s="617">
+        <f>ROW()-ROW($A$9)+1</f>
+        <v/>
+      </c>
+      <c r="B15" s="410" t="n"/>
+      <c r="C15" s="604" t="n"/>
+      <c r="D15" s="409" t="n"/>
+      <c r="E15" s="409" t="n"/>
+      <c r="F15" s="409" t="n"/>
+      <c r="G15" s="409" t="n"/>
+      <c r="H15" s="409" t="n"/>
+      <c r="I15" s="409" t="n"/>
+      <c r="J15" s="409" t="n"/>
+      <c r="K15" s="409" t="n"/>
+      <c r="L15" s="410" t="n"/>
+      <c r="M15" s="604" t="n"/>
+      <c r="N15" s="409" t="n"/>
+      <c r="O15" s="409" t="n"/>
+      <c r="P15" s="409" t="n"/>
+      <c r="Q15" s="409" t="n"/>
+      <c r="R15" s="409" t="n"/>
+      <c r="S15" s="409" t="n"/>
+      <c r="T15" s="409" t="n"/>
+      <c r="U15" s="409" t="n"/>
+      <c r="V15" s="409" t="n"/>
+      <c r="W15" s="409" t="n"/>
+      <c r="X15" s="410" t="n"/>
+      <c r="Y15" s="604" t="n"/>
+      <c r="Z15" s="409" t="n"/>
+      <c r="AA15" s="409" t="n"/>
+      <c r="AB15" s="409" t="n"/>
+      <c r="AC15" s="410" t="n"/>
+      <c r="AD15" s="604" t="n"/>
+      <c r="AE15" s="409" t="n"/>
+      <c r="AF15" s="409" t="n"/>
+      <c r="AG15" s="409" t="n"/>
+      <c r="AH15" s="410" t="n"/>
+      <c r="AI15" s="604" t="n"/>
+      <c r="AJ15" s="409" t="n"/>
+      <c r="AK15" s="410" t="n"/>
+      <c r="AL15" s="605" t="n"/>
+      <c r="AM15" s="409" t="n"/>
+      <c r="AN15" s="556" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1" s="329">
-      <c r="A16" s="465" t="n"/>
-      <c r="B16" s="467" t="n"/>
-      <c r="C16" s="517" t="n"/>
-      <c r="D16" s="517" t="n"/>
-      <c r="E16" s="517" t="n"/>
-      <c r="F16" s="517" t="n"/>
-      <c r="G16" s="517" t="n"/>
-      <c r="H16" s="517" t="n"/>
-      <c r="I16" s="518" t="n"/>
-      <c r="J16" s="518" t="n"/>
-      <c r="K16" s="518" t="n"/>
-      <c r="L16" s="518" t="n"/>
-      <c r="M16" s="518" t="n"/>
-      <c r="N16" s="518" t="n"/>
-      <c r="O16" s="518" t="n"/>
-      <c r="P16" s="518" t="n"/>
-      <c r="Q16" s="518" t="n"/>
-      <c r="R16" s="518" t="n"/>
-      <c r="S16" s="518" t="n"/>
-      <c r="T16" s="518" t="n"/>
-      <c r="U16" s="518" t="n"/>
-      <c r="V16" s="518" t="n"/>
-      <c r="W16" s="518" t="n"/>
-      <c r="X16" s="518" t="n"/>
-      <c r="Y16" s="518" t="n"/>
-      <c r="Z16" s="518" t="n"/>
-      <c r="AA16" s="518" t="n"/>
-      <c r="AB16" s="518" t="n"/>
-      <c r="AC16" s="518" t="n"/>
-      <c r="AD16" s="518" t="n"/>
-      <c r="AE16" s="518" t="n"/>
-      <c r="AF16" s="518" t="n"/>
-      <c r="AG16" s="518" t="n"/>
-      <c r="AH16" s="518" t="n"/>
-      <c r="AI16" s="518" t="n"/>
-      <c r="AJ16" s="518" t="n"/>
-      <c r="AK16" s="518" t="n"/>
-      <c r="AL16" s="518" t="n"/>
-      <c r="AM16" s="518" t="n"/>
-      <c r="AN16" s="519" t="n"/>
+      <c r="A16" s="618">
+        <f>ROW()-ROW($A$9)+1</f>
+        <v/>
+      </c>
+      <c r="B16" s="410" t="n"/>
+      <c r="C16" s="607" t="n"/>
+      <c r="D16" s="409" t="n"/>
+      <c r="E16" s="409" t="n"/>
+      <c r="F16" s="409" t="n"/>
+      <c r="G16" s="409" t="n"/>
+      <c r="H16" s="409" t="n"/>
+      <c r="I16" s="409" t="n"/>
+      <c r="J16" s="409" t="n"/>
+      <c r="K16" s="409" t="n"/>
+      <c r="L16" s="410" t="n"/>
+      <c r="M16" s="607" t="n"/>
+      <c r="N16" s="409" t="n"/>
+      <c r="O16" s="409" t="n"/>
+      <c r="P16" s="409" t="n"/>
+      <c r="Q16" s="409" t="n"/>
+      <c r="R16" s="409" t="n"/>
+      <c r="S16" s="409" t="n"/>
+      <c r="T16" s="409" t="n"/>
+      <c r="U16" s="409" t="n"/>
+      <c r="V16" s="409" t="n"/>
+      <c r="W16" s="409" t="n"/>
+      <c r="X16" s="410" t="n"/>
+      <c r="Y16" s="607" t="n"/>
+      <c r="Z16" s="409" t="n"/>
+      <c r="AA16" s="409" t="n"/>
+      <c r="AB16" s="409" t="n"/>
+      <c r="AC16" s="410" t="n"/>
+      <c r="AD16" s="607" t="n"/>
+      <c r="AE16" s="409" t="n"/>
+      <c r="AF16" s="409" t="n"/>
+      <c r="AG16" s="409" t="n"/>
+      <c r="AH16" s="410" t="n"/>
+      <c r="AI16" s="607" t="n"/>
+      <c r="AJ16" s="409" t="n"/>
+      <c r="AK16" s="410" t="n"/>
+      <c r="AL16" s="608" t="n"/>
+      <c r="AM16" s="409" t="n"/>
+      <c r="AN16" s="556" t="n"/>
     </row>
-    <row r="17" ht="20" customHeight="1" s="329"/>
-    <row r="18" ht="20" customHeight="1" s="329"/>
-    <row r="19" ht="20" customHeight="1" s="329"/>
-    <row r="20" ht="20" customHeight="1" s="329"/>
-    <row r="21" ht="20" customHeight="1" s="329"/>
-    <row r="22" ht="20" customHeight="1" s="329"/>
-    <row r="23" ht="20" customHeight="1" s="329"/>
-    <row r="24" ht="20" customHeight="1" s="329"/>
-    <row r="25" ht="20" customHeight="1" s="329"/>
-    <row r="26" ht="20" customHeight="1" s="329"/>
-    <row r="27" ht="20" customHeight="1" s="329"/>
-    <row r="28" ht="20" customHeight="1" s="329"/>
-    <row r="29" ht="20" customHeight="1" s="329"/>
-    <row r="30" ht="20" customHeight="1" s="329"/>
-    <row r="31" ht="20" customHeight="1" s="329"/>
-    <row r="32" ht="20" customHeight="1" s="329"/>
-    <row r="33" ht="20" customHeight="1" s="329"/>
-    <row r="34" ht="20" customHeight="1" s="329"/>
-    <row r="35" ht="20" customHeight="1" s="329"/>
-    <row r="36" ht="20" customHeight="1" s="329"/>
-    <row r="37" ht="20" customHeight="1" s="329"/>
-    <row r="38" ht="20" customHeight="1" s="329"/>
-    <row r="39" ht="20" customHeight="1" s="329"/>
-    <row r="40" ht="20" customHeight="1" s="329"/>
+    <row r="17" ht="20" customHeight="1" s="329">
+      <c r="A17" s="617">
+        <f>ROW()-ROW($A$9)+1</f>
+        <v/>
+      </c>
+      <c r="B17" s="410" t="n"/>
+      <c r="C17" s="604" t="n"/>
+      <c r="D17" s="409" t="n"/>
+      <c r="E17" s="409" t="n"/>
+      <c r="F17" s="409" t="n"/>
+      <c r="G17" s="409" t="n"/>
+      <c r="H17" s="409" t="n"/>
+      <c r="I17" s="409" t="n"/>
+      <c r="J17" s="409" t="n"/>
+      <c r="K17" s="409" t="n"/>
+      <c r="L17" s="410" t="n"/>
+      <c r="M17" s="604" t="n"/>
+      <c r="N17" s="409" t="n"/>
+      <c r="O17" s="409" t="n"/>
+      <c r="P17" s="409" t="n"/>
+      <c r="Q17" s="409" t="n"/>
+      <c r="R17" s="409" t="n"/>
+      <c r="S17" s="409" t="n"/>
+      <c r="T17" s="409" t="n"/>
+      <c r="U17" s="409" t="n"/>
+      <c r="V17" s="409" t="n"/>
+      <c r="W17" s="409" t="n"/>
+      <c r="X17" s="410" t="n"/>
+      <c r="Y17" s="604" t="n"/>
+      <c r="Z17" s="409" t="n"/>
+      <c r="AA17" s="409" t="n"/>
+      <c r="AB17" s="409" t="n"/>
+      <c r="AC17" s="410" t="n"/>
+      <c r="AD17" s="604" t="n"/>
+      <c r="AE17" s="409" t="n"/>
+      <c r="AF17" s="409" t="n"/>
+      <c r="AG17" s="409" t="n"/>
+      <c r="AH17" s="410" t="n"/>
+      <c r="AI17" s="604" t="n"/>
+      <c r="AJ17" s="409" t="n"/>
+      <c r="AK17" s="410" t="n"/>
+      <c r="AL17" s="605" t="n"/>
+      <c r="AM17" s="409" t="n"/>
+      <c r="AN17" s="556" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1" s="329">
+      <c r="A18" s="619">
+        <f>ROW()-ROW($A$9)+1</f>
+        <v/>
+      </c>
+      <c r="B18" s="546" t="n"/>
+      <c r="C18" s="610" t="n"/>
+      <c r="D18" s="545" t="n"/>
+      <c r="E18" s="545" t="n"/>
+      <c r="F18" s="545" t="n"/>
+      <c r="G18" s="545" t="n"/>
+      <c r="H18" s="545" t="n"/>
+      <c r="I18" s="545" t="n"/>
+      <c r="J18" s="545" t="n"/>
+      <c r="K18" s="545" t="n"/>
+      <c r="L18" s="546" t="n"/>
+      <c r="M18" s="610" t="n"/>
+      <c r="N18" s="545" t="n"/>
+      <c r="O18" s="545" t="n"/>
+      <c r="P18" s="545" t="n"/>
+      <c r="Q18" s="545" t="n"/>
+      <c r="R18" s="545" t="n"/>
+      <c r="S18" s="545" t="n"/>
+      <c r="T18" s="545" t="n"/>
+      <c r="U18" s="545" t="n"/>
+      <c r="V18" s="545" t="n"/>
+      <c r="W18" s="545" t="n"/>
+      <c r="X18" s="546" t="n"/>
+      <c r="Y18" s="610" t="n"/>
+      <c r="Z18" s="545" t="n"/>
+      <c r="AA18" s="545" t="n"/>
+      <c r="AB18" s="545" t="n"/>
+      <c r="AC18" s="546" t="n"/>
+      <c r="AD18" s="610" t="n"/>
+      <c r="AE18" s="545" t="n"/>
+      <c r="AF18" s="545" t="n"/>
+      <c r="AG18" s="545" t="n"/>
+      <c r="AH18" s="546" t="n"/>
+      <c r="AI18" s="610" t="n"/>
+      <c r="AJ18" s="545" t="n"/>
+      <c r="AK18" s="546" t="n"/>
+      <c r="AL18" s="611" t="n"/>
+      <c r="AM18" s="545" t="n"/>
+      <c r="AN18" s="548" t="n"/>
+    </row>
+    <row r="19" ht="20" customHeight="1" s="329">
+      <c r="A19" s="616" t="n"/>
+      <c r="B19" s="616" t="n"/>
+      <c r="C19" s="616" t="n"/>
+      <c r="D19" s="616" t="n"/>
+      <c r="E19" s="616" t="n"/>
+      <c r="F19" s="616" t="n"/>
+      <c r="G19" s="616" t="n"/>
+      <c r="H19" s="616" t="n"/>
+      <c r="I19" s="616" t="n"/>
+      <c r="J19" s="616" t="n"/>
+      <c r="K19" s="616" t="n"/>
+      <c r="L19" s="616" t="n"/>
+      <c r="M19" s="616" t="n"/>
+      <c r="N19" s="616" t="n"/>
+      <c r="O19" s="616" t="n"/>
+      <c r="P19" s="616" t="n"/>
+      <c r="Q19" s="616" t="n"/>
+      <c r="R19" s="616" t="n"/>
+      <c r="S19" s="616" t="n"/>
+      <c r="T19" s="616" t="n"/>
+      <c r="U19" s="616" t="n"/>
+      <c r="V19" s="616" t="n"/>
+      <c r="W19" s="616" t="n"/>
+      <c r="X19" s="616" t="n"/>
+      <c r="Y19" s="616" t="n"/>
+      <c r="Z19" s="616" t="n"/>
+      <c r="AA19" s="616" t="n"/>
+      <c r="AB19" s="616" t="n"/>
+      <c r="AC19" s="616" t="n"/>
+      <c r="AD19" s="616" t="n"/>
+      <c r="AE19" s="616" t="n"/>
+      <c r="AF19" s="616" t="n"/>
+      <c r="AG19" s="616" t="n"/>
+      <c r="AH19" s="616" t="n"/>
+      <c r="AI19" s="616" t="n"/>
+      <c r="AJ19" s="616" t="n"/>
+      <c r="AK19" s="616" t="n"/>
+      <c r="AL19" s="616" t="n"/>
+      <c r="AM19" s="616" t="n"/>
+      <c r="AN19" s="616" t="n"/>
+    </row>
+    <row r="20" ht="20" customHeight="1" s="329">
+      <c r="A20" s="616" t="n"/>
+      <c r="B20" s="616" t="n"/>
+      <c r="C20" s="616" t="n"/>
+      <c r="D20" s="616" t="n"/>
+      <c r="E20" s="616" t="n"/>
+      <c r="F20" s="616" t="n"/>
+      <c r="G20" s="616" t="n"/>
+      <c r="H20" s="616" t="n"/>
+      <c r="I20" s="616" t="n"/>
+      <c r="J20" s="616" t="n"/>
+      <c r="K20" s="616" t="n"/>
+      <c r="L20" s="616" t="n"/>
+      <c r="M20" s="616" t="n"/>
+      <c r="N20" s="616" t="n"/>
+      <c r="O20" s="616" t="n"/>
+      <c r="P20" s="616" t="n"/>
+      <c r="Q20" s="616" t="n"/>
+      <c r="R20" s="616" t="n"/>
+      <c r="S20" s="616" t="n"/>
+      <c r="T20" s="616" t="n"/>
+      <c r="U20" s="616" t="n"/>
+      <c r="V20" s="616" t="n"/>
+      <c r="W20" s="616" t="n"/>
+      <c r="X20" s="616" t="n"/>
+      <c r="Y20" s="616" t="n"/>
+      <c r="Z20" s="616" t="n"/>
+      <c r="AA20" s="616" t="n"/>
+      <c r="AB20" s="616" t="n"/>
+      <c r="AC20" s="616" t="n"/>
+      <c r="AD20" s="616" t="n"/>
+      <c r="AE20" s="616" t="n"/>
+      <c r="AF20" s="616" t="n"/>
+      <c r="AG20" s="616" t="n"/>
+      <c r="AH20" s="616" t="n"/>
+      <c r="AI20" s="616" t="n"/>
+      <c r="AJ20" s="616" t="n"/>
+      <c r="AK20" s="616" t="n"/>
+      <c r="AL20" s="616" t="n"/>
+      <c r="AM20" s="616" t="n"/>
+      <c r="AN20" s="616" t="n"/>
+    </row>
+    <row r="21" ht="20" customHeight="1" s="329">
+      <c r="A21" s="616" t="n"/>
+      <c r="B21" s="616" t="n"/>
+      <c r="C21" s="616" t="n"/>
+      <c r="D21" s="616" t="n"/>
+      <c r="E21" s="616" t="n"/>
+      <c r="F21" s="616" t="n"/>
+      <c r="G21" s="616" t="n"/>
+      <c r="H21" s="616" t="n"/>
+      <c r="I21" s="616" t="n"/>
+      <c r="J21" s="616" t="n"/>
+      <c r="K21" s="616" t="n"/>
+      <c r="L21" s="616" t="n"/>
+      <c r="M21" s="616" t="n"/>
+      <c r="N21" s="616" t="n"/>
+      <c r="O21" s="616" t="n"/>
+      <c r="P21" s="616" t="n"/>
+      <c r="Q21" s="616" t="n"/>
+      <c r="R21" s="616" t="n"/>
+      <c r="S21" s="616" t="n"/>
+      <c r="T21" s="616" t="n"/>
+      <c r="U21" s="616" t="n"/>
+      <c r="V21" s="616" t="n"/>
+      <c r="W21" s="616" t="n"/>
+      <c r="X21" s="616" t="n"/>
+      <c r="Y21" s="616" t="n"/>
+      <c r="Z21" s="616" t="n"/>
+      <c r="AA21" s="616" t="n"/>
+      <c r="AB21" s="616" t="n"/>
+      <c r="AC21" s="616" t="n"/>
+      <c r="AD21" s="616" t="n"/>
+      <c r="AE21" s="616" t="n"/>
+      <c r="AF21" s="616" t="n"/>
+      <c r="AG21" s="616" t="n"/>
+      <c r="AH21" s="616" t="n"/>
+      <c r="AI21" s="616" t="n"/>
+      <c r="AJ21" s="616" t="n"/>
+      <c r="AK21" s="616" t="n"/>
+      <c r="AL21" s="616" t="n"/>
+      <c r="AM21" s="616" t="n"/>
+      <c r="AN21" s="616" t="n"/>
+    </row>
+    <row r="22" ht="20" customHeight="1" s="329">
+      <c r="A22" s="616" t="n"/>
+      <c r="B22" s="616" t="n"/>
+      <c r="C22" s="616" t="n"/>
+      <c r="D22" s="616" t="n"/>
+      <c r="E22" s="616" t="n"/>
+      <c r="F22" s="616" t="n"/>
+      <c r="G22" s="616" t="n"/>
+      <c r="H22" s="616" t="n"/>
+      <c r="I22" s="616" t="n"/>
+      <c r="J22" s="616" t="n"/>
+      <c r="K22" s="616" t="n"/>
+      <c r="L22" s="616" t="n"/>
+      <c r="M22" s="616" t="n"/>
+      <c r="N22" s="616" t="n"/>
+      <c r="O22" s="616" t="n"/>
+      <c r="P22" s="616" t="n"/>
+      <c r="Q22" s="616" t="n"/>
+      <c r="R22" s="616" t="n"/>
+      <c r="S22" s="616" t="n"/>
+      <c r="T22" s="616" t="n"/>
+      <c r="U22" s="616" t="n"/>
+      <c r="V22" s="616" t="n"/>
+      <c r="W22" s="616" t="n"/>
+      <c r="X22" s="616" t="n"/>
+      <c r="Y22" s="616" t="n"/>
+      <c r="Z22" s="616" t="n"/>
+      <c r="AA22" s="616" t="n"/>
+      <c r="AB22" s="616" t="n"/>
+      <c r="AC22" s="616" t="n"/>
+      <c r="AD22" s="616" t="n"/>
+      <c r="AE22" s="616" t="n"/>
+      <c r="AF22" s="616" t="n"/>
+      <c r="AG22" s="616" t="n"/>
+      <c r="AH22" s="616" t="n"/>
+      <c r="AI22" s="616" t="n"/>
+      <c r="AJ22" s="616" t="n"/>
+      <c r="AK22" s="616" t="n"/>
+      <c r="AL22" s="616" t="n"/>
+      <c r="AM22" s="616" t="n"/>
+      <c r="AN22" s="616" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1" s="329">
+      <c r="A23" s="616" t="n"/>
+      <c r="B23" s="616" t="n"/>
+      <c r="C23" s="616" t="n"/>
+      <c r="D23" s="616" t="n"/>
+      <c r="E23" s="616" t="n"/>
+      <c r="F23" s="616" t="n"/>
+      <c r="G23" s="616" t="n"/>
+      <c r="H23" s="616" t="n"/>
+      <c r="I23" s="616" t="n"/>
+      <c r="J23" s="616" t="n"/>
+      <c r="K23" s="616" t="n"/>
+      <c r="L23" s="616" t="n"/>
+      <c r="M23" s="616" t="n"/>
+      <c r="N23" s="616" t="n"/>
+      <c r="O23" s="616" t="n"/>
+      <c r="P23" s="616" t="n"/>
+      <c r="Q23" s="616" t="n"/>
+      <c r="R23" s="616" t="n"/>
+      <c r="S23" s="616" t="n"/>
+      <c r="T23" s="616" t="n"/>
+      <c r="U23" s="616" t="n"/>
+      <c r="V23" s="616" t="n"/>
+      <c r="W23" s="616" t="n"/>
+      <c r="X23" s="616" t="n"/>
+      <c r="Y23" s="616" t="n"/>
+      <c r="Z23" s="616" t="n"/>
+      <c r="AA23" s="616" t="n"/>
+      <c r="AB23" s="616" t="n"/>
+      <c r="AC23" s="616" t="n"/>
+      <c r="AD23" s="616" t="n"/>
+      <c r="AE23" s="616" t="n"/>
+      <c r="AF23" s="616" t="n"/>
+      <c r="AG23" s="616" t="n"/>
+      <c r="AH23" s="616" t="n"/>
+      <c r="AI23" s="616" t="n"/>
+      <c r="AJ23" s="616" t="n"/>
+      <c r="AK23" s="616" t="n"/>
+      <c r="AL23" s="616" t="n"/>
+      <c r="AM23" s="616" t="n"/>
+      <c r="AN23" s="616" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1" s="329">
+      <c r="A24" s="616" t="n"/>
+      <c r="B24" s="616" t="n"/>
+      <c r="C24" s="616" t="n"/>
+      <c r="D24" s="616" t="n"/>
+      <c r="E24" s="616" t="n"/>
+      <c r="F24" s="616" t="n"/>
+      <c r="G24" s="616" t="n"/>
+      <c r="H24" s="616" t="n"/>
+      <c r="I24" s="616" t="n"/>
+      <c r="J24" s="616" t="n"/>
+      <c r="K24" s="616" t="n"/>
+      <c r="L24" s="616" t="n"/>
+      <c r="M24" s="616" t="n"/>
+      <c r="N24" s="616" t="n"/>
+      <c r="O24" s="616" t="n"/>
+      <c r="P24" s="616" t="n"/>
+      <c r="Q24" s="616" t="n"/>
+      <c r="R24" s="616" t="n"/>
+      <c r="S24" s="616" t="n"/>
+      <c r="T24" s="616" t="n"/>
+      <c r="U24" s="616" t="n"/>
+      <c r="V24" s="616" t="n"/>
+      <c r="W24" s="616" t="n"/>
+      <c r="X24" s="616" t="n"/>
+      <c r="Y24" s="616" t="n"/>
+      <c r="Z24" s="616" t="n"/>
+      <c r="AA24" s="616" t="n"/>
+      <c r="AB24" s="616" t="n"/>
+      <c r="AC24" s="616" t="n"/>
+      <c r="AD24" s="616" t="n"/>
+      <c r="AE24" s="616" t="n"/>
+      <c r="AF24" s="616" t="n"/>
+      <c r="AG24" s="616" t="n"/>
+      <c r="AH24" s="616" t="n"/>
+      <c r="AI24" s="616" t="n"/>
+      <c r="AJ24" s="616" t="n"/>
+      <c r="AK24" s="616" t="n"/>
+      <c r="AL24" s="616" t="n"/>
+      <c r="AM24" s="616" t="n"/>
+      <c r="AN24" s="616" t="n"/>
+    </row>
+    <row r="25" ht="20" customHeight="1" s="329">
+      <c r="A25" s="616" t="n"/>
+      <c r="B25" s="616" t="n"/>
+      <c r="C25" s="616" t="n"/>
+      <c r="D25" s="616" t="n"/>
+      <c r="E25" s="616" t="n"/>
+      <c r="F25" s="616" t="n"/>
+      <c r="G25" s="616" t="n"/>
+      <c r="H25" s="616" t="n"/>
+      <c r="I25" s="616" t="n"/>
+      <c r="J25" s="616" t="n"/>
+      <c r="K25" s="616" t="n"/>
+      <c r="L25" s="616" t="n"/>
+      <c r="M25" s="616" t="n"/>
+      <c r="N25" s="616" t="n"/>
+      <c r="O25" s="616" t="n"/>
+      <c r="P25" s="616" t="n"/>
+      <c r="Q25" s="616" t="n"/>
+      <c r="R25" s="616" t="n"/>
+      <c r="S25" s="616" t="n"/>
+      <c r="T25" s="616" t="n"/>
+      <c r="U25" s="616" t="n"/>
+      <c r="V25" s="616" t="n"/>
+      <c r="W25" s="616" t="n"/>
+      <c r="X25" s="616" t="n"/>
+      <c r="Y25" s="616" t="n"/>
+      <c r="Z25" s="616" t="n"/>
+      <c r="AA25" s="616" t="n"/>
+      <c r="AB25" s="616" t="n"/>
+      <c r="AC25" s="616" t="n"/>
+      <c r="AD25" s="616" t="n"/>
+      <c r="AE25" s="616" t="n"/>
+      <c r="AF25" s="616" t="n"/>
+      <c r="AG25" s="616" t="n"/>
+      <c r="AH25" s="616" t="n"/>
+      <c r="AI25" s="616" t="n"/>
+      <c r="AJ25" s="616" t="n"/>
+      <c r="AK25" s="616" t="n"/>
+      <c r="AL25" s="616" t="n"/>
+      <c r="AM25" s="616" t="n"/>
+      <c r="AN25" s="616" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1" s="329">
+      <c r="A26" s="616" t="n"/>
+      <c r="B26" s="616" t="n"/>
+      <c r="C26" s="616" t="n"/>
+      <c r="D26" s="616" t="n"/>
+      <c r="E26" s="616" t="n"/>
+      <c r="F26" s="616" t="n"/>
+      <c r="G26" s="616" t="n"/>
+      <c r="H26" s="616" t="n"/>
+      <c r="I26" s="616" t="n"/>
+      <c r="J26" s="616" t="n"/>
+      <c r="K26" s="616" t="n"/>
+      <c r="L26" s="616" t="n"/>
+      <c r="M26" s="616" t="n"/>
+      <c r="N26" s="616" t="n"/>
+      <c r="O26" s="616" t="n"/>
+      <c r="P26" s="616" t="n"/>
+      <c r="Q26" s="616" t="n"/>
+      <c r="R26" s="616" t="n"/>
+      <c r="S26" s="616" t="n"/>
+      <c r="T26" s="616" t="n"/>
+      <c r="U26" s="616" t="n"/>
+      <c r="V26" s="616" t="n"/>
+      <c r="W26" s="616" t="n"/>
+      <c r="X26" s="616" t="n"/>
+      <c r="Y26" s="616" t="n"/>
+      <c r="Z26" s="616" t="n"/>
+      <c r="AA26" s="616" t="n"/>
+      <c r="AB26" s="616" t="n"/>
+      <c r="AC26" s="616" t="n"/>
+      <c r="AD26" s="616" t="n"/>
+      <c r="AE26" s="616" t="n"/>
+      <c r="AF26" s="616" t="n"/>
+      <c r="AG26" s="616" t="n"/>
+      <c r="AH26" s="616" t="n"/>
+      <c r="AI26" s="616" t="n"/>
+      <c r="AJ26" s="616" t="n"/>
+      <c r="AK26" s="616" t="n"/>
+      <c r="AL26" s="616" t="n"/>
+      <c r="AM26" s="616" t="n"/>
+      <c r="AN26" s="616" t="n"/>
+    </row>
+    <row r="27" ht="20" customHeight="1" s="329">
+      <c r="A27" s="616" t="n"/>
+      <c r="B27" s="616" t="n"/>
+      <c r="C27" s="616" t="n"/>
+      <c r="D27" s="616" t="n"/>
+      <c r="E27" s="616" t="n"/>
+      <c r="F27" s="616" t="n"/>
+      <c r="G27" s="616" t="n"/>
+      <c r="H27" s="616" t="n"/>
+      <c r="I27" s="616" t="n"/>
+      <c r="J27" s="616" t="n"/>
+      <c r="K27" s="616" t="n"/>
+      <c r="L27" s="616" t="n"/>
+      <c r="M27" s="616" t="n"/>
+      <c r="N27" s="616" t="n"/>
+      <c r="O27" s="616" t="n"/>
+      <c r="P27" s="616" t="n"/>
+      <c r="Q27" s="616" t="n"/>
+      <c r="R27" s="616" t="n"/>
+      <c r="S27" s="616" t="n"/>
+      <c r="T27" s="616" t="n"/>
+      <c r="U27" s="616" t="n"/>
+      <c r="V27" s="616" t="n"/>
+      <c r="W27" s="616" t="n"/>
+      <c r="X27" s="616" t="n"/>
+      <c r="Y27" s="616" t="n"/>
+      <c r="Z27" s="616" t="n"/>
+      <c r="AA27" s="616" t="n"/>
+      <c r="AB27" s="616" t="n"/>
+      <c r="AC27" s="616" t="n"/>
+      <c r="AD27" s="616" t="n"/>
+      <c r="AE27" s="616" t="n"/>
+      <c r="AF27" s="616" t="n"/>
+      <c r="AG27" s="616" t="n"/>
+      <c r="AH27" s="616" t="n"/>
+      <c r="AI27" s="616" t="n"/>
+      <c r="AJ27" s="616" t="n"/>
+      <c r="AK27" s="616" t="n"/>
+      <c r="AL27" s="616" t="n"/>
+      <c r="AM27" s="616" t="n"/>
+      <c r="AN27" s="616" t="n"/>
+    </row>
+    <row r="28" ht="20" customHeight="1" s="329">
+      <c r="A28" s="616" t="n"/>
+      <c r="B28" s="616" t="n"/>
+      <c r="C28" s="616" t="n"/>
+      <c r="D28" s="616" t="n"/>
+      <c r="E28" s="616" t="n"/>
+      <c r="F28" s="616" t="n"/>
+      <c r="G28" s="616" t="n"/>
+      <c r="H28" s="616" t="n"/>
+      <c r="I28" s="616" t="n"/>
+      <c r="J28" s="616" t="n"/>
+      <c r="K28" s="616" t="n"/>
+      <c r="L28" s="616" t="n"/>
+      <c r="M28" s="616" t="n"/>
+      <c r="N28" s="616" t="n"/>
+      <c r="O28" s="616" t="n"/>
+      <c r="P28" s="616" t="n"/>
+      <c r="Q28" s="616" t="n"/>
+      <c r="R28" s="616" t="n"/>
+      <c r="S28" s="616" t="n"/>
+      <c r="T28" s="616" t="n"/>
+      <c r="U28" s="616" t="n"/>
+      <c r="V28" s="616" t="n"/>
+      <c r="W28" s="616" t="n"/>
+      <c r="X28" s="616" t="n"/>
+      <c r="Y28" s="616" t="n"/>
+      <c r="Z28" s="616" t="n"/>
+      <c r="AA28" s="616" t="n"/>
+      <c r="AB28" s="616" t="n"/>
+      <c r="AC28" s="616" t="n"/>
+      <c r="AD28" s="616" t="n"/>
+      <c r="AE28" s="616" t="n"/>
+      <c r="AF28" s="616" t="n"/>
+      <c r="AG28" s="616" t="n"/>
+      <c r="AH28" s="616" t="n"/>
+      <c r="AI28" s="616" t="n"/>
+      <c r="AJ28" s="616" t="n"/>
+      <c r="AK28" s="616" t="n"/>
+      <c r="AL28" s="616" t="n"/>
+      <c r="AM28" s="616" t="n"/>
+      <c r="AN28" s="616" t="n"/>
+    </row>
+    <row r="29" ht="20" customHeight="1" s="329">
+      <c r="A29" s="616" t="n"/>
+      <c r="B29" s="616" t="n"/>
+      <c r="C29" s="616" t="n"/>
+      <c r="D29" s="616" t="n"/>
+      <c r="E29" s="616" t="n"/>
+      <c r="F29" s="616" t="n"/>
+      <c r="G29" s="616" t="n"/>
+      <c r="H29" s="616" t="n"/>
+      <c r="I29" s="616" t="n"/>
+      <c r="J29" s="616" t="n"/>
+      <c r="K29" s="616" t="n"/>
+      <c r="L29" s="616" t="n"/>
+      <c r="M29" s="616" t="n"/>
+      <c r="N29" s="616" t="n"/>
+      <c r="O29" s="616" t="n"/>
+      <c r="P29" s="616" t="n"/>
+      <c r="Q29" s="616" t="n"/>
+      <c r="R29" s="616" t="n"/>
+      <c r="S29" s="616" t="n"/>
+      <c r="T29" s="616" t="n"/>
+      <c r="U29" s="616" t="n"/>
+      <c r="V29" s="616" t="n"/>
+      <c r="W29" s="616" t="n"/>
+      <c r="X29" s="616" t="n"/>
+      <c r="Y29" s="616" t="n"/>
+      <c r="Z29" s="616" t="n"/>
+      <c r="AA29" s="616" t="n"/>
+      <c r="AB29" s="616" t="n"/>
+      <c r="AC29" s="616" t="n"/>
+      <c r="AD29" s="616" t="n"/>
+      <c r="AE29" s="616" t="n"/>
+      <c r="AF29" s="616" t="n"/>
+      <c r="AG29" s="616" t="n"/>
+      <c r="AH29" s="616" t="n"/>
+      <c r="AI29" s="616" t="n"/>
+      <c r="AJ29" s="616" t="n"/>
+      <c r="AK29" s="616" t="n"/>
+      <c r="AL29" s="616" t="n"/>
+      <c r="AM29" s="616" t="n"/>
+      <c r="AN29" s="616" t="n"/>
+    </row>
+    <row r="30" ht="20" customHeight="1" s="329">
+      <c r="A30" s="616" t="n"/>
+      <c r="B30" s="616" t="n"/>
+      <c r="C30" s="616" t="n"/>
+      <c r="D30" s="616" t="n"/>
+      <c r="E30" s="616" t="n"/>
+      <c r="F30" s="616" t="n"/>
+      <c r="G30" s="616" t="n"/>
+      <c r="H30" s="616" t="n"/>
+      <c r="I30" s="616" t="n"/>
+      <c r="J30" s="616" t="n"/>
+      <c r="K30" s="616" t="n"/>
+      <c r="L30" s="616" t="n"/>
+      <c r="M30" s="616" t="n"/>
+      <c r="N30" s="616" t="n"/>
+      <c r="O30" s="616" t="n"/>
+      <c r="P30" s="616" t="n"/>
+      <c r="Q30" s="616" t="n"/>
+      <c r="R30" s="616" t="n"/>
+      <c r="S30" s="616" t="n"/>
+      <c r="T30" s="616" t="n"/>
+      <c r="U30" s="616" t="n"/>
+      <c r="V30" s="616" t="n"/>
+      <c r="W30" s="616" t="n"/>
+      <c r="X30" s="616" t="n"/>
+      <c r="Y30" s="616" t="n"/>
+      <c r="Z30" s="616" t="n"/>
+      <c r="AA30" s="616" t="n"/>
+      <c r="AB30" s="616" t="n"/>
+      <c r="AC30" s="616" t="n"/>
+      <c r="AD30" s="616" t="n"/>
+      <c r="AE30" s="616" t="n"/>
+      <c r="AF30" s="616" t="n"/>
+      <c r="AG30" s="616" t="n"/>
+      <c r="AH30" s="616" t="n"/>
+      <c r="AI30" s="616" t="n"/>
+      <c r="AJ30" s="616" t="n"/>
+      <c r="AK30" s="616" t="n"/>
+      <c r="AL30" s="616" t="n"/>
+      <c r="AM30" s="616" t="n"/>
+      <c r="AN30" s="616" t="n"/>
+    </row>
+    <row r="31" ht="20" customHeight="1" s="329">
+      <c r="A31" s="616" t="n"/>
+      <c r="B31" s="616" t="n"/>
+      <c r="C31" s="616" t="n"/>
+      <c r="D31" s="616" t="n"/>
+      <c r="E31" s="616" t="n"/>
+      <c r="F31" s="616" t="n"/>
+      <c r="G31" s="616" t="n"/>
+      <c r="H31" s="616" t="n"/>
+      <c r="I31" s="616" t="n"/>
+      <c r="J31" s="616" t="n"/>
+      <c r="K31" s="616" t="n"/>
+      <c r="L31" s="616" t="n"/>
+      <c r="M31" s="616" t="n"/>
+      <c r="N31" s="616" t="n"/>
+      <c r="O31" s="616" t="n"/>
+      <c r="P31" s="616" t="n"/>
+      <c r="Q31" s="616" t="n"/>
+      <c r="R31" s="616" t="n"/>
+      <c r="S31" s="616" t="n"/>
+      <c r="T31" s="616" t="n"/>
+      <c r="U31" s="616" t="n"/>
+      <c r="V31" s="616" t="n"/>
+      <c r="W31" s="616" t="n"/>
+      <c r="X31" s="616" t="n"/>
+      <c r="Y31" s="616" t="n"/>
+      <c r="Z31" s="616" t="n"/>
+      <c r="AA31" s="616" t="n"/>
+      <c r="AB31" s="616" t="n"/>
+      <c r="AC31" s="616" t="n"/>
+      <c r="AD31" s="616" t="n"/>
+      <c r="AE31" s="616" t="n"/>
+      <c r="AF31" s="616" t="n"/>
+      <c r="AG31" s="616" t="n"/>
+      <c r="AH31" s="616" t="n"/>
+      <c r="AI31" s="616" t="n"/>
+      <c r="AJ31" s="616" t="n"/>
+      <c r="AK31" s="616" t="n"/>
+      <c r="AL31" s="616" t="n"/>
+      <c r="AM31" s="616" t="n"/>
+      <c r="AN31" s="616" t="n"/>
+    </row>
+    <row r="32" ht="20" customHeight="1" s="329">
+      <c r="A32" s="616" t="n"/>
+      <c r="B32" s="616" t="n"/>
+      <c r="C32" s="616" t="n"/>
+      <c r="D32" s="616" t="n"/>
+      <c r="E32" s="616" t="n"/>
+      <c r="F32" s="616" t="n"/>
+      <c r="G32" s="616" t="n"/>
+      <c r="H32" s="616" t="n"/>
+      <c r="I32" s="616" t="n"/>
+      <c r="J32" s="616" t="n"/>
+      <c r="K32" s="616" t="n"/>
+      <c r="L32" s="616" t="n"/>
+      <c r="M32" s="616" t="n"/>
+      <c r="N32" s="616" t="n"/>
+      <c r="O32" s="616" t="n"/>
+      <c r="P32" s="616" t="n"/>
+      <c r="Q32" s="616" t="n"/>
+      <c r="R32" s="616" t="n"/>
+      <c r="S32" s="616" t="n"/>
+      <c r="T32" s="616" t="n"/>
+      <c r="U32" s="616" t="n"/>
+      <c r="V32" s="616" t="n"/>
+      <c r="W32" s="616" t="n"/>
+      <c r="X32" s="616" t="n"/>
+      <c r="Y32" s="616" t="n"/>
+      <c r="Z32" s="616" t="n"/>
+      <c r="AA32" s="616" t="n"/>
+      <c r="AB32" s="616" t="n"/>
+      <c r="AC32" s="616" t="n"/>
+      <c r="AD32" s="616" t="n"/>
+      <c r="AE32" s="616" t="n"/>
+      <c r="AF32" s="616" t="n"/>
+      <c r="AG32" s="616" t="n"/>
+      <c r="AH32" s="616" t="n"/>
+      <c r="AI32" s="616" t="n"/>
+      <c r="AJ32" s="616" t="n"/>
+      <c r="AK32" s="616" t="n"/>
+      <c r="AL32" s="616" t="n"/>
+      <c r="AM32" s="616" t="n"/>
+      <c r="AN32" s="616" t="n"/>
+    </row>
+    <row r="33" ht="20" customHeight="1" s="329">
+      <c r="A33" s="616" t="n"/>
+      <c r="B33" s="616" t="n"/>
+      <c r="C33" s="616" t="n"/>
+      <c r="D33" s="616" t="n"/>
+      <c r="E33" s="616" t="n"/>
+      <c r="F33" s="616" t="n"/>
+      <c r="G33" s="616" t="n"/>
+      <c r="H33" s="616" t="n"/>
+      <c r="I33" s="616" t="n"/>
+      <c r="J33" s="616" t="n"/>
+      <c r="K33" s="616" t="n"/>
+      <c r="L33" s="616" t="n"/>
+      <c r="M33" s="616" t="n"/>
+      <c r="N33" s="616" t="n"/>
+      <c r="O33" s="616" t="n"/>
+      <c r="P33" s="616" t="n"/>
+      <c r="Q33" s="616" t="n"/>
+      <c r="R33" s="616" t="n"/>
+      <c r="S33" s="616" t="n"/>
+      <c r="T33" s="616" t="n"/>
+      <c r="U33" s="616" t="n"/>
+      <c r="V33" s="616" t="n"/>
+      <c r="W33" s="616" t="n"/>
+      <c r="X33" s="616" t="n"/>
+      <c r="Y33" s="616" t="n"/>
+      <c r="Z33" s="616" t="n"/>
+      <c r="AA33" s="616" t="n"/>
+      <c r="AB33" s="616" t="n"/>
+      <c r="AC33" s="616" t="n"/>
+      <c r="AD33" s="616" t="n"/>
+      <c r="AE33" s="616" t="n"/>
+      <c r="AF33" s="616" t="n"/>
+      <c r="AG33" s="616" t="n"/>
+      <c r="AH33" s="616" t="n"/>
+      <c r="AI33" s="616" t="n"/>
+      <c r="AJ33" s="616" t="n"/>
+      <c r="AK33" s="616" t="n"/>
+      <c r="AL33" s="616" t="n"/>
+      <c r="AM33" s="616" t="n"/>
+      <c r="AN33" s="616" t="n"/>
+    </row>
+    <row r="34" ht="20" customHeight="1" s="329">
+      <c r="A34" s="616" t="n"/>
+      <c r="B34" s="616" t="n"/>
+      <c r="C34" s="616" t="n"/>
+      <c r="D34" s="616" t="n"/>
+      <c r="E34" s="616" t="n"/>
+      <c r="F34" s="616" t="n"/>
+      <c r="G34" s="616" t="n"/>
+      <c r="H34" s="616" t="n"/>
+      <c r="I34" s="616" t="n"/>
+      <c r="J34" s="616" t="n"/>
+      <c r="K34" s="616" t="n"/>
+      <c r="L34" s="616" t="n"/>
+      <c r="M34" s="616" t="n"/>
+      <c r="N34" s="616" t="n"/>
+      <c r="O34" s="616" t="n"/>
+      <c r="P34" s="616" t="n"/>
+      <c r="Q34" s="616" t="n"/>
+      <c r="R34" s="616" t="n"/>
+      <c r="S34" s="616" t="n"/>
+      <c r="T34" s="616" t="n"/>
+      <c r="U34" s="616" t="n"/>
+      <c r="V34" s="616" t="n"/>
+      <c r="W34" s="616" t="n"/>
+      <c r="X34" s="616" t="n"/>
+      <c r="Y34" s="616" t="n"/>
+      <c r="Z34" s="616" t="n"/>
+      <c r="AA34" s="616" t="n"/>
+      <c r="AB34" s="616" t="n"/>
+      <c r="AC34" s="616" t="n"/>
+      <c r="AD34" s="616" t="n"/>
+      <c r="AE34" s="616" t="n"/>
+      <c r="AF34" s="616" t="n"/>
+      <c r="AG34" s="616" t="n"/>
+      <c r="AH34" s="616" t="n"/>
+      <c r="AI34" s="616" t="n"/>
+      <c r="AJ34" s="616" t="n"/>
+      <c r="AK34" s="616" t="n"/>
+      <c r="AL34" s="616" t="n"/>
+      <c r="AM34" s="616" t="n"/>
+      <c r="AN34" s="616" t="n"/>
+    </row>
+    <row r="35" ht="20" customHeight="1" s="329">
+      <c r="A35" s="616" t="n"/>
+      <c r="B35" s="616" t="n"/>
+      <c r="C35" s="616" t="n"/>
+      <c r="D35" s="616" t="n"/>
+      <c r="E35" s="616" t="n"/>
+      <c r="F35" s="616" t="n"/>
+      <c r="G35" s="616" t="n"/>
+      <c r="H35" s="616" t="n"/>
+      <c r="I35" s="616" t="n"/>
+      <c r="J35" s="616" t="n"/>
+      <c r="K35" s="616" t="n"/>
+      <c r="L35" s="616" t="n"/>
+      <c r="M35" s="616" t="n"/>
+      <c r="N35" s="616" t="n"/>
+      <c r="O35" s="616" t="n"/>
+      <c r="P35" s="616" t="n"/>
+      <c r="Q35" s="616" t="n"/>
+      <c r="R35" s="616" t="n"/>
+      <c r="S35" s="616" t="n"/>
+      <c r="T35" s="616" t="n"/>
+      <c r="U35" s="616" t="n"/>
+      <c r="V35" s="616" t="n"/>
+      <c r="W35" s="616" t="n"/>
+      <c r="X35" s="616" t="n"/>
+      <c r="Y35" s="616" t="n"/>
+      <c r="Z35" s="616" t="n"/>
+      <c r="AA35" s="616" t="n"/>
+      <c r="AB35" s="616" t="n"/>
+      <c r="AC35" s="616" t="n"/>
+      <c r="AD35" s="616" t="n"/>
+      <c r="AE35" s="616" t="n"/>
+      <c r="AF35" s="616" t="n"/>
+      <c r="AG35" s="616" t="n"/>
+      <c r="AH35" s="616" t="n"/>
+      <c r="AI35" s="616" t="n"/>
+      <c r="AJ35" s="616" t="n"/>
+      <c r="AK35" s="616" t="n"/>
+      <c r="AL35" s="616" t="n"/>
+      <c r="AM35" s="616" t="n"/>
+      <c r="AN35" s="616" t="n"/>
+    </row>
+    <row r="36" ht="20" customHeight="1" s="329">
+      <c r="A36" s="616" t="n"/>
+      <c r="B36" s="616" t="n"/>
+      <c r="C36" s="616" t="n"/>
+      <c r="D36" s="616" t="n"/>
+      <c r="E36" s="616" t="n"/>
+      <c r="F36" s="616" t="n"/>
+      <c r="G36" s="616" t="n"/>
+      <c r="H36" s="616" t="n"/>
+      <c r="I36" s="616" t="n"/>
+      <c r="J36" s="616" t="n"/>
+      <c r="K36" s="616" t="n"/>
+      <c r="L36" s="616" t="n"/>
+      <c r="M36" s="616" t="n"/>
+      <c r="N36" s="616" t="n"/>
+      <c r="O36" s="616" t="n"/>
+      <c r="P36" s="616" t="n"/>
+      <c r="Q36" s="616" t="n"/>
+      <c r="R36" s="616" t="n"/>
+      <c r="S36" s="616" t="n"/>
+      <c r="T36" s="616" t="n"/>
+      <c r="U36" s="616" t="n"/>
+      <c r="V36" s="616" t="n"/>
+      <c r="W36" s="616" t="n"/>
+      <c r="X36" s="616" t="n"/>
+      <c r="Y36" s="616" t="n"/>
+      <c r="Z36" s="616" t="n"/>
+      <c r="AA36" s="616" t="n"/>
+      <c r="AB36" s="616" t="n"/>
+      <c r="AC36" s="616" t="n"/>
+      <c r="AD36" s="616" t="n"/>
+      <c r="AE36" s="616" t="n"/>
+      <c r="AF36" s="616" t="n"/>
+      <c r="AG36" s="616" t="n"/>
+      <c r="AH36" s="616" t="n"/>
+      <c r="AI36" s="616" t="n"/>
+      <c r="AJ36" s="616" t="n"/>
+      <c r="AK36" s="616" t="n"/>
+      <c r="AL36" s="616" t="n"/>
+      <c r="AM36" s="616" t="n"/>
+      <c r="AN36" s="616" t="n"/>
+    </row>
+    <row r="37" ht="20" customHeight="1" s="329">
+      <c r="A37" s="616" t="n"/>
+      <c r="B37" s="616" t="n"/>
+      <c r="C37" s="616" t="n"/>
+      <c r="D37" s="616" t="n"/>
+      <c r="E37" s="616" t="n"/>
+      <c r="F37" s="616" t="n"/>
+      <c r="G37" s="616" t="n"/>
+      <c r="H37" s="616" t="n"/>
+      <c r="I37" s="616" t="n"/>
+      <c r="J37" s="616" t="n"/>
+      <c r="K37" s="616" t="n"/>
+      <c r="L37" s="616" t="n"/>
+      <c r="M37" s="616" t="n"/>
+      <c r="N37" s="616" t="n"/>
+      <c r="O37" s="616" t="n"/>
+      <c r="P37" s="616" t="n"/>
+      <c r="Q37" s="616" t="n"/>
+      <c r="R37" s="616" t="n"/>
+      <c r="S37" s="616" t="n"/>
+      <c r="T37" s="616" t="n"/>
+      <c r="U37" s="616" t="n"/>
+      <c r="V37" s="616" t="n"/>
+      <c r="W37" s="616" t="n"/>
+      <c r="X37" s="616" t="n"/>
+      <c r="Y37" s="616" t="n"/>
+      <c r="Z37" s="616" t="n"/>
+      <c r="AA37" s="616" t="n"/>
+      <c r="AB37" s="616" t="n"/>
+      <c r="AC37" s="616" t="n"/>
+      <c r="AD37" s="616" t="n"/>
+      <c r="AE37" s="616" t="n"/>
+      <c r="AF37" s="616" t="n"/>
+      <c r="AG37" s="616" t="n"/>
+      <c r="AH37" s="616" t="n"/>
+      <c r="AI37" s="616" t="n"/>
+      <c r="AJ37" s="616" t="n"/>
+      <c r="AK37" s="616" t="n"/>
+      <c r="AL37" s="616" t="n"/>
+      <c r="AM37" s="616" t="n"/>
+      <c r="AN37" s="616" t="n"/>
+    </row>
+    <row r="38" ht="20" customHeight="1" s="329">
+      <c r="A38" s="616" t="n"/>
+      <c r="B38" s="616" t="n"/>
+      <c r="C38" s="616" t="n"/>
+      <c r="D38" s="616" t="n"/>
+      <c r="E38" s="616" t="n"/>
+      <c r="F38" s="616" t="n"/>
+      <c r="G38" s="616" t="n"/>
+      <c r="H38" s="616" t="n"/>
+      <c r="I38" s="616" t="n"/>
+      <c r="J38" s="616" t="n"/>
+      <c r="K38" s="616" t="n"/>
+      <c r="L38" s="616" t="n"/>
+      <c r="M38" s="616" t="n"/>
+      <c r="N38" s="616" t="n"/>
+      <c r="O38" s="616" t="n"/>
+      <c r="P38" s="616" t="n"/>
+      <c r="Q38" s="616" t="n"/>
+      <c r="R38" s="616" t="n"/>
+      <c r="S38" s="616" t="n"/>
+      <c r="T38" s="616" t="n"/>
+      <c r="U38" s="616" t="n"/>
+      <c r="V38" s="616" t="n"/>
+      <c r="W38" s="616" t="n"/>
+      <c r="X38" s="616" t="n"/>
+      <c r="Y38" s="616" t="n"/>
+      <c r="Z38" s="616" t="n"/>
+      <c r="AA38" s="616" t="n"/>
+      <c r="AB38" s="616" t="n"/>
+      <c r="AC38" s="616" t="n"/>
+      <c r="AD38" s="616" t="n"/>
+      <c r="AE38" s="616" t="n"/>
+      <c r="AF38" s="616" t="n"/>
+      <c r="AG38" s="616" t="n"/>
+      <c r="AH38" s="616" t="n"/>
+      <c r="AI38" s="616" t="n"/>
+      <c r="AJ38" s="616" t="n"/>
+      <c r="AK38" s="616" t="n"/>
+      <c r="AL38" s="616" t="n"/>
+      <c r="AM38" s="616" t="n"/>
+      <c r="AN38" s="616" t="n"/>
+    </row>
+    <row r="39" ht="20" customHeight="1" s="329">
+      <c r="A39" s="616" t="n"/>
+      <c r="B39" s="616" t="n"/>
+      <c r="C39" s="616" t="n"/>
+      <c r="D39" s="616" t="n"/>
+      <c r="E39" s="616" t="n"/>
+      <c r="F39" s="616" t="n"/>
+      <c r="G39" s="616" t="n"/>
+      <c r="H39" s="616" t="n"/>
+      <c r="I39" s="616" t="n"/>
+      <c r="J39" s="616" t="n"/>
+      <c r="K39" s="616" t="n"/>
+      <c r="L39" s="616" t="n"/>
+      <c r="M39" s="616" t="n"/>
+      <c r="N39" s="616" t="n"/>
+      <c r="O39" s="616" t="n"/>
+      <c r="P39" s="616" t="n"/>
+      <c r="Q39" s="616" t="n"/>
+      <c r="R39" s="616" t="n"/>
+      <c r="S39" s="616" t="n"/>
+      <c r="T39" s="616" t="n"/>
+      <c r="U39" s="616" t="n"/>
+      <c r="V39" s="616" t="n"/>
+      <c r="W39" s="616" t="n"/>
+      <c r="X39" s="616" t="n"/>
+      <c r="Y39" s="616" t="n"/>
+      <c r="Z39" s="616" t="n"/>
+      <c r="AA39" s="616" t="n"/>
+      <c r="AB39" s="616" t="n"/>
+      <c r="AC39" s="616" t="n"/>
+      <c r="AD39" s="616" t="n"/>
+      <c r="AE39" s="616" t="n"/>
+      <c r="AF39" s="616" t="n"/>
+      <c r="AG39" s="616" t="n"/>
+      <c r="AH39" s="616" t="n"/>
+      <c r="AI39" s="616" t="n"/>
+      <c r="AJ39" s="616" t="n"/>
+      <c r="AK39" s="616" t="n"/>
+      <c r="AL39" s="616" t="n"/>
+      <c r="AM39" s="616" t="n"/>
+      <c r="AN39" s="616" t="n"/>
+    </row>
+    <row r="40" ht="20" customHeight="1" s="329">
+      <c r="A40" s="616" t="n"/>
+      <c r="B40" s="616" t="n"/>
+      <c r="C40" s="616" t="n"/>
+      <c r="D40" s="616" t="n"/>
+      <c r="E40" s="616" t="n"/>
+      <c r="F40" s="616" t="n"/>
+      <c r="G40" s="616" t="n"/>
+      <c r="H40" s="616" t="n"/>
+      <c r="I40" s="616" t="n"/>
+      <c r="J40" s="616" t="n"/>
+      <c r="K40" s="616" t="n"/>
+      <c r="L40" s="616" t="n"/>
+      <c r="M40" s="616" t="n"/>
+      <c r="N40" s="616" t="n"/>
+      <c r="O40" s="616" t="n"/>
+      <c r="P40" s="616" t="n"/>
+      <c r="Q40" s="616" t="n"/>
+      <c r="R40" s="616" t="n"/>
+      <c r="S40" s="616" t="n"/>
+      <c r="T40" s="616" t="n"/>
+      <c r="U40" s="616" t="n"/>
+      <c r="V40" s="616" t="n"/>
+      <c r="W40" s="616" t="n"/>
+      <c r="X40" s="616" t="n"/>
+      <c r="Y40" s="616" t="n"/>
+      <c r="Z40" s="616" t="n"/>
+      <c r="AA40" s="616" t="n"/>
+      <c r="AB40" s="616" t="n"/>
+      <c r="AC40" s="616" t="n"/>
+      <c r="AD40" s="616" t="n"/>
+      <c r="AE40" s="616" t="n"/>
+      <c r="AF40" s="616" t="n"/>
+      <c r="AG40" s="616" t="n"/>
+      <c r="AH40" s="616" t="n"/>
+      <c r="AI40" s="616" t="n"/>
+      <c r="AJ40" s="616" t="n"/>
+      <c r="AK40" s="616" t="n"/>
+      <c r="AL40" s="616" t="n"/>
+      <c r="AM40" s="616" t="n"/>
+      <c r="AN40" s="616" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="616" t="n"/>
+      <c r="B41" s="616" t="n"/>
+      <c r="C41" s="616" t="n"/>
+      <c r="D41" s="616" t="n"/>
+      <c r="E41" s="616" t="n"/>
+      <c r="F41" s="616" t="n"/>
+      <c r="G41" s="616" t="n"/>
+      <c r="H41" s="616" t="n"/>
+      <c r="I41" s="616" t="n"/>
+      <c r="J41" s="616" t="n"/>
+      <c r="K41" s="616" t="n"/>
+      <c r="L41" s="616" t="n"/>
+      <c r="M41" s="616" t="n"/>
+      <c r="N41" s="616" t="n"/>
+      <c r="O41" s="616" t="n"/>
+      <c r="P41" s="616" t="n"/>
+      <c r="Q41" s="616" t="n"/>
+      <c r="R41" s="616" t="n"/>
+      <c r="S41" s="616" t="n"/>
+      <c r="T41" s="616" t="n"/>
+      <c r="U41" s="616" t="n"/>
+      <c r="V41" s="616" t="n"/>
+      <c r="W41" s="616" t="n"/>
+      <c r="X41" s="616" t="n"/>
+      <c r="Y41" s="616" t="n"/>
+      <c r="Z41" s="616" t="n"/>
+      <c r="AA41" s="616" t="n"/>
+      <c r="AB41" s="616" t="n"/>
+      <c r="AC41" s="616" t="n"/>
+      <c r="AD41" s="616" t="n"/>
+      <c r="AE41" s="616" t="n"/>
+      <c r="AF41" s="616" t="n"/>
+      <c r="AG41" s="616" t="n"/>
+      <c r="AH41" s="616" t="n"/>
+      <c r="AI41" s="616" t="n"/>
+      <c r="AJ41" s="616" t="n"/>
+      <c r="AK41" s="616" t="n"/>
+      <c r="AL41" s="616" t="n"/>
+      <c r="AM41" s="616" t="n"/>
+      <c r="AN41" s="616" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="616" t="n"/>
+      <c r="B42" s="616" t="n"/>
+      <c r="C42" s="616" t="n"/>
+      <c r="D42" s="616" t="n"/>
+      <c r="E42" s="616" t="n"/>
+      <c r="F42" s="616" t="n"/>
+      <c r="G42" s="616" t="n"/>
+      <c r="H42" s="616" t="n"/>
+      <c r="I42" s="616" t="n"/>
+      <c r="J42" s="616" t="n"/>
+      <c r="K42" s="616" t="n"/>
+      <c r="L42" s="616" t="n"/>
+      <c r="M42" s="616" t="n"/>
+      <c r="N42" s="616" t="n"/>
+      <c r="O42" s="616" t="n"/>
+      <c r="P42" s="616" t="n"/>
+      <c r="Q42" s="616" t="n"/>
+      <c r="R42" s="616" t="n"/>
+      <c r="S42" s="616" t="n"/>
+      <c r="T42" s="616" t="n"/>
+      <c r="U42" s="616" t="n"/>
+      <c r="V42" s="616" t="n"/>
+      <c r="W42" s="616" t="n"/>
+      <c r="X42" s="616" t="n"/>
+      <c r="Y42" s="616" t="n"/>
+      <c r="Z42" s="616" t="n"/>
+      <c r="AA42" s="616" t="n"/>
+      <c r="AB42" s="616" t="n"/>
+      <c r="AC42" s="616" t="n"/>
+      <c r="AD42" s="616" t="n"/>
+      <c r="AE42" s="616" t="n"/>
+      <c r="AF42" s="616" t="n"/>
+      <c r="AG42" s="616" t="n"/>
+      <c r="AH42" s="616" t="n"/>
+      <c r="AI42" s="616" t="n"/>
+      <c r="AJ42" s="616" t="n"/>
+      <c r="AK42" s="616" t="n"/>
+      <c r="AL42" s="616" t="n"/>
+      <c r="AM42" s="616" t="n"/>
+      <c r="AN42" s="616" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="616" t="n"/>
+      <c r="B43" s="616" t="n"/>
+      <c r="C43" s="616" t="n"/>
+      <c r="D43" s="616" t="n"/>
+      <c r="E43" s="616" t="n"/>
+      <c r="F43" s="616" t="n"/>
+      <c r="G43" s="616" t="n"/>
+      <c r="H43" s="616" t="n"/>
+      <c r="I43" s="616" t="n"/>
+      <c r="J43" s="616" t="n"/>
+      <c r="K43" s="616" t="n"/>
+      <c r="L43" s="616" t="n"/>
+      <c r="M43" s="616" t="n"/>
+      <c r="N43" s="616" t="n"/>
+      <c r="O43" s="616" t="n"/>
+      <c r="P43" s="616" t="n"/>
+      <c r="Q43" s="616" t="n"/>
+      <c r="R43" s="616" t="n"/>
+      <c r="S43" s="616" t="n"/>
+      <c r="T43" s="616" t="n"/>
+      <c r="U43" s="616" t="n"/>
+      <c r="V43" s="616" t="n"/>
+      <c r="W43" s="616" t="n"/>
+      <c r="X43" s="616" t="n"/>
+      <c r="Y43" s="616" t="n"/>
+      <c r="Z43" s="616" t="n"/>
+      <c r="AA43" s="616" t="n"/>
+      <c r="AB43" s="616" t="n"/>
+      <c r="AC43" s="616" t="n"/>
+      <c r="AD43" s="616" t="n"/>
+      <c r="AE43" s="616" t="n"/>
+      <c r="AF43" s="616" t="n"/>
+      <c r="AG43" s="616" t="n"/>
+      <c r="AH43" s="616" t="n"/>
+      <c r="AI43" s="616" t="n"/>
+      <c r="AJ43" s="616" t="n"/>
+      <c r="AK43" s="616" t="n"/>
+      <c r="AL43" s="616" t="n"/>
+      <c r="AM43" s="616" t="n"/>
+      <c r="AN43" s="616" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="616" t="n"/>
+      <c r="B44" s="616" t="n"/>
+      <c r="C44" s="616" t="n"/>
+      <c r="D44" s="616" t="n"/>
+      <c r="E44" s="616" t="n"/>
+      <c r="F44" s="616" t="n"/>
+      <c r="G44" s="616" t="n"/>
+      <c r="H44" s="616" t="n"/>
+      <c r="I44" s="616" t="n"/>
+      <c r="J44" s="616" t="n"/>
+      <c r="K44" s="616" t="n"/>
+      <c r="L44" s="616" t="n"/>
+      <c r="M44" s="616" t="n"/>
+      <c r="N44" s="616" t="n"/>
+      <c r="O44" s="616" t="n"/>
+      <c r="P44" s="616" t="n"/>
+      <c r="Q44" s="616" t="n"/>
+      <c r="R44" s="616" t="n"/>
+      <c r="S44" s="616" t="n"/>
+      <c r="T44" s="616" t="n"/>
+      <c r="U44" s="616" t="n"/>
+      <c r="V44" s="616" t="n"/>
+      <c r="W44" s="616" t="n"/>
+      <c r="X44" s="616" t="n"/>
+      <c r="Y44" s="616" t="n"/>
+      <c r="Z44" s="616" t="n"/>
+      <c r="AA44" s="616" t="n"/>
+      <c r="AB44" s="616" t="n"/>
+      <c r="AC44" s="616" t="n"/>
+      <c r="AD44" s="616" t="n"/>
+      <c r="AE44" s="616" t="n"/>
+      <c r="AF44" s="616" t="n"/>
+      <c r="AG44" s="616" t="n"/>
+      <c r="AH44" s="616" t="n"/>
+      <c r="AI44" s="616" t="n"/>
+      <c r="AJ44" s="616" t="n"/>
+      <c r="AK44" s="616" t="n"/>
+      <c r="AL44" s="616" t="n"/>
+      <c r="AM44" s="616" t="n"/>
+      <c r="AN44" s="616" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="616" t="n"/>
+      <c r="B45" s="616" t="n"/>
+      <c r="C45" s="616" t="n"/>
+      <c r="D45" s="616" t="n"/>
+      <c r="E45" s="616" t="n"/>
+      <c r="F45" s="616" t="n"/>
+      <c r="G45" s="616" t="n"/>
+      <c r="H45" s="616" t="n"/>
+      <c r="I45" s="616" t="n"/>
+      <c r="J45" s="616" t="n"/>
+      <c r="K45" s="616" t="n"/>
+      <c r="L45" s="616" t="n"/>
+      <c r="M45" s="616" t="n"/>
+      <c r="N45" s="616" t="n"/>
+      <c r="O45" s="616" t="n"/>
+      <c r="P45" s="616" t="n"/>
+      <c r="Q45" s="616" t="n"/>
+      <c r="R45" s="616" t="n"/>
+      <c r="S45" s="616" t="n"/>
+      <c r="T45" s="616" t="n"/>
+      <c r="U45" s="616" t="n"/>
+      <c r="V45" s="616" t="n"/>
+      <c r="W45" s="616" t="n"/>
+      <c r="X45" s="616" t="n"/>
+      <c r="Y45" s="616" t="n"/>
+      <c r="Z45" s="616" t="n"/>
+      <c r="AA45" s="616" t="n"/>
+      <c r="AB45" s="616" t="n"/>
+      <c r="AC45" s="616" t="n"/>
+      <c r="AD45" s="616" t="n"/>
+      <c r="AE45" s="616" t="n"/>
+      <c r="AF45" s="616" t="n"/>
+      <c r="AG45" s="616" t="n"/>
+      <c r="AH45" s="616" t="n"/>
+      <c r="AI45" s="616" t="n"/>
+      <c r="AJ45" s="616" t="n"/>
+      <c r="AK45" s="616" t="n"/>
+      <c r="AL45" s="616" t="n"/>
+      <c r="AM45" s="616" t="n"/>
+      <c r="AN45" s="616" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="616" t="n"/>
+      <c r="B46" s="616" t="n"/>
+      <c r="C46" s="616" t="n"/>
+      <c r="D46" s="616" t="n"/>
+      <c r="E46" s="616" t="n"/>
+      <c r="F46" s="616" t="n"/>
+      <c r="G46" s="616" t="n"/>
+      <c r="H46" s="616" t="n"/>
+      <c r="I46" s="616" t="n"/>
+      <c r="J46" s="616" t="n"/>
+      <c r="K46" s="616" t="n"/>
+      <c r="L46" s="616" t="n"/>
+      <c r="M46" s="616" t="n"/>
+      <c r="N46" s="616" t="n"/>
+      <c r="O46" s="616" t="n"/>
+      <c r="P46" s="616" t="n"/>
+      <c r="Q46" s="616" t="n"/>
+      <c r="R46" s="616" t="n"/>
+      <c r="S46" s="616" t="n"/>
+      <c r="T46" s="616" t="n"/>
+      <c r="U46" s="616" t="n"/>
+      <c r="V46" s="616" t="n"/>
+      <c r="W46" s="616" t="n"/>
+      <c r="X46" s="616" t="n"/>
+      <c r="Y46" s="616" t="n"/>
+      <c r="Z46" s="616" t="n"/>
+      <c r="AA46" s="616" t="n"/>
+      <c r="AB46" s="616" t="n"/>
+      <c r="AC46" s="616" t="n"/>
+      <c r="AD46" s="616" t="n"/>
+      <c r="AE46" s="616" t="n"/>
+      <c r="AF46" s="616" t="n"/>
+      <c r="AG46" s="616" t="n"/>
+      <c r="AH46" s="616" t="n"/>
+      <c r="AI46" s="616" t="n"/>
+      <c r="AJ46" s="616" t="n"/>
+      <c r="AK46" s="616" t="n"/>
+      <c r="AL46" s="616" t="n"/>
+      <c r="AM46" s="616" t="n"/>
+      <c r="AN46" s="616" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="616" t="n"/>
+      <c r="B47" s="616" t="n"/>
+      <c r="C47" s="616" t="n"/>
+      <c r="D47" s="616" t="n"/>
+      <c r="E47" s="616" t="n"/>
+      <c r="F47" s="616" t="n"/>
+      <c r="G47" s="616" t="n"/>
+      <c r="H47" s="616" t="n"/>
+      <c r="I47" s="616" t="n"/>
+      <c r="J47" s="616" t="n"/>
+      <c r="K47" s="616" t="n"/>
+      <c r="L47" s="616" t="n"/>
+      <c r="M47" s="616" t="n"/>
+      <c r="N47" s="616" t="n"/>
+      <c r="O47" s="616" t="n"/>
+      <c r="P47" s="616" t="n"/>
+      <c r="Q47" s="616" t="n"/>
+      <c r="R47" s="616" t="n"/>
+      <c r="S47" s="616" t="n"/>
+      <c r="T47" s="616" t="n"/>
+      <c r="U47" s="616" t="n"/>
+      <c r="V47" s="616" t="n"/>
+      <c r="W47" s="616" t="n"/>
+      <c r="X47" s="616" t="n"/>
+      <c r="Y47" s="616" t="n"/>
+      <c r="Z47" s="616" t="n"/>
+      <c r="AA47" s="616" t="n"/>
+      <c r="AB47" s="616" t="n"/>
+      <c r="AC47" s="616" t="n"/>
+      <c r="AD47" s="616" t="n"/>
+      <c r="AE47" s="616" t="n"/>
+      <c r="AF47" s="616" t="n"/>
+      <c r="AG47" s="616" t="n"/>
+      <c r="AH47" s="616" t="n"/>
+      <c r="AI47" s="616" t="n"/>
+      <c r="AJ47" s="616" t="n"/>
+      <c r="AK47" s="616" t="n"/>
+      <c r="AL47" s="616" t="n"/>
+      <c r="AM47" s="616" t="n"/>
+      <c r="AN47" s="616" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="616" t="n"/>
+      <c r="B48" s="616" t="n"/>
+      <c r="C48" s="616" t="n"/>
+      <c r="D48" s="616" t="n"/>
+      <c r="E48" s="616" t="n"/>
+      <c r="F48" s="616" t="n"/>
+      <c r="G48" s="616" t="n"/>
+      <c r="H48" s="616" t="n"/>
+      <c r="I48" s="616" t="n"/>
+      <c r="J48" s="616" t="n"/>
+      <c r="K48" s="616" t="n"/>
+      <c r="L48" s="616" t="n"/>
+      <c r="M48" s="616" t="n"/>
+      <c r="N48" s="616" t="n"/>
+      <c r="O48" s="616" t="n"/>
+      <c r="P48" s="616" t="n"/>
+      <c r="Q48" s="616" t="n"/>
+      <c r="R48" s="616" t="n"/>
+      <c r="S48" s="616" t="n"/>
+      <c r="T48" s="616" t="n"/>
+      <c r="U48" s="616" t="n"/>
+      <c r="V48" s="616" t="n"/>
+      <c r="W48" s="616" t="n"/>
+      <c r="X48" s="616" t="n"/>
+      <c r="Y48" s="616" t="n"/>
+      <c r="Z48" s="616" t="n"/>
+      <c r="AA48" s="616" t="n"/>
+      <c r="AB48" s="616" t="n"/>
+      <c r="AC48" s="616" t="n"/>
+      <c r="AD48" s="616" t="n"/>
+      <c r="AE48" s="616" t="n"/>
+      <c r="AF48" s="616" t="n"/>
+      <c r="AG48" s="616" t="n"/>
+      <c r="AH48" s="616" t="n"/>
+      <c r="AI48" s="616" t="n"/>
+      <c r="AJ48" s="616" t="n"/>
+      <c r="AK48" s="616" t="n"/>
+      <c r="AL48" s="616" t="n"/>
+      <c r="AM48" s="616" t="n"/>
+      <c r="AN48" s="616" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="616" t="n"/>
+      <c r="B49" s="616" t="n"/>
+      <c r="C49" s="616" t="n"/>
+      <c r="D49" s="616" t="n"/>
+      <c r="E49" s="616" t="n"/>
+      <c r="F49" s="616" t="n"/>
+      <c r="G49" s="616" t="n"/>
+      <c r="H49" s="616" t="n"/>
+      <c r="I49" s="616" t="n"/>
+      <c r="J49" s="616" t="n"/>
+      <c r="K49" s="616" t="n"/>
+      <c r="L49" s="616" t="n"/>
+      <c r="M49" s="616" t="n"/>
+      <c r="N49" s="616" t="n"/>
+      <c r="O49" s="616" t="n"/>
+      <c r="P49" s="616" t="n"/>
+      <c r="Q49" s="616" t="n"/>
+      <c r="R49" s="616" t="n"/>
+      <c r="S49" s="616" t="n"/>
+      <c r="T49" s="616" t="n"/>
+      <c r="U49" s="616" t="n"/>
+      <c r="V49" s="616" t="n"/>
+      <c r="W49" s="616" t="n"/>
+      <c r="X49" s="616" t="n"/>
+      <c r="Y49" s="616" t="n"/>
+      <c r="Z49" s="616" t="n"/>
+      <c r="AA49" s="616" t="n"/>
+      <c r="AB49" s="616" t="n"/>
+      <c r="AC49" s="616" t="n"/>
+      <c r="AD49" s="616" t="n"/>
+      <c r="AE49" s="616" t="n"/>
+      <c r="AF49" s="616" t="n"/>
+      <c r="AG49" s="616" t="n"/>
+      <c r="AH49" s="616" t="n"/>
+      <c r="AI49" s="616" t="n"/>
+      <c r="AJ49" s="616" t="n"/>
+      <c r="AK49" s="616" t="n"/>
+      <c r="AL49" s="616" t="n"/>
+      <c r="AM49" s="616" t="n"/>
+      <c r="AN49" s="616" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="616" t="n"/>
+      <c r="B50" s="616" t="n"/>
+      <c r="C50" s="616" t="n"/>
+      <c r="D50" s="616" t="n"/>
+      <c r="E50" s="616" t="n"/>
+      <c r="F50" s="616" t="n"/>
+      <c r="G50" s="616" t="n"/>
+      <c r="H50" s="616" t="n"/>
+      <c r="I50" s="616" t="n"/>
+      <c r="J50" s="616" t="n"/>
+      <c r="K50" s="616" t="n"/>
+      <c r="L50" s="616" t="n"/>
+      <c r="M50" s="616" t="n"/>
+      <c r="N50" s="616" t="n"/>
+      <c r="O50" s="616" t="n"/>
+      <c r="P50" s="616" t="n"/>
+      <c r="Q50" s="616" t="n"/>
+      <c r="R50" s="616" t="n"/>
+      <c r="S50" s="616" t="n"/>
+      <c r="T50" s="616" t="n"/>
+      <c r="U50" s="616" t="n"/>
+      <c r="V50" s="616" t="n"/>
+      <c r="W50" s="616" t="n"/>
+      <c r="X50" s="616" t="n"/>
+      <c r="Y50" s="616" t="n"/>
+      <c r="Z50" s="616" t="n"/>
+      <c r="AA50" s="616" t="n"/>
+      <c r="AB50" s="616" t="n"/>
+      <c r="AC50" s="616" t="n"/>
+      <c r="AD50" s="616" t="n"/>
+      <c r="AE50" s="616" t="n"/>
+      <c r="AF50" s="616" t="n"/>
+      <c r="AG50" s="616" t="n"/>
+      <c r="AH50" s="616" t="n"/>
+      <c r="AI50" s="616" t="n"/>
+      <c r="AJ50" s="616" t="n"/>
+      <c r="AK50" s="616" t="n"/>
+      <c r="AL50" s="616" t="n"/>
+      <c r="AM50" s="616" t="n"/>
+      <c r="AN50" s="616" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+  <mergeCells count="92">
+    <mergeCell ref="AI15:AK15"/>
+    <mergeCell ref="AL16:AN16"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="AD8:AH8"/>
+    <mergeCell ref="AL18:AN18"/>
+    <mergeCell ref="I4:AD4"/>
+    <mergeCell ref="M12:X12"/>
+    <mergeCell ref="I1:AD3"/>
+    <mergeCell ref="AE4:AH4"/>
+    <mergeCell ref="C18:L18"/>
+    <mergeCell ref="Y11:AC11"/>
+    <mergeCell ref="AD11:AH11"/>
+    <mergeCell ref="AI17:AK17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="Y13:AC13"/>
+    <mergeCell ref="AL15:AN15"/>
+    <mergeCell ref="AI1:AN1"/>
+    <mergeCell ref="M9:X9"/>
+    <mergeCell ref="C12:L12"/>
+    <mergeCell ref="AI9:AK9"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="Y8:AC8"/>
+    <mergeCell ref="AD9:AH9"/>
+    <mergeCell ref="M11:X11"/>
+    <mergeCell ref="AI11:AK11"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="I5:AD5"/>
+    <mergeCell ref="AE5:AH5"/>
+    <mergeCell ref="Y9:AC9"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="M15:X15"/>
+    <mergeCell ref="AD10:AH10"/>
+    <mergeCell ref="AL8:AN8"/>
+    <mergeCell ref="Y14:AC14"/>
+    <mergeCell ref="C15:L15"/>
+    <mergeCell ref="AL17:AN17"/>
+    <mergeCell ref="AI3:AN3"/>
+    <mergeCell ref="AL10:AN10"/>
+    <mergeCell ref="AI5:AN5"/>
+    <mergeCell ref="AL9:AN9"/>
+    <mergeCell ref="AI8:AK8"/>
+    <mergeCell ref="C10:L10"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C16:L16"/>
+    <mergeCell ref="Y12:AC12"/>
+    <mergeCell ref="C9:L9"/>
+    <mergeCell ref="AL11:AN11"/>
+    <mergeCell ref="AI10:AK10"/>
+    <mergeCell ref="A7:AN7"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C11:L11"/>
+    <mergeCell ref="AE1:AH1"/>
+    <mergeCell ref="AD12:AH12"/>
+    <mergeCell ref="AL13:AN13"/>
+    <mergeCell ref="AD14:AH14"/>
+    <mergeCell ref="AD13:AH13"/>
+    <mergeCell ref="A1:H5"/>
+    <mergeCell ref="AD15:AH15"/>
+    <mergeCell ref="AI12:AK12"/>
+    <mergeCell ref="C14:L14"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="Y17:AC17"/>
+    <mergeCell ref="AI2:AN2"/>
+    <mergeCell ref="M14:X14"/>
+    <mergeCell ref="AE3:AH3"/>
+    <mergeCell ref="AI14:AK14"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="AI13:AK13"/>
+    <mergeCell ref="AD18:AH18"/>
+    <mergeCell ref="AD17:AH17"/>
+    <mergeCell ref="C8:L8"/>
+    <mergeCell ref="M10:X10"/>
+    <mergeCell ref="C17:L17"/>
+    <mergeCell ref="AI4:AN4"/>
+    <mergeCell ref="M13:X13"/>
+    <mergeCell ref="Y15:AC15"/>
+    <mergeCell ref="M16:X16"/>
+    <mergeCell ref="AL12:AN12"/>
+    <mergeCell ref="AI16:AK16"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="M18:X18"/>
+    <mergeCell ref="AL14:AN14"/>
+    <mergeCell ref="AI18:AK18"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="M8:X8"/>
+    <mergeCell ref="Y10:AC10"/>
+    <mergeCell ref="M17:X17"/>
+    <mergeCell ref="Y16:AC16"/>
+    <mergeCell ref="AE2:AH2"/>
+    <mergeCell ref="Y18:AC18"/>
+    <mergeCell ref="AD16:AH16"/>
+    <mergeCell ref="A13:B13"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation sqref="F5:F16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Use only the controlled dropdown values." promptTitle="Controlled dropdown" prompt="Select a controlled value from the list." type="list">
@@ -9933,1506 +11500,4 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AN13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="2.33" customWidth="1" style="329" min="1" max="1"/>
-    <col width="2.33" customWidth="1" style="329" min="2" max="2"/>
-    <col width="2.33" customWidth="1" style="329" min="3" max="3"/>
-    <col width="2.33" customWidth="1" style="329" min="4" max="4"/>
-    <col width="2.33" customWidth="1" style="329" min="5" max="5"/>
-    <col width="2.33" customWidth="1" style="329" min="6" max="6"/>
-    <col width="2.33" customWidth="1" style="329" min="7" max="7"/>
-    <col width="2.33" customWidth="1" style="329" min="8" max="8"/>
-    <col width="2.33" customWidth="1" style="329" min="9" max="9"/>
-    <col width="2.33" customWidth="1" style="329" min="10" max="10"/>
-    <col width="2.33" customWidth="1" style="329" min="11" max="11"/>
-    <col width="2.33" customWidth="1" style="329" min="12" max="12"/>
-    <col width="2.33" customWidth="1" style="329" min="13" max="13"/>
-    <col width="2.33" customWidth="1" style="329" min="14" max="14"/>
-    <col width="2.33" customWidth="1" style="329" min="15" max="15"/>
-    <col width="2.33" customWidth="1" style="329" min="16" max="16"/>
-    <col width="2.33" customWidth="1" style="329" min="17" max="17"/>
-    <col width="2.33" customWidth="1" style="329" min="18" max="18"/>
-    <col width="2.33" customWidth="1" style="329" min="19" max="19"/>
-    <col width="2.33" customWidth="1" style="329" min="20" max="20"/>
-    <col width="2.33" customWidth="1" style="329" min="21" max="21"/>
-    <col width="2.33" customWidth="1" style="329" min="22" max="22"/>
-    <col width="2.33" customWidth="1" style="329" min="23" max="23"/>
-    <col width="2.33" customWidth="1" style="329" min="24" max="24"/>
-    <col width="2.33" customWidth="1" style="329" min="25" max="25"/>
-    <col width="2.33" customWidth="1" style="329" min="26" max="26"/>
-    <col width="2.33" customWidth="1" style="329" min="27" max="27"/>
-    <col width="2.33" customWidth="1" style="329" min="28" max="28"/>
-    <col width="2.33" customWidth="1" style="329" min="29" max="29"/>
-    <col width="2.33" customWidth="1" style="329" min="30" max="30"/>
-    <col width="2.33" customWidth="1" style="329" min="31" max="31"/>
-    <col width="2.33" customWidth="1" style="329" min="32" max="32"/>
-    <col width="2.33" customWidth="1" style="329" min="33" max="33"/>
-    <col width="2.33" customWidth="1" style="329" min="34" max="34"/>
-    <col width="2.33" customWidth="1" style="329" min="35" max="35"/>
-    <col width="2.33" customWidth="1" style="329" min="36" max="36"/>
-    <col width="2.33" customWidth="1" style="329" min="37" max="37"/>
-    <col width="2.33" customWidth="1" style="329" min="38" max="38"/>
-    <col width="2.33" customWidth="1" style="329" min="39" max="39"/>
-    <col width="2.33" customWidth="1" style="329" min="40" max="40"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15" customHeight="1" s="329">
-      <c r="A1" s="497" t="inlineStr">
-        <is>
-          <t>Upstream References / Import Guidance</t>
-        </is>
-      </c>
-      <c r="B1" s="527" t="n"/>
-      <c r="C1" s="527" t="n"/>
-      <c r="D1" s="527" t="n"/>
-      <c r="E1" s="527" t="n"/>
-      <c r="F1" s="527" t="n"/>
-      <c r="G1" s="527" t="n"/>
-      <c r="H1" s="498" t="n"/>
-      <c r="I1" s="417" t="n"/>
-      <c r="J1" s="418" t="n"/>
-      <c r="K1" s="418" t="n"/>
-      <c r="L1" s="418" t="n"/>
-      <c r="M1" s="418" t="n"/>
-      <c r="N1" s="418" t="n"/>
-      <c r="O1" s="418" t="n"/>
-      <c r="P1" s="418" t="n"/>
-      <c r="Q1" s="418" t="n"/>
-      <c r="R1" s="418" t="n"/>
-      <c r="S1" s="418" t="n"/>
-      <c r="T1" s="418" t="n"/>
-      <c r="U1" s="418" t="n"/>
-      <c r="V1" s="418" t="n"/>
-      <c r="W1" s="418" t="n"/>
-      <c r="X1" s="418" t="n"/>
-      <c r="Y1" s="418" t="n"/>
-      <c r="Z1" s="418" t="n"/>
-      <c r="AA1" s="418" t="n"/>
-      <c r="AB1" s="418" t="n"/>
-      <c r="AC1" s="418" t="n"/>
-      <c r="AD1" s="419" t="n"/>
-      <c r="AE1" s="420" t="n"/>
-      <c r="AF1" s="421" t="n"/>
-      <c r="AG1" s="421" t="n"/>
-      <c r="AH1" s="422" t="n"/>
-      <c r="AI1" s="423" t="n"/>
-      <c r="AJ1" s="424" t="n"/>
-      <c r="AK1" s="424" t="n"/>
-      <c r="AL1" s="424" t="n"/>
-      <c r="AM1" s="424" t="n"/>
-      <c r="AN1" s="425" t="n"/>
-    </row>
-    <row r="2" ht="15" customHeight="1" s="329">
-      <c r="A2" s="499" t="inlineStr">
-        <is>
-          <t>Incoming verification event record for outsourced process returns and discrete disposition decisions.</t>
-        </is>
-      </c>
-      <c r="H2" s="500" t="n"/>
-      <c r="I2" s="428" t="n"/>
-      <c r="J2" s="429" t="n"/>
-      <c r="K2" s="429" t="n"/>
-      <c r="L2" s="429" t="n"/>
-      <c r="M2" s="429" t="n"/>
-      <c r="N2" s="429" t="n"/>
-      <c r="O2" s="429" t="n"/>
-      <c r="P2" s="429" t="n"/>
-      <c r="Q2" s="429" t="n"/>
-      <c r="R2" s="429" t="n"/>
-      <c r="S2" s="429" t="n"/>
-      <c r="T2" s="429" t="n"/>
-      <c r="U2" s="429" t="n"/>
-      <c r="V2" s="429" t="n"/>
-      <c r="W2" s="429" t="n"/>
-      <c r="X2" s="429" t="n"/>
-      <c r="Y2" s="429" t="n"/>
-      <c r="Z2" s="429" t="n"/>
-      <c r="AA2" s="429" t="n"/>
-      <c r="AB2" s="429" t="n"/>
-      <c r="AC2" s="429" t="n"/>
-      <c r="AD2" s="430" t="n"/>
-      <c r="AE2" s="431" t="n"/>
-      <c r="AF2" s="432" t="n"/>
-      <c r="AG2" s="432" t="n"/>
-      <c r="AH2" s="433" t="n"/>
-      <c r="AI2" s="434" t="n"/>
-      <c r="AJ2" s="435" t="n"/>
-      <c r="AK2" s="435" t="n"/>
-      <c r="AL2" s="435" t="n"/>
-      <c r="AM2" s="435" t="n"/>
-      <c r="AN2" s="436" t="n"/>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="329">
-      <c r="A3" s="501" t="n"/>
-      <c r="B3" s="502" t="n"/>
-      <c r="C3" s="502" t="n"/>
-      <c r="D3" s="502" t="n"/>
-      <c r="E3" s="502" t="n"/>
-      <c r="F3" s="502" t="n"/>
-      <c r="G3" s="502" t="n"/>
-      <c r="H3" s="500" t="n"/>
-      <c r="I3" s="428" t="n"/>
-      <c r="J3" s="429" t="n"/>
-      <c r="K3" s="429" t="n"/>
-      <c r="L3" s="429" t="n"/>
-      <c r="M3" s="429" t="n"/>
-      <c r="N3" s="429" t="n"/>
-      <c r="O3" s="429" t="n"/>
-      <c r="P3" s="429" t="n"/>
-      <c r="Q3" s="429" t="n"/>
-      <c r="R3" s="429" t="n"/>
-      <c r="S3" s="429" t="n"/>
-      <c r="T3" s="429" t="n"/>
-      <c r="U3" s="429" t="n"/>
-      <c r="V3" s="429" t="n"/>
-      <c r="W3" s="429" t="n"/>
-      <c r="X3" s="429" t="n"/>
-      <c r="Y3" s="429" t="n"/>
-      <c r="Z3" s="429" t="n"/>
-      <c r="AA3" s="429" t="n"/>
-      <c r="AB3" s="429" t="n"/>
-      <c r="AC3" s="429" t="n"/>
-      <c r="AD3" s="430" t="n"/>
-      <c r="AE3" s="431" t="n"/>
-      <c r="AF3" s="432" t="n"/>
-      <c r="AG3" s="432" t="n"/>
-      <c r="AH3" s="433" t="n"/>
-      <c r="AI3" s="434" t="n"/>
-      <c r="AJ3" s="435" t="n"/>
-      <c r="AK3" s="435" t="n"/>
-      <c r="AL3" s="435" t="n"/>
-      <c r="AM3" s="435" t="n"/>
-      <c r="AN3" s="436" t="n"/>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="329">
-      <c r="A4" s="503" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="B4" s="504" t="inlineStr">
-        <is>
-          <t>Value / Reference</t>
-        </is>
-      </c>
-      <c r="C4" s="504" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="D4" s="502" t="n"/>
-      <c r="E4" s="502" t="n"/>
-      <c r="F4" s="502" t="n"/>
-      <c r="G4" s="502" t="n"/>
-      <c r="H4" s="500" t="n"/>
-      <c r="I4" s="437" t="n"/>
-      <c r="J4" s="438" t="n"/>
-      <c r="K4" s="438" t="n"/>
-      <c r="L4" s="438" t="n"/>
-      <c r="M4" s="438" t="n"/>
-      <c r="N4" s="438" t="n"/>
-      <c r="O4" s="438" t="n"/>
-      <c r="P4" s="438" t="n"/>
-      <c r="Q4" s="438" t="n"/>
-      <c r="R4" s="438" t="n"/>
-      <c r="S4" s="438" t="n"/>
-      <c r="T4" s="438" t="n"/>
-      <c r="U4" s="438" t="n"/>
-      <c r="V4" s="438" t="n"/>
-      <c r="W4" s="438" t="n"/>
-      <c r="X4" s="438" t="n"/>
-      <c r="Y4" s="438" t="n"/>
-      <c r="Z4" s="438" t="n"/>
-      <c r="AA4" s="438" t="n"/>
-      <c r="AB4" s="438" t="n"/>
-      <c r="AC4" s="438" t="n"/>
-      <c r="AD4" s="439" t="n"/>
-      <c r="AE4" s="431" t="n"/>
-      <c r="AF4" s="432" t="n"/>
-      <c r="AG4" s="432" t="n"/>
-      <c r="AH4" s="433" t="n"/>
-      <c r="AI4" s="434" t="n"/>
-      <c r="AJ4" s="435" t="n"/>
-      <c r="AK4" s="435" t="n"/>
-      <c r="AL4" s="435" t="n"/>
-      <c r="AM4" s="435" t="n"/>
-      <c r="AN4" s="436" t="n"/>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="329">
-      <c r="A5" s="506" t="inlineStr">
-        <is>
-          <t>Source of Truth</t>
-        </is>
-      </c>
-      <c r="B5" s="507" t="inlineStr">
-        <is>
-          <t>Epicor transaction + M365 evidence</t>
-        </is>
-      </c>
-      <c r="C5" s="507" t="inlineStr">
-        <is>
-          <t>Do not duplicate ERP/M365/ANNEX master data.</t>
-        </is>
-      </c>
-      <c r="D5" s="520" t="n"/>
-      <c r="E5" s="520" t="n"/>
-      <c r="F5" s="520" t="n"/>
-      <c r="G5" s="520" t="n"/>
-      <c r="H5" s="521" t="n"/>
-      <c r="I5" s="443" t="n"/>
-      <c r="J5" s="444" t="n"/>
-      <c r="K5" s="444" t="n"/>
-      <c r="L5" s="444" t="n"/>
-      <c r="M5" s="444" t="n"/>
-      <c r="N5" s="444" t="n"/>
-      <c r="O5" s="444" t="n"/>
-      <c r="P5" s="444" t="n"/>
-      <c r="Q5" s="444" t="n"/>
-      <c r="R5" s="444" t="n"/>
-      <c r="S5" s="444" t="n"/>
-      <c r="T5" s="444" t="n"/>
-      <c r="U5" s="444" t="n"/>
-      <c r="V5" s="444" t="n"/>
-      <c r="W5" s="444" t="n"/>
-      <c r="X5" s="444" t="n"/>
-      <c r="Y5" s="444" t="n"/>
-      <c r="Z5" s="444" t="n"/>
-      <c r="AA5" s="444" t="n"/>
-      <c r="AB5" s="444" t="n"/>
-      <c r="AC5" s="444" t="n"/>
-      <c r="AD5" s="445" t="n"/>
-      <c r="AE5" s="446" t="n"/>
-      <c r="AF5" s="447" t="n"/>
-      <c r="AG5" s="447" t="n"/>
-      <c r="AH5" s="448" t="n"/>
-      <c r="AI5" s="449" t="n"/>
-      <c r="AJ5" s="450" t="n"/>
-      <c r="AK5" s="450" t="n"/>
-      <c r="AL5" s="450" t="n"/>
-      <c r="AM5" s="450" t="n"/>
-      <c r="AN5" s="451" t="n"/>
-    </row>
-    <row r="6" ht="20" customHeight="1" s="329">
-      <c r="A6" s="509" t="inlineStr">
-        <is>
-          <t>Cross-Reference Boundary</t>
-        </is>
-      </c>
-      <c r="B6" s="510" t="inlineStr">
-        <is>
-          <t>This form does not replace SOP-402; it records the evidence, data or decision required by that SOP.
-Rules, matrices, dictionaries, acceptance criteria and data definitions belong in ANNEX-PUR-001/002/003 + ANNEX-ENG-002; do not copy ANNEX content into the live data-entry body.
-System-of-record / source-of-truth boundary: Epicor transaction + M365 evidence. If the master data already live there, reference or import them; do not re-key without need.</t>
-        </is>
-      </c>
-      <c r="C6" s="511" t="inlineStr">
-        <is>
-          <t>This form does not replace SOP-402; it records the evidence, data or decision required by that SOP.
-Rules, matrices, dictionaries, acceptance criteria and data definitions belong in ANNEX-PUR-001/002/003 + ANNEX-ENG-002; do not copy ANNEX content into the live data-entry body.
-System-of-record / source-of-truth boundary: Epicor transaction + M365 evidence. If the master data already live there, reference or import them; do not re-key without need.</t>
-        </is>
-      </c>
-      <c r="D6" s="457" t="n"/>
-      <c r="E6" s="457" t="n"/>
-      <c r="F6" s="457" t="n"/>
-      <c r="G6" s="457" t="n"/>
-      <c r="H6" s="457" t="n"/>
-      <c r="I6" s="457" t="n"/>
-      <c r="J6" s="457" t="n"/>
-      <c r="K6" s="457" t="n"/>
-      <c r="L6" s="457" t="n"/>
-      <c r="M6" s="457" t="n"/>
-      <c r="N6" s="457" t="n"/>
-      <c r="O6" s="457" t="n"/>
-      <c r="P6" s="457" t="n"/>
-      <c r="Q6" s="457" t="n"/>
-      <c r="R6" s="457" t="n"/>
-      <c r="S6" s="457" t="n"/>
-      <c r="T6" s="457" t="n"/>
-      <c r="U6" s="457" t="n"/>
-      <c r="V6" s="457" t="n"/>
-      <c r="W6" s="457" t="n"/>
-      <c r="X6" s="457" t="n"/>
-      <c r="Y6" s="457" t="n"/>
-      <c r="Z6" s="457" t="n"/>
-      <c r="AA6" s="457" t="n"/>
-      <c r="AB6" s="457" t="n"/>
-      <c r="AC6" s="457" t="n"/>
-      <c r="AD6" s="457" t="n"/>
-      <c r="AE6" s="457" t="n"/>
-      <c r="AF6" s="457" t="n"/>
-      <c r="AG6" s="457" t="n"/>
-      <c r="AH6" s="457" t="n"/>
-      <c r="AI6" s="457" t="n"/>
-      <c r="AJ6" s="457" t="n"/>
-      <c r="AK6" s="457" t="n"/>
-      <c r="AL6" s="457" t="n"/>
-      <c r="AM6" s="457" t="n"/>
-      <c r="AN6" s="460" t="n"/>
-    </row>
-    <row r="7" ht="20" customHeight="1" s="329">
-      <c r="A7" s="512" t="inlineStr">
-        <is>
-          <t>SOP-402</t>
-        </is>
-      </c>
-      <c r="B7" s="513" t="inlineStr">
-        <is>
-          <t>SOP-402 — Xác minh vật liệu, truy xuất và phòng chống vật tư giả/không rõ nguồn gốc | HESEM QMS</t>
-        </is>
-      </c>
-      <c r="C7" s="514" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/01-SOPs/04-SOP-400/sop-402-material-verification-traceability-and-counterfeit-prevention.html</t>
-        </is>
-      </c>
-      <c r="D7" s="341" t="n"/>
-      <c r="E7" s="341" t="n"/>
-      <c r="F7" s="341" t="n"/>
-      <c r="G7" s="341" t="n"/>
-      <c r="H7" s="341" t="n"/>
-      <c r="I7" s="341" t="n"/>
-      <c r="J7" s="341" t="n"/>
-      <c r="K7" s="341" t="n"/>
-      <c r="L7" s="341" t="n"/>
-      <c r="M7" s="341" t="n"/>
-      <c r="N7" s="341" t="n"/>
-      <c r="O7" s="341" t="n"/>
-      <c r="P7" s="341" t="n"/>
-      <c r="Q7" s="341" t="n"/>
-      <c r="R7" s="341" t="n"/>
-      <c r="S7" s="341" t="n"/>
-      <c r="T7" s="341" t="n"/>
-      <c r="U7" s="341" t="n"/>
-      <c r="V7" s="341" t="n"/>
-      <c r="W7" s="341" t="n"/>
-      <c r="X7" s="341" t="n"/>
-      <c r="Y7" s="341" t="n"/>
-      <c r="Z7" s="341" t="n"/>
-      <c r="AA7" s="341" t="n"/>
-      <c r="AB7" s="341" t="n"/>
-      <c r="AC7" s="341" t="n"/>
-      <c r="AD7" s="341" t="n"/>
-      <c r="AE7" s="341" t="n"/>
-      <c r="AF7" s="341" t="n"/>
-      <c r="AG7" s="341" t="n"/>
-      <c r="AH7" s="341" t="n"/>
-      <c r="AI7" s="341" t="n"/>
-      <c r="AJ7" s="341" t="n"/>
-      <c r="AK7" s="341" t="n"/>
-      <c r="AL7" s="341" t="n"/>
-      <c r="AM7" s="341" t="n"/>
-      <c r="AN7" s="464" t="n"/>
-    </row>
-    <row r="8" ht="20" customHeight="1" s="329">
-      <c r="A8" s="461" t="inlineStr">
-        <is>
-          <t>ANNEX-PUR-001</t>
-        </is>
-      </c>
-      <c r="B8" s="462" t="inlineStr">
-        <is>
-          <t>ANNEX-PUR-001 — Mô hình rủi ro nhà cung cấp và phương pháp scorecard</t>
-        </is>
-      </c>
-      <c r="C8" s="515" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-001-supplier-risk-model-and-scorecard-method.html</t>
-        </is>
-      </c>
-      <c r="D8" s="353" t="n"/>
-      <c r="E8" s="353" t="n"/>
-      <c r="F8" s="353" t="n"/>
-      <c r="G8" s="353" t="n"/>
-      <c r="H8" s="353" t="n"/>
-      <c r="I8" s="353" t="n"/>
-      <c r="J8" s="353" t="n"/>
-      <c r="K8" s="353" t="n"/>
-      <c r="L8" s="353" t="n"/>
-      <c r="M8" s="353" t="n"/>
-      <c r="N8" s="353" t="n"/>
-      <c r="O8" s="353" t="n"/>
-      <c r="P8" s="353" t="n"/>
-      <c r="Q8" s="353" t="n"/>
-      <c r="R8" s="353" t="n"/>
-      <c r="S8" s="353" t="n"/>
-      <c r="T8" s="353" t="n"/>
-      <c r="U8" s="353" t="n"/>
-      <c r="V8" s="353" t="n"/>
-      <c r="W8" s="353" t="n"/>
-      <c r="X8" s="353" t="n"/>
-      <c r="Y8" s="353" t="n"/>
-      <c r="Z8" s="353" t="n"/>
-      <c r="AA8" s="353" t="n"/>
-      <c r="AB8" s="353" t="n"/>
-      <c r="AC8" s="353" t="n"/>
-      <c r="AD8" s="353" t="n"/>
-      <c r="AE8" s="353" t="n"/>
-      <c r="AF8" s="353" t="n"/>
-      <c r="AG8" s="353" t="n"/>
-      <c r="AH8" s="353" t="n"/>
-      <c r="AI8" s="353" t="n"/>
-      <c r="AJ8" s="353" t="n"/>
-      <c r="AK8" s="353" t="n"/>
-      <c r="AL8" s="353" t="n"/>
-      <c r="AM8" s="353" t="n"/>
-      <c r="AN8" s="516" t="n"/>
-    </row>
-    <row r="9" ht="20" customHeight="1" s="329">
-      <c r="A9" s="461" t="inlineStr">
-        <is>
-          <t>ANNEX-PUR-002</t>
-        </is>
-      </c>
-      <c r="B9" s="462" t="inlineStr">
-        <is>
-          <t>ANNEX-PUR-002 — Gói kiểm soát outsource / special process / cert flow-down</t>
-        </is>
-      </c>
-      <c r="C9" s="515" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-002-outsource-special-process-pack.html</t>
-        </is>
-      </c>
-      <c r="D9" s="353" t="n"/>
-      <c r="E9" s="353" t="n"/>
-      <c r="F9" s="353" t="n"/>
-      <c r="G9" s="353" t="n"/>
-      <c r="H9" s="353" t="n"/>
-      <c r="I9" s="353" t="n"/>
-      <c r="J9" s="353" t="n"/>
-      <c r="K9" s="353" t="n"/>
-      <c r="L9" s="353" t="n"/>
-      <c r="M9" s="353" t="n"/>
-      <c r="N9" s="353" t="n"/>
-      <c r="O9" s="353" t="n"/>
-      <c r="P9" s="353" t="n"/>
-      <c r="Q9" s="353" t="n"/>
-      <c r="R9" s="353" t="n"/>
-      <c r="S9" s="353" t="n"/>
-      <c r="T9" s="353" t="n"/>
-      <c r="U9" s="353" t="n"/>
-      <c r="V9" s="353" t="n"/>
-      <c r="W9" s="353" t="n"/>
-      <c r="X9" s="353" t="n"/>
-      <c r="Y9" s="353" t="n"/>
-      <c r="Z9" s="353" t="n"/>
-      <c r="AA9" s="353" t="n"/>
-      <c r="AB9" s="353" t="n"/>
-      <c r="AC9" s="353" t="n"/>
-      <c r="AD9" s="353" t="n"/>
-      <c r="AE9" s="353" t="n"/>
-      <c r="AF9" s="353" t="n"/>
-      <c r="AG9" s="353" t="n"/>
-      <c r="AH9" s="353" t="n"/>
-      <c r="AI9" s="353" t="n"/>
-      <c r="AJ9" s="353" t="n"/>
-      <c r="AK9" s="353" t="n"/>
-      <c r="AL9" s="353" t="n"/>
-      <c r="AM9" s="353" t="n"/>
-      <c r="AN9" s="516" t="n"/>
-    </row>
-    <row r="10" ht="20" customHeight="1" s="329">
-      <c r="A10" s="461" t="inlineStr">
-        <is>
-          <t>ANNEX-PUR-003</t>
-        </is>
-      </c>
-      <c r="B10" s="462" t="inlineStr">
-        <is>
-          <t>ANNEX-PUR-003 — Approved processor list, scope approval và rule tạm ngưng</t>
-        </is>
-      </c>
-      <c r="C10" s="515" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-003-approved-processor-list.html</t>
-        </is>
-      </c>
-      <c r="D10" s="353" t="n"/>
-      <c r="E10" s="353" t="n"/>
-      <c r="F10" s="353" t="n"/>
-      <c r="G10" s="353" t="n"/>
-      <c r="H10" s="353" t="n"/>
-      <c r="I10" s="353" t="n"/>
-      <c r="J10" s="353" t="n"/>
-      <c r="K10" s="353" t="n"/>
-      <c r="L10" s="353" t="n"/>
-      <c r="M10" s="353" t="n"/>
-      <c r="N10" s="353" t="n"/>
-      <c r="O10" s="353" t="n"/>
-      <c r="P10" s="353" t="n"/>
-      <c r="Q10" s="353" t="n"/>
-      <c r="R10" s="353" t="n"/>
-      <c r="S10" s="353" t="n"/>
-      <c r="T10" s="353" t="n"/>
-      <c r="U10" s="353" t="n"/>
-      <c r="V10" s="353" t="n"/>
-      <c r="W10" s="353" t="n"/>
-      <c r="X10" s="353" t="n"/>
-      <c r="Y10" s="353" t="n"/>
-      <c r="Z10" s="353" t="n"/>
-      <c r="AA10" s="353" t="n"/>
-      <c r="AB10" s="353" t="n"/>
-      <c r="AC10" s="353" t="n"/>
-      <c r="AD10" s="353" t="n"/>
-      <c r="AE10" s="353" t="n"/>
-      <c r="AF10" s="353" t="n"/>
-      <c r="AG10" s="353" t="n"/>
-      <c r="AH10" s="353" t="n"/>
-      <c r="AI10" s="353" t="n"/>
-      <c r="AJ10" s="353" t="n"/>
-      <c r="AK10" s="353" t="n"/>
-      <c r="AL10" s="353" t="n"/>
-      <c r="AM10" s="353" t="n"/>
-      <c r="AN10" s="516" t="n"/>
-    </row>
-    <row r="11" ht="20" customHeight="1" s="329">
-      <c r="A11" s="461" t="inlineStr">
-        <is>
-          <t>ANNEX-ENG-002</t>
-        </is>
-      </c>
-      <c r="B11" s="462" t="inlineStr">
-        <is>
-          <t>ANNEX-ENG-002 — Approved materials list, source restriction và rule thay thế</t>
-        </is>
-      </c>
-      <c r="C11" s="515" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-eng-002-approved-materials-list.html</t>
-        </is>
-      </c>
-      <c r="D11" s="353" t="n"/>
-      <c r="E11" s="353" t="n"/>
-      <c r="F11" s="353" t="n"/>
-      <c r="G11" s="353" t="n"/>
-      <c r="H11" s="353" t="n"/>
-      <c r="I11" s="353" t="n"/>
-      <c r="J11" s="353" t="n"/>
-      <c r="K11" s="353" t="n"/>
-      <c r="L11" s="353" t="n"/>
-      <c r="M11" s="353" t="n"/>
-      <c r="N11" s="353" t="n"/>
-      <c r="O11" s="353" t="n"/>
-      <c r="P11" s="353" t="n"/>
-      <c r="Q11" s="353" t="n"/>
-      <c r="R11" s="353" t="n"/>
-      <c r="S11" s="353" t="n"/>
-      <c r="T11" s="353" t="n"/>
-      <c r="U11" s="353" t="n"/>
-      <c r="V11" s="353" t="n"/>
-      <c r="W11" s="353" t="n"/>
-      <c r="X11" s="353" t="n"/>
-      <c r="Y11" s="353" t="n"/>
-      <c r="Z11" s="353" t="n"/>
-      <c r="AA11" s="353" t="n"/>
-      <c r="AB11" s="353" t="n"/>
-      <c r="AC11" s="353" t="n"/>
-      <c r="AD11" s="353" t="n"/>
-      <c r="AE11" s="353" t="n"/>
-      <c r="AF11" s="353" t="n"/>
-      <c r="AG11" s="353" t="n"/>
-      <c r="AH11" s="353" t="n"/>
-      <c r="AI11" s="353" t="n"/>
-      <c r="AJ11" s="353" t="n"/>
-      <c r="AK11" s="353" t="n"/>
-      <c r="AL11" s="353" t="n"/>
-      <c r="AM11" s="353" t="n"/>
-      <c r="AN11" s="516" t="n"/>
-    </row>
-    <row r="12" ht="20" customHeight="1" s="329">
-      <c r="A12" s="461" t="inlineStr">
-        <is>
-          <t>Open When</t>
-        </is>
-      </c>
-      <c r="B12" s="462" t="inlineStr">
-        <is>
-          <t>Open immediately when the event, request, issue, change, complaint, risk or incident is detected or formally raised.</t>
-        </is>
-      </c>
-      <c r="C12" s="515" t="inlineStr">
-        <is>
-          <t>Operational trigger</t>
-        </is>
-      </c>
-      <c r="D12" s="353" t="n"/>
-      <c r="E12" s="353" t="n"/>
-      <c r="F12" s="353" t="n"/>
-      <c r="G12" s="353" t="n"/>
-      <c r="H12" s="353" t="n"/>
-      <c r="I12" s="353" t="n"/>
-      <c r="J12" s="353" t="n"/>
-      <c r="K12" s="353" t="n"/>
-      <c r="L12" s="353" t="n"/>
-      <c r="M12" s="353" t="n"/>
-      <c r="N12" s="353" t="n"/>
-      <c r="O12" s="353" t="n"/>
-      <c r="P12" s="353" t="n"/>
-      <c r="Q12" s="353" t="n"/>
-      <c r="R12" s="353" t="n"/>
-      <c r="S12" s="353" t="n"/>
-      <c r="T12" s="353" t="n"/>
-      <c r="U12" s="353" t="n"/>
-      <c r="V12" s="353" t="n"/>
-      <c r="W12" s="353" t="n"/>
-      <c r="X12" s="353" t="n"/>
-      <c r="Y12" s="353" t="n"/>
-      <c r="Z12" s="353" t="n"/>
-      <c r="AA12" s="353" t="n"/>
-      <c r="AB12" s="353" t="n"/>
-      <c r="AC12" s="353" t="n"/>
-      <c r="AD12" s="353" t="n"/>
-      <c r="AE12" s="353" t="n"/>
-      <c r="AF12" s="353" t="n"/>
-      <c r="AG12" s="353" t="n"/>
-      <c r="AH12" s="353" t="n"/>
-      <c r="AI12" s="353" t="n"/>
-      <c r="AJ12" s="353" t="n"/>
-      <c r="AK12" s="353" t="n"/>
-      <c r="AL12" s="353" t="n"/>
-      <c r="AM12" s="353" t="n"/>
-      <c r="AN12" s="516" t="n"/>
-    </row>
-    <row r="13" ht="20" customHeight="1" s="329">
-      <c r="A13" s="522" t="inlineStr">
-        <is>
-          <t>Close When</t>
-        </is>
-      </c>
-      <c r="B13" s="523" t="inlineStr">
-        <is>
-          <t>Close when the final decision, final owner, final disposition and required follow-up actions are all recorded and the evidence package is complete.</t>
-        </is>
-      </c>
-      <c r="C13" s="518" t="inlineStr">
-        <is>
-          <t>Release / closure rule</t>
-        </is>
-      </c>
-      <c r="D13" s="518" t="n"/>
-      <c r="E13" s="518" t="n"/>
-      <c r="F13" s="518" t="n"/>
-      <c r="G13" s="518" t="n"/>
-      <c r="H13" s="518" t="n"/>
-      <c r="I13" s="518" t="n"/>
-      <c r="J13" s="518" t="n"/>
-      <c r="K13" s="518" t="n"/>
-      <c r="L13" s="518" t="n"/>
-      <c r="M13" s="518" t="n"/>
-      <c r="N13" s="518" t="n"/>
-      <c r="O13" s="518" t="n"/>
-      <c r="P13" s="518" t="n"/>
-      <c r="Q13" s="518" t="n"/>
-      <c r="R13" s="518" t="n"/>
-      <c r="S13" s="518" t="n"/>
-      <c r="T13" s="518" t="n"/>
-      <c r="U13" s="518" t="n"/>
-      <c r="V13" s="518" t="n"/>
-      <c r="W13" s="518" t="n"/>
-      <c r="X13" s="518" t="n"/>
-      <c r="Y13" s="518" t="n"/>
-      <c r="Z13" s="518" t="n"/>
-      <c r="AA13" s="518" t="n"/>
-      <c r="AB13" s="518" t="n"/>
-      <c r="AC13" s="518" t="n"/>
-      <c r="AD13" s="518" t="n"/>
-      <c r="AE13" s="518" t="n"/>
-      <c r="AF13" s="518" t="n"/>
-      <c r="AG13" s="518" t="n"/>
-      <c r="AH13" s="518" t="n"/>
-      <c r="AI13" s="518" t="n"/>
-      <c r="AJ13" s="518" t="n"/>
-      <c r="AK13" s="518" t="n"/>
-      <c r="AL13" s="518" t="n"/>
-      <c r="AM13" s="518" t="n"/>
-      <c r="AN13" s="519" t="n"/>
-    </row>
-    <row r="14" ht="20" customHeight="1" s="329"/>
-    <row r="15" ht="20" customHeight="1" s="329"/>
-    <row r="16" ht="20" customHeight="1" s="329"/>
-    <row r="17" ht="20" customHeight="1" s="329"/>
-    <row r="18" ht="20" customHeight="1" s="329"/>
-    <row r="19" ht="20" customHeight="1" s="329"/>
-    <row r="20" ht="20" customHeight="1" s="329"/>
-    <row r="21" ht="20" customHeight="1" s="329"/>
-    <row r="22" ht="20" customHeight="1" s="329"/>
-    <row r="23" ht="20" customHeight="1" s="329"/>
-    <row r="24" ht="20" customHeight="1" s="329"/>
-    <row r="25" ht="20" customHeight="1" s="329"/>
-    <row r="26" ht="20" customHeight="1" s="329"/>
-    <row r="27" ht="20" customHeight="1" s="329"/>
-    <row r="28" ht="20" customHeight="1" s="329"/>
-    <row r="29" ht="20" customHeight="1" s="329"/>
-    <row r="30" ht="20" customHeight="1" s="329"/>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
-  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AN13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="2.33" customWidth="1" style="329" min="1" max="1"/>
-    <col width="2.33" customWidth="1" style="329" min="2" max="2"/>
-    <col width="2.33" customWidth="1" style="329" min="3" max="3"/>
-    <col width="2.33" customWidth="1" style="329" min="4" max="4"/>
-    <col width="2.33" customWidth="1" style="329" min="5" max="5"/>
-    <col width="2.33" customWidth="1" style="329" min="6" max="6"/>
-    <col width="2.33" customWidth="1" style="329" min="7" max="7"/>
-    <col width="2.33" customWidth="1" style="329" min="8" max="8"/>
-    <col width="2.33" customWidth="1" style="329" min="9" max="9"/>
-    <col width="2.33" customWidth="1" style="329" min="10" max="10"/>
-    <col width="2.33" customWidth="1" style="329" min="11" max="11"/>
-    <col width="2.33" customWidth="1" style="329" min="12" max="12"/>
-    <col width="2.33" customWidth="1" style="329" min="13" max="13"/>
-    <col width="2.33" customWidth="1" style="329" min="14" max="14"/>
-    <col width="2.33" customWidth="1" style="329" min="15" max="15"/>
-    <col width="2.33" customWidth="1" style="329" min="16" max="16"/>
-    <col width="2.33" customWidth="1" style="329" min="17" max="17"/>
-    <col width="2.33" customWidth="1" style="329" min="18" max="18"/>
-    <col width="2.33" customWidth="1" style="329" min="19" max="19"/>
-    <col width="2.33" customWidth="1" style="329" min="20" max="20"/>
-    <col width="2.33" customWidth="1" style="329" min="21" max="21"/>
-    <col width="2.33" customWidth="1" style="329" min="22" max="22"/>
-    <col width="2.33" customWidth="1" style="329" min="23" max="23"/>
-    <col width="2.33" customWidth="1" style="329" min="24" max="24"/>
-    <col width="2.33" customWidth="1" style="329" min="25" max="25"/>
-    <col width="2.33" customWidth="1" style="329" min="26" max="26"/>
-    <col width="2.33" customWidth="1" style="329" min="27" max="27"/>
-    <col width="2.33" customWidth="1" style="329" min="28" max="28"/>
-    <col width="2.33" customWidth="1" style="329" min="29" max="29"/>
-    <col width="2.33" customWidth="1" style="329" min="30" max="30"/>
-    <col width="2.33" customWidth="1" style="329" min="31" max="31"/>
-    <col width="2.33" customWidth="1" style="329" min="32" max="32"/>
-    <col width="2.33" customWidth="1" style="329" min="33" max="33"/>
-    <col width="2.33" customWidth="1" style="329" min="34" max="34"/>
-    <col width="2.33" customWidth="1" style="329" min="35" max="35"/>
-    <col width="2.33" customWidth="1" style="329" min="36" max="36"/>
-    <col width="2.33" customWidth="1" style="329" min="37" max="37"/>
-    <col width="2.33" customWidth="1" style="329" min="38" max="38"/>
-    <col width="2.33" customWidth="1" style="329" min="39" max="39"/>
-    <col width="2.33" customWidth="1" style="329" min="40" max="40"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15" customHeight="1" s="329">
-      <c r="A1" s="497" t="inlineStr">
-        <is>
-          <t>Evidence Reference / Attachment Guidance</t>
-        </is>
-      </c>
-      <c r="B1" s="527" t="n"/>
-      <c r="C1" s="527" t="n"/>
-      <c r="D1" s="527" t="n"/>
-      <c r="E1" s="527" t="n"/>
-      <c r="F1" s="527" t="n"/>
-      <c r="G1" s="527" t="n"/>
-      <c r="H1" s="498" t="n"/>
-      <c r="I1" s="417" t="n"/>
-      <c r="J1" s="418" t="n"/>
-      <c r="K1" s="418" t="n"/>
-      <c r="L1" s="418" t="n"/>
-      <c r="M1" s="418" t="n"/>
-      <c r="N1" s="418" t="n"/>
-      <c r="O1" s="418" t="n"/>
-      <c r="P1" s="418" t="n"/>
-      <c r="Q1" s="418" t="n"/>
-      <c r="R1" s="418" t="n"/>
-      <c r="S1" s="418" t="n"/>
-      <c r="T1" s="418" t="n"/>
-      <c r="U1" s="418" t="n"/>
-      <c r="V1" s="418" t="n"/>
-      <c r="W1" s="418" t="n"/>
-      <c r="X1" s="418" t="n"/>
-      <c r="Y1" s="418" t="n"/>
-      <c r="Z1" s="418" t="n"/>
-      <c r="AA1" s="418" t="n"/>
-      <c r="AB1" s="418" t="n"/>
-      <c r="AC1" s="418" t="n"/>
-      <c r="AD1" s="419" t="n"/>
-      <c r="AE1" s="420" t="n"/>
-      <c r="AF1" s="421" t="n"/>
-      <c r="AG1" s="421" t="n"/>
-      <c r="AH1" s="422" t="n"/>
-      <c r="AI1" s="423" t="n"/>
-      <c r="AJ1" s="424" t="n"/>
-      <c r="AK1" s="424" t="n"/>
-      <c r="AL1" s="424" t="n"/>
-      <c r="AM1" s="424" t="n"/>
-      <c r="AN1" s="425" t="n"/>
-    </row>
-    <row r="2" ht="15" customHeight="1" s="329">
-      <c r="A2" s="499" t="inlineStr">
-        <is>
-          <t>Use controlled evidence package references; do not free-type vague placeholders.</t>
-        </is>
-      </c>
-      <c r="H2" s="500" t="n"/>
-      <c r="I2" s="428" t="n"/>
-      <c r="J2" s="429" t="n"/>
-      <c r="K2" s="429" t="n"/>
-      <c r="L2" s="429" t="n"/>
-      <c r="M2" s="429" t="n"/>
-      <c r="N2" s="429" t="n"/>
-      <c r="O2" s="429" t="n"/>
-      <c r="P2" s="429" t="n"/>
-      <c r="Q2" s="429" t="n"/>
-      <c r="R2" s="429" t="n"/>
-      <c r="S2" s="429" t="n"/>
-      <c r="T2" s="429" t="n"/>
-      <c r="U2" s="429" t="n"/>
-      <c r="V2" s="429" t="n"/>
-      <c r="W2" s="429" t="n"/>
-      <c r="X2" s="429" t="n"/>
-      <c r="Y2" s="429" t="n"/>
-      <c r="Z2" s="429" t="n"/>
-      <c r="AA2" s="429" t="n"/>
-      <c r="AB2" s="429" t="n"/>
-      <c r="AC2" s="429" t="n"/>
-      <c r="AD2" s="430" t="n"/>
-      <c r="AE2" s="431" t="n"/>
-      <c r="AF2" s="432" t="n"/>
-      <c r="AG2" s="432" t="n"/>
-      <c r="AH2" s="433" t="n"/>
-      <c r="AI2" s="434" t="n"/>
-      <c r="AJ2" s="435" t="n"/>
-      <c r="AK2" s="435" t="n"/>
-      <c r="AL2" s="435" t="n"/>
-      <c r="AM2" s="435" t="n"/>
-      <c r="AN2" s="436" t="n"/>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="329">
-      <c r="A3" s="501" t="n"/>
-      <c r="B3" s="502" t="n"/>
-      <c r="C3" s="502" t="n"/>
-      <c r="D3" s="502" t="n"/>
-      <c r="E3" s="502" t="n"/>
-      <c r="F3" s="502" t="n"/>
-      <c r="G3" s="502" t="n"/>
-      <c r="H3" s="500" t="n"/>
-      <c r="I3" s="428" t="n"/>
-      <c r="J3" s="429" t="n"/>
-      <c r="K3" s="429" t="n"/>
-      <c r="L3" s="429" t="n"/>
-      <c r="M3" s="429" t="n"/>
-      <c r="N3" s="429" t="n"/>
-      <c r="O3" s="429" t="n"/>
-      <c r="P3" s="429" t="n"/>
-      <c r="Q3" s="429" t="n"/>
-      <c r="R3" s="429" t="n"/>
-      <c r="S3" s="429" t="n"/>
-      <c r="T3" s="429" t="n"/>
-      <c r="U3" s="429" t="n"/>
-      <c r="V3" s="429" t="n"/>
-      <c r="W3" s="429" t="n"/>
-      <c r="X3" s="429" t="n"/>
-      <c r="Y3" s="429" t="n"/>
-      <c r="Z3" s="429" t="n"/>
-      <c r="AA3" s="429" t="n"/>
-      <c r="AB3" s="429" t="n"/>
-      <c r="AC3" s="429" t="n"/>
-      <c r="AD3" s="430" t="n"/>
-      <c r="AE3" s="431" t="n"/>
-      <c r="AF3" s="432" t="n"/>
-      <c r="AG3" s="432" t="n"/>
-      <c r="AH3" s="433" t="n"/>
-      <c r="AI3" s="434" t="n"/>
-      <c r="AJ3" s="435" t="n"/>
-      <c r="AK3" s="435" t="n"/>
-      <c r="AL3" s="435" t="n"/>
-      <c r="AM3" s="435" t="n"/>
-      <c r="AN3" s="436" t="n"/>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="329">
-      <c r="A4" s="503" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="B4" s="504" t="inlineStr">
-        <is>
-          <t>Value / Reference</t>
-        </is>
-      </c>
-      <c r="C4" s="504" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="D4" s="502" t="n"/>
-      <c r="E4" s="502" t="n"/>
-      <c r="F4" s="502" t="n"/>
-      <c r="G4" s="502" t="n"/>
-      <c r="H4" s="500" t="n"/>
-      <c r="I4" s="437" t="n"/>
-      <c r="J4" s="438" t="n"/>
-      <c r="K4" s="438" t="n"/>
-      <c r="L4" s="438" t="n"/>
-      <c r="M4" s="438" t="n"/>
-      <c r="N4" s="438" t="n"/>
-      <c r="O4" s="438" t="n"/>
-      <c r="P4" s="438" t="n"/>
-      <c r="Q4" s="438" t="n"/>
-      <c r="R4" s="438" t="n"/>
-      <c r="S4" s="438" t="n"/>
-      <c r="T4" s="438" t="n"/>
-      <c r="U4" s="438" t="n"/>
-      <c r="V4" s="438" t="n"/>
-      <c r="W4" s="438" t="n"/>
-      <c r="X4" s="438" t="n"/>
-      <c r="Y4" s="438" t="n"/>
-      <c r="Z4" s="438" t="n"/>
-      <c r="AA4" s="438" t="n"/>
-      <c r="AB4" s="438" t="n"/>
-      <c r="AC4" s="438" t="n"/>
-      <c r="AD4" s="439" t="n"/>
-      <c r="AE4" s="431" t="n"/>
-      <c r="AF4" s="432" t="n"/>
-      <c r="AG4" s="432" t="n"/>
-      <c r="AH4" s="433" t="n"/>
-      <c r="AI4" s="434" t="n"/>
-      <c r="AJ4" s="435" t="n"/>
-      <c r="AK4" s="435" t="n"/>
-      <c r="AL4" s="435" t="n"/>
-      <c r="AM4" s="435" t="n"/>
-      <c r="AN4" s="436" t="n"/>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="329">
-      <c r="A5" s="506" t="inlineStr">
-        <is>
-          <t>Source of Truth</t>
-        </is>
-      </c>
-      <c r="B5" s="507" t="inlineStr">
-        <is>
-          <t>Epicor transaction + M365 evidence</t>
-        </is>
-      </c>
-      <c r="C5" s="507" t="inlineStr">
-        <is>
-          <t>Do not duplicate ERP/M365/ANNEX master data.</t>
-        </is>
-      </c>
-      <c r="D5" s="520" t="n"/>
-      <c r="E5" s="520" t="n"/>
-      <c r="F5" s="520" t="n"/>
-      <c r="G5" s="520" t="n"/>
-      <c r="H5" s="521" t="n"/>
-      <c r="I5" s="443" t="n"/>
-      <c r="J5" s="444" t="n"/>
-      <c r="K5" s="444" t="n"/>
-      <c r="L5" s="444" t="n"/>
-      <c r="M5" s="444" t="n"/>
-      <c r="N5" s="444" t="n"/>
-      <c r="O5" s="444" t="n"/>
-      <c r="P5" s="444" t="n"/>
-      <c r="Q5" s="444" t="n"/>
-      <c r="R5" s="444" t="n"/>
-      <c r="S5" s="444" t="n"/>
-      <c r="T5" s="444" t="n"/>
-      <c r="U5" s="444" t="n"/>
-      <c r="V5" s="444" t="n"/>
-      <c r="W5" s="444" t="n"/>
-      <c r="X5" s="444" t="n"/>
-      <c r="Y5" s="444" t="n"/>
-      <c r="Z5" s="444" t="n"/>
-      <c r="AA5" s="444" t="n"/>
-      <c r="AB5" s="444" t="n"/>
-      <c r="AC5" s="444" t="n"/>
-      <c r="AD5" s="445" t="n"/>
-      <c r="AE5" s="446" t="n"/>
-      <c r="AF5" s="447" t="n"/>
-      <c r="AG5" s="447" t="n"/>
-      <c r="AH5" s="448" t="n"/>
-      <c r="AI5" s="449" t="n"/>
-      <c r="AJ5" s="450" t="n"/>
-      <c r="AK5" s="450" t="n"/>
-      <c r="AL5" s="450" t="n"/>
-      <c r="AM5" s="450" t="n"/>
-      <c r="AN5" s="451" t="n"/>
-    </row>
-    <row r="6" ht="20" customHeight="1" s="329">
-      <c r="A6" s="509" t="inlineStr">
-        <is>
-          <t>Cross-Reference Boundary</t>
-        </is>
-      </c>
-      <c r="B6" s="510" t="inlineStr">
-        <is>
-          <t>This form does not replace SOP-402; it records the evidence, data or decision required by that SOP.
-Rules, matrices, dictionaries, acceptance criteria and data definitions belong in ANNEX-PUR-001/002/003 + ANNEX-ENG-002; do not copy ANNEX content into the live data-entry body.
-System-of-record / source-of-truth boundary: Epicor transaction + M365 evidence. If the master data already live there, reference or import them; do not re-key without need.</t>
-        </is>
-      </c>
-      <c r="C6" s="511" t="inlineStr">
-        <is>
-          <t>This form does not replace SOP-402; it records the evidence, data or decision required by that SOP.
-Rules, matrices, dictionaries, acceptance criteria and data definitions belong in ANNEX-PUR-001/002/003 + ANNEX-ENG-002; do not copy ANNEX content into the live data-entry body.
-System-of-record / source-of-truth boundary: Epicor transaction + M365 evidence. If the master data already live there, reference or import them; do not re-key without need.</t>
-        </is>
-      </c>
-      <c r="D6" s="457" t="n"/>
-      <c r="E6" s="457" t="n"/>
-      <c r="F6" s="457" t="n"/>
-      <c r="G6" s="457" t="n"/>
-      <c r="H6" s="457" t="n"/>
-      <c r="I6" s="457" t="n"/>
-      <c r="J6" s="457" t="n"/>
-      <c r="K6" s="457" t="n"/>
-      <c r="L6" s="457" t="n"/>
-      <c r="M6" s="457" t="n"/>
-      <c r="N6" s="457" t="n"/>
-      <c r="O6" s="457" t="n"/>
-      <c r="P6" s="457" t="n"/>
-      <c r="Q6" s="457" t="n"/>
-      <c r="R6" s="457" t="n"/>
-      <c r="S6" s="457" t="n"/>
-      <c r="T6" s="457" t="n"/>
-      <c r="U6" s="457" t="n"/>
-      <c r="V6" s="457" t="n"/>
-      <c r="W6" s="457" t="n"/>
-      <c r="X6" s="457" t="n"/>
-      <c r="Y6" s="457" t="n"/>
-      <c r="Z6" s="457" t="n"/>
-      <c r="AA6" s="457" t="n"/>
-      <c r="AB6" s="457" t="n"/>
-      <c r="AC6" s="457" t="n"/>
-      <c r="AD6" s="457" t="n"/>
-      <c r="AE6" s="457" t="n"/>
-      <c r="AF6" s="457" t="n"/>
-      <c r="AG6" s="457" t="n"/>
-      <c r="AH6" s="457" t="n"/>
-      <c r="AI6" s="457" t="n"/>
-      <c r="AJ6" s="457" t="n"/>
-      <c r="AK6" s="457" t="n"/>
-      <c r="AL6" s="457" t="n"/>
-      <c r="AM6" s="457" t="n"/>
-      <c r="AN6" s="460" t="n"/>
-    </row>
-    <row r="7" ht="20" customHeight="1" s="329">
-      <c r="A7" s="512" t="inlineStr">
-        <is>
-          <t>SOP-402</t>
-        </is>
-      </c>
-      <c r="B7" s="513" t="inlineStr">
-        <is>
-          <t>SOP-402 — Xác minh vật liệu, truy xuất và phòng chống vật tư giả/không rõ nguồn gốc | HESEM QMS</t>
-        </is>
-      </c>
-      <c r="C7" s="514" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/01-SOPs/04-SOP-400/sop-402-material-verification-traceability-and-counterfeit-prevention.html</t>
-        </is>
-      </c>
-      <c r="D7" s="341" t="n"/>
-      <c r="E7" s="341" t="n"/>
-      <c r="F7" s="341" t="n"/>
-      <c r="G7" s="341" t="n"/>
-      <c r="H7" s="341" t="n"/>
-      <c r="I7" s="341" t="n"/>
-      <c r="J7" s="341" t="n"/>
-      <c r="K7" s="341" t="n"/>
-      <c r="L7" s="341" t="n"/>
-      <c r="M7" s="341" t="n"/>
-      <c r="N7" s="341" t="n"/>
-      <c r="O7" s="341" t="n"/>
-      <c r="P7" s="341" t="n"/>
-      <c r="Q7" s="341" t="n"/>
-      <c r="R7" s="341" t="n"/>
-      <c r="S7" s="341" t="n"/>
-      <c r="T7" s="341" t="n"/>
-      <c r="U7" s="341" t="n"/>
-      <c r="V7" s="341" t="n"/>
-      <c r="W7" s="341" t="n"/>
-      <c r="X7" s="341" t="n"/>
-      <c r="Y7" s="341" t="n"/>
-      <c r="Z7" s="341" t="n"/>
-      <c r="AA7" s="341" t="n"/>
-      <c r="AB7" s="341" t="n"/>
-      <c r="AC7" s="341" t="n"/>
-      <c r="AD7" s="341" t="n"/>
-      <c r="AE7" s="341" t="n"/>
-      <c r="AF7" s="341" t="n"/>
-      <c r="AG7" s="341" t="n"/>
-      <c r="AH7" s="341" t="n"/>
-      <c r="AI7" s="341" t="n"/>
-      <c r="AJ7" s="341" t="n"/>
-      <c r="AK7" s="341" t="n"/>
-      <c r="AL7" s="341" t="n"/>
-      <c r="AM7" s="341" t="n"/>
-      <c r="AN7" s="464" t="n"/>
-    </row>
-    <row r="8" ht="20" customHeight="1" s="329">
-      <c r="A8" s="461" t="inlineStr">
-        <is>
-          <t>ANNEX-PUR-001</t>
-        </is>
-      </c>
-      <c r="B8" s="462" t="inlineStr">
-        <is>
-          <t>ANNEX-PUR-001 — Mô hình rủi ro nhà cung cấp và phương pháp scorecard</t>
-        </is>
-      </c>
-      <c r="C8" s="515" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-001-supplier-risk-model-and-scorecard-method.html</t>
-        </is>
-      </c>
-      <c r="D8" s="353" t="n"/>
-      <c r="E8" s="353" t="n"/>
-      <c r="F8" s="353" t="n"/>
-      <c r="G8" s="353" t="n"/>
-      <c r="H8" s="353" t="n"/>
-      <c r="I8" s="353" t="n"/>
-      <c r="J8" s="353" t="n"/>
-      <c r="K8" s="353" t="n"/>
-      <c r="L8" s="353" t="n"/>
-      <c r="M8" s="353" t="n"/>
-      <c r="N8" s="353" t="n"/>
-      <c r="O8" s="353" t="n"/>
-      <c r="P8" s="353" t="n"/>
-      <c r="Q8" s="353" t="n"/>
-      <c r="R8" s="353" t="n"/>
-      <c r="S8" s="353" t="n"/>
-      <c r="T8" s="353" t="n"/>
-      <c r="U8" s="353" t="n"/>
-      <c r="V8" s="353" t="n"/>
-      <c r="W8" s="353" t="n"/>
-      <c r="X8" s="353" t="n"/>
-      <c r="Y8" s="353" t="n"/>
-      <c r="Z8" s="353" t="n"/>
-      <c r="AA8" s="353" t="n"/>
-      <c r="AB8" s="353" t="n"/>
-      <c r="AC8" s="353" t="n"/>
-      <c r="AD8" s="353" t="n"/>
-      <c r="AE8" s="353" t="n"/>
-      <c r="AF8" s="353" t="n"/>
-      <c r="AG8" s="353" t="n"/>
-      <c r="AH8" s="353" t="n"/>
-      <c r="AI8" s="353" t="n"/>
-      <c r="AJ8" s="353" t="n"/>
-      <c r="AK8" s="353" t="n"/>
-      <c r="AL8" s="353" t="n"/>
-      <c r="AM8" s="353" t="n"/>
-      <c r="AN8" s="516" t="n"/>
-    </row>
-    <row r="9" ht="20" customHeight="1" s="329">
-      <c r="A9" s="524" t="inlineStr">
-        <is>
-          <t>ANNEX-PUR-002</t>
-        </is>
-      </c>
-      <c r="B9" s="525" t="inlineStr">
-        <is>
-          <t>ANNEX-PUR-002 — Gói kiểm soát outsource / special process / cert flow-down</t>
-        </is>
-      </c>
-      <c r="C9" s="353" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-002-outsource-special-process-pack.html</t>
-        </is>
-      </c>
-      <c r="D9" s="353" t="n"/>
-      <c r="E9" s="353" t="n"/>
-      <c r="F9" s="353" t="n"/>
-      <c r="G9" s="353" t="n"/>
-      <c r="H9" s="353" t="n"/>
-      <c r="I9" s="353" t="n"/>
-      <c r="J9" s="353" t="n"/>
-      <c r="K9" s="353" t="n"/>
-      <c r="L9" s="353" t="n"/>
-      <c r="M9" s="353" t="n"/>
-      <c r="N9" s="353" t="n"/>
-      <c r="O9" s="353" t="n"/>
-      <c r="P9" s="353" t="n"/>
-      <c r="Q9" s="353" t="n"/>
-      <c r="R9" s="353" t="n"/>
-      <c r="S9" s="353" t="n"/>
-      <c r="T9" s="353" t="n"/>
-      <c r="U9" s="353" t="n"/>
-      <c r="V9" s="353" t="n"/>
-      <c r="W9" s="353" t="n"/>
-      <c r="X9" s="353" t="n"/>
-      <c r="Y9" s="353" t="n"/>
-      <c r="Z9" s="353" t="n"/>
-      <c r="AA9" s="353" t="n"/>
-      <c r="AB9" s="353" t="n"/>
-      <c r="AC9" s="353" t="n"/>
-      <c r="AD9" s="353" t="n"/>
-      <c r="AE9" s="353" t="n"/>
-      <c r="AF9" s="353" t="n"/>
-      <c r="AG9" s="353" t="n"/>
-      <c r="AH9" s="353" t="n"/>
-      <c r="AI9" s="353" t="n"/>
-      <c r="AJ9" s="353" t="n"/>
-      <c r="AK9" s="353" t="n"/>
-      <c r="AL9" s="353" t="n"/>
-      <c r="AM9" s="353" t="n"/>
-      <c r="AN9" s="516" t="n"/>
-    </row>
-    <row r="10" ht="20" customHeight="1" s="329">
-      <c r="A10" s="524" t="inlineStr">
-        <is>
-          <t>ANNEX-PUR-003</t>
-        </is>
-      </c>
-      <c r="B10" s="525" t="inlineStr">
-        <is>
-          <t>ANNEX-PUR-003 — Approved processor list, scope approval và rule tạm ngưng</t>
-        </is>
-      </c>
-      <c r="C10" s="353" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-pur-003-approved-processor-list.html</t>
-        </is>
-      </c>
-      <c r="D10" s="353" t="n"/>
-      <c r="E10" s="353" t="n"/>
-      <c r="F10" s="353" t="n"/>
-      <c r="G10" s="353" t="n"/>
-      <c r="H10" s="353" t="n"/>
-      <c r="I10" s="353" t="n"/>
-      <c r="J10" s="353" t="n"/>
-      <c r="K10" s="353" t="n"/>
-      <c r="L10" s="353" t="n"/>
-      <c r="M10" s="353" t="n"/>
-      <c r="N10" s="353" t="n"/>
-      <c r="O10" s="353" t="n"/>
-      <c r="P10" s="353" t="n"/>
-      <c r="Q10" s="353" t="n"/>
-      <c r="R10" s="353" t="n"/>
-      <c r="S10" s="353" t="n"/>
-      <c r="T10" s="353" t="n"/>
-      <c r="U10" s="353" t="n"/>
-      <c r="V10" s="353" t="n"/>
-      <c r="W10" s="353" t="n"/>
-      <c r="X10" s="353" t="n"/>
-      <c r="Y10" s="353" t="n"/>
-      <c r="Z10" s="353" t="n"/>
-      <c r="AA10" s="353" t="n"/>
-      <c r="AB10" s="353" t="n"/>
-      <c r="AC10" s="353" t="n"/>
-      <c r="AD10" s="353" t="n"/>
-      <c r="AE10" s="353" t="n"/>
-      <c r="AF10" s="353" t="n"/>
-      <c r="AG10" s="353" t="n"/>
-      <c r="AH10" s="353" t="n"/>
-      <c r="AI10" s="353" t="n"/>
-      <c r="AJ10" s="353" t="n"/>
-      <c r="AK10" s="353" t="n"/>
-      <c r="AL10" s="353" t="n"/>
-      <c r="AM10" s="353" t="n"/>
-      <c r="AN10" s="516" t="n"/>
-    </row>
-    <row r="11" ht="20" customHeight="1" s="329">
-      <c r="A11" s="524" t="inlineStr">
-        <is>
-          <t>ANNEX-ENG-002</t>
-        </is>
-      </c>
-      <c r="B11" s="525" t="inlineStr">
-        <is>
-          <t>ANNEX-ENG-002 — Approved materials list, source restriction và rule thay thế</t>
-        </is>
-      </c>
-      <c r="C11" s="353" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-eng-002-approved-materials-list.html</t>
-        </is>
-      </c>
-      <c r="D11" s="353" t="n"/>
-      <c r="E11" s="353" t="n"/>
-      <c r="F11" s="353" t="n"/>
-      <c r="G11" s="353" t="n"/>
-      <c r="H11" s="353" t="n"/>
-      <c r="I11" s="353" t="n"/>
-      <c r="J11" s="353" t="n"/>
-      <c r="K11" s="353" t="n"/>
-      <c r="L11" s="353" t="n"/>
-      <c r="M11" s="353" t="n"/>
-      <c r="N11" s="353" t="n"/>
-      <c r="O11" s="353" t="n"/>
-      <c r="P11" s="353" t="n"/>
-      <c r="Q11" s="353" t="n"/>
-      <c r="R11" s="353" t="n"/>
-      <c r="S11" s="353" t="n"/>
-      <c r="T11" s="353" t="n"/>
-      <c r="U11" s="353" t="n"/>
-      <c r="V11" s="353" t="n"/>
-      <c r="W11" s="353" t="n"/>
-      <c r="X11" s="353" t="n"/>
-      <c r="Y11" s="353" t="n"/>
-      <c r="Z11" s="353" t="n"/>
-      <c r="AA11" s="353" t="n"/>
-      <c r="AB11" s="353" t="n"/>
-      <c r="AC11" s="353" t="n"/>
-      <c r="AD11" s="353" t="n"/>
-      <c r="AE11" s="353" t="n"/>
-      <c r="AF11" s="353" t="n"/>
-      <c r="AG11" s="353" t="n"/>
-      <c r="AH11" s="353" t="n"/>
-      <c r="AI11" s="353" t="n"/>
-      <c r="AJ11" s="353" t="n"/>
-      <c r="AK11" s="353" t="n"/>
-      <c r="AL11" s="353" t="n"/>
-      <c r="AM11" s="353" t="n"/>
-      <c r="AN11" s="516" t="n"/>
-    </row>
-    <row r="12" ht="20" customHeight="1" s="329">
-      <c r="A12" s="524" t="inlineStr">
-        <is>
-          <t>Open When</t>
-        </is>
-      </c>
-      <c r="B12" s="525" t="inlineStr">
-        <is>
-          <t>Open immediately when the event, request, issue, change, complaint, risk or incident is detected or formally raised.</t>
-        </is>
-      </c>
-      <c r="C12" s="353" t="inlineStr">
-        <is>
-          <t>Operational trigger</t>
-        </is>
-      </c>
-      <c r="D12" s="353" t="n"/>
-      <c r="E12" s="353" t="n"/>
-      <c r="F12" s="353" t="n"/>
-      <c r="G12" s="353" t="n"/>
-      <c r="H12" s="353" t="n"/>
-      <c r="I12" s="353" t="n"/>
-      <c r="J12" s="353" t="n"/>
-      <c r="K12" s="353" t="n"/>
-      <c r="L12" s="353" t="n"/>
-      <c r="M12" s="353" t="n"/>
-      <c r="N12" s="353" t="n"/>
-      <c r="O12" s="353" t="n"/>
-      <c r="P12" s="353" t="n"/>
-      <c r="Q12" s="353" t="n"/>
-      <c r="R12" s="353" t="n"/>
-      <c r="S12" s="353" t="n"/>
-      <c r="T12" s="353" t="n"/>
-      <c r="U12" s="353" t="n"/>
-      <c r="V12" s="353" t="n"/>
-      <c r="W12" s="353" t="n"/>
-      <c r="X12" s="353" t="n"/>
-      <c r="Y12" s="353" t="n"/>
-      <c r="Z12" s="353" t="n"/>
-      <c r="AA12" s="353" t="n"/>
-      <c r="AB12" s="353" t="n"/>
-      <c r="AC12" s="353" t="n"/>
-      <c r="AD12" s="353" t="n"/>
-      <c r="AE12" s="353" t="n"/>
-      <c r="AF12" s="353" t="n"/>
-      <c r="AG12" s="353" t="n"/>
-      <c r="AH12" s="353" t="n"/>
-      <c r="AI12" s="353" t="n"/>
-      <c r="AJ12" s="353" t="n"/>
-      <c r="AK12" s="353" t="n"/>
-      <c r="AL12" s="353" t="n"/>
-      <c r="AM12" s="353" t="n"/>
-      <c r="AN12" s="516" t="n"/>
-    </row>
-    <row r="13" ht="20" customHeight="1" s="329">
-      <c r="A13" s="522" t="inlineStr">
-        <is>
-          <t>Close When</t>
-        </is>
-      </c>
-      <c r="B13" s="523" t="inlineStr">
-        <is>
-          <t>Close when the final decision, final owner, final disposition and required follow-up actions are all recorded and the evidence package is complete.</t>
-        </is>
-      </c>
-      <c r="C13" s="518" t="inlineStr">
-        <is>
-          <t>Release / closure rule</t>
-        </is>
-      </c>
-      <c r="D13" s="518" t="n"/>
-      <c r="E13" s="518" t="n"/>
-      <c r="F13" s="518" t="n"/>
-      <c r="G13" s="518" t="n"/>
-      <c r="H13" s="518" t="n"/>
-      <c r="I13" s="518" t="n"/>
-      <c r="J13" s="518" t="n"/>
-      <c r="K13" s="518" t="n"/>
-      <c r="L13" s="518" t="n"/>
-      <c r="M13" s="518" t="n"/>
-      <c r="N13" s="518" t="n"/>
-      <c r="O13" s="518" t="n"/>
-      <c r="P13" s="518" t="n"/>
-      <c r="Q13" s="518" t="n"/>
-      <c r="R13" s="518" t="n"/>
-      <c r="S13" s="518" t="n"/>
-      <c r="T13" s="518" t="n"/>
-      <c r="U13" s="518" t="n"/>
-      <c r="V13" s="518" t="n"/>
-      <c r="W13" s="518" t="n"/>
-      <c r="X13" s="518" t="n"/>
-      <c r="Y13" s="518" t="n"/>
-      <c r="Z13" s="518" t="n"/>
-      <c r="AA13" s="518" t="n"/>
-      <c r="AB13" s="518" t="n"/>
-      <c r="AC13" s="518" t="n"/>
-      <c r="AD13" s="518" t="n"/>
-      <c r="AE13" s="518" t="n"/>
-      <c r="AF13" s="518" t="n"/>
-      <c r="AG13" s="518" t="n"/>
-      <c r="AH13" s="518" t="n"/>
-      <c r="AI13" s="518" t="n"/>
-      <c r="AJ13" s="518" t="n"/>
-      <c r="AK13" s="518" t="n"/>
-      <c r="AL13" s="518" t="n"/>
-      <c r="AM13" s="518" t="n"/>
-      <c r="AN13" s="519" t="n"/>
-    </row>
-    <row r="14" ht="20" customHeight="1" s="329"/>
-    <row r="15" ht="20" customHeight="1" s="329"/>
-    <row r="16" ht="20" customHeight="1" s="329"/>
-    <row r="17" ht="20" customHeight="1" s="329"/>
-    <row r="18" ht="20" customHeight="1" s="329"/>
-    <row r="19" ht="20" customHeight="1" s="329"/>
-    <row r="20" ht="20" customHeight="1" s="329"/>
-    <row r="21" ht="20" customHeight="1" s="329"/>
-    <row r="22" ht="20" customHeight="1" s="329"/>
-    <row r="23" ht="20" customHeight="1" s="329"/>
-    <row r="24" ht="20" customHeight="1" s="329"/>
-    <row r="25" ht="20" customHeight="1" s="329"/>
-    <row r="26" ht="20" customHeight="1" s="329"/>
-    <row r="27" ht="20" customHeight="1" s="329"/>
-    <row r="28" ht="20" customHeight="1" s="329"/>
-    <row r="29" ht="20" customHeight="1" s="329"/>
-    <row r="30" ht="20" customHeight="1" s="329"/>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
-  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
 </file>
--- a/04-Bieu-Mau/04-FRM-400/FRM-411_Outsourced_Process_Incoming_Verification.xlsx
+++ b/04-Bieu-Mau/04-FRM-400/FRM-411_Outsourced_Process_Incoming_Verification.xlsx
@@ -13,270 +13,10 @@
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
-  <si>
-    <t>  1. REFERENCE INFORMATION</t>
-  </si>
-  <si>
-    <t>  2. INCOMING VERIFICATION / FINDING DETAIL</t>
-  </si>
-  <si>
-    <t>  3. IMPACT / CONTAINMENT / ACTIONS</t>
-  </si>
-  <si>
-    <t>  4. FINAL DECISION / CLOSURE</t>
-  </si>
-  <si>
-    <t>  5. APPROVAL / SIGN-OFF</t>
-  </si>
-  <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>=ROW()-ROW($A$27)+1</t>
-  </si>
-  <si>
-    <t>=ROW()-ROW($A$9)+1</t>
-  </si>
-  <si>
-    <t>ACTION TRACKER</t>
-  </si>
-  <si>
-    <t>ACTION_STATUS</t>
-  </si>
-  <si>
-    <t>APPROVED</t>
-  </si>
-  <si>
-    <t>Affected Job Ref</t>
-  </si>
-  <si>
-    <t>Approved by</t>
-  </si>
-  <si>
-    <t>CLOSED</t>
-  </si>
-  <si>
-    <t>CONDITIONAL</t>
-  </si>
-  <si>
-    <t>CRITICAL</t>
-  </si>
-  <si>
-    <t>Cat.</t>
-  </si>
-  <si>
-    <t>Containment Required (YES/NO)</t>
-  </si>
-  <si>
-    <t>Countermeasure / Trigger</t>
-  </si>
-  <si>
-    <t>Customer Special Requirement (YES/NO)</t>
-  </si>
-  <si>
-    <t>DISPOSITION_GATE</t>
-  </si>
-  <si>
-    <t>Disposition Status</t>
-  </si>
-  <si>
-    <t>Due Date</t>
-  </si>
-  <si>
-    <t>ENG</t>
-  </si>
-  <si>
-    <t>Evidence / Criteria</t>
-  </si>
-  <si>
-    <t>FRM-411</t>
-  </si>
-  <si>
-    <t>Final Decision</t>
-  </si>
-  <si>
-    <t>Finding / Check</t>
-  </si>
-  <si>
-    <t>General Manager</t>
-  </si>
-  <si>
-    <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
-  </si>
-  <si>
-    <t>HIGH</t>
-  </si>
-  <si>
-    <t>HOLD</t>
-  </si>
-  <si>
-    <t>HR</t>
-  </si>
-  <si>
-    <t>IN PROGRESS</t>
-  </si>
-  <si>
-    <t>INEFFECTIVE</t>
-  </si>
-  <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>Incoming Verification ID</t>
-  </si>
-  <si>
-    <t>Issue / Requirement</t>
-  </si>
-  <si>
-    <t>LOW</t>
-  </si>
-  <si>
-    <t>MEDIUM</t>
-  </si>
-  <si>
-    <t>MGT</t>
-  </si>
-  <si>
-    <t>MONITORING</t>
-  </si>
-  <si>
-    <t>Method / Acceptance Ref</t>
-  </si>
-  <si>
-    <t>NOTICE: Use for outsourced incoming verification only. Normal receiving / put-away remains in FRM-701; abnormal hold / disposition goes to FRM-413.</t>
-  </si>
-  <si>
-    <t>Name / Signature / Date</t>
-  </si>
-  <si>
-    <t>OBSERVATION / CONTAINMENT / CERT CHECK</t>
-  </si>
-  <si>
-    <t>OPEN</t>
-  </si>
-  <si>
-    <t>OVERDUE</t>
-  </si>
-  <si>
-    <t>OWNER_DEPT</t>
-  </si>
-  <si>
-    <t>Outsourced Process Incoming Verification</t>
-  </si>
-  <si>
-    <t>Owner</t>
-  </si>
-  <si>
-    <t>PLANNING</t>
-  </si>
-  <si>
-    <t>PO / Cert / Lot Ref</t>
-  </si>
-  <si>
-    <t>PROD</t>
-  </si>
-  <si>
-    <t>PUR</t>
-  </si>
-  <si>
-    <t>Part / Lot / Qty</t>
-  </si>
-  <si>
-    <t>Prepared by</t>
-  </si>
-  <si>
-    <t>Prepared by / Date-Time</t>
-  </si>
-  <si>
-    <t>Process Cert Matches Spec?</t>
-  </si>
-  <si>
-    <t>Purchasing + QA</t>
-  </si>
-  <si>
-    <t>QA</t>
-  </si>
-  <si>
-    <t>Quality Management System · Controlled Document</t>
-  </si>
-  <si>
-    <t>REJECT</t>
-  </si>
-  <si>
-    <t>RISK</t>
-  </si>
-  <si>
-    <t>Record Status</t>
-  </si>
-  <si>
-    <t>Ref.</t>
-  </si>
-  <si>
-    <t>Related Requirement / Package</t>
-  </si>
-  <si>
-    <t>Required Action</t>
-  </si>
-  <si>
-    <t>Result</t>
-  </si>
-  <si>
-    <t>Reviewed by</t>
-  </si>
-  <si>
-    <t>Risk Level</t>
-  </si>
-  <si>
-    <t>SALES</t>
-  </si>
-  <si>
-    <t>STATUS</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Supplier / Processor / Cert</t>
-  </si>
-  <si>
-    <t>Supplier-Quality Owner</t>
-  </si>
-  <si>
-    <t>Target Closeout</t>
-  </si>
-  <si>
-    <t>V0</t>
-  </si>
-  <si>
-    <t>VERIFICATION / SCOPE DESCRIPTION</t>
-  </si>
-  <si>
-    <t>VERIFIED</t>
-  </si>
-  <si>
-    <t>Verified by</t>
-  </si>
-  <si>
-    <t>Visual Inspection Result</t>
-  </si>
-  <si>
-    <t>WHS</t>
-  </si>
-  <si>
-    <t>YYYY-MM-DD</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="89">
+  <fonts count="90">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -777,6 +517,9 @@
       <color theme="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+    </font>
   </fonts>
   <fills count="54">
     <fill>
@@ -1046,7 +789,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="368">
+  <borders count="369">
     <border>
       <left/>
       <right/>
@@ -5041,11 +4784,21 @@
         <color rgb="002C9CD7"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="620">
+  <cellXfs count="640">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -6450,6 +6203,40 @@
     <xf numFmtId="0" fontId="82" fillId="53" borderId="346" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="89" fillId="4" borderId="293" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="294" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="295" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="296" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="298" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="299" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="48" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="283" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="303" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="304" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="305" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="48" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="368" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="47" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -8802,7 +8589,7 @@
       <c r="AM43" s="350" t="n"/>
       <c r="AN43" s="350" t="n"/>
     </row>
-    <row r="44" ht="20" customHeight="1" s="329">
+    <row r="44" ht="26" customHeight="1" s="329">
       <c r="A44" s="569" t="inlineStr">
         <is>
           <t>NOTICE: Use for outsourced incoming verification only. Normal receiving / put-away remains in FRM-701; abnormal hold / disposition goes to FRM-413.</t>
@@ -8998,224 +8785,1074 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:AN20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" style="329" min="1" max="1"/>
-    <col width="18" customWidth="1" style="329" min="2" max="2"/>
-    <col width="18" customWidth="1" style="329" min="3" max="3"/>
-    <col width="18" customWidth="1" style="329" min="4" max="4"/>
-    <col width="18" customWidth="1" style="329" min="5" max="5"/>
-    <col width="20" customWidth="1" style="329" min="6" max="6"/>
-    <col width="20" customWidth="1" style="329" min="7" max="7"/>
+    <col width="2.33" customWidth="1" style="329" min="1" max="1"/>
+    <col width="2.33" customWidth="1" style="329" min="2" max="2"/>
+    <col width="2.33" customWidth="1" style="329" min="3" max="3"/>
+    <col width="2.33" customWidth="1" style="329" min="4" max="4"/>
+    <col width="2.33" customWidth="1" style="329" min="5" max="5"/>
+    <col width="2.33" customWidth="1" style="329" min="6" max="6"/>
+    <col width="2.33" customWidth="1" style="329" min="7" max="7"/>
+    <col width="2.33" customWidth="1" style="329" min="8" max="8"/>
+    <col width="2.33" customWidth="1" style="329" min="9" max="9"/>
+    <col width="2.33" customWidth="1" style="329" min="10" max="10"/>
+    <col width="2.33" customWidth="1" style="329" min="11" max="11"/>
+    <col width="2.33" customWidth="1" style="329" min="12" max="12"/>
+    <col width="2.33" customWidth="1" style="329" min="13" max="13"/>
+    <col width="2.33" customWidth="1" style="329" min="14" max="14"/>
+    <col width="2.33" customWidth="1" style="329" min="15" max="15"/>
+    <col width="2.33" customWidth="1" style="329" min="16" max="16"/>
+    <col width="2.33" customWidth="1" style="329" min="17" max="17"/>
+    <col width="2.33" customWidth="1" style="329" min="18" max="18"/>
+    <col width="2.33" customWidth="1" style="329" min="19" max="19"/>
+    <col width="2.33" customWidth="1" style="329" min="20" max="20"/>
+    <col width="2.33" customWidth="1" style="329" min="21" max="21"/>
+    <col width="2.33" customWidth="1" style="329" min="22" max="22"/>
+    <col width="2.33" customWidth="1" style="329" min="23" max="23"/>
+    <col width="2.33" customWidth="1" style="329" min="24" max="24"/>
+    <col width="2.33" customWidth="1" style="329" min="25" max="25"/>
+    <col width="2.33" customWidth="1" style="329" min="26" max="26"/>
+    <col width="2.33" customWidth="1" style="329" min="27" max="27"/>
+    <col width="2.33" customWidth="1" style="329" min="28" max="28"/>
+    <col width="2.33" customWidth="1" style="329" min="29" max="29"/>
+    <col width="2.33" customWidth="1" style="329" min="30" max="30"/>
+    <col width="2.33" customWidth="1" style="329" min="31" max="31"/>
+    <col width="2.33" customWidth="1" style="329" min="32" max="32"/>
+    <col width="2.33" customWidth="1" style="329" min="33" max="33"/>
+    <col width="2.33" customWidth="1" style="329" min="34" max="34"/>
+    <col width="2.33" customWidth="1" style="329" min="35" max="35"/>
+    <col width="2.33" customWidth="1" style="329" min="36" max="36"/>
+    <col width="2.33" customWidth="1" style="329" min="37" max="37"/>
+    <col width="2.33" customWidth="1" style="329" min="38" max="38"/>
+    <col width="2.33" customWidth="1" style="329" min="39" max="39"/>
+    <col width="2.33" customWidth="1" style="329" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="265" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" s="329">
+      <c r="A1" s="620" t="n"/>
+      <c r="B1" s="621" t="n"/>
+      <c r="C1" s="621" t="n"/>
+      <c r="D1" s="621" t="n"/>
+      <c r="E1" s="621" t="n"/>
+      <c r="F1" s="621" t="n"/>
+      <c r="G1" s="621" t="n"/>
+      <c r="H1" s="622" t="n"/>
+      <c r="I1" s="623" t="inlineStr">
+        <is>
+          <t>Outsourced Process Incoming Verification</t>
+        </is>
+      </c>
+      <c r="J1" s="621" t="n"/>
+      <c r="K1" s="621" t="n"/>
+      <c r="L1" s="621" t="n"/>
+      <c r="M1" s="621" t="n"/>
+      <c r="N1" s="621" t="n"/>
+      <c r="O1" s="621" t="n"/>
+      <c r="P1" s="621" t="n"/>
+      <c r="Q1" s="621" t="n"/>
+      <c r="R1" s="621" t="n"/>
+      <c r="S1" s="621" t="n"/>
+      <c r="T1" s="621" t="n"/>
+      <c r="U1" s="621" t="n"/>
+      <c r="V1" s="621" t="n"/>
+      <c r="W1" s="621" t="n"/>
+      <c r="X1" s="621" t="n"/>
+      <c r="Y1" s="621" t="n"/>
+      <c r="Z1" s="621" t="n"/>
+      <c r="AA1" s="621" t="n"/>
+      <c r="AB1" s="621" t="n"/>
+      <c r="AC1" s="621" t="n"/>
+      <c r="AD1" s="622" t="n"/>
+      <c r="AE1" s="421" t="inlineStr">
+        <is>
+          <t>Form Code</t>
+        </is>
+      </c>
+      <c r="AF1" s="621" t="n"/>
+      <c r="AG1" s="621" t="n"/>
+      <c r="AH1" s="624" t="n"/>
+      <c r="AI1" s="424" t="n"/>
+      <c r="AJ1" s="621" t="n"/>
+      <c r="AK1" s="621" t="n"/>
+      <c r="AL1" s="621" t="n"/>
+      <c r="AM1" s="621" t="n"/>
+      <c r="AN1" s="622" t="n"/>
+    </row>
+    <row r="2" ht="15" customHeight="1" s="329">
+      <c r="A2" s="625" t="n"/>
+      <c r="B2" s="10" t="n"/>
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="10" t="n"/>
+      <c r="H2" s="626" t="n"/>
+      <c r="I2" s="10" t="n"/>
+      <c r="J2" s="10" t="n"/>
+      <c r="K2" s="10" t="n"/>
+      <c r="L2" s="10" t="n"/>
+      <c r="M2" s="10" t="n"/>
+      <c r="N2" s="10" t="n"/>
+      <c r="O2" s="10" t="n"/>
+      <c r="P2" s="10" t="n"/>
+      <c r="Q2" s="10" t="n"/>
+      <c r="R2" s="10" t="n"/>
+      <c r="S2" s="10" t="n"/>
+      <c r="T2" s="10" t="n"/>
+      <c r="U2" s="10" t="n"/>
+      <c r="V2" s="10" t="n"/>
+      <c r="W2" s="10" t="n"/>
+      <c r="X2" s="10" t="n"/>
+      <c r="Y2" s="10" t="n"/>
+      <c r="Z2" s="10" t="n"/>
+      <c r="AA2" s="10" t="n"/>
+      <c r="AB2" s="10" t="n"/>
+      <c r="AC2" s="10" t="n"/>
+      <c r="AD2" s="626" t="n"/>
+      <c r="AE2" s="627" t="inlineStr">
+        <is>
+          <t>Revision</t>
+        </is>
+      </c>
+      <c r="AF2" s="10" t="n"/>
+      <c r="AG2" s="10" t="n"/>
+      <c r="AH2" s="628" t="n"/>
+      <c r="AI2" s="629" t="n"/>
+      <c r="AJ2" s="10" t="n"/>
+      <c r="AK2" s="10" t="n"/>
+      <c r="AL2" s="10" t="n"/>
+      <c r="AM2" s="10" t="n"/>
+      <c r="AN2" s="626" t="n"/>
+    </row>
+    <row r="3" ht="15" customHeight="1" s="329">
+      <c r="A3" s="625" t="n"/>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="626" t="n"/>
+      <c r="I3" s="10" t="n"/>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="10" t="n"/>
+      <c r="O3" s="10" t="n"/>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="10" t="n"/>
+      <c r="W3" s="10" t="n"/>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="10" t="n"/>
+      <c r="AB3" s="10" t="n"/>
+      <c r="AC3" s="10" t="n"/>
+      <c r="AD3" s="626" t="n"/>
+      <c r="AE3" s="627" t="inlineStr">
+        <is>
+          <t>Eff. Date</t>
+        </is>
+      </c>
+      <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="10" t="n"/>
+      <c r="AH3" s="628" t="n"/>
+      <c r="AI3" s="629" t="n"/>
+      <c r="AJ3" s="10" t="n"/>
+      <c r="AK3" s="10" t="n"/>
+      <c r="AL3" s="10" t="n"/>
+      <c r="AM3" s="10" t="n"/>
+      <c r="AN3" s="626" t="n"/>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="329">
+      <c r="A4" s="625" t="n"/>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="626" t="n"/>
+      <c r="I4" s="630" t="inlineStr">
+        <is>
+          <t>Quality Management System · Controlled Document</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="n"/>
+      <c r="K4" s="10" t="n"/>
+      <c r="L4" s="10" t="n"/>
+      <c r="M4" s="10" t="n"/>
+      <c r="N4" s="10" t="n"/>
+      <c r="O4" s="10" t="n"/>
+      <c r="P4" s="10" t="n"/>
+      <c r="Q4" s="10" t="n"/>
+      <c r="R4" s="10" t="n"/>
+      <c r="S4" s="10" t="n"/>
+      <c r="T4" s="10" t="n"/>
+      <c r="U4" s="10" t="n"/>
+      <c r="V4" s="10" t="n"/>
+      <c r="W4" s="10" t="n"/>
+      <c r="X4" s="10" t="n"/>
+      <c r="Y4" s="10" t="n"/>
+      <c r="Z4" s="10" t="n"/>
+      <c r="AA4" s="10" t="n"/>
+      <c r="AB4" s="10" t="n"/>
+      <c r="AC4" s="10" t="n"/>
+      <c r="AD4" s="626" t="n"/>
+      <c r="AE4" s="627" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="AF4" s="10" t="n"/>
+      <c r="AG4" s="10" t="n"/>
+      <c r="AH4" s="628" t="n"/>
+      <c r="AI4" s="629" t="n"/>
+      <c r="AJ4" s="10" t="n"/>
+      <c r="AK4" s="10" t="n"/>
+      <c r="AL4" s="10" t="n"/>
+      <c r="AM4" s="10" t="n"/>
+      <c r="AN4" s="626" t="n"/>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="329">
+      <c r="A5" s="631" t="n"/>
+      <c r="B5" s="632" t="n"/>
+      <c r="C5" s="632" t="n"/>
+      <c r="D5" s="632" t="n"/>
+      <c r="E5" s="632" t="n"/>
+      <c r="F5" s="632" t="n"/>
+      <c r="G5" s="632" t="n"/>
+      <c r="H5" s="633" t="n"/>
+      <c r="I5" s="634" t="inlineStr">
+        <is>
+          <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
+        </is>
+      </c>
+      <c r="J5" s="632" t="n"/>
+      <c r="K5" s="632" t="n"/>
+      <c r="L5" s="632" t="n"/>
+      <c r="M5" s="632" t="n"/>
+      <c r="N5" s="632" t="n"/>
+      <c r="O5" s="632" t="n"/>
+      <c r="P5" s="632" t="n"/>
+      <c r="Q5" s="632" t="n"/>
+      <c r="R5" s="632" t="n"/>
+      <c r="S5" s="632" t="n"/>
+      <c r="T5" s="632" t="n"/>
+      <c r="U5" s="632" t="n"/>
+      <c r="V5" s="632" t="n"/>
+      <c r="W5" s="632" t="n"/>
+      <c r="X5" s="632" t="n"/>
+      <c r="Y5" s="632" t="n"/>
+      <c r="Z5" s="632" t="n"/>
+      <c r="AA5" s="632" t="n"/>
+      <c r="AB5" s="632" t="n"/>
+      <c r="AC5" s="632" t="n"/>
+      <c r="AD5" s="633" t="n"/>
+      <c r="AE5" s="635" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="AF5" s="632" t="n"/>
+      <c r="AG5" s="632" t="n"/>
+      <c r="AH5" s="636" t="n"/>
+      <c r="AI5" s="637" t="n"/>
+      <c r="AJ5" s="632" t="n"/>
+      <c r="AK5" s="632" t="n"/>
+      <c r="AL5" s="632" t="n"/>
+      <c r="AM5" s="632" t="n"/>
+      <c r="AN5" s="633" t="n"/>
+    </row>
+    <row r="6" ht="1.5" customHeight="1" s="329">
+      <c r="A6" s="638" t="n"/>
+      <c r="B6" s="638" t="n"/>
+      <c r="C6" s="638" t="n"/>
+      <c r="D6" s="638" t="n"/>
+      <c r="E6" s="638" t="n"/>
+      <c r="F6" s="638" t="n"/>
+      <c r="G6" s="638" t="n"/>
+      <c r="H6" s="638" t="n"/>
+      <c r="I6" s="638" t="n"/>
+      <c r="J6" s="638" t="n"/>
+      <c r="K6" s="638" t="n"/>
+      <c r="L6" s="638" t="n"/>
+      <c r="M6" s="638" t="n"/>
+      <c r="N6" s="638" t="n"/>
+      <c r="O6" s="638" t="n"/>
+      <c r="P6" s="638" t="n"/>
+      <c r="Q6" s="638" t="n"/>
+      <c r="R6" s="638" t="n"/>
+      <c r="S6" s="638" t="n"/>
+      <c r="T6" s="638" t="n"/>
+      <c r="U6" s="638" t="n"/>
+      <c r="V6" s="638" t="n"/>
+      <c r="W6" s="638" t="n"/>
+      <c r="X6" s="638" t="n"/>
+      <c r="Y6" s="638" t="n"/>
+      <c r="Z6" s="638" t="n"/>
+      <c r="AA6" s="638" t="n"/>
+      <c r="AB6" s="638" t="n"/>
+      <c r="AC6" s="638" t="n"/>
+      <c r="AD6" s="638" t="n"/>
+      <c r="AE6" s="638" t="n"/>
+      <c r="AF6" s="638" t="n"/>
+      <c r="AG6" s="638" t="n"/>
+      <c r="AH6" s="638" t="n"/>
+      <c r="AI6" s="638" t="n"/>
+      <c r="AJ6" s="638" t="n"/>
+      <c r="AK6" s="638" t="n"/>
+      <c r="AL6" s="638" t="n"/>
+      <c r="AM6" s="638" t="n"/>
+      <c r="AN6" s="638" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="265" t="inlineStr">
         <is>
           <t>STATUS</t>
         </is>
       </c>
-      <c r="B1" s="265" t="inlineStr">
+      <c r="B7" s="265" t="inlineStr">
         <is>
           <t>DISPOSITION_GATE</t>
         </is>
       </c>
-      <c r="C1" s="265" t="inlineStr">
+      <c r="C7" s="265" t="inlineStr">
         <is>
           <t>RISK</t>
         </is>
       </c>
-      <c r="D1" s="265" t="inlineStr">
+      <c r="D7" s="265" t="inlineStr">
         <is>
           <t>OWNER_DEPT</t>
         </is>
       </c>
-      <c r="E1" s="265" t="inlineStr">
+      <c r="E7" s="265" t="inlineStr">
         <is>
           <t>ACTION_STATUS</t>
         </is>
       </c>
-      <c r="F1" s="265" t="n"/>
-      <c r="G1" s="265" t="n"/>
+      <c r="F7" s="639" t="n"/>
+      <c r="G7" s="639" t="n"/>
+      <c r="H7" s="639" t="n"/>
+      <c r="I7" s="639" t="n"/>
+      <c r="J7" s="639" t="n"/>
+      <c r="K7" s="639" t="n"/>
+      <c r="L7" s="639" t="n"/>
+      <c r="M7" s="639" t="n"/>
+      <c r="N7" s="639" t="n"/>
+      <c r="O7" s="639" t="n"/>
+      <c r="P7" s="639" t="n"/>
+      <c r="Q7" s="639" t="n"/>
+      <c r="R7" s="639" t="n"/>
+      <c r="S7" s="639" t="n"/>
+      <c r="T7" s="639" t="n"/>
+      <c r="U7" s="639" t="n"/>
+      <c r="V7" s="639" t="n"/>
+      <c r="W7" s="639" t="n"/>
+      <c r="X7" s="639" t="n"/>
+      <c r="Y7" s="639" t="n"/>
+      <c r="Z7" s="639" t="n"/>
+      <c r="AA7" s="639" t="n"/>
+      <c r="AB7" s="639" t="n"/>
+      <c r="AC7" s="639" t="n"/>
+      <c r="AD7" s="639" t="n"/>
+      <c r="AE7" s="639" t="n"/>
+      <c r="AF7" s="639" t="n"/>
+      <c r="AG7" s="639" t="n"/>
+      <c r="AH7" s="639" t="n"/>
+      <c r="AI7" s="639" t="n"/>
+      <c r="AJ7" s="639" t="n"/>
+      <c r="AK7" s="639" t="n"/>
+      <c r="AL7" s="639" t="n"/>
+      <c r="AM7" s="639" t="n"/>
+      <c r="AN7" s="639" t="n"/>
     </row>
-    <row r="2">
-      <c r="A2" s="266" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="266" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="B2" s="266" t="inlineStr">
+      <c r="B8" s="266" t="inlineStr">
         <is>
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="C2" s="266" t="inlineStr">
+      <c r="C8" s="266" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D2" s="266" t="inlineStr">
+      <c r="D8" s="266" t="inlineStr">
         <is>
           <t>SALES</t>
         </is>
       </c>
-      <c r="E2" s="266" t="inlineStr">
+      <c r="E8" s="266" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="F2" s="266" t="n"/>
-      <c r="G2" s="266" t="n"/>
+      <c r="F8" s="639" t="n"/>
+      <c r="G8" s="639" t="n"/>
+      <c r="H8" s="639" t="n"/>
+      <c r="I8" s="639" t="n"/>
+      <c r="J8" s="639" t="n"/>
+      <c r="K8" s="639" t="n"/>
+      <c r="L8" s="639" t="n"/>
+      <c r="M8" s="639" t="n"/>
+      <c r="N8" s="639" t="n"/>
+      <c r="O8" s="639" t="n"/>
+      <c r="P8" s="639" t="n"/>
+      <c r="Q8" s="639" t="n"/>
+      <c r="R8" s="639" t="n"/>
+      <c r="S8" s="639" t="n"/>
+      <c r="T8" s="639" t="n"/>
+      <c r="U8" s="639" t="n"/>
+      <c r="V8" s="639" t="n"/>
+      <c r="W8" s="639" t="n"/>
+      <c r="X8" s="639" t="n"/>
+      <c r="Y8" s="639" t="n"/>
+      <c r="Z8" s="639" t="n"/>
+      <c r="AA8" s="639" t="n"/>
+      <c r="AB8" s="639" t="n"/>
+      <c r="AC8" s="639" t="n"/>
+      <c r="AD8" s="639" t="n"/>
+      <c r="AE8" s="639" t="n"/>
+      <c r="AF8" s="639" t="n"/>
+      <c r="AG8" s="639" t="n"/>
+      <c r="AH8" s="639" t="n"/>
+      <c r="AI8" s="639" t="n"/>
+      <c r="AJ8" s="639" t="n"/>
+      <c r="AK8" s="639" t="n"/>
+      <c r="AL8" s="639" t="n"/>
+      <c r="AM8" s="639" t="n"/>
+      <c r="AN8" s="639" t="n"/>
     </row>
-    <row r="3">
-      <c r="A3" s="266" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="266" t="inlineStr">
         <is>
           <t>IN PROGRESS</t>
         </is>
       </c>
-      <c r="B3" s="266" t="inlineStr">
+      <c r="B9" s="266" t="inlineStr">
         <is>
           <t>CONDITIONAL</t>
         </is>
       </c>
-      <c r="C3" s="266" t="inlineStr">
+      <c r="C9" s="266" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D3" s="266" t="inlineStr">
+      <c r="D9" s="266" t="inlineStr">
         <is>
           <t>ENG</t>
         </is>
       </c>
-      <c r="E3" s="266" t="inlineStr">
+      <c r="E9" s="266" t="inlineStr">
         <is>
           <t>IN PROGRESS</t>
         </is>
       </c>
-      <c r="F3" s="266" t="n"/>
-      <c r="G3" s="266" t="n"/>
+      <c r="F9" s="639" t="n"/>
+      <c r="G9" s="639" t="n"/>
+      <c r="H9" s="639" t="n"/>
+      <c r="I9" s="639" t="n"/>
+      <c r="J9" s="639" t="n"/>
+      <c r="K9" s="639" t="n"/>
+      <c r="L9" s="639" t="n"/>
+      <c r="M9" s="639" t="n"/>
+      <c r="N9" s="639" t="n"/>
+      <c r="O9" s="639" t="n"/>
+      <c r="P9" s="639" t="n"/>
+      <c r="Q9" s="639" t="n"/>
+      <c r="R9" s="639" t="n"/>
+      <c r="S9" s="639" t="n"/>
+      <c r="T9" s="639" t="n"/>
+      <c r="U9" s="639" t="n"/>
+      <c r="V9" s="639" t="n"/>
+      <c r="W9" s="639" t="n"/>
+      <c r="X9" s="639" t="n"/>
+      <c r="Y9" s="639" t="n"/>
+      <c r="Z9" s="639" t="n"/>
+      <c r="AA9" s="639" t="n"/>
+      <c r="AB9" s="639" t="n"/>
+      <c r="AC9" s="639" t="n"/>
+      <c r="AD9" s="639" t="n"/>
+      <c r="AE9" s="639" t="n"/>
+      <c r="AF9" s="639" t="n"/>
+      <c r="AG9" s="639" t="n"/>
+      <c r="AH9" s="639" t="n"/>
+      <c r="AI9" s="639" t="n"/>
+      <c r="AJ9" s="639" t="n"/>
+      <c r="AK9" s="639" t="n"/>
+      <c r="AL9" s="639" t="n"/>
+      <c r="AM9" s="639" t="n"/>
+      <c r="AN9" s="639" t="n"/>
     </row>
-    <row r="4">
-      <c r="A4" s="266" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="266" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
       </c>
-      <c r="B4" s="266" t="inlineStr">
+      <c r="B10" s="266" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="C4" s="266" t="inlineStr">
+      <c r="C10" s="266" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D4" s="266" t="inlineStr">
+      <c r="D10" s="266" t="inlineStr">
         <is>
           <t>PLANNING</t>
         </is>
       </c>
-      <c r="E4" s="266" t="inlineStr">
+      <c r="E10" s="266" t="inlineStr">
         <is>
           <t>OVERDUE</t>
         </is>
       </c>
-      <c r="F4" s="266" t="n"/>
-      <c r="G4" s="266" t="n"/>
+      <c r="F10" s="639" t="n"/>
+      <c r="G10" s="639" t="n"/>
+      <c r="H10" s="639" t="n"/>
+      <c r="I10" s="639" t="n"/>
+      <c r="J10" s="639" t="n"/>
+      <c r="K10" s="639" t="n"/>
+      <c r="L10" s="639" t="n"/>
+      <c r="M10" s="639" t="n"/>
+      <c r="N10" s="639" t="n"/>
+      <c r="O10" s="639" t="n"/>
+      <c r="P10" s="639" t="n"/>
+      <c r="Q10" s="639" t="n"/>
+      <c r="R10" s="639" t="n"/>
+      <c r="S10" s="639" t="n"/>
+      <c r="T10" s="639" t="n"/>
+      <c r="U10" s="639" t="n"/>
+      <c r="V10" s="639" t="n"/>
+      <c r="W10" s="639" t="n"/>
+      <c r="X10" s="639" t="n"/>
+      <c r="Y10" s="639" t="n"/>
+      <c r="Z10" s="639" t="n"/>
+      <c r="AA10" s="639" t="n"/>
+      <c r="AB10" s="639" t="n"/>
+      <c r="AC10" s="639" t="n"/>
+      <c r="AD10" s="639" t="n"/>
+      <c r="AE10" s="639" t="n"/>
+      <c r="AF10" s="639" t="n"/>
+      <c r="AG10" s="639" t="n"/>
+      <c r="AH10" s="639" t="n"/>
+      <c r="AI10" s="639" t="n"/>
+      <c r="AJ10" s="639" t="n"/>
+      <c r="AK10" s="639" t="n"/>
+      <c r="AL10" s="639" t="n"/>
+      <c r="AM10" s="639" t="n"/>
+      <c r="AN10" s="639" t="n"/>
     </row>
-    <row r="5">
-      <c r="A5" s="266" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="266" t="inlineStr">
         <is>
           <t>MONITORING</t>
         </is>
       </c>
-      <c r="B5" s="266" t="inlineStr">
+      <c r="B11" s="266" t="inlineStr">
         <is>
           <t>REJECT</t>
         </is>
       </c>
-      <c r="C5" s="266" t="inlineStr">
+      <c r="C11" s="266" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="D5" s="266" t="inlineStr">
+      <c r="D11" s="266" t="inlineStr">
         <is>
           <t>PROD</t>
         </is>
       </c>
-      <c r="E5" s="345" t="inlineStr">
+      <c r="E11" s="345" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
       </c>
-      <c r="F5" s="266" t="n"/>
-      <c r="G5" s="266" t="n"/>
+      <c r="F11" s="639" t="n"/>
+      <c r="G11" s="639" t="n"/>
+      <c r="H11" s="639" t="n"/>
+      <c r="I11" s="639" t="n"/>
+      <c r="J11" s="639" t="n"/>
+      <c r="K11" s="639" t="n"/>
+      <c r="L11" s="639" t="n"/>
+      <c r="M11" s="639" t="n"/>
+      <c r="N11" s="639" t="n"/>
+      <c r="O11" s="639" t="n"/>
+      <c r="P11" s="639" t="n"/>
+      <c r="Q11" s="639" t="n"/>
+      <c r="R11" s="639" t="n"/>
+      <c r="S11" s="639" t="n"/>
+      <c r="T11" s="639" t="n"/>
+      <c r="U11" s="639" t="n"/>
+      <c r="V11" s="639" t="n"/>
+      <c r="W11" s="639" t="n"/>
+      <c r="X11" s="639" t="n"/>
+      <c r="Y11" s="639" t="n"/>
+      <c r="Z11" s="639" t="n"/>
+      <c r="AA11" s="639" t="n"/>
+      <c r="AB11" s="639" t="n"/>
+      <c r="AC11" s="639" t="n"/>
+      <c r="AD11" s="639" t="n"/>
+      <c r="AE11" s="639" t="n"/>
+      <c r="AF11" s="639" t="n"/>
+      <c r="AG11" s="639" t="n"/>
+      <c r="AH11" s="639" t="n"/>
+      <c r="AI11" s="639" t="n"/>
+      <c r="AJ11" s="639" t="n"/>
+      <c r="AK11" s="639" t="n"/>
+      <c r="AL11" s="639" t="n"/>
+      <c r="AM11" s="639" t="n"/>
+      <c r="AN11" s="639" t="n"/>
     </row>
-    <row r="6">
-      <c r="D6" s="345" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="639" t="n"/>
+      <c r="B12" s="639" t="n"/>
+      <c r="C12" s="639" t="n"/>
+      <c r="D12" s="345" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="E6" s="345" t="inlineStr">
+      <c r="E12" s="345" t="inlineStr">
         <is>
           <t>INEFFECTIVE</t>
         </is>
       </c>
-      <c r="F6" s="266" t="n"/>
-      <c r="G6" s="266" t="n"/>
+      <c r="F12" s="639" t="n"/>
+      <c r="G12" s="639" t="n"/>
+      <c r="H12" s="639" t="n"/>
+      <c r="I12" s="639" t="n"/>
+      <c r="J12" s="639" t="n"/>
+      <c r="K12" s="639" t="n"/>
+      <c r="L12" s="639" t="n"/>
+      <c r="M12" s="639" t="n"/>
+      <c r="N12" s="639" t="n"/>
+      <c r="O12" s="639" t="n"/>
+      <c r="P12" s="639" t="n"/>
+      <c r="Q12" s="639" t="n"/>
+      <c r="R12" s="639" t="n"/>
+      <c r="S12" s="639" t="n"/>
+      <c r="T12" s="639" t="n"/>
+      <c r="U12" s="639" t="n"/>
+      <c r="V12" s="639" t="n"/>
+      <c r="W12" s="639" t="n"/>
+      <c r="X12" s="639" t="n"/>
+      <c r="Y12" s="639" t="n"/>
+      <c r="Z12" s="639" t="n"/>
+      <c r="AA12" s="639" t="n"/>
+      <c r="AB12" s="639" t="n"/>
+      <c r="AC12" s="639" t="n"/>
+      <c r="AD12" s="639" t="n"/>
+      <c r="AE12" s="639" t="n"/>
+      <c r="AF12" s="639" t="n"/>
+      <c r="AG12" s="639" t="n"/>
+      <c r="AH12" s="639" t="n"/>
+      <c r="AI12" s="639" t="n"/>
+      <c r="AJ12" s="639" t="n"/>
+      <c r="AK12" s="639" t="n"/>
+      <c r="AL12" s="639" t="n"/>
+      <c r="AM12" s="639" t="n"/>
+      <c r="AN12" s="639" t="n"/>
     </row>
-    <row r="7">
-      <c r="D7" s="345" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="639" t="n"/>
+      <c r="B13" s="639" t="n"/>
+      <c r="C13" s="639" t="n"/>
+      <c r="D13" s="345" t="inlineStr">
         <is>
           <t>PUR</t>
         </is>
       </c>
-      <c r="E7" s="345" t="inlineStr">
+      <c r="E13" s="345" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
       </c>
-      <c r="F7" s="266" t="n"/>
+      <c r="F13" s="639" t="n"/>
+      <c r="G13" s="639" t="n"/>
+      <c r="H13" s="639" t="n"/>
+      <c r="I13" s="639" t="n"/>
+      <c r="J13" s="639" t="n"/>
+      <c r="K13" s="639" t="n"/>
+      <c r="L13" s="639" t="n"/>
+      <c r="M13" s="639" t="n"/>
+      <c r="N13" s="639" t="n"/>
+      <c r="O13" s="639" t="n"/>
+      <c r="P13" s="639" t="n"/>
+      <c r="Q13" s="639" t="n"/>
+      <c r="R13" s="639" t="n"/>
+      <c r="S13" s="639" t="n"/>
+      <c r="T13" s="639" t="n"/>
+      <c r="U13" s="639" t="n"/>
+      <c r="V13" s="639" t="n"/>
+      <c r="W13" s="639" t="n"/>
+      <c r="X13" s="639" t="n"/>
+      <c r="Y13" s="639" t="n"/>
+      <c r="Z13" s="639" t="n"/>
+      <c r="AA13" s="639" t="n"/>
+      <c r="AB13" s="639" t="n"/>
+      <c r="AC13" s="639" t="n"/>
+      <c r="AD13" s="639" t="n"/>
+      <c r="AE13" s="639" t="n"/>
+      <c r="AF13" s="639" t="n"/>
+      <c r="AG13" s="639" t="n"/>
+      <c r="AH13" s="639" t="n"/>
+      <c r="AI13" s="639" t="n"/>
+      <c r="AJ13" s="639" t="n"/>
+      <c r="AK13" s="639" t="n"/>
+      <c r="AL13" s="639" t="n"/>
+      <c r="AM13" s="639" t="n"/>
+      <c r="AN13" s="639" t="n"/>
     </row>
-    <row r="8">
-      <c r="D8" s="345" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="639" t="n"/>
+      <c r="B14" s="639" t="n"/>
+      <c r="C14" s="639" t="n"/>
+      <c r="D14" s="345" t="inlineStr">
         <is>
           <t>WHS</t>
         </is>
       </c>
-      <c r="F8" s="266" t="n"/>
+      <c r="E14" s="639" t="n"/>
+      <c r="F14" s="639" t="n"/>
+      <c r="G14" s="639" t="n"/>
+      <c r="H14" s="639" t="n"/>
+      <c r="I14" s="639" t="n"/>
+      <c r="J14" s="639" t="n"/>
+      <c r="K14" s="639" t="n"/>
+      <c r="L14" s="639" t="n"/>
+      <c r="M14" s="639" t="n"/>
+      <c r="N14" s="639" t="n"/>
+      <c r="O14" s="639" t="n"/>
+      <c r="P14" s="639" t="n"/>
+      <c r="Q14" s="639" t="n"/>
+      <c r="R14" s="639" t="n"/>
+      <c r="S14" s="639" t="n"/>
+      <c r="T14" s="639" t="n"/>
+      <c r="U14" s="639" t="n"/>
+      <c r="V14" s="639" t="n"/>
+      <c r="W14" s="639" t="n"/>
+      <c r="X14" s="639" t="n"/>
+      <c r="Y14" s="639" t="n"/>
+      <c r="Z14" s="639" t="n"/>
+      <c r="AA14" s="639" t="n"/>
+      <c r="AB14" s="639" t="n"/>
+      <c r="AC14" s="639" t="n"/>
+      <c r="AD14" s="639" t="n"/>
+      <c r="AE14" s="639" t="n"/>
+      <c r="AF14" s="639" t="n"/>
+      <c r="AG14" s="639" t="n"/>
+      <c r="AH14" s="639" t="n"/>
+      <c r="AI14" s="639" t="n"/>
+      <c r="AJ14" s="639" t="n"/>
+      <c r="AK14" s="639" t="n"/>
+      <c r="AL14" s="639" t="n"/>
+      <c r="AM14" s="639" t="n"/>
+      <c r="AN14" s="639" t="n"/>
     </row>
-    <row r="9">
-      <c r="D9" s="345" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="639" t="n"/>
+      <c r="B15" s="639" t="n"/>
+      <c r="C15" s="639" t="n"/>
+      <c r="D15" s="345" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="F9" s="266" t="n"/>
+      <c r="E15" s="639" t="n"/>
+      <c r="F15" s="639" t="n"/>
+      <c r="G15" s="639" t="n"/>
+      <c r="H15" s="639" t="n"/>
+      <c r="I15" s="639" t="n"/>
+      <c r="J15" s="639" t="n"/>
+      <c r="K15" s="639" t="n"/>
+      <c r="L15" s="639" t="n"/>
+      <c r="M15" s="639" t="n"/>
+      <c r="N15" s="639" t="n"/>
+      <c r="O15" s="639" t="n"/>
+      <c r="P15" s="639" t="n"/>
+      <c r="Q15" s="639" t="n"/>
+      <c r="R15" s="639" t="n"/>
+      <c r="S15" s="639" t="n"/>
+      <c r="T15" s="639" t="n"/>
+      <c r="U15" s="639" t="n"/>
+      <c r="V15" s="639" t="n"/>
+      <c r="W15" s="639" t="n"/>
+      <c r="X15" s="639" t="n"/>
+      <c r="Y15" s="639" t="n"/>
+      <c r="Z15" s="639" t="n"/>
+      <c r="AA15" s="639" t="n"/>
+      <c r="AB15" s="639" t="n"/>
+      <c r="AC15" s="639" t="n"/>
+      <c r="AD15" s="639" t="n"/>
+      <c r="AE15" s="639" t="n"/>
+      <c r="AF15" s="639" t="n"/>
+      <c r="AG15" s="639" t="n"/>
+      <c r="AH15" s="639" t="n"/>
+      <c r="AI15" s="639" t="n"/>
+      <c r="AJ15" s="639" t="n"/>
+      <c r="AK15" s="639" t="n"/>
+      <c r="AL15" s="639" t="n"/>
+      <c r="AM15" s="639" t="n"/>
+      <c r="AN15" s="639" t="n"/>
     </row>
-    <row r="10">
-      <c r="D10" s="345" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="639" t="n"/>
+      <c r="B16" s="639" t="n"/>
+      <c r="C16" s="639" t="n"/>
+      <c r="D16" s="345" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="F10" s="266" t="n"/>
+      <c r="E16" s="639" t="n"/>
+      <c r="F16" s="639" t="n"/>
+      <c r="G16" s="639" t="n"/>
+      <c r="H16" s="639" t="n"/>
+      <c r="I16" s="639" t="n"/>
+      <c r="J16" s="639" t="n"/>
+      <c r="K16" s="639" t="n"/>
+      <c r="L16" s="639" t="n"/>
+      <c r="M16" s="639" t="n"/>
+      <c r="N16" s="639" t="n"/>
+      <c r="O16" s="639" t="n"/>
+      <c r="P16" s="639" t="n"/>
+      <c r="Q16" s="639" t="n"/>
+      <c r="R16" s="639" t="n"/>
+      <c r="S16" s="639" t="n"/>
+      <c r="T16" s="639" t="n"/>
+      <c r="U16" s="639" t="n"/>
+      <c r="V16" s="639" t="n"/>
+      <c r="W16" s="639" t="n"/>
+      <c r="X16" s="639" t="n"/>
+      <c r="Y16" s="639" t="n"/>
+      <c r="Z16" s="639" t="n"/>
+      <c r="AA16" s="639" t="n"/>
+      <c r="AB16" s="639" t="n"/>
+      <c r="AC16" s="639" t="n"/>
+      <c r="AD16" s="639" t="n"/>
+      <c r="AE16" s="639" t="n"/>
+      <c r="AF16" s="639" t="n"/>
+      <c r="AG16" s="639" t="n"/>
+      <c r="AH16" s="639" t="n"/>
+      <c r="AI16" s="639" t="n"/>
+      <c r="AJ16" s="639" t="n"/>
+      <c r="AK16" s="639" t="n"/>
+      <c r="AL16" s="639" t="n"/>
+      <c r="AM16" s="639" t="n"/>
+      <c r="AN16" s="639" t="n"/>
     </row>
-    <row r="11">
-      <c r="D11" s="345" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="639" t="n"/>
+      <c r="B17" s="639" t="n"/>
+      <c r="C17" s="639" t="n"/>
+      <c r="D17" s="345" t="inlineStr">
         <is>
           <t>MGT</t>
         </is>
       </c>
-      <c r="F11" s="266" t="n"/>
+      <c r="E17" s="639" t="n"/>
+      <c r="F17" s="639" t="n"/>
+      <c r="G17" s="639" t="n"/>
+      <c r="H17" s="639" t="n"/>
+      <c r="I17" s="639" t="n"/>
+      <c r="J17" s="639" t="n"/>
+      <c r="K17" s="639" t="n"/>
+      <c r="L17" s="639" t="n"/>
+      <c r="M17" s="639" t="n"/>
+      <c r="N17" s="639" t="n"/>
+      <c r="O17" s="639" t="n"/>
+      <c r="P17" s="639" t="n"/>
+      <c r="Q17" s="639" t="n"/>
+      <c r="R17" s="639" t="n"/>
+      <c r="S17" s="639" t="n"/>
+      <c r="T17" s="639" t="n"/>
+      <c r="U17" s="639" t="n"/>
+      <c r="V17" s="639" t="n"/>
+      <c r="W17" s="639" t="n"/>
+      <c r="X17" s="639" t="n"/>
+      <c r="Y17" s="639" t="n"/>
+      <c r="Z17" s="639" t="n"/>
+      <c r="AA17" s="639" t="n"/>
+      <c r="AB17" s="639" t="n"/>
+      <c r="AC17" s="639" t="n"/>
+      <c r="AD17" s="639" t="n"/>
+      <c r="AE17" s="639" t="n"/>
+      <c r="AF17" s="639" t="n"/>
+      <c r="AG17" s="639" t="n"/>
+      <c r="AH17" s="639" t="n"/>
+      <c r="AI17" s="639" t="n"/>
+      <c r="AJ17" s="639" t="n"/>
+      <c r="AK17" s="639" t="n"/>
+      <c r="AL17" s="639" t="n"/>
+      <c r="AM17" s="639" t="n"/>
+      <c r="AN17" s="639" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="639" t="n"/>
+      <c r="B18" s="639" t="n"/>
+      <c r="C18" s="639" t="n"/>
+      <c r="D18" s="639" t="n"/>
+      <c r="E18" s="639" t="n"/>
+      <c r="F18" s="639" t="n"/>
+      <c r="G18" s="639" t="n"/>
+      <c r="H18" s="639" t="n"/>
+      <c r="I18" s="639" t="n"/>
+      <c r="J18" s="639" t="n"/>
+      <c r="K18" s="639" t="n"/>
+      <c r="L18" s="639" t="n"/>
+      <c r="M18" s="639" t="n"/>
+      <c r="N18" s="639" t="n"/>
+      <c r="O18" s="639" t="n"/>
+      <c r="P18" s="639" t="n"/>
+      <c r="Q18" s="639" t="n"/>
+      <c r="R18" s="639" t="n"/>
+      <c r="S18" s="639" t="n"/>
+      <c r="T18" s="639" t="n"/>
+      <c r="U18" s="639" t="n"/>
+      <c r="V18" s="639" t="n"/>
+      <c r="W18" s="639" t="n"/>
+      <c r="X18" s="639" t="n"/>
+      <c r="Y18" s="639" t="n"/>
+      <c r="Z18" s="639" t="n"/>
+      <c r="AA18" s="639" t="n"/>
+      <c r="AB18" s="639" t="n"/>
+      <c r="AC18" s="639" t="n"/>
+      <c r="AD18" s="639" t="n"/>
+      <c r="AE18" s="639" t="n"/>
+      <c r="AF18" s="639" t="n"/>
+      <c r="AG18" s="639" t="n"/>
+      <c r="AH18" s="639" t="n"/>
+      <c r="AI18" s="639" t="n"/>
+      <c r="AJ18" s="639" t="n"/>
+      <c r="AK18" s="639" t="n"/>
+      <c r="AL18" s="639" t="n"/>
+      <c r="AM18" s="639" t="n"/>
+      <c r="AN18" s="639" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="639" t="n"/>
+      <c r="B19" s="639" t="n"/>
+      <c r="C19" s="639" t="n"/>
+      <c r="D19" s="639" t="n"/>
+      <c r="E19" s="639" t="n"/>
+      <c r="F19" s="639" t="n"/>
+      <c r="G19" s="639" t="n"/>
+      <c r="H19" s="639" t="n"/>
+      <c r="I19" s="639" t="n"/>
+      <c r="J19" s="639" t="n"/>
+      <c r="K19" s="639" t="n"/>
+      <c r="L19" s="639" t="n"/>
+      <c r="M19" s="639" t="n"/>
+      <c r="N19" s="639" t="n"/>
+      <c r="O19" s="639" t="n"/>
+      <c r="P19" s="639" t="n"/>
+      <c r="Q19" s="639" t="n"/>
+      <c r="R19" s="639" t="n"/>
+      <c r="S19" s="639" t="n"/>
+      <c r="T19" s="639" t="n"/>
+      <c r="U19" s="639" t="n"/>
+      <c r="V19" s="639" t="n"/>
+      <c r="W19" s="639" t="n"/>
+      <c r="X19" s="639" t="n"/>
+      <c r="Y19" s="639" t="n"/>
+      <c r="Z19" s="639" t="n"/>
+      <c r="AA19" s="639" t="n"/>
+      <c r="AB19" s="639" t="n"/>
+      <c r="AC19" s="639" t="n"/>
+      <c r="AD19" s="639" t="n"/>
+      <c r="AE19" s="639" t="n"/>
+      <c r="AF19" s="639" t="n"/>
+      <c r="AG19" s="639" t="n"/>
+      <c r="AH19" s="639" t="n"/>
+      <c r="AI19" s="639" t="n"/>
+      <c r="AJ19" s="639" t="n"/>
+      <c r="AK19" s="639" t="n"/>
+      <c r="AL19" s="639" t="n"/>
+      <c r="AM19" s="639" t="n"/>
+      <c r="AN19" s="639" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="639" t="n"/>
+      <c r="B20" s="639" t="n"/>
+      <c r="C20" s="639" t="n"/>
+      <c r="D20" s="639" t="n"/>
+      <c r="E20" s="639" t="n"/>
+      <c r="F20" s="639" t="n"/>
+      <c r="G20" s="639" t="n"/>
+      <c r="H20" s="639" t="n"/>
+      <c r="I20" s="639" t="n"/>
+      <c r="J20" s="639" t="n"/>
+      <c r="K20" s="639" t="n"/>
+      <c r="L20" s="639" t="n"/>
+      <c r="M20" s="639" t="n"/>
+      <c r="N20" s="639" t="n"/>
+      <c r="O20" s="639" t="n"/>
+      <c r="P20" s="639" t="n"/>
+      <c r="Q20" s="639" t="n"/>
+      <c r="R20" s="639" t="n"/>
+      <c r="S20" s="639" t="n"/>
+      <c r="T20" s="639" t="n"/>
+      <c r="U20" s="639" t="n"/>
+      <c r="V20" s="639" t="n"/>
+      <c r="W20" s="639" t="n"/>
+      <c r="X20" s="639" t="n"/>
+      <c r="Y20" s="639" t="n"/>
+      <c r="Z20" s="639" t="n"/>
+      <c r="AA20" s="639" t="n"/>
+      <c r="AB20" s="639" t="n"/>
+      <c r="AC20" s="639" t="n"/>
+      <c r="AD20" s="639" t="n"/>
+      <c r="AE20" s="639" t="n"/>
+      <c r="AF20" s="639" t="n"/>
+      <c r="AG20" s="639" t="n"/>
+      <c r="AH20" s="639" t="n"/>
+      <c r="AI20" s="639" t="n"/>
+      <c r="AJ20" s="639" t="n"/>
+      <c r="AK20" s="639" t="n"/>
+      <c r="AL20" s="639" t="n"/>
+      <c r="AM20" s="639" t="n"/>
+      <c r="AN20" s="639" t="n"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <mergeCells count="14">
+    <mergeCell ref="AI2:AN2"/>
+    <mergeCell ref="I1:AD3"/>
+    <mergeCell ref="AE4:AH4"/>
+    <mergeCell ref="AI1:AN1"/>
+    <mergeCell ref="I5:AD5"/>
+    <mergeCell ref="AE3:AH3"/>
+    <mergeCell ref="AI5:AN5"/>
+    <mergeCell ref="A1:H5"/>
+    <mergeCell ref="AI4:AN4"/>
+    <mergeCell ref="AE2:AH2"/>
+    <mergeCell ref="I4:AD4"/>
+    <mergeCell ref="AI3:AN3"/>
+    <mergeCell ref="AE1:AH1"/>
+    <mergeCell ref="AE5:AH5"/>
+  </mergeCells>
+  <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 

--- a/04-Bieu-Mau/04-FRM-400/FRM-411_Outsourced_Process_Incoming_Verification.xlsx
+++ b/04-Bieu-Mau/04-FRM-400/FRM-411_Outsourced_Process_Incoming_Verification.xlsx
@@ -789,7 +789,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="369">
+  <borders count="396">
     <border>
       <left/>
       <right/>
@@ -4793,12 +4793,346 @@
       <bottom style="medium">
         <color rgb="002C9CD7"/>
       </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="000078D4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="000078D4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="000078D4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="000078D4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="000078D4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="640">
+  <cellXfs count="748">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -6237,6 +6571,276 @@
     </xf>
     <xf numFmtId="0" fontId="89" fillId="47" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="370" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="370" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="371" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="372" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="373" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="373" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="375" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="376" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="376" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="377" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="130" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="378" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="378" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="379" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="380" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="370" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="370" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="371" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="372" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="373" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="373" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="375" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="376" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="376" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="377" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="370" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="371" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="4" borderId="372" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="4" borderId="373" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="4" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="4" borderId="335" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="4" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="89" fillId="4" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="89" fillId="4" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="89" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="89" fillId="4" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="87" fillId="4" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="87" fillId="4" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="87" fillId="4" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="87" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="3" borderId="269" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="3" borderId="381" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="3" borderId="380" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="382" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="268" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="382" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="268" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="383" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="384" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="377" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="386" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="388" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="389" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="392" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="385" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="387" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="390" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="391" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="394" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="395" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -6321,7 +6925,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1303776" cy="376089"/>
+    <ext cx="1123950" cy="323850"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -6335,9 +6939,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6354,7 +6955,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1303776" cy="376089"/>
+    <ext cx="1123950" cy="323850"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -6368,37 +6969,36 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
   </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>0</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="523875" cy="523875"/>
+    <ext cx="1123950" cy="323850"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6621,49 +7221,49 @@
   <dimension ref="A1:AN44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="2.329999923706055" customWidth="1" style="329" min="1" max="1"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="2" max="2"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="3" max="3"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="4" max="4"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="5" max="5"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="6" max="6"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="7" max="7"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="8" max="8"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="9" max="9"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="10" max="10"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="11" max="11"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="12" max="12"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="13" max="13"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="14" max="14"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="15" max="15"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="16" max="16"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="17" max="17"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="18" max="18"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="19" max="19"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="20" max="20"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="21" max="21"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="22" max="22"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="23" max="23"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="24" max="24"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="25" max="25"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="26" max="26"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="27" max="27"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="28" max="28"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="29" max="29"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="30" max="30"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="31" max="31"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="32" max="32"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="33" max="33"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="34" max="34"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="35" max="35"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="36" max="36"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="37" max="37"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="38" max="38"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="39" max="39"/>
-    <col width="2.329999923706055" customWidth="1" style="329" min="40" max="40"/>
+    <col width="2.33" customWidth="1" style="329" min="1" max="1"/>
+    <col width="2.33" customWidth="1" style="329" min="2" max="2"/>
+    <col width="2.33" customWidth="1" style="329" min="3" max="3"/>
+    <col width="2.33" customWidth="1" style="329" min="4" max="4"/>
+    <col width="2.33" customWidth="1" style="329" min="5" max="5"/>
+    <col width="2.33" customWidth="1" style="329" min="6" max="6"/>
+    <col width="2.33" customWidth="1" style="329" min="7" max="7"/>
+    <col width="2.33" customWidth="1" style="329" min="8" max="8"/>
+    <col width="2.33" customWidth="1" style="329" min="9" max="9"/>
+    <col width="2.33" customWidth="1" style="329" min="10" max="10"/>
+    <col width="2.33" customWidth="1" style="329" min="11" max="11"/>
+    <col width="2.33" customWidth="1" style="329" min="12" max="12"/>
+    <col width="2.33" customWidth="1" style="329" min="13" max="13"/>
+    <col width="2.33" customWidth="1" style="329" min="14" max="14"/>
+    <col width="2.33" customWidth="1" style="329" min="15" max="15"/>
+    <col width="2.33" customWidth="1" style="329" min="16" max="16"/>
+    <col width="2.33" customWidth="1" style="329" min="17" max="17"/>
+    <col width="2.33" customWidth="1" style="329" min="18" max="18"/>
+    <col width="2.33" customWidth="1" style="329" min="19" max="19"/>
+    <col width="2.33" customWidth="1" style="329" min="20" max="20"/>
+    <col width="2.33" customWidth="1" style="329" min="21" max="21"/>
+    <col width="2.33" customWidth="1" style="329" min="22" max="22"/>
+    <col width="2.33" customWidth="1" style="329" min="23" max="23"/>
+    <col width="2.33" customWidth="1" style="329" min="24" max="24"/>
+    <col width="2.33" customWidth="1" style="329" min="25" max="25"/>
+    <col width="2.33" customWidth="1" style="329" min="26" max="26"/>
+    <col width="2.33" customWidth="1" style="329" min="27" max="27"/>
+    <col width="2.33" customWidth="1" style="329" min="28" max="28"/>
+    <col width="2.33" customWidth="1" style="329" min="29" max="29"/>
+    <col width="2.33" customWidth="1" style="329" min="30" max="30"/>
+    <col width="2.33" customWidth="1" style="329" min="31" max="31"/>
+    <col width="2.33" customWidth="1" style="329" min="32" max="32"/>
+    <col width="2.33" customWidth="1" style="329" min="33" max="33"/>
+    <col width="2.33" customWidth="1" style="329" min="34" max="34"/>
+    <col width="2.33" customWidth="1" style="329" min="35" max="35"/>
+    <col width="2.33" customWidth="1" style="329" min="36" max="36"/>
+    <col width="2.33" customWidth="1" style="329" min="37" max="37"/>
+    <col width="2.33" customWidth="1" style="329" min="38" max="38"/>
+    <col width="2.33" customWidth="1" style="329" min="39" max="39"/>
+    <col width="2.33" customWidth="1" style="329" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="329">
+    <row r="1" hidden="1" s="329">
       <c r="A1" s="526" t="n"/>
       <c r="B1" s="527" t="n"/>
       <c r="C1" s="527" t="n"/>
@@ -6714,506 +7314,580 @@
       <c r="AN1" s="528" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1" s="329">
-      <c r="A2" s="533" t="n"/>
-      <c r="H2" s="534" t="n"/>
-      <c r="I2" s="533" t="n"/>
-      <c r="AD2" s="534" t="n"/>
-      <c r="AE2" s="535" t="n"/>
-      <c r="AF2" s="408" t="n"/>
-      <c r="AG2" s="408" t="n"/>
-      <c r="AH2" s="536" t="n"/>
-      <c r="AI2" s="537" t="inlineStr">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="640" t="n"/>
+      <c r="C2" s="640" t="n"/>
+      <c r="D2" s="640" t="n"/>
+      <c r="E2" s="640" t="n"/>
+      <c r="F2" s="640" t="n"/>
+      <c r="G2" s="640" t="n"/>
+      <c r="H2" s="641" t="n"/>
+      <c r="I2" s="640" t="n"/>
+      <c r="J2" s="640" t="n"/>
+      <c r="K2" s="640" t="n"/>
+      <c r="L2" s="640" t="n"/>
+      <c r="M2" s="640" t="n"/>
+      <c r="N2" s="640" t="n"/>
+      <c r="O2" s="640" t="n"/>
+      <c r="P2" s="640" t="n"/>
+      <c r="Q2" s="640" t="n"/>
+      <c r="R2" s="640" t="n"/>
+      <c r="S2" s="640" t="n"/>
+      <c r="T2" s="640" t="n"/>
+      <c r="U2" s="640" t="n"/>
+      <c r="V2" s="640" t="n"/>
+      <c r="W2" s="640" t="n"/>
+      <c r="X2" s="640" t="n"/>
+      <c r="Y2" s="640" t="n"/>
+      <c r="Z2" s="640" t="n"/>
+      <c r="AA2" s="640" t="n"/>
+      <c r="AB2" s="640" t="n"/>
+      <c r="AC2" s="640" t="n"/>
+      <c r="AD2" s="641" t="n"/>
+      <c r="AE2" s="642" t="n"/>
+      <c r="AF2" s="643" t="n"/>
+      <c r="AG2" s="643" t="n"/>
+      <c r="AH2" s="644" t="n"/>
+      <c r="AI2" s="645" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AJ2" s="408" t="n"/>
-      <c r="AK2" s="408" t="n"/>
-      <c r="AL2" s="408" t="n"/>
-      <c r="AM2" s="408" t="n"/>
-      <c r="AN2" s="538" t="n"/>
+      <c r="AJ2" s="646" t="n"/>
+      <c r="AK2" s="646" t="n"/>
+      <c r="AL2" s="646" t="n"/>
+      <c r="AM2" s="646" t="n"/>
+      <c r="AN2" s="647" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1" s="329">
-      <c r="A3" s="533" t="n"/>
-      <c r="H3" s="534" t="n"/>
-      <c r="I3" s="533" t="n"/>
-      <c r="AD3" s="534" t="n"/>
-      <c r="AE3" s="535" t="n"/>
-      <c r="AF3" s="408" t="n"/>
-      <c r="AG3" s="408" t="n"/>
-      <c r="AH3" s="536" t="n"/>
-      <c r="AI3" s="537" t="inlineStr">
+      <c r="A3" s="648" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="649" t="n"/>
+      <c r="I3" s="25" t="n"/>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="25" t="n"/>
+      <c r="L3" s="25" t="n"/>
+      <c r="M3" s="25" t="n"/>
+      <c r="N3" s="25" t="n"/>
+      <c r="O3" s="25" t="n"/>
+      <c r="P3" s="25" t="n"/>
+      <c r="Q3" s="25" t="n"/>
+      <c r="R3" s="25" t="n"/>
+      <c r="S3" s="25" t="n"/>
+      <c r="T3" s="25" t="n"/>
+      <c r="U3" s="25" t="n"/>
+      <c r="V3" s="25" t="n"/>
+      <c r="W3" s="25" t="n"/>
+      <c r="X3" s="25" t="n"/>
+      <c r="Y3" s="25" t="n"/>
+      <c r="Z3" s="25" t="n"/>
+      <c r="AA3" s="25" t="n"/>
+      <c r="AB3" s="25" t="n"/>
+      <c r="AC3" s="25" t="n"/>
+      <c r="AD3" s="649" t="n"/>
+      <c r="AE3" s="650" t="n"/>
+      <c r="AF3" s="651" t="n"/>
+      <c r="AG3" s="651" t="n"/>
+      <c r="AH3" s="652" t="n"/>
+      <c r="AI3" s="653" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AJ3" s="408" t="n"/>
-      <c r="AK3" s="408" t="n"/>
-      <c r="AL3" s="408" t="n"/>
-      <c r="AM3" s="408" t="n"/>
-      <c r="AN3" s="538" t="n"/>
+      <c r="AJ3" s="654" t="n"/>
+      <c r="AK3" s="654" t="n"/>
+      <c r="AL3" s="654" t="n"/>
+      <c r="AM3" s="654" t="n"/>
+      <c r="AN3" s="655" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1" s="329">
-      <c r="A4" s="533" t="n"/>
-      <c r="H4" s="534" t="n"/>
-      <c r="I4" s="539" t="inlineStr">
+      <c r="A4" s="648" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="25" t="n"/>
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="649" t="n"/>
+      <c r="I4" s="656" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AD4" s="534" t="n"/>
-      <c r="AE4" s="535" t="n"/>
-      <c r="AF4" s="408" t="n"/>
-      <c r="AG4" s="408" t="n"/>
-      <c r="AH4" s="536" t="n"/>
-      <c r="AI4" s="537" t="inlineStr">
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="25" t="n"/>
+      <c r="L4" s="25" t="n"/>
+      <c r="M4" s="25" t="n"/>
+      <c r="N4" s="25" t="n"/>
+      <c r="O4" s="25" t="n"/>
+      <c r="P4" s="25" t="n"/>
+      <c r="Q4" s="25" t="n"/>
+      <c r="R4" s="25" t="n"/>
+      <c r="S4" s="25" t="n"/>
+      <c r="T4" s="25" t="n"/>
+      <c r="U4" s="25" t="n"/>
+      <c r="V4" s="25" t="n"/>
+      <c r="W4" s="25" t="n"/>
+      <c r="X4" s="25" t="n"/>
+      <c r="Y4" s="25" t="n"/>
+      <c r="Z4" s="25" t="n"/>
+      <c r="AA4" s="25" t="n"/>
+      <c r="AB4" s="25" t="n"/>
+      <c r="AC4" s="25" t="n"/>
+      <c r="AD4" s="649" t="n"/>
+      <c r="AE4" s="650" t="n"/>
+      <c r="AF4" s="651" t="n"/>
+      <c r="AG4" s="651" t="n"/>
+      <c r="AH4" s="652" t="n"/>
+      <c r="AI4" s="653" t="inlineStr">
         <is>
           <t>Purchasing + QA</t>
         </is>
       </c>
-      <c r="AJ4" s="408" t="n"/>
-      <c r="AK4" s="408" t="n"/>
-      <c r="AL4" s="408" t="n"/>
-      <c r="AM4" s="408" t="n"/>
-      <c r="AN4" s="538" t="n"/>
+      <c r="AJ4" s="654" t="n"/>
+      <c r="AK4" s="654" t="n"/>
+      <c r="AL4" s="654" t="n"/>
+      <c r="AM4" s="654" t="n"/>
+      <c r="AN4" s="655" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1" s="329">
-      <c r="A5" s="540" t="n"/>
-      <c r="B5" s="541" t="n"/>
-      <c r="C5" s="541" t="n"/>
-      <c r="D5" s="541" t="n"/>
-      <c r="E5" s="541" t="n"/>
-      <c r="F5" s="541" t="n"/>
-      <c r="G5" s="541" t="n"/>
-      <c r="H5" s="542" t="n"/>
-      <c r="I5" s="543" t="inlineStr">
+      <c r="A5" s="648" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="25" t="n"/>
+      <c r="H5" s="649" t="n"/>
+      <c r="I5" s="657" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="J5" s="541" t="n"/>
-      <c r="K5" s="541" t="n"/>
-      <c r="L5" s="541" t="n"/>
-      <c r="M5" s="541" t="n"/>
-      <c r="N5" s="541" t="n"/>
-      <c r="O5" s="541" t="n"/>
-      <c r="P5" s="541" t="n"/>
-      <c r="Q5" s="541" t="n"/>
-      <c r="R5" s="541" t="n"/>
-      <c r="S5" s="541" t="n"/>
-      <c r="T5" s="541" t="n"/>
-      <c r="U5" s="541" t="n"/>
-      <c r="V5" s="541" t="n"/>
-      <c r="W5" s="541" t="n"/>
-      <c r="X5" s="541" t="n"/>
-      <c r="Y5" s="541" t="n"/>
-      <c r="Z5" s="541" t="n"/>
-      <c r="AA5" s="541" t="n"/>
-      <c r="AB5" s="541" t="n"/>
-      <c r="AC5" s="541" t="n"/>
-      <c r="AD5" s="542" t="n"/>
-      <c r="AE5" s="544" t="n"/>
-      <c r="AF5" s="545" t="n"/>
-      <c r="AG5" s="545" t="n"/>
-      <c r="AH5" s="546" t="n"/>
-      <c r="AI5" s="547" t="inlineStr">
+      <c r="J5" s="25" t="n"/>
+      <c r="K5" s="25" t="n"/>
+      <c r="L5" s="25" t="n"/>
+      <c r="M5" s="25" t="n"/>
+      <c r="N5" s="25" t="n"/>
+      <c r="O5" s="25" t="n"/>
+      <c r="P5" s="25" t="n"/>
+      <c r="Q5" s="25" t="n"/>
+      <c r="R5" s="25" t="n"/>
+      <c r="S5" s="25" t="n"/>
+      <c r="T5" s="25" t="n"/>
+      <c r="U5" s="25" t="n"/>
+      <c r="V5" s="25" t="n"/>
+      <c r="W5" s="25" t="n"/>
+      <c r="X5" s="25" t="n"/>
+      <c r="Y5" s="25" t="n"/>
+      <c r="Z5" s="25" t="n"/>
+      <c r="AA5" s="25" t="n"/>
+      <c r="AB5" s="25" t="n"/>
+      <c r="AC5" s="25" t="n"/>
+      <c r="AD5" s="649" t="n"/>
+      <c r="AE5" s="650" t="n"/>
+      <c r="AF5" s="651" t="n"/>
+      <c r="AG5" s="651" t="n"/>
+      <c r="AH5" s="652" t="n"/>
+      <c r="AI5" s="653" t="inlineStr">
         <is>
           <t>General Manager</t>
         </is>
       </c>
-      <c r="AJ5" s="545" t="n"/>
-      <c r="AK5" s="545" t="n"/>
-      <c r="AL5" s="545" t="n"/>
-      <c r="AM5" s="545" t="n"/>
-      <c r="AN5" s="548" t="n"/>
+      <c r="AJ5" s="654" t="n"/>
+      <c r="AK5" s="654" t="n"/>
+      <c r="AL5" s="654" t="n"/>
+      <c r="AM5" s="654" t="n"/>
+      <c r="AN5" s="655" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1" s="329">
-      <c r="A6" s="452" t="n"/>
-      <c r="B6" s="452" t="n"/>
-      <c r="C6" s="452" t="n"/>
-      <c r="D6" s="452" t="n"/>
-      <c r="E6" s="452" t="n"/>
-      <c r="F6" s="452" t="n"/>
-      <c r="G6" s="452" t="n"/>
-      <c r="H6" s="452" t="n"/>
-      <c r="I6" s="452" t="n"/>
-      <c r="J6" s="452" t="n"/>
-      <c r="K6" s="452" t="n"/>
-      <c r="L6" s="452" t="n"/>
-      <c r="M6" s="452" t="n"/>
-      <c r="N6" s="452" t="n"/>
-      <c r="O6" s="452" t="n"/>
-      <c r="P6" s="452" t="n"/>
-      <c r="Q6" s="452" t="n"/>
-      <c r="R6" s="452" t="n"/>
-      <c r="S6" s="452" t="n"/>
-      <c r="T6" s="452" t="n"/>
-      <c r="U6" s="452" t="n"/>
-      <c r="V6" s="452" t="n"/>
-      <c r="W6" s="452" t="n"/>
-      <c r="X6" s="452" t="n"/>
-      <c r="Y6" s="452" t="n"/>
-      <c r="Z6" s="452" t="n"/>
-      <c r="AA6" s="452" t="n"/>
-      <c r="AB6" s="452" t="n"/>
-      <c r="AC6" s="452" t="n"/>
-      <c r="AD6" s="452" t="n"/>
-      <c r="AE6" s="452" t="n"/>
-      <c r="AF6" s="452" t="n"/>
-      <c r="AG6" s="452" t="n"/>
-      <c r="AH6" s="452" t="n"/>
-      <c r="AI6" s="452" t="n"/>
-      <c r="AJ6" s="452" t="n"/>
-      <c r="AK6" s="452" t="n"/>
-      <c r="AL6" s="452" t="n"/>
-      <c r="AM6" s="452" t="n"/>
-      <c r="AN6" s="452" t="n"/>
+    <row r="6" ht="15" customHeight="1" s="329">
+      <c r="A6" s="658" t="n"/>
+      <c r="B6" s="659" t="n"/>
+      <c r="C6" s="659" t="n"/>
+      <c r="D6" s="659" t="n"/>
+      <c r="E6" s="659" t="n"/>
+      <c r="F6" s="659" t="n"/>
+      <c r="G6" s="659" t="n"/>
+      <c r="H6" s="660" t="n"/>
+      <c r="I6" s="659" t="n"/>
+      <c r="J6" s="659" t="n"/>
+      <c r="K6" s="659" t="n"/>
+      <c r="L6" s="659" t="n"/>
+      <c r="M6" s="659" t="n"/>
+      <c r="N6" s="659" t="n"/>
+      <c r="O6" s="659" t="n"/>
+      <c r="P6" s="659" t="n"/>
+      <c r="Q6" s="659" t="n"/>
+      <c r="R6" s="659" t="n"/>
+      <c r="S6" s="659" t="n"/>
+      <c r="T6" s="659" t="n"/>
+      <c r="U6" s="659" t="n"/>
+      <c r="V6" s="659" t="n"/>
+      <c r="W6" s="659" t="n"/>
+      <c r="X6" s="659" t="n"/>
+      <c r="Y6" s="659" t="n"/>
+      <c r="Z6" s="659" t="n"/>
+      <c r="AA6" s="659" t="n"/>
+      <c r="AB6" s="659" t="n"/>
+      <c r="AC6" s="659" t="n"/>
+      <c r="AD6" s="660" t="n"/>
+      <c r="AE6" s="661" t="n"/>
+      <c r="AF6" s="661" t="n"/>
+      <c r="AG6" s="661" t="n"/>
+      <c r="AH6" s="662" t="n"/>
+      <c r="AI6" s="663" t="n"/>
+      <c r="AJ6" s="663" t="n"/>
+      <c r="AK6" s="663" t="n"/>
+      <c r="AL6" s="663" t="n"/>
+      <c r="AM6" s="663" t="n"/>
+      <c r="AN6" s="664" t="n"/>
     </row>
-    <row r="7" ht="18" customHeight="1" s="329">
-      <c r="A7" s="549" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1. REFERENCE INFORMATION</t>
-        </is>
-      </c>
-      <c r="B7" s="550" t="n"/>
-      <c r="C7" s="550" t="n"/>
-      <c r="D7" s="550" t="n"/>
-      <c r="E7" s="550" t="n"/>
-      <c r="F7" s="550" t="n"/>
-      <c r="G7" s="550" t="n"/>
-      <c r="H7" s="550" t="n"/>
-      <c r="I7" s="550" t="n"/>
-      <c r="J7" s="550" t="n"/>
-      <c r="K7" s="550" t="n"/>
-      <c r="L7" s="550" t="n"/>
-      <c r="M7" s="550" t="n"/>
-      <c r="N7" s="550" t="n"/>
-      <c r="O7" s="550" t="n"/>
-      <c r="P7" s="550" t="n"/>
-      <c r="Q7" s="550" t="n"/>
-      <c r="R7" s="550" t="n"/>
-      <c r="S7" s="550" t="n"/>
-      <c r="T7" s="550" t="n"/>
-      <c r="U7" s="550" t="n"/>
-      <c r="V7" s="550" t="n"/>
-      <c r="W7" s="550" t="n"/>
-      <c r="X7" s="550" t="n"/>
-      <c r="Y7" s="550" t="n"/>
-      <c r="Z7" s="550" t="n"/>
-      <c r="AA7" s="550" t="n"/>
-      <c r="AB7" s="550" t="n"/>
-      <c r="AC7" s="550" t="n"/>
-      <c r="AD7" s="550" t="n"/>
-      <c r="AE7" s="550" t="n"/>
-      <c r="AF7" s="550" t="n"/>
-      <c r="AG7" s="550" t="n"/>
-      <c r="AH7" s="550" t="n"/>
-      <c r="AI7" s="550" t="n"/>
-      <c r="AJ7" s="550" t="n"/>
-      <c r="AK7" s="550" t="n"/>
-      <c r="AL7" s="550" t="n"/>
-      <c r="AM7" s="550" t="n"/>
-      <c r="AN7" s="551" t="n"/>
+    <row r="7" ht="4" customHeight="1" s="329">
+      <c r="A7" s="665" t="n"/>
+      <c r="B7" s="666" t="n"/>
+      <c r="C7" s="666" t="n"/>
+      <c r="D7" s="666" t="n"/>
+      <c r="E7" s="666" t="n"/>
+      <c r="F7" s="666" t="n"/>
+      <c r="G7" s="666" t="n"/>
+      <c r="H7" s="666" t="n"/>
+      <c r="I7" s="666" t="n"/>
+      <c r="J7" s="666" t="n"/>
+      <c r="K7" s="666" t="n"/>
+      <c r="L7" s="666" t="n"/>
+      <c r="M7" s="666" t="n"/>
+      <c r="N7" s="666" t="n"/>
+      <c r="O7" s="666" t="n"/>
+      <c r="P7" s="666" t="n"/>
+      <c r="Q7" s="666" t="n"/>
+      <c r="R7" s="666" t="n"/>
+      <c r="S7" s="666" t="n"/>
+      <c r="T7" s="666" t="n"/>
+      <c r="U7" s="666" t="n"/>
+      <c r="V7" s="666" t="n"/>
+      <c r="W7" s="666" t="n"/>
+      <c r="X7" s="666" t="n"/>
+      <c r="Y7" s="666" t="n"/>
+      <c r="Z7" s="666" t="n"/>
+      <c r="AA7" s="666" t="n"/>
+      <c r="AB7" s="666" t="n"/>
+      <c r="AC7" s="666" t="n"/>
+      <c r="AD7" s="666" t="n"/>
+      <c r="AE7" s="666" t="n"/>
+      <c r="AF7" s="666" t="n"/>
+      <c r="AG7" s="666" t="n"/>
+      <c r="AH7" s="666" t="n"/>
+      <c r="AI7" s="666" t="n"/>
+      <c r="AJ7" s="666" t="n"/>
+      <c r="AK7" s="666" t="n"/>
+      <c r="AL7" s="666" t="n"/>
+      <c r="AM7" s="666" t="n"/>
+      <c r="AN7" s="666" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1" s="329">
-      <c r="A8" s="456" t="inlineStr">
+      <c r="A8" s="667" t="inlineStr">
         <is>
           <t>Incoming Verification ID</t>
         </is>
       </c>
-      <c r="B8" s="552" t="n"/>
-      <c r="C8" s="552" t="n"/>
-      <c r="D8" s="552" t="n"/>
-      <c r="E8" s="552" t="n"/>
-      <c r="F8" s="552" t="n"/>
-      <c r="G8" s="552" t="n"/>
-      <c r="H8" s="458" t="n"/>
-      <c r="I8" s="552" t="n"/>
-      <c r="J8" s="552" t="n"/>
-      <c r="K8" s="552" t="n"/>
-      <c r="L8" s="552" t="n"/>
-      <c r="M8" s="552" t="n"/>
-      <c r="N8" s="552" t="n"/>
-      <c r="O8" s="552" t="n"/>
-      <c r="P8" s="552" t="n"/>
-      <c r="Q8" s="552" t="n"/>
-      <c r="R8" s="552" t="n"/>
-      <c r="S8" s="552" t="n"/>
-      <c r="T8" s="552" t="n"/>
-      <c r="U8" s="459" t="inlineStr">
+      <c r="B8" s="317" t="n"/>
+      <c r="C8" s="317" t="n"/>
+      <c r="D8" s="317" t="n"/>
+      <c r="E8" s="317" t="n"/>
+      <c r="F8" s="317" t="n"/>
+      <c r="G8" s="317" t="n"/>
+      <c r="H8" s="668" t="n"/>
+      <c r="I8" s="317" t="n"/>
+      <c r="J8" s="317" t="n"/>
+      <c r="K8" s="317" t="n"/>
+      <c r="L8" s="317" t="n"/>
+      <c r="M8" s="317" t="n"/>
+      <c r="N8" s="317" t="n"/>
+      <c r="O8" s="317" t="n"/>
+      <c r="P8" s="317" t="n"/>
+      <c r="Q8" s="317" t="n"/>
+      <c r="R8" s="317" t="n"/>
+      <c r="S8" s="317" t="n"/>
+      <c r="T8" s="317" t="n"/>
+      <c r="U8" s="669" t="inlineStr">
         <is>
           <t>Disposition Status</t>
         </is>
       </c>
-      <c r="V8" s="552" t="n"/>
-      <c r="W8" s="552" t="n"/>
-      <c r="X8" s="552" t="n"/>
-      <c r="Y8" s="552" t="n"/>
-      <c r="Z8" s="552" t="n"/>
-      <c r="AA8" s="552" t="n"/>
-      <c r="AB8" s="553" t="n"/>
-      <c r="AC8" s="552" t="n"/>
-      <c r="AD8" s="552" t="n"/>
-      <c r="AE8" s="552" t="n"/>
-      <c r="AF8" s="552" t="n"/>
-      <c r="AG8" s="552" t="n"/>
-      <c r="AH8" s="552" t="n"/>
-      <c r="AI8" s="552" t="n"/>
-      <c r="AJ8" s="552" t="n"/>
-      <c r="AK8" s="552" t="n"/>
-      <c r="AL8" s="552" t="n"/>
-      <c r="AM8" s="552" t="n"/>
-      <c r="AN8" s="554" t="n"/>
+      <c r="V8" s="317" t="n"/>
+      <c r="W8" s="317" t="n"/>
+      <c r="X8" s="317" t="n"/>
+      <c r="Y8" s="317" t="n"/>
+      <c r="Z8" s="317" t="n"/>
+      <c r="AA8" s="317" t="n"/>
+      <c r="AB8" s="670" t="n"/>
+      <c r="AC8" s="317" t="n"/>
+      <c r="AD8" s="317" t="n"/>
+      <c r="AE8" s="317" t="n"/>
+      <c r="AF8" s="317" t="n"/>
+      <c r="AG8" s="317" t="n"/>
+      <c r="AH8" s="317" t="n"/>
+      <c r="AI8" s="317" t="n"/>
+      <c r="AJ8" s="317" t="n"/>
+      <c r="AK8" s="317" t="n"/>
+      <c r="AL8" s="317" t="n"/>
+      <c r="AM8" s="317" t="n"/>
+      <c r="AN8" s="319" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1" s="329">
-      <c r="A9" s="461" t="inlineStr">
+      <c r="A9" s="671" t="inlineStr">
         <is>
           <t>Supplier / Processor / Cert</t>
         </is>
       </c>
-      <c r="B9" s="409" t="n"/>
-      <c r="C9" s="409" t="n"/>
-      <c r="D9" s="409" t="n"/>
-      <c r="E9" s="409" t="n"/>
-      <c r="F9" s="409" t="n"/>
-      <c r="G9" s="409" t="n"/>
-      <c r="H9" s="462" t="n"/>
-      <c r="I9" s="409" t="n"/>
-      <c r="J9" s="409" t="n"/>
-      <c r="K9" s="409" t="n"/>
-      <c r="L9" s="409" t="n"/>
-      <c r="M9" s="409" t="n"/>
-      <c r="N9" s="409" t="n"/>
-      <c r="O9" s="409" t="n"/>
-      <c r="P9" s="409" t="n"/>
-      <c r="Q9" s="409" t="n"/>
-      <c r="R9" s="409" t="n"/>
-      <c r="S9" s="409" t="n"/>
-      <c r="T9" s="409" t="n"/>
-      <c r="U9" s="463" t="inlineStr">
+      <c r="B9" s="738" t="n"/>
+      <c r="C9" s="738" t="n"/>
+      <c r="D9" s="738" t="n"/>
+      <c r="E9" s="738" t="n"/>
+      <c r="F9" s="738" t="n"/>
+      <c r="G9" s="738" t="n"/>
+      <c r="H9" s="672" t="n"/>
+      <c r="I9" s="738" t="n"/>
+      <c r="J9" s="738" t="n"/>
+      <c r="K9" s="738" t="n"/>
+      <c r="L9" s="738" t="n"/>
+      <c r="M9" s="738" t="n"/>
+      <c r="N9" s="738" t="n"/>
+      <c r="O9" s="738" t="n"/>
+      <c r="P9" s="738" t="n"/>
+      <c r="Q9" s="738" t="n"/>
+      <c r="R9" s="738" t="n"/>
+      <c r="S9" s="738" t="n"/>
+      <c r="T9" s="738" t="n"/>
+      <c r="U9" s="673" t="inlineStr">
         <is>
           <t>PO / Cert / Lot Ref</t>
         </is>
       </c>
-      <c r="V9" s="409" t="n"/>
-      <c r="W9" s="409" t="n"/>
-      <c r="X9" s="409" t="n"/>
-      <c r="Y9" s="409" t="n"/>
-      <c r="Z9" s="409" t="n"/>
-      <c r="AA9" s="409" t="n"/>
-      <c r="AB9" s="555" t="n"/>
-      <c r="AC9" s="409" t="n"/>
-      <c r="AD9" s="409" t="n"/>
-      <c r="AE9" s="409" t="n"/>
-      <c r="AF9" s="409" t="n"/>
-      <c r="AG9" s="409" t="n"/>
-      <c r="AH9" s="409" t="n"/>
-      <c r="AI9" s="409" t="n"/>
-      <c r="AJ9" s="409" t="n"/>
-      <c r="AK9" s="409" t="n"/>
-      <c r="AL9" s="409" t="n"/>
-      <c r="AM9" s="409" t="n"/>
-      <c r="AN9" s="556" t="n"/>
+      <c r="V9" s="738" t="n"/>
+      <c r="W9" s="738" t="n"/>
+      <c r="X9" s="738" t="n"/>
+      <c r="Y9" s="738" t="n"/>
+      <c r="Z9" s="738" t="n"/>
+      <c r="AA9" s="738" t="n"/>
+      <c r="AB9" s="674" t="n"/>
+      <c r="AC9" s="738" t="n"/>
+      <c r="AD9" s="738" t="n"/>
+      <c r="AE9" s="738" t="n"/>
+      <c r="AF9" s="738" t="n"/>
+      <c r="AG9" s="738" t="n"/>
+      <c r="AH9" s="738" t="n"/>
+      <c r="AI9" s="738" t="n"/>
+      <c r="AJ9" s="738" t="n"/>
+      <c r="AK9" s="738" t="n"/>
+      <c r="AL9" s="738" t="n"/>
+      <c r="AM9" s="738" t="n"/>
+      <c r="AN9" s="739" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1" s="329">
-      <c r="A10" s="461" t="inlineStr">
+      <c r="A10" s="671" t="inlineStr">
         <is>
           <t>Part / Lot / Qty</t>
         </is>
       </c>
-      <c r="B10" s="409" t="n"/>
-      <c r="C10" s="409" t="n"/>
-      <c r="D10" s="409" t="n"/>
-      <c r="E10" s="409" t="n"/>
-      <c r="F10" s="409" t="n"/>
-      <c r="G10" s="409" t="n"/>
-      <c r="H10" s="462" t="n"/>
-      <c r="I10" s="409" t="n"/>
-      <c r="J10" s="409" t="n"/>
-      <c r="K10" s="409" t="n"/>
-      <c r="L10" s="409" t="n"/>
-      <c r="M10" s="409" t="n"/>
-      <c r="N10" s="409" t="n"/>
-      <c r="O10" s="409" t="n"/>
-      <c r="P10" s="409" t="n"/>
-      <c r="Q10" s="409" t="n"/>
-      <c r="R10" s="409" t="n"/>
-      <c r="S10" s="409" t="n"/>
-      <c r="T10" s="409" t="n"/>
-      <c r="U10" s="463" t="inlineStr">
+      <c r="B10" s="738" t="n"/>
+      <c r="C10" s="738" t="n"/>
+      <c r="D10" s="738" t="n"/>
+      <c r="E10" s="738" t="n"/>
+      <c r="F10" s="738" t="n"/>
+      <c r="G10" s="738" t="n"/>
+      <c r="H10" s="672" t="n"/>
+      <c r="I10" s="738" t="n"/>
+      <c r="J10" s="738" t="n"/>
+      <c r="K10" s="738" t="n"/>
+      <c r="L10" s="738" t="n"/>
+      <c r="M10" s="738" t="n"/>
+      <c r="N10" s="738" t="n"/>
+      <c r="O10" s="738" t="n"/>
+      <c r="P10" s="738" t="n"/>
+      <c r="Q10" s="738" t="n"/>
+      <c r="R10" s="738" t="n"/>
+      <c r="S10" s="738" t="n"/>
+      <c r="T10" s="738" t="n"/>
+      <c r="U10" s="673" t="inlineStr">
         <is>
           <t>Supplier-Quality Owner</t>
         </is>
       </c>
-      <c r="V10" s="409" t="n"/>
-      <c r="W10" s="409" t="n"/>
-      <c r="X10" s="409" t="n"/>
-      <c r="Y10" s="409" t="n"/>
-      <c r="Z10" s="409" t="n"/>
-      <c r="AA10" s="409" t="n"/>
-      <c r="AB10" s="555" t="n"/>
-      <c r="AC10" s="409" t="n"/>
-      <c r="AD10" s="409" t="n"/>
-      <c r="AE10" s="409" t="n"/>
-      <c r="AF10" s="409" t="n"/>
-      <c r="AG10" s="409" t="n"/>
-      <c r="AH10" s="409" t="n"/>
-      <c r="AI10" s="409" t="n"/>
-      <c r="AJ10" s="409" t="n"/>
-      <c r="AK10" s="409" t="n"/>
-      <c r="AL10" s="409" t="n"/>
-      <c r="AM10" s="409" t="n"/>
-      <c r="AN10" s="556" t="n"/>
+      <c r="V10" s="738" t="n"/>
+      <c r="W10" s="738" t="n"/>
+      <c r="X10" s="738" t="n"/>
+      <c r="Y10" s="738" t="n"/>
+      <c r="Z10" s="738" t="n"/>
+      <c r="AA10" s="738" t="n"/>
+      <c r="AB10" s="674" t="n"/>
+      <c r="AC10" s="738" t="n"/>
+      <c r="AD10" s="738" t="n"/>
+      <c r="AE10" s="738" t="n"/>
+      <c r="AF10" s="738" t="n"/>
+      <c r="AG10" s="738" t="n"/>
+      <c r="AH10" s="738" t="n"/>
+      <c r="AI10" s="738" t="n"/>
+      <c r="AJ10" s="738" t="n"/>
+      <c r="AK10" s="738" t="n"/>
+      <c r="AL10" s="738" t="n"/>
+      <c r="AM10" s="738" t="n"/>
+      <c r="AN10" s="739" t="n"/>
     </row>
     <row r="11" ht="26" customHeight="1" s="329">
-      <c r="A11" s="461" t="inlineStr">
+      <c r="A11" s="671" t="inlineStr">
         <is>
           <t>Prepared by / Date-Time</t>
         </is>
       </c>
-      <c r="B11" s="409" t="n"/>
-      <c r="C11" s="409" t="n"/>
-      <c r="D11" s="409" t="n"/>
-      <c r="E11" s="409" t="n"/>
-      <c r="F11" s="409" t="n"/>
-      <c r="G11" s="409" t="n"/>
-      <c r="H11" s="462" t="n"/>
-      <c r="I11" s="409" t="n"/>
-      <c r="J11" s="409" t="n"/>
-      <c r="K11" s="409" t="n"/>
-      <c r="L11" s="409" t="n"/>
-      <c r="M11" s="409" t="n"/>
-      <c r="N11" s="409" t="n"/>
-      <c r="O11" s="409" t="n"/>
-      <c r="P11" s="409" t="n"/>
-      <c r="Q11" s="409" t="n"/>
-      <c r="R11" s="409" t="n"/>
-      <c r="S11" s="409" t="n"/>
-      <c r="T11" s="409" t="n"/>
-      <c r="U11" s="463" t="inlineStr">
+      <c r="B11" s="738" t="n"/>
+      <c r="C11" s="738" t="n"/>
+      <c r="D11" s="738" t="n"/>
+      <c r="E11" s="738" t="n"/>
+      <c r="F11" s="738" t="n"/>
+      <c r="G11" s="738" t="n"/>
+      <c r="H11" s="672" t="n"/>
+      <c r="I11" s="738" t="n"/>
+      <c r="J11" s="738" t="n"/>
+      <c r="K11" s="738" t="n"/>
+      <c r="L11" s="738" t="n"/>
+      <c r="M11" s="738" t="n"/>
+      <c r="N11" s="738" t="n"/>
+      <c r="O11" s="738" t="n"/>
+      <c r="P11" s="738" t="n"/>
+      <c r="Q11" s="738" t="n"/>
+      <c r="R11" s="738" t="n"/>
+      <c r="S11" s="738" t="n"/>
+      <c r="T11" s="738" t="n"/>
+      <c r="U11" s="673" t="inlineStr">
         <is>
           <t>Record Status</t>
         </is>
       </c>
-      <c r="V11" s="409" t="n"/>
-      <c r="W11" s="409" t="n"/>
-      <c r="X11" s="409" t="n"/>
-      <c r="Y11" s="409" t="n"/>
-      <c r="Z11" s="409" t="n"/>
-      <c r="AA11" s="409" t="n"/>
-      <c r="AB11" s="555" t="n"/>
-      <c r="AC11" s="409" t="n"/>
-      <c r="AD11" s="409" t="n"/>
-      <c r="AE11" s="409" t="n"/>
-      <c r="AF11" s="409" t="n"/>
-      <c r="AG11" s="409" t="n"/>
-      <c r="AH11" s="409" t="n"/>
-      <c r="AI11" s="409" t="n"/>
-      <c r="AJ11" s="409" t="n"/>
-      <c r="AK11" s="409" t="n"/>
-      <c r="AL11" s="409" t="n"/>
-      <c r="AM11" s="409" t="n"/>
-      <c r="AN11" s="556" t="n"/>
+      <c r="V11" s="738" t="n"/>
+      <c r="W11" s="738" t="n"/>
+      <c r="X11" s="738" t="n"/>
+      <c r="Y11" s="738" t="n"/>
+      <c r="Z11" s="738" t="n"/>
+      <c r="AA11" s="738" t="n"/>
+      <c r="AB11" s="674" t="n"/>
+      <c r="AC11" s="738" t="n"/>
+      <c r="AD11" s="738" t="n"/>
+      <c r="AE11" s="738" t="n"/>
+      <c r="AF11" s="738" t="n"/>
+      <c r="AG11" s="738" t="n"/>
+      <c r="AH11" s="738" t="n"/>
+      <c r="AI11" s="738" t="n"/>
+      <c r="AJ11" s="738" t="n"/>
+      <c r="AK11" s="738" t="n"/>
+      <c r="AL11" s="738" t="n"/>
+      <c r="AM11" s="738" t="n"/>
+      <c r="AN11" s="739" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1" s="329">
-      <c r="A12" s="461" t="inlineStr">
+      <c r="A12" s="671" t="inlineStr">
         <is>
           <t>Process Cert Matches Spec?</t>
         </is>
       </c>
-      <c r="B12" s="409" t="n"/>
-      <c r="C12" s="409" t="n"/>
-      <c r="D12" s="409" t="n"/>
-      <c r="E12" s="409" t="n"/>
-      <c r="F12" s="409" t="n"/>
-      <c r="G12" s="409" t="n"/>
-      <c r="H12" s="462" t="n"/>
-      <c r="I12" s="409" t="n"/>
-      <c r="J12" s="409" t="n"/>
-      <c r="K12" s="409" t="n"/>
-      <c r="L12" s="409" t="n"/>
-      <c r="M12" s="409" t="n"/>
-      <c r="N12" s="409" t="n"/>
-      <c r="O12" s="409" t="n"/>
-      <c r="P12" s="409" t="n"/>
-      <c r="Q12" s="409" t="n"/>
-      <c r="R12" s="409" t="n"/>
-      <c r="S12" s="409" t="n"/>
-      <c r="T12" s="409" t="n"/>
-      <c r="U12" s="463" t="inlineStr">
+      <c r="B12" s="738" t="n"/>
+      <c r="C12" s="738" t="n"/>
+      <c r="D12" s="738" t="n"/>
+      <c r="E12" s="738" t="n"/>
+      <c r="F12" s="738" t="n"/>
+      <c r="G12" s="738" t="n"/>
+      <c r="H12" s="672" t="n"/>
+      <c r="I12" s="738" t="n"/>
+      <c r="J12" s="738" t="n"/>
+      <c r="K12" s="738" t="n"/>
+      <c r="L12" s="738" t="n"/>
+      <c r="M12" s="738" t="n"/>
+      <c r="N12" s="738" t="n"/>
+      <c r="O12" s="738" t="n"/>
+      <c r="P12" s="738" t="n"/>
+      <c r="Q12" s="738" t="n"/>
+      <c r="R12" s="738" t="n"/>
+      <c r="S12" s="738" t="n"/>
+      <c r="T12" s="738" t="n"/>
+      <c r="U12" s="673" t="inlineStr">
         <is>
           <t>Visual Inspection Result</t>
         </is>
       </c>
-      <c r="V12" s="409" t="n"/>
-      <c r="W12" s="409" t="n"/>
-      <c r="X12" s="409" t="n"/>
-      <c r="Y12" s="409" t="n"/>
-      <c r="Z12" s="409" t="n"/>
-      <c r="AA12" s="409" t="n"/>
-      <c r="AB12" s="555" t="n"/>
-      <c r="AC12" s="409" t="n"/>
-      <c r="AD12" s="409" t="n"/>
-      <c r="AE12" s="409" t="n"/>
-      <c r="AF12" s="409" t="n"/>
-      <c r="AG12" s="409" t="n"/>
-      <c r="AH12" s="409" t="n"/>
-      <c r="AI12" s="409" t="n"/>
-      <c r="AJ12" s="409" t="n"/>
-      <c r="AK12" s="409" t="n"/>
-      <c r="AL12" s="409" t="n"/>
-      <c r="AM12" s="409" t="n"/>
-      <c r="AN12" s="556" t="n"/>
+      <c r="V12" s="738" t="n"/>
+      <c r="W12" s="738" t="n"/>
+      <c r="X12" s="738" t="n"/>
+      <c r="Y12" s="738" t="n"/>
+      <c r="Z12" s="738" t="n"/>
+      <c r="AA12" s="738" t="n"/>
+      <c r="AB12" s="674" t="n"/>
+      <c r="AC12" s="738" t="n"/>
+      <c r="AD12" s="738" t="n"/>
+      <c r="AE12" s="738" t="n"/>
+      <c r="AF12" s="738" t="n"/>
+      <c r="AG12" s="738" t="n"/>
+      <c r="AH12" s="738" t="n"/>
+      <c r="AI12" s="738" t="n"/>
+      <c r="AJ12" s="738" t="n"/>
+      <c r="AK12" s="738" t="n"/>
+      <c r="AL12" s="738" t="n"/>
+      <c r="AM12" s="738" t="n"/>
+      <c r="AN12" s="739" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1" s="329">
-      <c r="A13" s="465" t="inlineStr">
+      <c r="A13" s="675" t="inlineStr">
         <is>
           <t>Method / Acceptance Ref</t>
         </is>
       </c>
-      <c r="B13" s="545" t="n"/>
-      <c r="C13" s="545" t="n"/>
-      <c r="D13" s="545" t="n"/>
-      <c r="E13" s="545" t="n"/>
-      <c r="F13" s="545" t="n"/>
-      <c r="G13" s="545" t="n"/>
-      <c r="H13" s="467" t="n"/>
-      <c r="I13" s="545" t="n"/>
-      <c r="J13" s="545" t="n"/>
-      <c r="K13" s="545" t="n"/>
-      <c r="L13" s="545" t="n"/>
-      <c r="M13" s="545" t="n"/>
-      <c r="N13" s="545" t="n"/>
-      <c r="O13" s="545" t="n"/>
-      <c r="P13" s="545" t="n"/>
-      <c r="Q13" s="545" t="n"/>
-      <c r="R13" s="545" t="n"/>
-      <c r="S13" s="545" t="n"/>
-      <c r="T13" s="545" t="n"/>
-      <c r="U13" s="468" t="inlineStr">
+      <c r="B13" s="740" t="n"/>
+      <c r="C13" s="740" t="n"/>
+      <c r="D13" s="740" t="n"/>
+      <c r="E13" s="740" t="n"/>
+      <c r="F13" s="740" t="n"/>
+      <c r="G13" s="740" t="n"/>
+      <c r="H13" s="676" t="n"/>
+      <c r="I13" s="740" t="n"/>
+      <c r="J13" s="740" t="n"/>
+      <c r="K13" s="740" t="n"/>
+      <c r="L13" s="740" t="n"/>
+      <c r="M13" s="740" t="n"/>
+      <c r="N13" s="740" t="n"/>
+      <c r="O13" s="740" t="n"/>
+      <c r="P13" s="740" t="n"/>
+      <c r="Q13" s="740" t="n"/>
+      <c r="R13" s="740" t="n"/>
+      <c r="S13" s="740" t="n"/>
+      <c r="T13" s="740" t="n"/>
+      <c r="U13" s="677" t="inlineStr">
         <is>
           <t>Affected Job Ref</t>
         </is>
       </c>
-      <c r="V13" s="545" t="n"/>
-      <c r="W13" s="545" t="n"/>
-      <c r="X13" s="545" t="n"/>
-      <c r="Y13" s="545" t="n"/>
-      <c r="Z13" s="545" t="n"/>
-      <c r="AA13" s="545" t="n"/>
-      <c r="AB13" s="557" t="n"/>
-      <c r="AC13" s="545" t="n"/>
-      <c r="AD13" s="545" t="n"/>
-      <c r="AE13" s="545" t="n"/>
-      <c r="AF13" s="545" t="n"/>
-      <c r="AG13" s="545" t="n"/>
-      <c r="AH13" s="545" t="n"/>
-      <c r="AI13" s="545" t="n"/>
-      <c r="AJ13" s="545" t="n"/>
-      <c r="AK13" s="545" t="n"/>
-      <c r="AL13" s="545" t="n"/>
-      <c r="AM13" s="545" t="n"/>
-      <c r="AN13" s="548" t="n"/>
+      <c r="V13" s="740" t="n"/>
+      <c r="W13" s="740" t="n"/>
+      <c r="X13" s="740" t="n"/>
+      <c r="Y13" s="740" t="n"/>
+      <c r="Z13" s="740" t="n"/>
+      <c r="AA13" s="740" t="n"/>
+      <c r="AB13" s="678" t="n"/>
+      <c r="AC13" s="740" t="n"/>
+      <c r="AD13" s="740" t="n"/>
+      <c r="AE13" s="740" t="n"/>
+      <c r="AF13" s="740" t="n"/>
+      <c r="AG13" s="740" t="n"/>
+      <c r="AH13" s="740" t="n"/>
+      <c r="AI13" s="740" t="n"/>
+      <c r="AJ13" s="740" t="n"/>
+      <c r="AK13" s="740" t="n"/>
+      <c r="AL13" s="740" t="n"/>
+      <c r="AM13" s="740" t="n"/>
+      <c r="AN13" s="741" t="n"/>
     </row>
     <row r="14" ht="3" customHeight="1" s="329">
       <c r="A14" s="357" t="n"/>
@@ -7258,410 +7932,410 @@
       <c r="AN14" s="350" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1" s="329">
-      <c r="A15" s="549" t="inlineStr">
+      <c r="A15" s="679" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. INCOMING VERIFICATION / FINDING DETAIL</t>
         </is>
       </c>
-      <c r="B15" s="550" t="n"/>
-      <c r="C15" s="550" t="n"/>
-      <c r="D15" s="550" t="n"/>
-      <c r="E15" s="550" t="n"/>
-      <c r="F15" s="550" t="n"/>
-      <c r="G15" s="550" t="n"/>
-      <c r="H15" s="550" t="n"/>
-      <c r="I15" s="550" t="n"/>
-      <c r="J15" s="550" t="n"/>
-      <c r="K15" s="550" t="n"/>
-      <c r="L15" s="550" t="n"/>
-      <c r="M15" s="550" t="n"/>
-      <c r="N15" s="550" t="n"/>
-      <c r="O15" s="550" t="n"/>
-      <c r="P15" s="550" t="n"/>
-      <c r="Q15" s="550" t="n"/>
-      <c r="R15" s="550" t="n"/>
-      <c r="S15" s="550" t="n"/>
-      <c r="T15" s="550" t="n"/>
-      <c r="U15" s="550" t="n"/>
-      <c r="V15" s="550" t="n"/>
-      <c r="W15" s="550" t="n"/>
-      <c r="X15" s="550" t="n"/>
-      <c r="Y15" s="550" t="n"/>
-      <c r="Z15" s="550" t="n"/>
-      <c r="AA15" s="550" t="n"/>
-      <c r="AB15" s="550" t="n"/>
-      <c r="AC15" s="550" t="n"/>
-      <c r="AD15" s="550" t="n"/>
-      <c r="AE15" s="550" t="n"/>
-      <c r="AF15" s="550" t="n"/>
-      <c r="AG15" s="550" t="n"/>
-      <c r="AH15" s="550" t="n"/>
-      <c r="AI15" s="550" t="n"/>
-      <c r="AJ15" s="550" t="n"/>
-      <c r="AK15" s="550" t="n"/>
-      <c r="AL15" s="550" t="n"/>
-      <c r="AM15" s="550" t="n"/>
-      <c r="AN15" s="551" t="n"/>
+      <c r="B15" s="285" t="n"/>
+      <c r="C15" s="285" t="n"/>
+      <c r="D15" s="285" t="n"/>
+      <c r="E15" s="285" t="n"/>
+      <c r="F15" s="285" t="n"/>
+      <c r="G15" s="285" t="n"/>
+      <c r="H15" s="285" t="n"/>
+      <c r="I15" s="285" t="n"/>
+      <c r="J15" s="285" t="n"/>
+      <c r="K15" s="285" t="n"/>
+      <c r="L15" s="285" t="n"/>
+      <c r="M15" s="285" t="n"/>
+      <c r="N15" s="285" t="n"/>
+      <c r="O15" s="285" t="n"/>
+      <c r="P15" s="285" t="n"/>
+      <c r="Q15" s="285" t="n"/>
+      <c r="R15" s="285" t="n"/>
+      <c r="S15" s="285" t="n"/>
+      <c r="T15" s="285" t="n"/>
+      <c r="U15" s="285" t="n"/>
+      <c r="V15" s="285" t="n"/>
+      <c r="W15" s="285" t="n"/>
+      <c r="X15" s="285" t="n"/>
+      <c r="Y15" s="285" t="n"/>
+      <c r="Z15" s="285" t="n"/>
+      <c r="AA15" s="285" t="n"/>
+      <c r="AB15" s="285" t="n"/>
+      <c r="AC15" s="285" t="n"/>
+      <c r="AD15" s="285" t="n"/>
+      <c r="AE15" s="285" t="n"/>
+      <c r="AF15" s="285" t="n"/>
+      <c r="AG15" s="285" t="n"/>
+      <c r="AH15" s="285" t="n"/>
+      <c r="AI15" s="285" t="n"/>
+      <c r="AJ15" s="285" t="n"/>
+      <c r="AK15" s="285" t="n"/>
+      <c r="AL15" s="285" t="n"/>
+      <c r="AM15" s="285" t="n"/>
+      <c r="AN15" s="286" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1" s="329">
-      <c r="A16" s="456" t="inlineStr">
+      <c r="A16" s="667" t="inlineStr">
         <is>
           <t>Risk Level</t>
         </is>
       </c>
-      <c r="B16" s="552" t="n"/>
-      <c r="C16" s="552" t="n"/>
-      <c r="D16" s="552" t="n"/>
-      <c r="E16" s="552" t="n"/>
-      <c r="F16" s="552" t="n"/>
-      <c r="G16" s="552" t="n"/>
-      <c r="H16" s="458" t="n"/>
-      <c r="I16" s="552" t="n"/>
-      <c r="J16" s="552" t="n"/>
-      <c r="K16" s="552" t="n"/>
-      <c r="L16" s="552" t="n"/>
-      <c r="M16" s="552" t="n"/>
-      <c r="N16" s="552" t="n"/>
-      <c r="O16" s="552" t="n"/>
-      <c r="P16" s="552" t="n"/>
-      <c r="Q16" s="552" t="n"/>
-      <c r="R16" s="552" t="n"/>
-      <c r="S16" s="552" t="n"/>
-      <c r="T16" s="552" t="n"/>
-      <c r="U16" s="459" t="inlineStr">
+      <c r="B16" s="317" t="n"/>
+      <c r="C16" s="317" t="n"/>
+      <c r="D16" s="317" t="n"/>
+      <c r="E16" s="317" t="n"/>
+      <c r="F16" s="317" t="n"/>
+      <c r="G16" s="317" t="n"/>
+      <c r="H16" s="668" t="n"/>
+      <c r="I16" s="317" t="n"/>
+      <c r="J16" s="317" t="n"/>
+      <c r="K16" s="317" t="n"/>
+      <c r="L16" s="317" t="n"/>
+      <c r="M16" s="317" t="n"/>
+      <c r="N16" s="317" t="n"/>
+      <c r="O16" s="317" t="n"/>
+      <c r="P16" s="317" t="n"/>
+      <c r="Q16" s="317" t="n"/>
+      <c r="R16" s="317" t="n"/>
+      <c r="S16" s="317" t="n"/>
+      <c r="T16" s="317" t="n"/>
+      <c r="U16" s="669" t="inlineStr">
         <is>
           <t>Countermeasure / Trigger</t>
         </is>
       </c>
-      <c r="V16" s="552" t="n"/>
-      <c r="W16" s="552" t="n"/>
-      <c r="X16" s="552" t="n"/>
-      <c r="Y16" s="552" t="n"/>
-      <c r="Z16" s="552" t="n"/>
-      <c r="AA16" s="552" t="n"/>
-      <c r="AB16" s="553" t="n"/>
-      <c r="AC16" s="552" t="n"/>
-      <c r="AD16" s="552" t="n"/>
-      <c r="AE16" s="552" t="n"/>
-      <c r="AF16" s="552" t="n"/>
-      <c r="AG16" s="552" t="n"/>
-      <c r="AH16" s="552" t="n"/>
-      <c r="AI16" s="552" t="n"/>
-      <c r="AJ16" s="552" t="n"/>
-      <c r="AK16" s="552" t="n"/>
-      <c r="AL16" s="552" t="n"/>
-      <c r="AM16" s="552" t="n"/>
-      <c r="AN16" s="554" t="n"/>
+      <c r="V16" s="317" t="n"/>
+      <c r="W16" s="317" t="n"/>
+      <c r="X16" s="317" t="n"/>
+      <c r="Y16" s="317" t="n"/>
+      <c r="Z16" s="317" t="n"/>
+      <c r="AA16" s="317" t="n"/>
+      <c r="AB16" s="670" t="n"/>
+      <c r="AC16" s="317" t="n"/>
+      <c r="AD16" s="317" t="n"/>
+      <c r="AE16" s="317" t="n"/>
+      <c r="AF16" s="317" t="n"/>
+      <c r="AG16" s="317" t="n"/>
+      <c r="AH16" s="317" t="n"/>
+      <c r="AI16" s="317" t="n"/>
+      <c r="AJ16" s="317" t="n"/>
+      <c r="AK16" s="317" t="n"/>
+      <c r="AL16" s="317" t="n"/>
+      <c r="AM16" s="317" t="n"/>
+      <c r="AN16" s="319" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1" s="329">
-      <c r="A17" s="461" t="inlineStr">
+      <c r="A17" s="671" t="inlineStr">
         <is>
           <t>Related Requirement / Package</t>
         </is>
       </c>
-      <c r="B17" s="409" t="n"/>
-      <c r="C17" s="409" t="n"/>
-      <c r="D17" s="409" t="n"/>
-      <c r="E17" s="409" t="n"/>
-      <c r="F17" s="409" t="n"/>
-      <c r="G17" s="409" t="n"/>
-      <c r="H17" s="462" t="n"/>
-      <c r="I17" s="409" t="n"/>
-      <c r="J17" s="409" t="n"/>
-      <c r="K17" s="409" t="n"/>
-      <c r="L17" s="409" t="n"/>
-      <c r="M17" s="409" t="n"/>
-      <c r="N17" s="409" t="n"/>
-      <c r="O17" s="409" t="n"/>
-      <c r="P17" s="409" t="n"/>
-      <c r="Q17" s="409" t="n"/>
-      <c r="R17" s="409" t="n"/>
-      <c r="S17" s="409" t="n"/>
-      <c r="T17" s="409" t="n"/>
-      <c r="U17" s="463" t="inlineStr">
+      <c r="B17" s="738" t="n"/>
+      <c r="C17" s="738" t="n"/>
+      <c r="D17" s="738" t="n"/>
+      <c r="E17" s="738" t="n"/>
+      <c r="F17" s="738" t="n"/>
+      <c r="G17" s="738" t="n"/>
+      <c r="H17" s="672" t="n"/>
+      <c r="I17" s="738" t="n"/>
+      <c r="J17" s="738" t="n"/>
+      <c r="K17" s="738" t="n"/>
+      <c r="L17" s="738" t="n"/>
+      <c r="M17" s="738" t="n"/>
+      <c r="N17" s="738" t="n"/>
+      <c r="O17" s="738" t="n"/>
+      <c r="P17" s="738" t="n"/>
+      <c r="Q17" s="738" t="n"/>
+      <c r="R17" s="738" t="n"/>
+      <c r="S17" s="738" t="n"/>
+      <c r="T17" s="738" t="n"/>
+      <c r="U17" s="673" t="inlineStr">
         <is>
           <t>Customer Special Requirement (YES/NO)</t>
         </is>
       </c>
-      <c r="V17" s="409" t="n"/>
-      <c r="W17" s="409" t="n"/>
-      <c r="X17" s="409" t="n"/>
-      <c r="Y17" s="409" t="n"/>
-      <c r="Z17" s="409" t="n"/>
-      <c r="AA17" s="409" t="n"/>
-      <c r="AB17" s="555" t="n"/>
-      <c r="AC17" s="409" t="n"/>
-      <c r="AD17" s="409" t="n"/>
-      <c r="AE17" s="409" t="n"/>
-      <c r="AF17" s="409" t="n"/>
-      <c r="AG17" s="409" t="n"/>
-      <c r="AH17" s="409" t="n"/>
-      <c r="AI17" s="409" t="n"/>
-      <c r="AJ17" s="409" t="n"/>
-      <c r="AK17" s="409" t="n"/>
-      <c r="AL17" s="409" t="n"/>
-      <c r="AM17" s="409" t="n"/>
-      <c r="AN17" s="556" t="n"/>
+      <c r="V17" s="738" t="n"/>
+      <c r="W17" s="738" t="n"/>
+      <c r="X17" s="738" t="n"/>
+      <c r="Y17" s="738" t="n"/>
+      <c r="Z17" s="738" t="n"/>
+      <c r="AA17" s="738" t="n"/>
+      <c r="AB17" s="674" t="n"/>
+      <c r="AC17" s="738" t="n"/>
+      <c r="AD17" s="738" t="n"/>
+      <c r="AE17" s="738" t="n"/>
+      <c r="AF17" s="738" t="n"/>
+      <c r="AG17" s="738" t="n"/>
+      <c r="AH17" s="738" t="n"/>
+      <c r="AI17" s="738" t="n"/>
+      <c r="AJ17" s="738" t="n"/>
+      <c r="AK17" s="738" t="n"/>
+      <c r="AL17" s="738" t="n"/>
+      <c r="AM17" s="738" t="n"/>
+      <c r="AN17" s="739" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1" s="329">
-      <c r="A18" s="558" t="inlineStr">
+      <c r="A18" s="680" t="inlineStr">
         <is>
           <t>VERIFICATION / SCOPE DESCRIPTION</t>
         </is>
       </c>
-      <c r="B18" s="409" t="n"/>
-      <c r="C18" s="409" t="n"/>
-      <c r="D18" s="409" t="n"/>
-      <c r="E18" s="409" t="n"/>
-      <c r="F18" s="409" t="n"/>
-      <c r="G18" s="409" t="n"/>
-      <c r="H18" s="409" t="n"/>
-      <c r="I18" s="409" t="n"/>
-      <c r="J18" s="409" t="n"/>
-      <c r="K18" s="409" t="n"/>
-      <c r="L18" s="409" t="n"/>
-      <c r="M18" s="409" t="n"/>
-      <c r="N18" s="409" t="n"/>
-      <c r="O18" s="409" t="n"/>
-      <c r="P18" s="409" t="n"/>
-      <c r="Q18" s="409" t="n"/>
-      <c r="R18" s="409" t="n"/>
-      <c r="S18" s="409" t="n"/>
-      <c r="T18" s="409" t="n"/>
-      <c r="U18" s="409" t="n"/>
-      <c r="V18" s="409" t="n"/>
-      <c r="W18" s="409" t="n"/>
-      <c r="X18" s="409" t="n"/>
-      <c r="Y18" s="409" t="n"/>
-      <c r="Z18" s="409" t="n"/>
-      <c r="AA18" s="409" t="n"/>
-      <c r="AB18" s="409" t="n"/>
-      <c r="AC18" s="409" t="n"/>
-      <c r="AD18" s="409" t="n"/>
-      <c r="AE18" s="409" t="n"/>
-      <c r="AF18" s="409" t="n"/>
-      <c r="AG18" s="409" t="n"/>
-      <c r="AH18" s="409" t="n"/>
-      <c r="AI18" s="409" t="n"/>
-      <c r="AJ18" s="409" t="n"/>
-      <c r="AK18" s="409" t="n"/>
-      <c r="AL18" s="409" t="n"/>
-      <c r="AM18" s="409" t="n"/>
-      <c r="AN18" s="556" t="n"/>
+      <c r="B18" s="738" t="n"/>
+      <c r="C18" s="738" t="n"/>
+      <c r="D18" s="738" t="n"/>
+      <c r="E18" s="738" t="n"/>
+      <c r="F18" s="738" t="n"/>
+      <c r="G18" s="738" t="n"/>
+      <c r="H18" s="738" t="n"/>
+      <c r="I18" s="738" t="n"/>
+      <c r="J18" s="738" t="n"/>
+      <c r="K18" s="738" t="n"/>
+      <c r="L18" s="738" t="n"/>
+      <c r="M18" s="738" t="n"/>
+      <c r="N18" s="738" t="n"/>
+      <c r="O18" s="738" t="n"/>
+      <c r="P18" s="738" t="n"/>
+      <c r="Q18" s="738" t="n"/>
+      <c r="R18" s="738" t="n"/>
+      <c r="S18" s="738" t="n"/>
+      <c r="T18" s="738" t="n"/>
+      <c r="U18" s="738" t="n"/>
+      <c r="V18" s="738" t="n"/>
+      <c r="W18" s="738" t="n"/>
+      <c r="X18" s="738" t="n"/>
+      <c r="Y18" s="738" t="n"/>
+      <c r="Z18" s="738" t="n"/>
+      <c r="AA18" s="738" t="n"/>
+      <c r="AB18" s="738" t="n"/>
+      <c r="AC18" s="738" t="n"/>
+      <c r="AD18" s="738" t="n"/>
+      <c r="AE18" s="738" t="n"/>
+      <c r="AF18" s="738" t="n"/>
+      <c r="AG18" s="738" t="n"/>
+      <c r="AH18" s="738" t="n"/>
+      <c r="AI18" s="738" t="n"/>
+      <c r="AJ18" s="738" t="n"/>
+      <c r="AK18" s="738" t="n"/>
+      <c r="AL18" s="738" t="n"/>
+      <c r="AM18" s="738" t="n"/>
+      <c r="AN18" s="739" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1" s="329">
-      <c r="A19" s="559" t="n"/>
-      <c r="B19" s="408" t="n"/>
-      <c r="C19" s="408" t="n"/>
-      <c r="D19" s="408" t="n"/>
-      <c r="E19" s="408" t="n"/>
-      <c r="F19" s="408" t="n"/>
-      <c r="G19" s="408" t="n"/>
-      <c r="H19" s="408" t="n"/>
-      <c r="I19" s="408" t="n"/>
-      <c r="J19" s="408" t="n"/>
-      <c r="K19" s="408" t="n"/>
-      <c r="L19" s="408" t="n"/>
-      <c r="M19" s="408" t="n"/>
-      <c r="N19" s="408" t="n"/>
-      <c r="O19" s="408" t="n"/>
-      <c r="P19" s="408" t="n"/>
-      <c r="Q19" s="408" t="n"/>
-      <c r="R19" s="408" t="n"/>
-      <c r="S19" s="408" t="n"/>
-      <c r="T19" s="408" t="n"/>
-      <c r="U19" s="408" t="n"/>
-      <c r="V19" s="408" t="n"/>
-      <c r="W19" s="408" t="n"/>
-      <c r="X19" s="408" t="n"/>
-      <c r="Y19" s="408" t="n"/>
-      <c r="Z19" s="408" t="n"/>
-      <c r="AA19" s="408" t="n"/>
-      <c r="AB19" s="408" t="n"/>
-      <c r="AC19" s="408" t="n"/>
-      <c r="AD19" s="408" t="n"/>
-      <c r="AE19" s="408" t="n"/>
-      <c r="AF19" s="408" t="n"/>
-      <c r="AG19" s="408" t="n"/>
-      <c r="AH19" s="408" t="n"/>
-      <c r="AI19" s="408" t="n"/>
-      <c r="AJ19" s="408" t="n"/>
-      <c r="AK19" s="408" t="n"/>
-      <c r="AL19" s="408" t="n"/>
-      <c r="AM19" s="408" t="n"/>
-      <c r="AN19" s="538" t="n"/>
+      <c r="A19" s="681" t="n"/>
+      <c r="B19" s="742" t="n"/>
+      <c r="C19" s="742" t="n"/>
+      <c r="D19" s="742" t="n"/>
+      <c r="E19" s="742" t="n"/>
+      <c r="F19" s="742" t="n"/>
+      <c r="G19" s="742" t="n"/>
+      <c r="H19" s="742" t="n"/>
+      <c r="I19" s="742" t="n"/>
+      <c r="J19" s="742" t="n"/>
+      <c r="K19" s="742" t="n"/>
+      <c r="L19" s="742" t="n"/>
+      <c r="M19" s="742" t="n"/>
+      <c r="N19" s="742" t="n"/>
+      <c r="O19" s="742" t="n"/>
+      <c r="P19" s="742" t="n"/>
+      <c r="Q19" s="742" t="n"/>
+      <c r="R19" s="742" t="n"/>
+      <c r="S19" s="742" t="n"/>
+      <c r="T19" s="742" t="n"/>
+      <c r="U19" s="742" t="n"/>
+      <c r="V19" s="742" t="n"/>
+      <c r="W19" s="742" t="n"/>
+      <c r="X19" s="742" t="n"/>
+      <c r="Y19" s="742" t="n"/>
+      <c r="Z19" s="742" t="n"/>
+      <c r="AA19" s="742" t="n"/>
+      <c r="AB19" s="742" t="n"/>
+      <c r="AC19" s="742" t="n"/>
+      <c r="AD19" s="742" t="n"/>
+      <c r="AE19" s="742" t="n"/>
+      <c r="AF19" s="742" t="n"/>
+      <c r="AG19" s="742" t="n"/>
+      <c r="AH19" s="742" t="n"/>
+      <c r="AI19" s="742" t="n"/>
+      <c r="AJ19" s="742" t="n"/>
+      <c r="AK19" s="742" t="n"/>
+      <c r="AL19" s="742" t="n"/>
+      <c r="AM19" s="742" t="n"/>
+      <c r="AN19" s="743" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1" s="329">
-      <c r="A20" s="560" t="n"/>
-      <c r="B20" s="413" t="n"/>
-      <c r="C20" s="413" t="n"/>
-      <c r="D20" s="413" t="n"/>
-      <c r="E20" s="413" t="n"/>
-      <c r="F20" s="413" t="n"/>
-      <c r="G20" s="413" t="n"/>
-      <c r="H20" s="413" t="n"/>
-      <c r="I20" s="413" t="n"/>
-      <c r="J20" s="413" t="n"/>
-      <c r="K20" s="413" t="n"/>
-      <c r="L20" s="413" t="n"/>
-      <c r="M20" s="413" t="n"/>
-      <c r="N20" s="413" t="n"/>
-      <c r="O20" s="413" t="n"/>
-      <c r="P20" s="413" t="n"/>
-      <c r="Q20" s="413" t="n"/>
-      <c r="R20" s="413" t="n"/>
-      <c r="S20" s="413" t="n"/>
-      <c r="T20" s="413" t="n"/>
-      <c r="U20" s="413" t="n"/>
-      <c r="V20" s="413" t="n"/>
-      <c r="W20" s="413" t="n"/>
-      <c r="X20" s="413" t="n"/>
-      <c r="Y20" s="413" t="n"/>
-      <c r="Z20" s="413" t="n"/>
-      <c r="AA20" s="413" t="n"/>
-      <c r="AB20" s="413" t="n"/>
-      <c r="AC20" s="413" t="n"/>
-      <c r="AD20" s="413" t="n"/>
-      <c r="AE20" s="413" t="n"/>
-      <c r="AF20" s="413" t="n"/>
-      <c r="AG20" s="413" t="n"/>
-      <c r="AH20" s="413" t="n"/>
-      <c r="AI20" s="413" t="n"/>
-      <c r="AJ20" s="413" t="n"/>
-      <c r="AK20" s="413" t="n"/>
-      <c r="AL20" s="413" t="n"/>
-      <c r="AM20" s="413" t="n"/>
-      <c r="AN20" s="561" t="n"/>
+      <c r="A20" s="279" t="n"/>
+      <c r="B20" s="322" t="n"/>
+      <c r="C20" s="322" t="n"/>
+      <c r="D20" s="322" t="n"/>
+      <c r="E20" s="322" t="n"/>
+      <c r="F20" s="322" t="n"/>
+      <c r="G20" s="322" t="n"/>
+      <c r="H20" s="322" t="n"/>
+      <c r="I20" s="322" t="n"/>
+      <c r="J20" s="322" t="n"/>
+      <c r="K20" s="322" t="n"/>
+      <c r="L20" s="322" t="n"/>
+      <c r="M20" s="322" t="n"/>
+      <c r="N20" s="322" t="n"/>
+      <c r="O20" s="322" t="n"/>
+      <c r="P20" s="322" t="n"/>
+      <c r="Q20" s="322" t="n"/>
+      <c r="R20" s="322" t="n"/>
+      <c r="S20" s="322" t="n"/>
+      <c r="T20" s="322" t="n"/>
+      <c r="U20" s="322" t="n"/>
+      <c r="V20" s="322" t="n"/>
+      <c r="W20" s="322" t="n"/>
+      <c r="X20" s="322" t="n"/>
+      <c r="Y20" s="322" t="n"/>
+      <c r="Z20" s="322" t="n"/>
+      <c r="AA20" s="322" t="n"/>
+      <c r="AB20" s="322" t="n"/>
+      <c r="AC20" s="322" t="n"/>
+      <c r="AD20" s="322" t="n"/>
+      <c r="AE20" s="322" t="n"/>
+      <c r="AF20" s="322" t="n"/>
+      <c r="AG20" s="322" t="n"/>
+      <c r="AH20" s="322" t="n"/>
+      <c r="AI20" s="322" t="n"/>
+      <c r="AJ20" s="322" t="n"/>
+      <c r="AK20" s="322" t="n"/>
+      <c r="AL20" s="322" t="n"/>
+      <c r="AM20" s="322" t="n"/>
+      <c r="AN20" s="324" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1" s="329">
-      <c r="A21" s="558" t="inlineStr">
+      <c r="A21" s="680" t="inlineStr">
         <is>
           <t>OBSERVATION / CONTAINMENT / CERT CHECK</t>
         </is>
       </c>
-      <c r="B21" s="409" t="n"/>
-      <c r="C21" s="409" t="n"/>
-      <c r="D21" s="409" t="n"/>
-      <c r="E21" s="409" t="n"/>
-      <c r="F21" s="409" t="n"/>
-      <c r="G21" s="409" t="n"/>
-      <c r="H21" s="409" t="n"/>
-      <c r="I21" s="409" t="n"/>
-      <c r="J21" s="409" t="n"/>
-      <c r="K21" s="409" t="n"/>
-      <c r="L21" s="409" t="n"/>
-      <c r="M21" s="409" t="n"/>
-      <c r="N21" s="409" t="n"/>
-      <c r="O21" s="409" t="n"/>
-      <c r="P21" s="409" t="n"/>
-      <c r="Q21" s="409" t="n"/>
-      <c r="R21" s="409" t="n"/>
-      <c r="S21" s="409" t="n"/>
-      <c r="T21" s="409" t="n"/>
-      <c r="U21" s="409" t="n"/>
-      <c r="V21" s="409" t="n"/>
-      <c r="W21" s="409" t="n"/>
-      <c r="X21" s="409" t="n"/>
-      <c r="Y21" s="409" t="n"/>
-      <c r="Z21" s="409" t="n"/>
-      <c r="AA21" s="409" t="n"/>
-      <c r="AB21" s="409" t="n"/>
-      <c r="AC21" s="409" t="n"/>
-      <c r="AD21" s="409" t="n"/>
-      <c r="AE21" s="409" t="n"/>
-      <c r="AF21" s="409" t="n"/>
-      <c r="AG21" s="409" t="n"/>
-      <c r="AH21" s="409" t="n"/>
-      <c r="AI21" s="409" t="n"/>
-      <c r="AJ21" s="409" t="n"/>
-      <c r="AK21" s="409" t="n"/>
-      <c r="AL21" s="409" t="n"/>
-      <c r="AM21" s="409" t="n"/>
-      <c r="AN21" s="556" t="n"/>
+      <c r="B21" s="738" t="n"/>
+      <c r="C21" s="738" t="n"/>
+      <c r="D21" s="738" t="n"/>
+      <c r="E21" s="738" t="n"/>
+      <c r="F21" s="738" t="n"/>
+      <c r="G21" s="738" t="n"/>
+      <c r="H21" s="738" t="n"/>
+      <c r="I21" s="738" t="n"/>
+      <c r="J21" s="738" t="n"/>
+      <c r="K21" s="738" t="n"/>
+      <c r="L21" s="738" t="n"/>
+      <c r="M21" s="738" t="n"/>
+      <c r="N21" s="738" t="n"/>
+      <c r="O21" s="738" t="n"/>
+      <c r="P21" s="738" t="n"/>
+      <c r="Q21" s="738" t="n"/>
+      <c r="R21" s="738" t="n"/>
+      <c r="S21" s="738" t="n"/>
+      <c r="T21" s="738" t="n"/>
+      <c r="U21" s="738" t="n"/>
+      <c r="V21" s="738" t="n"/>
+      <c r="W21" s="738" t="n"/>
+      <c r="X21" s="738" t="n"/>
+      <c r="Y21" s="738" t="n"/>
+      <c r="Z21" s="738" t="n"/>
+      <c r="AA21" s="738" t="n"/>
+      <c r="AB21" s="738" t="n"/>
+      <c r="AC21" s="738" t="n"/>
+      <c r="AD21" s="738" t="n"/>
+      <c r="AE21" s="738" t="n"/>
+      <c r="AF21" s="738" t="n"/>
+      <c r="AG21" s="738" t="n"/>
+      <c r="AH21" s="738" t="n"/>
+      <c r="AI21" s="738" t="n"/>
+      <c r="AJ21" s="738" t="n"/>
+      <c r="AK21" s="738" t="n"/>
+      <c r="AL21" s="738" t="n"/>
+      <c r="AM21" s="738" t="n"/>
+      <c r="AN21" s="739" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1" s="329">
-      <c r="A22" s="559" t="n"/>
-      <c r="B22" s="408" t="n"/>
-      <c r="C22" s="408" t="n"/>
-      <c r="D22" s="408" t="n"/>
-      <c r="E22" s="408" t="n"/>
-      <c r="F22" s="408" t="n"/>
-      <c r="G22" s="408" t="n"/>
-      <c r="H22" s="408" t="n"/>
-      <c r="I22" s="408" t="n"/>
-      <c r="J22" s="408" t="n"/>
-      <c r="K22" s="408" t="n"/>
-      <c r="L22" s="408" t="n"/>
-      <c r="M22" s="408" t="n"/>
-      <c r="N22" s="408" t="n"/>
-      <c r="O22" s="408" t="n"/>
-      <c r="P22" s="408" t="n"/>
-      <c r="Q22" s="408" t="n"/>
-      <c r="R22" s="408" t="n"/>
-      <c r="S22" s="408" t="n"/>
-      <c r="T22" s="408" t="n"/>
-      <c r="U22" s="408" t="n"/>
-      <c r="V22" s="408" t="n"/>
-      <c r="W22" s="408" t="n"/>
-      <c r="X22" s="408" t="n"/>
-      <c r="Y22" s="408" t="n"/>
-      <c r="Z22" s="408" t="n"/>
-      <c r="AA22" s="408" t="n"/>
-      <c r="AB22" s="408" t="n"/>
-      <c r="AC22" s="408" t="n"/>
-      <c r="AD22" s="408" t="n"/>
-      <c r="AE22" s="408" t="n"/>
-      <c r="AF22" s="408" t="n"/>
-      <c r="AG22" s="408" t="n"/>
-      <c r="AH22" s="408" t="n"/>
-      <c r="AI22" s="408" t="n"/>
-      <c r="AJ22" s="408" t="n"/>
-      <c r="AK22" s="408" t="n"/>
-      <c r="AL22" s="408" t="n"/>
-      <c r="AM22" s="408" t="n"/>
-      <c r="AN22" s="538" t="n"/>
+      <c r="A22" s="681" t="n"/>
+      <c r="B22" s="742" t="n"/>
+      <c r="C22" s="742" t="n"/>
+      <c r="D22" s="742" t="n"/>
+      <c r="E22" s="742" t="n"/>
+      <c r="F22" s="742" t="n"/>
+      <c r="G22" s="742" t="n"/>
+      <c r="H22" s="742" t="n"/>
+      <c r="I22" s="742" t="n"/>
+      <c r="J22" s="742" t="n"/>
+      <c r="K22" s="742" t="n"/>
+      <c r="L22" s="742" t="n"/>
+      <c r="M22" s="742" t="n"/>
+      <c r="N22" s="742" t="n"/>
+      <c r="O22" s="742" t="n"/>
+      <c r="P22" s="742" t="n"/>
+      <c r="Q22" s="742" t="n"/>
+      <c r="R22" s="742" t="n"/>
+      <c r="S22" s="742" t="n"/>
+      <c r="T22" s="742" t="n"/>
+      <c r="U22" s="742" t="n"/>
+      <c r="V22" s="742" t="n"/>
+      <c r="W22" s="742" t="n"/>
+      <c r="X22" s="742" t="n"/>
+      <c r="Y22" s="742" t="n"/>
+      <c r="Z22" s="742" t="n"/>
+      <c r="AA22" s="742" t="n"/>
+      <c r="AB22" s="742" t="n"/>
+      <c r="AC22" s="742" t="n"/>
+      <c r="AD22" s="742" t="n"/>
+      <c r="AE22" s="742" t="n"/>
+      <c r="AF22" s="742" t="n"/>
+      <c r="AG22" s="742" t="n"/>
+      <c r="AH22" s="742" t="n"/>
+      <c r="AI22" s="742" t="n"/>
+      <c r="AJ22" s="742" t="n"/>
+      <c r="AK22" s="742" t="n"/>
+      <c r="AL22" s="742" t="n"/>
+      <c r="AM22" s="742" t="n"/>
+      <c r="AN22" s="743" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1" s="329">
-      <c r="A23" s="560" t="n"/>
-      <c r="B23" s="413" t="n"/>
-      <c r="C23" s="413" t="n"/>
-      <c r="D23" s="413" t="n"/>
-      <c r="E23" s="413" t="n"/>
-      <c r="F23" s="413" t="n"/>
-      <c r="G23" s="413" t="n"/>
-      <c r="H23" s="413" t="n"/>
-      <c r="I23" s="413" t="n"/>
-      <c r="J23" s="413" t="n"/>
-      <c r="K23" s="413" t="n"/>
-      <c r="L23" s="413" t="n"/>
-      <c r="M23" s="413" t="n"/>
-      <c r="N23" s="413" t="n"/>
-      <c r="O23" s="413" t="n"/>
-      <c r="P23" s="413" t="n"/>
-      <c r="Q23" s="413" t="n"/>
-      <c r="R23" s="413" t="n"/>
-      <c r="S23" s="413" t="n"/>
-      <c r="T23" s="413" t="n"/>
-      <c r="U23" s="413" t="n"/>
-      <c r="V23" s="413" t="n"/>
-      <c r="W23" s="413" t="n"/>
-      <c r="X23" s="413" t="n"/>
-      <c r="Y23" s="413" t="n"/>
-      <c r="Z23" s="413" t="n"/>
-      <c r="AA23" s="413" t="n"/>
-      <c r="AB23" s="413" t="n"/>
-      <c r="AC23" s="413" t="n"/>
-      <c r="AD23" s="413" t="n"/>
-      <c r="AE23" s="413" t="n"/>
-      <c r="AF23" s="413" t="n"/>
-      <c r="AG23" s="413" t="n"/>
-      <c r="AH23" s="413" t="n"/>
-      <c r="AI23" s="413" t="n"/>
-      <c r="AJ23" s="413" t="n"/>
-      <c r="AK23" s="413" t="n"/>
-      <c r="AL23" s="413" t="n"/>
-      <c r="AM23" s="413" t="n"/>
-      <c r="AN23" s="561" t="n"/>
+      <c r="A23" s="279" t="n"/>
+      <c r="B23" s="322" t="n"/>
+      <c r="C23" s="322" t="n"/>
+      <c r="D23" s="322" t="n"/>
+      <c r="E23" s="322" t="n"/>
+      <c r="F23" s="322" t="n"/>
+      <c r="G23" s="322" t="n"/>
+      <c r="H23" s="322" t="n"/>
+      <c r="I23" s="322" t="n"/>
+      <c r="J23" s="322" t="n"/>
+      <c r="K23" s="322" t="n"/>
+      <c r="L23" s="322" t="n"/>
+      <c r="M23" s="322" t="n"/>
+      <c r="N23" s="322" t="n"/>
+      <c r="O23" s="322" t="n"/>
+      <c r="P23" s="322" t="n"/>
+      <c r="Q23" s="322" t="n"/>
+      <c r="R23" s="322" t="n"/>
+      <c r="S23" s="322" t="n"/>
+      <c r="T23" s="322" t="n"/>
+      <c r="U23" s="322" t="n"/>
+      <c r="V23" s="322" t="n"/>
+      <c r="W23" s="322" t="n"/>
+      <c r="X23" s="322" t="n"/>
+      <c r="Y23" s="322" t="n"/>
+      <c r="Z23" s="322" t="n"/>
+      <c r="AA23" s="322" t="n"/>
+      <c r="AB23" s="322" t="n"/>
+      <c r="AC23" s="322" t="n"/>
+      <c r="AD23" s="322" t="n"/>
+      <c r="AE23" s="322" t="n"/>
+      <c r="AF23" s="322" t="n"/>
+      <c r="AG23" s="322" t="n"/>
+      <c r="AH23" s="322" t="n"/>
+      <c r="AI23" s="322" t="n"/>
+      <c r="AJ23" s="322" t="n"/>
+      <c r="AK23" s="322" t="n"/>
+      <c r="AL23" s="322" t="n"/>
+      <c r="AM23" s="322" t="n"/>
+      <c r="AN23" s="324" t="n"/>
     </row>
     <row r="24" ht="3" customHeight="1" s="329">
       <c r="A24" s="362" t="n"/>
@@ -7706,414 +8380,414 @@
       <c r="AN24" s="350" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1" s="329">
-      <c r="A25" s="549" t="inlineStr">
+      <c r="A25" s="679" t="inlineStr">
         <is>
           <t xml:space="preserve">  3. IMPACT / CONTAINMENT / ACTIONS</t>
         </is>
       </c>
-      <c r="B25" s="550" t="n"/>
-      <c r="C25" s="550" t="n"/>
-      <c r="D25" s="550" t="n"/>
-      <c r="E25" s="550" t="n"/>
-      <c r="F25" s="550" t="n"/>
-      <c r="G25" s="550" t="n"/>
-      <c r="H25" s="550" t="n"/>
-      <c r="I25" s="550" t="n"/>
-      <c r="J25" s="550" t="n"/>
-      <c r="K25" s="550" t="n"/>
-      <c r="L25" s="550" t="n"/>
-      <c r="M25" s="550" t="n"/>
-      <c r="N25" s="550" t="n"/>
-      <c r="O25" s="550" t="n"/>
-      <c r="P25" s="550" t="n"/>
-      <c r="Q25" s="550" t="n"/>
-      <c r="R25" s="550" t="n"/>
-      <c r="S25" s="550" t="n"/>
-      <c r="T25" s="550" t="n"/>
-      <c r="U25" s="550" t="n"/>
-      <c r="V25" s="550" t="n"/>
-      <c r="W25" s="550" t="n"/>
-      <c r="X25" s="550" t="n"/>
-      <c r="Y25" s="550" t="n"/>
-      <c r="Z25" s="550" t="n"/>
-      <c r="AA25" s="550" t="n"/>
-      <c r="AB25" s="550" t="n"/>
-      <c r="AC25" s="550" t="n"/>
-      <c r="AD25" s="550" t="n"/>
-      <c r="AE25" s="550" t="n"/>
-      <c r="AF25" s="550" t="n"/>
-      <c r="AG25" s="550" t="n"/>
-      <c r="AH25" s="550" t="n"/>
-      <c r="AI25" s="550" t="n"/>
-      <c r="AJ25" s="550" t="n"/>
-      <c r="AK25" s="550" t="n"/>
-      <c r="AL25" s="550" t="n"/>
-      <c r="AM25" s="550" t="n"/>
-      <c r="AN25" s="551" t="n"/>
+      <c r="B25" s="285" t="n"/>
+      <c r="C25" s="285" t="n"/>
+      <c r="D25" s="285" t="n"/>
+      <c r="E25" s="285" t="n"/>
+      <c r="F25" s="285" t="n"/>
+      <c r="G25" s="285" t="n"/>
+      <c r="H25" s="285" t="n"/>
+      <c r="I25" s="285" t="n"/>
+      <c r="J25" s="285" t="n"/>
+      <c r="K25" s="285" t="n"/>
+      <c r="L25" s="285" t="n"/>
+      <c r="M25" s="285" t="n"/>
+      <c r="N25" s="285" t="n"/>
+      <c r="O25" s="285" t="n"/>
+      <c r="P25" s="285" t="n"/>
+      <c r="Q25" s="285" t="n"/>
+      <c r="R25" s="285" t="n"/>
+      <c r="S25" s="285" t="n"/>
+      <c r="T25" s="285" t="n"/>
+      <c r="U25" s="285" t="n"/>
+      <c r="V25" s="285" t="n"/>
+      <c r="W25" s="285" t="n"/>
+      <c r="X25" s="285" t="n"/>
+      <c r="Y25" s="285" t="n"/>
+      <c r="Z25" s="285" t="n"/>
+      <c r="AA25" s="285" t="n"/>
+      <c r="AB25" s="285" t="n"/>
+      <c r="AC25" s="285" t="n"/>
+      <c r="AD25" s="285" t="n"/>
+      <c r="AE25" s="285" t="n"/>
+      <c r="AF25" s="285" t="n"/>
+      <c r="AG25" s="285" t="n"/>
+      <c r="AH25" s="285" t="n"/>
+      <c r="AI25" s="285" t="n"/>
+      <c r="AJ25" s="285" t="n"/>
+      <c r="AK25" s="285" t="n"/>
+      <c r="AL25" s="285" t="n"/>
+      <c r="AM25" s="285" t="n"/>
+      <c r="AN25" s="286" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1" s="329">
-      <c r="A26" s="475" t="inlineStr">
+      <c r="A26" s="682" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B26" s="550" t="n"/>
-      <c r="C26" s="477" t="inlineStr">
+      <c r="B26" s="285" t="n"/>
+      <c r="C26" s="683" t="inlineStr">
         <is>
           <t>Cat.</t>
         </is>
       </c>
-      <c r="D26" s="550" t="n"/>
-      <c r="E26" s="550" t="n"/>
-      <c r="F26" s="477" t="inlineStr">
+      <c r="D26" s="285" t="n"/>
+      <c r="E26" s="285" t="n"/>
+      <c r="F26" s="683" t="inlineStr">
         <is>
           <t>Finding / Check</t>
         </is>
       </c>
-      <c r="G26" s="550" t="n"/>
-      <c r="H26" s="550" t="n"/>
-      <c r="I26" s="550" t="n"/>
-      <c r="J26" s="550" t="n"/>
-      <c r="K26" s="550" t="n"/>
-      <c r="L26" s="550" t="n"/>
-      <c r="M26" s="550" t="n"/>
-      <c r="N26" s="550" t="n"/>
-      <c r="O26" s="550" t="n"/>
-      <c r="P26" s="550" t="n"/>
-      <c r="Q26" s="550" t="n"/>
-      <c r="R26" s="550" t="n"/>
-      <c r="S26" s="550" t="n"/>
-      <c r="T26" s="477" t="inlineStr">
+      <c r="G26" s="285" t="n"/>
+      <c r="H26" s="285" t="n"/>
+      <c r="I26" s="285" t="n"/>
+      <c r="J26" s="285" t="n"/>
+      <c r="K26" s="285" t="n"/>
+      <c r="L26" s="285" t="n"/>
+      <c r="M26" s="285" t="n"/>
+      <c r="N26" s="285" t="n"/>
+      <c r="O26" s="285" t="n"/>
+      <c r="P26" s="285" t="n"/>
+      <c r="Q26" s="285" t="n"/>
+      <c r="R26" s="285" t="n"/>
+      <c r="S26" s="285" t="n"/>
+      <c r="T26" s="683" t="inlineStr">
         <is>
           <t>Evidence / Criteria</t>
         </is>
       </c>
-      <c r="U26" s="550" t="n"/>
-      <c r="V26" s="550" t="n"/>
-      <c r="W26" s="550" t="n"/>
-      <c r="X26" s="550" t="n"/>
-      <c r="Y26" s="550" t="n"/>
-      <c r="Z26" s="550" t="n"/>
-      <c r="AA26" s="550" t="n"/>
-      <c r="AB26" s="550" t="n"/>
-      <c r="AC26" s="550" t="n"/>
-      <c r="AD26" s="550" t="n"/>
-      <c r="AE26" s="550" t="n"/>
-      <c r="AF26" s="477" t="inlineStr">
+      <c r="U26" s="285" t="n"/>
+      <c r="V26" s="285" t="n"/>
+      <c r="W26" s="285" t="n"/>
+      <c r="X26" s="285" t="n"/>
+      <c r="Y26" s="285" t="n"/>
+      <c r="Z26" s="285" t="n"/>
+      <c r="AA26" s="285" t="n"/>
+      <c r="AB26" s="285" t="n"/>
+      <c r="AC26" s="285" t="n"/>
+      <c r="AD26" s="285" t="n"/>
+      <c r="AE26" s="285" t="n"/>
+      <c r="AF26" s="683" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="AG26" s="550" t="n"/>
-      <c r="AH26" s="550" t="n"/>
-      <c r="AI26" s="550" t="n"/>
-      <c r="AJ26" s="477" t="inlineStr">
+      <c r="AG26" s="285" t="n"/>
+      <c r="AH26" s="285" t="n"/>
+      <c r="AI26" s="285" t="n"/>
+      <c r="AJ26" s="683" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AK26" s="550" t="n"/>
-      <c r="AL26" s="550" t="n"/>
-      <c r="AM26" s="562" t="inlineStr">
+      <c r="AK26" s="285" t="n"/>
+      <c r="AL26" s="285" t="n"/>
+      <c r="AM26" s="684" t="inlineStr">
         <is>
           <t>Ref.</t>
         </is>
       </c>
-      <c r="AN26" s="551" t="n"/>
+      <c r="AN26" s="286" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1" s="329">
-      <c r="A27" s="479">
+      <c r="A27" s="685">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B27" s="552" t="n"/>
-      <c r="C27" s="480" t="inlineStr">
+      <c r="B27" s="317" t="n"/>
+      <c r="C27" s="686" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D27" s="552" t="n"/>
-      <c r="E27" s="552" t="n"/>
-      <c r="F27" s="458" t="n"/>
-      <c r="G27" s="552" t="n"/>
-      <c r="H27" s="552" t="n"/>
-      <c r="I27" s="552" t="n"/>
-      <c r="J27" s="552" t="n"/>
-      <c r="K27" s="552" t="n"/>
-      <c r="L27" s="552" t="n"/>
-      <c r="M27" s="552" t="n"/>
-      <c r="N27" s="552" t="n"/>
-      <c r="O27" s="552" t="n"/>
-      <c r="P27" s="552" t="n"/>
-      <c r="Q27" s="552" t="n"/>
-      <c r="R27" s="552" t="n"/>
-      <c r="S27" s="552" t="n"/>
-      <c r="T27" s="481" t="n"/>
-      <c r="U27" s="552" t="n"/>
-      <c r="V27" s="552" t="n"/>
-      <c r="W27" s="552" t="n"/>
-      <c r="X27" s="552" t="n"/>
-      <c r="Y27" s="552" t="n"/>
-      <c r="Z27" s="552" t="n"/>
-      <c r="AA27" s="552" t="n"/>
-      <c r="AB27" s="552" t="n"/>
-      <c r="AC27" s="552" t="n"/>
-      <c r="AD27" s="552" t="n"/>
-      <c r="AE27" s="552" t="n"/>
-      <c r="AF27" s="458" t="n"/>
-      <c r="AG27" s="552" t="n"/>
-      <c r="AH27" s="552" t="n"/>
-      <c r="AI27" s="552" t="n"/>
-      <c r="AJ27" s="458" t="n"/>
-      <c r="AK27" s="552" t="n"/>
-      <c r="AL27" s="552" t="n"/>
-      <c r="AM27" s="563" t="n"/>
-      <c r="AN27" s="554" t="n"/>
+      <c r="D27" s="317" t="n"/>
+      <c r="E27" s="317" t="n"/>
+      <c r="F27" s="668" t="n"/>
+      <c r="G27" s="317" t="n"/>
+      <c r="H27" s="317" t="n"/>
+      <c r="I27" s="317" t="n"/>
+      <c r="J27" s="317" t="n"/>
+      <c r="K27" s="317" t="n"/>
+      <c r="L27" s="317" t="n"/>
+      <c r="M27" s="317" t="n"/>
+      <c r="N27" s="317" t="n"/>
+      <c r="O27" s="317" t="n"/>
+      <c r="P27" s="317" t="n"/>
+      <c r="Q27" s="317" t="n"/>
+      <c r="R27" s="317" t="n"/>
+      <c r="S27" s="317" t="n"/>
+      <c r="T27" s="687" t="n"/>
+      <c r="U27" s="317" t="n"/>
+      <c r="V27" s="317" t="n"/>
+      <c r="W27" s="317" t="n"/>
+      <c r="X27" s="317" t="n"/>
+      <c r="Y27" s="317" t="n"/>
+      <c r="Z27" s="317" t="n"/>
+      <c r="AA27" s="317" t="n"/>
+      <c r="AB27" s="317" t="n"/>
+      <c r="AC27" s="317" t="n"/>
+      <c r="AD27" s="317" t="n"/>
+      <c r="AE27" s="317" t="n"/>
+      <c r="AF27" s="668" t="n"/>
+      <c r="AG27" s="317" t="n"/>
+      <c r="AH27" s="317" t="n"/>
+      <c r="AI27" s="317" t="n"/>
+      <c r="AJ27" s="668" t="n"/>
+      <c r="AK27" s="317" t="n"/>
+      <c r="AL27" s="317" t="n"/>
+      <c r="AM27" s="688" t="n"/>
+      <c r="AN27" s="319" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1" s="329">
-      <c r="A28" s="483">
+      <c r="A28" s="689">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B28" s="409" t="n"/>
-      <c r="C28" s="484" t="inlineStr">
+      <c r="B28" s="738" t="n"/>
+      <c r="C28" s="690" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D28" s="409" t="n"/>
-      <c r="E28" s="409" t="n"/>
-      <c r="F28" s="462" t="n"/>
-      <c r="G28" s="409" t="n"/>
-      <c r="H28" s="409" t="n"/>
-      <c r="I28" s="409" t="n"/>
-      <c r="J28" s="409" t="n"/>
-      <c r="K28" s="409" t="n"/>
-      <c r="L28" s="409" t="n"/>
-      <c r="M28" s="409" t="n"/>
-      <c r="N28" s="409" t="n"/>
-      <c r="O28" s="409" t="n"/>
-      <c r="P28" s="409" t="n"/>
-      <c r="Q28" s="409" t="n"/>
-      <c r="R28" s="409" t="n"/>
-      <c r="S28" s="409" t="n"/>
-      <c r="T28" s="485" t="n"/>
-      <c r="U28" s="409" t="n"/>
-      <c r="V28" s="409" t="n"/>
-      <c r="W28" s="409" t="n"/>
-      <c r="X28" s="409" t="n"/>
-      <c r="Y28" s="409" t="n"/>
-      <c r="Z28" s="409" t="n"/>
-      <c r="AA28" s="409" t="n"/>
-      <c r="AB28" s="409" t="n"/>
-      <c r="AC28" s="409" t="n"/>
-      <c r="AD28" s="409" t="n"/>
-      <c r="AE28" s="409" t="n"/>
-      <c r="AF28" s="462" t="n"/>
-      <c r="AG28" s="409" t="n"/>
-      <c r="AH28" s="409" t="n"/>
-      <c r="AI28" s="409" t="n"/>
-      <c r="AJ28" s="462" t="n"/>
-      <c r="AK28" s="409" t="n"/>
-      <c r="AL28" s="409" t="n"/>
-      <c r="AM28" s="564" t="n"/>
-      <c r="AN28" s="556" t="n"/>
+      <c r="D28" s="738" t="n"/>
+      <c r="E28" s="738" t="n"/>
+      <c r="F28" s="672" t="n"/>
+      <c r="G28" s="738" t="n"/>
+      <c r="H28" s="738" t="n"/>
+      <c r="I28" s="738" t="n"/>
+      <c r="J28" s="738" t="n"/>
+      <c r="K28" s="738" t="n"/>
+      <c r="L28" s="738" t="n"/>
+      <c r="M28" s="738" t="n"/>
+      <c r="N28" s="738" t="n"/>
+      <c r="O28" s="738" t="n"/>
+      <c r="P28" s="738" t="n"/>
+      <c r="Q28" s="738" t="n"/>
+      <c r="R28" s="738" t="n"/>
+      <c r="S28" s="738" t="n"/>
+      <c r="T28" s="691" t="n"/>
+      <c r="U28" s="738" t="n"/>
+      <c r="V28" s="738" t="n"/>
+      <c r="W28" s="738" t="n"/>
+      <c r="X28" s="738" t="n"/>
+      <c r="Y28" s="738" t="n"/>
+      <c r="Z28" s="738" t="n"/>
+      <c r="AA28" s="738" t="n"/>
+      <c r="AB28" s="738" t="n"/>
+      <c r="AC28" s="738" t="n"/>
+      <c r="AD28" s="738" t="n"/>
+      <c r="AE28" s="738" t="n"/>
+      <c r="AF28" s="672" t="n"/>
+      <c r="AG28" s="738" t="n"/>
+      <c r="AH28" s="738" t="n"/>
+      <c r="AI28" s="738" t="n"/>
+      <c r="AJ28" s="672" t="n"/>
+      <c r="AK28" s="738" t="n"/>
+      <c r="AL28" s="738" t="n"/>
+      <c r="AM28" s="692" t="n"/>
+      <c r="AN28" s="739" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1" s="329">
-      <c r="A29" s="483">
+      <c r="A29" s="689">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B29" s="409" t="n"/>
-      <c r="C29" s="484" t="inlineStr">
+      <c r="B29" s="738" t="n"/>
+      <c r="C29" s="690" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D29" s="409" t="n"/>
-      <c r="E29" s="409" t="n"/>
-      <c r="F29" s="462" t="n"/>
-      <c r="G29" s="409" t="n"/>
-      <c r="H29" s="409" t="n"/>
-      <c r="I29" s="409" t="n"/>
-      <c r="J29" s="409" t="n"/>
-      <c r="K29" s="409" t="n"/>
-      <c r="L29" s="409" t="n"/>
-      <c r="M29" s="409" t="n"/>
-      <c r="N29" s="409" t="n"/>
-      <c r="O29" s="409" t="n"/>
-      <c r="P29" s="409" t="n"/>
-      <c r="Q29" s="409" t="n"/>
-      <c r="R29" s="409" t="n"/>
-      <c r="S29" s="409" t="n"/>
-      <c r="T29" s="485" t="n"/>
-      <c r="U29" s="409" t="n"/>
-      <c r="V29" s="409" t="n"/>
-      <c r="W29" s="409" t="n"/>
-      <c r="X29" s="409" t="n"/>
-      <c r="Y29" s="409" t="n"/>
-      <c r="Z29" s="409" t="n"/>
-      <c r="AA29" s="409" t="n"/>
-      <c r="AB29" s="409" t="n"/>
-      <c r="AC29" s="409" t="n"/>
-      <c r="AD29" s="409" t="n"/>
-      <c r="AE29" s="409" t="n"/>
-      <c r="AF29" s="462" t="n"/>
-      <c r="AG29" s="409" t="n"/>
-      <c r="AH29" s="409" t="n"/>
-      <c r="AI29" s="409" t="n"/>
-      <c r="AJ29" s="462" t="n"/>
-      <c r="AK29" s="409" t="n"/>
-      <c r="AL29" s="409" t="n"/>
-      <c r="AM29" s="564" t="n"/>
-      <c r="AN29" s="556" t="n"/>
+      <c r="D29" s="738" t="n"/>
+      <c r="E29" s="738" t="n"/>
+      <c r="F29" s="672" t="n"/>
+      <c r="G29" s="738" t="n"/>
+      <c r="H29" s="738" t="n"/>
+      <c r="I29" s="738" t="n"/>
+      <c r="J29" s="738" t="n"/>
+      <c r="K29" s="738" t="n"/>
+      <c r="L29" s="738" t="n"/>
+      <c r="M29" s="738" t="n"/>
+      <c r="N29" s="738" t="n"/>
+      <c r="O29" s="738" t="n"/>
+      <c r="P29" s="738" t="n"/>
+      <c r="Q29" s="738" t="n"/>
+      <c r="R29" s="738" t="n"/>
+      <c r="S29" s="738" t="n"/>
+      <c r="T29" s="691" t="n"/>
+      <c r="U29" s="738" t="n"/>
+      <c r="V29" s="738" t="n"/>
+      <c r="W29" s="738" t="n"/>
+      <c r="X29" s="738" t="n"/>
+      <c r="Y29" s="738" t="n"/>
+      <c r="Z29" s="738" t="n"/>
+      <c r="AA29" s="738" t="n"/>
+      <c r="AB29" s="738" t="n"/>
+      <c r="AC29" s="738" t="n"/>
+      <c r="AD29" s="738" t="n"/>
+      <c r="AE29" s="738" t="n"/>
+      <c r="AF29" s="672" t="n"/>
+      <c r="AG29" s="738" t="n"/>
+      <c r="AH29" s="738" t="n"/>
+      <c r="AI29" s="738" t="n"/>
+      <c r="AJ29" s="672" t="n"/>
+      <c r="AK29" s="738" t="n"/>
+      <c r="AL29" s="738" t="n"/>
+      <c r="AM29" s="692" t="n"/>
+      <c r="AN29" s="739" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1" s="329">
-      <c r="A30" s="483">
+      <c r="A30" s="689">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B30" s="409" t="n"/>
-      <c r="C30" s="484" t="inlineStr">
+      <c r="B30" s="738" t="n"/>
+      <c r="C30" s="690" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D30" s="409" t="n"/>
-      <c r="E30" s="409" t="n"/>
-      <c r="F30" s="462" t="n"/>
-      <c r="G30" s="409" t="n"/>
-      <c r="H30" s="409" t="n"/>
-      <c r="I30" s="409" t="n"/>
-      <c r="J30" s="409" t="n"/>
-      <c r="K30" s="409" t="n"/>
-      <c r="L30" s="409" t="n"/>
-      <c r="M30" s="409" t="n"/>
-      <c r="N30" s="409" t="n"/>
-      <c r="O30" s="409" t="n"/>
-      <c r="P30" s="409" t="n"/>
-      <c r="Q30" s="409" t="n"/>
-      <c r="R30" s="409" t="n"/>
-      <c r="S30" s="409" t="n"/>
-      <c r="T30" s="485" t="n"/>
-      <c r="U30" s="409" t="n"/>
-      <c r="V30" s="409" t="n"/>
-      <c r="W30" s="409" t="n"/>
-      <c r="X30" s="409" t="n"/>
-      <c r="Y30" s="409" t="n"/>
-      <c r="Z30" s="409" t="n"/>
-      <c r="AA30" s="409" t="n"/>
-      <c r="AB30" s="409" t="n"/>
-      <c r="AC30" s="409" t="n"/>
-      <c r="AD30" s="409" t="n"/>
-      <c r="AE30" s="409" t="n"/>
-      <c r="AF30" s="462" t="n"/>
-      <c r="AG30" s="409" t="n"/>
-      <c r="AH30" s="409" t="n"/>
-      <c r="AI30" s="409" t="n"/>
-      <c r="AJ30" s="462" t="n"/>
-      <c r="AK30" s="409" t="n"/>
-      <c r="AL30" s="409" t="n"/>
-      <c r="AM30" s="564" t="n"/>
-      <c r="AN30" s="556" t="n"/>
+      <c r="D30" s="738" t="n"/>
+      <c r="E30" s="738" t="n"/>
+      <c r="F30" s="672" t="n"/>
+      <c r="G30" s="738" t="n"/>
+      <c r="H30" s="738" t="n"/>
+      <c r="I30" s="738" t="n"/>
+      <c r="J30" s="738" t="n"/>
+      <c r="K30" s="738" t="n"/>
+      <c r="L30" s="738" t="n"/>
+      <c r="M30" s="738" t="n"/>
+      <c r="N30" s="738" t="n"/>
+      <c r="O30" s="738" t="n"/>
+      <c r="P30" s="738" t="n"/>
+      <c r="Q30" s="738" t="n"/>
+      <c r="R30" s="738" t="n"/>
+      <c r="S30" s="738" t="n"/>
+      <c r="T30" s="691" t="n"/>
+      <c r="U30" s="738" t="n"/>
+      <c r="V30" s="738" t="n"/>
+      <c r="W30" s="738" t="n"/>
+      <c r="X30" s="738" t="n"/>
+      <c r="Y30" s="738" t="n"/>
+      <c r="Z30" s="738" t="n"/>
+      <c r="AA30" s="738" t="n"/>
+      <c r="AB30" s="738" t="n"/>
+      <c r="AC30" s="738" t="n"/>
+      <c r="AD30" s="738" t="n"/>
+      <c r="AE30" s="738" t="n"/>
+      <c r="AF30" s="672" t="n"/>
+      <c r="AG30" s="738" t="n"/>
+      <c r="AH30" s="738" t="n"/>
+      <c r="AI30" s="738" t="n"/>
+      <c r="AJ30" s="672" t="n"/>
+      <c r="AK30" s="738" t="n"/>
+      <c r="AL30" s="738" t="n"/>
+      <c r="AM30" s="692" t="n"/>
+      <c r="AN30" s="739" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1" s="329">
-      <c r="A31" s="483">
+      <c r="A31" s="689">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B31" s="409" t="n"/>
-      <c r="C31" s="484" t="inlineStr">
+      <c r="B31" s="738" t="n"/>
+      <c r="C31" s="690" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D31" s="409" t="n"/>
-      <c r="E31" s="409" t="n"/>
-      <c r="F31" s="462" t="n"/>
-      <c r="G31" s="409" t="n"/>
-      <c r="H31" s="409" t="n"/>
-      <c r="I31" s="409" t="n"/>
-      <c r="J31" s="409" t="n"/>
-      <c r="K31" s="409" t="n"/>
-      <c r="L31" s="409" t="n"/>
-      <c r="M31" s="409" t="n"/>
-      <c r="N31" s="409" t="n"/>
-      <c r="O31" s="409" t="n"/>
-      <c r="P31" s="409" t="n"/>
-      <c r="Q31" s="409" t="n"/>
-      <c r="R31" s="409" t="n"/>
-      <c r="S31" s="409" t="n"/>
-      <c r="T31" s="485" t="n"/>
-      <c r="U31" s="409" t="n"/>
-      <c r="V31" s="409" t="n"/>
-      <c r="W31" s="409" t="n"/>
-      <c r="X31" s="409" t="n"/>
-      <c r="Y31" s="409" t="n"/>
-      <c r="Z31" s="409" t="n"/>
-      <c r="AA31" s="409" t="n"/>
-      <c r="AB31" s="409" t="n"/>
-      <c r="AC31" s="409" t="n"/>
-      <c r="AD31" s="409" t="n"/>
-      <c r="AE31" s="409" t="n"/>
-      <c r="AF31" s="462" t="n"/>
-      <c r="AG31" s="409" t="n"/>
-      <c r="AH31" s="409" t="n"/>
-      <c r="AI31" s="409" t="n"/>
-      <c r="AJ31" s="462" t="n"/>
-      <c r="AK31" s="409" t="n"/>
-      <c r="AL31" s="409" t="n"/>
-      <c r="AM31" s="564" t="n"/>
-      <c r="AN31" s="556" t="n"/>
+      <c r="D31" s="738" t="n"/>
+      <c r="E31" s="738" t="n"/>
+      <c r="F31" s="672" t="n"/>
+      <c r="G31" s="738" t="n"/>
+      <c r="H31" s="738" t="n"/>
+      <c r="I31" s="738" t="n"/>
+      <c r="J31" s="738" t="n"/>
+      <c r="K31" s="738" t="n"/>
+      <c r="L31" s="738" t="n"/>
+      <c r="M31" s="738" t="n"/>
+      <c r="N31" s="738" t="n"/>
+      <c r="O31" s="738" t="n"/>
+      <c r="P31" s="738" t="n"/>
+      <c r="Q31" s="738" t="n"/>
+      <c r="R31" s="738" t="n"/>
+      <c r="S31" s="738" t="n"/>
+      <c r="T31" s="691" t="n"/>
+      <c r="U31" s="738" t="n"/>
+      <c r="V31" s="738" t="n"/>
+      <c r="W31" s="738" t="n"/>
+      <c r="X31" s="738" t="n"/>
+      <c r="Y31" s="738" t="n"/>
+      <c r="Z31" s="738" t="n"/>
+      <c r="AA31" s="738" t="n"/>
+      <c r="AB31" s="738" t="n"/>
+      <c r="AC31" s="738" t="n"/>
+      <c r="AD31" s="738" t="n"/>
+      <c r="AE31" s="738" t="n"/>
+      <c r="AF31" s="672" t="n"/>
+      <c r="AG31" s="738" t="n"/>
+      <c r="AH31" s="738" t="n"/>
+      <c r="AI31" s="738" t="n"/>
+      <c r="AJ31" s="672" t="n"/>
+      <c r="AK31" s="738" t="n"/>
+      <c r="AL31" s="738" t="n"/>
+      <c r="AM31" s="692" t="n"/>
+      <c r="AN31" s="739" t="n"/>
     </row>
     <row r="32" ht="20" customHeight="1" s="329">
-      <c r="A32" s="487">
+      <c r="A32" s="693">
         <f>ROW()-ROW($A$27)+1</f>
         <v/>
       </c>
-      <c r="B32" s="545" t="n"/>
-      <c r="C32" s="488" t="inlineStr">
+      <c r="B32" s="740" t="n"/>
+      <c r="C32" s="694" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D32" s="545" t="n"/>
-      <c r="E32" s="545" t="n"/>
-      <c r="F32" s="467" t="n"/>
-      <c r="G32" s="545" t="n"/>
-      <c r="H32" s="545" t="n"/>
-      <c r="I32" s="545" t="n"/>
-      <c r="J32" s="545" t="n"/>
-      <c r="K32" s="545" t="n"/>
-      <c r="L32" s="545" t="n"/>
-      <c r="M32" s="545" t="n"/>
-      <c r="N32" s="545" t="n"/>
-      <c r="O32" s="545" t="n"/>
-      <c r="P32" s="545" t="n"/>
-      <c r="Q32" s="545" t="n"/>
-      <c r="R32" s="545" t="n"/>
-      <c r="S32" s="545" t="n"/>
-      <c r="T32" s="489" t="n"/>
-      <c r="U32" s="545" t="n"/>
-      <c r="V32" s="545" t="n"/>
-      <c r="W32" s="545" t="n"/>
-      <c r="X32" s="545" t="n"/>
-      <c r="Y32" s="545" t="n"/>
-      <c r="Z32" s="545" t="n"/>
-      <c r="AA32" s="545" t="n"/>
-      <c r="AB32" s="545" t="n"/>
-      <c r="AC32" s="545" t="n"/>
-      <c r="AD32" s="545" t="n"/>
-      <c r="AE32" s="545" t="n"/>
-      <c r="AF32" s="467" t="n"/>
-      <c r="AG32" s="545" t="n"/>
-      <c r="AH32" s="545" t="n"/>
-      <c r="AI32" s="545" t="n"/>
-      <c r="AJ32" s="467" t="n"/>
-      <c r="AK32" s="545" t="n"/>
-      <c r="AL32" s="545" t="n"/>
-      <c r="AM32" s="565" t="n"/>
-      <c r="AN32" s="548" t="n"/>
+      <c r="D32" s="740" t="n"/>
+      <c r="E32" s="740" t="n"/>
+      <c r="F32" s="676" t="n"/>
+      <c r="G32" s="740" t="n"/>
+      <c r="H32" s="740" t="n"/>
+      <c r="I32" s="740" t="n"/>
+      <c r="J32" s="740" t="n"/>
+      <c r="K32" s="740" t="n"/>
+      <c r="L32" s="740" t="n"/>
+      <c r="M32" s="740" t="n"/>
+      <c r="N32" s="740" t="n"/>
+      <c r="O32" s="740" t="n"/>
+      <c r="P32" s="740" t="n"/>
+      <c r="Q32" s="740" t="n"/>
+      <c r="R32" s="740" t="n"/>
+      <c r="S32" s="740" t="n"/>
+      <c r="T32" s="695" t="n"/>
+      <c r="U32" s="740" t="n"/>
+      <c r="V32" s="740" t="n"/>
+      <c r="W32" s="740" t="n"/>
+      <c r="X32" s="740" t="n"/>
+      <c r="Y32" s="740" t="n"/>
+      <c r="Z32" s="740" t="n"/>
+      <c r="AA32" s="740" t="n"/>
+      <c r="AB32" s="740" t="n"/>
+      <c r="AC32" s="740" t="n"/>
+      <c r="AD32" s="740" t="n"/>
+      <c r="AE32" s="740" t="n"/>
+      <c r="AF32" s="676" t="n"/>
+      <c r="AG32" s="740" t="n"/>
+      <c r="AH32" s="740" t="n"/>
+      <c r="AI32" s="740" t="n"/>
+      <c r="AJ32" s="676" t="n"/>
+      <c r="AK32" s="740" t="n"/>
+      <c r="AL32" s="740" t="n"/>
+      <c r="AM32" s="696" t="n"/>
+      <c r="AN32" s="741" t="n"/>
     </row>
     <row r="33" ht="3" customHeight="1" s="329">
       <c r="A33" s="357" t="n"/>
@@ -8158,150 +8832,150 @@
       <c r="AN33" s="350" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1" s="329">
-      <c r="A34" s="549" t="inlineStr">
+      <c r="A34" s="679" t="inlineStr">
         <is>
           <t xml:space="preserve">  4. FINAL DECISION / CLOSURE</t>
         </is>
       </c>
-      <c r="B34" s="550" t="n"/>
-      <c r="C34" s="550" t="n"/>
-      <c r="D34" s="550" t="n"/>
-      <c r="E34" s="550" t="n"/>
-      <c r="F34" s="550" t="n"/>
-      <c r="G34" s="550" t="n"/>
-      <c r="H34" s="550" t="n"/>
-      <c r="I34" s="550" t="n"/>
-      <c r="J34" s="550" t="n"/>
-      <c r="K34" s="550" t="n"/>
-      <c r="L34" s="550" t="n"/>
-      <c r="M34" s="550" t="n"/>
-      <c r="N34" s="550" t="n"/>
-      <c r="O34" s="550" t="n"/>
-      <c r="P34" s="550" t="n"/>
-      <c r="Q34" s="550" t="n"/>
-      <c r="R34" s="550" t="n"/>
-      <c r="S34" s="550" t="n"/>
-      <c r="T34" s="550" t="n"/>
-      <c r="U34" s="550" t="n"/>
-      <c r="V34" s="550" t="n"/>
-      <c r="W34" s="550" t="n"/>
-      <c r="X34" s="550" t="n"/>
-      <c r="Y34" s="550" t="n"/>
-      <c r="Z34" s="550" t="n"/>
-      <c r="AA34" s="550" t="n"/>
-      <c r="AB34" s="550" t="n"/>
-      <c r="AC34" s="550" t="n"/>
-      <c r="AD34" s="550" t="n"/>
-      <c r="AE34" s="550" t="n"/>
-      <c r="AF34" s="550" t="n"/>
-      <c r="AG34" s="550" t="n"/>
-      <c r="AH34" s="550" t="n"/>
-      <c r="AI34" s="550" t="n"/>
-      <c r="AJ34" s="550" t="n"/>
-      <c r="AK34" s="550" t="n"/>
-      <c r="AL34" s="550" t="n"/>
-      <c r="AM34" s="550" t="n"/>
-      <c r="AN34" s="551" t="n"/>
+      <c r="B34" s="285" t="n"/>
+      <c r="C34" s="285" t="n"/>
+      <c r="D34" s="285" t="n"/>
+      <c r="E34" s="285" t="n"/>
+      <c r="F34" s="285" t="n"/>
+      <c r="G34" s="285" t="n"/>
+      <c r="H34" s="285" t="n"/>
+      <c r="I34" s="285" t="n"/>
+      <c r="J34" s="285" t="n"/>
+      <c r="K34" s="285" t="n"/>
+      <c r="L34" s="285" t="n"/>
+      <c r="M34" s="285" t="n"/>
+      <c r="N34" s="285" t="n"/>
+      <c r="O34" s="285" t="n"/>
+      <c r="P34" s="285" t="n"/>
+      <c r="Q34" s="285" t="n"/>
+      <c r="R34" s="285" t="n"/>
+      <c r="S34" s="285" t="n"/>
+      <c r="T34" s="285" t="n"/>
+      <c r="U34" s="285" t="n"/>
+      <c r="V34" s="285" t="n"/>
+      <c r="W34" s="285" t="n"/>
+      <c r="X34" s="285" t="n"/>
+      <c r="Y34" s="285" t="n"/>
+      <c r="Z34" s="285" t="n"/>
+      <c r="AA34" s="285" t="n"/>
+      <c r="AB34" s="285" t="n"/>
+      <c r="AC34" s="285" t="n"/>
+      <c r="AD34" s="285" t="n"/>
+      <c r="AE34" s="285" t="n"/>
+      <c r="AF34" s="285" t="n"/>
+      <c r="AG34" s="285" t="n"/>
+      <c r="AH34" s="285" t="n"/>
+      <c r="AI34" s="285" t="n"/>
+      <c r="AJ34" s="285" t="n"/>
+      <c r="AK34" s="285" t="n"/>
+      <c r="AL34" s="285" t="n"/>
+      <c r="AM34" s="285" t="n"/>
+      <c r="AN34" s="286" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1" s="329">
-      <c r="A35" s="456" t="inlineStr">
+      <c r="A35" s="667" t="inlineStr">
         <is>
           <t>Final Decision</t>
         </is>
       </c>
-      <c r="B35" s="552" t="n"/>
-      <c r="C35" s="552" t="n"/>
-      <c r="D35" s="552" t="n"/>
-      <c r="E35" s="552" t="n"/>
-      <c r="F35" s="552" t="n"/>
-      <c r="G35" s="552" t="n"/>
-      <c r="H35" s="458" t="n"/>
-      <c r="I35" s="552" t="n"/>
-      <c r="J35" s="552" t="n"/>
-      <c r="K35" s="552" t="n"/>
-      <c r="L35" s="552" t="n"/>
-      <c r="M35" s="552" t="n"/>
-      <c r="N35" s="552" t="n"/>
-      <c r="O35" s="552" t="n"/>
-      <c r="P35" s="552" t="n"/>
-      <c r="Q35" s="552" t="n"/>
-      <c r="R35" s="552" t="n"/>
-      <c r="S35" s="552" t="n"/>
-      <c r="T35" s="552" t="n"/>
-      <c r="U35" s="459" t="inlineStr">
+      <c r="B35" s="317" t="n"/>
+      <c r="C35" s="317" t="n"/>
+      <c r="D35" s="317" t="n"/>
+      <c r="E35" s="317" t="n"/>
+      <c r="F35" s="317" t="n"/>
+      <c r="G35" s="317" t="n"/>
+      <c r="H35" s="668" t="n"/>
+      <c r="I35" s="317" t="n"/>
+      <c r="J35" s="317" t="n"/>
+      <c r="K35" s="317" t="n"/>
+      <c r="L35" s="317" t="n"/>
+      <c r="M35" s="317" t="n"/>
+      <c r="N35" s="317" t="n"/>
+      <c r="O35" s="317" t="n"/>
+      <c r="P35" s="317" t="n"/>
+      <c r="Q35" s="317" t="n"/>
+      <c r="R35" s="317" t="n"/>
+      <c r="S35" s="317" t="n"/>
+      <c r="T35" s="317" t="n"/>
+      <c r="U35" s="669" t="inlineStr">
         <is>
           <t>Reviewed by</t>
         </is>
       </c>
-      <c r="V35" s="552" t="n"/>
-      <c r="W35" s="552" t="n"/>
-      <c r="X35" s="552" t="n"/>
-      <c r="Y35" s="552" t="n"/>
-      <c r="Z35" s="552" t="n"/>
-      <c r="AA35" s="552" t="n"/>
-      <c r="AB35" s="553" t="n"/>
-      <c r="AC35" s="552" t="n"/>
-      <c r="AD35" s="552" t="n"/>
-      <c r="AE35" s="552" t="n"/>
-      <c r="AF35" s="552" t="n"/>
-      <c r="AG35" s="552" t="n"/>
-      <c r="AH35" s="552" t="n"/>
-      <c r="AI35" s="552" t="n"/>
-      <c r="AJ35" s="552" t="n"/>
-      <c r="AK35" s="552" t="n"/>
-      <c r="AL35" s="552" t="n"/>
-      <c r="AM35" s="552" t="n"/>
-      <c r="AN35" s="554" t="n"/>
+      <c r="V35" s="317" t="n"/>
+      <c r="W35" s="317" t="n"/>
+      <c r="X35" s="317" t="n"/>
+      <c r="Y35" s="317" t="n"/>
+      <c r="Z35" s="317" t="n"/>
+      <c r="AA35" s="317" t="n"/>
+      <c r="AB35" s="670" t="n"/>
+      <c r="AC35" s="317" t="n"/>
+      <c r="AD35" s="317" t="n"/>
+      <c r="AE35" s="317" t="n"/>
+      <c r="AF35" s="317" t="n"/>
+      <c r="AG35" s="317" t="n"/>
+      <c r="AH35" s="317" t="n"/>
+      <c r="AI35" s="317" t="n"/>
+      <c r="AJ35" s="317" t="n"/>
+      <c r="AK35" s="317" t="n"/>
+      <c r="AL35" s="317" t="n"/>
+      <c r="AM35" s="317" t="n"/>
+      <c r="AN35" s="319" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1" s="329">
-      <c r="A36" s="465" t="inlineStr">
+      <c r="A36" s="675" t="inlineStr">
         <is>
           <t>Containment Required (YES/NO)</t>
         </is>
       </c>
-      <c r="B36" s="545" t="n"/>
-      <c r="C36" s="545" t="n"/>
-      <c r="D36" s="545" t="n"/>
-      <c r="E36" s="545" t="n"/>
-      <c r="F36" s="545" t="n"/>
-      <c r="G36" s="545" t="n"/>
-      <c r="H36" s="467" t="n"/>
-      <c r="I36" s="545" t="n"/>
-      <c r="J36" s="545" t="n"/>
-      <c r="K36" s="545" t="n"/>
-      <c r="L36" s="545" t="n"/>
-      <c r="M36" s="545" t="n"/>
-      <c r="N36" s="545" t="n"/>
-      <c r="O36" s="545" t="n"/>
-      <c r="P36" s="545" t="n"/>
-      <c r="Q36" s="545" t="n"/>
-      <c r="R36" s="545" t="n"/>
-      <c r="S36" s="545" t="n"/>
-      <c r="T36" s="545" t="n"/>
-      <c r="U36" s="468" t="inlineStr">
+      <c r="B36" s="740" t="n"/>
+      <c r="C36" s="740" t="n"/>
+      <c r="D36" s="740" t="n"/>
+      <c r="E36" s="740" t="n"/>
+      <c r="F36" s="740" t="n"/>
+      <c r="G36" s="740" t="n"/>
+      <c r="H36" s="676" t="n"/>
+      <c r="I36" s="740" t="n"/>
+      <c r="J36" s="740" t="n"/>
+      <c r="K36" s="740" t="n"/>
+      <c r="L36" s="740" t="n"/>
+      <c r="M36" s="740" t="n"/>
+      <c r="N36" s="740" t="n"/>
+      <c r="O36" s="740" t="n"/>
+      <c r="P36" s="740" t="n"/>
+      <c r="Q36" s="740" t="n"/>
+      <c r="R36" s="740" t="n"/>
+      <c r="S36" s="740" t="n"/>
+      <c r="T36" s="740" t="n"/>
+      <c r="U36" s="677" t="inlineStr">
         <is>
           <t>Target Closeout</t>
         </is>
       </c>
-      <c r="V36" s="545" t="n"/>
-      <c r="W36" s="545" t="n"/>
-      <c r="X36" s="545" t="n"/>
-      <c r="Y36" s="545" t="n"/>
-      <c r="Z36" s="545" t="n"/>
-      <c r="AA36" s="545" t="n"/>
-      <c r="AB36" s="557" t="n"/>
-      <c r="AC36" s="545" t="n"/>
-      <c r="AD36" s="545" t="n"/>
-      <c r="AE36" s="545" t="n"/>
-      <c r="AF36" s="545" t="n"/>
-      <c r="AG36" s="545" t="n"/>
-      <c r="AH36" s="545" t="n"/>
-      <c r="AI36" s="545" t="n"/>
-      <c r="AJ36" s="545" t="n"/>
-      <c r="AK36" s="545" t="n"/>
-      <c r="AL36" s="545" t="n"/>
-      <c r="AM36" s="545" t="n"/>
-      <c r="AN36" s="548" t="n"/>
+      <c r="V36" s="740" t="n"/>
+      <c r="W36" s="740" t="n"/>
+      <c r="X36" s="740" t="n"/>
+      <c r="Y36" s="740" t="n"/>
+      <c r="Z36" s="740" t="n"/>
+      <c r="AA36" s="740" t="n"/>
+      <c r="AB36" s="678" t="n"/>
+      <c r="AC36" s="740" t="n"/>
+      <c r="AD36" s="740" t="n"/>
+      <c r="AE36" s="740" t="n"/>
+      <c r="AF36" s="740" t="n"/>
+      <c r="AG36" s="740" t="n"/>
+      <c r="AH36" s="740" t="n"/>
+      <c r="AI36" s="740" t="n"/>
+      <c r="AJ36" s="740" t="n"/>
+      <c r="AK36" s="740" t="n"/>
+      <c r="AL36" s="740" t="n"/>
+      <c r="AM36" s="740" t="n"/>
+      <c r="AN36" s="741" t="n"/>
     </row>
     <row r="37" ht="3" customHeight="1" s="329">
       <c r="A37" s="362" t="n"/>
@@ -8346,206 +9020,206 @@
       <c r="AN37" s="350" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1" s="329">
-      <c r="A38" s="549" t="inlineStr">
+      <c r="A38" s="679" t="inlineStr">
         <is>
           <t xml:space="preserve">  5. APPROVAL / SIGN-OFF</t>
         </is>
       </c>
-      <c r="B38" s="550" t="n"/>
-      <c r="C38" s="550" t="n"/>
-      <c r="D38" s="550" t="n"/>
-      <c r="E38" s="550" t="n"/>
-      <c r="F38" s="550" t="n"/>
-      <c r="G38" s="550" t="n"/>
-      <c r="H38" s="550" t="n"/>
-      <c r="I38" s="550" t="n"/>
-      <c r="J38" s="550" t="n"/>
-      <c r="K38" s="550" t="n"/>
-      <c r="L38" s="550" t="n"/>
-      <c r="M38" s="550" t="n"/>
-      <c r="N38" s="550" t="n"/>
-      <c r="O38" s="550" t="n"/>
-      <c r="P38" s="550" t="n"/>
-      <c r="Q38" s="550" t="n"/>
-      <c r="R38" s="550" t="n"/>
-      <c r="S38" s="550" t="n"/>
-      <c r="T38" s="550" t="n"/>
-      <c r="U38" s="550" t="n"/>
-      <c r="V38" s="550" t="n"/>
-      <c r="W38" s="550" t="n"/>
-      <c r="X38" s="550" t="n"/>
-      <c r="Y38" s="550" t="n"/>
-      <c r="Z38" s="550" t="n"/>
-      <c r="AA38" s="550" t="n"/>
-      <c r="AB38" s="550" t="n"/>
-      <c r="AC38" s="550" t="n"/>
-      <c r="AD38" s="550" t="n"/>
-      <c r="AE38" s="550" t="n"/>
-      <c r="AF38" s="550" t="n"/>
-      <c r="AG38" s="550" t="n"/>
-      <c r="AH38" s="550" t="n"/>
-      <c r="AI38" s="550" t="n"/>
-      <c r="AJ38" s="550" t="n"/>
-      <c r="AK38" s="550" t="n"/>
-      <c r="AL38" s="550" t="n"/>
-      <c r="AM38" s="550" t="n"/>
-      <c r="AN38" s="551" t="n"/>
+      <c r="B38" s="285" t="n"/>
+      <c r="C38" s="285" t="n"/>
+      <c r="D38" s="285" t="n"/>
+      <c r="E38" s="285" t="n"/>
+      <c r="F38" s="285" t="n"/>
+      <c r="G38" s="285" t="n"/>
+      <c r="H38" s="285" t="n"/>
+      <c r="I38" s="285" t="n"/>
+      <c r="J38" s="285" t="n"/>
+      <c r="K38" s="285" t="n"/>
+      <c r="L38" s="285" t="n"/>
+      <c r="M38" s="285" t="n"/>
+      <c r="N38" s="285" t="n"/>
+      <c r="O38" s="285" t="n"/>
+      <c r="P38" s="285" t="n"/>
+      <c r="Q38" s="285" t="n"/>
+      <c r="R38" s="285" t="n"/>
+      <c r="S38" s="285" t="n"/>
+      <c r="T38" s="285" t="n"/>
+      <c r="U38" s="285" t="n"/>
+      <c r="V38" s="285" t="n"/>
+      <c r="W38" s="285" t="n"/>
+      <c r="X38" s="285" t="n"/>
+      <c r="Y38" s="285" t="n"/>
+      <c r="Z38" s="285" t="n"/>
+      <c r="AA38" s="285" t="n"/>
+      <c r="AB38" s="285" t="n"/>
+      <c r="AC38" s="285" t="n"/>
+      <c r="AD38" s="285" t="n"/>
+      <c r="AE38" s="285" t="n"/>
+      <c r="AF38" s="285" t="n"/>
+      <c r="AG38" s="285" t="n"/>
+      <c r="AH38" s="285" t="n"/>
+      <c r="AI38" s="285" t="n"/>
+      <c r="AJ38" s="285" t="n"/>
+      <c r="AK38" s="285" t="n"/>
+      <c r="AL38" s="285" t="n"/>
+      <c r="AM38" s="285" t="n"/>
+      <c r="AN38" s="286" t="n"/>
     </row>
     <row r="39" ht="26" customHeight="1" s="329">
-      <c r="A39" s="479" t="inlineStr">
+      <c r="A39" s="685" t="inlineStr">
         <is>
           <t>Prepared by</t>
         </is>
       </c>
-      <c r="B39" s="552" t="n"/>
-      <c r="C39" s="552" t="n"/>
-      <c r="D39" s="552" t="n"/>
-      <c r="E39" s="552" t="n"/>
-      <c r="F39" s="552" t="n"/>
-      <c r="G39" s="552" t="n"/>
-      <c r="H39" s="552" t="n"/>
-      <c r="I39" s="552" t="n"/>
-      <c r="J39" s="552" t="n"/>
-      <c r="K39" s="552" t="n"/>
-      <c r="L39" s="552" t="n"/>
-      <c r="M39" s="552" t="n"/>
-      <c r="N39" s="491" t="inlineStr">
+      <c r="B39" s="317" t="n"/>
+      <c r="C39" s="317" t="n"/>
+      <c r="D39" s="317" t="n"/>
+      <c r="E39" s="317" t="n"/>
+      <c r="F39" s="317" t="n"/>
+      <c r="G39" s="317" t="n"/>
+      <c r="H39" s="317" t="n"/>
+      <c r="I39" s="317" t="n"/>
+      <c r="J39" s="317" t="n"/>
+      <c r="K39" s="317" t="n"/>
+      <c r="L39" s="317" t="n"/>
+      <c r="M39" s="317" t="n"/>
+      <c r="N39" s="697" t="inlineStr">
         <is>
           <t>Reviewed by</t>
         </is>
       </c>
-      <c r="O39" s="552" t="n"/>
-      <c r="P39" s="552" t="n"/>
-      <c r="Q39" s="552" t="n"/>
-      <c r="R39" s="552" t="n"/>
-      <c r="S39" s="552" t="n"/>
-      <c r="T39" s="552" t="n"/>
-      <c r="U39" s="552" t="n"/>
-      <c r="V39" s="552" t="n"/>
-      <c r="W39" s="552" t="n"/>
-      <c r="X39" s="552" t="n"/>
-      <c r="Y39" s="552" t="n"/>
-      <c r="Z39" s="552" t="n"/>
-      <c r="AA39" s="566" t="inlineStr">
+      <c r="O39" s="317" t="n"/>
+      <c r="P39" s="317" t="n"/>
+      <c r="Q39" s="317" t="n"/>
+      <c r="R39" s="317" t="n"/>
+      <c r="S39" s="317" t="n"/>
+      <c r="T39" s="317" t="n"/>
+      <c r="U39" s="317" t="n"/>
+      <c r="V39" s="317" t="n"/>
+      <c r="W39" s="317" t="n"/>
+      <c r="X39" s="317" t="n"/>
+      <c r="Y39" s="317" t="n"/>
+      <c r="Z39" s="317" t="n"/>
+      <c r="AA39" s="698" t="inlineStr">
         <is>
           <t>Approved by</t>
         </is>
       </c>
-      <c r="AB39" s="552" t="n"/>
-      <c r="AC39" s="552" t="n"/>
-      <c r="AD39" s="552" t="n"/>
-      <c r="AE39" s="552" t="n"/>
-      <c r="AF39" s="552" t="n"/>
-      <c r="AG39" s="552" t="n"/>
-      <c r="AH39" s="552" t="n"/>
-      <c r="AI39" s="552" t="n"/>
-      <c r="AJ39" s="552" t="n"/>
-      <c r="AK39" s="552" t="n"/>
-      <c r="AL39" s="552" t="n"/>
-      <c r="AM39" s="552" t="n"/>
-      <c r="AN39" s="554" t="n"/>
+      <c r="AB39" s="317" t="n"/>
+      <c r="AC39" s="317" t="n"/>
+      <c r="AD39" s="317" t="n"/>
+      <c r="AE39" s="317" t="n"/>
+      <c r="AF39" s="317" t="n"/>
+      <c r="AG39" s="317" t="n"/>
+      <c r="AH39" s="317" t="n"/>
+      <c r="AI39" s="317" t="n"/>
+      <c r="AJ39" s="317" t="n"/>
+      <c r="AK39" s="317" t="n"/>
+      <c r="AL39" s="317" t="n"/>
+      <c r="AM39" s="317" t="n"/>
+      <c r="AN39" s="319" t="n"/>
     </row>
     <row r="40" ht="26" customHeight="1" s="329">
-      <c r="A40" s="492" t="inlineStr">
+      <c r="A40" s="699" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="B40" s="408" t="n"/>
-      <c r="C40" s="408" t="n"/>
-      <c r="D40" s="408" t="n"/>
-      <c r="E40" s="408" t="n"/>
-      <c r="F40" s="408" t="n"/>
-      <c r="G40" s="408" t="n"/>
-      <c r="H40" s="408" t="n"/>
-      <c r="I40" s="408" t="n"/>
-      <c r="J40" s="408" t="n"/>
-      <c r="K40" s="408" t="n"/>
-      <c r="L40" s="408" t="n"/>
-      <c r="M40" s="408" t="n"/>
-      <c r="N40" s="493" t="inlineStr">
+      <c r="B40" s="742" t="n"/>
+      <c r="C40" s="742" t="n"/>
+      <c r="D40" s="742" t="n"/>
+      <c r="E40" s="742" t="n"/>
+      <c r="F40" s="742" t="n"/>
+      <c r="G40" s="742" t="n"/>
+      <c r="H40" s="742" t="n"/>
+      <c r="I40" s="742" t="n"/>
+      <c r="J40" s="742" t="n"/>
+      <c r="K40" s="742" t="n"/>
+      <c r="L40" s="742" t="n"/>
+      <c r="M40" s="742" t="n"/>
+      <c r="N40" s="700" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="O40" s="408" t="n"/>
-      <c r="P40" s="408" t="n"/>
-      <c r="Q40" s="408" t="n"/>
-      <c r="R40" s="408" t="n"/>
-      <c r="S40" s="408" t="n"/>
-      <c r="T40" s="408" t="n"/>
-      <c r="U40" s="408" t="n"/>
-      <c r="V40" s="408" t="n"/>
-      <c r="W40" s="408" t="n"/>
-      <c r="X40" s="408" t="n"/>
-      <c r="Y40" s="408" t="n"/>
-      <c r="Z40" s="408" t="n"/>
-      <c r="AA40" s="567" t="inlineStr">
+      <c r="O40" s="742" t="n"/>
+      <c r="P40" s="742" t="n"/>
+      <c r="Q40" s="742" t="n"/>
+      <c r="R40" s="742" t="n"/>
+      <c r="S40" s="742" t="n"/>
+      <c r="T40" s="742" t="n"/>
+      <c r="U40" s="742" t="n"/>
+      <c r="V40" s="742" t="n"/>
+      <c r="W40" s="742" t="n"/>
+      <c r="X40" s="742" t="n"/>
+      <c r="Y40" s="742" t="n"/>
+      <c r="Z40" s="742" t="n"/>
+      <c r="AA40" s="701" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="AB40" s="408" t="n"/>
-      <c r="AC40" s="408" t="n"/>
-      <c r="AD40" s="408" t="n"/>
-      <c r="AE40" s="408" t="n"/>
-      <c r="AF40" s="408" t="n"/>
-      <c r="AG40" s="408" t="n"/>
-      <c r="AH40" s="408" t="n"/>
-      <c r="AI40" s="408" t="n"/>
-      <c r="AJ40" s="408" t="n"/>
-      <c r="AK40" s="408" t="n"/>
-      <c r="AL40" s="408" t="n"/>
-      <c r="AM40" s="408" t="n"/>
-      <c r="AN40" s="538" t="n"/>
+      <c r="AB40" s="742" t="n"/>
+      <c r="AC40" s="742" t="n"/>
+      <c r="AD40" s="742" t="n"/>
+      <c r="AE40" s="742" t="n"/>
+      <c r="AF40" s="742" t="n"/>
+      <c r="AG40" s="742" t="n"/>
+      <c r="AH40" s="742" t="n"/>
+      <c r="AI40" s="742" t="n"/>
+      <c r="AJ40" s="742" t="n"/>
+      <c r="AK40" s="742" t="n"/>
+      <c r="AL40" s="742" t="n"/>
+      <c r="AM40" s="742" t="n"/>
+      <c r="AN40" s="743" t="n"/>
     </row>
     <row r="41" ht="20" customHeight="1" s="329">
-      <c r="A41" s="533" t="n"/>
-      <c r="N41" s="411" t="n"/>
-      <c r="AA41" s="411" t="n"/>
-      <c r="AN41" s="534" t="n"/>
+      <c r="A41" s="328" t="n"/>
+      <c r="N41" s="744" t="n"/>
+      <c r="AA41" s="744" t="n"/>
+      <c r="AN41" s="330" t="n"/>
     </row>
     <row r="42" ht="20" customHeight="1" s="329">
-      <c r="A42" s="560" t="n"/>
-      <c r="B42" s="413" t="n"/>
-      <c r="C42" s="413" t="n"/>
-      <c r="D42" s="413" t="n"/>
-      <c r="E42" s="413" t="n"/>
-      <c r="F42" s="413" t="n"/>
-      <c r="G42" s="413" t="n"/>
-      <c r="H42" s="413" t="n"/>
-      <c r="I42" s="413" t="n"/>
-      <c r="J42" s="413" t="n"/>
-      <c r="K42" s="413" t="n"/>
-      <c r="L42" s="413" t="n"/>
-      <c r="M42" s="413" t="n"/>
-      <c r="N42" s="412" t="n"/>
-      <c r="O42" s="413" t="n"/>
-      <c r="P42" s="413" t="n"/>
-      <c r="Q42" s="413" t="n"/>
-      <c r="R42" s="413" t="n"/>
-      <c r="S42" s="413" t="n"/>
-      <c r="T42" s="413" t="n"/>
-      <c r="U42" s="413" t="n"/>
-      <c r="V42" s="413" t="n"/>
-      <c r="W42" s="413" t="n"/>
-      <c r="X42" s="413" t="n"/>
-      <c r="Y42" s="413" t="n"/>
-      <c r="Z42" s="413" t="n"/>
-      <c r="AA42" s="412" t="n"/>
-      <c r="AB42" s="413" t="n"/>
-      <c r="AC42" s="413" t="n"/>
-      <c r="AD42" s="413" t="n"/>
-      <c r="AE42" s="413" t="n"/>
-      <c r="AF42" s="413" t="n"/>
-      <c r="AG42" s="413" t="n"/>
-      <c r="AH42" s="413" t="n"/>
-      <c r="AI42" s="413" t="n"/>
-      <c r="AJ42" s="413" t="n"/>
-      <c r="AK42" s="413" t="n"/>
-      <c r="AL42" s="413" t="n"/>
-      <c r="AM42" s="413" t="n"/>
-      <c r="AN42" s="561" t="n"/>
+      <c r="A42" s="279" t="n"/>
+      <c r="B42" s="322" t="n"/>
+      <c r="C42" s="322" t="n"/>
+      <c r="D42" s="322" t="n"/>
+      <c r="E42" s="322" t="n"/>
+      <c r="F42" s="322" t="n"/>
+      <c r="G42" s="322" t="n"/>
+      <c r="H42" s="322" t="n"/>
+      <c r="I42" s="322" t="n"/>
+      <c r="J42" s="322" t="n"/>
+      <c r="K42" s="322" t="n"/>
+      <c r="L42" s="322" t="n"/>
+      <c r="M42" s="322" t="n"/>
+      <c r="N42" s="745" t="n"/>
+      <c r="O42" s="322" t="n"/>
+      <c r="P42" s="322" t="n"/>
+      <c r="Q42" s="322" t="n"/>
+      <c r="R42" s="322" t="n"/>
+      <c r="S42" s="322" t="n"/>
+      <c r="T42" s="322" t="n"/>
+      <c r="U42" s="322" t="n"/>
+      <c r="V42" s="322" t="n"/>
+      <c r="W42" s="322" t="n"/>
+      <c r="X42" s="322" t="n"/>
+      <c r="Y42" s="322" t="n"/>
+      <c r="Z42" s="322" t="n"/>
+      <c r="AA42" s="745" t="n"/>
+      <c r="AB42" s="322" t="n"/>
+      <c r="AC42" s="322" t="n"/>
+      <c r="AD42" s="322" t="n"/>
+      <c r="AE42" s="322" t="n"/>
+      <c r="AF42" s="322" t="n"/>
+      <c r="AG42" s="322" t="n"/>
+      <c r="AH42" s="322" t="n"/>
+      <c r="AI42" s="322" t="n"/>
+      <c r="AJ42" s="322" t="n"/>
+      <c r="AK42" s="322" t="n"/>
+      <c r="AL42" s="322" t="n"/>
+      <c r="AM42" s="322" t="n"/>
+      <c r="AN42" s="324" t="n"/>
     </row>
     <row r="43" ht="3" customHeight="1" s="329">
       <c r="A43" s="384" t="n"/>
@@ -8590,50 +9264,50 @@
       <c r="AN43" s="350" t="n"/>
     </row>
     <row r="44" ht="26" customHeight="1" s="329">
-      <c r="A44" s="569" t="inlineStr">
+      <c r="A44" s="702" t="inlineStr">
         <is>
           <t>NOTICE: Use for outsourced incoming verification only. Normal receiving / put-away remains in FRM-701; abnormal hold / disposition goes to FRM-413.</t>
         </is>
       </c>
-      <c r="B44" s="570" t="n"/>
-      <c r="C44" s="570" t="n"/>
-      <c r="D44" s="570" t="n"/>
-      <c r="E44" s="570" t="n"/>
-      <c r="F44" s="570" t="n"/>
-      <c r="G44" s="570" t="n"/>
-      <c r="H44" s="570" t="n"/>
-      <c r="I44" s="570" t="n"/>
-      <c r="J44" s="570" t="n"/>
-      <c r="K44" s="570" t="n"/>
-      <c r="L44" s="570" t="n"/>
-      <c r="M44" s="570" t="n"/>
-      <c r="N44" s="570" t="n"/>
-      <c r="O44" s="570" t="n"/>
-      <c r="P44" s="570" t="n"/>
-      <c r="Q44" s="570" t="n"/>
-      <c r="R44" s="570" t="n"/>
-      <c r="S44" s="570" t="n"/>
-      <c r="T44" s="570" t="n"/>
-      <c r="U44" s="570" t="n"/>
-      <c r="V44" s="570" t="n"/>
-      <c r="W44" s="570" t="n"/>
-      <c r="X44" s="570" t="n"/>
-      <c r="Y44" s="570" t="n"/>
-      <c r="Z44" s="570" t="n"/>
-      <c r="AA44" s="570" t="n"/>
-      <c r="AB44" s="570" t="n"/>
-      <c r="AC44" s="570" t="n"/>
-      <c r="AD44" s="570" t="n"/>
-      <c r="AE44" s="570" t="n"/>
-      <c r="AF44" s="570" t="n"/>
-      <c r="AG44" s="570" t="n"/>
-      <c r="AH44" s="570" t="n"/>
-      <c r="AI44" s="570" t="n"/>
-      <c r="AJ44" s="570" t="n"/>
-      <c r="AK44" s="570" t="n"/>
-      <c r="AL44" s="570" t="n"/>
-      <c r="AM44" s="570" t="n"/>
-      <c r="AN44" s="571" t="n"/>
+      <c r="B44" s="703" t="n"/>
+      <c r="C44" s="703" t="n"/>
+      <c r="D44" s="703" t="n"/>
+      <c r="E44" s="703" t="n"/>
+      <c r="F44" s="703" t="n"/>
+      <c r="G44" s="703" t="n"/>
+      <c r="H44" s="703" t="n"/>
+      <c r="I44" s="703" t="n"/>
+      <c r="J44" s="703" t="n"/>
+      <c r="K44" s="703" t="n"/>
+      <c r="L44" s="703" t="n"/>
+      <c r="M44" s="703" t="n"/>
+      <c r="N44" s="703" t="n"/>
+      <c r="O44" s="703" t="n"/>
+      <c r="P44" s="703" t="n"/>
+      <c r="Q44" s="703" t="n"/>
+      <c r="R44" s="703" t="n"/>
+      <c r="S44" s="703" t="n"/>
+      <c r="T44" s="703" t="n"/>
+      <c r="U44" s="703" t="n"/>
+      <c r="V44" s="703" t="n"/>
+      <c r="W44" s="703" t="n"/>
+      <c r="X44" s="703" t="n"/>
+      <c r="Y44" s="703" t="n"/>
+      <c r="Z44" s="703" t="n"/>
+      <c r="AA44" s="703" t="n"/>
+      <c r="AB44" s="703" t="n"/>
+      <c r="AC44" s="703" t="n"/>
+      <c r="AD44" s="703" t="n"/>
+      <c r="AE44" s="703" t="n"/>
+      <c r="AF44" s="703" t="n"/>
+      <c r="AG44" s="703" t="n"/>
+      <c r="AH44" s="703" t="n"/>
+      <c r="AI44" s="703" t="n"/>
+      <c r="AJ44" s="703" t="n"/>
+      <c r="AK44" s="703" t="n"/>
+      <c r="AL44" s="703" t="n"/>
+      <c r="AM44" s="703" t="n"/>
+      <c r="AN44" s="704" t="n"/>
     </row>
     <row r="45" ht="26" customHeight="1" s="329"/>
     <row r="46" ht="4" customHeight="1" s="329"/>
@@ -8830,351 +9504,331 @@
     <col width="2.33" customWidth="1" style="329" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="329">
-      <c r="A1" s="620" t="n"/>
-      <c r="B1" s="621" t="n"/>
-      <c r="C1" s="621" t="n"/>
-      <c r="D1" s="621" t="n"/>
-      <c r="E1" s="621" t="n"/>
-      <c r="F1" s="621" t="n"/>
-      <c r="G1" s="621" t="n"/>
-      <c r="H1" s="622" t="n"/>
-      <c r="I1" s="623" t="inlineStr">
+    <row r="1" hidden="1" s="329">
+      <c r="A1" s="705" t="n"/>
+      <c r="B1" s="527" t="n"/>
+      <c r="C1" s="527" t="n"/>
+      <c r="D1" s="527" t="n"/>
+      <c r="E1" s="527" t="n"/>
+      <c r="F1" s="527" t="n"/>
+      <c r="G1" s="527" t="n"/>
+      <c r="H1" s="528" t="n"/>
+      <c r="I1" s="706" t="inlineStr">
         <is>
           <t>Outsourced Process Incoming Verification</t>
         </is>
       </c>
-      <c r="J1" s="621" t="n"/>
-      <c r="K1" s="621" t="n"/>
-      <c r="L1" s="621" t="n"/>
-      <c r="M1" s="621" t="n"/>
-      <c r="N1" s="621" t="n"/>
-      <c r="O1" s="621" t="n"/>
-      <c r="P1" s="621" t="n"/>
-      <c r="Q1" s="621" t="n"/>
-      <c r="R1" s="621" t="n"/>
-      <c r="S1" s="621" t="n"/>
-      <c r="T1" s="621" t="n"/>
-      <c r="U1" s="621" t="n"/>
-      <c r="V1" s="621" t="n"/>
-      <c r="W1" s="621" t="n"/>
-      <c r="X1" s="621" t="n"/>
-      <c r="Y1" s="621" t="n"/>
-      <c r="Z1" s="621" t="n"/>
-      <c r="AA1" s="621" t="n"/>
-      <c r="AB1" s="621" t="n"/>
-      <c r="AC1" s="621" t="n"/>
-      <c r="AD1" s="622" t="n"/>
-      <c r="AE1" s="421" t="inlineStr">
+      <c r="J1" s="527" t="n"/>
+      <c r="K1" s="527" t="n"/>
+      <c r="L1" s="527" t="n"/>
+      <c r="M1" s="527" t="n"/>
+      <c r="N1" s="527" t="n"/>
+      <c r="O1" s="527" t="n"/>
+      <c r="P1" s="527" t="n"/>
+      <c r="Q1" s="527" t="n"/>
+      <c r="R1" s="527" t="n"/>
+      <c r="S1" s="527" t="n"/>
+      <c r="T1" s="527" t="n"/>
+      <c r="U1" s="527" t="n"/>
+      <c r="V1" s="527" t="n"/>
+      <c r="W1" s="527" t="n"/>
+      <c r="X1" s="527" t="n"/>
+      <c r="Y1" s="527" t="n"/>
+      <c r="Z1" s="527" t="n"/>
+      <c r="AA1" s="527" t="n"/>
+      <c r="AB1" s="527" t="n"/>
+      <c r="AC1" s="527" t="n"/>
+      <c r="AD1" s="528" t="n"/>
+      <c r="AE1" s="422" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AF1" s="621" t="n"/>
-      <c r="AG1" s="621" t="n"/>
-      <c r="AH1" s="624" t="n"/>
-      <c r="AI1" s="424" t="n"/>
-      <c r="AJ1" s="621" t="n"/>
-      <c r="AK1" s="621" t="n"/>
-      <c r="AL1" s="621" t="n"/>
-      <c r="AM1" s="621" t="n"/>
-      <c r="AN1" s="622" t="n"/>
+      <c r="AF1" s="527" t="n"/>
+      <c r="AG1" s="527" t="n"/>
+      <c r="AH1" s="531" t="n"/>
+      <c r="AI1" s="425" t="n"/>
+      <c r="AJ1" s="527" t="n"/>
+      <c r="AK1" s="527" t="n"/>
+      <c r="AL1" s="527" t="n"/>
+      <c r="AM1" s="527" t="n"/>
+      <c r="AN1" s="528" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1" s="329">
-      <c r="A2" s="625" t="n"/>
-      <c r="B2" s="10" t="n"/>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="10" t="n"/>
-      <c r="H2" s="626" t="n"/>
-      <c r="I2" s="10" t="n"/>
-      <c r="J2" s="10" t="n"/>
-      <c r="K2" s="10" t="n"/>
-      <c r="L2" s="10" t="n"/>
-      <c r="M2" s="10" t="n"/>
-      <c r="N2" s="10" t="n"/>
-      <c r="O2" s="10" t="n"/>
-      <c r="P2" s="10" t="n"/>
-      <c r="Q2" s="10" t="n"/>
-      <c r="R2" s="10" t="n"/>
-      <c r="S2" s="10" t="n"/>
-      <c r="T2" s="10" t="n"/>
-      <c r="U2" s="10" t="n"/>
-      <c r="V2" s="10" t="n"/>
-      <c r="W2" s="10" t="n"/>
-      <c r="X2" s="10" t="n"/>
-      <c r="Y2" s="10" t="n"/>
-      <c r="Z2" s="10" t="n"/>
-      <c r="AA2" s="10" t="n"/>
-      <c r="AB2" s="10" t="n"/>
-      <c r="AC2" s="10" t="n"/>
-      <c r="AD2" s="626" t="n"/>
-      <c r="AE2" s="627" t="inlineStr">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="640" t="n"/>
+      <c r="C2" s="640" t="n"/>
+      <c r="D2" s="640" t="n"/>
+      <c r="E2" s="640" t="n"/>
+      <c r="F2" s="640" t="n"/>
+      <c r="G2" s="640" t="n"/>
+      <c r="H2" s="641" t="n"/>
+      <c r="I2" s="640" t="n"/>
+      <c r="J2" s="640" t="n"/>
+      <c r="K2" s="640" t="n"/>
+      <c r="L2" s="640" t="n"/>
+      <c r="M2" s="640" t="n"/>
+      <c r="N2" s="640" t="n"/>
+      <c r="O2" s="640" t="n"/>
+      <c r="P2" s="640" t="n"/>
+      <c r="Q2" s="640" t="n"/>
+      <c r="R2" s="640" t="n"/>
+      <c r="S2" s="640" t="n"/>
+      <c r="T2" s="640" t="n"/>
+      <c r="U2" s="640" t="n"/>
+      <c r="V2" s="640" t="n"/>
+      <c r="W2" s="640" t="n"/>
+      <c r="X2" s="640" t="n"/>
+      <c r="Y2" s="640" t="n"/>
+      <c r="Z2" s="640" t="n"/>
+      <c r="AA2" s="640" t="n"/>
+      <c r="AB2" s="640" t="n"/>
+      <c r="AC2" s="640" t="n"/>
+      <c r="AD2" s="641" t="n"/>
+      <c r="AE2" s="707" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AF2" s="10" t="n"/>
-      <c r="AG2" s="10" t="n"/>
-      <c r="AH2" s="628" t="n"/>
-      <c r="AI2" s="629" t="n"/>
-      <c r="AJ2" s="10" t="n"/>
-      <c r="AK2" s="10" t="n"/>
-      <c r="AL2" s="10" t="n"/>
-      <c r="AM2" s="10" t="n"/>
-      <c r="AN2" s="626" t="n"/>
+      <c r="AF2" s="643" t="n"/>
+      <c r="AG2" s="643" t="n"/>
+      <c r="AH2" s="644" t="n"/>
+      <c r="AI2" s="708" t="n"/>
+      <c r="AJ2" s="646" t="n"/>
+      <c r="AK2" s="646" t="n"/>
+      <c r="AL2" s="646" t="n"/>
+      <c r="AM2" s="646" t="n"/>
+      <c r="AN2" s="647" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1" s="329">
-      <c r="A3" s="625" t="n"/>
-      <c r="B3" s="10" t="n"/>
-      <c r="C3" s="10" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="10" t="n"/>
-      <c r="G3" s="10" t="n"/>
-      <c r="H3" s="626" t="n"/>
-      <c r="I3" s="10" t="n"/>
-      <c r="J3" s="10" t="n"/>
-      <c r="K3" s="10" t="n"/>
-      <c r="L3" s="10" t="n"/>
-      <c r="M3" s="10" t="n"/>
-      <c r="N3" s="10" t="n"/>
-      <c r="O3" s="10" t="n"/>
-      <c r="P3" s="10" t="n"/>
-      <c r="Q3" s="10" t="n"/>
-      <c r="R3" s="10" t="n"/>
-      <c r="S3" s="10" t="n"/>
-      <c r="T3" s="10" t="n"/>
-      <c r="U3" s="10" t="n"/>
-      <c r="V3" s="10" t="n"/>
-      <c r="W3" s="10" t="n"/>
-      <c r="X3" s="10" t="n"/>
-      <c r="Y3" s="10" t="n"/>
-      <c r="Z3" s="10" t="n"/>
-      <c r="AA3" s="10" t="n"/>
-      <c r="AB3" s="10" t="n"/>
-      <c r="AC3" s="10" t="n"/>
-      <c r="AD3" s="626" t="n"/>
-      <c r="AE3" s="627" t="inlineStr">
+      <c r="A3" s="648" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="649" t="n"/>
+      <c r="I3" s="25" t="n"/>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="25" t="n"/>
+      <c r="L3" s="25" t="n"/>
+      <c r="M3" s="25" t="n"/>
+      <c r="N3" s="25" t="n"/>
+      <c r="O3" s="25" t="n"/>
+      <c r="P3" s="25" t="n"/>
+      <c r="Q3" s="25" t="n"/>
+      <c r="R3" s="25" t="n"/>
+      <c r="S3" s="25" t="n"/>
+      <c r="T3" s="25" t="n"/>
+      <c r="U3" s="25" t="n"/>
+      <c r="V3" s="25" t="n"/>
+      <c r="W3" s="25" t="n"/>
+      <c r="X3" s="25" t="n"/>
+      <c r="Y3" s="25" t="n"/>
+      <c r="Z3" s="25" t="n"/>
+      <c r="AA3" s="25" t="n"/>
+      <c r="AB3" s="25" t="n"/>
+      <c r="AC3" s="25" t="n"/>
+      <c r="AD3" s="649" t="n"/>
+      <c r="AE3" s="709" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AF3" s="10" t="n"/>
-      <c r="AG3" s="10" t="n"/>
-      <c r="AH3" s="628" t="n"/>
-      <c r="AI3" s="629" t="n"/>
-      <c r="AJ3" s="10" t="n"/>
-      <c r="AK3" s="10" t="n"/>
-      <c r="AL3" s="10" t="n"/>
-      <c r="AM3" s="10" t="n"/>
-      <c r="AN3" s="626" t="n"/>
+      <c r="AF3" s="651" t="n"/>
+      <c r="AG3" s="651" t="n"/>
+      <c r="AH3" s="652" t="n"/>
+      <c r="AI3" s="710" t="n"/>
+      <c r="AJ3" s="654" t="n"/>
+      <c r="AK3" s="654" t="n"/>
+      <c r="AL3" s="654" t="n"/>
+      <c r="AM3" s="654" t="n"/>
+      <c r="AN3" s="655" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1" s="329">
-      <c r="A4" s="625" t="n"/>
-      <c r="B4" s="10" t="n"/>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="10" t="n"/>
-      <c r="G4" s="10" t="n"/>
-      <c r="H4" s="626" t="n"/>
-      <c r="I4" s="630" t="inlineStr">
+      <c r="A4" s="648" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="25" t="n"/>
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="649" t="n"/>
+      <c r="I4" s="656" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="J4" s="10" t="n"/>
-      <c r="K4" s="10" t="n"/>
-      <c r="L4" s="10" t="n"/>
-      <c r="M4" s="10" t="n"/>
-      <c r="N4" s="10" t="n"/>
-      <c r="O4" s="10" t="n"/>
-      <c r="P4" s="10" t="n"/>
-      <c r="Q4" s="10" t="n"/>
-      <c r="R4" s="10" t="n"/>
-      <c r="S4" s="10" t="n"/>
-      <c r="T4" s="10" t="n"/>
-      <c r="U4" s="10" t="n"/>
-      <c r="V4" s="10" t="n"/>
-      <c r="W4" s="10" t="n"/>
-      <c r="X4" s="10" t="n"/>
-      <c r="Y4" s="10" t="n"/>
-      <c r="Z4" s="10" t="n"/>
-      <c r="AA4" s="10" t="n"/>
-      <c r="AB4" s="10" t="n"/>
-      <c r="AC4" s="10" t="n"/>
-      <c r="AD4" s="626" t="n"/>
-      <c r="AE4" s="627" t="inlineStr">
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="25" t="n"/>
+      <c r="L4" s="25" t="n"/>
+      <c r="M4" s="25" t="n"/>
+      <c r="N4" s="25" t="n"/>
+      <c r="O4" s="25" t="n"/>
+      <c r="P4" s="25" t="n"/>
+      <c r="Q4" s="25" t="n"/>
+      <c r="R4" s="25" t="n"/>
+      <c r="S4" s="25" t="n"/>
+      <c r="T4" s="25" t="n"/>
+      <c r="U4" s="25" t="n"/>
+      <c r="V4" s="25" t="n"/>
+      <c r="W4" s="25" t="n"/>
+      <c r="X4" s="25" t="n"/>
+      <c r="Y4" s="25" t="n"/>
+      <c r="Z4" s="25" t="n"/>
+      <c r="AA4" s="25" t="n"/>
+      <c r="AB4" s="25" t="n"/>
+      <c r="AC4" s="25" t="n"/>
+      <c r="AD4" s="649" t="n"/>
+      <c r="AE4" s="709" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AF4" s="10" t="n"/>
-      <c r="AG4" s="10" t="n"/>
-      <c r="AH4" s="628" t="n"/>
-      <c r="AI4" s="629" t="n"/>
-      <c r="AJ4" s="10" t="n"/>
-      <c r="AK4" s="10" t="n"/>
-      <c r="AL4" s="10" t="n"/>
-      <c r="AM4" s="10" t="n"/>
-      <c r="AN4" s="626" t="n"/>
+      <c r="AF4" s="651" t="n"/>
+      <c r="AG4" s="651" t="n"/>
+      <c r="AH4" s="652" t="n"/>
+      <c r="AI4" s="710" t="n"/>
+      <c r="AJ4" s="654" t="n"/>
+      <c r="AK4" s="654" t="n"/>
+      <c r="AL4" s="654" t="n"/>
+      <c r="AM4" s="654" t="n"/>
+      <c r="AN4" s="655" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1" s="329">
-      <c r="A5" s="631" t="n"/>
-      <c r="B5" s="632" t="n"/>
-      <c r="C5" s="632" t="n"/>
-      <c r="D5" s="632" t="n"/>
-      <c r="E5" s="632" t="n"/>
-      <c r="F5" s="632" t="n"/>
-      <c r="G5" s="632" t="n"/>
-      <c r="H5" s="633" t="n"/>
-      <c r="I5" s="634" t="inlineStr">
+      <c r="A5" s="648" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="25" t="n"/>
+      <c r="H5" s="649" t="n"/>
+      <c r="I5" s="657" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="J5" s="632" t="n"/>
-      <c r="K5" s="632" t="n"/>
-      <c r="L5" s="632" t="n"/>
-      <c r="M5" s="632" t="n"/>
-      <c r="N5" s="632" t="n"/>
-      <c r="O5" s="632" t="n"/>
-      <c r="P5" s="632" t="n"/>
-      <c r="Q5" s="632" t="n"/>
-      <c r="R5" s="632" t="n"/>
-      <c r="S5" s="632" t="n"/>
-      <c r="T5" s="632" t="n"/>
-      <c r="U5" s="632" t="n"/>
-      <c r="V5" s="632" t="n"/>
-      <c r="W5" s="632" t="n"/>
-      <c r="X5" s="632" t="n"/>
-      <c r="Y5" s="632" t="n"/>
-      <c r="Z5" s="632" t="n"/>
-      <c r="AA5" s="632" t="n"/>
-      <c r="AB5" s="632" t="n"/>
-      <c r="AC5" s="632" t="n"/>
-      <c r="AD5" s="633" t="n"/>
-      <c r="AE5" s="635" t="inlineStr">
+      <c r="J5" s="25" t="n"/>
+      <c r="K5" s="25" t="n"/>
+      <c r="L5" s="25" t="n"/>
+      <c r="M5" s="25" t="n"/>
+      <c r="N5" s="25" t="n"/>
+      <c r="O5" s="25" t="n"/>
+      <c r="P5" s="25" t="n"/>
+      <c r="Q5" s="25" t="n"/>
+      <c r="R5" s="25" t="n"/>
+      <c r="S5" s="25" t="n"/>
+      <c r="T5" s="25" t="n"/>
+      <c r="U5" s="25" t="n"/>
+      <c r="V5" s="25" t="n"/>
+      <c r="W5" s="25" t="n"/>
+      <c r="X5" s="25" t="n"/>
+      <c r="Y5" s="25" t="n"/>
+      <c r="Z5" s="25" t="n"/>
+      <c r="AA5" s="25" t="n"/>
+      <c r="AB5" s="25" t="n"/>
+      <c r="AC5" s="25" t="n"/>
+      <c r="AD5" s="649" t="n"/>
+      <c r="AE5" s="709" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AF5" s="632" t="n"/>
-      <c r="AG5" s="632" t="n"/>
-      <c r="AH5" s="636" t="n"/>
-      <c r="AI5" s="637" t="n"/>
-      <c r="AJ5" s="632" t="n"/>
-      <c r="AK5" s="632" t="n"/>
-      <c r="AL5" s="632" t="n"/>
-      <c r="AM5" s="632" t="n"/>
-      <c r="AN5" s="633" t="n"/>
+      <c r="AF5" s="651" t="n"/>
+      <c r="AG5" s="651" t="n"/>
+      <c r="AH5" s="652" t="n"/>
+      <c r="AI5" s="710" t="n"/>
+      <c r="AJ5" s="654" t="n"/>
+      <c r="AK5" s="654" t="n"/>
+      <c r="AL5" s="654" t="n"/>
+      <c r="AM5" s="654" t="n"/>
+      <c r="AN5" s="655" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1" s="329">
-      <c r="A6" s="638" t="n"/>
-      <c r="B6" s="638" t="n"/>
-      <c r="C6" s="638" t="n"/>
-      <c r="D6" s="638" t="n"/>
-      <c r="E6" s="638" t="n"/>
-      <c r="F6" s="638" t="n"/>
-      <c r="G6" s="638" t="n"/>
-      <c r="H6" s="638" t="n"/>
-      <c r="I6" s="638" t="n"/>
-      <c r="J6" s="638" t="n"/>
-      <c r="K6" s="638" t="n"/>
-      <c r="L6" s="638" t="n"/>
-      <c r="M6" s="638" t="n"/>
-      <c r="N6" s="638" t="n"/>
-      <c r="O6" s="638" t="n"/>
-      <c r="P6" s="638" t="n"/>
-      <c r="Q6" s="638" t="n"/>
-      <c r="R6" s="638" t="n"/>
-      <c r="S6" s="638" t="n"/>
-      <c r="T6" s="638" t="n"/>
-      <c r="U6" s="638" t="n"/>
-      <c r="V6" s="638" t="n"/>
-      <c r="W6" s="638" t="n"/>
-      <c r="X6" s="638" t="n"/>
-      <c r="Y6" s="638" t="n"/>
-      <c r="Z6" s="638" t="n"/>
-      <c r="AA6" s="638" t="n"/>
-      <c r="AB6" s="638" t="n"/>
-      <c r="AC6" s="638" t="n"/>
-      <c r="AD6" s="638" t="n"/>
-      <c r="AE6" s="638" t="n"/>
-      <c r="AF6" s="638" t="n"/>
-      <c r="AG6" s="638" t="n"/>
-      <c r="AH6" s="638" t="n"/>
-      <c r="AI6" s="638" t="n"/>
-      <c r="AJ6" s="638" t="n"/>
-      <c r="AK6" s="638" t="n"/>
-      <c r="AL6" s="638" t="n"/>
-      <c r="AM6" s="638" t="n"/>
-      <c r="AN6" s="638" t="n"/>
+    <row r="6" ht="15" customHeight="1" s="329">
+      <c r="A6" s="711" t="n"/>
+      <c r="B6" s="712" t="n"/>
+      <c r="C6" s="712" t="n"/>
+      <c r="D6" s="712" t="n"/>
+      <c r="E6" s="712" t="n"/>
+      <c r="F6" s="712" t="n"/>
+      <c r="G6" s="712" t="n"/>
+      <c r="H6" s="713" t="n"/>
+      <c r="I6" s="712" t="n"/>
+      <c r="J6" s="712" t="n"/>
+      <c r="K6" s="712" t="n"/>
+      <c r="L6" s="712" t="n"/>
+      <c r="M6" s="712" t="n"/>
+      <c r="N6" s="712" t="n"/>
+      <c r="O6" s="712" t="n"/>
+      <c r="P6" s="712" t="n"/>
+      <c r="Q6" s="712" t="n"/>
+      <c r="R6" s="712" t="n"/>
+      <c r="S6" s="712" t="n"/>
+      <c r="T6" s="712" t="n"/>
+      <c r="U6" s="712" t="n"/>
+      <c r="V6" s="712" t="n"/>
+      <c r="W6" s="712" t="n"/>
+      <c r="X6" s="712" t="n"/>
+      <c r="Y6" s="712" t="n"/>
+      <c r="Z6" s="712" t="n"/>
+      <c r="AA6" s="712" t="n"/>
+      <c r="AB6" s="712" t="n"/>
+      <c r="AC6" s="712" t="n"/>
+      <c r="AD6" s="713" t="n"/>
+      <c r="AE6" s="714" t="n"/>
+      <c r="AF6" s="714" t="n"/>
+      <c r="AG6" s="714" t="n"/>
+      <c r="AH6" s="715" t="n"/>
+      <c r="AI6" s="716" t="n"/>
+      <c r="AJ6" s="716" t="n"/>
+      <c r="AK6" s="716" t="n"/>
+      <c r="AL6" s="716" t="n"/>
+      <c r="AM6" s="716" t="n"/>
+      <c r="AN6" s="717" t="n"/>
     </row>
-    <row r="7">
-      <c r="A7" s="265" t="inlineStr">
-        <is>
-          <t>STATUS</t>
-        </is>
-      </c>
-      <c r="B7" s="265" t="inlineStr">
-        <is>
-          <t>DISPOSITION_GATE</t>
-        </is>
-      </c>
-      <c r="C7" s="265" t="inlineStr">
-        <is>
-          <t>RISK</t>
-        </is>
-      </c>
-      <c r="D7" s="265" t="inlineStr">
-        <is>
-          <t>OWNER_DEPT</t>
-        </is>
-      </c>
-      <c r="E7" s="265" t="inlineStr">
-        <is>
-          <t>ACTION_STATUS</t>
-        </is>
-      </c>
-      <c r="F7" s="639" t="n"/>
-      <c r="G7" s="639" t="n"/>
-      <c r="H7" s="639" t="n"/>
-      <c r="I7" s="639" t="n"/>
-      <c r="J7" s="639" t="n"/>
-      <c r="K7" s="639" t="n"/>
-      <c r="L7" s="639" t="n"/>
-      <c r="M7" s="639" t="n"/>
-      <c r="N7" s="639" t="n"/>
-      <c r="O7" s="639" t="n"/>
-      <c r="P7" s="639" t="n"/>
-      <c r="Q7" s="639" t="n"/>
-      <c r="R7" s="639" t="n"/>
-      <c r="S7" s="639" t="n"/>
-      <c r="T7" s="639" t="n"/>
-      <c r="U7" s="639" t="n"/>
-      <c r="V7" s="639" t="n"/>
-      <c r="W7" s="639" t="n"/>
-      <c r="X7" s="639" t="n"/>
-      <c r="Y7" s="639" t="n"/>
-      <c r="Z7" s="639" t="n"/>
-      <c r="AA7" s="639" t="n"/>
-      <c r="AB7" s="639" t="n"/>
-      <c r="AC7" s="639" t="n"/>
-      <c r="AD7" s="639" t="n"/>
-      <c r="AE7" s="639" t="n"/>
-      <c r="AF7" s="639" t="n"/>
-      <c r="AG7" s="639" t="n"/>
-      <c r="AH7" s="639" t="n"/>
-      <c r="AI7" s="639" t="n"/>
-      <c r="AJ7" s="639" t="n"/>
-      <c r="AK7" s="639" t="n"/>
-      <c r="AL7" s="639" t="n"/>
-      <c r="AM7" s="639" t="n"/>
-      <c r="AN7" s="639" t="n"/>
+    <row r="7" ht="4" customHeight="1" s="329">
+      <c r="A7" s="718" t="n"/>
+      <c r="B7" s="718" t="n"/>
+      <c r="C7" s="718" t="n"/>
+      <c r="D7" s="718" t="n"/>
+      <c r="E7" s="718" t="n"/>
+      <c r="F7" s="719" t="n"/>
+      <c r="G7" s="719" t="n"/>
+      <c r="H7" s="719" t="n"/>
+      <c r="I7" s="719" t="n"/>
+      <c r="J7" s="719" t="n"/>
+      <c r="K7" s="719" t="n"/>
+      <c r="L7" s="719" t="n"/>
+      <c r="M7" s="719" t="n"/>
+      <c r="N7" s="719" t="n"/>
+      <c r="O7" s="719" t="n"/>
+      <c r="P7" s="719" t="n"/>
+      <c r="Q7" s="719" t="n"/>
+      <c r="R7" s="719" t="n"/>
+      <c r="S7" s="719" t="n"/>
+      <c r="T7" s="719" t="n"/>
+      <c r="U7" s="719" t="n"/>
+      <c r="V7" s="719" t="n"/>
+      <c r="W7" s="719" t="n"/>
+      <c r="X7" s="719" t="n"/>
+      <c r="Y7" s="719" t="n"/>
+      <c r="Z7" s="719" t="n"/>
+      <c r="AA7" s="719" t="n"/>
+      <c r="AB7" s="719" t="n"/>
+      <c r="AC7" s="719" t="n"/>
+      <c r="AD7" s="719" t="n"/>
+      <c r="AE7" s="719" t="n"/>
+      <c r="AF7" s="719" t="n"/>
+      <c r="AG7" s="719" t="n"/>
+      <c r="AH7" s="719" t="n"/>
+      <c r="AI7" s="719" t="n"/>
+      <c r="AJ7" s="719" t="n"/>
+      <c r="AK7" s="719" t="n"/>
+      <c r="AL7" s="719" t="n"/>
+      <c r="AM7" s="719" t="n"/>
+      <c r="AN7" s="719" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="266" t="inlineStr">
@@ -9853,6 +10507,7 @@
   </mergeCells>
   <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -9907,7 +10562,7 @@
     <col width="2.33" customWidth="1" style="329" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="329">
+    <row r="1" hidden="1" s="329">
       <c r="A1" s="526" t="n"/>
       <c r="B1" s="527" t="n"/>
       <c r="C1" s="527" t="n"/>
@@ -9958,726 +10613,800 @@
       <c r="AN1" s="528" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1" s="329">
-      <c r="A2" s="533" t="n"/>
-      <c r="H2" s="534" t="n"/>
-      <c r="I2" s="533" t="n"/>
-      <c r="AD2" s="534" t="n"/>
-      <c r="AE2" s="535" t="n"/>
-      <c r="AF2" s="408" t="n"/>
-      <c r="AG2" s="408" t="n"/>
-      <c r="AH2" s="536" t="n"/>
-      <c r="AI2" s="537" t="inlineStr">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="640" t="n"/>
+      <c r="C2" s="640" t="n"/>
+      <c r="D2" s="640" t="n"/>
+      <c r="E2" s="640" t="n"/>
+      <c r="F2" s="640" t="n"/>
+      <c r="G2" s="640" t="n"/>
+      <c r="H2" s="641" t="n"/>
+      <c r="I2" s="640" t="n"/>
+      <c r="J2" s="640" t="n"/>
+      <c r="K2" s="640" t="n"/>
+      <c r="L2" s="640" t="n"/>
+      <c r="M2" s="640" t="n"/>
+      <c r="N2" s="640" t="n"/>
+      <c r="O2" s="640" t="n"/>
+      <c r="P2" s="640" t="n"/>
+      <c r="Q2" s="640" t="n"/>
+      <c r="R2" s="640" t="n"/>
+      <c r="S2" s="640" t="n"/>
+      <c r="T2" s="640" t="n"/>
+      <c r="U2" s="640" t="n"/>
+      <c r="V2" s="640" t="n"/>
+      <c r="W2" s="640" t="n"/>
+      <c r="X2" s="640" t="n"/>
+      <c r="Y2" s="640" t="n"/>
+      <c r="Z2" s="640" t="n"/>
+      <c r="AA2" s="640" t="n"/>
+      <c r="AB2" s="640" t="n"/>
+      <c r="AC2" s="640" t="n"/>
+      <c r="AD2" s="641" t="n"/>
+      <c r="AE2" s="642" t="n"/>
+      <c r="AF2" s="643" t="n"/>
+      <c r="AG2" s="643" t="n"/>
+      <c r="AH2" s="644" t="n"/>
+      <c r="AI2" s="645" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AJ2" s="408" t="n"/>
-      <c r="AK2" s="408" t="n"/>
-      <c r="AL2" s="408" t="n"/>
-      <c r="AM2" s="408" t="n"/>
-      <c r="AN2" s="538" t="n"/>
+      <c r="AJ2" s="646" t="n"/>
+      <c r="AK2" s="646" t="n"/>
+      <c r="AL2" s="646" t="n"/>
+      <c r="AM2" s="646" t="n"/>
+      <c r="AN2" s="647" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1" s="329">
-      <c r="A3" s="533" t="n"/>
-      <c r="H3" s="534" t="n"/>
-      <c r="I3" s="533" t="n"/>
-      <c r="AD3" s="534" t="n"/>
-      <c r="AE3" s="535" t="n"/>
-      <c r="AF3" s="408" t="n"/>
-      <c r="AG3" s="408" t="n"/>
-      <c r="AH3" s="536" t="n"/>
-      <c r="AI3" s="537" t="inlineStr">
+      <c r="A3" s="648" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="649" t="n"/>
+      <c r="I3" s="25" t="n"/>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="25" t="n"/>
+      <c r="L3" s="25" t="n"/>
+      <c r="M3" s="25" t="n"/>
+      <c r="N3" s="25" t="n"/>
+      <c r="O3" s="25" t="n"/>
+      <c r="P3" s="25" t="n"/>
+      <c r="Q3" s="25" t="n"/>
+      <c r="R3" s="25" t="n"/>
+      <c r="S3" s="25" t="n"/>
+      <c r="T3" s="25" t="n"/>
+      <c r="U3" s="25" t="n"/>
+      <c r="V3" s="25" t="n"/>
+      <c r="W3" s="25" t="n"/>
+      <c r="X3" s="25" t="n"/>
+      <c r="Y3" s="25" t="n"/>
+      <c r="Z3" s="25" t="n"/>
+      <c r="AA3" s="25" t="n"/>
+      <c r="AB3" s="25" t="n"/>
+      <c r="AC3" s="25" t="n"/>
+      <c r="AD3" s="649" t="n"/>
+      <c r="AE3" s="650" t="n"/>
+      <c r="AF3" s="651" t="n"/>
+      <c r="AG3" s="651" t="n"/>
+      <c r="AH3" s="652" t="n"/>
+      <c r="AI3" s="653" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AJ3" s="408" t="n"/>
-      <c r="AK3" s="408" t="n"/>
-      <c r="AL3" s="408" t="n"/>
-      <c r="AM3" s="408" t="n"/>
-      <c r="AN3" s="538" t="n"/>
+      <c r="AJ3" s="654" t="n"/>
+      <c r="AK3" s="654" t="n"/>
+      <c r="AL3" s="654" t="n"/>
+      <c r="AM3" s="654" t="n"/>
+      <c r="AN3" s="655" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1" s="329">
-      <c r="A4" s="533" t="n"/>
-      <c r="H4" s="534" t="n"/>
-      <c r="I4" s="539" t="inlineStr">
+      <c r="A4" s="648" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="25" t="n"/>
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="649" t="n"/>
+      <c r="I4" s="656" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AD4" s="534" t="n"/>
-      <c r="AE4" s="535" t="n"/>
-      <c r="AF4" s="408" t="n"/>
-      <c r="AG4" s="408" t="n"/>
-      <c r="AH4" s="536" t="n"/>
-      <c r="AI4" s="537" t="inlineStr">
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="25" t="n"/>
+      <c r="L4" s="25" t="n"/>
+      <c r="M4" s="25" t="n"/>
+      <c r="N4" s="25" t="n"/>
+      <c r="O4" s="25" t="n"/>
+      <c r="P4" s="25" t="n"/>
+      <c r="Q4" s="25" t="n"/>
+      <c r="R4" s="25" t="n"/>
+      <c r="S4" s="25" t="n"/>
+      <c r="T4" s="25" t="n"/>
+      <c r="U4" s="25" t="n"/>
+      <c r="V4" s="25" t="n"/>
+      <c r="W4" s="25" t="n"/>
+      <c r="X4" s="25" t="n"/>
+      <c r="Y4" s="25" t="n"/>
+      <c r="Z4" s="25" t="n"/>
+      <c r="AA4" s="25" t="n"/>
+      <c r="AB4" s="25" t="n"/>
+      <c r="AC4" s="25" t="n"/>
+      <c r="AD4" s="649" t="n"/>
+      <c r="AE4" s="650" t="n"/>
+      <c r="AF4" s="651" t="n"/>
+      <c r="AG4" s="651" t="n"/>
+      <c r="AH4" s="652" t="n"/>
+      <c r="AI4" s="653" t="inlineStr">
         <is>
           <t>Purchasing + QA</t>
         </is>
       </c>
-      <c r="AJ4" s="408" t="n"/>
-      <c r="AK4" s="408" t="n"/>
-      <c r="AL4" s="408" t="n"/>
-      <c r="AM4" s="408" t="n"/>
-      <c r="AN4" s="538" t="n"/>
+      <c r="AJ4" s="654" t="n"/>
+      <c r="AK4" s="654" t="n"/>
+      <c r="AL4" s="654" t="n"/>
+      <c r="AM4" s="654" t="n"/>
+      <c r="AN4" s="655" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1" s="329">
-      <c r="A5" s="540" t="n"/>
-      <c r="B5" s="541" t="n"/>
-      <c r="C5" s="541" t="n"/>
-      <c r="D5" s="541" t="n"/>
-      <c r="E5" s="541" t="n"/>
-      <c r="F5" s="541" t="n"/>
-      <c r="G5" s="541" t="n"/>
-      <c r="H5" s="542" t="n"/>
-      <c r="I5" s="543" t="inlineStr">
+      <c r="A5" s="648" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="25" t="n"/>
+      <c r="H5" s="649" t="n"/>
+      <c r="I5" s="657" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="J5" s="541" t="n"/>
-      <c r="K5" s="541" t="n"/>
-      <c r="L5" s="541" t="n"/>
-      <c r="M5" s="541" t="n"/>
-      <c r="N5" s="541" t="n"/>
-      <c r="O5" s="541" t="n"/>
-      <c r="P5" s="541" t="n"/>
-      <c r="Q5" s="541" t="n"/>
-      <c r="R5" s="541" t="n"/>
-      <c r="S5" s="541" t="n"/>
-      <c r="T5" s="541" t="n"/>
-      <c r="U5" s="541" t="n"/>
-      <c r="V5" s="541" t="n"/>
-      <c r="W5" s="541" t="n"/>
-      <c r="X5" s="541" t="n"/>
-      <c r="Y5" s="541" t="n"/>
-      <c r="Z5" s="541" t="n"/>
-      <c r="AA5" s="541" t="n"/>
-      <c r="AB5" s="541" t="n"/>
-      <c r="AC5" s="541" t="n"/>
-      <c r="AD5" s="542" t="n"/>
-      <c r="AE5" s="544" t="n"/>
-      <c r="AF5" s="545" t="n"/>
-      <c r="AG5" s="545" t="n"/>
-      <c r="AH5" s="546" t="n"/>
-      <c r="AI5" s="547" t="inlineStr">
+      <c r="J5" s="25" t="n"/>
+      <c r="K5" s="25" t="n"/>
+      <c r="L5" s="25" t="n"/>
+      <c r="M5" s="25" t="n"/>
+      <c r="N5" s="25" t="n"/>
+      <c r="O5" s="25" t="n"/>
+      <c r="P5" s="25" t="n"/>
+      <c r="Q5" s="25" t="n"/>
+      <c r="R5" s="25" t="n"/>
+      <c r="S5" s="25" t="n"/>
+      <c r="T5" s="25" t="n"/>
+      <c r="U5" s="25" t="n"/>
+      <c r="V5" s="25" t="n"/>
+      <c r="W5" s="25" t="n"/>
+      <c r="X5" s="25" t="n"/>
+      <c r="Y5" s="25" t="n"/>
+      <c r="Z5" s="25" t="n"/>
+      <c r="AA5" s="25" t="n"/>
+      <c r="AB5" s="25" t="n"/>
+      <c r="AC5" s="25" t="n"/>
+      <c r="AD5" s="649" t="n"/>
+      <c r="AE5" s="650" t="n"/>
+      <c r="AF5" s="651" t="n"/>
+      <c r="AG5" s="651" t="n"/>
+      <c r="AH5" s="652" t="n"/>
+      <c r="AI5" s="653" t="inlineStr">
         <is>
           <t>General Manager</t>
         </is>
       </c>
-      <c r="AJ5" s="545" t="n"/>
-      <c r="AK5" s="545" t="n"/>
-      <c r="AL5" s="545" t="n"/>
-      <c r="AM5" s="545" t="n"/>
-      <c r="AN5" s="548" t="n"/>
+      <c r="AJ5" s="654" t="n"/>
+      <c r="AK5" s="654" t="n"/>
+      <c r="AL5" s="654" t="n"/>
+      <c r="AM5" s="654" t="n"/>
+      <c r="AN5" s="655" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1" s="329">
-      <c r="A6" s="612" t="n"/>
-      <c r="B6" s="612" t="n"/>
-      <c r="C6" s="612" t="n"/>
-      <c r="D6" s="612" t="n"/>
-      <c r="E6" s="612" t="n"/>
-      <c r="F6" s="612" t="n"/>
-      <c r="G6" s="612" t="n"/>
-      <c r="H6" s="612" t="n"/>
-      <c r="I6" s="612" t="n"/>
-      <c r="J6" s="612" t="n"/>
-      <c r="K6" s="612" t="n"/>
-      <c r="L6" s="612" t="n"/>
-      <c r="M6" s="612" t="n"/>
-      <c r="N6" s="612" t="n"/>
-      <c r="O6" s="612" t="n"/>
-      <c r="P6" s="612" t="n"/>
-      <c r="Q6" s="612" t="n"/>
-      <c r="R6" s="612" t="n"/>
-      <c r="S6" s="612" t="n"/>
-      <c r="T6" s="612" t="n"/>
-      <c r="U6" s="612" t="n"/>
-      <c r="V6" s="612" t="n"/>
-      <c r="W6" s="612" t="n"/>
-      <c r="X6" s="612" t="n"/>
-      <c r="Y6" s="612" t="n"/>
-      <c r="Z6" s="612" t="n"/>
-      <c r="AA6" s="612" t="n"/>
-      <c r="AB6" s="612" t="n"/>
-      <c r="AC6" s="612" t="n"/>
-      <c r="AD6" s="612" t="n"/>
-      <c r="AE6" s="612" t="n"/>
-      <c r="AF6" s="612" t="n"/>
-      <c r="AG6" s="612" t="n"/>
-      <c r="AH6" s="612" t="n"/>
-      <c r="AI6" s="612" t="n"/>
-      <c r="AJ6" s="612" t="n"/>
-      <c r="AK6" s="612" t="n"/>
-      <c r="AL6" s="612" t="n"/>
-      <c r="AM6" s="612" t="n"/>
-      <c r="AN6" s="612" t="n"/>
+    <row r="6" ht="15" customHeight="1" s="329">
+      <c r="A6" s="720" t="n"/>
+      <c r="B6" s="721" t="n"/>
+      <c r="C6" s="721" t="n"/>
+      <c r="D6" s="721" t="n"/>
+      <c r="E6" s="721" t="n"/>
+      <c r="F6" s="721" t="n"/>
+      <c r="G6" s="721" t="n"/>
+      <c r="H6" s="722" t="n"/>
+      <c r="I6" s="721" t="n"/>
+      <c r="J6" s="721" t="n"/>
+      <c r="K6" s="721" t="n"/>
+      <c r="L6" s="721" t="n"/>
+      <c r="M6" s="721" t="n"/>
+      <c r="N6" s="721" t="n"/>
+      <c r="O6" s="721" t="n"/>
+      <c r="P6" s="721" t="n"/>
+      <c r="Q6" s="721" t="n"/>
+      <c r="R6" s="721" t="n"/>
+      <c r="S6" s="721" t="n"/>
+      <c r="T6" s="721" t="n"/>
+      <c r="U6" s="721" t="n"/>
+      <c r="V6" s="721" t="n"/>
+      <c r="W6" s="721" t="n"/>
+      <c r="X6" s="721" t="n"/>
+      <c r="Y6" s="721" t="n"/>
+      <c r="Z6" s="721" t="n"/>
+      <c r="AA6" s="721" t="n"/>
+      <c r="AB6" s="721" t="n"/>
+      <c r="AC6" s="721" t="n"/>
+      <c r="AD6" s="722" t="n"/>
+      <c r="AE6" s="723" t="n"/>
+      <c r="AF6" s="723" t="n"/>
+      <c r="AG6" s="723" t="n"/>
+      <c r="AH6" s="724" t="n"/>
+      <c r="AI6" s="725" t="n"/>
+      <c r="AJ6" s="725" t="n"/>
+      <c r="AK6" s="725" t="n"/>
+      <c r="AL6" s="725" t="n"/>
+      <c r="AM6" s="725" t="n"/>
+      <c r="AN6" s="726" t="n"/>
     </row>
-    <row r="7" ht="18" customHeight="1" s="329">
-      <c r="A7" s="549" t="inlineStr">
-        <is>
-          <t>ACTION TRACKER</t>
-        </is>
-      </c>
-      <c r="B7" s="550" t="n"/>
-      <c r="C7" s="550" t="n"/>
-      <c r="D7" s="550" t="n"/>
-      <c r="E7" s="550" t="n"/>
-      <c r="F7" s="550" t="n"/>
-      <c r="G7" s="550" t="n"/>
-      <c r="H7" s="550" t="n"/>
-      <c r="I7" s="550" t="n"/>
-      <c r="J7" s="550" t="n"/>
-      <c r="K7" s="550" t="n"/>
-      <c r="L7" s="550" t="n"/>
-      <c r="M7" s="550" t="n"/>
-      <c r="N7" s="550" t="n"/>
-      <c r="O7" s="550" t="n"/>
-      <c r="P7" s="550" t="n"/>
-      <c r="Q7" s="550" t="n"/>
-      <c r="R7" s="550" t="n"/>
-      <c r="S7" s="550" t="n"/>
-      <c r="T7" s="550" t="n"/>
-      <c r="U7" s="550" t="n"/>
-      <c r="V7" s="550" t="n"/>
-      <c r="W7" s="550" t="n"/>
-      <c r="X7" s="550" t="n"/>
-      <c r="Y7" s="550" t="n"/>
-      <c r="Z7" s="550" t="n"/>
-      <c r="AA7" s="550" t="n"/>
-      <c r="AB7" s="550" t="n"/>
-      <c r="AC7" s="550" t="n"/>
-      <c r="AD7" s="550" t="n"/>
-      <c r="AE7" s="550" t="n"/>
-      <c r="AF7" s="550" t="n"/>
-      <c r="AG7" s="550" t="n"/>
-      <c r="AH7" s="550" t="n"/>
-      <c r="AI7" s="550" t="n"/>
-      <c r="AJ7" s="550" t="n"/>
-      <c r="AK7" s="550" t="n"/>
-      <c r="AL7" s="550" t="n"/>
-      <c r="AM7" s="550" t="n"/>
-      <c r="AN7" s="551" t="n"/>
+    <row r="7" ht="4" customHeight="1" s="329">
+      <c r="A7" s="665" t="n"/>
+      <c r="B7" s="666" t="n"/>
+      <c r="C7" s="666" t="n"/>
+      <c r="D7" s="666" t="n"/>
+      <c r="E7" s="666" t="n"/>
+      <c r="F7" s="666" t="n"/>
+      <c r="G7" s="666" t="n"/>
+      <c r="H7" s="666" t="n"/>
+      <c r="I7" s="666" t="n"/>
+      <c r="J7" s="666" t="n"/>
+      <c r="K7" s="666" t="n"/>
+      <c r="L7" s="666" t="n"/>
+      <c r="M7" s="666" t="n"/>
+      <c r="N7" s="666" t="n"/>
+      <c r="O7" s="666" t="n"/>
+      <c r="P7" s="666" t="n"/>
+      <c r="Q7" s="666" t="n"/>
+      <c r="R7" s="666" t="n"/>
+      <c r="S7" s="666" t="n"/>
+      <c r="T7" s="666" t="n"/>
+      <c r="U7" s="666" t="n"/>
+      <c r="V7" s="666" t="n"/>
+      <c r="W7" s="666" t="n"/>
+      <c r="X7" s="666" t="n"/>
+      <c r="Y7" s="666" t="n"/>
+      <c r="Z7" s="666" t="n"/>
+      <c r="AA7" s="666" t="n"/>
+      <c r="AB7" s="666" t="n"/>
+      <c r="AC7" s="666" t="n"/>
+      <c r="AD7" s="666" t="n"/>
+      <c r="AE7" s="666" t="n"/>
+      <c r="AF7" s="666" t="n"/>
+      <c r="AG7" s="666" t="n"/>
+      <c r="AH7" s="666" t="n"/>
+      <c r="AI7" s="666" t="n"/>
+      <c r="AJ7" s="666" t="n"/>
+      <c r="AK7" s="666" t="n"/>
+      <c r="AL7" s="666" t="n"/>
+      <c r="AM7" s="666" t="n"/>
+      <c r="AN7" s="666" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1" s="329">
-      <c r="A8" s="599" t="inlineStr">
+      <c r="A8" s="727" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B8" s="600" t="n"/>
-      <c r="C8" s="601" t="inlineStr">
+      <c r="B8" s="326" t="n"/>
+      <c r="C8" s="728" t="inlineStr">
         <is>
           <t>Issue / Requirement</t>
         </is>
       </c>
-      <c r="D8" s="550" t="n"/>
-      <c r="E8" s="550" t="n"/>
-      <c r="F8" s="550" t="n"/>
-      <c r="G8" s="550" t="n"/>
-      <c r="H8" s="550" t="n"/>
-      <c r="I8" s="550" t="n"/>
-      <c r="J8" s="550" t="n"/>
-      <c r="K8" s="550" t="n"/>
-      <c r="L8" s="600" t="n"/>
-      <c r="M8" s="601" t="inlineStr">
+      <c r="D8" s="285" t="n"/>
+      <c r="E8" s="285" t="n"/>
+      <c r="F8" s="285" t="n"/>
+      <c r="G8" s="285" t="n"/>
+      <c r="H8" s="285" t="n"/>
+      <c r="I8" s="285" t="n"/>
+      <c r="J8" s="285" t="n"/>
+      <c r="K8" s="285" t="n"/>
+      <c r="L8" s="326" t="n"/>
+      <c r="M8" s="728" t="inlineStr">
         <is>
           <t>Required Action</t>
         </is>
       </c>
-      <c r="N8" s="550" t="n"/>
-      <c r="O8" s="550" t="n"/>
-      <c r="P8" s="550" t="n"/>
-      <c r="Q8" s="550" t="n"/>
-      <c r="R8" s="550" t="n"/>
-      <c r="S8" s="550" t="n"/>
-      <c r="T8" s="550" t="n"/>
-      <c r="U8" s="550" t="n"/>
-      <c r="V8" s="550" t="n"/>
-      <c r="W8" s="550" t="n"/>
-      <c r="X8" s="600" t="n"/>
-      <c r="Y8" s="601" t="inlineStr">
+      <c r="N8" s="285" t="n"/>
+      <c r="O8" s="285" t="n"/>
+      <c r="P8" s="285" t="n"/>
+      <c r="Q8" s="285" t="n"/>
+      <c r="R8" s="285" t="n"/>
+      <c r="S8" s="285" t="n"/>
+      <c r="T8" s="285" t="n"/>
+      <c r="U8" s="285" t="n"/>
+      <c r="V8" s="285" t="n"/>
+      <c r="W8" s="285" t="n"/>
+      <c r="X8" s="326" t="n"/>
+      <c r="Y8" s="728" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="Z8" s="550" t="n"/>
-      <c r="AA8" s="550" t="n"/>
-      <c r="AB8" s="550" t="n"/>
-      <c r="AC8" s="600" t="n"/>
-      <c r="AD8" s="601" t="inlineStr">
+      <c r="Z8" s="285" t="n"/>
+      <c r="AA8" s="285" t="n"/>
+      <c r="AB8" s="285" t="n"/>
+      <c r="AC8" s="326" t="n"/>
+      <c r="AD8" s="728" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="AE8" s="550" t="n"/>
-      <c r="AF8" s="550" t="n"/>
-      <c r="AG8" s="550" t="n"/>
-      <c r="AH8" s="600" t="n"/>
-      <c r="AI8" s="601" t="inlineStr">
+      <c r="AE8" s="285" t="n"/>
+      <c r="AF8" s="285" t="n"/>
+      <c r="AG8" s="285" t="n"/>
+      <c r="AH8" s="326" t="n"/>
+      <c r="AI8" s="728" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="AJ8" s="550" t="n"/>
-      <c r="AK8" s="600" t="n"/>
-      <c r="AL8" s="602" t="inlineStr">
+      <c r="AJ8" s="285" t="n"/>
+      <c r="AK8" s="326" t="n"/>
+      <c r="AL8" s="729" t="inlineStr">
         <is>
           <t>Verified by</t>
         </is>
       </c>
-      <c r="AM8" s="550" t="n"/>
-      <c r="AN8" s="551" t="n"/>
+      <c r="AM8" s="285" t="n"/>
+      <c r="AN8" s="286" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1" s="329">
-      <c r="A9" s="617">
+      <c r="A9" s="730">
         <f>ROW()-ROW($A$9)+1</f>
         <v/>
       </c>
-      <c r="B9" s="410" t="n"/>
-      <c r="C9" s="604" t="n"/>
-      <c r="D9" s="409" t="n"/>
-      <c r="E9" s="409" t="n"/>
-      <c r="F9" s="409" t="n"/>
-      <c r="G9" s="409" t="n"/>
-      <c r="H9" s="409" t="n"/>
-      <c r="I9" s="409" t="n"/>
-      <c r="J9" s="409" t="n"/>
-      <c r="K9" s="409" t="n"/>
-      <c r="L9" s="410" t="n"/>
-      <c r="M9" s="604" t="n"/>
-      <c r="N9" s="409" t="n"/>
-      <c r="O9" s="409" t="n"/>
-      <c r="P9" s="409" t="n"/>
-      <c r="Q9" s="409" t="n"/>
-      <c r="R9" s="409" t="n"/>
-      <c r="S9" s="409" t="n"/>
-      <c r="T9" s="409" t="n"/>
-      <c r="U9" s="409" t="n"/>
-      <c r="V9" s="409" t="n"/>
-      <c r="W9" s="409" t="n"/>
-      <c r="X9" s="410" t="n"/>
-      <c r="Y9" s="604" t="n"/>
-      <c r="Z9" s="409" t="n"/>
-      <c r="AA9" s="409" t="n"/>
-      <c r="AB9" s="409" t="n"/>
-      <c r="AC9" s="410" t="n"/>
-      <c r="AD9" s="604" t="n"/>
-      <c r="AE9" s="409" t="n"/>
-      <c r="AF9" s="409" t="n"/>
-      <c r="AG9" s="409" t="n"/>
-      <c r="AH9" s="410" t="n"/>
-      <c r="AI9" s="604" t="n"/>
-      <c r="AJ9" s="409" t="n"/>
-      <c r="AK9" s="410" t="n"/>
-      <c r="AL9" s="605" t="n"/>
-      <c r="AM9" s="409" t="n"/>
-      <c r="AN9" s="556" t="n"/>
+      <c r="B9" s="746" t="n"/>
+      <c r="C9" s="731" t="n"/>
+      <c r="D9" s="738" t="n"/>
+      <c r="E9" s="738" t="n"/>
+      <c r="F9" s="738" t="n"/>
+      <c r="G9" s="738" t="n"/>
+      <c r="H9" s="738" t="n"/>
+      <c r="I9" s="738" t="n"/>
+      <c r="J9" s="738" t="n"/>
+      <c r="K9" s="738" t="n"/>
+      <c r="L9" s="746" t="n"/>
+      <c r="M9" s="731" t="n"/>
+      <c r="N9" s="738" t="n"/>
+      <c r="O9" s="738" t="n"/>
+      <c r="P9" s="738" t="n"/>
+      <c r="Q9" s="738" t="n"/>
+      <c r="R9" s="738" t="n"/>
+      <c r="S9" s="738" t="n"/>
+      <c r="T9" s="738" t="n"/>
+      <c r="U9" s="738" t="n"/>
+      <c r="V9" s="738" t="n"/>
+      <c r="W9" s="738" t="n"/>
+      <c r="X9" s="746" t="n"/>
+      <c r="Y9" s="731" t="n"/>
+      <c r="Z9" s="738" t="n"/>
+      <c r="AA9" s="738" t="n"/>
+      <c r="AB9" s="738" t="n"/>
+      <c r="AC9" s="746" t="n"/>
+      <c r="AD9" s="731" t="n"/>
+      <c r="AE9" s="738" t="n"/>
+      <c r="AF9" s="738" t="n"/>
+      <c r="AG9" s="738" t="n"/>
+      <c r="AH9" s="746" t="n"/>
+      <c r="AI9" s="731" t="n"/>
+      <c r="AJ9" s="738" t="n"/>
+      <c r="AK9" s="746" t="n"/>
+      <c r="AL9" s="674" t="n"/>
+      <c r="AM9" s="738" t="n"/>
+      <c r="AN9" s="739" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1" s="329">
-      <c r="A10" s="618">
+      <c r="A10" s="732">
         <f>ROW()-ROW($A$9)+1</f>
         <v/>
       </c>
-      <c r="B10" s="410" t="n"/>
-      <c r="C10" s="607" t="n"/>
-      <c r="D10" s="409" t="n"/>
-      <c r="E10" s="409" t="n"/>
-      <c r="F10" s="409" t="n"/>
-      <c r="G10" s="409" t="n"/>
-      <c r="H10" s="409" t="n"/>
-      <c r="I10" s="409" t="n"/>
-      <c r="J10" s="409" t="n"/>
-      <c r="K10" s="409" t="n"/>
-      <c r="L10" s="410" t="n"/>
-      <c r="M10" s="607" t="n"/>
-      <c r="N10" s="409" t="n"/>
-      <c r="O10" s="409" t="n"/>
-      <c r="P10" s="409" t="n"/>
-      <c r="Q10" s="409" t="n"/>
-      <c r="R10" s="409" t="n"/>
-      <c r="S10" s="409" t="n"/>
-      <c r="T10" s="409" t="n"/>
-      <c r="U10" s="409" t="n"/>
-      <c r="V10" s="409" t="n"/>
-      <c r="W10" s="409" t="n"/>
-      <c r="X10" s="410" t="n"/>
-      <c r="Y10" s="607" t="n"/>
-      <c r="Z10" s="409" t="n"/>
-      <c r="AA10" s="409" t="n"/>
-      <c r="AB10" s="409" t="n"/>
-      <c r="AC10" s="410" t="n"/>
-      <c r="AD10" s="607" t="n"/>
-      <c r="AE10" s="409" t="n"/>
-      <c r="AF10" s="409" t="n"/>
-      <c r="AG10" s="409" t="n"/>
-      <c r="AH10" s="410" t="n"/>
-      <c r="AI10" s="607" t="n"/>
-      <c r="AJ10" s="409" t="n"/>
-      <c r="AK10" s="410" t="n"/>
-      <c r="AL10" s="608" t="n"/>
-      <c r="AM10" s="409" t="n"/>
-      <c r="AN10" s="556" t="n"/>
+      <c r="B10" s="746" t="n"/>
+      <c r="C10" s="733" t="n"/>
+      <c r="D10" s="738" t="n"/>
+      <c r="E10" s="738" t="n"/>
+      <c r="F10" s="738" t="n"/>
+      <c r="G10" s="738" t="n"/>
+      <c r="H10" s="738" t="n"/>
+      <c r="I10" s="738" t="n"/>
+      <c r="J10" s="738" t="n"/>
+      <c r="K10" s="738" t="n"/>
+      <c r="L10" s="746" t="n"/>
+      <c r="M10" s="733" t="n"/>
+      <c r="N10" s="738" t="n"/>
+      <c r="O10" s="738" t="n"/>
+      <c r="P10" s="738" t="n"/>
+      <c r="Q10" s="738" t="n"/>
+      <c r="R10" s="738" t="n"/>
+      <c r="S10" s="738" t="n"/>
+      <c r="T10" s="738" t="n"/>
+      <c r="U10" s="738" t="n"/>
+      <c r="V10" s="738" t="n"/>
+      <c r="W10" s="738" t="n"/>
+      <c r="X10" s="746" t="n"/>
+      <c r="Y10" s="733" t="n"/>
+      <c r="Z10" s="738" t="n"/>
+      <c r="AA10" s="738" t="n"/>
+      <c r="AB10" s="738" t="n"/>
+      <c r="AC10" s="746" t="n"/>
+      <c r="AD10" s="733" t="n"/>
+      <c r="AE10" s="738" t="n"/>
+      <c r="AF10" s="738" t="n"/>
+      <c r="AG10" s="738" t="n"/>
+      <c r="AH10" s="746" t="n"/>
+      <c r="AI10" s="733" t="n"/>
+      <c r="AJ10" s="738" t="n"/>
+      <c r="AK10" s="746" t="n"/>
+      <c r="AL10" s="734" t="n"/>
+      <c r="AM10" s="738" t="n"/>
+      <c r="AN10" s="739" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1" s="329">
-      <c r="A11" s="617">
+      <c r="A11" s="730">
         <f>ROW()-ROW($A$9)+1</f>
         <v/>
       </c>
-      <c r="B11" s="410" t="n"/>
-      <c r="C11" s="604" t="n"/>
-      <c r="D11" s="409" t="n"/>
-      <c r="E11" s="409" t="n"/>
-      <c r="F11" s="409" t="n"/>
-      <c r="G11" s="409" t="n"/>
-      <c r="H11" s="409" t="n"/>
-      <c r="I11" s="409" t="n"/>
-      <c r="J11" s="409" t="n"/>
-      <c r="K11" s="409" t="n"/>
-      <c r="L11" s="410" t="n"/>
-      <c r="M11" s="604" t="n"/>
-      <c r="N11" s="409" t="n"/>
-      <c r="O11" s="409" t="n"/>
-      <c r="P11" s="409" t="n"/>
-      <c r="Q11" s="409" t="n"/>
-      <c r="R11" s="409" t="n"/>
-      <c r="S11" s="409" t="n"/>
-      <c r="T11" s="409" t="n"/>
-      <c r="U11" s="409" t="n"/>
-      <c r="V11" s="409" t="n"/>
-      <c r="W11" s="409" t="n"/>
-      <c r="X11" s="410" t="n"/>
-      <c r="Y11" s="604" t="n"/>
-      <c r="Z11" s="409" t="n"/>
-      <c r="AA11" s="409" t="n"/>
-      <c r="AB11" s="409" t="n"/>
-      <c r="AC11" s="410" t="n"/>
-      <c r="AD11" s="604" t="n"/>
-      <c r="AE11" s="409" t="n"/>
-      <c r="AF11" s="409" t="n"/>
-      <c r="AG11" s="409" t="n"/>
-      <c r="AH11" s="410" t="n"/>
-      <c r="AI11" s="604" t="n"/>
-      <c r="AJ11" s="409" t="n"/>
-      <c r="AK11" s="410" t="n"/>
-      <c r="AL11" s="605" t="n"/>
-      <c r="AM11" s="409" t="n"/>
-      <c r="AN11" s="556" t="n"/>
+      <c r="B11" s="746" t="n"/>
+      <c r="C11" s="731" t="n"/>
+      <c r="D11" s="738" t="n"/>
+      <c r="E11" s="738" t="n"/>
+      <c r="F11" s="738" t="n"/>
+      <c r="G11" s="738" t="n"/>
+      <c r="H11" s="738" t="n"/>
+      <c r="I11" s="738" t="n"/>
+      <c r="J11" s="738" t="n"/>
+      <c r="K11" s="738" t="n"/>
+      <c r="L11" s="746" t="n"/>
+      <c r="M11" s="731" t="n"/>
+      <c r="N11" s="738" t="n"/>
+      <c r="O11" s="738" t="n"/>
+      <c r="P11" s="738" t="n"/>
+      <c r="Q11" s="738" t="n"/>
+      <c r="R11" s="738" t="n"/>
+      <c r="S11" s="738" t="n"/>
+      <c r="T11" s="738" t="n"/>
+      <c r="U11" s="738" t="n"/>
+      <c r="V11" s="738" t="n"/>
+      <c r="W11" s="738" t="n"/>
+      <c r="X11" s="746" t="n"/>
+      <c r="Y11" s="731" t="n"/>
+      <c r="Z11" s="738" t="n"/>
+      <c r="AA11" s="738" t="n"/>
+      <c r="AB11" s="738" t="n"/>
+      <c r="AC11" s="746" t="n"/>
+      <c r="AD11" s="731" t="n"/>
+      <c r="AE11" s="738" t="n"/>
+      <c r="AF11" s="738" t="n"/>
+      <c r="AG11" s="738" t="n"/>
+      <c r="AH11" s="746" t="n"/>
+      <c r="AI11" s="731" t="n"/>
+      <c r="AJ11" s="738" t="n"/>
+      <c r="AK11" s="746" t="n"/>
+      <c r="AL11" s="674" t="n"/>
+      <c r="AM11" s="738" t="n"/>
+      <c r="AN11" s="739" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1" s="329">
-      <c r="A12" s="618">
+      <c r="A12" s="732">
         <f>ROW()-ROW($A$9)+1</f>
         <v/>
       </c>
-      <c r="B12" s="410" t="n"/>
-      <c r="C12" s="607" t="n"/>
-      <c r="D12" s="409" t="n"/>
-      <c r="E12" s="409" t="n"/>
-      <c r="F12" s="409" t="n"/>
-      <c r="G12" s="409" t="n"/>
-      <c r="H12" s="409" t="n"/>
-      <c r="I12" s="409" t="n"/>
-      <c r="J12" s="409" t="n"/>
-      <c r="K12" s="409" t="n"/>
-      <c r="L12" s="410" t="n"/>
-      <c r="M12" s="607" t="n"/>
-      <c r="N12" s="409" t="n"/>
-      <c r="O12" s="409" t="n"/>
-      <c r="P12" s="409" t="n"/>
-      <c r="Q12" s="409" t="n"/>
-      <c r="R12" s="409" t="n"/>
-      <c r="S12" s="409" t="n"/>
-      <c r="T12" s="409" t="n"/>
-      <c r="U12" s="409" t="n"/>
-      <c r="V12" s="409" t="n"/>
-      <c r="W12" s="409" t="n"/>
-      <c r="X12" s="410" t="n"/>
-      <c r="Y12" s="607" t="n"/>
-      <c r="Z12" s="409" t="n"/>
-      <c r="AA12" s="409" t="n"/>
-      <c r="AB12" s="409" t="n"/>
-      <c r="AC12" s="410" t="n"/>
-      <c r="AD12" s="607" t="n"/>
-      <c r="AE12" s="409" t="n"/>
-      <c r="AF12" s="409" t="n"/>
-      <c r="AG12" s="409" t="n"/>
-      <c r="AH12" s="410" t="n"/>
-      <c r="AI12" s="607" t="n"/>
-      <c r="AJ12" s="409" t="n"/>
-      <c r="AK12" s="410" t="n"/>
-      <c r="AL12" s="608" t="n"/>
-      <c r="AM12" s="409" t="n"/>
-      <c r="AN12" s="556" t="n"/>
+      <c r="B12" s="746" t="n"/>
+      <c r="C12" s="733" t="n"/>
+      <c r="D12" s="738" t="n"/>
+      <c r="E12" s="738" t="n"/>
+      <c r="F12" s="738" t="n"/>
+      <c r="G12" s="738" t="n"/>
+      <c r="H12" s="738" t="n"/>
+      <c r="I12" s="738" t="n"/>
+      <c r="J12" s="738" t="n"/>
+      <c r="K12" s="738" t="n"/>
+      <c r="L12" s="746" t="n"/>
+      <c r="M12" s="733" t="n"/>
+      <c r="N12" s="738" t="n"/>
+      <c r="O12" s="738" t="n"/>
+      <c r="P12" s="738" t="n"/>
+      <c r="Q12" s="738" t="n"/>
+      <c r="R12" s="738" t="n"/>
+      <c r="S12" s="738" t="n"/>
+      <c r="T12" s="738" t="n"/>
+      <c r="U12" s="738" t="n"/>
+      <c r="V12" s="738" t="n"/>
+      <c r="W12" s="738" t="n"/>
+      <c r="X12" s="746" t="n"/>
+      <c r="Y12" s="733" t="n"/>
+      <c r="Z12" s="738" t="n"/>
+      <c r="AA12" s="738" t="n"/>
+      <c r="AB12" s="738" t="n"/>
+      <c r="AC12" s="746" t="n"/>
+      <c r="AD12" s="733" t="n"/>
+      <c r="AE12" s="738" t="n"/>
+      <c r="AF12" s="738" t="n"/>
+      <c r="AG12" s="738" t="n"/>
+      <c r="AH12" s="746" t="n"/>
+      <c r="AI12" s="733" t="n"/>
+      <c r="AJ12" s="738" t="n"/>
+      <c r="AK12" s="746" t="n"/>
+      <c r="AL12" s="734" t="n"/>
+      <c r="AM12" s="738" t="n"/>
+      <c r="AN12" s="739" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1" s="329">
-      <c r="A13" s="617">
+      <c r="A13" s="730">
         <f>ROW()-ROW($A$9)+1</f>
         <v/>
       </c>
-      <c r="B13" s="410" t="n"/>
-      <c r="C13" s="604" t="n"/>
-      <c r="D13" s="409" t="n"/>
-      <c r="E13" s="409" t="n"/>
-      <c r="F13" s="409" t="n"/>
-      <c r="G13" s="409" t="n"/>
-      <c r="H13" s="409" t="n"/>
-      <c r="I13" s="409" t="n"/>
-      <c r="J13" s="409" t="n"/>
-      <c r="K13" s="409" t="n"/>
-      <c r="L13" s="410" t="n"/>
-      <c r="M13" s="604" t="n"/>
-      <c r="N13" s="409" t="n"/>
-      <c r="O13" s="409" t="n"/>
-      <c r="P13" s="409" t="n"/>
-      <c r="Q13" s="409" t="n"/>
-      <c r="R13" s="409" t="n"/>
-      <c r="S13" s="409" t="n"/>
-      <c r="T13" s="409" t="n"/>
-      <c r="U13" s="409" t="n"/>
-      <c r="V13" s="409" t="n"/>
-      <c r="W13" s="409" t="n"/>
-      <c r="X13" s="410" t="n"/>
-      <c r="Y13" s="604" t="n"/>
-      <c r="Z13" s="409" t="n"/>
-      <c r="AA13" s="409" t="n"/>
-      <c r="AB13" s="409" t="n"/>
-      <c r="AC13" s="410" t="n"/>
-      <c r="AD13" s="604" t="n"/>
-      <c r="AE13" s="409" t="n"/>
-      <c r="AF13" s="409" t="n"/>
-      <c r="AG13" s="409" t="n"/>
-      <c r="AH13" s="410" t="n"/>
-      <c r="AI13" s="604" t="n"/>
-      <c r="AJ13" s="409" t="n"/>
-      <c r="AK13" s="410" t="n"/>
-      <c r="AL13" s="605" t="n"/>
-      <c r="AM13" s="409" t="n"/>
-      <c r="AN13" s="556" t="n"/>
+      <c r="B13" s="746" t="n"/>
+      <c r="C13" s="731" t="n"/>
+      <c r="D13" s="738" t="n"/>
+      <c r="E13" s="738" t="n"/>
+      <c r="F13" s="738" t="n"/>
+      <c r="G13" s="738" t="n"/>
+      <c r="H13" s="738" t="n"/>
+      <c r="I13" s="738" t="n"/>
+      <c r="J13" s="738" t="n"/>
+      <c r="K13" s="738" t="n"/>
+      <c r="L13" s="746" t="n"/>
+      <c r="M13" s="731" t="n"/>
+      <c r="N13" s="738" t="n"/>
+      <c r="O13" s="738" t="n"/>
+      <c r="P13" s="738" t="n"/>
+      <c r="Q13" s="738" t="n"/>
+      <c r="R13" s="738" t="n"/>
+      <c r="S13" s="738" t="n"/>
+      <c r="T13" s="738" t="n"/>
+      <c r="U13" s="738" t="n"/>
+      <c r="V13" s="738" t="n"/>
+      <c r="W13" s="738" t="n"/>
+      <c r="X13" s="746" t="n"/>
+      <c r="Y13" s="731" t="n"/>
+      <c r="Z13" s="738" t="n"/>
+      <c r="AA13" s="738" t="n"/>
+      <c r="AB13" s="738" t="n"/>
+      <c r="AC13" s="746" t="n"/>
+      <c r="AD13" s="731" t="n"/>
+      <c r="AE13" s="738" t="n"/>
+      <c r="AF13" s="738" t="n"/>
+      <c r="AG13" s="738" t="n"/>
+      <c r="AH13" s="746" t="n"/>
+      <c r="AI13" s="731" t="n"/>
+      <c r="AJ13" s="738" t="n"/>
+      <c r="AK13" s="746" t="n"/>
+      <c r="AL13" s="674" t="n"/>
+      <c r="AM13" s="738" t="n"/>
+      <c r="AN13" s="739" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1" s="329">
-      <c r="A14" s="618">
+      <c r="A14" s="732">
         <f>ROW()-ROW($A$9)+1</f>
         <v/>
       </c>
-      <c r="B14" s="410" t="n"/>
-      <c r="C14" s="607" t="n"/>
-      <c r="D14" s="409" t="n"/>
-      <c r="E14" s="409" t="n"/>
-      <c r="F14" s="409" t="n"/>
-      <c r="G14" s="409" t="n"/>
-      <c r="H14" s="409" t="n"/>
-      <c r="I14" s="409" t="n"/>
-      <c r="J14" s="409" t="n"/>
-      <c r="K14" s="409" t="n"/>
-      <c r="L14" s="410" t="n"/>
-      <c r="M14" s="607" t="n"/>
-      <c r="N14" s="409" t="n"/>
-      <c r="O14" s="409" t="n"/>
-      <c r="P14" s="409" t="n"/>
-      <c r="Q14" s="409" t="n"/>
-      <c r="R14" s="409" t="n"/>
-      <c r="S14" s="409" t="n"/>
-      <c r="T14" s="409" t="n"/>
-      <c r="U14" s="409" t="n"/>
-      <c r="V14" s="409" t="n"/>
-      <c r="W14" s="409" t="n"/>
-      <c r="X14" s="410" t="n"/>
-      <c r="Y14" s="607" t="n"/>
-      <c r="Z14" s="409" t="n"/>
-      <c r="AA14" s="409" t="n"/>
-      <c r="AB14" s="409" t="n"/>
-      <c r="AC14" s="410" t="n"/>
-      <c r="AD14" s="607" t="n"/>
-      <c r="AE14" s="409" t="n"/>
-      <c r="AF14" s="409" t="n"/>
-      <c r="AG14" s="409" t="n"/>
-      <c r="AH14" s="410" t="n"/>
-      <c r="AI14" s="607" t="n"/>
-      <c r="AJ14" s="409" t="n"/>
-      <c r="AK14" s="410" t="n"/>
-      <c r="AL14" s="608" t="n"/>
-      <c r="AM14" s="409" t="n"/>
-      <c r="AN14" s="556" t="n"/>
+      <c r="B14" s="746" t="n"/>
+      <c r="C14" s="733" t="n"/>
+      <c r="D14" s="738" t="n"/>
+      <c r="E14" s="738" t="n"/>
+      <c r="F14" s="738" t="n"/>
+      <c r="G14" s="738" t="n"/>
+      <c r="H14" s="738" t="n"/>
+      <c r="I14" s="738" t="n"/>
+      <c r="J14" s="738" t="n"/>
+      <c r="K14" s="738" t="n"/>
+      <c r="L14" s="746" t="n"/>
+      <c r="M14" s="733" t="n"/>
+      <c r="N14" s="738" t="n"/>
+      <c r="O14" s="738" t="n"/>
+      <c r="P14" s="738" t="n"/>
+      <c r="Q14" s="738" t="n"/>
+      <c r="R14" s="738" t="n"/>
+      <c r="S14" s="738" t="n"/>
+      <c r="T14" s="738" t="n"/>
+      <c r="U14" s="738" t="n"/>
+      <c r="V14" s="738" t="n"/>
+      <c r="W14" s="738" t="n"/>
+      <c r="X14" s="746" t="n"/>
+      <c r="Y14" s="733" t="n"/>
+      <c r="Z14" s="738" t="n"/>
+      <c r="AA14" s="738" t="n"/>
+      <c r="AB14" s="738" t="n"/>
+      <c r="AC14" s="746" t="n"/>
+      <c r="AD14" s="733" t="n"/>
+      <c r="AE14" s="738" t="n"/>
+      <c r="AF14" s="738" t="n"/>
+      <c r="AG14" s="738" t="n"/>
+      <c r="AH14" s="746" t="n"/>
+      <c r="AI14" s="733" t="n"/>
+      <c r="AJ14" s="738" t="n"/>
+      <c r="AK14" s="746" t="n"/>
+      <c r="AL14" s="734" t="n"/>
+      <c r="AM14" s="738" t="n"/>
+      <c r="AN14" s="739" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1" s="329">
-      <c r="A15" s="617">
+      <c r="A15" s="730">
         <f>ROW()-ROW($A$9)+1</f>
         <v/>
       </c>
-      <c r="B15" s="410" t="n"/>
-      <c r="C15" s="604" t="n"/>
-      <c r="D15" s="409" t="n"/>
-      <c r="E15" s="409" t="n"/>
-      <c r="F15" s="409" t="n"/>
-      <c r="G15" s="409" t="n"/>
-      <c r="H15" s="409" t="n"/>
-      <c r="I15" s="409" t="n"/>
-      <c r="J15" s="409" t="n"/>
-      <c r="K15" s="409" t="n"/>
-      <c r="L15" s="410" t="n"/>
-      <c r="M15" s="604" t="n"/>
-      <c r="N15" s="409" t="n"/>
-      <c r="O15" s="409" t="n"/>
-      <c r="P15" s="409" t="n"/>
-      <c r="Q15" s="409" t="n"/>
-      <c r="R15" s="409" t="n"/>
-      <c r="S15" s="409" t="n"/>
-      <c r="T15" s="409" t="n"/>
-      <c r="U15" s="409" t="n"/>
-      <c r="V15" s="409" t="n"/>
-      <c r="W15" s="409" t="n"/>
-      <c r="X15" s="410" t="n"/>
-      <c r="Y15" s="604" t="n"/>
-      <c r="Z15" s="409" t="n"/>
-      <c r="AA15" s="409" t="n"/>
-      <c r="AB15" s="409" t="n"/>
-      <c r="AC15" s="410" t="n"/>
-      <c r="AD15" s="604" t="n"/>
-      <c r="AE15" s="409" t="n"/>
-      <c r="AF15" s="409" t="n"/>
-      <c r="AG15" s="409" t="n"/>
-      <c r="AH15" s="410" t="n"/>
-      <c r="AI15" s="604" t="n"/>
-      <c r="AJ15" s="409" t="n"/>
-      <c r="AK15" s="410" t="n"/>
-      <c r="AL15" s="605" t="n"/>
-      <c r="AM15" s="409" t="n"/>
-      <c r="AN15" s="556" t="n"/>
+      <c r="B15" s="746" t="n"/>
+      <c r="C15" s="731" t="n"/>
+      <c r="D15" s="738" t="n"/>
+      <c r="E15" s="738" t="n"/>
+      <c r="F15" s="738" t="n"/>
+      <c r="G15" s="738" t="n"/>
+      <c r="H15" s="738" t="n"/>
+      <c r="I15" s="738" t="n"/>
+      <c r="J15" s="738" t="n"/>
+      <c r="K15" s="738" t="n"/>
+      <c r="L15" s="746" t="n"/>
+      <c r="M15" s="731" t="n"/>
+      <c r="N15" s="738" t="n"/>
+      <c r="O15" s="738" t="n"/>
+      <c r="P15" s="738" t="n"/>
+      <c r="Q15" s="738" t="n"/>
+      <c r="R15" s="738" t="n"/>
+      <c r="S15" s="738" t="n"/>
+      <c r="T15" s="738" t="n"/>
+      <c r="U15" s="738" t="n"/>
+      <c r="V15" s="738" t="n"/>
+      <c r="W15" s="738" t="n"/>
+      <c r="X15" s="746" t="n"/>
+      <c r="Y15" s="731" t="n"/>
+      <c r="Z15" s="738" t="n"/>
+      <c r="AA15" s="738" t="n"/>
+      <c r="AB15" s="738" t="n"/>
+      <c r="AC15" s="746" t="n"/>
+      <c r="AD15" s="731" t="n"/>
+      <c r="AE15" s="738" t="n"/>
+      <c r="AF15" s="738" t="n"/>
+      <c r="AG15" s="738" t="n"/>
+      <c r="AH15" s="746" t="n"/>
+      <c r="AI15" s="731" t="n"/>
+      <c r="AJ15" s="738" t="n"/>
+      <c r="AK15" s="746" t="n"/>
+      <c r="AL15" s="674" t="n"/>
+      <c r="AM15" s="738" t="n"/>
+      <c r="AN15" s="739" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1" s="329">
-      <c r="A16" s="618">
+      <c r="A16" s="732">
         <f>ROW()-ROW($A$9)+1</f>
         <v/>
       </c>
-      <c r="B16" s="410" t="n"/>
-      <c r="C16" s="607" t="n"/>
-      <c r="D16" s="409" t="n"/>
-      <c r="E16" s="409" t="n"/>
-      <c r="F16" s="409" t="n"/>
-      <c r="G16" s="409" t="n"/>
-      <c r="H16" s="409" t="n"/>
-      <c r="I16" s="409" t="n"/>
-      <c r="J16" s="409" t="n"/>
-      <c r="K16" s="409" t="n"/>
-      <c r="L16" s="410" t="n"/>
-      <c r="M16" s="607" t="n"/>
-      <c r="N16" s="409" t="n"/>
-      <c r="O16" s="409" t="n"/>
-      <c r="P16" s="409" t="n"/>
-      <c r="Q16" s="409" t="n"/>
-      <c r="R16" s="409" t="n"/>
-      <c r="S16" s="409" t="n"/>
-      <c r="T16" s="409" t="n"/>
-      <c r="U16" s="409" t="n"/>
-      <c r="V16" s="409" t="n"/>
-      <c r="W16" s="409" t="n"/>
-      <c r="X16" s="410" t="n"/>
-      <c r="Y16" s="607" t="n"/>
-      <c r="Z16" s="409" t="n"/>
-      <c r="AA16" s="409" t="n"/>
-      <c r="AB16" s="409" t="n"/>
-      <c r="AC16" s="410" t="n"/>
-      <c r="AD16" s="607" t="n"/>
-      <c r="AE16" s="409" t="n"/>
-      <c r="AF16" s="409" t="n"/>
-      <c r="AG16" s="409" t="n"/>
-      <c r="AH16" s="410" t="n"/>
-      <c r="AI16" s="607" t="n"/>
-      <c r="AJ16" s="409" t="n"/>
-      <c r="AK16" s="410" t="n"/>
-      <c r="AL16" s="608" t="n"/>
-      <c r="AM16" s="409" t="n"/>
-      <c r="AN16" s="556" t="n"/>
+      <c r="B16" s="746" t="n"/>
+      <c r="C16" s="733" t="n"/>
+      <c r="D16" s="738" t="n"/>
+      <c r="E16" s="738" t="n"/>
+      <c r="F16" s="738" t="n"/>
+      <c r="G16" s="738" t="n"/>
+      <c r="H16" s="738" t="n"/>
+      <c r="I16" s="738" t="n"/>
+      <c r="J16" s="738" t="n"/>
+      <c r="K16" s="738" t="n"/>
+      <c r="L16" s="746" t="n"/>
+      <c r="M16" s="733" t="n"/>
+      <c r="N16" s="738" t="n"/>
+      <c r="O16" s="738" t="n"/>
+      <c r="P16" s="738" t="n"/>
+      <c r="Q16" s="738" t="n"/>
+      <c r="R16" s="738" t="n"/>
+      <c r="S16" s="738" t="n"/>
+      <c r="T16" s="738" t="n"/>
+      <c r="U16" s="738" t="n"/>
+      <c r="V16" s="738" t="n"/>
+      <c r="W16" s="738" t="n"/>
+      <c r="X16" s="746" t="n"/>
+      <c r="Y16" s="733" t="n"/>
+      <c r="Z16" s="738" t="n"/>
+      <c r="AA16" s="738" t="n"/>
+      <c r="AB16" s="738" t="n"/>
+      <c r="AC16" s="746" t="n"/>
+      <c r="AD16" s="733" t="n"/>
+      <c r="AE16" s="738" t="n"/>
+      <c r="AF16" s="738" t="n"/>
+      <c r="AG16" s="738" t="n"/>
+      <c r="AH16" s="746" t="n"/>
+      <c r="AI16" s="733" t="n"/>
+      <c r="AJ16" s="738" t="n"/>
+      <c r="AK16" s="746" t="n"/>
+      <c r="AL16" s="734" t="n"/>
+      <c r="AM16" s="738" t="n"/>
+      <c r="AN16" s="739" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1" s="329">
-      <c r="A17" s="617">
+      <c r="A17" s="730">
         <f>ROW()-ROW($A$9)+1</f>
         <v/>
       </c>
-      <c r="B17" s="410" t="n"/>
-      <c r="C17" s="604" t="n"/>
-      <c r="D17" s="409" t="n"/>
-      <c r="E17" s="409" t="n"/>
-      <c r="F17" s="409" t="n"/>
-      <c r="G17" s="409" t="n"/>
-      <c r="H17" s="409" t="n"/>
-      <c r="I17" s="409" t="n"/>
-      <c r="J17" s="409" t="n"/>
-      <c r="K17" s="409" t="n"/>
-      <c r="L17" s="410" t="n"/>
-      <c r="M17" s="604" t="n"/>
-      <c r="N17" s="409" t="n"/>
-      <c r="O17" s="409" t="n"/>
-      <c r="P17" s="409" t="n"/>
-      <c r="Q17" s="409" t="n"/>
-      <c r="R17" s="409" t="n"/>
-      <c r="S17" s="409" t="n"/>
-      <c r="T17" s="409" t="n"/>
-      <c r="U17" s="409" t="n"/>
-      <c r="V17" s="409" t="n"/>
-      <c r="W17" s="409" t="n"/>
-      <c r="X17" s="410" t="n"/>
-      <c r="Y17" s="604" t="n"/>
-      <c r="Z17" s="409" t="n"/>
-      <c r="AA17" s="409" t="n"/>
-      <c r="AB17" s="409" t="n"/>
-      <c r="AC17" s="410" t="n"/>
-      <c r="AD17" s="604" t="n"/>
-      <c r="AE17" s="409" t="n"/>
-      <c r="AF17" s="409" t="n"/>
-      <c r="AG17" s="409" t="n"/>
-      <c r="AH17" s="410" t="n"/>
-      <c r="AI17" s="604" t="n"/>
-      <c r="AJ17" s="409" t="n"/>
-      <c r="AK17" s="410" t="n"/>
-      <c r="AL17" s="605" t="n"/>
-      <c r="AM17" s="409" t="n"/>
-      <c r="AN17" s="556" t="n"/>
+      <c r="B17" s="746" t="n"/>
+      <c r="C17" s="731" t="n"/>
+      <c r="D17" s="738" t="n"/>
+      <c r="E17" s="738" t="n"/>
+      <c r="F17" s="738" t="n"/>
+      <c r="G17" s="738" t="n"/>
+      <c r="H17" s="738" t="n"/>
+      <c r="I17" s="738" t="n"/>
+      <c r="J17" s="738" t="n"/>
+      <c r="K17" s="738" t="n"/>
+      <c r="L17" s="746" t="n"/>
+      <c r="M17" s="731" t="n"/>
+      <c r="N17" s="738" t="n"/>
+      <c r="O17" s="738" t="n"/>
+      <c r="P17" s="738" t="n"/>
+      <c r="Q17" s="738" t="n"/>
+      <c r="R17" s="738" t="n"/>
+      <c r="S17" s="738" t="n"/>
+      <c r="T17" s="738" t="n"/>
+      <c r="U17" s="738" t="n"/>
+      <c r="V17" s="738" t="n"/>
+      <c r="W17" s="738" t="n"/>
+      <c r="X17" s="746" t="n"/>
+      <c r="Y17" s="731" t="n"/>
+      <c r="Z17" s="738" t="n"/>
+      <c r="AA17" s="738" t="n"/>
+      <c r="AB17" s="738" t="n"/>
+      <c r="AC17" s="746" t="n"/>
+      <c r="AD17" s="731" t="n"/>
+      <c r="AE17" s="738" t="n"/>
+      <c r="AF17" s="738" t="n"/>
+      <c r="AG17" s="738" t="n"/>
+      <c r="AH17" s="746" t="n"/>
+      <c r="AI17" s="731" t="n"/>
+      <c r="AJ17" s="738" t="n"/>
+      <c r="AK17" s="746" t="n"/>
+      <c r="AL17" s="674" t="n"/>
+      <c r="AM17" s="738" t="n"/>
+      <c r="AN17" s="739" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1" s="329">
-      <c r="A18" s="619">
+      <c r="A18" s="735">
         <f>ROW()-ROW($A$9)+1</f>
         <v/>
       </c>
-      <c r="B18" s="546" t="n"/>
-      <c r="C18" s="610" t="n"/>
-      <c r="D18" s="545" t="n"/>
-      <c r="E18" s="545" t="n"/>
-      <c r="F18" s="545" t="n"/>
-      <c r="G18" s="545" t="n"/>
-      <c r="H18" s="545" t="n"/>
-      <c r="I18" s="545" t="n"/>
-      <c r="J18" s="545" t="n"/>
-      <c r="K18" s="545" t="n"/>
-      <c r="L18" s="546" t="n"/>
-      <c r="M18" s="610" t="n"/>
-      <c r="N18" s="545" t="n"/>
-      <c r="O18" s="545" t="n"/>
-      <c r="P18" s="545" t="n"/>
-      <c r="Q18" s="545" t="n"/>
-      <c r="R18" s="545" t="n"/>
-      <c r="S18" s="545" t="n"/>
-      <c r="T18" s="545" t="n"/>
-      <c r="U18" s="545" t="n"/>
-      <c r="V18" s="545" t="n"/>
-      <c r="W18" s="545" t="n"/>
-      <c r="X18" s="546" t="n"/>
-      <c r="Y18" s="610" t="n"/>
-      <c r="Z18" s="545" t="n"/>
-      <c r="AA18" s="545" t="n"/>
-      <c r="AB18" s="545" t="n"/>
-      <c r="AC18" s="546" t="n"/>
-      <c r="AD18" s="610" t="n"/>
-      <c r="AE18" s="545" t="n"/>
-      <c r="AF18" s="545" t="n"/>
-      <c r="AG18" s="545" t="n"/>
-      <c r="AH18" s="546" t="n"/>
-      <c r="AI18" s="610" t="n"/>
-      <c r="AJ18" s="545" t="n"/>
-      <c r="AK18" s="546" t="n"/>
-      <c r="AL18" s="611" t="n"/>
-      <c r="AM18" s="545" t="n"/>
-      <c r="AN18" s="548" t="n"/>
+      <c r="B18" s="747" t="n"/>
+      <c r="C18" s="736" t="n"/>
+      <c r="D18" s="740" t="n"/>
+      <c r="E18" s="740" t="n"/>
+      <c r="F18" s="740" t="n"/>
+      <c r="G18" s="740" t="n"/>
+      <c r="H18" s="740" t="n"/>
+      <c r="I18" s="740" t="n"/>
+      <c r="J18" s="740" t="n"/>
+      <c r="K18" s="740" t="n"/>
+      <c r="L18" s="747" t="n"/>
+      <c r="M18" s="736" t="n"/>
+      <c r="N18" s="740" t="n"/>
+      <c r="O18" s="740" t="n"/>
+      <c r="P18" s="740" t="n"/>
+      <c r="Q18" s="740" t="n"/>
+      <c r="R18" s="740" t="n"/>
+      <c r="S18" s="740" t="n"/>
+      <c r="T18" s="740" t="n"/>
+      <c r="U18" s="740" t="n"/>
+      <c r="V18" s="740" t="n"/>
+      <c r="W18" s="740" t="n"/>
+      <c r="X18" s="747" t="n"/>
+      <c r="Y18" s="736" t="n"/>
+      <c r="Z18" s="740" t="n"/>
+      <c r="AA18" s="740" t="n"/>
+      <c r="AB18" s="740" t="n"/>
+      <c r="AC18" s="747" t="n"/>
+      <c r="AD18" s="736" t="n"/>
+      <c r="AE18" s="740" t="n"/>
+      <c r="AF18" s="740" t="n"/>
+      <c r="AG18" s="740" t="n"/>
+      <c r="AH18" s="747" t="n"/>
+      <c r="AI18" s="736" t="n"/>
+      <c r="AJ18" s="740" t="n"/>
+      <c r="AK18" s="747" t="n"/>
+      <c r="AL18" s="737" t="n"/>
+      <c r="AM18" s="740" t="n"/>
+      <c r="AN18" s="741" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1" s="329">
       <c r="A19" s="616" t="n"/>

--- a/04-Bieu-Mau/04-FRM-400/FRM-411_Outsourced_Process_Incoming_Verification.xlsx
+++ b/04-Bieu-Mau/04-FRM-400/FRM-411_Outsourced_Process_Incoming_Verification.xlsx
@@ -4494,6 +4494,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4524,6 +4527,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4554,6 +4560,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>

--- a/04-Bieu-Mau/04-FRM-400/FRM-411_Outsourced_Process_Incoming_Verification.xlsx
+++ b/04-Bieu-Mau/04-FRM-400/FRM-411_Outsourced_Process_Incoming_Verification.xlsx
@@ -4,10 +4,10 @@
   <workbookPr/>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INCOMING_VERIFY" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ACTIONS" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_IMPORT" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVIDENCE_REF" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="2" state="veryHidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ACTIONS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_IMPORT" sheetId="4" state="veryHidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVIDENCE_REF" sheetId="5" state="veryHidden" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'INCOMING_VERIFY'!$A$1:$AN$44</definedName>

--- a/04-Bieu-Mau/04-FRM-400/FRM-411_Outsourced_Process_Incoming_Verification.xlsx
+++ b/04-Bieu-Mau/04-FRM-400/FRM-411_Outsourced_Process_Incoming_Verification.xlsx
@@ -4,10 +4,11 @@
   <workbookPr/>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INCOMING_VERIFY" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="2" state="veryHidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ACTIONS" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_IMPORT" sheetId="4" state="veryHidden" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVIDENCE_REF" sheetId="5" state="veryHidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ACTIONS" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_IMPORT" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVIDENCE_REF" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REV_HISTORY" sheetId="6" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'INCOMING_VERIFY'!$A$1:$AN$44</definedName>
@@ -4365,6 +4366,41 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="009C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+          <bgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="009C6500"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFEB9C"/>
+          <bgColor rgb="00FFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="00006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+          <bgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -4455,105 +4491,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>161925</colOff>
-      <row>0</row>
-      <rowOff>314325</rowOff>
-    </from>
-    <ext cx="1123950" cy="323850"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>161925</colOff>
-      <row>0</row>
-      <rowOff>314325</rowOff>
-    </from>
-    <ext cx="1123950" cy="323850"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>161925</colOff>
-      <row>0</row>
-      <rowOff>314325</rowOff>
-    </from>
-    <ext cx="1123950" cy="323850"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -4782,7 +4719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AN44"/>
+  <dimension ref="A1:AW44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.329999923706055" customWidth="1" style="329" min="1" max="1"/>
@@ -5308,7 +5245,7 @@
     <row r="13" ht="20" customHeight="1" s="329">
       <c r="A13" s="287" t="inlineStr">
         <is>
-          <t>Method / Acceptance Ref</t>
+          <t>Linked FRM-403 / FRM-701</t>
         </is>
       </c>
       <c r="B13" s="317" t="n"/>
@@ -5332,7 +5269,7 @@
       <c r="T13" s="318" t="n"/>
       <c r="U13" s="289" t="inlineStr">
         <is>
-          <t>Affected Job Ref</t>
+          <t>Ref: SOP-401</t>
         </is>
       </c>
       <c r="V13" s="317" t="n"/>
@@ -5341,7 +5278,11 @@
       <c r="Y13" s="317" t="n"/>
       <c r="Z13" s="317" t="n"/>
       <c r="AA13" s="318" t="n"/>
-      <c r="AB13" s="290" t="n"/>
+      <c r="AB13" s="290" t="inlineStr">
+        <is>
+          <t>Retain: 10 years per QMS schedule</t>
+        </is>
+      </c>
       <c r="AC13" s="317" t="n"/>
       <c r="AD13" s="317" t="n"/>
       <c r="AE13" s="317" t="n"/>
@@ -6683,6 +6624,17 @@
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="H16:T16"/>
   </mergeCells>
+  <conditionalFormatting sqref="AF27:AF32">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"FAIL"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"HOLD"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>"PASS"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="H35:T35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=LISTS!$B$2:$B$5</formula1>
@@ -7202,10 +7154,9 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <tableParts count="2">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
@@ -7446,7 +7397,6 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7686,6 +7636,85 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Rev</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Author</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>V0</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Initial release</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>QMS Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Cross-ref: FRM-403, FRM-701; Parent ref: SOP-401; CF: checklist Result</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>QMS Upgrade</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/04-Bieu-Mau/04-FRM-400/FRM-411_Outsourced_Process_Incoming_Verification.xlsx
+++ b/04-Bieu-Mau/04-FRM-400/FRM-411_Outsourced_Process_Incoming_Verification.xlsx
@@ -4968,6 +4968,86 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>QMS</author>
+  </authors>
+  <commentList>
+    <comment ref="A9" authorId="0" shapeId="0">
+      <text>
+        <t>Số công việc
+Job mà parts trở về từ NCC.</t>
+      </text>
+    </comment>
+    <comment ref="U9" authorId="0" shapeId="0">
+      <text>
+        <t>Nhà cung cấp
+NCC đã gia công.</t>
+      </text>
+    </comment>
+    <comment ref="A10" authorId="0" shapeId="0">
+      <text>
+        <t>Ngày nhận
+Ngày nhận hàng trở về.</t>
+      </text>
+    </comment>
+    <comment ref="U10" authorId="0" shapeId="0">
+      <text>
+        <t>Người nhận
+Tên người tiếp nhận và kiểm tra.</t>
+      </text>
+    </comment>
+    <comment ref="A12" authorId="0" shapeId="0">
+      <text>
+        <t>Kiểm tra nhận hàng
+Kiểm tra parts trở về từ NCC trước khi đưa vào production tiếp.</t>
+      </text>
+    </comment>
+    <comment ref="F14" authorId="0" shapeId="0">
+      <text>
+        <t>Số lượng
+Đếm so với PO. Thiếu hoặc dư đều phải ghi nhận.</t>
+      </text>
+    </comment>
+    <comment ref="F15" authorId="0" shapeId="0">
+      <text>
+        <t>Kiểm tra ngoại quan
+Kiểm tra: hư hỏng vận chuyển, ô nhiễm, xử lý sai.
+Ví dụ: Anodize không đều, passivation có vết.</t>
+      </text>
+    </comment>
+    <comment ref="F16" authorId="0" shapeId="0">
+      <text>
+        <t>Kiểm tra kích thước
+Nếu spec yêu cầu kiểm tra sau xử lý.
+Ví dụ: Hardness test sau heat treatment.</t>
+      </text>
+    </comment>
+    <comment ref="F17" authorId="0" shapeId="0">
+      <text>
+        <t>Chứng nhận
+NCC phải cung cấp cert theo yêu cầu trên PO.
+Lưu cert vào job dossier.</t>
+      </text>
+    </comment>
+    <comment ref="F18" authorId="0" shapeId="0">
+      <text>
+        <t>Nhận dạng / Marking
+Kiểm tra marking trên part đúng theo yêu cầu.</t>
+      </text>
+    </comment>
+    <comment ref="F19" authorId="0" shapeId="0">
+      <text>
+        <t>Quyết định
+ACCEPT → chuyển parts vào production tiếp.
+REJECT → HOLD tag + lập NCR (FRM-651).</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5877,8 +5957,9 @@
       <c r="AN13" s="479" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1" s="264">
-      <c r="A14" s="490" t="n">
-        <v>1</v>
+      <c r="A14" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B14" s="491" t="n"/>
       <c r="C14" s="492" t="inlineStr">
@@ -5910,7 +5991,7 @@
       <c r="U14" s="491" t="n"/>
       <c r="V14" s="495" t="inlineStr">
         <is>
-          <t>Count verified.</t>
+          <t>Count verified — no shortage or excess.</t>
         </is>
       </c>
       <c r="W14" s="493" t="n"/>
@@ -5933,8 +6014,9 @@
       <c r="AN14" s="498" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1" s="264">
-      <c r="A15" s="490" t="n">
-        <v>2</v>
+      <c r="A15" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B15" s="491" t="n"/>
       <c r="C15" s="499" t="inlineStr">
@@ -5946,7 +6028,7 @@
       <c r="E15" s="491" t="n"/>
       <c r="F15" s="500" t="inlineStr">
         <is>
-          <t>Visual inspection acceptable (no damage, contamination).</t>
+          <t>Visual inspection acceptable.</t>
         </is>
       </c>
       <c r="G15" s="493" t="n"/>
@@ -5966,7 +6048,7 @@
       <c r="U15" s="491" t="n"/>
       <c r="V15" s="495" t="inlineStr">
         <is>
-          <t>Surface condition OK.</t>
+          <t>No damage, contamination, wrong treatment.</t>
         </is>
       </c>
       <c r="W15" s="493" t="n"/>
@@ -5989,8 +6071,9 @@
       <c r="AN15" s="498" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1" s="264">
-      <c r="A16" s="490" t="n">
-        <v>3</v>
+      <c r="A16" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B16" s="491" t="n"/>
       <c r="C16" s="499" t="inlineStr">
@@ -6002,7 +6085,7 @@
       <c r="E16" s="491" t="n"/>
       <c r="F16" s="494" t="inlineStr">
         <is>
-          <t>Dimensional check (if required by spec).</t>
+          <t>Dimensional check (if required).</t>
         </is>
       </c>
       <c r="G16" s="493" t="n"/>
@@ -6022,7 +6105,7 @@
       <c r="U16" s="491" t="n"/>
       <c r="V16" s="495" t="inlineStr">
         <is>
-          <t>Key dimensions within tolerance.</t>
+          <t>Key dimensions within spec.</t>
         </is>
       </c>
       <c r="W16" s="493" t="n"/>
@@ -6045,8 +6128,9 @@
       <c r="AN16" s="498" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1" s="264">
-      <c r="A17" s="490" t="n">
-        <v>4</v>
+      <c r="A17" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B17" s="491" t="n"/>
       <c r="C17" s="499" t="inlineStr">
@@ -6058,7 +6142,7 @@
       <c r="E17" s="491" t="n"/>
       <c r="F17" s="500" t="inlineStr">
         <is>
-          <t>Certification / test report received and matches spec.</t>
+          <t>Certification / test report received.</t>
         </is>
       </c>
       <c r="G17" s="493" t="n"/>
@@ -6078,7 +6162,7 @@
       <c r="U17" s="491" t="n"/>
       <c r="V17" s="495" t="inlineStr">
         <is>
-          <t>Cert reviewed and filed.</t>
+          <t>Cert matches spec, filed in dossier.</t>
         </is>
       </c>
       <c r="W17" s="493" t="n"/>
@@ -6101,8 +6185,9 @@
       <c r="AN17" s="498" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1" s="264">
-      <c r="A18" s="490" t="n">
-        <v>5</v>
+      <c r="A18" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B18" s="491" t="n"/>
       <c r="C18" s="499" t="inlineStr">
@@ -6134,7 +6219,7 @@
       <c r="U18" s="491" t="n"/>
       <c r="V18" s="495" t="inlineStr">
         <is>
-          <t>Part marking matches PO.</t>
+          <t>Part marking matches PO requirements.</t>
         </is>
       </c>
       <c r="W18" s="493" t="n"/>
@@ -6157,8 +6242,9 @@
       <c r="AN18" s="498" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1" s="264">
-      <c r="A19" s="490" t="n">
-        <v>6</v>
+      <c r="A19" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B19" s="491" t="n"/>
       <c r="C19" s="499" t="inlineStr">
@@ -6190,7 +6276,7 @@
       <c r="U19" s="491" t="n"/>
       <c r="V19" s="495" t="inlineStr">
         <is>
-          <t>Disposition recorded.</t>
+          <t>ACCEPT → continue production. REJECT → HOLD + NCR.</t>
         </is>
       </c>
       <c r="W19" s="493" t="n"/>
@@ -6213,8 +6299,9 @@
       <c r="AN19" s="498" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1" s="264">
-      <c r="A20" s="490" t="n">
-        <v>7</v>
+      <c r="A20" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B20" s="491" t="n"/>
       <c r="C20" s="501" t="n"/>
@@ -6257,8 +6344,9 @@
       <c r="AN20" s="498" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1" s="264">
-      <c r="A21" s="503" t="n">
-        <v>8</v>
+      <c r="A21" s="503">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B21" s="482" t="n"/>
       <c r="C21" s="504" t="n"/>
@@ -6581,7 +6669,7 @@
     <row r="29" ht="24" customHeight="1" s="264">
       <c r="A29" s="515" t="inlineStr">
         <is>
-          <t>NOTICE — One form per incoming receipt. Ref: SOP-401. Retain: 10 years.</t>
+          <t>NOTICE — Required for every outsource return. If REJECT → HOLD + NCR + notify supplier. Ref: SOP-401. Retain: 10 years.</t>
         </is>
       </c>
       <c r="B29" s="471" t="n"/>
@@ -6734,6 +6822,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
